--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITEMS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEMPLATE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RATES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LV453-B61" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PART LIST REFERENCE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ITEMS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TEMPLATE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="RATES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LISTS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="LV453-B61" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PART LIST REFERENCE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -486,39 +486,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1524000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20557,7 +20524,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -21,15 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="[$Rp]#,##0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -103,6 +104,45 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -324,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -412,6 +452,57 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9962,4384 +10053,6520 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E168"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col width="19" customWidth="1" style="59" min="1" max="1"/>
-    <col width="62" customWidth="1" style="59" min="2" max="2"/>
-    <col width="16" customWidth="1" style="59" min="3" max="3"/>
-    <col width="11" customWidth="1" style="59" min="4" max="4"/>
-    <col width="72" customWidth="1" style="59" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="59" min="6" max="26"/>
-  </cols>
+  <dimension ref="A1:AA1000"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="59">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>RATES: PLV BOM Rate Card 29 Sep 26 (rates_version 2026-09-29), with the 30 Sep changes: finishing split into four rates, 40 × 40 section rule</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="74" t="inlineStr">
         <is>
           <t>Blue = base figure (change it and every cost in this workbook follows). Black = formula. Item tabs look rates up by the code in column A. Only the rate owner edits this tab.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Same rate card as the PLV BOM Costing Workbook v3 (teak, mindi, meranti, plywood). No rates yet for oak / ash, MDF, oak veneer, rattan or metal frames.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="59">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A3" s="75" t="inlineStr">
+        <is>
+          <t>Same rate card as the PLV BOM Costing Workbook v3 (teak, mindi, meranti, plywood). Plywood keeps the Mojo Indah Sep 2026 rates; columns F and G show the Linyi Ocean landed quote of 16 Oct 2026 in USD and IDR for comparison. MDF, marine plywood (rows 170 onward) and DTC rails and hinges (rows 227–229) are priced from USD. Orange rows = rate with both a USD and an IDR price. No rates yet for oak / ash, oak veneer, rattan or metal frames.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="76" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="76" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="E4" s="76" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="F4" s="78" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
+      <c r="G4" s="79" t="inlineStr">
+        <is>
+          <t>Quote USD (Linyi Ocean landed, 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="H4" s="79" t="inlineStr">
+        <is>
+          <t>Quote IDR (USD × FX_USD)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="75" t="inlineStr">
         <is>
           <t>BASE FIGURES: STMV (Standard Maldives) ledger, payroll and vendor lists</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="75" t="inlineStr">
         <is>
           <t>log_teak</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="74" t="inlineStr">
         <is>
           <t>Teak log price, implied</t>
         </is>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="80" t="n">
         <v>6000000</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="74" t="inlineStr">
         <is>
           <t>Ledger 152.3m ÷ 14 m³. Status CONFIRM: replace with nota price</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="75" t="inlineStr">
         <is>
           <t>log_mindi</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="74" t="inlineStr">
         <is>
           <t>Mindi log price, implied</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n">
+      <c r="C7" s="80" t="n">
         <v>3000000</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="74" t="inlineStr">
         <is>
           <t>Ledger 126.1m ÷ 41 m³. Status CONFIRM</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>meranti_sawn</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>Meranti dry sawn timber</t>
         </is>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="80" t="n">
         <v>8500000</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="74" t="inlineStr">
         <is>
           <t>STMV BOM price. Status CONFIRM</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="75" t="inlineStr">
         <is>
           <t>processing</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="74" t="inlineStr">
         <is>
           <t>Wood processing (kiln + sawmill + hauling + sawmill staff), per m³ of log</t>
         </is>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C9" s="80" t="n">
         <v>598978</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="74" t="inlineStr">
         <is>
           <t>Ledger ÷ 75.82 m³ teak + mindi</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="75" t="inlineStr">
         <is>
           <t>carp_pool</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="74" t="inlineStr">
         <is>
           <t>Carpentry payroll pool Mar–Sep 2026</t>
         </is>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="80" t="n">
         <v>270175017</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="74" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="74" t="inlineStr">
         <is>
           <t>Payroll categorised by name, 29 Sep</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="75" t="inlineStr">
         <is>
           <t>carp_deduct</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="74" t="inlineStr">
         <is>
           <t>Less panel cutting / pressing (already in panel rate)</t>
         </is>
       </c>
-      <c r="C11" s="42" t="n">
+      <c r="C11" s="80" t="n">
         <v>0.1</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="74" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="74" t="inlineStr">
         <is>
           <t>Decision 29 Sep</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t>comp_m3</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="74" t="inlineStr">
         <is>
           <t>STMV solid wood in components (teak 12.21 + mindi 13.15 + meranti 7.20)</t>
         </is>
       </c>
-      <c r="C12" s="43" t="n">
+      <c r="C12" s="80" t="n">
         <v>32.56</v>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="74" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="74" t="inlineStr">
         <is>
           <t>REVISI BOM 21 MEI 26</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="75" t="inlineStr">
         <is>
           <t>yield_A</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="74" t="inlineStr">
         <is>
           <t>Yield factor tier A (exposed, straight, ≥ 1000 mm)</t>
         </is>
       </c>
-      <c r="C13" s="43" t="n">
+      <c r="C13" s="80" t="n">
         <v>3.5</v>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="74" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>Judgement, open item</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="75" t="inlineStr">
         <is>
           <t>yield_AC</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="74" t="inlineStr">
         <is>
           <t>Yield factor tier A-CURVED / wide board</t>
         </is>
       </c>
-      <c r="C14" s="43" t="n">
+      <c r="C14" s="80" t="n">
         <v>4.6</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="74" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>STMV mindi</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="75" t="inlineStr">
         <is>
           <t>yield_B</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="74" t="inlineStr">
         <is>
           <t>Yield factor tier B (exposed &lt; 1000 mm, or section ≤ 40 × 40 up to 1500 mm)</t>
         </is>
       </c>
-      <c r="C15" s="43" t="n">
+      <c r="C15" s="80" t="n">
         <v>2.5</v>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="74" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="74" t="inlineStr">
         <is>
           <t>Judgement, open item</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>yield_C</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="74" t="inlineStr">
         <is>
           <t>Yield factor tier C (not exposed)</t>
         </is>
       </c>
-      <c r="C16" s="43" t="n">
+      <c r="C16" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="74" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>STMV teak</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>yield_D</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="74" t="inlineStr">
         <is>
           <t>Yield factor tier D (very small parts)</t>
         </is>
       </c>
-      <c r="C17" s="43" t="n">
+      <c r="C17" s="80" t="n">
         <v>1.5</v>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="74" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>Judgement, open item</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="75" t="inlineStr">
         <is>
           <t>yield_MER</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="74" t="inlineStr">
         <is>
           <t>Meranti sawn-to-component yield</t>
         </is>
       </c>
-      <c r="C18" s="43" t="n">
+      <c r="C18" s="80" t="n">
         <v>1.5</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="74" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="74" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="75" t="inlineStr">
         <is>
           <t>fast_total</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="74" t="inlineStr">
         <is>
           <t>Screws, nails, dowels, wood glue: STMV ledger estimate</t>
         </is>
       </c>
-      <c r="C19" s="41" t="n">
+      <c r="C19" s="80" t="n">
         <v>57000000</v>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="74" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>Status CONFIRM</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="75" t="inlineStr">
         <is>
           <t>paint_total</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="74" t="inlineStr">
         <is>
           <t>Finishing materials: Zhanchen all-in 52,888,326 + thinner 31,249,000</t>
         </is>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="80" t="n">
         <v>84137326</v>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="74" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="74" t="inlineStr">
         <is>
           <t>Ledger, agreed 28 Sep</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="59">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="75" t="inlineStr">
         <is>
           <t>abrasive_total</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="74" t="inlineStr">
         <is>
           <t>Sanding materials: abrasives / sandpaper</t>
         </is>
       </c>
-      <c r="C21" s="41" t="n">
+      <c r="C21" s="80" t="n">
         <v>27713000</v>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="74" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="74" t="inlineStr">
         <is>
           <t>Ledger, agreed 28 Sep</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="59">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="75" t="inlineStr">
         <is>
           <t>fin_pool</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="74" t="inlineStr">
         <is>
           <t>Finishing payroll pool excl. sanding (finishing, PU, gerinda, helper)</t>
         </is>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="80" t="n">
         <v>192243271</v>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="74" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="74" t="inlineStr">
         <is>
           <t>Payroll, 29 Sep</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="59">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="75" t="inlineStr">
         <is>
           <t>sand_pool</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="74" t="inlineStr">
         <is>
           <t>Sanding payroll pool, as paid</t>
         </is>
       </c>
-      <c r="C23" s="41" t="n">
+      <c r="C23" s="80" t="n">
         <v>131550191</v>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="74" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>Payroll, 29 Sep</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="59">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="75" t="inlineStr">
         <is>
           <t>sand_keep</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="74" t="inlineStr">
         <is>
           <t>Sanding share kept (35% removed: bleach re-sanding, packing work)</t>
         </is>
       </c>
-      <c r="C24" s="42" t="n">
+      <c r="C24" s="80" t="n">
         <v>0.65</v>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="74" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="74" t="inlineStr">
         <is>
           <t>Decision 29 Sep</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="59">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="75" t="inlineStr">
         <is>
           <t>fin_m2</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="74" t="inlineStr">
         <is>
           <t>STMV finishing surface</t>
         </is>
       </c>
-      <c r="C25" s="41" t="n">
+      <c r="C25" s="80" t="n">
         <v>2166</v>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="74" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>Items tab estimate</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="59">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="75" t="inlineStr">
         <is>
           <t>oh_pool</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="74" t="inlineStr">
         <is>
           <t>Overhead payroll 213,627,079 + utilities 144,633,030 − PLN upgrade 49,700,000</t>
         </is>
       </c>
-      <c r="C26" s="41" t="n">
+      <c r="C26" s="80" t="n">
         <v>308560109</v>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="74" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>Payroll + reconciliation 23 Sep</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="59">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="75" t="inlineStr">
         <is>
           <t>stmv_direct</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="74" t="inlineStr">
         <is>
           <t>STMV direct cost</t>
         </is>
       </c>
-      <c r="C27" s="41" t="n">
+      <c r="C27" s="80" t="n">
         <v>2374841837</v>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="74" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>Reconciliation 23 Sep, section A</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="59">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="75" t="inlineStr">
         <is>
           <t>glue_tape</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="74" t="inlineStr">
         <is>
           <t>Adino glue + gum tape per m² veneered</t>
         </is>
       </c>
-      <c r="C28" s="41" t="n">
+      <c r="C28" s="80" t="n">
         <v>10424</v>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>3,912,750 + 600,000 ÷ 432.9 m² (122 doors × 2 faces)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="59">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="75" t="inlineStr">
         <is>
           <t>ven_teak</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="74" t="inlineStr">
         <is>
           <t>Teak veneer per running metre (1.35 m wide)</t>
         </is>
       </c>
-      <c r="C29" s="41" t="n">
+      <c r="C29" s="80" t="n">
         <v>110000</v>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="74" t="inlineStr">
         <is>
           <t>IDR/m</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="74" t="inlineStr">
         <is>
           <t>User figure 28 Sep. Status CONFIRM</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="59">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="75" t="inlineStr">
         <is>
           <t>ven_mindi</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="74" t="inlineStr">
         <is>
           <t>Mindi veneer per running metre</t>
         </is>
       </c>
-      <c r="C30" s="41" t="n">
+      <c r="C30" s="80" t="n">
         <v>20000</v>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="74" t="inlineStr">
         <is>
           <t>IDR/m</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>User figure 28 Sep. Status CONFIRM (width ≥ 1.22 m)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="59">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="75" t="inlineStr">
         <is>
           <t>ven_len</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="74" t="inlineStr">
         <is>
           <t>Veneer length used per face</t>
         </is>
       </c>
-      <c r="C31" s="43" t="n">
+      <c r="C31" s="80" t="n">
         <v>2.5</v>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="74" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>One 2.5 m length per face, offcuts not reused</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="59">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="75" t="inlineStr">
         <is>
           <t>ven_labour</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="74" t="inlineStr">
         <is>
           <t>Pressing labour per face (tape, press, sand, cut)</t>
         </is>
       </c>
-      <c r="C32" s="41" t="n">
+      <c r="C32" s="80" t="n">
         <v>57142.86</v>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="74" t="inlineStr">
         <is>
           <t>IDR/face</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>800,000 ÷ 14 sheets. Status CONFIRM</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="59">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="75" t="inlineStr">
         <is>
           <t>RATE CARD: applied by the item tabs</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" s="59">
-      <c r="A34" s="5" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" s="75" t="inlineStr">
         <is>
           <t>LAB_CARP</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="74" t="inlineStr">
         <is>
           <t>Carpentry labour per m³ of component (inside every tier rate)</t>
         </is>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="81">
         <f>$C$10*(1-$C$11)/$C$12</f>
         <v/>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="81" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="E34" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>Pool less 10% ÷ component m³</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="59">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="75" t="inlineStr">
         <is>
           <t>TEAK_A</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="74" t="inlineStr">
         <is>
           <t>Teak tier A</t>
         </is>
       </c>
-      <c r="C35" s="44">
+      <c r="C35" s="81">
         <f>($C$6+$C$9)*$C$13+$C$34</f>
         <v/>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="81">
+        <f>C35*0.9</f>
+        <v/>
+      </c>
+      <c r="E35" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>(log + processing) × yield + labour</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="59">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="75" t="inlineStr">
         <is>
           <t>TEAK_AC</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="74" t="inlineStr">
         <is>
           <t>Teak tier A-CURVED</t>
         </is>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="81">
         <f>($C$6+$C$9)*$C$14+$C$34</f>
         <v/>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="81">
+        <f>C36*0.9</f>
+        <v/>
+      </c>
+      <c r="E36" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="59">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="75" t="inlineStr">
         <is>
           <t>TEAK_B</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="74" t="inlineStr">
         <is>
           <t>Teak tier B</t>
         </is>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="81">
         <f>($C$6+$C$9)*$C$15+$C$34</f>
         <v/>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="81">
+        <f>C37*0.9</f>
+        <v/>
+      </c>
+      <c r="E37" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="59">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="75" t="inlineStr">
         <is>
           <t>TEAK_C</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="74" t="inlineStr">
         <is>
           <t>Teak tier C</t>
         </is>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="81">
         <f>($C$6+$C$9)*$C$16+$C$34</f>
         <v/>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="81">
+        <f>C38*0.9</f>
+        <v/>
+      </c>
+      <c r="E38" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="59">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="75" t="inlineStr">
         <is>
           <t>TEAK_D</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="74" t="inlineStr">
         <is>
           <t>Teak tier D</t>
         </is>
       </c>
-      <c r="C39" s="44">
+      <c r="C39" s="81">
         <f>($C$6+$C$9)*$C$17+$C$34</f>
         <v/>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="81">
+        <f>C39*0.9</f>
+        <v/>
+      </c>
+      <c r="E39" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="59">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="75" t="inlineStr">
         <is>
           <t>MINDI_A</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="74" t="inlineStr">
         <is>
           <t>Mindi tier A</t>
         </is>
       </c>
-      <c r="C40" s="44">
+      <c r="C40" s="81">
         <f>($C$7+$C$9)*$C$13+$C$34</f>
         <v/>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="81">
+        <f>C40*0.9</f>
+        <v/>
+      </c>
+      <c r="E40" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="59">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="75" t="inlineStr">
         <is>
           <t>MINDI_AC</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="74" t="inlineStr">
         <is>
           <t>Mindi tier A-CURVED</t>
         </is>
       </c>
-      <c r="C41" s="44">
+      <c r="C41" s="81">
         <f>($C$7+$C$9)*$C$14+$C$34</f>
         <v/>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="81">
+        <f>C41*0.9</f>
+        <v/>
+      </c>
+      <c r="E41" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="59">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="75" t="inlineStr">
         <is>
           <t>MINDI_B</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="74" t="inlineStr">
         <is>
           <t>Mindi tier B</t>
         </is>
       </c>
-      <c r="C42" s="44">
+      <c r="C42" s="81">
         <f>($C$7+$C$9)*$C$15+$C$34</f>
         <v/>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="81">
+        <f>C42*0.9</f>
+        <v/>
+      </c>
+      <c r="E42" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="59">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="75" t="inlineStr">
         <is>
           <t>MINDI_C</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="74" t="inlineStr">
         <is>
           <t>Mindi tier C</t>
         </is>
       </c>
-      <c r="C43" s="44">
+      <c r="C43" s="81">
         <f>($C$7+$C$9)*$C$16+$C$34</f>
         <v/>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="81">
+        <f>C43*0.9</f>
+        <v/>
+      </c>
+      <c r="E43" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1" s="59">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="75" t="inlineStr">
         <is>
           <t>MINDI_D</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="74" t="inlineStr">
         <is>
           <t>Mindi tier D</t>
         </is>
       </c>
-      <c r="C44" s="44">
+      <c r="C44" s="81">
         <f>($C$7+$C$9)*$C$17+$C$34</f>
         <v/>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="81">
+        <f>C44*0.9</f>
+        <v/>
+      </c>
+      <c r="E44" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="59">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="75" t="inlineStr">
         <is>
           <t>MERANTI</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="74" t="inlineStr">
         <is>
           <t>Meranti, any tier</t>
         </is>
       </c>
-      <c r="C45" s="44">
+      <c r="C45" s="81">
         <f>$C$8*$C$18+$C$34</f>
         <v/>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="81">
+        <f>C45*0.9</f>
+        <v/>
+      </c>
+      <c r="E45" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>Sawn price × yield + labour, no processing</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="59">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="75" t="inlineStr">
         <is>
           <t>FASTENERS</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="74" t="inlineStr">
         <is>
           <t>Screws, nails, dowels, glue per m³ of component</t>
         </is>
       </c>
-      <c r="C46" s="44">
+      <c r="C46" s="81">
         <f>$C$19/$C$12</f>
         <v/>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="81" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E46" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="59">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="75" t="inlineStr">
         <is>
           <t>FIN_MAT</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="74" t="inlineStr">
         <is>
           <t>Finishing materials (Zhanchen + thinner) per m² exposed</t>
         </is>
       </c>
-      <c r="C47" s="44">
+      <c r="C47" s="81">
         <f>$C$20/$C$25</f>
         <v/>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="81" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E47" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="59">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="75" t="inlineStr">
         <is>
           <t>SAND_MAT</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="74" t="inlineStr">
         <is>
           <t>Sanding materials (abrasives) per m² exposed</t>
         </is>
       </c>
-      <c r="C48" s="44">
+      <c r="C48" s="81">
         <f>$C$21/$C$25</f>
         <v/>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="81">
+        <f>C48*0.8</f>
+        <v/>
+      </c>
+      <c r="E48" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1" s="59">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="75" t="inlineStr">
         <is>
           <t>SAND_LAB</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="74" t="inlineStr">
         <is>
           <t>Sanding labour (65% of sanding pool) per m² exposed</t>
         </is>
       </c>
-      <c r="C49" s="44">
+      <c r="C49" s="81">
         <f>$C$23*$C$24/$C$25</f>
         <v/>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="81" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E49" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1" s="59">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="75" t="inlineStr">
         <is>
           <t>FIN_LAB</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="74" t="inlineStr">
         <is>
           <t>Finishing labour (finishing pool) per m² exposed</t>
         </is>
       </c>
-      <c r="C50" s="44">
+      <c r="C50" s="81">
         <f>$C$22/$C$25</f>
         <v/>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="81" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E50" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1" s="59">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="75" t="inlineStr">
         <is>
           <t>CARTON_M2</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="74" t="inlineStr">
         <is>
           <t>Carton + consumables per m² of carton board (6 sides)</t>
         </is>
       </c>
-      <c r="C51" s="41" t="n">
+      <c r="C51" s="80" t="n">
         <v>42000</v>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="80" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E51" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="F51" s="74" t="inlineStr">
         <is>
           <t>Cartons 59.4m + 40% of other packing materials</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1" s="59">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="75" t="inlineStr">
         <is>
           <t>PACK_LAB</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="74" t="inlineStr">
         <is>
           <t>Packing labour per m³ of carton</t>
         </is>
       </c>
-      <c r="C52" s="41" t="n">
+      <c r="C52" s="80" t="n">
         <v>100000</v>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="80" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E52" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="F52" s="74" t="inlineStr">
         <is>
           <t>6 people × 8 days per container. Status CONFIRM</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="59">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="75" t="inlineStr">
         <is>
           <t>GRP_A</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="74" t="inlineStr">
         <is>
           <t>Carton group A price (boxes under CARTON_MIN_M2)</t>
         </is>
       </c>
-      <c r="C53" s="41" t="n">
+      <c r="C53" s="80" t="n">
         <v>24000</v>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="E53" s="74" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="F53" s="74" t="inlineStr">
         <is>
           <t>STMV carton groups, 28 Sep</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1" s="59">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="75" t="inlineStr">
         <is>
           <t>MISC_PCT</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="74" t="inlineStr">
         <is>
           <t>Miscellaneous, × direct cost</t>
         </is>
       </c>
-      <c r="C54" s="42" t="n">
+      <c r="C54" s="80" t="n">
         <v>0.05</v>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="E54" s="74" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="F54" s="74" t="inlineStr">
         <is>
           <t>Decision 29 Sep</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1" s="59">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="75" t="inlineStr">
         <is>
           <t>OH_PCT</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="74" t="inlineStr">
         <is>
           <t>Overhead, × (direct + misc)</t>
         </is>
       </c>
-      <c r="C55" s="45">
+      <c r="C55" s="81">
         <f>$C$26/$C$27</f>
         <v/>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="E55" s="74" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="F55" s="74" t="inlineStr">
         <is>
           <t>Overhead pool ÷ STMV direct cost</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1" s="59">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="75" t="inlineStr">
         <is>
           <t>PLYWOOD per 2440 × 1220 sheet. RAW = board only; MSF / MDF = mindi veneer 1 / 2 faces; TSF / TDF = teak veneer 1 / 2 faces</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" s="59">
-      <c r="A57" s="5" t="inlineStr">
+    </row>
+    <row r="57">
+      <c r="A57" s="75" t="inlineStr">
         <is>
           <t>VEN_TEAK_FACE</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="74" t="inlineStr">
         <is>
           <t>Teak veneer added cost per face (veneer + glue/tape + pressing labour)</t>
         </is>
       </c>
-      <c r="C57" s="44">
+      <c r="C57" s="81">
         <f>$C$29*$C$31+$C$28*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
         <v/>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="E57" s="74" t="inlineStr">
         <is>
           <t>IDR/face</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1" s="59">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="75" t="inlineStr">
         <is>
           <t>VEN_MINDI_FACE</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="74" t="inlineStr">
         <is>
           <t>Mindi veneer added cost per face</t>
         </is>
       </c>
-      <c r="C58" s="44">
+      <c r="C58" s="81">
         <f>$C$30*$C$31+$C$28*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
         <v/>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="81" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E58" s="74" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="75" t="inlineStr">
+        <is>
+          <t>PLY-3-RAW</t>
+        </is>
+      </c>
+      <c r="B59" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 3 mm, raw</t>
+        </is>
+      </c>
+      <c r="C59" s="80">
+        <f>H59</f>
+        <v/>
+      </c>
+      <c r="E59" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F59" s="74" t="inlineStr">
+        <is>
+          <t>Mojo Indah list, Sep 2026</t>
+        </is>
+      </c>
+      <c r="G59" s="82">
+        <f t="array" ref="G59">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H59" s="83">
+        <f>G59*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="75" t="inlineStr">
+        <is>
+          <t>PLY-3-MSF</t>
+        </is>
+      </c>
+      <c r="B60" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 3 mm, mindi single face</t>
+        </is>
+      </c>
+      <c r="C60" s="81">
+        <f>C59+$C$175</f>
+        <v/>
+      </c>
+      <c r="E60" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="75" t="inlineStr">
+        <is>
+          <t>PLY-3-MDF</t>
+        </is>
+      </c>
+      <c r="B61" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 3 mm, mindi double face</t>
+        </is>
+      </c>
+      <c r="C61" s="81">
+        <f>C59+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="E61" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="75" t="inlineStr">
+        <is>
+          <t>PLY-3-TSF</t>
+        </is>
+      </c>
+      <c r="B62" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 3 mm, teak single face</t>
+        </is>
+      </c>
+      <c r="C62" s="81">
+        <f>C59+$C$176</f>
+        <v/>
+      </c>
+      <c r="E62" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="75" t="inlineStr">
+        <is>
+          <t>PLY-3-TDF</t>
+        </is>
+      </c>
+      <c r="B63" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 3 mm, teak double face</t>
+        </is>
+      </c>
+      <c r="C63" s="81">
+        <f>C59+2*$C$176</f>
+        <v/>
+      </c>
+      <c r="E63" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="75" t="inlineStr">
+        <is>
+          <t>PLY-6-RAW</t>
+        </is>
+      </c>
+      <c r="B64" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 6 mm, raw</t>
+        </is>
+      </c>
+      <c r="C64" s="80">
+        <f>H64</f>
+        <v/>
+      </c>
+      <c r="E64" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F64" s="74" t="inlineStr">
+        <is>
+          <t>Mojo Indah list, Sep 2026</t>
+        </is>
+      </c>
+      <c r="G64" s="82">
+        <f t="array" ref="G64">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H64" s="83">
+        <f>G64*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="75" t="inlineStr">
+        <is>
+          <t>PLY-6-MSF</t>
+        </is>
+      </c>
+      <c r="B65" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 6 mm, mindi single face</t>
+        </is>
+      </c>
+      <c r="C65" s="81">
+        <f>C64+$C$175</f>
+        <v/>
+      </c>
+      <c r="E65" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="75" t="inlineStr">
+        <is>
+          <t>PLY-6-MDF</t>
+        </is>
+      </c>
+      <c r="B66" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 6 mm, mindi double face</t>
+        </is>
+      </c>
+      <c r="C66" s="81">
+        <f>C64+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="E66" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="75" t="inlineStr">
+        <is>
+          <t>PLY-6-TSF</t>
+        </is>
+      </c>
+      <c r="B67" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 6 mm, teak single face</t>
+        </is>
+      </c>
+      <c r="C67" s="81">
+        <f>C64+$C$176</f>
+        <v/>
+      </c>
+      <c r="E67" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="75" t="inlineStr">
+        <is>
+          <t>PLY-6-TDF</t>
+        </is>
+      </c>
+      <c r="B68" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 6 mm, teak double face</t>
+        </is>
+      </c>
+      <c r="C68" s="81">
+        <f>C64+2*$C$176</f>
+        <v/>
+      </c>
+      <c r="E68" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="75" t="inlineStr">
+        <is>
+          <t>PLY-9-RAW</t>
+        </is>
+      </c>
+      <c r="B69" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 9 mm, raw</t>
+        </is>
+      </c>
+      <c r="C69" s="80">
+        <f>H69</f>
+        <v/>
+      </c>
+      <c r="E69" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F69" s="74" t="inlineStr">
+        <is>
+          <t>Mojo Indah list, Sep 2026</t>
+        </is>
+      </c>
+      <c r="G69" s="82">
+        <f t="array" ref="G69">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H69" s="83">
+        <f>G69*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="75" t="inlineStr">
+        <is>
+          <t>PLY-9-MSF</t>
+        </is>
+      </c>
+      <c r="B70" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 9 mm, mindi single face</t>
+        </is>
+      </c>
+      <c r="C70" s="81">
+        <f>C69+$C$175</f>
+        <v/>
+      </c>
+      <c r="E70" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="75" t="inlineStr">
+        <is>
+          <t>PLY-9-MDF</t>
+        </is>
+      </c>
+      <c r="B71" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 9 mm, mindi double face</t>
+        </is>
+      </c>
+      <c r="C71" s="81">
+        <f>C69+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="E71" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="75" t="inlineStr">
+        <is>
+          <t>PLY-9-TSF</t>
+        </is>
+      </c>
+      <c r="B72" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 9 mm, teak single face</t>
+        </is>
+      </c>
+      <c r="C72" s="81">
+        <f>C69+$C$176</f>
+        <v/>
+      </c>
+      <c r="E72" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="75" t="inlineStr">
+        <is>
+          <t>PLY-9-TDF</t>
+        </is>
+      </c>
+      <c r="B73" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 9 mm, teak double face</t>
+        </is>
+      </c>
+      <c r="C73" s="81">
+        <f>C69+2*$C$176</f>
+        <v/>
+      </c>
+      <c r="E73" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="75" t="inlineStr">
+        <is>
+          <t>PLY-12-RAW</t>
+        </is>
+      </c>
+      <c r="B74" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 12 mm, raw</t>
+        </is>
+      </c>
+      <c r="C74" s="80">
+        <f>H74</f>
+        <v/>
+      </c>
+      <c r="E74" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F74" s="74" t="inlineStr">
+        <is>
+          <t>Mojo Indah list, Sep 2026</t>
+        </is>
+      </c>
+      <c r="G74" s="82">
+        <f t="array" ref="G74">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H74" s="83">
+        <f>G74*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="75" t="inlineStr">
+        <is>
+          <t>PLY-12-MSF</t>
+        </is>
+      </c>
+      <c r="B75" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 12 mm, mindi single face</t>
+        </is>
+      </c>
+      <c r="C75" s="81">
+        <f>C74+$C$175</f>
+        <v/>
+      </c>
+      <c r="E75" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="75" t="inlineStr">
+        <is>
+          <t>PLY-12-MDF</t>
+        </is>
+      </c>
+      <c r="B76" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 12 mm, mindi double face</t>
+        </is>
+      </c>
+      <c r="C76" s="81">
+        <f>C74+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="E76" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="75" t="inlineStr">
+        <is>
+          <t>PLY-12-TSF</t>
+        </is>
+      </c>
+      <c r="B77" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 12 mm, teak single face</t>
+        </is>
+      </c>
+      <c r="C77" s="81">
+        <f>C74+$C$176</f>
+        <v/>
+      </c>
+      <c r="E77" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="75" t="inlineStr">
+        <is>
+          <t>PLY-12-TDF</t>
+        </is>
+      </c>
+      <c r="B78" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 12 mm, teak double face</t>
+        </is>
+      </c>
+      <c r="C78" s="81">
+        <f>C74+2*$C$176</f>
+        <v/>
+      </c>
+      <c r="E78" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="75" t="inlineStr">
+        <is>
+          <t>PLY-15-RAW</t>
+        </is>
+      </c>
+      <c r="B79" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 15 mm, raw</t>
+        </is>
+      </c>
+      <c r="C79" s="80" t="n">
+        <v>260000</v>
+      </c>
+      <c r="E79" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F79" s="74" t="inlineStr">
+        <is>
+          <t>Mojo Indah list, Sep 2026</t>
+        </is>
+      </c>
+      <c r="G79" s="82">
+        <f t="array" ref="G79">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H79" s="83">
+        <f>G79*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="75" t="inlineStr">
+        <is>
+          <t>PLY-15-MSF</t>
+        </is>
+      </c>
+      <c r="B80" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 15 mm, mindi single face</t>
+        </is>
+      </c>
+      <c r="C80" s="81" t="n">
+        <v>407709.02</v>
+      </c>
+      <c r="E80" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="75" t="inlineStr">
+        <is>
+          <t>PLY-15-MDF</t>
+        </is>
+      </c>
+      <c r="B81" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 15 mm, mindi double face</t>
+        </is>
+      </c>
+      <c r="C81" s="81" t="n">
+        <v>555418.04</v>
+      </c>
+      <c r="E81" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="75" t="inlineStr">
+        <is>
+          <t>PLY-15-TSF</t>
+        </is>
+      </c>
+      <c r="B82" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 15 mm, teak single face</t>
+        </is>
+      </c>
+      <c r="C82" s="81" t="n">
+        <v>601201.02</v>
+      </c>
+      <c r="E82" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="75" t="inlineStr">
+        <is>
+          <t>PLY-15-TDF</t>
+        </is>
+      </c>
+      <c r="B83" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 15 mm, teak double face</t>
+        </is>
+      </c>
+      <c r="C83" s="81" t="n">
+        <v>942402.04</v>
+      </c>
+      <c r="E83" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="75" t="inlineStr">
+        <is>
+          <t>PLY-18-RAW</t>
+        </is>
+      </c>
+      <c r="B84" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 18 mm, raw</t>
+        </is>
+      </c>
+      <c r="C84" s="80">
+        <f>H84</f>
+        <v/>
+      </c>
+      <c r="E84" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F84" s="74" t="inlineStr">
+        <is>
+          <t>Mojo Indah list, Sep 2026</t>
+        </is>
+      </c>
+      <c r="G84" s="82">
+        <f t="array" ref="G84">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H84" s="83">
+        <f>G84*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="75" t="inlineStr">
+        <is>
+          <t>PLY-18-MSF</t>
+        </is>
+      </c>
+      <c r="B85" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 18 mm, mindi single face</t>
+        </is>
+      </c>
+      <c r="C85" s="81">
+        <f>C84+$C$175</f>
+        <v/>
+      </c>
+      <c r="E85" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="75" t="inlineStr">
+        <is>
+          <t>PLY-18-MDF</t>
+        </is>
+      </c>
+      <c r="B86" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 18 mm, mindi double face</t>
+        </is>
+      </c>
+      <c r="C86" s="81">
+        <f>C84+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="E86" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="75" t="inlineStr">
+        <is>
+          <t>PLY-18-TSF</t>
+        </is>
+      </c>
+      <c r="B87" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 18 mm, teak single face</t>
+        </is>
+      </c>
+      <c r="C87" s="81">
+        <f>C84+$C$176</f>
+        <v/>
+      </c>
+      <c r="E87" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="75" t="inlineStr">
+        <is>
+          <t>PLY-18-TDF</t>
+        </is>
+      </c>
+      <c r="B88" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 18 mm, teak double face</t>
+        </is>
+      </c>
+      <c r="C88" s="81">
+        <f>C84+2*$C$176</f>
+        <v/>
+      </c>
+      <c r="E88" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="75" t="inlineStr">
+        <is>
+          <t>PLY-24-RAW</t>
+        </is>
+      </c>
+      <c r="B89" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 24 mm, raw</t>
+        </is>
+      </c>
+      <c r="C89" s="80" t="n">
+        <v>375000</v>
+      </c>
+      <c r="E89" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F89" s="74" t="inlineStr">
+        <is>
+          <t>Extrapolated. Status CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="75" t="inlineStr">
+        <is>
+          <t>PLY-24-MSF</t>
+        </is>
+      </c>
+      <c r="B90" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 24 mm, mindi single face</t>
+        </is>
+      </c>
+      <c r="C90" s="81" t="n">
+        <v>522709.02</v>
+      </c>
+      <c r="E90" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="75" t="inlineStr">
+        <is>
+          <t>PLY-24-MDF</t>
+        </is>
+      </c>
+      <c r="B91" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 24 mm, mindi double face</t>
+        </is>
+      </c>
+      <c r="C91" s="81" t="n">
+        <v>670418.04</v>
+      </c>
+      <c r="E91" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="75" t="inlineStr">
+        <is>
+          <t>PLY-24-TSF</t>
+        </is>
+      </c>
+      <c r="B92" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 24 mm, teak single face</t>
+        </is>
+      </c>
+      <c r="C92" s="81" t="n">
+        <v>716201.02</v>
+      </c>
+      <c r="E92" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="75" t="inlineStr">
+        <is>
+          <t>PLY-24-TDF</t>
+        </is>
+      </c>
+      <c r="B93" s="74" t="inlineStr">
+        <is>
+          <t>Plywood 24 mm, teak double face</t>
+        </is>
+      </c>
+      <c r="C93" s="81" t="n">
+        <v>1057402.04</v>
+      </c>
+      <c r="E93" s="74" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="75" t="inlineStr">
+        <is>
+          <t>NORMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="75" t="inlineStr">
+        <is>
+          <t>CARTON_MIN_M2</t>
+        </is>
+      </c>
+      <c r="B95" s="74" t="inlineStr">
+        <is>
+          <t>Below this carton area use group A price</t>
+        </is>
+      </c>
+      <c r="C95" s="80" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E95" s="74" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="75" t="inlineStr">
+        <is>
+          <t>KD_PACK_FACTOR</t>
+        </is>
+      </c>
+      <c r="B96" s="74" t="inlineStr">
+        <is>
+          <t>Extra consumables factor for flatpack (2+ boxes)</t>
+        </is>
+      </c>
+      <c r="C96" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="74" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F96" s="74" t="inlineStr">
+        <is>
+          <t>0 = off</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="75" t="inlineStr">
+        <is>
+          <t>WASTE_REUSE_MIN</t>
+        </is>
+      </c>
+      <c r="B97" s="74" t="inlineStr">
+        <is>
+          <t>Offcut on the last sheet counts as reusable when waste exceeds this</t>
+        </is>
+      </c>
+      <c r="C97" s="80" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E97" s="74" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F97" s="74" t="inlineStr">
+        <is>
+          <t>Decision 29 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="75" t="inlineStr">
+        <is>
+          <t>OFFCUT_HANDLING</t>
+        </is>
+      </c>
+      <c r="B98" s="74" t="inlineStr">
+        <is>
+          <t>Handling factor on fractional sheets when the offcut is reused</t>
+        </is>
+      </c>
+      <c r="C98" s="80" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E98" s="74" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-CDF</t>
+        </is>
+      </c>
+      <c r="C99" s="85" t="n">
+        <v>718794.04</v>
+      </c>
+      <c r="E99" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F99" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-CSF</t>
+        </is>
+      </c>
+      <c r="C100" s="85" t="n">
+        <v>466897.02</v>
+      </c>
+      <c r="E100" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F100" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-HDF</t>
+        </is>
+      </c>
+      <c r="C101" s="85" t="n">
+        <v>510418.04</v>
+      </c>
+      <c r="E101" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F101" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-HSF</t>
+        </is>
+      </c>
+      <c r="C102" s="85" t="n">
+        <v>362709.02</v>
+      </c>
+      <c r="E102" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F102" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-ODF</t>
+        </is>
+      </c>
+      <c r="C103" s="85" t="n">
+        <v>1016474.04</v>
+      </c>
+      <c r="E103" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F103" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-OSF</t>
+        </is>
+      </c>
+      <c r="C104" s="85" t="n">
+        <v>615737.02</v>
+      </c>
+      <c r="E104" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F104" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-SDF</t>
+        </is>
+      </c>
+      <c r="C105" s="85" t="n">
+        <v>689026.04</v>
+      </c>
+      <c r="E105" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F105" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-SSF</t>
+        </is>
+      </c>
+      <c r="C106" s="85" t="n">
+        <v>452013.02</v>
+      </c>
+      <c r="E106" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F106" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-WDF</t>
+        </is>
+      </c>
+      <c r="C107" s="85" t="n">
+        <v>1105778.04</v>
+      </c>
+      <c r="E107" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F107" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="84" t="inlineStr">
+        <is>
+          <t>PLY-12-WSF</t>
+        </is>
+      </c>
+      <c r="C108" s="85" t="n">
+        <v>660389.02</v>
+      </c>
+      <c r="E108" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F108" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-CDF</t>
+        </is>
+      </c>
+      <c r="C109" s="85" t="n">
+        <v>763794.04</v>
+      </c>
+      <c r="E109" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F109" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-CSF</t>
+        </is>
+      </c>
+      <c r="C110" s="85" t="n">
+        <v>511897.02</v>
+      </c>
+      <c r="E110" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F110" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-HDF</t>
+        </is>
+      </c>
+      <c r="C111" s="85" t="n">
+        <v>555418.04</v>
+      </c>
+      <c r="E111" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F111" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-HSF</t>
+        </is>
+      </c>
+      <c r="C112" s="85" t="n">
+        <v>407709.02</v>
+      </c>
+      <c r="E112" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F112" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-ODF</t>
+        </is>
+      </c>
+      <c r="C113" s="85" t="n">
+        <v>1061474.04</v>
+      </c>
+      <c r="E113" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F113" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-OSF</t>
+        </is>
+      </c>
+      <c r="C114" s="85" t="n">
+        <v>660737.02</v>
+      </c>
+      <c r="E114" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F114" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-SDF</t>
+        </is>
+      </c>
+      <c r="C115" s="85" t="n">
+        <v>734026.04</v>
+      </c>
+      <c r="E115" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F115" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-SSF</t>
+        </is>
+      </c>
+      <c r="C116" s="85" t="n">
+        <v>497013.02</v>
+      </c>
+      <c r="E116" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F116" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-WDF</t>
+        </is>
+      </c>
+      <c r="C117" s="85" t="n">
+        <v>1150778.04</v>
+      </c>
+      <c r="E117" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F117" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-WSF</t>
+        </is>
+      </c>
+      <c r="C118" s="85" t="n">
+        <v>705389.02</v>
+      </c>
+      <c r="E118" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F118" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-CDF</t>
+        </is>
+      </c>
+      <c r="C119" s="85" t="n">
+        <v>798794.04</v>
+      </c>
+      <c r="E119" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F119" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-CSF</t>
+        </is>
+      </c>
+      <c r="C120" s="85" t="n">
+        <v>546897.02</v>
+      </c>
+      <c r="E120" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F120" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-HDF</t>
+        </is>
+      </c>
+      <c r="C121" s="85" t="n">
+        <v>590418.04</v>
+      </c>
+      <c r="E121" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F121" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-HSF</t>
+        </is>
+      </c>
+      <c r="C122" s="85" t="n">
+        <v>442709.02</v>
+      </c>
+      <c r="E122" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F122" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-ODF</t>
+        </is>
+      </c>
+      <c r="C123" s="85" t="n">
+        <v>1096474.04</v>
+      </c>
+      <c r="E123" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F123" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-OSF</t>
+        </is>
+      </c>
+      <c r="C124" s="85" t="n">
+        <v>695737.02</v>
+      </c>
+      <c r="E124" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F124" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-SDF</t>
+        </is>
+      </c>
+      <c r="C125" s="85" t="n">
+        <v>769026.04</v>
+      </c>
+      <c r="E125" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F125" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-SSF</t>
+        </is>
+      </c>
+      <c r="C126" s="85" t="n">
+        <v>532013.02</v>
+      </c>
+      <c r="E126" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F126" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-WDF</t>
+        </is>
+      </c>
+      <c r="C127" s="85" t="n">
+        <v>1185778.04</v>
+      </c>
+      <c r="E127" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F127" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-WSF</t>
+        </is>
+      </c>
+      <c r="C128" s="85" t="n">
+        <v>740389.02</v>
+      </c>
+      <c r="E128" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F128" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-CDF</t>
+        </is>
+      </c>
+      <c r="C129" s="85" t="n">
+        <v>878794.04</v>
+      </c>
+      <c r="E129" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F129" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-CSF</t>
+        </is>
+      </c>
+      <c r="C130" s="85" t="n">
+        <v>626897.02</v>
+      </c>
+      <c r="E130" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F130" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-HDF</t>
+        </is>
+      </c>
+      <c r="C131" s="85" t="n">
+        <v>670418.04</v>
+      </c>
+      <c r="E131" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F131" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-HSF</t>
+        </is>
+      </c>
+      <c r="C132" s="85" t="n">
+        <v>522709.02</v>
+      </c>
+      <c r="E132" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F132" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-ODF</t>
+        </is>
+      </c>
+      <c r="C133" s="85" t="n">
+        <v>1176474.04</v>
+      </c>
+      <c r="E133" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F133" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-OSF</t>
+        </is>
+      </c>
+      <c r="C134" s="85" t="n">
+        <v>775737.02</v>
+      </c>
+      <c r="E134" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F134" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-SDF</t>
+        </is>
+      </c>
+      <c r="C135" s="85" t="n">
+        <v>849026.04</v>
+      </c>
+      <c r="E135" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F135" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-SSF</t>
+        </is>
+      </c>
+      <c r="C136" s="85" t="n">
+        <v>612013.02</v>
+      </c>
+      <c r="E136" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F136" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-WDF</t>
+        </is>
+      </c>
+      <c r="C137" s="85" t="n">
+        <v>1265778.04</v>
+      </c>
+      <c r="E137" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F137" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="84" t="inlineStr">
+        <is>
+          <t>PLY-24-WSF</t>
+        </is>
+      </c>
+      <c r="C138" s="85" t="n">
+        <v>820389.02</v>
+      </c>
+      <c r="E138" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F138" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-CDF</t>
+        </is>
+      </c>
+      <c r="C139" s="85" t="n">
+        <v>581294.04</v>
+      </c>
+      <c r="E139" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F139" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-CSF</t>
+        </is>
+      </c>
+      <c r="C140" s="85" t="n">
+        <v>329397.02</v>
+      </c>
+      <c r="E140" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F140" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-HDF</t>
+        </is>
+      </c>
+      <c r="C141" s="85" t="n">
+        <v>372918.04</v>
+      </c>
+      <c r="E141" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F141" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-HSF</t>
+        </is>
+      </c>
+      <c r="C142" s="85" t="n">
+        <v>225209.02</v>
+      </c>
+      <c r="E142" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F142" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-ODF</t>
+        </is>
+      </c>
+      <c r="C143" s="85" t="n">
+        <v>878974.04</v>
+      </c>
+      <c r="E143" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F143" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-OSF</t>
+        </is>
+      </c>
+      <c r="C144" s="85" t="n">
+        <v>478237.02</v>
+      </c>
+      <c r="E144" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F144" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-SDF</t>
+        </is>
+      </c>
+      <c r="C145" s="85" t="n">
+        <v>551526.04</v>
+      </c>
+      <c r="E145" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F145" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-SSF</t>
+        </is>
+      </c>
+      <c r="C146" s="85" t="n">
+        <v>314513.02</v>
+      </c>
+      <c r="E146" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F146" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-WDF</t>
+        </is>
+      </c>
+      <c r="C147" s="85" t="n">
+        <v>968278.04</v>
+      </c>
+      <c r="E147" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F147" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="84" t="inlineStr">
+        <is>
+          <t>PLY-3-WSF</t>
+        </is>
+      </c>
+      <c r="C148" s="85" t="n">
+        <v>522889.02</v>
+      </c>
+      <c r="E148" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F148" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-CDF</t>
+        </is>
+      </c>
+      <c r="C149" s="85" t="n">
+        <v>618794.04</v>
+      </c>
+      <c r="E149" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F149" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-CSF</t>
+        </is>
+      </c>
+      <c r="C150" s="85" t="n">
+        <v>366897.02</v>
+      </c>
+      <c r="E150" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F150" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-HDF</t>
+        </is>
+      </c>
+      <c r="C151" s="85" t="n">
+        <v>410418.04</v>
+      </c>
+      <c r="E151" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F151" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-HSF</t>
+        </is>
+      </c>
+      <c r="C152" s="85" t="n">
+        <v>262709.02</v>
+      </c>
+      <c r="E152" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F152" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-ODF</t>
+        </is>
+      </c>
+      <c r="C153" s="85" t="n">
+        <v>916474.04</v>
+      </c>
+      <c r="E153" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F153" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-OSF</t>
+        </is>
+      </c>
+      <c r="C154" s="85" t="n">
+        <v>515737.02</v>
+      </c>
+      <c r="E154" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F154" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-SDF</t>
+        </is>
+      </c>
+      <c r="C155" s="85" t="n">
+        <v>589026.04</v>
+      </c>
+      <c r="E155" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F155" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-SSF</t>
+        </is>
+      </c>
+      <c r="C156" s="85" t="n">
+        <v>352013.02</v>
+      </c>
+      <c r="E156" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F156" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-WDF</t>
+        </is>
+      </c>
+      <c r="C157" s="85" t="n">
+        <v>1005778.04</v>
+      </c>
+      <c r="E157" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F157" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="84" t="inlineStr">
+        <is>
+          <t>PLY-6-WSF</t>
+        </is>
+      </c>
+      <c r="C158" s="85" t="n">
+        <v>560389.02</v>
+      </c>
+      <c r="E158" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F158" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-CDF</t>
+        </is>
+      </c>
+      <c r="C159" s="85" t="n">
+        <v>676294.04</v>
+      </c>
+      <c r="E159" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F159" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-CSF</t>
+        </is>
+      </c>
+      <c r="C160" s="85" t="n">
+        <v>424397.02</v>
+      </c>
+      <c r="E160" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F160" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-HDF</t>
+        </is>
+      </c>
+      <c r="C161" s="85" t="n">
+        <v>467918.04</v>
+      </c>
+      <c r="E161" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F161" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-HSF</t>
+        </is>
+      </c>
+      <c r="C162" s="85" t="n">
+        <v>320209.02</v>
+      </c>
+      <c r="E162" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F162" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-ODF</t>
+        </is>
+      </c>
+      <c r="C163" s="85" t="n">
+        <v>973974.04</v>
+      </c>
+      <c r="E163" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F163" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-OSF</t>
+        </is>
+      </c>
+      <c r="C164" s="85" t="n">
+        <v>573237.02</v>
+      </c>
+      <c r="E164" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F164" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-SDF</t>
+        </is>
+      </c>
+      <c r="C165" s="85" t="n">
+        <v>646526.04</v>
+      </c>
+      <c r="E165" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F165" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-SSF</t>
+        </is>
+      </c>
+      <c r="C166" s="85" t="n">
+        <v>409513.02</v>
+      </c>
+      <c r="E166" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F166" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-WDF</t>
+        </is>
+      </c>
+      <c r="C167" s="85" t="n">
+        <v>1063278.04</v>
+      </c>
+      <c r="E167" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F167" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="84" t="inlineStr">
+        <is>
+          <t>PLY-9-WSF</t>
+        </is>
+      </c>
+      <c r="C168" s="85" t="n">
+        <v>617889.02</v>
+      </c>
+      <c r="E168" s="84" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="F168" s="84" t="inlineStr">
+        <is>
+          <t>rate card DB (price list 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169"/>
+    <row r="170">
+      <c r="A170" s="84" t="inlineStr">
+        <is>
+          <t>LANDED BOARD PRICES: Linyi Ocean International Trading, quotation 16 Oct 2026, valid to 30 Oct 2026. CIF Semarang plus port, clearance and trucking to the Kudus factory (bonded; duty, PPN and PPh excluded). Value = CIF USD per sheet × FX_USD + LAND_40HC ÷ sheets per 40' HC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="84" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B171" s="84" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C171" s="85" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E171" s="84" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F171" s="84" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="G171" s="86" t="inlineStr">
+        <is>
+          <t>Quote USD / sheet (landed Kudus)</t>
+        </is>
+      </c>
+      <c r="H171" s="87" t="inlineStr">
+        <is>
+          <t>Quote IDR / sheet (USD × FX_USD)</t>
+        </is>
+      </c>
+      <c r="I171" s="79" t="inlineStr">
+        <is>
+          <t>CIF USD / sheet</t>
+        </is>
+      </c>
+      <c r="J171" s="79" t="inlineStr">
+        <is>
+          <t>Sheets / 40' HC</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="84" t="inlineStr">
+        <is>
+          <t>FX_USD</t>
+        </is>
+      </c>
+      <c r="B172" s="84" t="inlineStr">
+        <is>
+          <t>Exchange rate</t>
+        </is>
+      </c>
+      <c r="C172" s="85" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E172" s="84" t="inlineStr">
+        <is>
+          <t>IDR/USD</t>
+        </is>
+      </c>
+      <c r="F172" s="84" t="inlineStr">
+        <is>
+          <t>RFQ file, Landing Assumptions. Change to the booked rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="84" t="inlineStr">
+        <is>
+          <t>LAND_40HC</t>
+        </is>
+      </c>
+      <c r="B173" s="84" t="inlineStr">
+        <is>
+          <t>Landing cost per 40' HC: line local charges, THC, lift-off, PPJK (BC 2.3), documents, trucking Tg. Emas to Kudus, 20% red-lane allowance</t>
+        </is>
+      </c>
+      <c r="C173" s="85" t="n">
+        <v>13350000</v>
+      </c>
+      <c r="E173" s="84" t="inlineStr">
+        <is>
+          <t>IDR/box</t>
+        </is>
+      </c>
+      <c r="F173" s="84" t="inlineStr">
+        <is>
+          <t>RFQ file, Landing Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="84" t="inlineStr">
+        <is>
+          <t>PANEL_GRADE</t>
+        </is>
+      </c>
+      <c r="B174" s="84" t="inlineStr">
+        <is>
+          <t>Board grade feeding the PLY-x and MDF-x rates (type E2, E0 or CARB)</t>
+        </is>
+      </c>
+      <c r="C174" s="85" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="E174" s="84" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F174" s="84" t="inlineStr">
+        <is>
+          <t>CARB Phase 2 / TSCA Title VI: required for US hotel projects, accepted for EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="84" t="inlineStr">
+        <is>
+          <t>VEN_M_ADD</t>
+        </is>
+      </c>
+      <c r="B175" s="84" t="inlineStr">
+        <is>
+          <t>Mindi veneer added per face inside the PLY-x-MSF / MDF rates</t>
+        </is>
+      </c>
+      <c r="C175" s="85" t="n">
+        <v>147709.02</v>
+      </c>
+      <c r="E175" s="84" t="inlineStr">
         <is>
           <t>IDR/face</t>
         </is>
       </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1" s="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>PLY-3-RAW</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 3 mm, raw</t>
-        </is>
-      </c>
-      <c r="C59" s="41" t="n">
-        <v>77500</v>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="F175" s="84" t="inlineStr">
+        <is>
+          <t>Back-calculated from the 29 Sep rate card (PLY-x-MSF minus PLY-x-RAW). Not the same as VEN_MINDI_FACE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="84" t="inlineStr">
+        <is>
+          <t>VEN_T_ADD</t>
+        </is>
+      </c>
+      <c r="B176" s="84" t="inlineStr">
+        <is>
+          <t>Teak veneer added per face inside the PLY-x-TSF / TDF rates</t>
+        </is>
+      </c>
+      <c r="C176" s="85" t="n">
+        <v>341201.02</v>
+      </c>
+      <c r="E176" s="84" t="inlineStr">
+        <is>
+          <t>IDR/face</t>
+        </is>
+      </c>
+      <c r="F176" s="84" t="inlineStr">
+        <is>
+          <t>Back-calculated from the 29 Sep rate card (PLY-x-TSF minus PLY-x-RAW). Not the same as VEN_TEAK_FACE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177"/>
+    <row r="178">
+      <c r="A178" s="79" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3</t>
+        </is>
+      </c>
+      <c r="B178" s="79" t="inlineStr">
+        <is>
+          <t>Furniture plywood 3 mm, E2, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C178" s="88">
+        <f>H178</f>
+        <v/>
+      </c>
+      <c r="E178" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Mojo Indah list, Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1" s="59">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>PLY-3-MSF</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 3 mm, mindi single face</t>
-        </is>
-      </c>
-      <c r="C60" s="44" t="n">
-        <v>225209.02</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="F178" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G178" s="86">
+        <f>I178+$C$173/$C$172/J178</f>
+        <v/>
+      </c>
+      <c r="H178" s="87">
+        <f>G178*$C$172</f>
+        <v/>
+      </c>
+      <c r="I178" s="86" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J178" s="87" t="n">
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="79" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6</t>
+        </is>
+      </c>
+      <c r="B179" s="79" t="inlineStr">
+        <is>
+          <t>Furniture plywood 6 mm, E2, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C179" s="88">
+        <f>H179</f>
+        <v/>
+      </c>
+      <c r="E179" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1" s="59">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>PLY-3-MDF</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 3 mm, mindi double face</t>
-        </is>
-      </c>
-      <c r="C61" s="44" t="n">
-        <v>372918.04</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="F179" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G179" s="86">
+        <f>I179+$C$173/$C$172/J179</f>
+        <v/>
+      </c>
+      <c r="H179" s="87">
+        <f>G179*$C$172</f>
+        <v/>
+      </c>
+      <c r="I179" s="86" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J179" s="87" t="n">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="79" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9</t>
+        </is>
+      </c>
+      <c r="B180" s="79" t="inlineStr">
+        <is>
+          <t>Furniture plywood 9 mm, E2, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C180" s="88">
+        <f>H180</f>
+        <v/>
+      </c>
+      <c r="E180" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1" s="59">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>PLY-3-TSF</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 3 mm, teak single face</t>
-        </is>
-      </c>
-      <c r="C62" s="44" t="n">
-        <v>418701.02</v>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="F180" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G180" s="86">
+        <f>I180+$C$173/$C$172/J180</f>
+        <v/>
+      </c>
+      <c r="H180" s="87">
+        <f>G180*$C$172</f>
+        <v/>
+      </c>
+      <c r="I180" s="86" t="n">
+        <v>12</v>
+      </c>
+      <c r="J180" s="87" t="n">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="79" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12</t>
+        </is>
+      </c>
+      <c r="B181" s="79" t="inlineStr">
+        <is>
+          <t>Furniture plywood 12 mm, E2, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C181" s="88">
+        <f>H181</f>
+        <v/>
+      </c>
+      <c r="E181" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" s="59">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>PLY-3-TDF</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 3 mm, teak double face</t>
-        </is>
-      </c>
-      <c r="C63" s="44" t="n">
-        <v>759902.04</v>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="F181" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G181" s="86">
+        <f>I181+$C$173/$C$172/J181</f>
+        <v/>
+      </c>
+      <c r="H181" s="87">
+        <f>G181*$C$172</f>
+        <v/>
+      </c>
+      <c r="I181" s="86" t="n">
+        <v>15.1050125313283</v>
+      </c>
+      <c r="J181" s="87" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="79" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15</t>
+        </is>
+      </c>
+      <c r="B182" s="79" t="inlineStr">
+        <is>
+          <t>Furniture plywood 15 mm, E2, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C182" s="88">
+        <f>H182</f>
+        <v/>
+      </c>
+      <c r="E182" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1" s="59">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>PLY-6-RAW</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 6 mm, raw</t>
-        </is>
-      </c>
-      <c r="C64" s="41" t="n">
-        <v>115000</v>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="F182" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G182" s="86">
+        <f>I182+$C$173/$C$172/J182</f>
+        <v/>
+      </c>
+      <c r="H182" s="87">
+        <f>G182*$C$172</f>
+        <v/>
+      </c>
+      <c r="I182" s="86" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J182" s="87" t="n">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="79" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18</t>
+        </is>
+      </c>
+      <c r="B183" s="79" t="inlineStr">
+        <is>
+          <t>Furniture plywood 18 mm, E2, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C183" s="88">
+        <f>H183</f>
+        <v/>
+      </c>
+      <c r="E183" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Mojo Indah list, Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1" s="59">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>PLY-6-MSF</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 6 mm, mindi single face</t>
-        </is>
-      </c>
-      <c r="C65" s="44" t="n">
-        <v>262709.02</v>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="F183" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G183" s="86">
+        <f>I183+$C$173/$C$172/J183</f>
+        <v/>
+      </c>
+      <c r="H183" s="87">
+        <f>G183*$C$172</f>
+        <v/>
+      </c>
+      <c r="I183" s="86" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J183" s="87" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-3</t>
+        </is>
+      </c>
+      <c r="B184" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 3 mm, E0, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C184" s="89">
+        <f>H184</f>
+        <v/>
+      </c>
+      <c r="E184" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" s="59">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>PLY-6-MDF</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 6 mm, mindi double face</t>
-        </is>
-      </c>
-      <c r="C66" s="44" t="n">
-        <v>410418.04</v>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="F184" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G184" s="82">
+        <f>I184+$C$173/$C$172/J184</f>
+        <v/>
+      </c>
+      <c r="H184" s="83">
+        <f>G184*$C$172</f>
+        <v/>
+      </c>
+      <c r="I184" s="82" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="J184" s="83" t="n">
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-6</t>
+        </is>
+      </c>
+      <c r="B185" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 6 mm, E0, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C185" s="89">
+        <f>H185</f>
+        <v/>
+      </c>
+      <c r="E185" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1" s="59">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>PLY-6-TSF</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 6 mm, teak single face</t>
-        </is>
-      </c>
-      <c r="C67" s="44" t="n">
-        <v>456201.02</v>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="F185" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G185" s="82">
+        <f>I185+$C$173/$C$172/J185</f>
+        <v/>
+      </c>
+      <c r="H185" s="83">
+        <f>G185*$C$172</f>
+        <v/>
+      </c>
+      <c r="I185" s="82" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="J185" s="83" t="n">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-9</t>
+        </is>
+      </c>
+      <c r="B186" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 9 mm, E0, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C186" s="89">
+        <f>H186</f>
+        <v/>
+      </c>
+      <c r="E186" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1" s="59">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>PLY-6-TDF</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 6 mm, teak double face</t>
-        </is>
-      </c>
-      <c r="C68" s="44" t="n">
-        <v>797402.04</v>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="F186" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G186" s="82">
+        <f>I186+$C$173/$C$172/J186</f>
+        <v/>
+      </c>
+      <c r="H186" s="83">
+        <f>G186*$C$172</f>
+        <v/>
+      </c>
+      <c r="I186" s="82" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J186" s="83" t="n">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-12</t>
+        </is>
+      </c>
+      <c r="B187" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 12 mm, E0, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C187" s="89">
+        <f>H187</f>
+        <v/>
+      </c>
+      <c r="E187" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1" s="59">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>PLY-9-RAW</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 9 mm, raw</t>
-        </is>
-      </c>
-      <c r="C69" s="41" t="n">
-        <v>172500</v>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="F187" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G187" s="82">
+        <f>I187+$C$173/$C$172/J187</f>
+        <v/>
+      </c>
+      <c r="H187" s="83">
+        <f>G187*$C$172</f>
+        <v/>
+      </c>
+      <c r="I187" s="82" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J187" s="83" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-15</t>
+        </is>
+      </c>
+      <c r="B188" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 15 mm, E0, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C188" s="89">
+        <f>H188</f>
+        <v/>
+      </c>
+      <c r="E188" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Mojo Indah list, Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1" s="59">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>PLY-9-MSF</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 9 mm, mindi single face</t>
-        </is>
-      </c>
-      <c r="C70" s="44" t="n">
-        <v>320209.02</v>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="F188" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G188" s="82">
+        <f>I188+$C$173/$C$172/J188</f>
+        <v/>
+      </c>
+      <c r="H188" s="83">
+        <f>G188*$C$172</f>
+        <v/>
+      </c>
+      <c r="I188" s="82" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="J188" s="83" t="n">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-18</t>
+        </is>
+      </c>
+      <c r="B189" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 18 mm, E0, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C189" s="89">
+        <f>H189</f>
+        <v/>
+      </c>
+      <c r="E189" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" s="59">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>PLY-9-MDF</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 9 mm, mindi double face</t>
-        </is>
-      </c>
-      <c r="C71" s="44" t="n">
-        <v>467918.04</v>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="F189" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G189" s="82">
+        <f>I189+$C$173/$C$172/J189</f>
+        <v/>
+      </c>
+      <c r="H189" s="83">
+        <f>G189*$C$172</f>
+        <v/>
+      </c>
+      <c r="I189" s="82" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="J189" s="83" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-CARB-3</t>
+        </is>
+      </c>
+      <c r="B190" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 3 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C190" s="89">
+        <f>H190</f>
+        <v/>
+      </c>
+      <c r="E190" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1" s="59">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>PLY-9-TSF</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 9 mm, teak single face</t>
-        </is>
-      </c>
-      <c r="C72" s="44" t="n">
-        <v>513701.02</v>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="F190" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G190" s="82">
+        <f>I190+$C$173/$C$172/J190</f>
+        <v/>
+      </c>
+      <c r="H190" s="83">
+        <f>G190*$C$172</f>
+        <v/>
+      </c>
+      <c r="I190" s="82" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J190" s="83" t="n">
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-CARB-6</t>
+        </is>
+      </c>
+      <c r="B191" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 6 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C191" s="89">
+        <f>H191</f>
+        <v/>
+      </c>
+      <c r="E191" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" s="59">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>PLY-9-TDF</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 9 mm, teak double face</t>
-        </is>
-      </c>
-      <c r="C73" s="44" t="n">
-        <v>854902.04</v>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="F191" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G191" s="82">
+        <f>I191+$C$173/$C$172/J191</f>
+        <v/>
+      </c>
+      <c r="H191" s="83">
+        <f>G191*$C$172</f>
+        <v/>
+      </c>
+      <c r="I191" s="82" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J191" s="83" t="n">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-CARB-9</t>
+        </is>
+      </c>
+      <c r="B192" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 9 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C192" s="89">
+        <f>H192</f>
+        <v/>
+      </c>
+      <c r="E192" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1" s="59">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>PLY-12-RAW</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 12 mm, raw</t>
-        </is>
-      </c>
-      <c r="C74" s="41" t="n">
-        <v>215000</v>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="F192" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G192" s="82">
+        <f>I192+$C$173/$C$172/J192</f>
+        <v/>
+      </c>
+      <c r="H192" s="83">
+        <f>G192*$C$172</f>
+        <v/>
+      </c>
+      <c r="I192" s="82" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J192" s="83" t="n">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-CARB-12</t>
+        </is>
+      </c>
+      <c r="B193" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 12 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C193" s="89">
+        <f>H193</f>
+        <v/>
+      </c>
+      <c r="E193" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Mojo Indah list, Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" s="59">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>PLY-12-MSF</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 12 mm, mindi single face</t>
-        </is>
-      </c>
-      <c r="C75" s="44" t="n">
-        <v>362709.02</v>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="F193" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G193" s="82">
+        <f>I193+$C$173/$C$172/J193</f>
+        <v/>
+      </c>
+      <c r="H193" s="83">
+        <f>G193*$C$172</f>
+        <v/>
+      </c>
+      <c r="I193" s="82" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J193" s="83" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-CARB-15</t>
+        </is>
+      </c>
+      <c r="B194" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 15 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C194" s="89">
+        <f>H194</f>
+        <v/>
+      </c>
+      <c r="E194" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1" s="59">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>PLY-12-MDF</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 12 mm, mindi double face</t>
-        </is>
-      </c>
-      <c r="C76" s="44" t="n">
-        <v>510418.04</v>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="F194" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G194" s="82">
+        <f>I194+$C$173/$C$172/J194</f>
+        <v/>
+      </c>
+      <c r="H194" s="83">
+        <f>G194*$C$172</f>
+        <v/>
+      </c>
+      <c r="I194" s="82" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J194" s="83" t="n">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="84" t="inlineStr">
+        <is>
+          <t>LND-PLY-CARB-18</t>
+        </is>
+      </c>
+      <c r="B195" s="84" t="inlineStr">
+        <is>
+          <t>Furniture plywood 18 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C195" s="89">
+        <f>H195</f>
+        <v/>
+      </c>
+      <c r="E195" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" s="59">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>PLY-12-TSF</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 12 mm, teak single face</t>
-        </is>
-      </c>
-      <c r="C77" s="44" t="n">
-        <v>556201.02</v>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="F195" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G195" s="82">
+        <f>I195+$C$173/$C$172/J195</f>
+        <v/>
+      </c>
+      <c r="H195" s="83">
+        <f>G195*$C$172</f>
+        <v/>
+      </c>
+      <c r="I195" s="82" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J195" s="83" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="79" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-3</t>
+        </is>
+      </c>
+      <c r="B196" s="79" t="inlineStr">
+        <is>
+          <t>MDF 3 mm, E2, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C196" s="88">
+        <f>H196</f>
+        <v/>
+      </c>
+      <c r="E196" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1" s="59">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>PLY-12-TDF</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 12 mm, teak double face</t>
-        </is>
-      </c>
-      <c r="C78" s="44" t="n">
-        <v>897402.04</v>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="F196" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G196" s="86">
+        <f>I196+$C$173/$C$172/J196</f>
+        <v/>
+      </c>
+      <c r="H196" s="87">
+        <f>G196*$C$172</f>
+        <v/>
+      </c>
+      <c r="I196" s="86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J196" s="87" t="n">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="79" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-6</t>
+        </is>
+      </c>
+      <c r="B197" s="79" t="inlineStr">
+        <is>
+          <t>MDF 6 mm, E2, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C197" s="88">
+        <f>H197</f>
+        <v/>
+      </c>
+      <c r="E197" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1" s="59">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>PLY-15-RAW</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 15 mm, raw</t>
-        </is>
-      </c>
-      <c r="C79" s="41" t="n">
-        <v>260000</v>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="F197" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G197" s="86">
+        <f>I197+$C$173/$C$172/J197</f>
+        <v/>
+      </c>
+      <c r="H197" s="87">
+        <f>G197*$C$172</f>
+        <v/>
+      </c>
+      <c r="I197" s="86" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J197" s="87" t="n">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="79" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-9</t>
+        </is>
+      </c>
+      <c r="B198" s="79" t="inlineStr">
+        <is>
+          <t>MDF 9 mm, E2, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C198" s="88">
+        <f>H198</f>
+        <v/>
+      </c>
+      <c r="E198" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Mojo Indah list, Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" s="59">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>PLY-15-MSF</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 15 mm, mindi single face</t>
-        </is>
-      </c>
-      <c r="C80" s="44" t="n">
-        <v>407709.02</v>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="F198" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G198" s="86">
+        <f>I198+$C$173/$C$172/J198</f>
+        <v/>
+      </c>
+      <c r="H198" s="87">
+        <f>G198*$C$172</f>
+        <v/>
+      </c>
+      <c r="I198" s="86" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J198" s="87" t="n">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="79" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-12</t>
+        </is>
+      </c>
+      <c r="B199" s="79" t="inlineStr">
+        <is>
+          <t>MDF 12 mm, E2, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C199" s="88">
+        <f>H199</f>
+        <v/>
+      </c>
+      <c r="E199" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" s="59">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>PLY-15-MDF</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 15 mm, mindi double face</t>
-        </is>
-      </c>
-      <c r="C81" s="44" t="n">
-        <v>555418.04</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="F199" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G199" s="86">
+        <f>I199+$C$173/$C$172/J199</f>
+        <v/>
+      </c>
+      <c r="H199" s="87">
+        <f>G199*$C$172</f>
+        <v/>
+      </c>
+      <c r="I199" s="86" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J199" s="87" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="79" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-15</t>
+        </is>
+      </c>
+      <c r="B200" s="79" t="inlineStr">
+        <is>
+          <t>MDF 15 mm, E2, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C200" s="88">
+        <f>H200</f>
+        <v/>
+      </c>
+      <c r="E200" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1" s="59">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>PLY-15-TSF</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 15 mm, teak single face</t>
-        </is>
-      </c>
-      <c r="C82" s="44" t="n">
-        <v>601201.02</v>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="F200" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G200" s="86">
+        <f>I200+$C$173/$C$172/J200</f>
+        <v/>
+      </c>
+      <c r="H200" s="87">
+        <f>G200*$C$172</f>
+        <v/>
+      </c>
+      <c r="I200" s="86" t="n">
+        <v>10</v>
+      </c>
+      <c r="J200" s="87" t="n">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="79" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18</t>
+        </is>
+      </c>
+      <c r="B201" s="79" t="inlineStr">
+        <is>
+          <t>MDF 18 mm, E2, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C201" s="88">
+        <f>H201</f>
+        <v/>
+      </c>
+      <c r="E201" s="79" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1" s="59">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>PLY-15-TDF</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 15 mm, teak double face</t>
-        </is>
-      </c>
-      <c r="C83" s="44" t="n">
-        <v>942402.04</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="F201" s="79" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G201" s="86">
+        <f>I201+$C$173/$C$172/J201</f>
+        <v/>
+      </c>
+      <c r="H201" s="87">
+        <f>G201*$C$172</f>
+        <v/>
+      </c>
+      <c r="I201" s="86" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J201" s="87" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-3</t>
+        </is>
+      </c>
+      <c r="B202" s="84" t="inlineStr">
+        <is>
+          <t>MDF 3 mm, E0, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C202" s="89">
+        <f>H202</f>
+        <v/>
+      </c>
+      <c r="E202" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1" s="59">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>PLY-18-RAW</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 18 mm, raw</t>
-        </is>
-      </c>
-      <c r="C84" s="41" t="n">
-        <v>295000</v>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="F202" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G202" s="82">
+        <f>I202+$C$173/$C$172/J202</f>
+        <v/>
+      </c>
+      <c r="H202" s="83">
+        <f>G202*$C$172</f>
+        <v/>
+      </c>
+      <c r="I202" s="82" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J202" s="83" t="n">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-6</t>
+        </is>
+      </c>
+      <c r="B203" s="84" t="inlineStr">
+        <is>
+          <t>MDF 6 mm, E0, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C203" s="89">
+        <f>H203</f>
+        <v/>
+      </c>
+      <c r="E203" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Mojo Indah list, Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" s="59">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>PLY-18-MSF</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 18 mm, mindi single face</t>
-        </is>
-      </c>
-      <c r="C85" s="44" t="n">
-        <v>442709.02</v>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="F203" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G203" s="82">
+        <f>I203+$C$173/$C$172/J203</f>
+        <v/>
+      </c>
+      <c r="H203" s="83">
+        <f>G203*$C$172</f>
+        <v/>
+      </c>
+      <c r="I203" s="82" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J203" s="83" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-9</t>
+        </is>
+      </c>
+      <c r="B204" s="84" t="inlineStr">
+        <is>
+          <t>MDF 9 mm, E0, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C204" s="89">
+        <f>H204</f>
+        <v/>
+      </c>
+      <c r="E204" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" s="59">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>PLY-18-MDF</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 18 mm, mindi double face</t>
-        </is>
-      </c>
-      <c r="C86" s="44" t="n">
-        <v>590418.04</v>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="F204" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G204" s="82">
+        <f>I204+$C$173/$C$172/J204</f>
+        <v/>
+      </c>
+      <c r="H204" s="83">
+        <f>G204*$C$172</f>
+        <v/>
+      </c>
+      <c r="I204" s="82" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="J204" s="83" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12</t>
+        </is>
+      </c>
+      <c r="B205" s="84" t="inlineStr">
+        <is>
+          <t>MDF 12 mm, E0, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C205" s="89">
+        <f>H205</f>
+        <v/>
+      </c>
+      <c r="E205" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" s="59">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>PLY-18-TSF</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 18 mm, teak single face</t>
-        </is>
-      </c>
-      <c r="C87" s="44" t="n">
-        <v>636201.02</v>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="F205" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G205" s="82">
+        <f>I205+$C$173/$C$172/J205</f>
+        <v/>
+      </c>
+      <c r="H205" s="83">
+        <f>G205*$C$172</f>
+        <v/>
+      </c>
+      <c r="I205" s="82" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J205" s="83" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15</t>
+        </is>
+      </c>
+      <c r="B206" s="84" t="inlineStr">
+        <is>
+          <t>MDF 15 mm, E0, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C206" s="89">
+        <f>H206</f>
+        <v/>
+      </c>
+      <c r="E206" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1" s="59">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>PLY-18-TDF</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 18 mm, teak double face</t>
-        </is>
-      </c>
-      <c r="C88" s="44" t="n">
-        <v>977402.04</v>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="F206" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G206" s="82">
+        <f>I206+$C$173/$C$172/J206</f>
+        <v/>
+      </c>
+      <c r="H206" s="83">
+        <f>G206*$C$172</f>
+        <v/>
+      </c>
+      <c r="I206" s="82" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J206" s="83" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18</t>
+        </is>
+      </c>
+      <c r="B207" s="84" t="inlineStr">
+        <is>
+          <t>MDF 18 mm, E0, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C207" s="89">
+        <f>H207</f>
+        <v/>
+      </c>
+      <c r="E207" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1" s="59">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>PLY-24-RAW</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 24 mm, raw</t>
-        </is>
-      </c>
-      <c r="C89" s="41" t="n">
-        <v>375000</v>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="F207" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G207" s="82">
+        <f>I207+$C$173/$C$172/J207</f>
+        <v/>
+      </c>
+      <c r="H207" s="83">
+        <f>G207*$C$172</f>
+        <v/>
+      </c>
+      <c r="I207" s="82" t="n">
+        <v>16</v>
+      </c>
+      <c r="J207" s="83" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-CARB-3</t>
+        </is>
+      </c>
+      <c r="B208" s="84" t="inlineStr">
+        <is>
+          <t>MDF 3 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C208" s="89">
+        <f>H208</f>
+        <v/>
+      </c>
+      <c r="E208" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Extrapolated. Status CONFIRM</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1" s="59">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>PLY-24-MSF</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 24 mm, mindi single face</t>
-        </is>
-      </c>
-      <c r="C90" s="44" t="n">
-        <v>522709.02</v>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="F208" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G208" s="82">
+        <f>I208+$C$173/$C$172/J208</f>
+        <v/>
+      </c>
+      <c r="H208" s="83">
+        <f>G208*$C$172</f>
+        <v/>
+      </c>
+      <c r="I208" s="82" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J208" s="83" t="n">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-CARB-6</t>
+        </is>
+      </c>
+      <c r="B209" s="84" t="inlineStr">
+        <is>
+          <t>MDF 6 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C209" s="89">
+        <f>H209</f>
+        <v/>
+      </c>
+      <c r="E209" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1" s="59">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>PLY-24-MDF</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 24 mm, mindi double face</t>
-        </is>
-      </c>
-      <c r="C91" s="44" t="n">
-        <v>670418.04</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="F209" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G209" s="82">
+        <f>I209+$C$173/$C$172/J209</f>
+        <v/>
+      </c>
+      <c r="H209" s="83">
+        <f>G209*$C$172</f>
+        <v/>
+      </c>
+      <c r="I209" s="82" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="J209" s="83" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-CARB-9</t>
+        </is>
+      </c>
+      <c r="B210" s="84" t="inlineStr">
+        <is>
+          <t>MDF 9 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C210" s="89">
+        <f>H210</f>
+        <v/>
+      </c>
+      <c r="E210" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1" s="59">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>PLY-24-TSF</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 24 mm, teak single face</t>
-        </is>
-      </c>
-      <c r="C92" s="44" t="n">
-        <v>716201.02</v>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="F210" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G210" s="82">
+        <f>I210+$C$173/$C$172/J210</f>
+        <v/>
+      </c>
+      <c r="H210" s="83">
+        <f>G210*$C$172</f>
+        <v/>
+      </c>
+      <c r="I210" s="82" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J210" s="83" t="n">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-CARB-12</t>
+        </is>
+      </c>
+      <c r="B211" s="84" t="inlineStr">
+        <is>
+          <t>MDF 12 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C211" s="89">
+        <f>H211</f>
+        <v/>
+      </c>
+      <c r="E211" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1" s="59">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>PLY-24-TDF</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Plywood 24 mm, teak double face</t>
-        </is>
-      </c>
-      <c r="C93" s="44" t="n">
-        <v>1057402.04</v>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="F211" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G211" s="82">
+        <f>I211+$C$173/$C$172/J211</f>
+        <v/>
+      </c>
+      <c r="H211" s="83">
+        <f>G211*$C$172</f>
+        <v/>
+      </c>
+      <c r="I211" s="82" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J211" s="83" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-CARB-15</t>
+        </is>
+      </c>
+      <c r="B212" s="84" t="inlineStr">
+        <is>
+          <t>MDF 15 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C212" s="89">
+        <f>H212</f>
+        <v/>
+      </c>
+      <c r="E212" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
-    <row r="94" ht="15.75" customHeight="1" s="59">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>NORMS</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="n"/>
-      <c r="C94" s="4" t="n"/>
-      <c r="D94" s="4" t="n"/>
-      <c r="E94" s="4" t="n"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1" s="59">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>CARTON_MIN_M2</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Below this carton area use group A price</t>
-        </is>
-      </c>
-      <c r="C95" s="43" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15.75" customHeight="1" s="59">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>KD_PACK_FACTOR</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Extra consumables factor for flatpack (2+ boxes)</t>
-        </is>
-      </c>
-      <c r="C96" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>0 = off</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15.75" customHeight="1" s="59">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>WASTE_REUSE_MIN</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Offcut on the last sheet counts as reusable when waste exceeds this</t>
-        </is>
-      </c>
-      <c r="C97" s="42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Decision 29 Sep</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15.75" customHeight="1" s="59">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>OFFCUT_HANDLING</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Handling factor on fractional sheets when the offcut is reused</t>
-        </is>
-      </c>
-      <c r="C98" s="42" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1" s="59">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>PLY-12-CDF</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>718794.04</v>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="F212" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G212" s="82">
+        <f>I212+$C$173/$C$172/J212</f>
+        <v/>
+      </c>
+      <c r="H212" s="83">
+        <f>G212*$C$172</f>
+        <v/>
+      </c>
+      <c r="I212" s="82" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="J212" s="83" t="n">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="84" t="inlineStr">
+        <is>
+          <t>LND-MDF-CARB-18</t>
+        </is>
+      </c>
+      <c r="B213" s="84" t="inlineStr">
+        <is>
+          <t>MDF 18 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C213" s="89">
+        <f>H213</f>
+        <v/>
+      </c>
+      <c r="E213" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1" s="59">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>PLY-12-CSF</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>466897.02</v>
-      </c>
-      <c r="D100" t="inlineStr">
+      <c r="F213" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G213" s="82">
+        <f>I213+$C$173/$C$172/J213</f>
+        <v/>
+      </c>
+      <c r="H213" s="83">
+        <f>G213*$C$172</f>
+        <v/>
+      </c>
+      <c r="I213" s="82" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J213" s="83" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="84" t="inlineStr">
+        <is>
+          <t>LND-MAR-15</t>
+        </is>
+      </c>
+      <c r="B214" s="84" t="inlineStr">
+        <is>
+          <t>Marine plywood 15 mm, BS 1088 type, WBP glue, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C214" s="89">
+        <f>H214</f>
+        <v/>
+      </c>
+      <c r="E214" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15.75" customHeight="1" s="59">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>PLY-12-HDF</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>510418.04</v>
-      </c>
-      <c r="D101" t="inlineStr">
+      <c r="F214" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G214" s="82">
+        <f>I214+$C$173/$C$172/J214</f>
+        <v/>
+      </c>
+      <c r="H214" s="83">
+        <f>G214*$C$172</f>
+        <v/>
+      </c>
+      <c r="I214" s="82" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J214" s="83" t="n">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="84" t="inlineStr">
+        <is>
+          <t>LND-MAR-18</t>
+        </is>
+      </c>
+      <c r="B215" s="84" t="inlineStr">
+        <is>
+          <t>Marine plywood 18 mm, BS 1088 type, WBP glue, landed Kudus</t>
+        </is>
+      </c>
+      <c r="C215" s="89">
+        <f>H215</f>
+        <v/>
+      </c>
+      <c r="E215" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="15.75" customHeight="1" s="59">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>PLY-12-HSF</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>362709.02</v>
-      </c>
-      <c r="D102" t="inlineStr">
+      <c r="F215" s="84" t="inlineStr">
+        <is>
+          <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="G215" s="82">
+        <f>I215+$C$173/$C$172/J215</f>
+        <v/>
+      </c>
+      <c r="H215" s="83">
+        <f>G215*$C$172</f>
+        <v/>
+      </c>
+      <c r="I215" s="82" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="J215" s="83" t="n">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="216"/>
+    <row r="217">
+      <c r="A217" s="84" t="inlineStr">
+        <is>
+          <t>BOARD RATES ADDED 16 OCT 2026 (use as PANEL TYPE on item tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="84" t="inlineStr">
+        <is>
+          <t>MDF-3-RAW</t>
+        </is>
+      </c>
+      <c r="B218" s="84" t="inlineStr">
+        <is>
+          <t>MDF 3 mm, raw, grade per PANEL_GRADE</t>
+        </is>
+      </c>
+      <c r="C218" s="89">
+        <f t="array" ref="C218">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="E218" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="15.75" customHeight="1" s="59">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>PLY-12-ODF</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1016474.04</v>
-      </c>
-      <c r="D103" t="inlineStr">
+      <c r="F218" s="84" t="inlineStr">
+        <is>
+          <t>Landed rows above</t>
+        </is>
+      </c>
+      <c r="G218" s="82">
+        <f t="array" ref="G218">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H218" s="83">
+        <f>G218*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="84" t="inlineStr">
+        <is>
+          <t>MDF-6-RAW</t>
+        </is>
+      </c>
+      <c r="B219" s="84" t="inlineStr">
+        <is>
+          <t>MDF 6 mm, raw, grade per PANEL_GRADE</t>
+        </is>
+      </c>
+      <c r="C219" s="89">
+        <f t="array" ref="C219">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="E219" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15.75" customHeight="1" s="59">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>PLY-12-OSF</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>615737.02</v>
-      </c>
-      <c r="D104" t="inlineStr">
+      <c r="F219" s="84" t="inlineStr">
+        <is>
+          <t>Landed rows above</t>
+        </is>
+      </c>
+      <c r="G219" s="82">
+        <f t="array" ref="G219">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H219" s="83">
+        <f>G219*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="84" t="inlineStr">
+        <is>
+          <t>MDF-9-RAW</t>
+        </is>
+      </c>
+      <c r="B220" s="84" t="inlineStr">
+        <is>
+          <t>MDF 9 mm, raw, grade per PANEL_GRADE</t>
+        </is>
+      </c>
+      <c r="C220" s="89">
+        <f t="array" ref="C220">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="E220" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15.75" customHeight="1" s="59">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>PLY-12-SDF</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>689026.04</v>
-      </c>
-      <c r="D105" t="inlineStr">
+      <c r="F220" s="84" t="inlineStr">
+        <is>
+          <t>Landed rows above</t>
+        </is>
+      </c>
+      <c r="G220" s="82">
+        <f t="array" ref="G220">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H220" s="83">
+        <f>G220*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="84" t="inlineStr">
+        <is>
+          <t>MDF-12-RAW</t>
+        </is>
+      </c>
+      <c r="B221" s="84" t="inlineStr">
+        <is>
+          <t>MDF 12 mm, raw, grade per PANEL_GRADE</t>
+        </is>
+      </c>
+      <c r="C221" s="89">
+        <f t="array" ref="C221">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="E221" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15.75" customHeight="1" s="59">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>PLY-12-SSF</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>452013.02</v>
-      </c>
-      <c r="D106" t="inlineStr">
+      <c r="F221" s="84" t="inlineStr">
+        <is>
+          <t>Landed rows above</t>
+        </is>
+      </c>
+      <c r="G221" s="82">
+        <f t="array" ref="G221">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H221" s="83">
+        <f>G221*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="84" t="inlineStr">
+        <is>
+          <t>MDF-15-RAW</t>
+        </is>
+      </c>
+      <c r="B222" s="84" t="inlineStr">
+        <is>
+          <t>MDF 15 mm, raw, grade per PANEL_GRADE</t>
+        </is>
+      </c>
+      <c r="C222" s="89">
+        <f t="array" ref="C222">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="E222" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="15.75" customHeight="1" s="59">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>PLY-12-WDF</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>1105778.04</v>
-      </c>
-      <c r="D107" t="inlineStr">
+      <c r="F222" s="84" t="inlineStr">
+        <is>
+          <t>Landed rows above</t>
+        </is>
+      </c>
+      <c r="G222" s="82">
+        <f t="array" ref="G222">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H222" s="83">
+        <f>G222*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="84" t="inlineStr">
+        <is>
+          <t>MDF-18-RAW</t>
+        </is>
+      </c>
+      <c r="B223" s="84" t="inlineStr">
+        <is>
+          <t>MDF 18 mm, raw, grade per PANEL_GRADE</t>
+        </is>
+      </c>
+      <c r="C223" s="89">
+        <f t="array" ref="C223">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="E223" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="15.75" customHeight="1" s="59">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>PLY-12-WSF</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>660389.02</v>
-      </c>
-      <c r="D108" t="inlineStr">
+      <c r="F223" s="84" t="inlineStr">
+        <is>
+          <t>Landed rows above</t>
+        </is>
+      </c>
+      <c r="G223" s="82">
+        <f t="array" ref="G223">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H223" s="83">
+        <f>G223*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="84" t="inlineStr">
+        <is>
+          <t>PLY-15-MAR</t>
+        </is>
+      </c>
+      <c r="B224" s="84" t="inlineStr">
+        <is>
+          <t>Marine plywood 15 mm, raw</t>
+        </is>
+      </c>
+      <c r="C224" s="89">
+        <f t="array" ref="C224">INDEX($C$178:$C$215,MATCH("LND-MAR-15",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="E224" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1" s="59">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>PLY-15-CDF</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>763794.04</v>
-      </c>
-      <c r="D109" t="inlineStr">
+      <c r="F224" s="84" t="inlineStr">
+        <is>
+          <t>Landed rows above</t>
+        </is>
+      </c>
+      <c r="G224" s="82">
+        <f t="array" ref="G224">INDEX($G$178:$G$215,MATCH("LND-MAR-15",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H224" s="83">
+        <f>G224*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="84" t="inlineStr">
+        <is>
+          <t>PLY-18-MAR</t>
+        </is>
+      </c>
+      <c r="B225" s="84" t="inlineStr">
+        <is>
+          <t>Marine plywood 18 mm, raw</t>
+        </is>
+      </c>
+      <c r="C225" s="89">
+        <f t="array" ref="C225">INDEX($C$178:$C$215,MATCH("LND-MAR-18",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="E225" s="84" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="15.75" customHeight="1" s="59">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>PLY-15-CSF</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>511897.02</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1" s="59">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>PLY-15-HDF</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>555418.04</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="15.75" customHeight="1" s="59">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>PLY-15-HSF</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>407709.02</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1" s="59">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>PLY-15-ODF</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>1061474.04</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1" s="59">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>PLY-15-OSF</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>660737.02</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="15.75" customHeight="1" s="59">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>PLY-15-SDF</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>734026.04</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="15.75" customHeight="1" s="59">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>PLY-15-SSF</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>497013.02</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="15.75" customHeight="1" s="59">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>PLY-15-WDF</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>1150778.04</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="15.75" customHeight="1" s="59">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>PLY-15-WSF</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>705389.02</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="15.75" customHeight="1" s="59">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>PLY-18-CDF</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>798794.04</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="15.75" customHeight="1" s="59">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>PLY-18-CSF</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>546897.02</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="15.75" customHeight="1" s="59">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>PLY-18-HDF</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>590418.04</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="15.75" customHeight="1" s="59">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>PLY-18-HSF</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>442709.02</v>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="15.75" customHeight="1" s="59">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>PLY-18-ODF</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>1096474.04</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="15.75" customHeight="1" s="59">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>PLY-18-OSF</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>695737.02</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="15.75" customHeight="1" s="59">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>PLY-18-SDF</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>769026.04</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="15.75" customHeight="1" s="59">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>PLY-18-SSF</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>532013.02</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="15.75" customHeight="1" s="59">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>PLY-18-WDF</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>1185778.04</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="15.75" customHeight="1" s="59">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>PLY-18-WSF</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>740389.02</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="15.75" customHeight="1" s="59">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>PLY-24-CDF</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>878794.04</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="15.75" customHeight="1" s="59">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>PLY-24-CSF</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>626897.02</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="15.75" customHeight="1" s="59">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>PLY-24-HDF</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>670418.04</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="15.75" customHeight="1" s="59">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>PLY-24-HSF</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>522709.02</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="15.75" customHeight="1" s="59">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>PLY-24-ODF</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>1176474.04</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="15.75" customHeight="1" s="59">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>PLY-24-OSF</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>775737.02</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15.75" customHeight="1" s="59">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>PLY-24-SDF</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>849026.04</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="15.75" customHeight="1" s="59">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>PLY-24-SSF</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>612013.02</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="15.75" customHeight="1" s="59">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>PLY-24-WDF</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>1265778.04</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="15.75" customHeight="1" s="59">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>PLY-24-WSF</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>820389.02</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="15.75" customHeight="1" s="59">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>PLY-3-CDF</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>581294.04</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="15.75" customHeight="1" s="59">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>PLY-3-CSF</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>329397.02</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="15.75" customHeight="1" s="59">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>PLY-3-HDF</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>372918.04</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="15.75" customHeight="1" s="59">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>PLY-3-HSF</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>225209.02</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="15.75" customHeight="1" s="59">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>PLY-3-ODF</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>878974.04</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="15.75" customHeight="1" s="59">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>PLY-3-OSF</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>478237.02</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="15.75" customHeight="1" s="59">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>PLY-3-SDF</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>551526.04</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="15.75" customHeight="1" s="59">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>PLY-3-SSF</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>314513.02</v>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="15.75" customHeight="1" s="59">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>PLY-3-WDF</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>968278.04</v>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="15.75" customHeight="1" s="59">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>PLY-3-WSF</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>522889.02</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="15.75" customHeight="1" s="59">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>PLY-6-CDF</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>618794.04</v>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="15.75" customHeight="1" s="59">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>PLY-6-CSF</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>366897.02</v>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="15.75" customHeight="1" s="59">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>PLY-6-HDF</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>410418.04</v>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="15.75" customHeight="1" s="59">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>PLY-6-HSF</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>262709.02</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="15.75" customHeight="1" s="59">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>PLY-6-ODF</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>916474.04</v>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="15.75" customHeight="1" s="59">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>PLY-6-OSF</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>515737.02</v>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="15.75" customHeight="1" s="59">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>PLY-6-SDF</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>589026.04</v>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="15.75" customHeight="1" s="59">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>PLY-6-SSF</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>352013.02</v>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="15.75" customHeight="1" s="59">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>PLY-6-WDF</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>1005778.04</v>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="15.75" customHeight="1" s="59">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>PLY-6-WSF</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>560389.02</v>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="15.75" customHeight="1" s="59">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>PLY-9-CDF</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>676294.04</v>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="15.75" customHeight="1" s="59">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>PLY-9-CSF</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>424397.02</v>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="15.75" customHeight="1" s="59">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>PLY-9-HDF</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>467918.04</v>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="15.75" customHeight="1" s="59">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>PLY-9-HSF</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>320209.02</v>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="15.75" customHeight="1" s="59">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>PLY-9-ODF</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>973974.04</v>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="15.75" customHeight="1" s="59">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>PLY-9-OSF</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>573237.02</v>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="15.75" customHeight="1" s="59">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>PLY-9-SDF</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>646526.04</v>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="15.75" customHeight="1" s="59">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>PLY-9-SSF</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>409513.02</v>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="15.75" customHeight="1" s="59">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>PLY-9-WDF</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>1063278.04</v>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="15.75" customHeight="1" s="59">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>PLY-9-WSF</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>617889.02</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>IDR/sheet</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>rate card DB (price list 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="15.75" customHeight="1" s="59"/>
-    <row r="170" ht="15.75" customHeight="1" s="59"/>
-    <row r="171" ht="15.75" customHeight="1" s="59"/>
-    <row r="172" ht="15.75" customHeight="1" s="59"/>
-    <row r="173" ht="15.75" customHeight="1" s="59"/>
-    <row r="174" ht="15.75" customHeight="1" s="59"/>
-    <row r="175" ht="15.75" customHeight="1" s="59"/>
-    <row r="176" ht="15.75" customHeight="1" s="59"/>
-    <row r="177" ht="15.75" customHeight="1" s="59"/>
-    <row r="178" ht="15.75" customHeight="1" s="59"/>
-    <row r="179" ht="15.75" customHeight="1" s="59"/>
-    <row r="180" ht="15.75" customHeight="1" s="59"/>
-    <row r="181" ht="15.75" customHeight="1" s="59"/>
-    <row r="182" ht="15.75" customHeight="1" s="59"/>
-    <row r="183" ht="15.75" customHeight="1" s="59"/>
-    <row r="184" ht="15.75" customHeight="1" s="59"/>
-    <row r="185" ht="15.75" customHeight="1" s="59"/>
-    <row r="186" ht="15.75" customHeight="1" s="59"/>
-    <row r="187" ht="15.75" customHeight="1" s="59"/>
-    <row r="188" ht="15.75" customHeight="1" s="59"/>
-    <row r="189" ht="15.75" customHeight="1" s="59"/>
-    <row r="190" ht="15.75" customHeight="1" s="59"/>
-    <row r="191" ht="15.75" customHeight="1" s="59"/>
-    <row r="192" ht="15.75" customHeight="1" s="59"/>
-    <row r="193" ht="15.75" customHeight="1" s="59"/>
-    <row r="194" ht="15.75" customHeight="1" s="59"/>
-    <row r="195" ht="15.75" customHeight="1" s="59"/>
-    <row r="196" ht="15.75" customHeight="1" s="59"/>
-    <row r="197" ht="15.75" customHeight="1" s="59"/>
-    <row r="198" ht="15.75" customHeight="1" s="59"/>
-    <row r="199" ht="15.75" customHeight="1" s="59"/>
-    <row r="200" ht="15.75" customHeight="1" s="59"/>
-    <row r="201" ht="15.75" customHeight="1" s="59"/>
-    <row r="202" ht="15.75" customHeight="1" s="59"/>
-    <row r="203" ht="15.75" customHeight="1" s="59"/>
-    <row r="204" ht="15.75" customHeight="1" s="59"/>
-    <row r="205" ht="15.75" customHeight="1" s="59"/>
-    <row r="206" ht="15.75" customHeight="1" s="59"/>
-    <row r="207" ht="15.75" customHeight="1" s="59"/>
-    <row r="208" ht="15.75" customHeight="1" s="59"/>
-    <row r="209" ht="15.75" customHeight="1" s="59"/>
-    <row r="210" ht="15.75" customHeight="1" s="59"/>
-    <row r="211" ht="15.75" customHeight="1" s="59"/>
-    <row r="212" ht="15.75" customHeight="1" s="59"/>
-    <row r="213" ht="15.75" customHeight="1" s="59"/>
-    <row r="214" ht="15.75" customHeight="1" s="59"/>
-    <row r="215" ht="15.75" customHeight="1" s="59"/>
-    <row r="216" ht="15.75" customHeight="1" s="59"/>
-    <row r="217" ht="15.75" customHeight="1" s="59"/>
-    <row r="218" ht="15.75" customHeight="1" s="59"/>
-    <row r="219" ht="15.75" customHeight="1" s="59"/>
-    <row r="220" ht="15.75" customHeight="1" s="59"/>
-    <row r="221" ht="15.75" customHeight="1" s="59"/>
-    <row r="222" ht="15.75" customHeight="1" s="59"/>
-    <row r="223" ht="15.75" customHeight="1" s="59"/>
-    <row r="224" ht="15.75" customHeight="1" s="59"/>
-    <row r="225" ht="15.75" customHeight="1" s="59"/>
-    <row r="226" ht="15.75" customHeight="1" s="59"/>
-    <row r="227" ht="15.75" customHeight="1" s="59"/>
-    <row r="228" ht="15.75" customHeight="1" s="59"/>
-    <row r="229" ht="15.75" customHeight="1" s="59"/>
-    <row r="230" ht="15.75" customHeight="1" s="59"/>
-    <row r="231" ht="15.75" customHeight="1" s="59"/>
-    <row r="232" ht="15.75" customHeight="1" s="59"/>
-    <row r="233" ht="15.75" customHeight="1" s="59"/>
-    <row r="234" ht="15.75" customHeight="1" s="59"/>
-    <row r="235" ht="15.75" customHeight="1" s="59"/>
-    <row r="236" ht="15.75" customHeight="1" s="59"/>
-    <row r="237" ht="15.75" customHeight="1" s="59"/>
-    <row r="238" ht="15.75" customHeight="1" s="59"/>
-    <row r="239" ht="15.75" customHeight="1" s="59"/>
-    <row r="240" ht="15.75" customHeight="1" s="59"/>
-    <row r="241" ht="15.75" customHeight="1" s="59"/>
-    <row r="242" ht="15.75" customHeight="1" s="59"/>
-    <row r="243" ht="15.75" customHeight="1" s="59"/>
-    <row r="244" ht="15.75" customHeight="1" s="59"/>
-    <row r="245" ht="15.75" customHeight="1" s="59"/>
-    <row r="246" ht="15.75" customHeight="1" s="59"/>
-    <row r="247" ht="15.75" customHeight="1" s="59"/>
-    <row r="248" ht="15.75" customHeight="1" s="59"/>
-    <row r="249" ht="15.75" customHeight="1" s="59"/>
-    <row r="250" ht="15.75" customHeight="1" s="59"/>
-    <row r="251" ht="15.75" customHeight="1" s="59"/>
-    <row r="252" ht="15.75" customHeight="1" s="59"/>
-    <row r="253" ht="15.75" customHeight="1" s="59"/>
-    <row r="254" ht="15.75" customHeight="1" s="59"/>
-    <row r="255" ht="15.75" customHeight="1" s="59"/>
-    <row r="256" ht="15.75" customHeight="1" s="59"/>
-    <row r="257" ht="15.75" customHeight="1" s="59"/>
-    <row r="258" ht="15.75" customHeight="1" s="59"/>
-    <row r="259" ht="15.75" customHeight="1" s="59"/>
-    <row r="260" ht="15.75" customHeight="1" s="59"/>
-    <row r="261" ht="15.75" customHeight="1" s="59"/>
-    <row r="262" ht="15.75" customHeight="1" s="59"/>
-    <row r="263" ht="15.75" customHeight="1" s="59"/>
-    <row r="264" ht="15.75" customHeight="1" s="59"/>
-    <row r="265" ht="15.75" customHeight="1" s="59"/>
-    <row r="266" ht="15.75" customHeight="1" s="59"/>
-    <row r="267" ht="15.75" customHeight="1" s="59"/>
-    <row r="268" ht="15.75" customHeight="1" s="59"/>
-    <row r="269" ht="15.75" customHeight="1" s="59"/>
-    <row r="270" ht="15.75" customHeight="1" s="59"/>
-    <row r="271" ht="15.75" customHeight="1" s="59"/>
-    <row r="272" ht="15.75" customHeight="1" s="59"/>
-    <row r="273" ht="15.75" customHeight="1" s="59"/>
-    <row r="274" ht="15.75" customHeight="1" s="59"/>
-    <row r="275" ht="15.75" customHeight="1" s="59"/>
-    <row r="276" ht="15.75" customHeight="1" s="59"/>
-    <row r="277" ht="15.75" customHeight="1" s="59"/>
-    <row r="278" ht="15.75" customHeight="1" s="59"/>
-    <row r="279" ht="15.75" customHeight="1" s="59"/>
-    <row r="280" ht="15.75" customHeight="1" s="59"/>
-    <row r="281" ht="15.75" customHeight="1" s="59"/>
-    <row r="282" ht="15.75" customHeight="1" s="59"/>
-    <row r="283" ht="15.75" customHeight="1" s="59"/>
-    <row r="284" ht="15.75" customHeight="1" s="59"/>
-    <row r="285" ht="15.75" customHeight="1" s="59"/>
-    <row r="286" ht="15.75" customHeight="1" s="59"/>
-    <row r="287" ht="15.75" customHeight="1" s="59"/>
-    <row r="288" ht="15.75" customHeight="1" s="59"/>
-    <row r="289" ht="15.75" customHeight="1" s="59"/>
-    <row r="290" ht="15.75" customHeight="1" s="59"/>
-    <row r="291" ht="15.75" customHeight="1" s="59"/>
-    <row r="292" ht="15.75" customHeight="1" s="59"/>
-    <row r="293" ht="15.75" customHeight="1" s="59"/>
-    <row r="294" ht="15.75" customHeight="1" s="59"/>
-    <row r="295" ht="15.75" customHeight="1" s="59"/>
-    <row r="296" ht="15.75" customHeight="1" s="59"/>
-    <row r="297" ht="15.75" customHeight="1" s="59"/>
-    <row r="298" ht="15.75" customHeight="1" s="59"/>
-    <row r="299" ht="15.75" customHeight="1" s="59"/>
-    <row r="300" ht="15.75" customHeight="1" s="59"/>
-    <row r="301" ht="15.75" customHeight="1" s="59"/>
-    <row r="302" ht="15.75" customHeight="1" s="59"/>
-    <row r="303" ht="15.75" customHeight="1" s="59"/>
-    <row r="304" ht="15.75" customHeight="1" s="59"/>
-    <row r="305" ht="15.75" customHeight="1" s="59"/>
-    <row r="306" ht="15.75" customHeight="1" s="59"/>
-    <row r="307" ht="15.75" customHeight="1" s="59"/>
-    <row r="308" ht="15.75" customHeight="1" s="59"/>
-    <row r="309" ht="15.75" customHeight="1" s="59"/>
-    <row r="310" ht="15.75" customHeight="1" s="59"/>
-    <row r="311" ht="15.75" customHeight="1" s="59"/>
-    <row r="312" ht="15.75" customHeight="1" s="59"/>
-    <row r="313" ht="15.75" customHeight="1" s="59"/>
-    <row r="314" ht="15.75" customHeight="1" s="59"/>
-    <row r="315" ht="15.75" customHeight="1" s="59"/>
-    <row r="316" ht="15.75" customHeight="1" s="59"/>
-    <row r="317" ht="15.75" customHeight="1" s="59"/>
-    <row r="318" ht="15.75" customHeight="1" s="59"/>
-    <row r="319" ht="15.75" customHeight="1" s="59"/>
-    <row r="320" ht="15.75" customHeight="1" s="59"/>
-    <row r="321" ht="15.75" customHeight="1" s="59"/>
-    <row r="322" ht="15.75" customHeight="1" s="59"/>
-    <row r="323" ht="15.75" customHeight="1" s="59"/>
-    <row r="324" ht="15.75" customHeight="1" s="59"/>
-    <row r="325" ht="15.75" customHeight="1" s="59"/>
-    <row r="326" ht="15.75" customHeight="1" s="59"/>
-    <row r="327" ht="15.75" customHeight="1" s="59"/>
-    <row r="328" ht="15.75" customHeight="1" s="59"/>
-    <row r="329" ht="15.75" customHeight="1" s="59"/>
-    <row r="330" ht="15.75" customHeight="1" s="59"/>
-    <row r="331" ht="15.75" customHeight="1" s="59"/>
-    <row r="332" ht="15.75" customHeight="1" s="59"/>
-    <row r="333" ht="15.75" customHeight="1" s="59"/>
-    <row r="334" ht="15.75" customHeight="1" s="59"/>
-    <row r="335" ht="15.75" customHeight="1" s="59"/>
-    <row r="336" ht="15.75" customHeight="1" s="59"/>
-    <row r="337" ht="15.75" customHeight="1" s="59"/>
-    <row r="338" ht="15.75" customHeight="1" s="59"/>
-    <row r="339" ht="15.75" customHeight="1" s="59"/>
-    <row r="340" ht="15.75" customHeight="1" s="59"/>
-    <row r="341" ht="15.75" customHeight="1" s="59"/>
-    <row r="342" ht="15.75" customHeight="1" s="59"/>
-    <row r="343" ht="15.75" customHeight="1" s="59"/>
-    <row r="344" ht="15.75" customHeight="1" s="59"/>
-    <row r="345" ht="15.75" customHeight="1" s="59"/>
-    <row r="346" ht="15.75" customHeight="1" s="59"/>
-    <row r="347" ht="15.75" customHeight="1" s="59"/>
-    <row r="348" ht="15.75" customHeight="1" s="59"/>
-    <row r="349" ht="15.75" customHeight="1" s="59"/>
-    <row r="350" ht="15.75" customHeight="1" s="59"/>
-    <row r="351" ht="15.75" customHeight="1" s="59"/>
-    <row r="352" ht="15.75" customHeight="1" s="59"/>
-    <row r="353" ht="15.75" customHeight="1" s="59"/>
-    <row r="354" ht="15.75" customHeight="1" s="59"/>
-    <row r="355" ht="15.75" customHeight="1" s="59"/>
-    <row r="356" ht="15.75" customHeight="1" s="59"/>
-    <row r="357" ht="15.75" customHeight="1" s="59"/>
-    <row r="358" ht="15.75" customHeight="1" s="59"/>
-    <row r="359" ht="15.75" customHeight="1" s="59"/>
-    <row r="360" ht="15.75" customHeight="1" s="59"/>
-    <row r="361" ht="15.75" customHeight="1" s="59"/>
-    <row r="362" ht="15.75" customHeight="1" s="59"/>
-    <row r="363" ht="15.75" customHeight="1" s="59"/>
-    <row r="364" ht="15.75" customHeight="1" s="59"/>
-    <row r="365" ht="15.75" customHeight="1" s="59"/>
-    <row r="366" ht="15.75" customHeight="1" s="59"/>
-    <row r="367" ht="15.75" customHeight="1" s="59"/>
-    <row r="368" ht="15.75" customHeight="1" s="59"/>
-    <row r="369" ht="15.75" customHeight="1" s="59"/>
-    <row r="370" ht="15.75" customHeight="1" s="59"/>
-    <row r="371" ht="15.75" customHeight="1" s="59"/>
-    <row r="372" ht="15.75" customHeight="1" s="59"/>
-    <row r="373" ht="15.75" customHeight="1" s="59"/>
-    <row r="374" ht="15.75" customHeight="1" s="59"/>
-    <row r="375" ht="15.75" customHeight="1" s="59"/>
-    <row r="376" ht="15.75" customHeight="1" s="59"/>
-    <row r="377" ht="15.75" customHeight="1" s="59"/>
-    <row r="378" ht="15.75" customHeight="1" s="59"/>
-    <row r="379" ht="15.75" customHeight="1" s="59"/>
-    <row r="380" ht="15.75" customHeight="1" s="59"/>
-    <row r="381" ht="15.75" customHeight="1" s="59"/>
-    <row r="382" ht="15.75" customHeight="1" s="59"/>
-    <row r="383" ht="15.75" customHeight="1" s="59"/>
-    <row r="384" ht="15.75" customHeight="1" s="59"/>
-    <row r="385" ht="15.75" customHeight="1" s="59"/>
-    <row r="386" ht="15.75" customHeight="1" s="59"/>
-    <row r="387" ht="15.75" customHeight="1" s="59"/>
-    <row r="388" ht="15.75" customHeight="1" s="59"/>
-    <row r="389" ht="15.75" customHeight="1" s="59"/>
-    <row r="390" ht="15.75" customHeight="1" s="59"/>
-    <row r="391" ht="15.75" customHeight="1" s="59"/>
-    <row r="392" ht="15.75" customHeight="1" s="59"/>
-    <row r="393" ht="15.75" customHeight="1" s="59"/>
-    <row r="394" ht="15.75" customHeight="1" s="59"/>
-    <row r="395" ht="15.75" customHeight="1" s="59"/>
-    <row r="396" ht="15.75" customHeight="1" s="59"/>
-    <row r="397" ht="15.75" customHeight="1" s="59"/>
-    <row r="398" ht="15.75" customHeight="1" s="59"/>
-    <row r="399" ht="15.75" customHeight="1" s="59"/>
-    <row r="400" ht="15.75" customHeight="1" s="59"/>
-    <row r="401" ht="15.75" customHeight="1" s="59"/>
-    <row r="402" ht="15.75" customHeight="1" s="59"/>
-    <row r="403" ht="15.75" customHeight="1" s="59"/>
-    <row r="404" ht="15.75" customHeight="1" s="59"/>
-    <row r="405" ht="15.75" customHeight="1" s="59"/>
-    <row r="406" ht="15.75" customHeight="1" s="59"/>
-    <row r="407" ht="15.75" customHeight="1" s="59"/>
-    <row r="408" ht="15.75" customHeight="1" s="59"/>
-    <row r="409" ht="15.75" customHeight="1" s="59"/>
-    <row r="410" ht="15.75" customHeight="1" s="59"/>
-    <row r="411" ht="15.75" customHeight="1" s="59"/>
-    <row r="412" ht="15.75" customHeight="1" s="59"/>
-    <row r="413" ht="15.75" customHeight="1" s="59"/>
-    <row r="414" ht="15.75" customHeight="1" s="59"/>
-    <row r="415" ht="15.75" customHeight="1" s="59"/>
-    <row r="416" ht="15.75" customHeight="1" s="59"/>
-    <row r="417" ht="15.75" customHeight="1" s="59"/>
-    <row r="418" ht="15.75" customHeight="1" s="59"/>
-    <row r="419" ht="15.75" customHeight="1" s="59"/>
-    <row r="420" ht="15.75" customHeight="1" s="59"/>
-    <row r="421" ht="15.75" customHeight="1" s="59"/>
-    <row r="422" ht="15.75" customHeight="1" s="59"/>
-    <row r="423" ht="15.75" customHeight="1" s="59"/>
-    <row r="424" ht="15.75" customHeight="1" s="59"/>
-    <row r="425" ht="15.75" customHeight="1" s="59"/>
-    <row r="426" ht="15.75" customHeight="1" s="59"/>
-    <row r="427" ht="15.75" customHeight="1" s="59"/>
-    <row r="428" ht="15.75" customHeight="1" s="59"/>
-    <row r="429" ht="15.75" customHeight="1" s="59"/>
-    <row r="430" ht="15.75" customHeight="1" s="59"/>
-    <row r="431" ht="15.75" customHeight="1" s="59"/>
-    <row r="432" ht="15.75" customHeight="1" s="59"/>
-    <row r="433" ht="15.75" customHeight="1" s="59"/>
-    <row r="434" ht="15.75" customHeight="1" s="59"/>
-    <row r="435" ht="15.75" customHeight="1" s="59"/>
-    <row r="436" ht="15.75" customHeight="1" s="59"/>
-    <row r="437" ht="15.75" customHeight="1" s="59"/>
-    <row r="438" ht="15.75" customHeight="1" s="59"/>
-    <row r="439" ht="15.75" customHeight="1" s="59"/>
-    <row r="440" ht="15.75" customHeight="1" s="59"/>
-    <row r="441" ht="15.75" customHeight="1" s="59"/>
-    <row r="442" ht="15.75" customHeight="1" s="59"/>
-    <row r="443" ht="15.75" customHeight="1" s="59"/>
-    <row r="444" ht="15.75" customHeight="1" s="59"/>
-    <row r="445" ht="15.75" customHeight="1" s="59"/>
-    <row r="446" ht="15.75" customHeight="1" s="59"/>
-    <row r="447" ht="15.75" customHeight="1" s="59"/>
-    <row r="448" ht="15.75" customHeight="1" s="59"/>
-    <row r="449" ht="15.75" customHeight="1" s="59"/>
-    <row r="450" ht="15.75" customHeight="1" s="59"/>
-    <row r="451" ht="15.75" customHeight="1" s="59"/>
-    <row r="452" ht="15.75" customHeight="1" s="59"/>
-    <row r="453" ht="15.75" customHeight="1" s="59"/>
-    <row r="454" ht="15.75" customHeight="1" s="59"/>
-    <row r="455" ht="15.75" customHeight="1" s="59"/>
-    <row r="456" ht="15.75" customHeight="1" s="59"/>
-    <row r="457" ht="15.75" customHeight="1" s="59"/>
-    <row r="458" ht="15.75" customHeight="1" s="59"/>
-    <row r="459" ht="15.75" customHeight="1" s="59"/>
-    <row r="460" ht="15.75" customHeight="1" s="59"/>
-    <row r="461" ht="15.75" customHeight="1" s="59"/>
-    <row r="462" ht="15.75" customHeight="1" s="59"/>
-    <row r="463" ht="15.75" customHeight="1" s="59"/>
-    <row r="464" ht="15.75" customHeight="1" s="59"/>
-    <row r="465" ht="15.75" customHeight="1" s="59"/>
-    <row r="466" ht="15.75" customHeight="1" s="59"/>
-    <row r="467" ht="15.75" customHeight="1" s="59"/>
-    <row r="468" ht="15.75" customHeight="1" s="59"/>
-    <row r="469" ht="15.75" customHeight="1" s="59"/>
-    <row r="470" ht="15.75" customHeight="1" s="59"/>
-    <row r="471" ht="15.75" customHeight="1" s="59"/>
-    <row r="472" ht="15.75" customHeight="1" s="59"/>
-    <row r="473" ht="15.75" customHeight="1" s="59"/>
-    <row r="474" ht="15.75" customHeight="1" s="59"/>
-    <row r="475" ht="15.75" customHeight="1" s="59"/>
-    <row r="476" ht="15.75" customHeight="1" s="59"/>
-    <row r="477" ht="15.75" customHeight="1" s="59"/>
-    <row r="478" ht="15.75" customHeight="1" s="59"/>
-    <row r="479" ht="15.75" customHeight="1" s="59"/>
-    <row r="480" ht="15.75" customHeight="1" s="59"/>
-    <row r="481" ht="15.75" customHeight="1" s="59"/>
-    <row r="482" ht="15.75" customHeight="1" s="59"/>
-    <row r="483" ht="15.75" customHeight="1" s="59"/>
-    <row r="484" ht="15.75" customHeight="1" s="59"/>
-    <row r="485" ht="15.75" customHeight="1" s="59"/>
-    <row r="486" ht="15.75" customHeight="1" s="59"/>
-    <row r="487" ht="15.75" customHeight="1" s="59"/>
-    <row r="488" ht="15.75" customHeight="1" s="59"/>
-    <row r="489" ht="15.75" customHeight="1" s="59"/>
-    <row r="490" ht="15.75" customHeight="1" s="59"/>
-    <row r="491" ht="15.75" customHeight="1" s="59"/>
-    <row r="492" ht="15.75" customHeight="1" s="59"/>
-    <row r="493" ht="15.75" customHeight="1" s="59"/>
-    <row r="494" ht="15.75" customHeight="1" s="59"/>
-    <row r="495" ht="15.75" customHeight="1" s="59"/>
-    <row r="496" ht="15.75" customHeight="1" s="59"/>
-    <row r="497" ht="15.75" customHeight="1" s="59"/>
-    <row r="498" ht="15.75" customHeight="1" s="59"/>
-    <row r="499" ht="15.75" customHeight="1" s="59"/>
-    <row r="500" ht="15.75" customHeight="1" s="59"/>
-    <row r="501" ht="15.75" customHeight="1" s="59"/>
-    <row r="502" ht="15.75" customHeight="1" s="59"/>
-    <row r="503" ht="15.75" customHeight="1" s="59"/>
-    <row r="504" ht="15.75" customHeight="1" s="59"/>
-    <row r="505" ht="15.75" customHeight="1" s="59"/>
-    <row r="506" ht="15.75" customHeight="1" s="59"/>
-    <row r="507" ht="15.75" customHeight="1" s="59"/>
-    <row r="508" ht="15.75" customHeight="1" s="59"/>
-    <row r="509" ht="15.75" customHeight="1" s="59"/>
-    <row r="510" ht="15.75" customHeight="1" s="59"/>
-    <row r="511" ht="15.75" customHeight="1" s="59"/>
-    <row r="512" ht="15.75" customHeight="1" s="59"/>
-    <row r="513" ht="15.75" customHeight="1" s="59"/>
-    <row r="514" ht="15.75" customHeight="1" s="59"/>
-    <row r="515" ht="15.75" customHeight="1" s="59"/>
-    <row r="516" ht="15.75" customHeight="1" s="59"/>
-    <row r="517" ht="15.75" customHeight="1" s="59"/>
-    <row r="518" ht="15.75" customHeight="1" s="59"/>
-    <row r="519" ht="15.75" customHeight="1" s="59"/>
-    <row r="520" ht="15.75" customHeight="1" s="59"/>
-    <row r="521" ht="15.75" customHeight="1" s="59"/>
-    <row r="522" ht="15.75" customHeight="1" s="59"/>
-    <row r="523" ht="15.75" customHeight="1" s="59"/>
-    <row r="524" ht="15.75" customHeight="1" s="59"/>
-    <row r="525" ht="15.75" customHeight="1" s="59"/>
-    <row r="526" ht="15.75" customHeight="1" s="59"/>
-    <row r="527" ht="15.75" customHeight="1" s="59"/>
-    <row r="528" ht="15.75" customHeight="1" s="59"/>
-    <row r="529" ht="15.75" customHeight="1" s="59"/>
-    <row r="530" ht="15.75" customHeight="1" s="59"/>
-    <row r="531" ht="15.75" customHeight="1" s="59"/>
-    <row r="532" ht="15.75" customHeight="1" s="59"/>
-    <row r="533" ht="15.75" customHeight="1" s="59"/>
-    <row r="534" ht="15.75" customHeight="1" s="59"/>
-    <row r="535" ht="15.75" customHeight="1" s="59"/>
-    <row r="536" ht="15.75" customHeight="1" s="59"/>
-    <row r="537" ht="15.75" customHeight="1" s="59"/>
-    <row r="538" ht="15.75" customHeight="1" s="59"/>
-    <row r="539" ht="15.75" customHeight="1" s="59"/>
-    <row r="540" ht="15.75" customHeight="1" s="59"/>
-    <row r="541" ht="15.75" customHeight="1" s="59"/>
-    <row r="542" ht="15.75" customHeight="1" s="59"/>
-    <row r="543" ht="15.75" customHeight="1" s="59"/>
-    <row r="544" ht="15.75" customHeight="1" s="59"/>
-    <row r="545" ht="15.75" customHeight="1" s="59"/>
-    <row r="546" ht="15.75" customHeight="1" s="59"/>
-    <row r="547" ht="15.75" customHeight="1" s="59"/>
-    <row r="548" ht="15.75" customHeight="1" s="59"/>
-    <row r="549" ht="15.75" customHeight="1" s="59"/>
-    <row r="550" ht="15.75" customHeight="1" s="59"/>
-    <row r="551" ht="15.75" customHeight="1" s="59"/>
-    <row r="552" ht="15.75" customHeight="1" s="59"/>
-    <row r="553" ht="15.75" customHeight="1" s="59"/>
-    <row r="554" ht="15.75" customHeight="1" s="59"/>
-    <row r="555" ht="15.75" customHeight="1" s="59"/>
-    <row r="556" ht="15.75" customHeight="1" s="59"/>
-    <row r="557" ht="15.75" customHeight="1" s="59"/>
-    <row r="558" ht="15.75" customHeight="1" s="59"/>
-    <row r="559" ht="15.75" customHeight="1" s="59"/>
-    <row r="560" ht="15.75" customHeight="1" s="59"/>
-    <row r="561" ht="15.75" customHeight="1" s="59"/>
-    <row r="562" ht="15.75" customHeight="1" s="59"/>
-    <row r="563" ht="15.75" customHeight="1" s="59"/>
-    <row r="564" ht="15.75" customHeight="1" s="59"/>
-    <row r="565" ht="15.75" customHeight="1" s="59"/>
-    <row r="566" ht="15.75" customHeight="1" s="59"/>
-    <row r="567" ht="15.75" customHeight="1" s="59"/>
-    <row r="568" ht="15.75" customHeight="1" s="59"/>
-    <row r="569" ht="15.75" customHeight="1" s="59"/>
-    <row r="570" ht="15.75" customHeight="1" s="59"/>
-    <row r="571" ht="15.75" customHeight="1" s="59"/>
-    <row r="572" ht="15.75" customHeight="1" s="59"/>
-    <row r="573" ht="15.75" customHeight="1" s="59"/>
-    <row r="574" ht="15.75" customHeight="1" s="59"/>
-    <row r="575" ht="15.75" customHeight="1" s="59"/>
-    <row r="576" ht="15.75" customHeight="1" s="59"/>
-    <row r="577" ht="15.75" customHeight="1" s="59"/>
-    <row r="578" ht="15.75" customHeight="1" s="59"/>
-    <row r="579" ht="15.75" customHeight="1" s="59"/>
-    <row r="580" ht="15.75" customHeight="1" s="59"/>
-    <row r="581" ht="15.75" customHeight="1" s="59"/>
-    <row r="582" ht="15.75" customHeight="1" s="59"/>
-    <row r="583" ht="15.75" customHeight="1" s="59"/>
-    <row r="584" ht="15.75" customHeight="1" s="59"/>
-    <row r="585" ht="15.75" customHeight="1" s="59"/>
-    <row r="586" ht="15.75" customHeight="1" s="59"/>
-    <row r="587" ht="15.75" customHeight="1" s="59"/>
-    <row r="588" ht="15.75" customHeight="1" s="59"/>
-    <row r="589" ht="15.75" customHeight="1" s="59"/>
-    <row r="590" ht="15.75" customHeight="1" s="59"/>
-    <row r="591" ht="15.75" customHeight="1" s="59"/>
-    <row r="592" ht="15.75" customHeight="1" s="59"/>
-    <row r="593" ht="15.75" customHeight="1" s="59"/>
-    <row r="594" ht="15.75" customHeight="1" s="59"/>
-    <row r="595" ht="15.75" customHeight="1" s="59"/>
-    <row r="596" ht="15.75" customHeight="1" s="59"/>
-    <row r="597" ht="15.75" customHeight="1" s="59"/>
-    <row r="598" ht="15.75" customHeight="1" s="59"/>
-    <row r="599" ht="15.75" customHeight="1" s="59"/>
-    <row r="600" ht="15.75" customHeight="1" s="59"/>
-    <row r="601" ht="15.75" customHeight="1" s="59"/>
-    <row r="602" ht="15.75" customHeight="1" s="59"/>
-    <row r="603" ht="15.75" customHeight="1" s="59"/>
-    <row r="604" ht="15.75" customHeight="1" s="59"/>
-    <row r="605" ht="15.75" customHeight="1" s="59"/>
-    <row r="606" ht="15.75" customHeight="1" s="59"/>
-    <row r="607" ht="15.75" customHeight="1" s="59"/>
-    <row r="608" ht="15.75" customHeight="1" s="59"/>
-    <row r="609" ht="15.75" customHeight="1" s="59"/>
-    <row r="610" ht="15.75" customHeight="1" s="59"/>
-    <row r="611" ht="15.75" customHeight="1" s="59"/>
-    <row r="612" ht="15.75" customHeight="1" s="59"/>
-    <row r="613" ht="15.75" customHeight="1" s="59"/>
-    <row r="614" ht="15.75" customHeight="1" s="59"/>
-    <row r="615" ht="15.75" customHeight="1" s="59"/>
-    <row r="616" ht="15.75" customHeight="1" s="59"/>
-    <row r="617" ht="15.75" customHeight="1" s="59"/>
-    <row r="618" ht="15.75" customHeight="1" s="59"/>
-    <row r="619" ht="15.75" customHeight="1" s="59"/>
-    <row r="620" ht="15.75" customHeight="1" s="59"/>
-    <row r="621" ht="15.75" customHeight="1" s="59"/>
-    <row r="622" ht="15.75" customHeight="1" s="59"/>
-    <row r="623" ht="15.75" customHeight="1" s="59"/>
-    <row r="624" ht="15.75" customHeight="1" s="59"/>
-    <row r="625" ht="15.75" customHeight="1" s="59"/>
-    <row r="626" ht="15.75" customHeight="1" s="59"/>
-    <row r="627" ht="15.75" customHeight="1" s="59"/>
-    <row r="628" ht="15.75" customHeight="1" s="59"/>
-    <row r="629" ht="15.75" customHeight="1" s="59"/>
-    <row r="630" ht="15.75" customHeight="1" s="59"/>
-    <row r="631" ht="15.75" customHeight="1" s="59"/>
-    <row r="632" ht="15.75" customHeight="1" s="59"/>
-    <row r="633" ht="15.75" customHeight="1" s="59"/>
-    <row r="634" ht="15.75" customHeight="1" s="59"/>
-    <row r="635" ht="15.75" customHeight="1" s="59"/>
-    <row r="636" ht="15.75" customHeight="1" s="59"/>
-    <row r="637" ht="15.75" customHeight="1" s="59"/>
-    <row r="638" ht="15.75" customHeight="1" s="59"/>
-    <row r="639" ht="15.75" customHeight="1" s="59"/>
-    <row r="640" ht="15.75" customHeight="1" s="59"/>
-    <row r="641" ht="15.75" customHeight="1" s="59"/>
-    <row r="642" ht="15.75" customHeight="1" s="59"/>
-    <row r="643" ht="15.75" customHeight="1" s="59"/>
-    <row r="644" ht="15.75" customHeight="1" s="59"/>
-    <row r="645" ht="15.75" customHeight="1" s="59"/>
-    <row r="646" ht="15.75" customHeight="1" s="59"/>
-    <row r="647" ht="15.75" customHeight="1" s="59"/>
-    <row r="648" ht="15.75" customHeight="1" s="59"/>
-    <row r="649" ht="15.75" customHeight="1" s="59"/>
-    <row r="650" ht="15.75" customHeight="1" s="59"/>
-    <row r="651" ht="15.75" customHeight="1" s="59"/>
-    <row r="652" ht="15.75" customHeight="1" s="59"/>
-    <row r="653" ht="15.75" customHeight="1" s="59"/>
-    <row r="654" ht="15.75" customHeight="1" s="59"/>
-    <row r="655" ht="15.75" customHeight="1" s="59"/>
-    <row r="656" ht="15.75" customHeight="1" s="59"/>
-    <row r="657" ht="15.75" customHeight="1" s="59"/>
-    <row r="658" ht="15.75" customHeight="1" s="59"/>
-    <row r="659" ht="15.75" customHeight="1" s="59"/>
-    <row r="660" ht="15.75" customHeight="1" s="59"/>
-    <row r="661" ht="15.75" customHeight="1" s="59"/>
-    <row r="662" ht="15.75" customHeight="1" s="59"/>
-    <row r="663" ht="15.75" customHeight="1" s="59"/>
-    <row r="664" ht="15.75" customHeight="1" s="59"/>
-    <row r="665" ht="15.75" customHeight="1" s="59"/>
-    <row r="666" ht="15.75" customHeight="1" s="59"/>
-    <row r="667" ht="15.75" customHeight="1" s="59"/>
-    <row r="668" ht="15.75" customHeight="1" s="59"/>
-    <row r="669" ht="15.75" customHeight="1" s="59"/>
-    <row r="670" ht="15.75" customHeight="1" s="59"/>
-    <row r="671" ht="15.75" customHeight="1" s="59"/>
-    <row r="672" ht="15.75" customHeight="1" s="59"/>
-    <row r="673" ht="15.75" customHeight="1" s="59"/>
-    <row r="674" ht="15.75" customHeight="1" s="59"/>
-    <row r="675" ht="15.75" customHeight="1" s="59"/>
-    <row r="676" ht="15.75" customHeight="1" s="59"/>
-    <row r="677" ht="15.75" customHeight="1" s="59"/>
-    <row r="678" ht="15.75" customHeight="1" s="59"/>
-    <row r="679" ht="15.75" customHeight="1" s="59"/>
-    <row r="680" ht="15.75" customHeight="1" s="59"/>
-    <row r="681" ht="15.75" customHeight="1" s="59"/>
-    <row r="682" ht="15.75" customHeight="1" s="59"/>
-    <row r="683" ht="15.75" customHeight="1" s="59"/>
-    <row r="684" ht="15.75" customHeight="1" s="59"/>
-    <row r="685" ht="15.75" customHeight="1" s="59"/>
-    <row r="686" ht="15.75" customHeight="1" s="59"/>
-    <row r="687" ht="15.75" customHeight="1" s="59"/>
-    <row r="688" ht="15.75" customHeight="1" s="59"/>
-    <row r="689" ht="15.75" customHeight="1" s="59"/>
-    <row r="690" ht="15.75" customHeight="1" s="59"/>
-    <row r="691" ht="15.75" customHeight="1" s="59"/>
-    <row r="692" ht="15.75" customHeight="1" s="59"/>
-    <row r="693" ht="15.75" customHeight="1" s="59"/>
-    <row r="694" ht="15.75" customHeight="1" s="59"/>
-    <row r="695" ht="15.75" customHeight="1" s="59"/>
-    <row r="696" ht="15.75" customHeight="1" s="59"/>
-    <row r="697" ht="15.75" customHeight="1" s="59"/>
-    <row r="698" ht="15.75" customHeight="1" s="59"/>
-    <row r="699" ht="15.75" customHeight="1" s="59"/>
-    <row r="700" ht="15.75" customHeight="1" s="59"/>
-    <row r="701" ht="15.75" customHeight="1" s="59"/>
-    <row r="702" ht="15.75" customHeight="1" s="59"/>
-    <row r="703" ht="15.75" customHeight="1" s="59"/>
-    <row r="704" ht="15.75" customHeight="1" s="59"/>
-    <row r="705" ht="15.75" customHeight="1" s="59"/>
-    <row r="706" ht="15.75" customHeight="1" s="59"/>
-    <row r="707" ht="15.75" customHeight="1" s="59"/>
-    <row r="708" ht="15.75" customHeight="1" s="59"/>
-    <row r="709" ht="15.75" customHeight="1" s="59"/>
-    <row r="710" ht="15.75" customHeight="1" s="59"/>
-    <row r="711" ht="15.75" customHeight="1" s="59"/>
-    <row r="712" ht="15.75" customHeight="1" s="59"/>
-    <row r="713" ht="15.75" customHeight="1" s="59"/>
-    <row r="714" ht="15.75" customHeight="1" s="59"/>
-    <row r="715" ht="15.75" customHeight="1" s="59"/>
-    <row r="716" ht="15.75" customHeight="1" s="59"/>
-    <row r="717" ht="15.75" customHeight="1" s="59"/>
-    <row r="718" ht="15.75" customHeight="1" s="59"/>
-    <row r="719" ht="15.75" customHeight="1" s="59"/>
-    <row r="720" ht="15.75" customHeight="1" s="59"/>
-    <row r="721" ht="15.75" customHeight="1" s="59"/>
-    <row r="722" ht="15.75" customHeight="1" s="59"/>
-    <row r="723" ht="15.75" customHeight="1" s="59"/>
-    <row r="724" ht="15.75" customHeight="1" s="59"/>
-    <row r="725" ht="15.75" customHeight="1" s="59"/>
-    <row r="726" ht="15.75" customHeight="1" s="59"/>
-    <row r="727" ht="15.75" customHeight="1" s="59"/>
-    <row r="728" ht="15.75" customHeight="1" s="59"/>
-    <row r="729" ht="15.75" customHeight="1" s="59"/>
-    <row r="730" ht="15.75" customHeight="1" s="59"/>
-    <row r="731" ht="15.75" customHeight="1" s="59"/>
-    <row r="732" ht="15.75" customHeight="1" s="59"/>
-    <row r="733" ht="15.75" customHeight="1" s="59"/>
-    <row r="734" ht="15.75" customHeight="1" s="59"/>
-    <row r="735" ht="15.75" customHeight="1" s="59"/>
-    <row r="736" ht="15.75" customHeight="1" s="59"/>
-    <row r="737" ht="15.75" customHeight="1" s="59"/>
-    <row r="738" ht="15.75" customHeight="1" s="59"/>
-    <row r="739" ht="15.75" customHeight="1" s="59"/>
-    <row r="740" ht="15.75" customHeight="1" s="59"/>
-    <row r="741" ht="15.75" customHeight="1" s="59"/>
-    <row r="742" ht="15.75" customHeight="1" s="59"/>
-    <row r="743" ht="15.75" customHeight="1" s="59"/>
-    <row r="744" ht="15.75" customHeight="1" s="59"/>
-    <row r="745" ht="15.75" customHeight="1" s="59"/>
-    <row r="746" ht="15.75" customHeight="1" s="59"/>
-    <row r="747" ht="15.75" customHeight="1" s="59"/>
-    <row r="748" ht="15.75" customHeight="1" s="59"/>
-    <row r="749" ht="15.75" customHeight="1" s="59"/>
-    <row r="750" ht="15.75" customHeight="1" s="59"/>
-    <row r="751" ht="15.75" customHeight="1" s="59"/>
-    <row r="752" ht="15.75" customHeight="1" s="59"/>
-    <row r="753" ht="15.75" customHeight="1" s="59"/>
-    <row r="754" ht="15.75" customHeight="1" s="59"/>
-    <row r="755" ht="15.75" customHeight="1" s="59"/>
-    <row r="756" ht="15.75" customHeight="1" s="59"/>
-    <row r="757" ht="15.75" customHeight="1" s="59"/>
-    <row r="758" ht="15.75" customHeight="1" s="59"/>
-    <row r="759" ht="15.75" customHeight="1" s="59"/>
-    <row r="760" ht="15.75" customHeight="1" s="59"/>
-    <row r="761" ht="15.75" customHeight="1" s="59"/>
-    <row r="762" ht="15.75" customHeight="1" s="59"/>
-    <row r="763" ht="15.75" customHeight="1" s="59"/>
-    <row r="764" ht="15.75" customHeight="1" s="59"/>
-    <row r="765" ht="15.75" customHeight="1" s="59"/>
-    <row r="766" ht="15.75" customHeight="1" s="59"/>
-    <row r="767" ht="15.75" customHeight="1" s="59"/>
-    <row r="768" ht="15.75" customHeight="1" s="59"/>
-    <row r="769" ht="15.75" customHeight="1" s="59"/>
-    <row r="770" ht="15.75" customHeight="1" s="59"/>
-    <row r="771" ht="15.75" customHeight="1" s="59"/>
-    <row r="772" ht="15.75" customHeight="1" s="59"/>
-    <row r="773" ht="15.75" customHeight="1" s="59"/>
-    <row r="774" ht="15.75" customHeight="1" s="59"/>
-    <row r="775" ht="15.75" customHeight="1" s="59"/>
-    <row r="776" ht="15.75" customHeight="1" s="59"/>
-    <row r="777" ht="15.75" customHeight="1" s="59"/>
-    <row r="778" ht="15.75" customHeight="1" s="59"/>
-    <row r="779" ht="15.75" customHeight="1" s="59"/>
-    <row r="780" ht="15.75" customHeight="1" s="59"/>
-    <row r="781" ht="15.75" customHeight="1" s="59"/>
-    <row r="782" ht="15.75" customHeight="1" s="59"/>
-    <row r="783" ht="15.75" customHeight="1" s="59"/>
-    <row r="784" ht="15.75" customHeight="1" s="59"/>
-    <row r="785" ht="15.75" customHeight="1" s="59"/>
-    <row r="786" ht="15.75" customHeight="1" s="59"/>
-    <row r="787" ht="15.75" customHeight="1" s="59"/>
-    <row r="788" ht="15.75" customHeight="1" s="59"/>
-    <row r="789" ht="15.75" customHeight="1" s="59"/>
-    <row r="790" ht="15.75" customHeight="1" s="59"/>
-    <row r="791" ht="15.75" customHeight="1" s="59"/>
-    <row r="792" ht="15.75" customHeight="1" s="59"/>
-    <row r="793" ht="15.75" customHeight="1" s="59"/>
-    <row r="794" ht="15.75" customHeight="1" s="59"/>
-    <row r="795" ht="15.75" customHeight="1" s="59"/>
-    <row r="796" ht="15.75" customHeight="1" s="59"/>
-    <row r="797" ht="15.75" customHeight="1" s="59"/>
-    <row r="798" ht="15.75" customHeight="1" s="59"/>
-    <row r="799" ht="15.75" customHeight="1" s="59"/>
-    <row r="800" ht="15.75" customHeight="1" s="59"/>
-    <row r="801" ht="15.75" customHeight="1" s="59"/>
-    <row r="802" ht="15.75" customHeight="1" s="59"/>
-    <row r="803" ht="15.75" customHeight="1" s="59"/>
-    <row r="804" ht="15.75" customHeight="1" s="59"/>
-    <row r="805" ht="15.75" customHeight="1" s="59"/>
-    <row r="806" ht="15.75" customHeight="1" s="59"/>
-    <row r="807" ht="15.75" customHeight="1" s="59"/>
-    <row r="808" ht="15.75" customHeight="1" s="59"/>
-    <row r="809" ht="15.75" customHeight="1" s="59"/>
-    <row r="810" ht="15.75" customHeight="1" s="59"/>
-    <row r="811" ht="15.75" customHeight="1" s="59"/>
-    <row r="812" ht="15.75" customHeight="1" s="59"/>
-    <row r="813" ht="15.75" customHeight="1" s="59"/>
-    <row r="814" ht="15.75" customHeight="1" s="59"/>
-    <row r="815" ht="15.75" customHeight="1" s="59"/>
-    <row r="816" ht="15.75" customHeight="1" s="59"/>
-    <row r="817" ht="15.75" customHeight="1" s="59"/>
-    <row r="818" ht="15.75" customHeight="1" s="59"/>
-    <row r="819" ht="15.75" customHeight="1" s="59"/>
-    <row r="820" ht="15.75" customHeight="1" s="59"/>
-    <row r="821" ht="15.75" customHeight="1" s="59"/>
-    <row r="822" ht="15.75" customHeight="1" s="59"/>
-    <row r="823" ht="15.75" customHeight="1" s="59"/>
-    <row r="824" ht="15.75" customHeight="1" s="59"/>
-    <row r="825" ht="15.75" customHeight="1" s="59"/>
-    <row r="826" ht="15.75" customHeight="1" s="59"/>
-    <row r="827" ht="15.75" customHeight="1" s="59"/>
-    <row r="828" ht="15.75" customHeight="1" s="59"/>
-    <row r="829" ht="15.75" customHeight="1" s="59"/>
-    <row r="830" ht="15.75" customHeight="1" s="59"/>
-    <row r="831" ht="15.75" customHeight="1" s="59"/>
-    <row r="832" ht="15.75" customHeight="1" s="59"/>
-    <row r="833" ht="15.75" customHeight="1" s="59"/>
-    <row r="834" ht="15.75" customHeight="1" s="59"/>
-    <row r="835" ht="15.75" customHeight="1" s="59"/>
-    <row r="836" ht="15.75" customHeight="1" s="59"/>
-    <row r="837" ht="15.75" customHeight="1" s="59"/>
-    <row r="838" ht="15.75" customHeight="1" s="59"/>
-    <row r="839" ht="15.75" customHeight="1" s="59"/>
-    <row r="840" ht="15.75" customHeight="1" s="59"/>
-    <row r="841" ht="15.75" customHeight="1" s="59"/>
-    <row r="842" ht="15.75" customHeight="1" s="59"/>
-    <row r="843" ht="15.75" customHeight="1" s="59"/>
-    <row r="844" ht="15.75" customHeight="1" s="59"/>
-    <row r="845" ht="15.75" customHeight="1" s="59"/>
-    <row r="846" ht="15.75" customHeight="1" s="59"/>
-    <row r="847" ht="15.75" customHeight="1" s="59"/>
-    <row r="848" ht="15.75" customHeight="1" s="59"/>
-    <row r="849" ht="15.75" customHeight="1" s="59"/>
-    <row r="850" ht="15.75" customHeight="1" s="59"/>
-    <row r="851" ht="15.75" customHeight="1" s="59"/>
-    <row r="852" ht="15.75" customHeight="1" s="59"/>
-    <row r="853" ht="15.75" customHeight="1" s="59"/>
-    <row r="854" ht="15.75" customHeight="1" s="59"/>
-    <row r="855" ht="15.75" customHeight="1" s="59"/>
-    <row r="856" ht="15.75" customHeight="1" s="59"/>
-    <row r="857" ht="15.75" customHeight="1" s="59"/>
-    <row r="858" ht="15.75" customHeight="1" s="59"/>
-    <row r="859" ht="15.75" customHeight="1" s="59"/>
-    <row r="860" ht="15.75" customHeight="1" s="59"/>
-    <row r="861" ht="15.75" customHeight="1" s="59"/>
-    <row r="862" ht="15.75" customHeight="1" s="59"/>
-    <row r="863" ht="15.75" customHeight="1" s="59"/>
-    <row r="864" ht="15.75" customHeight="1" s="59"/>
-    <row r="865" ht="15.75" customHeight="1" s="59"/>
-    <row r="866" ht="15.75" customHeight="1" s="59"/>
-    <row r="867" ht="15.75" customHeight="1" s="59"/>
-    <row r="868" ht="15.75" customHeight="1" s="59"/>
-    <row r="869" ht="15.75" customHeight="1" s="59"/>
-    <row r="870" ht="15.75" customHeight="1" s="59"/>
-    <row r="871" ht="15.75" customHeight="1" s="59"/>
-    <row r="872" ht="15.75" customHeight="1" s="59"/>
-    <row r="873" ht="15.75" customHeight="1" s="59"/>
-    <row r="874" ht="15.75" customHeight="1" s="59"/>
-    <row r="875" ht="15.75" customHeight="1" s="59"/>
-    <row r="876" ht="15.75" customHeight="1" s="59"/>
-    <row r="877" ht="15.75" customHeight="1" s="59"/>
-    <row r="878" ht="15.75" customHeight="1" s="59"/>
-    <row r="879" ht="15.75" customHeight="1" s="59"/>
-    <row r="880" ht="15.75" customHeight="1" s="59"/>
-    <row r="881" ht="15.75" customHeight="1" s="59"/>
-    <row r="882" ht="15.75" customHeight="1" s="59"/>
-    <row r="883" ht="15.75" customHeight="1" s="59"/>
-    <row r="884" ht="15.75" customHeight="1" s="59"/>
-    <row r="885" ht="15.75" customHeight="1" s="59"/>
-    <row r="886" ht="15.75" customHeight="1" s="59"/>
-    <row r="887" ht="15.75" customHeight="1" s="59"/>
-    <row r="888" ht="15.75" customHeight="1" s="59"/>
-    <row r="889" ht="15.75" customHeight="1" s="59"/>
-    <row r="890" ht="15.75" customHeight="1" s="59"/>
-    <row r="891" ht="15.75" customHeight="1" s="59"/>
-    <row r="892" ht="15.75" customHeight="1" s="59"/>
-    <row r="893" ht="15.75" customHeight="1" s="59"/>
-    <row r="894" ht="15.75" customHeight="1" s="59"/>
-    <row r="895" ht="15.75" customHeight="1" s="59"/>
-    <row r="896" ht="15.75" customHeight="1" s="59"/>
-    <row r="897" ht="15.75" customHeight="1" s="59"/>
-    <row r="898" ht="15.75" customHeight="1" s="59"/>
-    <row r="899" ht="15.75" customHeight="1" s="59"/>
-    <row r="900" ht="15.75" customHeight="1" s="59"/>
-    <row r="901" ht="15.75" customHeight="1" s="59"/>
-    <row r="902" ht="15.75" customHeight="1" s="59"/>
-    <row r="903" ht="15.75" customHeight="1" s="59"/>
-    <row r="904" ht="15.75" customHeight="1" s="59"/>
-    <row r="905" ht="15.75" customHeight="1" s="59"/>
-    <row r="906" ht="15.75" customHeight="1" s="59"/>
-    <row r="907" ht="15.75" customHeight="1" s="59"/>
-    <row r="908" ht="15.75" customHeight="1" s="59"/>
-    <row r="909" ht="15.75" customHeight="1" s="59"/>
-    <row r="910" ht="15.75" customHeight="1" s="59"/>
-    <row r="911" ht="15.75" customHeight="1" s="59"/>
-    <row r="912" ht="15.75" customHeight="1" s="59"/>
-    <row r="913" ht="15.75" customHeight="1" s="59"/>
-    <row r="914" ht="15.75" customHeight="1" s="59"/>
-    <row r="915" ht="15.75" customHeight="1" s="59"/>
-    <row r="916" ht="15.75" customHeight="1" s="59"/>
-    <row r="917" ht="15.75" customHeight="1" s="59"/>
-    <row r="918" ht="15.75" customHeight="1" s="59"/>
-    <row r="919" ht="15.75" customHeight="1" s="59"/>
-    <row r="920" ht="15.75" customHeight="1" s="59"/>
-    <row r="921" ht="15.75" customHeight="1" s="59"/>
-    <row r="922" ht="15.75" customHeight="1" s="59"/>
-    <row r="923" ht="15.75" customHeight="1" s="59"/>
-    <row r="924" ht="15.75" customHeight="1" s="59"/>
-    <row r="925" ht="15.75" customHeight="1" s="59"/>
-    <row r="926" ht="15.75" customHeight="1" s="59"/>
-    <row r="927" ht="15.75" customHeight="1" s="59"/>
-    <row r="928" ht="15.75" customHeight="1" s="59"/>
-    <row r="929" ht="15.75" customHeight="1" s="59"/>
-    <row r="930" ht="15.75" customHeight="1" s="59"/>
-    <row r="931" ht="15.75" customHeight="1" s="59"/>
-    <row r="932" ht="15.75" customHeight="1" s="59"/>
-    <row r="933" ht="15.75" customHeight="1" s="59"/>
-    <row r="934" ht="15.75" customHeight="1" s="59"/>
-    <row r="935" ht="15.75" customHeight="1" s="59"/>
-    <row r="936" ht="15.75" customHeight="1" s="59"/>
-    <row r="937" ht="15.75" customHeight="1" s="59"/>
-    <row r="938" ht="15.75" customHeight="1" s="59"/>
-    <row r="939" ht="15.75" customHeight="1" s="59"/>
-    <row r="940" ht="15.75" customHeight="1" s="59"/>
-    <row r="941" ht="15.75" customHeight="1" s="59"/>
-    <row r="942" ht="15.75" customHeight="1" s="59"/>
-    <row r="943" ht="15.75" customHeight="1" s="59"/>
-    <row r="944" ht="15.75" customHeight="1" s="59"/>
-    <row r="945" ht="15.75" customHeight="1" s="59"/>
-    <row r="946" ht="15.75" customHeight="1" s="59"/>
-    <row r="947" ht="15.75" customHeight="1" s="59"/>
-    <row r="948" ht="15.75" customHeight="1" s="59"/>
-    <row r="949" ht="15.75" customHeight="1" s="59"/>
-    <row r="950" ht="15.75" customHeight="1" s="59"/>
-    <row r="951" ht="15.75" customHeight="1" s="59"/>
-    <row r="952" ht="15.75" customHeight="1" s="59"/>
-    <row r="953" ht="15.75" customHeight="1" s="59"/>
-    <row r="954" ht="15.75" customHeight="1" s="59"/>
-    <row r="955" ht="15.75" customHeight="1" s="59"/>
-    <row r="956" ht="15.75" customHeight="1" s="59"/>
-    <row r="957" ht="15.75" customHeight="1" s="59"/>
-    <row r="958" ht="15.75" customHeight="1" s="59"/>
-    <row r="959" ht="15.75" customHeight="1" s="59"/>
-    <row r="960" ht="15.75" customHeight="1" s="59"/>
-    <row r="961" ht="15.75" customHeight="1" s="59"/>
-    <row r="962" ht="15.75" customHeight="1" s="59"/>
-    <row r="963" ht="15.75" customHeight="1" s="59"/>
-    <row r="964" ht="15.75" customHeight="1" s="59"/>
-    <row r="965" ht="15.75" customHeight="1" s="59"/>
-    <row r="966" ht="15.75" customHeight="1" s="59"/>
-    <row r="967" ht="15.75" customHeight="1" s="59"/>
-    <row r="968" ht="15.75" customHeight="1" s="59"/>
-    <row r="969" ht="15.75" customHeight="1" s="59"/>
-    <row r="970" ht="15.75" customHeight="1" s="59"/>
-    <row r="971" ht="15.75" customHeight="1" s="59"/>
-    <row r="972" ht="15.75" customHeight="1" s="59"/>
-    <row r="973" ht="15.75" customHeight="1" s="59"/>
-    <row r="974" ht="15.75" customHeight="1" s="59"/>
-    <row r="975" ht="15.75" customHeight="1" s="59"/>
-    <row r="976" ht="15.75" customHeight="1" s="59"/>
-    <row r="977" ht="15.75" customHeight="1" s="59"/>
-    <row r="978" ht="15.75" customHeight="1" s="59"/>
-    <row r="979" ht="15.75" customHeight="1" s="59"/>
-    <row r="980" ht="15.75" customHeight="1" s="59"/>
-    <row r="981" ht="15.75" customHeight="1" s="59"/>
-    <row r="982" ht="15.75" customHeight="1" s="59"/>
-    <row r="983" ht="15.75" customHeight="1" s="59"/>
-    <row r="984" ht="15.75" customHeight="1" s="59"/>
-    <row r="985" ht="15.75" customHeight="1" s="59"/>
-    <row r="986" ht="15.75" customHeight="1" s="59"/>
-    <row r="987" ht="15.75" customHeight="1" s="59"/>
-    <row r="988" ht="15.75" customHeight="1" s="59"/>
-    <row r="989" ht="15.75" customHeight="1" s="59"/>
-    <row r="990" ht="15.75" customHeight="1" s="59"/>
-    <row r="991" ht="15.75" customHeight="1" s="59"/>
-    <row r="992" ht="15.75" customHeight="1" s="59"/>
-    <row r="993" ht="15.75" customHeight="1" s="59"/>
-    <row r="994" ht="15.75" customHeight="1" s="59"/>
-    <row r="995" ht="15.75" customHeight="1" s="59"/>
-    <row r="996" ht="15.75" customHeight="1" s="59"/>
-    <row r="997" ht="15.75" customHeight="1" s="59"/>
-    <row r="998" ht="15.75" customHeight="1" s="59"/>
-    <row r="999" ht="15.75" customHeight="1" s="59"/>
-    <row r="1000" ht="15.75" customHeight="1" s="59"/>
+      <c r="F225" s="84" t="inlineStr">
+        <is>
+          <t>Landed rows above</t>
+        </is>
+      </c>
+      <c r="G225" s="82">
+        <f t="array" ref="G225">INDEX($G$178:$G$215,MATCH("LND-MAR-18",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="H225" s="83">
+        <f>G225*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226"/>
+    <row r="227">
+      <c r="A227" s="84" t="inlineStr">
+        <is>
+          <t>HARDWARE (bought-in). Value = USD price × FX_USD.</t>
+        </is>
+      </c>
+      <c r="G227" s="86" t="inlineStr">
+        <is>
+          <t>Quote USD</t>
+        </is>
+      </c>
+      <c r="H227" s="87" t="inlineStr">
+        <is>
+          <t>Quote IDR (USD × FX_USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="84" t="inlineStr">
+        <is>
+          <t>HW-RAIL-DTC</t>
+        </is>
+      </c>
+      <c r="B228" s="84" t="inlineStr">
+        <is>
+          <t>Drawer rail DTC, side-mount, soft-close, ball-bearing</t>
+        </is>
+      </c>
+      <c r="C228" s="89">
+        <f>H228</f>
+        <v/>
+      </c>
+      <c r="E228" s="84" t="inlineStr">
+        <is>
+          <t>IDR/pair</t>
+        </is>
+      </c>
+      <c r="F228" s="84" t="inlineStr">
+        <is>
+          <t>Approved by David 7 Oct 2026 (project doc HARDWARE PRICE 16 OCT). Same price for all lengths.</t>
+        </is>
+      </c>
+      <c r="G228" s="82" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H228" s="83">
+        <f>G228*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="84" t="inlineStr">
+        <is>
+          <t>HW-HINGE-DTC</t>
+        </is>
+      </c>
+      <c r="B229" s="84" t="inlineStr">
+        <is>
+          <t>Soft-close hinge DTC</t>
+        </is>
+      </c>
+      <c r="C229" s="89">
+        <f>H229</f>
+        <v/>
+      </c>
+      <c r="E229" s="84" t="inlineStr">
+        <is>
+          <t>IDR/pc</t>
+        </is>
+      </c>
+      <c r="F229" s="84" t="inlineStr">
+        <is>
+          <t>Approved by David 7 Oct 2026 (project doc HARDWARE PRICE 16 OCT)</t>
+        </is>
+      </c>
+      <c r="G229" s="82" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H229" s="83">
+        <f>G229*$C$172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -2295,47 +2295,36 @@
       </c>
       <c r="J6" s="11">
         <f>IF($C6="","",IF(ISERROR(INDIRECT("'"&amp;$C6&amp;"'!C1")),"no tab yet",IF(N(Y6)+N(AA6)=0,"tab empty",IF(N(T6)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D87")+INDIRECT("'"&amp;$C6&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C6&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D97")+INDIRECT("'"&amp;$C6&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q6" s="16">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R6" s="12">
         <f>IF(AND(ISNUMBER(H6),ISNUMBER(Q6)),H6*Q6,"")</f>
-        <v/>
       </c>
       <c r="S6" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T6" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U6" s="10" t="n"/>
       <c r="V6" s="10" t="n"/>
@@ -2343,15 +2332,12 @@
       <c r="X6" s="10" t="n"/>
       <c r="Y6" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z6" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA6" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D89")+INDIRECT("'"&amp;$C6&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -3033,47 +3019,36 @@
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="11">
         <f>IF($C30="","",IF(ISERROR(INDIRECT("'"&amp;$C30&amp;"'!C1")),"no tab yet",IF(N(Y30)+N(AA30)=0,"tab empty",IF(N(T30)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D87")+INDIRECT("'"&amp;$C30&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C30&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D97")+INDIRECT("'"&amp;$C30&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q30" s="16">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R30" s="12">
         <f>IF(AND(ISNUMBER(H30),ISNUMBER(Q30)),H30*Q30,"")</f>
-        <v/>
       </c>
       <c r="S30" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T30" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U30" s="10" t="n"/>
       <c r="V30" s="10" t="n"/>
@@ -3081,15 +3056,12 @@
       <c r="X30" s="10" t="n"/>
       <c r="Y30" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z30" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA30" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D89")+INDIRECT("'"&amp;$C30&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="59">
@@ -3104,47 +3076,36 @@
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="11">
         <f>IF($C31="","",IF(ISERROR(INDIRECT("'"&amp;$C31&amp;"'!C1")),"no tab yet",IF(N(Y31)+N(AA31)=0,"tab empty",IF(N(T31)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D87")+INDIRECT("'"&amp;$C31&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C31&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D97")+INDIRECT("'"&amp;$C31&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q31" s="16">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R31" s="12">
         <f>IF(AND(ISNUMBER(H31),ISNUMBER(Q31)),H31*Q31,"")</f>
-        <v/>
       </c>
       <c r="S31" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T31" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U31" s="10" t="n"/>
       <c r="V31" s="10" t="n"/>
@@ -3152,15 +3113,12 @@
       <c r="X31" s="10" t="n"/>
       <c r="Y31" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z31" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA31" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D89")+INDIRECT("'"&amp;$C31&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="59">
@@ -3175,47 +3133,36 @@
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="11">
         <f>IF($C32="","",IF(ISERROR(INDIRECT("'"&amp;$C32&amp;"'!C1")),"no tab yet",IF(N(Y32)+N(AA32)=0,"tab empty",IF(N(T32)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D87")+INDIRECT("'"&amp;$C32&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C32&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D97")+INDIRECT("'"&amp;$C32&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q32" s="16">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R32" s="12">
         <f>IF(AND(ISNUMBER(H32),ISNUMBER(Q32)),H32*Q32,"")</f>
-        <v/>
       </c>
       <c r="S32" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T32" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
@@ -3223,15 +3170,12 @@
       <c r="X32" s="10" t="n"/>
       <c r="Y32" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z32" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA32" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D89")+INDIRECT("'"&amp;$C32&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="59">
@@ -3246,47 +3190,36 @@
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="11">
         <f>IF($C33="","",IF(ISERROR(INDIRECT("'"&amp;$C33&amp;"'!C1")),"no tab yet",IF(N(Y33)+N(AA33)=0,"tab empty",IF(N(T33)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D87")+INDIRECT("'"&amp;$C33&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C33&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D97")+INDIRECT("'"&amp;$C33&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q33" s="16">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R33" s="12">
         <f>IF(AND(ISNUMBER(H33),ISNUMBER(Q33)),H33*Q33,"")</f>
-        <v/>
       </c>
       <c r="S33" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T33" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U33" s="10" t="n"/>
       <c r="V33" s="10" t="n"/>
@@ -3294,15 +3227,12 @@
       <c r="X33" s="10" t="n"/>
       <c r="Y33" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z33" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA33" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D89")+INDIRECT("'"&amp;$C33&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="59">
@@ -3317,47 +3247,36 @@
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="11">
         <f>IF($C34="","",IF(ISERROR(INDIRECT("'"&amp;$C34&amp;"'!C1")),"no tab yet",IF(N(Y34)+N(AA34)=0,"tab empty",IF(N(T34)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D87")+INDIRECT("'"&amp;$C34&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C34&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D97")+INDIRECT("'"&amp;$C34&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q34" s="16">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R34" s="12">
         <f>IF(AND(ISNUMBER(H34),ISNUMBER(Q34)),H34*Q34,"")</f>
-        <v/>
       </c>
       <c r="S34" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T34" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
@@ -3365,15 +3284,12 @@
       <c r="X34" s="10" t="n"/>
       <c r="Y34" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z34" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA34" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D89")+INDIRECT("'"&amp;$C34&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="59">
@@ -3388,47 +3304,36 @@
       <c r="I35" s="10" t="n"/>
       <c r="J35" s="11">
         <f>IF($C35="","",IF(ISERROR(INDIRECT("'"&amp;$C35&amp;"'!C1")),"no tab yet",IF(N(Y35)+N(AA35)=0,"tab empty",IF(N(T35)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D87")+INDIRECT("'"&amp;$C35&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C35&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D97")+INDIRECT("'"&amp;$C35&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q35" s="16">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R35" s="12">
         <f>IF(AND(ISNUMBER(H35),ISNUMBER(Q35)),H35*Q35,"")</f>
-        <v/>
       </c>
       <c r="S35" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T35" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U35" s="10" t="n"/>
       <c r="V35" s="10" t="n"/>
@@ -3436,15 +3341,12 @@
       <c r="X35" s="10" t="n"/>
       <c r="Y35" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z35" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA35" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D89")+INDIRECT("'"&amp;$C35&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="59">
@@ -3459,47 +3361,36 @@
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="11">
         <f>IF($C36="","",IF(ISERROR(INDIRECT("'"&amp;$C36&amp;"'!C1")),"no tab yet",IF(N(Y36)+N(AA36)=0,"tab empty",IF(N(T36)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D87")+INDIRECT("'"&amp;$C36&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C36&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D97")+INDIRECT("'"&amp;$C36&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q36" s="16">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R36" s="12">
         <f>IF(AND(ISNUMBER(H36),ISNUMBER(Q36)),H36*Q36,"")</f>
-        <v/>
       </c>
       <c r="S36" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T36" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
@@ -3507,15 +3398,12 @@
       <c r="X36" s="10" t="n"/>
       <c r="Y36" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z36" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA36" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D89")+INDIRECT("'"&amp;$C36&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="59">
@@ -3530,47 +3418,36 @@
       <c r="I37" s="10" t="n"/>
       <c r="J37" s="11">
         <f>IF($C37="","",IF(ISERROR(INDIRECT("'"&amp;$C37&amp;"'!C1")),"no tab yet",IF(N(Y37)+N(AA37)=0,"tab empty",IF(N(T37)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D87")+INDIRECT("'"&amp;$C37&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C37&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D97")+INDIRECT("'"&amp;$C37&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q37" s="16">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R37" s="12">
         <f>IF(AND(ISNUMBER(H37),ISNUMBER(Q37)),H37*Q37,"")</f>
-        <v/>
       </c>
       <c r="S37" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T37" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U37" s="10" t="n"/>
       <c r="V37" s="10" t="n"/>
@@ -3578,15 +3455,12 @@
       <c r="X37" s="10" t="n"/>
       <c r="Y37" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z37" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA37" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D89")+INDIRECT("'"&amp;$C37&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="59">
@@ -3601,47 +3475,36 @@
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="11">
         <f>IF($C38="","",IF(ISERROR(INDIRECT("'"&amp;$C38&amp;"'!C1")),"no tab yet",IF(N(Y38)+N(AA38)=0,"tab empty",IF(N(T38)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D87")+INDIRECT("'"&amp;$C38&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C38&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D97")+INDIRECT("'"&amp;$C38&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q38" s="16">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R38" s="12">
         <f>IF(AND(ISNUMBER(H38),ISNUMBER(Q38)),H38*Q38,"")</f>
-        <v/>
       </c>
       <c r="S38" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T38" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
@@ -3649,15 +3512,12 @@
       <c r="X38" s="10" t="n"/>
       <c r="Y38" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z38" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA38" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D89")+INDIRECT("'"&amp;$C38&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="59">
@@ -3672,47 +3532,36 @@
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="11">
         <f>IF($C39="","",IF(ISERROR(INDIRECT("'"&amp;$C39&amp;"'!C1")),"no tab yet",IF(N(Y39)+N(AA39)=0,"tab empty",IF(N(T39)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D87")+INDIRECT("'"&amp;$C39&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C39&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D97")+INDIRECT("'"&amp;$C39&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q39" s="16">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R39" s="12">
         <f>IF(AND(ISNUMBER(H39),ISNUMBER(Q39)),H39*Q39,"")</f>
-        <v/>
       </c>
       <c r="S39" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T39" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
@@ -3720,15 +3569,12 @@
       <c r="X39" s="10" t="n"/>
       <c r="Y39" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z39" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA39" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D89")+INDIRECT("'"&amp;$C39&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="59">
@@ -3743,47 +3589,36 @@
       <c r="I40" s="10" t="n"/>
       <c r="J40" s="11">
         <f>IF($C40="","",IF(ISERROR(INDIRECT("'"&amp;$C40&amp;"'!C1")),"no tab yet",IF(N(Y40)+N(AA40)=0,"tab empty",IF(N(T40)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D87")+INDIRECT("'"&amp;$C40&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C40&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D97")+INDIRECT("'"&amp;$C40&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q40" s="16">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R40" s="12">
         <f>IF(AND(ISNUMBER(H40),ISNUMBER(Q40)),H40*Q40,"")</f>
-        <v/>
       </c>
       <c r="S40" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T40" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U40" s="10" t="n"/>
       <c r="V40" s="10" t="n"/>
@@ -3791,15 +3626,12 @@
       <c r="X40" s="10" t="n"/>
       <c r="Y40" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z40" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA40" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D89")+INDIRECT("'"&amp;$C40&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="59">
@@ -3814,47 +3646,36 @@
       <c r="I41" s="10" t="n"/>
       <c r="J41" s="11">
         <f>IF($C41="","",IF(ISERROR(INDIRECT("'"&amp;$C41&amp;"'!C1")),"no tab yet",IF(N(Y41)+N(AA41)=0,"tab empty",IF(N(T41)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D87")+INDIRECT("'"&amp;$C41&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C41&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D97")+INDIRECT("'"&amp;$C41&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q41" s="16">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R41" s="12">
         <f>IF(AND(ISNUMBER(H41),ISNUMBER(Q41)),H41*Q41,"")</f>
-        <v/>
       </c>
       <c r="S41" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T41" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U41" s="10" t="n"/>
       <c r="V41" s="10" t="n"/>
@@ -3862,15 +3683,12 @@
       <c r="X41" s="10" t="n"/>
       <c r="Y41" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z41" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA41" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D89")+INDIRECT("'"&amp;$C41&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="59">
@@ -3885,47 +3703,36 @@
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="11">
         <f>IF($C42="","",IF(ISERROR(INDIRECT("'"&amp;$C42&amp;"'!C1")),"no tab yet",IF(N(Y42)+N(AA42)=0,"tab empty",IF(N(T42)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D87")+INDIRECT("'"&amp;$C42&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C42&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D97")+INDIRECT("'"&amp;$C42&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q42" s="16">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R42" s="12">
         <f>IF(AND(ISNUMBER(H42),ISNUMBER(Q42)),H42*Q42,"")</f>
-        <v/>
       </c>
       <c r="S42" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T42" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
@@ -3933,15 +3740,12 @@
       <c r="X42" s="10" t="n"/>
       <c r="Y42" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z42" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA42" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D89")+INDIRECT("'"&amp;$C42&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="59">
@@ -3956,47 +3760,36 @@
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="11">
         <f>IF($C43="","",IF(ISERROR(INDIRECT("'"&amp;$C43&amp;"'!C1")),"no tab yet",IF(N(Y43)+N(AA43)=0,"tab empty",IF(N(T43)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D87")+INDIRECT("'"&amp;$C43&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C43&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D97")+INDIRECT("'"&amp;$C43&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q43" s="16">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R43" s="12">
         <f>IF(AND(ISNUMBER(H43),ISNUMBER(Q43)),H43*Q43,"")</f>
-        <v/>
       </c>
       <c r="S43" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T43" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
@@ -4004,15 +3797,12 @@
       <c r="X43" s="10" t="n"/>
       <c r="Y43" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z43" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA43" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D89")+INDIRECT("'"&amp;$C43&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="59">
@@ -4027,47 +3817,36 @@
       <c r="I44" s="10" t="n"/>
       <c r="J44" s="11">
         <f>IF($C44="","",IF(ISERROR(INDIRECT("'"&amp;$C44&amp;"'!C1")),"no tab yet",IF(N(Y44)+N(AA44)=0,"tab empty",IF(N(T44)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D87")+INDIRECT("'"&amp;$C44&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C44&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D97")+INDIRECT("'"&amp;$C44&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q44" s="16">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R44" s="12">
         <f>IF(AND(ISNUMBER(H44),ISNUMBER(Q44)),H44*Q44,"")</f>
-        <v/>
       </c>
       <c r="S44" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T44" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U44" s="10" t="n"/>
       <c r="V44" s="10" t="n"/>
@@ -4075,15 +3854,12 @@
       <c r="X44" s="10" t="n"/>
       <c r="Y44" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z44" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA44" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D89")+INDIRECT("'"&amp;$C44&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="59">
@@ -4098,47 +3874,36 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="11">
         <f>IF($C45="","",IF(ISERROR(INDIRECT("'"&amp;$C45&amp;"'!C1")),"no tab yet",IF(N(Y45)+N(AA45)=0,"tab empty",IF(N(T45)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D87")+INDIRECT("'"&amp;$C45&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C45&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D97")+INDIRECT("'"&amp;$C45&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q45" s="16">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R45" s="12">
         <f>IF(AND(ISNUMBER(H45),ISNUMBER(Q45)),H45*Q45,"")</f>
-        <v/>
       </c>
       <c r="S45" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T45" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
@@ -4146,15 +3911,12 @@
       <c r="X45" s="10" t="n"/>
       <c r="Y45" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z45" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA45" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D89")+INDIRECT("'"&amp;$C45&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="59">
@@ -4169,47 +3931,36 @@
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="11">
         <f>IF($C46="","",IF(ISERROR(INDIRECT("'"&amp;$C46&amp;"'!C1")),"no tab yet",IF(N(Y46)+N(AA46)=0,"tab empty",IF(N(T46)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D87")+INDIRECT("'"&amp;$C46&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C46&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D97")+INDIRECT("'"&amp;$C46&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q46" s="16">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R46" s="12">
         <f>IF(AND(ISNUMBER(H46),ISNUMBER(Q46)),H46*Q46,"")</f>
-        <v/>
       </c>
       <c r="S46" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T46" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
@@ -4217,15 +3968,12 @@
       <c r="X46" s="10" t="n"/>
       <c r="Y46" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z46" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA46" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D89")+INDIRECT("'"&amp;$C46&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="59">
@@ -4240,47 +3988,36 @@
       <c r="I47" s="10" t="n"/>
       <c r="J47" s="11">
         <f>IF($C47="","",IF(ISERROR(INDIRECT("'"&amp;$C47&amp;"'!C1")),"no tab yet",IF(N(Y47)+N(AA47)=0,"tab empty",IF(N(T47)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D87")+INDIRECT("'"&amp;$C47&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C47&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D97")+INDIRECT("'"&amp;$C47&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q47" s="16">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R47" s="12">
         <f>IF(AND(ISNUMBER(H47),ISNUMBER(Q47)),H47*Q47,"")</f>
-        <v/>
       </c>
       <c r="S47" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T47" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U47" s="10" t="n"/>
       <c r="V47" s="10" t="n"/>
@@ -4288,15 +4025,12 @@
       <c r="X47" s="10" t="n"/>
       <c r="Y47" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z47" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA47" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D89")+INDIRECT("'"&amp;$C47&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="59">
@@ -4311,47 +4045,36 @@
       <c r="I48" s="10" t="n"/>
       <c r="J48" s="11">
         <f>IF($C48="","",IF(ISERROR(INDIRECT("'"&amp;$C48&amp;"'!C1")),"no tab yet",IF(N(Y48)+N(AA48)=0,"tab empty",IF(N(T48)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D87")+INDIRECT("'"&amp;$C48&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C48&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D97")+INDIRECT("'"&amp;$C48&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q48" s="16">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R48" s="12">
         <f>IF(AND(ISNUMBER(H48),ISNUMBER(Q48)),H48*Q48,"")</f>
-        <v/>
       </c>
       <c r="S48" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T48" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U48" s="10" t="n"/>
       <c r="V48" s="10" t="n"/>
@@ -4359,15 +4082,12 @@
       <c r="X48" s="10" t="n"/>
       <c r="Y48" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z48" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA48" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D89")+INDIRECT("'"&amp;$C48&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="59">
@@ -4382,47 +4102,36 @@
       <c r="I49" s="10" t="n"/>
       <c r="J49" s="11">
         <f>IF($C49="","",IF(ISERROR(INDIRECT("'"&amp;$C49&amp;"'!C1")),"no tab yet",IF(N(Y49)+N(AA49)=0,"tab empty",IF(N(T49)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D87")+INDIRECT("'"&amp;$C49&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C49&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D97")+INDIRECT("'"&amp;$C49&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q49" s="16">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R49" s="12">
         <f>IF(AND(ISNUMBER(H49),ISNUMBER(Q49)),H49*Q49,"")</f>
-        <v/>
       </c>
       <c r="S49" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T49" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U49" s="10" t="n"/>
       <c r="V49" s="10" t="n"/>
@@ -4430,15 +4139,12 @@
       <c r="X49" s="10" t="n"/>
       <c r="Y49" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z49" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA49" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D89")+INDIRECT("'"&amp;$C49&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="59">
@@ -4453,47 +4159,36 @@
       <c r="I50" s="10" t="n"/>
       <c r="J50" s="11">
         <f>IF($C50="","",IF(ISERROR(INDIRECT("'"&amp;$C50&amp;"'!C1")),"no tab yet",IF(N(Y50)+N(AA50)=0,"tab empty",IF(N(T50)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D87")+INDIRECT("'"&amp;$C50&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C50&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D97")+INDIRECT("'"&amp;$C50&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q50" s="16">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R50" s="12">
         <f>IF(AND(ISNUMBER(H50),ISNUMBER(Q50)),H50*Q50,"")</f>
-        <v/>
       </c>
       <c r="S50" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T50" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
@@ -4501,15 +4196,12 @@
       <c r="X50" s="10" t="n"/>
       <c r="Y50" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z50" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA50" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D89")+INDIRECT("'"&amp;$C50&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="59">
@@ -4524,47 +4216,36 @@
       <c r="I51" s="10" t="n"/>
       <c r="J51" s="11">
         <f>IF($C51="","",IF(ISERROR(INDIRECT("'"&amp;$C51&amp;"'!C1")),"no tab yet",IF(N(Y51)+N(AA51)=0,"tab empty",IF(N(T51)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D87")+INDIRECT("'"&amp;$C51&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C51&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D97")+INDIRECT("'"&amp;$C51&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q51" s="16">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R51" s="12">
         <f>IF(AND(ISNUMBER(H51),ISNUMBER(Q51)),H51*Q51,"")</f>
-        <v/>
       </c>
       <c r="S51" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T51" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U51" s="10" t="n"/>
       <c r="V51" s="10" t="n"/>
@@ -4572,15 +4253,12 @@
       <c r="X51" s="10" t="n"/>
       <c r="Y51" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z51" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA51" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D89")+INDIRECT("'"&amp;$C51&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="59">
@@ -4595,47 +4273,36 @@
       <c r="I52" s="10" t="n"/>
       <c r="J52" s="11">
         <f>IF($C52="","",IF(ISERROR(INDIRECT("'"&amp;$C52&amp;"'!C1")),"no tab yet",IF(N(Y52)+N(AA52)=0,"tab empty",IF(N(T52)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D87")+INDIRECT("'"&amp;$C52&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C52&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D97")+INDIRECT("'"&amp;$C52&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q52" s="16">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R52" s="12">
         <f>IF(AND(ISNUMBER(H52),ISNUMBER(Q52)),H52*Q52,"")</f>
-        <v/>
       </c>
       <c r="S52" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T52" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
@@ -4643,15 +4310,12 @@
       <c r="X52" s="10" t="n"/>
       <c r="Y52" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z52" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA52" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D89")+INDIRECT("'"&amp;$C52&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="59">
@@ -4666,47 +4330,36 @@
       <c r="I53" s="10" t="n"/>
       <c r="J53" s="11">
         <f>IF($C53="","",IF(ISERROR(INDIRECT("'"&amp;$C53&amp;"'!C1")),"no tab yet",IF(N(Y53)+N(AA53)=0,"tab empty",IF(N(T53)&gt;0,"check inputs","costed"))))</f>
-        <v/>
       </c>
       <c r="K53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D87")+INDIRECT("'"&amp;$C53&amp;"'!D88"),""))</f>
-        <v/>
       </c>
       <c r="L53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D89")+0,""))</f>
-        <v/>
       </c>
       <c r="M53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C53&amp;"'!D90:D93")),""))</f>
-        <v/>
       </c>
       <c r="N53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D94")+0,""))</f>
-        <v/>
       </c>
       <c r="O53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D95")+0,""))</f>
-        <v/>
       </c>
       <c r="P53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D97")+INDIRECT("'"&amp;$C53&amp;"'!D98"),""))</f>
-        <v/>
       </c>
       <c r="Q53" s="16">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D99")+0,""))</f>
-        <v/>
       </c>
       <c r="R53" s="12">
         <f>IF(AND(ISNUMBER(H53),ISNUMBER(Q53)),H53*Q53,"")</f>
-        <v/>
       </c>
       <c r="S53" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D86")+0,"")</f>
-        <v/>
       </c>
       <c r="T53" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D102")+0,"")</f>
-        <v/>
       </c>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
@@ -4714,15 +4367,12 @@
       <c r="X53" s="10" t="n"/>
       <c r="Y53" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D82")+0,"")</f>
-        <v/>
       </c>
       <c r="Z53" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D84")+0,"")</f>
-        <v/>
       </c>
       <c r="AA53" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D89")+INDIRECT("'"&amp;$C53&amp;"'!D94"),"")</f>
-        <v/>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="59">
@@ -4737,7 +4387,6 @@
       <c r="I54" s="26" t="n"/>
       <c r="J54" s="27">
         <f>COUNTIF(J5:J53,"costed")&amp;" costed / "&amp;COUNTA(C5:C53)&amp;" items"</f>
-        <v/>
       </c>
       <c r="K54" s="26" t="n"/>
       <c r="L54" s="26" t="n"/>
@@ -4747,15 +4396,12 @@
       <c r="P54" s="26" t="n"/>
       <c r="Q54" s="28">
         <f>SUM(Q5:Q53)</f>
-        <v/>
       </c>
       <c r="R54" s="28">
         <f>SUM(R5:R53)</f>
-        <v/>
       </c>
       <c r="S54" s="29">
         <f>SUM(S5:S53)</f>
-        <v/>
       </c>
       <c r="T54" s="26" t="n"/>
       <c r="U54" s="26" t="n"/>
@@ -4764,11 +4410,9 @@
       <c r="X54" s="26" t="n"/>
       <c r="Y54" s="30">
         <f>SUM(Y5:Y53)</f>
-        <v/>
       </c>
       <c r="Z54" s="31">
         <f>SUM(Z5:Z53)</f>
-        <v/>
       </c>
       <c r="AA54" s="26" t="n"/>
     </row>
@@ -4835,7 +4479,6 @@
       <c r="I58" s="9" t="n"/>
       <c r="J58" s="9">
         <f>COUNTIFS($B$5:$B$53,$D58,$J$5:$J$53,"costed")</f>
-        <v/>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>
@@ -4845,15 +4488,12 @@
       <c r="P58" s="9" t="n"/>
       <c r="Q58" s="32">
         <f>SUMIF($B$5:$B$53,$D58,Q$5:Q$53)</f>
-        <v/>
       </c>
       <c r="R58" s="32">
         <f>SUMIF($B$5:$B$53,$D58,R$5:R$53)</f>
-        <v/>
       </c>
       <c r="S58" s="33">
         <f>SUMIF($B$5:$B$53,$D58,S$5:S$53)</f>
-        <v/>
       </c>
       <c r="T58" s="9" t="n"/>
       <c r="U58" s="9" t="n"/>
@@ -4862,11 +4502,9 @@
       <c r="X58" s="9" t="n"/>
       <c r="Y58" s="34">
         <f>SUMIF($B$5:$B$53,$D58,Y$5:Y$53)</f>
-        <v/>
       </c>
       <c r="Z58" s="35">
         <f>SUMIF($B$5:$B$53,$D58,Z$5:Z$53)</f>
-        <v/>
       </c>
       <c r="AA58" s="9" t="n"/>
     </row>
@@ -4879,7 +4517,6 @@
       <c r="I59" s="9" t="n"/>
       <c r="J59" s="9">
         <f>COUNTIFS($B$5:$B$53,$D59,$J$5:$J$53,"costed")</f>
-        <v/>
       </c>
       <c r="K59" s="9" t="n"/>
       <c r="L59" s="9" t="n"/>
@@ -4889,15 +4526,12 @@
       <c r="P59" s="9" t="n"/>
       <c r="Q59" s="32">
         <f>SUMIF($B$5:$B$53,$D59,Q$5:Q$53)</f>
-        <v/>
       </c>
       <c r="R59" s="32">
         <f>SUMIF($B$5:$B$53,$D59,R$5:R$53)</f>
-        <v/>
       </c>
       <c r="S59" s="33">
         <f>SUMIF($B$5:$B$53,$D59,S$5:S$53)</f>
-        <v/>
       </c>
       <c r="T59" s="9" t="n"/>
       <c r="U59" s="9" t="n"/>
@@ -4906,11 +4540,9 @@
       <c r="X59" s="9" t="n"/>
       <c r="Y59" s="34">
         <f>SUMIF($B$5:$B$53,$D59,Y$5:Y$53)</f>
-        <v/>
       </c>
       <c r="Z59" s="35">
         <f>SUMIF($B$5:$B$53,$D59,Z$5:Z$53)</f>
-        <v/>
       </c>
       <c r="AA59" s="9" t="n"/>
     </row>
@@ -4923,7 +4555,6 @@
       <c r="I60" s="9" t="n"/>
       <c r="J60" s="9">
         <f>COUNTIFS($B$5:$B$53,$D60,$J$5:$J$53,"costed")</f>
-        <v/>
       </c>
       <c r="K60" s="9" t="n"/>
       <c r="L60" s="9" t="n"/>
@@ -4933,15 +4564,12 @@
       <c r="P60" s="9" t="n"/>
       <c r="Q60" s="32">
         <f>SUMIF($B$5:$B$53,$D60,Q$5:Q$53)</f>
-        <v/>
       </c>
       <c r="R60" s="32">
         <f>SUMIF($B$5:$B$53,$D60,R$5:R$53)</f>
-        <v/>
       </c>
       <c r="S60" s="33">
         <f>SUMIF($B$5:$B$53,$D60,S$5:S$53)</f>
-        <v/>
       </c>
       <c r="T60" s="9" t="n"/>
       <c r="U60" s="9" t="n"/>
@@ -4950,11 +4578,9 @@
       <c r="X60" s="9" t="n"/>
       <c r="Y60" s="34">
         <f>SUMIF($B$5:$B$53,$D60,Y$5:Y$53)</f>
-        <v/>
       </c>
       <c r="Z60" s="35">
         <f>SUMIF($B$5:$B$53,$D60,Z$5:Z$53)</f>
-        <v/>
       </c>
       <c r="AA60" s="9" t="n"/>
     </row>
@@ -5943,7 +5569,6 @@
       </c>
       <c r="G1" s="9">
         <f t="array" ref="G1">IFERROR(IF(INDEX(ITEMS!$E$5:$E$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$E$5:$E$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H1" s="67" t="n"/>
       <c r="I1" s="67" t="n"/>
@@ -5951,7 +5576,6 @@
       <c r="K1" s="68" t="n"/>
       <c r="L1" s="69">
         <f>IF(G6="","photo",_xludf.IMAGE(G6))</f>
-        <v/>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="59">
@@ -5962,7 +5586,6 @@
       </c>
       <c r="C2" s="9">
         <f t="array" ref="C2">IFERROR(IF(INDEX(ITEMS!$D$5:$D$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$D$5:$D$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="D2" s="66" t="inlineStr">
         <is>
@@ -5971,7 +5594,6 @@
       </c>
       <c r="G2" s="9">
         <f t="array" ref="G2">IFERROR(IF(INDEX(ITEMS!$F$5:$F$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$F$5:$F$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H2" s="67" t="n"/>
       <c r="I2" s="67" t="n"/>
@@ -5986,7 +5608,6 @@
       </c>
       <c r="C3" s="9">
         <f t="array" ref="C3">IFERROR(INDEX(ITEMS!$B$5:$B$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))&amp;" / "&amp;INDEX(ITEMS!$W$5:$W$120,MATCH($C$1,ITEMS!$C$5:$C$120,0)),"")</f>
-        <v/>
       </c>
       <c r="D3" s="66" t="inlineStr">
         <is>
@@ -5995,7 +5616,6 @@
       </c>
       <c r="G3" s="9">
         <f t="array" ref="G3">IFERROR(IF(INDEX(ITEMS!$G$5:$G$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$G$5:$G$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H3" s="67" t="n"/>
       <c r="I3" s="67" t="n"/>
@@ -6010,7 +5630,6 @@
       </c>
       <c r="C4" s="9">
         <f t="array" ref="C4">IFERROR(IF(INDEX(ITEMS!$H$5:$H$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$H$5:$H$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="D4" s="66" t="inlineStr">
         <is>
@@ -6019,7 +5638,6 @@
       </c>
       <c r="G4" s="9">
         <f t="array" ref="G4">IFERROR(IF(INDEX(ITEMS!$I$5:$I$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$I$5:$I$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H4" s="67" t="n"/>
       <c r="I4" s="67" t="n"/>
@@ -6040,7 +5658,6 @@
       </c>
       <c r="G5" s="9">
         <f t="array" ref="G5">IFERROR(IF(INDEX(ITEMS!$V$5:$V$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$V$5:$V$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H5" s="67" t="n"/>
       <c r="I5" s="67" t="n"/>
@@ -6073,7 +5690,6 @@
       </c>
       <c r="C7" s="9">
         <f t="array" ref="C7">IFERROR(IF(INDEX(ITEMS!$X$5:$X$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$X$5:$X$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="D7" s="66" t="inlineStr">
         <is>
@@ -6165,24 +5781,19 @@
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="14">
         <f>IF(D11="","",D11+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="I11" s="14">
         <f>IF(E11="","",E11+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="J11" s="14">
         <f>IF(F11="","",F11+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="17">
         <f>IF(H11="","",2*(H11*I11+H11*J11+I11*J11)/1000000*IF(G11="",1,G11))</f>
-        <v/>
       </c>
       <c r="M11" s="19">
         <f>IF(H11="","",H11*I11*J11/1000000000*IF(G11="",1,G11))</f>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -6197,24 +5808,19 @@
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="14">
         <f>IF(D12="","",D12+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="I12" s="14">
         <f>IF(E12="","",E12+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="J12" s="14">
         <f>IF(F12="","",F12+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="17">
         <f>IF(H12="","",2*(H12*I12+H12*J12+I12*J12)/1000000*IF(G12="",1,G12))</f>
-        <v/>
       </c>
       <c r="M12" s="19">
         <f>IF(H12="","",H12*I12*J12/1000000000*IF(G12="",1,G12))</f>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -6229,24 +5835,19 @@
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="14">
         <f>IF(D13="","",D13+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="I13" s="14">
         <f>IF(E13="","",E13+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="J13" s="14">
         <f>IF(F13="","",F13+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="17">
         <f>IF(H13="","",2*(H13*I13+H13*J13+I13*J13)/1000000*IF(G13="",1,G13))</f>
-        <v/>
       </c>
       <c r="M13" s="19">
         <f>IF(H13="","",H13*I13*J13/1000000000*IF(G13="",1,G13))</f>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -6261,24 +5862,19 @@
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="14">
         <f>IF(D14="","",D14+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="I14" s="14">
         <f>IF(E14="","",E14+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="J14" s="14">
         <f>IF(F14="","",F14+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="17">
         <f>IF(H14="","",2*(H14*I14+H14*J14+I14*J14)/1000000*IF(G14="",1,G14))</f>
-        <v/>
       </c>
       <c r="M14" s="19">
         <f>IF(H14="","",H14*I14*J14/1000000000*IF(G14="",1,G14))</f>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -6294,7 +5890,6 @@
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="22">
         <f>IF(D11="",1,SUM(G11:G14)+COUNTIFS(D11:D14,"&lt;&gt;",G11:G14,""))</f>
-        <v/>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -6306,11 +5901,9 @@
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="23">
         <f>IF(D11="",IF(OR(G1="",G2="",G3=""),0,2*((G1+LISTS!$F$9)*(G2+LISTS!$F$9)+(G1+LISTS!$F$9)*(G3+LISTS!$F$9)+(G2+LISTS!$F$9)*(G3+LISTS!$F$9))/1000000),SUM(L11:L14))</f>
-        <v/>
       </c>
       <c r="M15" s="24">
         <f>IF(D11="",IF(OR(G1="",G2="",G3=""),0,(G1+LISTS!$F$9)*(G2+LISTS!$F$9)*(G3+LISTS!$F$9)/1000000000),SUM(M11:M14))</f>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -6431,29 +6024,23 @@
       <c r="L18" s="10" t="n"/>
       <c r="M18" s="25">
         <f>IF(OR(E18="",F18="",G18=""),"",E18*F18*G18/1000000000*IF(H18="",1,H18))</f>
-        <v/>
       </c>
       <c r="N18" s="19">
         <f>IF(OR(E18="",F18=""),"",E18*F18/1000000*IF(H18="",1,H18))</f>
-        <v/>
       </c>
       <c r="O18" s="14">
         <f>IF(E18="","",IF(K18&lt;&gt;"",K18,IF(AND(E18*F18*G18/1000000000&lt;LISTS!$F$4,MAX(E18,F18,G18)&lt;LISTS!$F$5),"D",IF(I18="N","C",IF(J18="Y","A-CURVED",IF(AND(MEDIAN(E18,F18,G18)&lt;=LISTS!$F$10,MAX(E18,F18,G18)&lt;=LISTS!$F$11),"B",IF(MAX(E18,F18,G18)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P18" s="14" t="n"/>
       <c r="Q18" s="14" t="n"/>
       <c r="R18" s="14">
         <f>IF(E18="","",IF(B18="","material?",IF(OR(F18="",G18=""),"size?",IF(I18="","exposed Y/N?",IF(H18="","qty?",IF(B18="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S18" s="12">
         <f t="array" ref="S18">IF(OR(O18="",M18=""),"",IF(B18="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B18&amp;"_"&amp;SUBSTITUTE(O18,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T18" s="12">
         <f>IF(ISNUMBER(S18),M18*S18,"")</f>
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -6473,29 +6060,23 @@
       <c r="L19" s="10" t="n"/>
       <c r="M19" s="25">
         <f>IF(OR(E19="",F19="",G19=""),"",E19*F19*G19/1000000000*IF(H19="",1,H19))</f>
-        <v/>
       </c>
       <c r="N19" s="19">
         <f>IF(OR(E19="",F19=""),"",E19*F19/1000000*IF(H19="",1,H19))</f>
-        <v/>
       </c>
       <c r="O19" s="14">
         <f>IF(E19="","",IF(K19&lt;&gt;"",K19,IF(AND(E19*F19*G19/1000000000&lt;LISTS!$F$4,MAX(E19,F19,G19)&lt;LISTS!$F$5),"D",IF(I19="N","C",IF(J19="Y","A-CURVED",IF(AND(MEDIAN(E19,F19,G19)&lt;=LISTS!$F$10,MAX(E19,F19,G19)&lt;=LISTS!$F$11),"B",IF(MAX(E19,F19,G19)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P19" s="14" t="n"/>
       <c r="Q19" s="14" t="n"/>
       <c r="R19" s="14">
         <f>IF(E19="","",IF(B19="","material?",IF(OR(F19="",G19=""),"size?",IF(I19="","exposed Y/N?",IF(H19="","qty?",IF(B19="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S19" s="12">
         <f t="array" ref="S19">IF(OR(O19="",M19=""),"",IF(B19="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B19&amp;"_"&amp;SUBSTITUTE(O19,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T19" s="12">
         <f>IF(ISNUMBER(S19),M19*S19,"")</f>
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -6515,29 +6096,23 @@
       <c r="L20" s="10" t="n"/>
       <c r="M20" s="25">
         <f>IF(OR(E20="",F20="",G20=""),"",E20*F20*G20/1000000000*IF(H20="",1,H20))</f>
-        <v/>
       </c>
       <c r="N20" s="19">
         <f>IF(OR(E20="",F20=""),"",E20*F20/1000000*IF(H20="",1,H20))</f>
-        <v/>
       </c>
       <c r="O20" s="14">
         <f>IF(E20="","",IF(K20&lt;&gt;"",K20,IF(AND(E20*F20*G20/1000000000&lt;LISTS!$F$4,MAX(E20,F20,G20)&lt;LISTS!$F$5),"D",IF(I20="N","C",IF(J20="Y","A-CURVED",IF(AND(MEDIAN(E20,F20,G20)&lt;=LISTS!$F$10,MAX(E20,F20,G20)&lt;=LISTS!$F$11),"B",IF(MAX(E20,F20,G20)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P20" s="14" t="n"/>
       <c r="Q20" s="14" t="n"/>
       <c r="R20" s="14">
         <f>IF(E20="","",IF(B20="","material?",IF(OR(F20="",G20=""),"size?",IF(I20="","exposed Y/N?",IF(H20="","qty?",IF(B20="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S20" s="12">
         <f t="array" ref="S20">IF(OR(O20="",M20=""),"",IF(B20="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B20&amp;"_"&amp;SUBSTITUTE(O20,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T20" s="12">
         <f>IF(ISNUMBER(S20),M20*S20,"")</f>
-        <v/>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="59">
@@ -6557,29 +6132,23 @@
       <c r="L21" s="10" t="n"/>
       <c r="M21" s="25">
         <f>IF(OR(E21="",F21="",G21=""),"",E21*F21*G21/1000000000*IF(H21="",1,H21))</f>
-        <v/>
       </c>
       <c r="N21" s="19">
         <f>IF(OR(E21="",F21=""),"",E21*F21/1000000*IF(H21="",1,H21))</f>
-        <v/>
       </c>
       <c r="O21" s="14">
         <f>IF(E21="","",IF(K21&lt;&gt;"",K21,IF(AND(E21*F21*G21/1000000000&lt;LISTS!$F$4,MAX(E21,F21,G21)&lt;LISTS!$F$5),"D",IF(I21="N","C",IF(J21="Y","A-CURVED",IF(AND(MEDIAN(E21,F21,G21)&lt;=LISTS!$F$10,MAX(E21,F21,G21)&lt;=LISTS!$F$11),"B",IF(MAX(E21,F21,G21)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P21" s="14" t="n"/>
       <c r="Q21" s="14" t="n"/>
       <c r="R21" s="14">
         <f>IF(E21="","",IF(B21="","material?",IF(OR(F21="",G21=""),"size?",IF(I21="","exposed Y/N?",IF(H21="","qty?",IF(B21="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S21" s="12">
         <f t="array" ref="S21">IF(OR(O21="",M21=""),"",IF(B21="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B21&amp;"_"&amp;SUBSTITUTE(O21,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T21" s="12">
         <f>IF(ISNUMBER(S21),M21*S21,"")</f>
-        <v/>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="59">
@@ -6599,29 +6168,23 @@
       <c r="L22" s="10" t="n"/>
       <c r="M22" s="25">
         <f>IF(OR(E22="",F22="",G22=""),"",E22*F22*G22/1000000000*IF(H22="",1,H22))</f>
-        <v/>
       </c>
       <c r="N22" s="19">
         <f>IF(OR(E22="",F22=""),"",E22*F22/1000000*IF(H22="",1,H22))</f>
-        <v/>
       </c>
       <c r="O22" s="14">
         <f>IF(E22="","",IF(K22&lt;&gt;"",K22,IF(AND(E22*F22*G22/1000000000&lt;LISTS!$F$4,MAX(E22,F22,G22)&lt;LISTS!$F$5),"D",IF(I22="N","C",IF(J22="Y","A-CURVED",IF(AND(MEDIAN(E22,F22,G22)&lt;=LISTS!$F$10,MAX(E22,F22,G22)&lt;=LISTS!$F$11),"B",IF(MAX(E22,F22,G22)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P22" s="14" t="n"/>
       <c r="Q22" s="14" t="n"/>
       <c r="R22" s="14">
         <f>IF(E22="","",IF(B22="","material?",IF(OR(F22="",G22=""),"size?",IF(I22="","exposed Y/N?",IF(H22="","qty?",IF(B22="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S22" s="12">
         <f t="array" ref="S22">IF(OR(O22="",M22=""),"",IF(B22="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B22&amp;"_"&amp;SUBSTITUTE(O22,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T22" s="12">
         <f>IF(ISNUMBER(S22),M22*S22,"")</f>
-        <v/>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="59">
@@ -6641,29 +6204,23 @@
       <c r="L23" s="10" t="n"/>
       <c r="M23" s="25">
         <f>IF(OR(E23="",F23="",G23=""),"",E23*F23*G23/1000000000*IF(H23="",1,H23))</f>
-        <v/>
       </c>
       <c r="N23" s="19">
         <f>IF(OR(E23="",F23=""),"",E23*F23/1000000*IF(H23="",1,H23))</f>
-        <v/>
       </c>
       <c r="O23" s="14">
         <f>IF(E23="","",IF(K23&lt;&gt;"",K23,IF(AND(E23*F23*G23/1000000000&lt;LISTS!$F$4,MAX(E23,F23,G23)&lt;LISTS!$F$5),"D",IF(I23="N","C",IF(J23="Y","A-CURVED",IF(AND(MEDIAN(E23,F23,G23)&lt;=LISTS!$F$10,MAX(E23,F23,G23)&lt;=LISTS!$F$11),"B",IF(MAX(E23,F23,G23)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P23" s="14" t="n"/>
       <c r="Q23" s="14" t="n"/>
       <c r="R23" s="14">
         <f>IF(E23="","",IF(B23="","material?",IF(OR(F23="",G23=""),"size?",IF(I23="","exposed Y/N?",IF(H23="","qty?",IF(B23="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S23" s="12">
         <f t="array" ref="S23">IF(OR(O23="",M23=""),"",IF(B23="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B23&amp;"_"&amp;SUBSTITUTE(O23,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T23" s="12">
         <f>IF(ISNUMBER(S23),M23*S23,"")</f>
-        <v/>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="59">
@@ -6683,29 +6240,23 @@
       <c r="L24" s="10" t="n"/>
       <c r="M24" s="25">
         <f>IF(OR(E24="",F24="",G24=""),"",E24*F24*G24/1000000000*IF(H24="",1,H24))</f>
-        <v/>
       </c>
       <c r="N24" s="19">
         <f>IF(OR(E24="",F24=""),"",E24*F24/1000000*IF(H24="",1,H24))</f>
-        <v/>
       </c>
       <c r="O24" s="14">
         <f>IF(E24="","",IF(K24&lt;&gt;"",K24,IF(AND(E24*F24*G24/1000000000&lt;LISTS!$F$4,MAX(E24,F24,G24)&lt;LISTS!$F$5),"D",IF(I24="N","C",IF(J24="Y","A-CURVED",IF(AND(MEDIAN(E24,F24,G24)&lt;=LISTS!$F$10,MAX(E24,F24,G24)&lt;=LISTS!$F$11),"B",IF(MAX(E24,F24,G24)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P24" s="14" t="n"/>
       <c r="Q24" s="14" t="n"/>
       <c r="R24" s="14">
         <f>IF(E24="","",IF(B24="","material?",IF(OR(F24="",G24=""),"size?",IF(I24="","exposed Y/N?",IF(H24="","qty?",IF(B24="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S24" s="12">
         <f t="array" ref="S24">IF(OR(O24="",M24=""),"",IF(B24="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B24&amp;"_"&amp;SUBSTITUTE(O24,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T24" s="12">
         <f>IF(ISNUMBER(S24),M24*S24,"")</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="59">
@@ -6725,29 +6276,23 @@
       <c r="L25" s="10" t="n"/>
       <c r="M25" s="25">
         <f>IF(OR(E25="",F25="",G25=""),"",E25*F25*G25/1000000000*IF(H25="",1,H25))</f>
-        <v/>
       </c>
       <c r="N25" s="19">
         <f>IF(OR(E25="",F25=""),"",E25*F25/1000000*IF(H25="",1,H25))</f>
-        <v/>
       </c>
       <c r="O25" s="14">
         <f>IF(E25="","",IF(K25&lt;&gt;"",K25,IF(AND(E25*F25*G25/1000000000&lt;LISTS!$F$4,MAX(E25,F25,G25)&lt;LISTS!$F$5),"D",IF(I25="N","C",IF(J25="Y","A-CURVED",IF(AND(MEDIAN(E25,F25,G25)&lt;=LISTS!$F$10,MAX(E25,F25,G25)&lt;=LISTS!$F$11),"B",IF(MAX(E25,F25,G25)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P25" s="14" t="n"/>
       <c r="Q25" s="14" t="n"/>
       <c r="R25" s="14">
         <f>IF(E25="","",IF(B25="","material?",IF(OR(F25="",G25=""),"size?",IF(I25="","exposed Y/N?",IF(H25="","qty?",IF(B25="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S25" s="12">
         <f t="array" ref="S25">IF(OR(O25="",M25=""),"",IF(B25="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B25&amp;"_"&amp;SUBSTITUTE(O25,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T25" s="12">
         <f>IF(ISNUMBER(S25),M25*S25,"")</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="59">
@@ -6767,29 +6312,23 @@
       <c r="L26" s="10" t="n"/>
       <c r="M26" s="25">
         <f>IF(OR(E26="",F26="",G26=""),"",E26*F26*G26/1000000000*IF(H26="",1,H26))</f>
-        <v/>
       </c>
       <c r="N26" s="19">
         <f>IF(OR(E26="",F26=""),"",E26*F26/1000000*IF(H26="",1,H26))</f>
-        <v/>
       </c>
       <c r="O26" s="14">
         <f>IF(E26="","",IF(K26&lt;&gt;"",K26,IF(AND(E26*F26*G26/1000000000&lt;LISTS!$F$4,MAX(E26,F26,G26)&lt;LISTS!$F$5),"D",IF(I26="N","C",IF(J26="Y","A-CURVED",IF(AND(MEDIAN(E26,F26,G26)&lt;=LISTS!$F$10,MAX(E26,F26,G26)&lt;=LISTS!$F$11),"B",IF(MAX(E26,F26,G26)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P26" s="14" t="n"/>
       <c r="Q26" s="14" t="n"/>
       <c r="R26" s="14">
         <f>IF(E26="","",IF(B26="","material?",IF(OR(F26="",G26=""),"size?",IF(I26="","exposed Y/N?",IF(H26="","qty?",IF(B26="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S26" s="12">
         <f t="array" ref="S26">IF(OR(O26="",M26=""),"",IF(B26="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B26&amp;"_"&amp;SUBSTITUTE(O26,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T26" s="12">
         <f>IF(ISNUMBER(S26),M26*S26,"")</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="59">
@@ -6809,29 +6348,23 @@
       <c r="L27" s="10" t="n"/>
       <c r="M27" s="25">
         <f>IF(OR(E27="",F27="",G27=""),"",E27*F27*G27/1000000000*IF(H27="",1,H27))</f>
-        <v/>
       </c>
       <c r="N27" s="19">
         <f>IF(OR(E27="",F27=""),"",E27*F27/1000000*IF(H27="",1,H27))</f>
-        <v/>
       </c>
       <c r="O27" s="14">
         <f>IF(E27="","",IF(K27&lt;&gt;"",K27,IF(AND(E27*F27*G27/1000000000&lt;LISTS!$F$4,MAX(E27,F27,G27)&lt;LISTS!$F$5),"D",IF(I27="N","C",IF(J27="Y","A-CURVED",IF(AND(MEDIAN(E27,F27,G27)&lt;=LISTS!$F$10,MAX(E27,F27,G27)&lt;=LISTS!$F$11),"B",IF(MAX(E27,F27,G27)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P27" s="14" t="n"/>
       <c r="Q27" s="14" t="n"/>
       <c r="R27" s="14">
         <f>IF(E27="","",IF(B27="","material?",IF(OR(F27="",G27=""),"size?",IF(I27="","exposed Y/N?",IF(H27="","qty?",IF(B27="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S27" s="12">
         <f t="array" ref="S27">IF(OR(O27="",M27=""),"",IF(B27="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B27&amp;"_"&amp;SUBSTITUTE(O27,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T27" s="12">
         <f>IF(ISNUMBER(S27),M27*S27,"")</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="59">
@@ -6851,29 +6384,23 @@
       <c r="L28" s="10" t="n"/>
       <c r="M28" s="25">
         <f>IF(OR(E28="",F28="",G28=""),"",E28*F28*G28/1000000000*IF(H28="",1,H28))</f>
-        <v/>
       </c>
       <c r="N28" s="19">
         <f>IF(OR(E28="",F28=""),"",E28*F28/1000000*IF(H28="",1,H28))</f>
-        <v/>
       </c>
       <c r="O28" s="14">
         <f>IF(E28="","",IF(K28&lt;&gt;"",K28,IF(AND(E28*F28*G28/1000000000&lt;LISTS!$F$4,MAX(E28,F28,G28)&lt;LISTS!$F$5),"D",IF(I28="N","C",IF(J28="Y","A-CURVED",IF(AND(MEDIAN(E28,F28,G28)&lt;=LISTS!$F$10,MAX(E28,F28,G28)&lt;=LISTS!$F$11),"B",IF(MAX(E28,F28,G28)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P28" s="14" t="n"/>
       <c r="Q28" s="14" t="n"/>
       <c r="R28" s="14">
         <f>IF(E28="","",IF(B28="","material?",IF(OR(F28="",G28=""),"size?",IF(I28="","exposed Y/N?",IF(H28="","qty?",IF(B28="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S28" s="12">
         <f t="array" ref="S28">IF(OR(O28="",M28=""),"",IF(B28="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B28&amp;"_"&amp;SUBSTITUTE(O28,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T28" s="12">
         <f>IF(ISNUMBER(S28),M28*S28,"")</f>
-        <v/>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="59">
@@ -6893,29 +6420,23 @@
       <c r="L29" s="10" t="n"/>
       <c r="M29" s="25">
         <f>IF(OR(E29="",F29="",G29=""),"",E29*F29*G29/1000000000*IF(H29="",1,H29))</f>
-        <v/>
       </c>
       <c r="N29" s="19">
         <f>IF(OR(E29="",F29=""),"",E29*F29/1000000*IF(H29="",1,H29))</f>
-        <v/>
       </c>
       <c r="O29" s="14">
         <f>IF(E29="","",IF(K29&lt;&gt;"",K29,IF(AND(E29*F29*G29/1000000000&lt;LISTS!$F$4,MAX(E29,F29,G29)&lt;LISTS!$F$5),"D",IF(I29="N","C",IF(J29="Y","A-CURVED",IF(AND(MEDIAN(E29,F29,G29)&lt;=LISTS!$F$10,MAX(E29,F29,G29)&lt;=LISTS!$F$11),"B",IF(MAX(E29,F29,G29)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P29" s="14" t="n"/>
       <c r="Q29" s="14" t="n"/>
       <c r="R29" s="14">
         <f>IF(E29="","",IF(B29="","material?",IF(OR(F29="",G29=""),"size?",IF(I29="","exposed Y/N?",IF(H29="","qty?",IF(B29="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S29" s="12">
         <f t="array" ref="S29">IF(OR(O29="",M29=""),"",IF(B29="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B29&amp;"_"&amp;SUBSTITUTE(O29,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T29" s="12">
         <f>IF(ISNUMBER(S29),M29*S29,"")</f>
-        <v/>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="59">
@@ -6935,29 +6456,23 @@
       <c r="L30" s="10" t="n"/>
       <c r="M30" s="25">
         <f>IF(OR(E30="",F30="",G30=""),"",E30*F30*G30/1000000000*IF(H30="",1,H30))</f>
-        <v/>
       </c>
       <c r="N30" s="19">
         <f>IF(OR(E30="",F30=""),"",E30*F30/1000000*IF(H30="",1,H30))</f>
-        <v/>
       </c>
       <c r="O30" s="14">
         <f>IF(E30="","",IF(K30&lt;&gt;"",K30,IF(AND(E30*F30*G30/1000000000&lt;LISTS!$F$4,MAX(E30,F30,G30)&lt;LISTS!$F$5),"D",IF(I30="N","C",IF(J30="Y","A-CURVED",IF(AND(MEDIAN(E30,F30,G30)&lt;=LISTS!$F$10,MAX(E30,F30,G30)&lt;=LISTS!$F$11),"B",IF(MAX(E30,F30,G30)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P30" s="14" t="n"/>
       <c r="Q30" s="14" t="n"/>
       <c r="R30" s="14">
         <f>IF(E30="","",IF(B30="","material?",IF(OR(F30="",G30=""),"size?",IF(I30="","exposed Y/N?",IF(H30="","qty?",IF(B30="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S30" s="12">
         <f t="array" ref="S30">IF(OR(O30="",M30=""),"",IF(B30="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B30&amp;"_"&amp;SUBSTITUTE(O30,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T30" s="12">
         <f>IF(ISNUMBER(S30),M30*S30,"")</f>
-        <v/>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="59">
@@ -6977,29 +6492,23 @@
       <c r="L31" s="10" t="n"/>
       <c r="M31" s="25">
         <f>IF(OR(E31="",F31="",G31=""),"",E31*F31*G31/1000000000*IF(H31="",1,H31))</f>
-        <v/>
       </c>
       <c r="N31" s="19">
         <f>IF(OR(E31="",F31=""),"",E31*F31/1000000*IF(H31="",1,H31))</f>
-        <v/>
       </c>
       <c r="O31" s="14">
         <f>IF(E31="","",IF(K31&lt;&gt;"",K31,IF(AND(E31*F31*G31/1000000000&lt;LISTS!$F$4,MAX(E31,F31,G31)&lt;LISTS!$F$5),"D",IF(I31="N","C",IF(J31="Y","A-CURVED",IF(AND(MEDIAN(E31,F31,G31)&lt;=LISTS!$F$10,MAX(E31,F31,G31)&lt;=LISTS!$F$11),"B",IF(MAX(E31,F31,G31)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P31" s="14" t="n"/>
       <c r="Q31" s="14" t="n"/>
       <c r="R31" s="14">
         <f>IF(E31="","",IF(B31="","material?",IF(OR(F31="",G31=""),"size?",IF(I31="","exposed Y/N?",IF(H31="","qty?",IF(B31="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S31" s="12">
         <f t="array" ref="S31">IF(OR(O31="",M31=""),"",IF(B31="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B31&amp;"_"&amp;SUBSTITUTE(O31,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T31" s="12">
         <f>IF(ISNUMBER(S31),M31*S31,"")</f>
-        <v/>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="59">
@@ -7019,29 +6528,23 @@
       <c r="L32" s="10" t="n"/>
       <c r="M32" s="25">
         <f>IF(OR(E32="",F32="",G32=""),"",E32*F32*G32/1000000000*IF(H32="",1,H32))</f>
-        <v/>
       </c>
       <c r="N32" s="19">
         <f>IF(OR(E32="",F32=""),"",E32*F32/1000000*IF(H32="",1,H32))</f>
-        <v/>
       </c>
       <c r="O32" s="14">
         <f>IF(E32="","",IF(K32&lt;&gt;"",K32,IF(AND(E32*F32*G32/1000000000&lt;LISTS!$F$4,MAX(E32,F32,G32)&lt;LISTS!$F$5),"D",IF(I32="N","C",IF(J32="Y","A-CURVED",IF(AND(MEDIAN(E32,F32,G32)&lt;=LISTS!$F$10,MAX(E32,F32,G32)&lt;=LISTS!$F$11),"B",IF(MAX(E32,F32,G32)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P32" s="14" t="n"/>
       <c r="Q32" s="14" t="n"/>
       <c r="R32" s="14">
         <f>IF(E32="","",IF(B32="","material?",IF(OR(F32="",G32=""),"size?",IF(I32="","exposed Y/N?",IF(H32="","qty?",IF(B32="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S32" s="12">
         <f t="array" ref="S32">IF(OR(O32="",M32=""),"",IF(B32="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B32&amp;"_"&amp;SUBSTITUTE(O32,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T32" s="12">
         <f>IF(ISNUMBER(S32),M32*S32,"")</f>
-        <v/>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="59">
@@ -7061,29 +6564,23 @@
       <c r="L33" s="10" t="n"/>
       <c r="M33" s="25">
         <f>IF(OR(E33="",F33="",G33=""),"",E33*F33*G33/1000000000*IF(H33="",1,H33))</f>
-        <v/>
       </c>
       <c r="N33" s="19">
         <f>IF(OR(E33="",F33=""),"",E33*F33/1000000*IF(H33="",1,H33))</f>
-        <v/>
       </c>
       <c r="O33" s="14">
         <f>IF(E33="","",IF(K33&lt;&gt;"",K33,IF(AND(E33*F33*G33/1000000000&lt;LISTS!$F$4,MAX(E33,F33,G33)&lt;LISTS!$F$5),"D",IF(I33="N","C",IF(J33="Y","A-CURVED",IF(AND(MEDIAN(E33,F33,G33)&lt;=LISTS!$F$10,MAX(E33,F33,G33)&lt;=LISTS!$F$11),"B",IF(MAX(E33,F33,G33)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P33" s="14" t="n"/>
       <c r="Q33" s="14" t="n"/>
       <c r="R33" s="14">
         <f>IF(E33="","",IF(B33="","material?",IF(OR(F33="",G33=""),"size?",IF(I33="","exposed Y/N?",IF(H33="","qty?",IF(B33="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S33" s="12">
         <f t="array" ref="S33">IF(OR(O33="",M33=""),"",IF(B33="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B33&amp;"_"&amp;SUBSTITUTE(O33,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T33" s="12">
         <f>IF(ISNUMBER(S33),M33*S33,"")</f>
-        <v/>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="59">
@@ -7103,29 +6600,23 @@
       <c r="L34" s="10" t="n"/>
       <c r="M34" s="25">
         <f>IF(OR(E34="",F34="",G34=""),"",E34*F34*G34/1000000000*IF(H34="",1,H34))</f>
-        <v/>
       </c>
       <c r="N34" s="19">
         <f>IF(OR(E34="",F34=""),"",E34*F34/1000000*IF(H34="",1,H34))</f>
-        <v/>
       </c>
       <c r="O34" s="14">
         <f>IF(E34="","",IF(K34&lt;&gt;"",K34,IF(AND(E34*F34*G34/1000000000&lt;LISTS!$F$4,MAX(E34,F34,G34)&lt;LISTS!$F$5),"D",IF(I34="N","C",IF(J34="Y","A-CURVED",IF(AND(MEDIAN(E34,F34,G34)&lt;=LISTS!$F$10,MAX(E34,F34,G34)&lt;=LISTS!$F$11),"B",IF(MAX(E34,F34,G34)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P34" s="14" t="n"/>
       <c r="Q34" s="14" t="n"/>
       <c r="R34" s="14">
         <f>IF(E34="","",IF(B34="","material?",IF(OR(F34="",G34=""),"size?",IF(I34="","exposed Y/N?",IF(H34="","qty?",IF(B34="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S34" s="12">
         <f t="array" ref="S34">IF(OR(O34="",M34=""),"",IF(B34="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B34&amp;"_"&amp;SUBSTITUTE(O34,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T34" s="12">
         <f>IF(ISNUMBER(S34),M34*S34,"")</f>
-        <v/>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="59">
@@ -7145,29 +6636,23 @@
       <c r="L35" s="10" t="n"/>
       <c r="M35" s="25">
         <f>IF(OR(E35="",F35="",G35=""),"",E35*F35*G35/1000000000*IF(H35="",1,H35))</f>
-        <v/>
       </c>
       <c r="N35" s="19">
         <f>IF(OR(E35="",F35=""),"",E35*F35/1000000*IF(H35="",1,H35))</f>
-        <v/>
       </c>
       <c r="O35" s="14">
         <f>IF(E35="","",IF(K35&lt;&gt;"",K35,IF(AND(E35*F35*G35/1000000000&lt;LISTS!$F$4,MAX(E35,F35,G35)&lt;LISTS!$F$5),"D",IF(I35="N","C",IF(J35="Y","A-CURVED",IF(AND(MEDIAN(E35,F35,G35)&lt;=LISTS!$F$10,MAX(E35,F35,G35)&lt;=LISTS!$F$11),"B",IF(MAX(E35,F35,G35)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P35" s="14" t="n"/>
       <c r="Q35" s="14" t="n"/>
       <c r="R35" s="14">
         <f>IF(E35="","",IF(B35="","material?",IF(OR(F35="",G35=""),"size?",IF(I35="","exposed Y/N?",IF(H35="","qty?",IF(B35="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S35" s="12">
         <f t="array" ref="S35">IF(OR(O35="",M35=""),"",IF(B35="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B35&amp;"_"&amp;SUBSTITUTE(O35,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T35" s="12">
         <f>IF(ISNUMBER(S35),M35*S35,"")</f>
-        <v/>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="59">
@@ -7187,29 +6672,23 @@
       <c r="L36" s="10" t="n"/>
       <c r="M36" s="25">
         <f>IF(OR(E36="",F36="",G36=""),"",E36*F36*G36/1000000000*IF(H36="",1,H36))</f>
-        <v/>
       </c>
       <c r="N36" s="19">
         <f>IF(OR(E36="",F36=""),"",E36*F36/1000000*IF(H36="",1,H36))</f>
-        <v/>
       </c>
       <c r="O36" s="14">
         <f>IF(E36="","",IF(K36&lt;&gt;"",K36,IF(AND(E36*F36*G36/1000000000&lt;LISTS!$F$4,MAX(E36,F36,G36)&lt;LISTS!$F$5),"D",IF(I36="N","C",IF(J36="Y","A-CURVED",IF(AND(MEDIAN(E36,F36,G36)&lt;=LISTS!$F$10,MAX(E36,F36,G36)&lt;=LISTS!$F$11),"B",IF(MAX(E36,F36,G36)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P36" s="14" t="n"/>
       <c r="Q36" s="14" t="n"/>
       <c r="R36" s="14">
         <f>IF(E36="","",IF(B36="","material?",IF(OR(F36="",G36=""),"size?",IF(I36="","exposed Y/N?",IF(H36="","qty?",IF(B36="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S36" s="12">
         <f t="array" ref="S36">IF(OR(O36="",M36=""),"",IF(B36="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B36&amp;"_"&amp;SUBSTITUTE(O36,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T36" s="12">
         <f>IF(ISNUMBER(S36),M36*S36,"")</f>
-        <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="59">
@@ -7229,29 +6708,23 @@
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="25">
         <f>IF(OR(E37="",F37="",G37=""),"",E37*F37*G37/1000000000*IF(H37="",1,H37))</f>
-        <v/>
       </c>
       <c r="N37" s="19">
         <f>IF(OR(E37="",F37=""),"",E37*F37/1000000*IF(H37="",1,H37))</f>
-        <v/>
       </c>
       <c r="O37" s="14">
         <f>IF(E37="","",IF(K37&lt;&gt;"",K37,IF(AND(E37*F37*G37/1000000000&lt;LISTS!$F$4,MAX(E37,F37,G37)&lt;LISTS!$F$5),"D",IF(I37="N","C",IF(J37="Y","A-CURVED",IF(AND(MEDIAN(E37,F37,G37)&lt;=LISTS!$F$10,MAX(E37,F37,G37)&lt;=LISTS!$F$11),"B",IF(MAX(E37,F37,G37)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
       <c r="R37" s="14">
         <f>IF(E37="","",IF(B37="","material?",IF(OR(F37="",G37=""),"size?",IF(I37="","exposed Y/N?",IF(H37="","qty?",IF(B37="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S37" s="12">
         <f t="array" ref="S37">IF(OR(O37="",M37=""),"",IF(B37="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B37&amp;"_"&amp;SUBSTITUTE(O37,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T37" s="12">
         <f>IF(ISNUMBER(S37),M37*S37,"")</f>
-        <v/>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="59">
@@ -7271,29 +6744,23 @@
       <c r="L38" s="10" t="n"/>
       <c r="M38" s="25">
         <f>IF(OR(E38="",F38="",G38=""),"",E38*F38*G38/1000000000*IF(H38="",1,H38))</f>
-        <v/>
       </c>
       <c r="N38" s="19">
         <f>IF(OR(E38="",F38=""),"",E38*F38/1000000*IF(H38="",1,H38))</f>
-        <v/>
       </c>
       <c r="O38" s="14">
         <f>IF(E38="","",IF(K38&lt;&gt;"",K38,IF(AND(E38*F38*G38/1000000000&lt;LISTS!$F$4,MAX(E38,F38,G38)&lt;LISTS!$F$5),"D",IF(I38="N","C",IF(J38="Y","A-CURVED",IF(AND(MEDIAN(E38,F38,G38)&lt;=LISTS!$F$10,MAX(E38,F38,G38)&lt;=LISTS!$F$11),"B",IF(MAX(E38,F38,G38)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P38" s="14" t="n"/>
       <c r="Q38" s="14" t="n"/>
       <c r="R38" s="14">
         <f>IF(E38="","",IF(B38="","material?",IF(OR(F38="",G38=""),"size?",IF(I38="","exposed Y/N?",IF(H38="","qty?",IF(B38="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S38" s="12">
         <f t="array" ref="S38">IF(OR(O38="",M38=""),"",IF(B38="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B38&amp;"_"&amp;SUBSTITUTE(O38,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T38" s="12">
         <f>IF(ISNUMBER(S38),M38*S38,"")</f>
-        <v/>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="59">
@@ -7313,29 +6780,23 @@
       <c r="L39" s="10" t="n"/>
       <c r="M39" s="25">
         <f>IF(OR(E39="",F39="",G39=""),"",E39*F39*G39/1000000000*IF(H39="",1,H39))</f>
-        <v/>
       </c>
       <c r="N39" s="19">
         <f>IF(OR(E39="",F39=""),"",E39*F39/1000000*IF(H39="",1,H39))</f>
-        <v/>
       </c>
       <c r="O39" s="14">
         <f>IF(E39="","",IF(K39&lt;&gt;"",K39,IF(AND(E39*F39*G39/1000000000&lt;LISTS!$F$4,MAX(E39,F39,G39)&lt;LISTS!$F$5),"D",IF(I39="N","C",IF(J39="Y","A-CURVED",IF(AND(MEDIAN(E39,F39,G39)&lt;=LISTS!$F$10,MAX(E39,F39,G39)&lt;=LISTS!$F$11),"B",IF(MAX(E39,F39,G39)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P39" s="14" t="n"/>
       <c r="Q39" s="14" t="n"/>
       <c r="R39" s="14">
         <f>IF(E39="","",IF(B39="","material?",IF(OR(F39="",G39=""),"size?",IF(I39="","exposed Y/N?",IF(H39="","qty?",IF(B39="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S39" s="12">
         <f t="array" ref="S39">IF(OR(O39="",M39=""),"",IF(B39="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B39&amp;"_"&amp;SUBSTITUTE(O39,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T39" s="12">
         <f>IF(ISNUMBER(S39),M39*S39,"")</f>
-        <v/>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="59">
@@ -7355,29 +6816,23 @@
       <c r="L40" s="10" t="n"/>
       <c r="M40" s="25">
         <f>IF(OR(E40="",F40="",G40=""),"",E40*F40*G40/1000000000*IF(H40="",1,H40))</f>
-        <v/>
       </c>
       <c r="N40" s="19">
         <f>IF(OR(E40="",F40=""),"",E40*F40/1000000*IF(H40="",1,H40))</f>
-        <v/>
       </c>
       <c r="O40" s="14">
         <f>IF(E40="","",IF(K40&lt;&gt;"",K40,IF(AND(E40*F40*G40/1000000000&lt;LISTS!$F$4,MAX(E40,F40,G40)&lt;LISTS!$F$5),"D",IF(I40="N","C",IF(J40="Y","A-CURVED",IF(AND(MEDIAN(E40,F40,G40)&lt;=LISTS!$F$10,MAX(E40,F40,G40)&lt;=LISTS!$F$11),"B",IF(MAX(E40,F40,G40)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P40" s="14" t="n"/>
       <c r="Q40" s="14" t="n"/>
       <c r="R40" s="14">
         <f>IF(E40="","",IF(B40="","material?",IF(OR(F40="",G40=""),"size?",IF(I40="","exposed Y/N?",IF(H40="","qty?",IF(B40="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S40" s="12">
         <f t="array" ref="S40">IF(OR(O40="",M40=""),"",IF(B40="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B40&amp;"_"&amp;SUBSTITUTE(O40,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T40" s="12">
         <f>IF(ISNUMBER(S40),M40*S40,"")</f>
-        <v/>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="59">
@@ -7397,29 +6852,23 @@
       <c r="L41" s="10" t="n"/>
       <c r="M41" s="25">
         <f>IF(OR(E41="",F41="",G41=""),"",E41*F41*G41/1000000000*IF(H41="",1,H41))</f>
-        <v/>
       </c>
       <c r="N41" s="19">
         <f>IF(OR(E41="",F41=""),"",E41*F41/1000000*IF(H41="",1,H41))</f>
-        <v/>
       </c>
       <c r="O41" s="14">
         <f>IF(E41="","",IF(K41&lt;&gt;"",K41,IF(AND(E41*F41*G41/1000000000&lt;LISTS!$F$4,MAX(E41,F41,G41)&lt;LISTS!$F$5),"D",IF(I41="N","C",IF(J41="Y","A-CURVED",IF(AND(MEDIAN(E41,F41,G41)&lt;=LISTS!$F$10,MAX(E41,F41,G41)&lt;=LISTS!$F$11),"B",IF(MAX(E41,F41,G41)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P41" s="14" t="n"/>
       <c r="Q41" s="14" t="n"/>
       <c r="R41" s="14">
         <f>IF(E41="","",IF(B41="","material?",IF(OR(F41="",G41=""),"size?",IF(I41="","exposed Y/N?",IF(H41="","qty?",IF(B41="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S41" s="12">
         <f t="array" ref="S41">IF(OR(O41="",M41=""),"",IF(B41="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B41&amp;"_"&amp;SUBSTITUTE(O41,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T41" s="12">
         <f>IF(ISNUMBER(S41),M41*S41,"")</f>
-        <v/>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="59">
@@ -7439,29 +6888,23 @@
       <c r="L42" s="10" t="n"/>
       <c r="M42" s="25">
         <f>IF(OR(E42="",F42="",G42=""),"",E42*F42*G42/1000000000*IF(H42="",1,H42))</f>
-        <v/>
       </c>
       <c r="N42" s="19">
         <f>IF(OR(E42="",F42=""),"",E42*F42/1000000*IF(H42="",1,H42))</f>
-        <v/>
       </c>
       <c r="O42" s="14">
         <f>IF(E42="","",IF(K42&lt;&gt;"",K42,IF(AND(E42*F42*G42/1000000000&lt;LISTS!$F$4,MAX(E42,F42,G42)&lt;LISTS!$F$5),"D",IF(I42="N","C",IF(J42="Y","A-CURVED",IF(AND(MEDIAN(E42,F42,G42)&lt;=LISTS!$F$10,MAX(E42,F42,G42)&lt;=LISTS!$F$11),"B",IF(MAX(E42,F42,G42)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P42" s="14" t="n"/>
       <c r="Q42" s="14" t="n"/>
       <c r="R42" s="14">
         <f>IF(E42="","",IF(B42="","material?",IF(OR(F42="",G42=""),"size?",IF(I42="","exposed Y/N?",IF(H42="","qty?",IF(B42="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S42" s="12">
         <f t="array" ref="S42">IF(OR(O42="",M42=""),"",IF(B42="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B42&amp;"_"&amp;SUBSTITUTE(O42,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T42" s="12">
         <f>IF(ISNUMBER(S42),M42*S42,"")</f>
-        <v/>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="59"/>
@@ -7587,35 +7030,27 @@
       <c r="L46" s="10" t="n"/>
       <c r="M46" s="25">
         <f>IF(OR(E46="",F46="",G46=""),"",E46*F46*G46/1000000000*IF(H46="",1,H46))</f>
-        <v/>
       </c>
       <c r="N46" s="19">
         <f>IF(OR(E46="",F46=""),"",E46*F46/1000000*IF(H46="",1,H46))</f>
-        <v/>
       </c>
       <c r="O46" s="14">
         <f>IF(OR(E46="",F46=""),"",MAX(INT(LISTS!$F$6/(E46+LISTS!$F$8))*INT(LISTS!$F$7/(F46+LISTS!$F$8)),INT(LISTS!$F$6/(F46+LISTS!$F$8))*INT(LISTS!$F$7/(E46+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P46" s="19">
         <f>IF(K46&lt;&gt;"",K46,IF(OR(O46="",O46=0),"",IF(H46="",1,H46)/O46))</f>
-        <v/>
       </c>
       <c r="Q46" s="36">
         <f>IF(OR(K46&lt;&gt;"",P46=""),"",1-(IF(H46="",1,H46)*E46*F46)/(ROUNDUP(P46,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R46" s="14">
         <f>IF(AND(E46="",K46=""),"",IF(B46="","panel type?",IF(AND(K46="",O46=0),"panel bigger than sheet",IF(AND(G46&lt;&gt;"",IFERROR(VALUE(MID(B46,5,FIND("-",B46,5)-5)),0)&lt;&gt;G46),"T must match panel type",IF(I46="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S46" s="12">
         <f t="array" ref="S46">IF(OR(B46="",P46=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B46,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T46" s="12">
         <f>IF(ISNUMBER(S46),IF(K46&lt;&gt;"",K46,IF(Q46&gt;RATES!$C$97,P46*(1+RATES!$C$98),ROUNDUP(P46,0)))*S46,"")</f>
-        <v/>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="59">
@@ -7635,35 +7070,27 @@
       <c r="L47" s="10" t="n"/>
       <c r="M47" s="25">
         <f>IF(OR(E47="",F47="",G47=""),"",E47*F47*G47/1000000000*IF(H47="",1,H47))</f>
-        <v/>
       </c>
       <c r="N47" s="19">
         <f>IF(OR(E47="",F47=""),"",E47*F47/1000000*IF(H47="",1,H47))</f>
-        <v/>
       </c>
       <c r="O47" s="14">
         <f>IF(OR(E47="",F47=""),"",MAX(INT(LISTS!$F$6/(E47+LISTS!$F$8))*INT(LISTS!$F$7/(F47+LISTS!$F$8)),INT(LISTS!$F$6/(F47+LISTS!$F$8))*INT(LISTS!$F$7/(E47+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P47" s="19">
         <f>IF(K47&lt;&gt;"",K47,IF(OR(O47="",O47=0),"",IF(H47="",1,H47)/O47))</f>
-        <v/>
       </c>
       <c r="Q47" s="36">
         <f>IF(OR(K47&lt;&gt;"",P47=""),"",1-(IF(H47="",1,H47)*E47*F47)/(ROUNDUP(P47,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R47" s="14">
         <f>IF(AND(E47="",K47=""),"",IF(B47="","panel type?",IF(AND(K47="",O47=0),"panel bigger than sheet",IF(AND(G47&lt;&gt;"",IFERROR(VALUE(MID(B47,5,FIND("-",B47,5)-5)),0)&lt;&gt;G47),"T must match panel type",IF(I47="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S47" s="12">
         <f t="array" ref="S47">IF(OR(B47="",P47=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B47,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T47" s="12">
         <f>IF(ISNUMBER(S47),IF(K47&lt;&gt;"",K47,IF(Q47&gt;RATES!$C$97,P47*(1+RATES!$C$98),ROUNDUP(P47,0)))*S47,"")</f>
-        <v/>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="59">
@@ -7683,35 +7110,27 @@
       <c r="L48" s="10" t="n"/>
       <c r="M48" s="25">
         <f>IF(OR(E48="",F48="",G48=""),"",E48*F48*G48/1000000000*IF(H48="",1,H48))</f>
-        <v/>
       </c>
       <c r="N48" s="19">
         <f>IF(OR(E48="",F48=""),"",E48*F48/1000000*IF(H48="",1,H48))</f>
-        <v/>
       </c>
       <c r="O48" s="14">
         <f>IF(OR(E48="",F48=""),"",MAX(INT(LISTS!$F$6/(E48+LISTS!$F$8))*INT(LISTS!$F$7/(F48+LISTS!$F$8)),INT(LISTS!$F$6/(F48+LISTS!$F$8))*INT(LISTS!$F$7/(E48+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P48" s="19">
         <f>IF(K48&lt;&gt;"",K48,IF(OR(O48="",O48=0),"",IF(H48="",1,H48)/O48))</f>
-        <v/>
       </c>
       <c r="Q48" s="36">
         <f>IF(OR(K48&lt;&gt;"",P48=""),"",1-(IF(H48="",1,H48)*E48*F48)/(ROUNDUP(P48,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R48" s="14">
         <f>IF(AND(E48="",K48=""),"",IF(B48="","panel type?",IF(AND(K48="",O48=0),"panel bigger than sheet",IF(AND(G48&lt;&gt;"",IFERROR(VALUE(MID(B48,5,FIND("-",B48,5)-5)),0)&lt;&gt;G48),"T must match panel type",IF(I48="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S48" s="12">
         <f t="array" ref="S48">IF(OR(B48="",P48=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B48,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T48" s="12">
         <f>IF(ISNUMBER(S48),IF(K48&lt;&gt;"",K48,IF(Q48&gt;RATES!$C$97,P48*(1+RATES!$C$98),ROUNDUP(P48,0)))*S48,"")</f>
-        <v/>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="59">
@@ -7731,35 +7150,27 @@
       <c r="L49" s="10" t="n"/>
       <c r="M49" s="25">
         <f>IF(OR(E49="",F49="",G49=""),"",E49*F49*G49/1000000000*IF(H49="",1,H49))</f>
-        <v/>
       </c>
       <c r="N49" s="19">
         <f>IF(OR(E49="",F49=""),"",E49*F49/1000000*IF(H49="",1,H49))</f>
-        <v/>
       </c>
       <c r="O49" s="14">
         <f>IF(OR(E49="",F49=""),"",MAX(INT(LISTS!$F$6/(E49+LISTS!$F$8))*INT(LISTS!$F$7/(F49+LISTS!$F$8)),INT(LISTS!$F$6/(F49+LISTS!$F$8))*INT(LISTS!$F$7/(E49+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P49" s="19">
         <f>IF(K49&lt;&gt;"",K49,IF(OR(O49="",O49=0),"",IF(H49="",1,H49)/O49))</f>
-        <v/>
       </c>
       <c r="Q49" s="36">
         <f>IF(OR(K49&lt;&gt;"",P49=""),"",1-(IF(H49="",1,H49)*E49*F49)/(ROUNDUP(P49,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R49" s="14">
         <f>IF(AND(E49="",K49=""),"",IF(B49="","panel type?",IF(AND(K49="",O49=0),"panel bigger than sheet",IF(AND(G49&lt;&gt;"",IFERROR(VALUE(MID(B49,5,FIND("-",B49,5)-5)),0)&lt;&gt;G49),"T must match panel type",IF(I49="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S49" s="12">
         <f t="array" ref="S49">IF(OR(B49="",P49=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B49,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T49" s="12">
         <f>IF(ISNUMBER(S49),IF(K49&lt;&gt;"",K49,IF(Q49&gt;RATES!$C$97,P49*(1+RATES!$C$98),ROUNDUP(P49,0)))*S49,"")</f>
-        <v/>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="59">
@@ -7779,35 +7190,27 @@
       <c r="L50" s="10" t="n"/>
       <c r="M50" s="25">
         <f>IF(OR(E50="",F50="",G50=""),"",E50*F50*G50/1000000000*IF(H50="",1,H50))</f>
-        <v/>
       </c>
       <c r="N50" s="19">
         <f>IF(OR(E50="",F50=""),"",E50*F50/1000000*IF(H50="",1,H50))</f>
-        <v/>
       </c>
       <c r="O50" s="14">
         <f>IF(OR(E50="",F50=""),"",MAX(INT(LISTS!$F$6/(E50+LISTS!$F$8))*INT(LISTS!$F$7/(F50+LISTS!$F$8)),INT(LISTS!$F$6/(F50+LISTS!$F$8))*INT(LISTS!$F$7/(E50+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P50" s="19">
         <f>IF(K50&lt;&gt;"",K50,IF(OR(O50="",O50=0),"",IF(H50="",1,H50)/O50))</f>
-        <v/>
       </c>
       <c r="Q50" s="36">
         <f>IF(OR(K50&lt;&gt;"",P50=""),"",1-(IF(H50="",1,H50)*E50*F50)/(ROUNDUP(P50,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R50" s="14">
         <f>IF(AND(E50="",K50=""),"",IF(B50="","panel type?",IF(AND(K50="",O50=0),"panel bigger than sheet",IF(AND(G50&lt;&gt;"",IFERROR(VALUE(MID(B50,5,FIND("-",B50,5)-5)),0)&lt;&gt;G50),"T must match panel type",IF(I50="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S50" s="12">
         <f t="array" ref="S50">IF(OR(B50="",P50=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B50,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T50" s="12">
         <f>IF(ISNUMBER(S50),IF(K50&lt;&gt;"",K50,IF(Q50&gt;RATES!$C$97,P50*(1+RATES!$C$98),ROUNDUP(P50,0)))*S50,"")</f>
-        <v/>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="59">
@@ -7827,35 +7230,27 @@
       <c r="L51" s="10" t="n"/>
       <c r="M51" s="25">
         <f>IF(OR(E51="",F51="",G51=""),"",E51*F51*G51/1000000000*IF(H51="",1,H51))</f>
-        <v/>
       </c>
       <c r="N51" s="19">
         <f>IF(OR(E51="",F51=""),"",E51*F51/1000000*IF(H51="",1,H51))</f>
-        <v/>
       </c>
       <c r="O51" s="14">
         <f>IF(OR(E51="",F51=""),"",MAX(INT(LISTS!$F$6/(E51+LISTS!$F$8))*INT(LISTS!$F$7/(F51+LISTS!$F$8)),INT(LISTS!$F$6/(F51+LISTS!$F$8))*INT(LISTS!$F$7/(E51+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P51" s="19">
         <f>IF(K51&lt;&gt;"",K51,IF(OR(O51="",O51=0),"",IF(H51="",1,H51)/O51))</f>
-        <v/>
       </c>
       <c r="Q51" s="36">
         <f>IF(OR(K51&lt;&gt;"",P51=""),"",1-(IF(H51="",1,H51)*E51*F51)/(ROUNDUP(P51,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R51" s="14">
         <f>IF(AND(E51="",K51=""),"",IF(B51="","panel type?",IF(AND(K51="",O51=0),"panel bigger than sheet",IF(AND(G51&lt;&gt;"",IFERROR(VALUE(MID(B51,5,FIND("-",B51,5)-5)),0)&lt;&gt;G51),"T must match panel type",IF(I51="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S51" s="12">
         <f t="array" ref="S51">IF(OR(B51="",P51=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B51,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T51" s="12">
         <f>IF(ISNUMBER(S51),IF(K51&lt;&gt;"",K51,IF(Q51&gt;RATES!$C$97,P51*(1+RATES!$C$98),ROUNDUP(P51,0)))*S51,"")</f>
-        <v/>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="59">
@@ -7875,35 +7270,27 @@
       <c r="L52" s="10" t="n"/>
       <c r="M52" s="25">
         <f>IF(OR(E52="",F52="",G52=""),"",E52*F52*G52/1000000000*IF(H52="",1,H52))</f>
-        <v/>
       </c>
       <c r="N52" s="19">
         <f>IF(OR(E52="",F52=""),"",E52*F52/1000000*IF(H52="",1,H52))</f>
-        <v/>
       </c>
       <c r="O52" s="14">
         <f>IF(OR(E52="",F52=""),"",MAX(INT(LISTS!$F$6/(E52+LISTS!$F$8))*INT(LISTS!$F$7/(F52+LISTS!$F$8)),INT(LISTS!$F$6/(F52+LISTS!$F$8))*INT(LISTS!$F$7/(E52+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P52" s="19">
         <f>IF(K52&lt;&gt;"",K52,IF(OR(O52="",O52=0),"",IF(H52="",1,H52)/O52))</f>
-        <v/>
       </c>
       <c r="Q52" s="36">
         <f>IF(OR(K52&lt;&gt;"",P52=""),"",1-(IF(H52="",1,H52)*E52*F52)/(ROUNDUP(P52,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R52" s="14">
         <f>IF(AND(E52="",K52=""),"",IF(B52="","panel type?",IF(AND(K52="",O52=0),"panel bigger than sheet",IF(AND(G52&lt;&gt;"",IFERROR(VALUE(MID(B52,5,FIND("-",B52,5)-5)),0)&lt;&gt;G52),"T must match panel type",IF(I52="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S52" s="12">
         <f t="array" ref="S52">IF(OR(B52="",P52=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B52,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T52" s="12">
         <f>IF(ISNUMBER(S52),IF(K52&lt;&gt;"",K52,IF(Q52&gt;RATES!$C$97,P52*(1+RATES!$C$98),ROUNDUP(P52,0)))*S52,"")</f>
-        <v/>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="59">
@@ -7923,35 +7310,27 @@
       <c r="L53" s="10" t="n"/>
       <c r="M53" s="25">
         <f>IF(OR(E53="",F53="",G53=""),"",E53*F53*G53/1000000000*IF(H53="",1,H53))</f>
-        <v/>
       </c>
       <c r="N53" s="19">
         <f>IF(OR(E53="",F53=""),"",E53*F53/1000000*IF(H53="",1,H53))</f>
-        <v/>
       </c>
       <c r="O53" s="14">
         <f>IF(OR(E53="",F53=""),"",MAX(INT(LISTS!$F$6/(E53+LISTS!$F$8))*INT(LISTS!$F$7/(F53+LISTS!$F$8)),INT(LISTS!$F$6/(F53+LISTS!$F$8))*INT(LISTS!$F$7/(E53+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P53" s="19">
         <f>IF(K53&lt;&gt;"",K53,IF(OR(O53="",O53=0),"",IF(H53="",1,H53)/O53))</f>
-        <v/>
       </c>
       <c r="Q53" s="36">
         <f>IF(OR(K53&lt;&gt;"",P53=""),"",1-(IF(H53="",1,H53)*E53*F53)/(ROUNDUP(P53,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R53" s="14">
         <f>IF(AND(E53="",K53=""),"",IF(B53="","panel type?",IF(AND(K53="",O53=0),"panel bigger than sheet",IF(AND(G53&lt;&gt;"",IFERROR(VALUE(MID(B53,5,FIND("-",B53,5)-5)),0)&lt;&gt;G53),"T must match panel type",IF(I53="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S53" s="12">
         <f t="array" ref="S53">IF(OR(B53="",P53=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B53,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T53" s="12">
         <f>IF(ISNUMBER(S53),IF(K53&lt;&gt;"",K53,IF(Q53&gt;RATES!$C$97,P53*(1+RATES!$C$98),ROUNDUP(P53,0)))*S53,"")</f>
-        <v/>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="59">
@@ -7971,35 +7350,27 @@
       <c r="L54" s="10" t="n"/>
       <c r="M54" s="25">
         <f>IF(OR(E54="",F54="",G54=""),"",E54*F54*G54/1000000000*IF(H54="",1,H54))</f>
-        <v/>
       </c>
       <c r="N54" s="19">
         <f>IF(OR(E54="",F54=""),"",E54*F54/1000000*IF(H54="",1,H54))</f>
-        <v/>
       </c>
       <c r="O54" s="14">
         <f>IF(OR(E54="",F54=""),"",MAX(INT(LISTS!$F$6/(E54+LISTS!$F$8))*INT(LISTS!$F$7/(F54+LISTS!$F$8)),INT(LISTS!$F$6/(F54+LISTS!$F$8))*INT(LISTS!$F$7/(E54+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P54" s="19">
         <f>IF(K54&lt;&gt;"",K54,IF(OR(O54="",O54=0),"",IF(H54="",1,H54)/O54))</f>
-        <v/>
       </c>
       <c r="Q54" s="36">
         <f>IF(OR(K54&lt;&gt;"",P54=""),"",1-(IF(H54="",1,H54)*E54*F54)/(ROUNDUP(P54,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R54" s="14">
         <f>IF(AND(E54="",K54=""),"",IF(B54="","panel type?",IF(AND(K54="",O54=0),"panel bigger than sheet",IF(AND(G54&lt;&gt;"",IFERROR(VALUE(MID(B54,5,FIND("-",B54,5)-5)),0)&lt;&gt;G54),"T must match panel type",IF(I54="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S54" s="12">
         <f t="array" ref="S54">IF(OR(B54="",P54=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B54,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T54" s="12">
         <f>IF(ISNUMBER(S54),IF(K54&lt;&gt;"",K54,IF(Q54&gt;RATES!$C$97,P54*(1+RATES!$C$98),ROUNDUP(P54,0)))*S54,"")</f>
-        <v/>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="59">
@@ -8019,35 +7390,27 @@
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="25">
         <f>IF(OR(E55="",F55="",G55=""),"",E55*F55*G55/1000000000*IF(H55="",1,H55))</f>
-        <v/>
       </c>
       <c r="N55" s="19">
         <f>IF(OR(E55="",F55=""),"",E55*F55/1000000*IF(H55="",1,H55))</f>
-        <v/>
       </c>
       <c r="O55" s="14">
         <f>IF(OR(E55="",F55=""),"",MAX(INT(LISTS!$F$6/(E55+LISTS!$F$8))*INT(LISTS!$F$7/(F55+LISTS!$F$8)),INT(LISTS!$F$6/(F55+LISTS!$F$8))*INT(LISTS!$F$7/(E55+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P55" s="19">
         <f>IF(K55&lt;&gt;"",K55,IF(OR(O55="",O55=0),"",IF(H55="",1,H55)/O55))</f>
-        <v/>
       </c>
       <c r="Q55" s="36">
         <f>IF(OR(K55&lt;&gt;"",P55=""),"",1-(IF(H55="",1,H55)*E55*F55)/(ROUNDUP(P55,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R55" s="14">
         <f>IF(AND(E55="",K55=""),"",IF(B55="","panel type?",IF(AND(K55="",O55=0),"panel bigger than sheet",IF(AND(G55&lt;&gt;"",IFERROR(VALUE(MID(B55,5,FIND("-",B55,5)-5)),0)&lt;&gt;G55),"T must match panel type",IF(I55="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S55" s="12">
         <f t="array" ref="S55">IF(OR(B55="",P55=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B55,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T55" s="12">
         <f>IF(ISNUMBER(S55),IF(K55&lt;&gt;"",K55,IF(Q55&gt;RATES!$C$97,P55*(1+RATES!$C$98),ROUNDUP(P55,0)))*S55,"")</f>
-        <v/>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="59">
@@ -8067,35 +7430,27 @@
       <c r="L56" s="10" t="n"/>
       <c r="M56" s="25">
         <f>IF(OR(E56="",F56="",G56=""),"",E56*F56*G56/1000000000*IF(H56="",1,H56))</f>
-        <v/>
       </c>
       <c r="N56" s="19">
         <f>IF(OR(E56="",F56=""),"",E56*F56/1000000*IF(H56="",1,H56))</f>
-        <v/>
       </c>
       <c r="O56" s="14">
         <f>IF(OR(E56="",F56=""),"",MAX(INT(LISTS!$F$6/(E56+LISTS!$F$8))*INT(LISTS!$F$7/(F56+LISTS!$F$8)),INT(LISTS!$F$6/(F56+LISTS!$F$8))*INT(LISTS!$F$7/(E56+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P56" s="19">
         <f>IF(K56&lt;&gt;"",K56,IF(OR(O56="",O56=0),"",IF(H56="",1,H56)/O56))</f>
-        <v/>
       </c>
       <c r="Q56" s="36">
         <f>IF(OR(K56&lt;&gt;"",P56=""),"",1-(IF(H56="",1,H56)*E56*F56)/(ROUNDUP(P56,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R56" s="14">
         <f>IF(AND(E56="",K56=""),"",IF(B56="","panel type?",IF(AND(K56="",O56=0),"panel bigger than sheet",IF(AND(G56&lt;&gt;"",IFERROR(VALUE(MID(B56,5,FIND("-",B56,5)-5)),0)&lt;&gt;G56),"T must match panel type",IF(I56="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S56" s="12">
         <f t="array" ref="S56">IF(OR(B56="",P56=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B56,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T56" s="12">
         <f>IF(ISNUMBER(S56),IF(K56&lt;&gt;"",K56,IF(Q56&gt;RATES!$C$97,P56*(1+RATES!$C$98),ROUNDUP(P56,0)))*S56,"")</f>
-        <v/>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="59">
@@ -8115,35 +7470,27 @@
       <c r="L57" s="10" t="n"/>
       <c r="M57" s="25">
         <f>IF(OR(E57="",F57="",G57=""),"",E57*F57*G57/1000000000*IF(H57="",1,H57))</f>
-        <v/>
       </c>
       <c r="N57" s="19">
         <f>IF(OR(E57="",F57=""),"",E57*F57/1000000*IF(H57="",1,H57))</f>
-        <v/>
       </c>
       <c r="O57" s="14">
         <f>IF(OR(E57="",F57=""),"",MAX(INT(LISTS!$F$6/(E57+LISTS!$F$8))*INT(LISTS!$F$7/(F57+LISTS!$F$8)),INT(LISTS!$F$6/(F57+LISTS!$F$8))*INT(LISTS!$F$7/(E57+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P57" s="19">
         <f>IF(K57&lt;&gt;"",K57,IF(OR(O57="",O57=0),"",IF(H57="",1,H57)/O57))</f>
-        <v/>
       </c>
       <c r="Q57" s="36">
         <f>IF(OR(K57&lt;&gt;"",P57=""),"",1-(IF(H57="",1,H57)*E57*F57)/(ROUNDUP(P57,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R57" s="14">
         <f>IF(AND(E57="",K57=""),"",IF(B57="","panel type?",IF(AND(K57="",O57=0),"panel bigger than sheet",IF(AND(G57&lt;&gt;"",IFERROR(VALUE(MID(B57,5,FIND("-",B57,5)-5)),0)&lt;&gt;G57),"T must match panel type",IF(I57="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S57" s="12">
         <f t="array" ref="S57">IF(OR(B57="",P57=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B57,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T57" s="12">
         <f>IF(ISNUMBER(S57),IF(K57&lt;&gt;"",K57,IF(Q57&gt;RATES!$C$97,P57*(1+RATES!$C$98),ROUNDUP(P57,0)))*S57,"")</f>
-        <v/>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="59">
@@ -8163,35 +7510,27 @@
       <c r="L58" s="10" t="n"/>
       <c r="M58" s="25">
         <f>IF(OR(E58="",F58="",G58=""),"",E58*F58*G58/1000000000*IF(H58="",1,H58))</f>
-        <v/>
       </c>
       <c r="N58" s="19">
         <f>IF(OR(E58="",F58=""),"",E58*F58/1000000*IF(H58="",1,H58))</f>
-        <v/>
       </c>
       <c r="O58" s="14">
         <f>IF(OR(E58="",F58=""),"",MAX(INT(LISTS!$F$6/(E58+LISTS!$F$8))*INT(LISTS!$F$7/(F58+LISTS!$F$8)),INT(LISTS!$F$6/(F58+LISTS!$F$8))*INT(LISTS!$F$7/(E58+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P58" s="19">
         <f>IF(K58&lt;&gt;"",K58,IF(OR(O58="",O58=0),"",IF(H58="",1,H58)/O58))</f>
-        <v/>
       </c>
       <c r="Q58" s="36">
         <f>IF(OR(K58&lt;&gt;"",P58=""),"",1-(IF(H58="",1,H58)*E58*F58)/(ROUNDUP(P58,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R58" s="14">
         <f>IF(AND(E58="",K58=""),"",IF(B58="","panel type?",IF(AND(K58="",O58=0),"panel bigger than sheet",IF(AND(G58&lt;&gt;"",IFERROR(VALUE(MID(B58,5,FIND("-",B58,5)-5)),0)&lt;&gt;G58),"T must match panel type",IF(I58="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S58" s="12">
         <f t="array" ref="S58">IF(OR(B58="",P58=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B58,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T58" s="12">
         <f>IF(ISNUMBER(S58),IF(K58&lt;&gt;"",K58,IF(Q58&gt;RATES!$C$97,P58*(1+RATES!$C$98),ROUNDUP(P58,0)))*S58,"")</f>
-        <v/>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="59">
@@ -8211,35 +7550,27 @@
       <c r="L59" s="10" t="n"/>
       <c r="M59" s="25">
         <f>IF(OR(E59="",F59="",G59=""),"",E59*F59*G59/1000000000*IF(H59="",1,H59))</f>
-        <v/>
       </c>
       <c r="N59" s="19">
         <f>IF(OR(E59="",F59=""),"",E59*F59/1000000*IF(H59="",1,H59))</f>
-        <v/>
       </c>
       <c r="O59" s="14">
         <f>IF(OR(E59="",F59=""),"",MAX(INT(LISTS!$F$6/(E59+LISTS!$F$8))*INT(LISTS!$F$7/(F59+LISTS!$F$8)),INT(LISTS!$F$6/(F59+LISTS!$F$8))*INT(LISTS!$F$7/(E59+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P59" s="19">
         <f>IF(K59&lt;&gt;"",K59,IF(OR(O59="",O59=0),"",IF(H59="",1,H59)/O59))</f>
-        <v/>
       </c>
       <c r="Q59" s="36">
         <f>IF(OR(K59&lt;&gt;"",P59=""),"",1-(IF(H59="",1,H59)*E59*F59)/(ROUNDUP(P59,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R59" s="14">
         <f>IF(AND(E59="",K59=""),"",IF(B59="","panel type?",IF(AND(K59="",O59=0),"panel bigger than sheet",IF(AND(G59&lt;&gt;"",IFERROR(VALUE(MID(B59,5,FIND("-",B59,5)-5)),0)&lt;&gt;G59),"T must match panel type",IF(I59="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S59" s="12">
         <f t="array" ref="S59">IF(OR(B59="",P59=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B59,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T59" s="12">
         <f>IF(ISNUMBER(S59),IF(K59&lt;&gt;"",K59,IF(Q59&gt;RATES!$C$97,P59*(1+RATES!$C$98),ROUNDUP(P59,0)))*S59,"")</f>
-        <v/>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="59">
@@ -8259,35 +7590,27 @@
       <c r="L60" s="10" t="n"/>
       <c r="M60" s="25">
         <f>IF(OR(E60="",F60="",G60=""),"",E60*F60*G60/1000000000*IF(H60="",1,H60))</f>
-        <v/>
       </c>
       <c r="N60" s="19">
         <f>IF(OR(E60="",F60=""),"",E60*F60/1000000*IF(H60="",1,H60))</f>
-        <v/>
       </c>
       <c r="O60" s="14">
         <f>IF(OR(E60="",F60=""),"",MAX(INT(LISTS!$F$6/(E60+LISTS!$F$8))*INT(LISTS!$F$7/(F60+LISTS!$F$8)),INT(LISTS!$F$6/(F60+LISTS!$F$8))*INT(LISTS!$F$7/(E60+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P60" s="19">
         <f>IF(K60&lt;&gt;"",K60,IF(OR(O60="",O60=0),"",IF(H60="",1,H60)/O60))</f>
-        <v/>
       </c>
       <c r="Q60" s="36">
         <f>IF(OR(K60&lt;&gt;"",P60=""),"",1-(IF(H60="",1,H60)*E60*F60)/(ROUNDUP(P60,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R60" s="14">
         <f>IF(AND(E60="",K60=""),"",IF(B60="","panel type?",IF(AND(K60="",O60=0),"panel bigger than sheet",IF(AND(G60&lt;&gt;"",IFERROR(VALUE(MID(B60,5,FIND("-",B60,5)-5)),0)&lt;&gt;G60),"T must match panel type",IF(I60="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S60" s="12">
         <f t="array" ref="S60">IF(OR(B60="",P60=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B60,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T60" s="12">
         <f>IF(ISNUMBER(S60),IF(K60&lt;&gt;"",K60,IF(Q60&gt;RATES!$C$97,P60*(1+RATES!$C$98),ROUNDUP(P60,0)))*S60,"")</f>
-        <v/>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="59"/>
@@ -8384,7 +7707,6 @@
       <c r="S64" s="37" t="n"/>
       <c r="T64" s="38">
         <f>IF(OR(H64="",S64=""),"",H64*S64)</f>
-        <v/>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="59">
@@ -8411,7 +7733,6 @@
       <c r="S65" s="37" t="n"/>
       <c r="T65" s="38">
         <f>IF(OR(H65="",S65=""),"",H65*S65)</f>
-        <v/>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="59">
@@ -8438,7 +7759,6 @@
       <c r="S66" s="37" t="n"/>
       <c r="T66" s="38">
         <f>IF(OR(H66="",S66=""),"",H66*S66)</f>
-        <v/>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="59">
@@ -8465,7 +7785,6 @@
       <c r="S67" s="37" t="n"/>
       <c r="T67" s="38">
         <f>IF(OR(H67="",S67=""),"",H67*S67)</f>
-        <v/>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="59">
@@ -8492,7 +7811,6 @@
       <c r="S68" s="37" t="n"/>
       <c r="T68" s="38">
         <f>IF(OR(H68="",S68=""),"",H68*S68)</f>
-        <v/>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="59">
@@ -8519,7 +7837,6 @@
       <c r="S69" s="37" t="n"/>
       <c r="T69" s="38">
         <f>IF(OR(H69="",S69=""),"",H69*S69)</f>
-        <v/>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="59">
@@ -8546,7 +7863,6 @@
       <c r="S70" s="37" t="n"/>
       <c r="T70" s="38">
         <f>IF(OR(H70="",S70=""),"",H70*S70)</f>
-        <v/>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="59">
@@ -8573,7 +7889,6 @@
       <c r="S71" s="37" t="n"/>
       <c r="T71" s="38">
         <f>IF(OR(H71="",S71=""),"",H71*S71)</f>
-        <v/>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="59">
@@ -8600,7 +7915,6 @@
       <c r="S72" s="37" t="n"/>
       <c r="T72" s="38">
         <f>IF(OR(H72="",S72=""),"",H72*S72)</f>
-        <v/>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="59">
@@ -8627,7 +7941,6 @@
       <c r="S73" s="37" t="n"/>
       <c r="T73" s="38">
         <f>IF(OR(H73="",S73=""),"",H73*S73)</f>
-        <v/>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="59">
@@ -8654,7 +7967,6 @@
       <c r="S74" s="37" t="n"/>
       <c r="T74" s="38">
         <f>IF(OR(H74="",S74=""),"",H74*S74)</f>
-        <v/>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="59">
@@ -8681,7 +7993,6 @@
       <c r="S75" s="37" t="n"/>
       <c r="T75" s="38">
         <f>IF(OR(H75="",S75=""),"",H75*S75)</f>
-        <v/>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="59">
@@ -8708,7 +8019,6 @@
       <c r="S76" s="37" t="n"/>
       <c r="T76" s="38">
         <f>IF(OR(H76="",S76=""),"",H76*S76)</f>
-        <v/>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="59">
@@ -8735,7 +8045,6 @@
       <c r="S77" s="37" t="n"/>
       <c r="T77" s="38">
         <f>IF(OR(H77="",S77=""),"",H77*S77)</f>
-        <v/>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="59">
@@ -8762,7 +8071,6 @@
       <c r="S78" s="37" t="n"/>
       <c r="T78" s="38">
         <f>IF(OR(H78="",S78=""),"",H78*S78)</f>
-        <v/>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="59"/>
@@ -8782,7 +8090,6 @@
       </c>
       <c r="D82" s="25">
         <f>SUM(M18:M42)</f>
-        <v/>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="59">
@@ -8793,7 +8100,6 @@
       </c>
       <c r="D83" s="17">
         <f>SUM(P46:P60)</f>
-        <v/>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="59">
@@ -8804,7 +8110,6 @@
       </c>
       <c r="D84" s="19">
         <f>SUMIF(I18:I42,"Y",N18:N42)+SUMIF(I46:I60,1,N46:N60)+2*SUMIF(I46:I60,2,N46:N60)</f>
-        <v/>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -8820,7 +8125,6 @@
       </c>
       <c r="D85" s="39">
         <f>G15</f>
-        <v/>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="59">
@@ -8831,7 +8135,6 @@
       </c>
       <c r="D86" s="19">
         <f>M15</f>
-        <v/>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="59">
@@ -8842,7 +8145,6 @@
       </c>
       <c r="D87" s="12">
         <f>SUM(T18:T42)</f>
-        <v/>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -8858,7 +8160,6 @@
       </c>
       <c r="D88" s="12">
         <f>D82*RATES!$C$46</f>
-        <v/>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -8874,7 +8175,6 @@
       </c>
       <c r="D89" s="12">
         <f>SUM(T46:T60)</f>
-        <v/>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -8890,7 +8190,6 @@
       </c>
       <c r="D90" s="12">
         <f>D84*RATES!$C$47*IF($C$5="NONE (RAW)",0,1)</f>
-        <v/>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -8906,7 +8205,6 @@
       </c>
       <c r="D91" s="12">
         <f>D84*RATES!$C$48*IF($C$5="NONE (RAW)",0,1)</f>
-        <v/>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -8922,7 +8220,6 @@
       </c>
       <c r="D92" s="12">
         <f>D84*RATES!$C$49*IF($C$5="NONE (RAW)",0,1)</f>
-        <v/>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -8938,7 +8235,6 @@
       </c>
       <c r="D93" s="12">
         <f>D84*RATES!$C$50*IF($C$5="NONE (RAW)",0,1)</f>
-        <v/>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -8954,7 +8250,6 @@
       </c>
       <c r="D94" s="12">
         <f>SUM(T64:T78)</f>
-        <v/>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -8970,7 +8265,6 @@
       </c>
       <c r="D95" s="12">
         <f>IF(L15=0,0,IF(L15&lt;RATES!$C$95,RATES!$C$53*G15,L15*RATES!$C$51*(1+IF(G15&gt;1,RATES!$C$96,0)))+M15*RATES!$C$52)</f>
-        <v/>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -8986,7 +8280,6 @@
       </c>
       <c r="D96" s="16">
         <f>SUM(D87:D95)</f>
-        <v/>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="59">
@@ -8997,7 +8290,6 @@
       </c>
       <c r="D97" s="12">
         <f>D96*RATES!$C$54</f>
-        <v/>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -9013,7 +8305,6 @@
       </c>
       <c r="D98" s="12">
         <f>(D96+D97)*RATES!$C$55</f>
-        <v/>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -9029,7 +8320,6 @@
       </c>
       <c r="D99" s="16">
         <f>D96+D97+D98</f>
-        <v/>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="59">
@@ -9040,7 +8330,6 @@
       </c>
       <c r="D100" s="19">
         <f>L15</f>
-        <v/>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="59">
@@ -9051,7 +8340,6 @@
       </c>
       <c r="D101" s="16">
         <f>IF(ISNUMBER(C4),C4,0)*D99</f>
-        <v/>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="59">
@@ -9062,7 +8350,6 @@
       </c>
       <c r="D102" s="40">
         <f>COUNTIF(R18:R42,"?*")-COUNTIF(R18:R42,"OK")+COUNTIF(R46:R60,"?*")-COUNTIF(R46:R60,"OK")+COUNTIF(S18:S60,"rate?")</f>
-        <v/>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -10053,7 +9340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1000"/>
+  <dimension ref="A1:J229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10816,7 +10103,6 @@
       </c>
       <c r="C34" s="81">
         <f>$C$10*(1-$C$11)/$C$12</f>
-        <v/>
       </c>
       <c r="D34" s="81" t="n">
         <v>4000000</v>
@@ -10845,11 +10131,9 @@
       </c>
       <c r="C35" s="81">
         <f>($C$6+$C$9)*$C$13+$C$34</f>
-        <v/>
       </c>
       <c r="D35" s="81">
         <f>C35*0.9</f>
-        <v/>
       </c>
       <c r="E35" s="74" t="inlineStr">
         <is>
@@ -10875,11 +10159,9 @@
       </c>
       <c r="C36" s="81">
         <f>($C$6+$C$9)*$C$14+$C$34</f>
-        <v/>
       </c>
       <c r="D36" s="81">
         <f>C36*0.9</f>
-        <v/>
       </c>
       <c r="E36" s="74" t="inlineStr">
         <is>
@@ -10900,11 +10182,9 @@
       </c>
       <c r="C37" s="81">
         <f>($C$6+$C$9)*$C$15+$C$34</f>
-        <v/>
       </c>
       <c r="D37" s="81">
         <f>C37*0.9</f>
-        <v/>
       </c>
       <c r="E37" s="74" t="inlineStr">
         <is>
@@ -10925,11 +10205,9 @@
       </c>
       <c r="C38" s="81">
         <f>($C$6+$C$9)*$C$16+$C$34</f>
-        <v/>
       </c>
       <c r="D38" s="81">
         <f>C38*0.9</f>
-        <v/>
       </c>
       <c r="E38" s="74" t="inlineStr">
         <is>
@@ -10950,11 +10228,9 @@
       </c>
       <c r="C39" s="81">
         <f>($C$6+$C$9)*$C$17+$C$34</f>
-        <v/>
       </c>
       <c r="D39" s="81">
         <f>C39*0.9</f>
-        <v/>
       </c>
       <c r="E39" s="74" t="inlineStr">
         <is>
@@ -10975,11 +10251,9 @@
       </c>
       <c r="C40" s="81">
         <f>($C$7+$C$9)*$C$13+$C$34</f>
-        <v/>
       </c>
       <c r="D40" s="81">
         <f>C40*0.9</f>
-        <v/>
       </c>
       <c r="E40" s="74" t="inlineStr">
         <is>
@@ -11000,11 +10274,9 @@
       </c>
       <c r="C41" s="81">
         <f>($C$7+$C$9)*$C$14+$C$34</f>
-        <v/>
       </c>
       <c r="D41" s="81">
         <f>C41*0.9</f>
-        <v/>
       </c>
       <c r="E41" s="74" t="inlineStr">
         <is>
@@ -11025,11 +10297,9 @@
       </c>
       <c r="C42" s="81">
         <f>($C$7+$C$9)*$C$15+$C$34</f>
-        <v/>
       </c>
       <c r="D42" s="81">
         <f>C42*0.9</f>
-        <v/>
       </c>
       <c r="E42" s="74" t="inlineStr">
         <is>
@@ -11050,11 +10320,9 @@
       </c>
       <c r="C43" s="81">
         <f>($C$7+$C$9)*$C$16+$C$34</f>
-        <v/>
       </c>
       <c r="D43" s="81">
         <f>C43*0.9</f>
-        <v/>
       </c>
       <c r="E43" s="74" t="inlineStr">
         <is>
@@ -11075,11 +10343,9 @@
       </c>
       <c r="C44" s="81">
         <f>($C$7+$C$9)*$C$17+$C$34</f>
-        <v/>
       </c>
       <c r="D44" s="81">
         <f>C44*0.9</f>
-        <v/>
       </c>
       <c r="E44" s="74" t="inlineStr">
         <is>
@@ -11100,11 +10366,9 @@
       </c>
       <c r="C45" s="81">
         <f>$C$8*$C$18+$C$34</f>
-        <v/>
       </c>
       <c r="D45" s="81">
         <f>C45*0.9</f>
-        <v/>
       </c>
       <c r="E45" s="74" t="inlineStr">
         <is>
@@ -11130,7 +10394,6 @@
       </c>
       <c r="C46" s="81">
         <f>$C$19/$C$12</f>
-        <v/>
       </c>
       <c r="D46" s="81" t="n">
         <v>1000000</v>
@@ -11154,7 +10417,6 @@
       </c>
       <c r="C47" s="81">
         <f>$C$20/$C$25</f>
-        <v/>
       </c>
       <c r="D47" s="81" t="n">
         <v>37000</v>
@@ -11178,11 +10440,9 @@
       </c>
       <c r="C48" s="81">
         <f>$C$21/$C$25</f>
-        <v/>
       </c>
       <c r="D48" s="81">
         <f>C48*0.8</f>
-        <v/>
       </c>
       <c r="E48" s="74" t="inlineStr">
         <is>
@@ -11203,7 +10463,6 @@
       </c>
       <c r="C49" s="81">
         <f>$C$23*$C$24/$C$25</f>
-        <v/>
       </c>
       <c r="D49" s="81" t="n">
         <v>20000</v>
@@ -11227,7 +10486,6 @@
       </c>
       <c r="C50" s="81">
         <f>$C$22/$C$25</f>
-        <v/>
       </c>
       <c r="D50" s="81" t="n">
         <v>45000</v>
@@ -11357,7 +10615,6 @@
       </c>
       <c r="C55" s="81">
         <f>$C$26/$C$27</f>
-        <v/>
       </c>
       <c r="E55" s="74" t="inlineStr">
         <is>
@@ -11390,7 +10647,6 @@
       </c>
       <c r="C57" s="81">
         <f>$C$29*$C$31+$C$28*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
-        <v/>
       </c>
       <c r="E57" s="74" t="inlineStr">
         <is>
@@ -11411,7 +10667,6 @@
       </c>
       <c r="C58" s="81">
         <f>$C$30*$C$31+$C$28*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
-        <v/>
       </c>
       <c r="D58" s="81" t="n">
         <v>18000</v>
@@ -11435,7 +10690,6 @@
       </c>
       <c r="C59" s="80">
         <f>H59</f>
-        <v/>
       </c>
       <c r="E59" s="74" t="inlineStr">
         <is>
@@ -11449,11 +10703,9 @@
       </c>
       <c r="G59" s="82">
         <f t="array" ref="G59">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H59" s="83">
         <f>G59*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="60">
@@ -11469,7 +10721,6 @@
       </c>
       <c r="C60" s="81">
         <f>C59+$C$175</f>
-        <v/>
       </c>
       <c r="E60" s="74" t="inlineStr">
         <is>
@@ -11490,7 +10741,6 @@
       </c>
       <c r="C61" s="81">
         <f>C59+2*$C$175</f>
-        <v/>
       </c>
       <c r="E61" s="74" t="inlineStr">
         <is>
@@ -11511,7 +10761,6 @@
       </c>
       <c r="C62" s="81">
         <f>C59+$C$176</f>
-        <v/>
       </c>
       <c r="E62" s="74" t="inlineStr">
         <is>
@@ -11532,7 +10781,6 @@
       </c>
       <c r="C63" s="81">
         <f>C59+2*$C$176</f>
-        <v/>
       </c>
       <c r="E63" s="74" t="inlineStr">
         <is>
@@ -11553,7 +10801,6 @@
       </c>
       <c r="C64" s="80">
         <f>H64</f>
-        <v/>
       </c>
       <c r="E64" s="74" t="inlineStr">
         <is>
@@ -11567,11 +10814,9 @@
       </c>
       <c r="G64" s="82">
         <f t="array" ref="G64">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H64" s="83">
         <f>G64*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="65">
@@ -11587,7 +10832,6 @@
       </c>
       <c r="C65" s="81">
         <f>C64+$C$175</f>
-        <v/>
       </c>
       <c r="E65" s="74" t="inlineStr">
         <is>
@@ -11608,7 +10852,6 @@
       </c>
       <c r="C66" s="81">
         <f>C64+2*$C$175</f>
-        <v/>
       </c>
       <c r="E66" s="74" t="inlineStr">
         <is>
@@ -11629,7 +10872,6 @@
       </c>
       <c r="C67" s="81">
         <f>C64+$C$176</f>
-        <v/>
       </c>
       <c r="E67" s="74" t="inlineStr">
         <is>
@@ -11650,7 +10892,6 @@
       </c>
       <c r="C68" s="81">
         <f>C64+2*$C$176</f>
-        <v/>
       </c>
       <c r="E68" s="74" t="inlineStr">
         <is>
@@ -11671,7 +10912,6 @@
       </c>
       <c r="C69" s="80">
         <f>H69</f>
-        <v/>
       </c>
       <c r="E69" s="74" t="inlineStr">
         <is>
@@ -11685,11 +10925,9 @@
       </c>
       <c r="G69" s="82">
         <f t="array" ref="G69">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H69" s="83">
         <f>G69*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="70">
@@ -11705,7 +10943,6 @@
       </c>
       <c r="C70" s="81">
         <f>C69+$C$175</f>
-        <v/>
       </c>
       <c r="E70" s="74" t="inlineStr">
         <is>
@@ -11726,7 +10963,6 @@
       </c>
       <c r="C71" s="81">
         <f>C69+2*$C$175</f>
-        <v/>
       </c>
       <c r="E71" s="74" t="inlineStr">
         <is>
@@ -11747,7 +10983,6 @@
       </c>
       <c r="C72" s="81">
         <f>C69+$C$176</f>
-        <v/>
       </c>
       <c r="E72" s="74" t="inlineStr">
         <is>
@@ -11768,7 +11003,6 @@
       </c>
       <c r="C73" s="81">
         <f>C69+2*$C$176</f>
-        <v/>
       </c>
       <c r="E73" s="74" t="inlineStr">
         <is>
@@ -11789,7 +11023,6 @@
       </c>
       <c r="C74" s="80">
         <f>H74</f>
-        <v/>
       </c>
       <c r="E74" s="74" t="inlineStr">
         <is>
@@ -11803,11 +11036,9 @@
       </c>
       <c r="G74" s="82">
         <f t="array" ref="G74">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H74" s="83">
         <f>G74*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="75">
@@ -11823,7 +11054,6 @@
       </c>
       <c r="C75" s="81">
         <f>C74+$C$175</f>
-        <v/>
       </c>
       <c r="E75" s="74" t="inlineStr">
         <is>
@@ -11844,7 +11074,6 @@
       </c>
       <c r="C76" s="81">
         <f>C74+2*$C$175</f>
-        <v/>
       </c>
       <c r="E76" s="74" t="inlineStr">
         <is>
@@ -11865,7 +11094,6 @@
       </c>
       <c r="C77" s="81">
         <f>C74+$C$176</f>
-        <v/>
       </c>
       <c r="E77" s="74" t="inlineStr">
         <is>
@@ -11886,7 +11114,6 @@
       </c>
       <c r="C78" s="81">
         <f>C74+2*$C$176</f>
-        <v/>
       </c>
       <c r="E78" s="74" t="inlineStr">
         <is>
@@ -11920,11 +11147,9 @@
       </c>
       <c r="G79" s="82">
         <f t="array" ref="G79">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H79" s="83">
         <f>G79*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="80">
@@ -12020,7 +11245,6 @@
       </c>
       <c r="C84" s="80">
         <f>H84</f>
-        <v/>
       </c>
       <c r="E84" s="74" t="inlineStr">
         <is>
@@ -12034,11 +11258,9 @@
       </c>
       <c r="G84" s="82">
         <f t="array" ref="G84">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H84" s="83">
         <f>G84*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="85">
@@ -12054,7 +11276,6 @@
       </c>
       <c r="C85" s="81">
         <f>C84+$C$175</f>
-        <v/>
       </c>
       <c r="E85" s="74" t="inlineStr">
         <is>
@@ -12075,7 +11296,6 @@
       </c>
       <c r="C86" s="81">
         <f>C84+2*$C$175</f>
-        <v/>
       </c>
       <c r="E86" s="74" t="inlineStr">
         <is>
@@ -12096,7 +11316,6 @@
       </c>
       <c r="C87" s="81">
         <f>C84+$C$176</f>
-        <v/>
       </c>
       <c r="E87" s="74" t="inlineStr">
         <is>
@@ -12117,7 +11336,6 @@
       </c>
       <c r="C88" s="81">
         <f>C84+2*$C$176</f>
-        <v/>
       </c>
       <c r="E88" s="74" t="inlineStr">
         <is>
@@ -13727,11 +12945,10 @@
         </is>
       </c>
     </row>
-    <row r="169"/>
     <row r="170">
       <c r="A170" s="84" t="inlineStr">
         <is>
-          <t>LANDED BOARD PRICES: Linyi Ocean International Trading, quotation 16 Oct 2026, valid to 30 Oct 2026. CIF Semarang plus port, clearance and trucking to the Kudus factory (bonded; duty, PPN and PPh excluded). Value = CIF USD per sheet × FX_USD + LAND_40HC ÷ sheets per 40' HC.</t>
+          <t>LANDED BOARD PRICES: Linyi Consmos Imp.&amp;Exp. Co., Ltd., quotation 14 Oct 2026. CIF Semarang plus port, clearance and trucking to Kudus. Value = CIF USD × FX_USD + LAND_40HC ÷ sheets/box.</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13011,7 @@
         </is>
       </c>
       <c r="C172" s="85" t="n">
-        <v>18000</v>
+        <v>18040</v>
       </c>
       <c r="E172" s="84" t="inlineStr">
         <is>
@@ -13909,7 +13126,6 @@
         </is>
       </c>
     </row>
-    <row r="177"/>
     <row r="178">
       <c r="A178" s="79" t="inlineStr">
         <is>
@@ -13923,7 +13139,6 @@
       </c>
       <c r="C178" s="88">
         <f>H178</f>
-        <v/>
       </c>
       <c r="E178" s="79" t="inlineStr">
         <is>
@@ -13937,17 +13152,15 @@
       </c>
       <c r="G178" s="86">
         <f>I178+$C$173/$C$172/J178</f>
-        <v/>
       </c>
       <c r="H178" s="87">
         <f>G178*$C$172</f>
-        <v/>
       </c>
       <c r="I178" s="86" t="n">
-        <v>5.3</v>
+        <v>5.248</v>
       </c>
       <c r="J178" s="87" t="n">
-        <v>5760</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="179">
@@ -13963,7 +13176,6 @@
       </c>
       <c r="C179" s="88">
         <f>H179</f>
-        <v/>
       </c>
       <c r="E179" s="79" t="inlineStr">
         <is>
@@ -13977,17 +13189,15 @@
       </c>
       <c r="G179" s="86">
         <f>I179+$C$173/$C$172/J179</f>
-        <v/>
       </c>
       <c r="H179" s="87">
         <f>G179*$C$172</f>
-        <v/>
       </c>
       <c r="I179" s="86" t="n">
-        <v>8.199999999999999</v>
+        <v>7.779</v>
       </c>
       <c r="J179" s="87" t="n">
-        <v>2880</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="180">
@@ -14003,7 +13213,6 @@
       </c>
       <c r="C180" s="88">
         <f>H180</f>
-        <v/>
       </c>
       <c r="E180" s="79" t="inlineStr">
         <is>
@@ -14017,17 +13226,15 @@
       </c>
       <c r="G180" s="86">
         <f>I180+$C$173/$C$172/J180</f>
-        <v/>
       </c>
       <c r="H180" s="87">
         <f>G180*$C$172</f>
-        <v/>
       </c>
       <c r="I180" s="86" t="n">
-        <v>12</v>
+        <v>11.017</v>
       </c>
       <c r="J180" s="87" t="n">
-        <v>1890</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="181">
@@ -14043,7 +13250,6 @@
       </c>
       <c r="C181" s="88">
         <f>H181</f>
-        <v/>
       </c>
       <c r="E181" s="79" t="inlineStr">
         <is>
@@ -14057,17 +13263,15 @@
       </c>
       <c r="G181" s="86">
         <f>I181+$C$173/$C$172/J181</f>
-        <v/>
       </c>
       <c r="H181" s="87">
         <f>G181*$C$172</f>
-        <v/>
       </c>
       <c r="I181" s="86" t="n">
-        <v>15.1050125313283</v>
+        <v>14.144</v>
       </c>
       <c r="J181" s="87" t="n">
-        <v>1440</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="182">
@@ -14083,7 +13287,6 @@
       </c>
       <c r="C182" s="88">
         <f>H182</f>
-        <v/>
       </c>
       <c r="E182" s="79" t="inlineStr">
         <is>
@@ -14097,17 +13300,15 @@
       </c>
       <c r="G182" s="86">
         <f>I182+$C$173/$C$172/J182</f>
-        <v/>
       </c>
       <c r="H182" s="87">
         <f>G182*$C$172</f>
-        <v/>
       </c>
       <c r="I182" s="86" t="n">
-        <v>18.4</v>
+        <v>17.655</v>
       </c>
       <c r="J182" s="87" t="n">
-        <v>1170</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="183">
@@ -14123,7 +13324,6 @@
       </c>
       <c r="C183" s="88">
         <f>H183</f>
-        <v/>
       </c>
       <c r="E183" s="79" t="inlineStr">
         <is>
@@ -14137,17 +13337,15 @@
       </c>
       <c r="G183" s="86">
         <f>I183+$C$173/$C$172/J183</f>
-        <v/>
       </c>
       <c r="H183" s="87">
         <f>G183*$C$172</f>
-        <v/>
       </c>
       <c r="I183" s="86" t="n">
-        <v>21.1</v>
+        <v>20.469</v>
       </c>
       <c r="J183" s="87" t="n">
-        <v>990</v>
+        <v>970</v>
       </c>
     </row>
     <row r="184">
@@ -14163,7 +13361,6 @@
       </c>
       <c r="C184" s="89">
         <f>H184</f>
-        <v/>
       </c>
       <c r="E184" s="84" t="inlineStr">
         <is>
@@ -14177,11 +13374,9 @@
       </c>
       <c r="G184" s="82">
         <f>I184+$C$173/$C$172/J184</f>
-        <v/>
       </c>
       <c r="H184" s="83">
         <f>G184*$C$172</f>
-        <v/>
       </c>
       <c r="I184" s="82" t="n">
         <v>5.45</v>
@@ -14203,7 +13398,6 @@
       </c>
       <c r="C185" s="89">
         <f>H185</f>
-        <v/>
       </c>
       <c r="E185" s="84" t="inlineStr">
         <is>
@@ -14217,11 +13411,9 @@
       </c>
       <c r="G185" s="82">
         <f>I185+$C$173/$C$172/J185</f>
-        <v/>
       </c>
       <c r="H185" s="83">
         <f>G185*$C$172</f>
-        <v/>
       </c>
       <c r="I185" s="82" t="n">
         <v>8.449999999999999</v>
@@ -14243,7 +13435,6 @@
       </c>
       <c r="C186" s="89">
         <f>H186</f>
-        <v/>
       </c>
       <c r="E186" s="84" t="inlineStr">
         <is>
@@ -14257,11 +13448,9 @@
       </c>
       <c r="G186" s="82">
         <f>I186+$C$173/$C$172/J186</f>
-        <v/>
       </c>
       <c r="H186" s="83">
         <f>G186*$C$172</f>
-        <v/>
       </c>
       <c r="I186" s="82" t="n">
         <v>12.4</v>
@@ -14283,7 +13472,6 @@
       </c>
       <c r="C187" s="89">
         <f>H187</f>
-        <v/>
       </c>
       <c r="E187" s="84" t="inlineStr">
         <is>
@@ -14297,11 +13485,9 @@
       </c>
       <c r="G187" s="82">
         <f>I187+$C$173/$C$172/J187</f>
-        <v/>
       </c>
       <c r="H187" s="83">
         <f>G187*$C$172</f>
-        <v/>
       </c>
       <c r="I187" s="82" t="n">
         <v>15.4</v>
@@ -14323,7 +13509,6 @@
       </c>
       <c r="C188" s="89">
         <f>H188</f>
-        <v/>
       </c>
       <c r="E188" s="84" t="inlineStr">
         <is>
@@ -14337,11 +13522,9 @@
       </c>
       <c r="G188" s="82">
         <f>I188+$C$173/$C$172/J188</f>
-        <v/>
       </c>
       <c r="H188" s="83">
         <f>G188*$C$172</f>
-        <v/>
       </c>
       <c r="I188" s="82" t="n">
         <v>18.7</v>
@@ -14363,7 +13546,6 @@
       </c>
       <c r="C189" s="89">
         <f>H189</f>
-        <v/>
       </c>
       <c r="E189" s="84" t="inlineStr">
         <is>
@@ -14377,11 +13559,9 @@
       </c>
       <c r="G189" s="82">
         <f>I189+$C$173/$C$172/J189</f>
-        <v/>
       </c>
       <c r="H189" s="83">
         <f>G189*$C$172</f>
-        <v/>
       </c>
       <c r="I189" s="82" t="n">
         <v>21.4</v>
@@ -14403,7 +13583,6 @@
       </c>
       <c r="C190" s="89">
         <f>H190</f>
-        <v/>
       </c>
       <c r="E190" s="84" t="inlineStr">
         <is>
@@ -14417,11 +13596,9 @@
       </c>
       <c r="G190" s="82">
         <f>I190+$C$173/$C$172/J190</f>
-        <v/>
       </c>
       <c r="H190" s="83">
         <f>G190*$C$172</f>
-        <v/>
       </c>
       <c r="I190" s="82" t="n">
         <v>5.5</v>
@@ -14443,7 +13620,6 @@
       </c>
       <c r="C191" s="89">
         <f>H191</f>
-        <v/>
       </c>
       <c r="E191" s="84" t="inlineStr">
         <is>
@@ -14457,11 +13633,9 @@
       </c>
       <c r="G191" s="82">
         <f>I191+$C$173/$C$172/J191</f>
-        <v/>
       </c>
       <c r="H191" s="83">
         <f>G191*$C$172</f>
-        <v/>
       </c>
       <c r="I191" s="82" t="n">
         <v>8.5</v>
@@ -14483,7 +13657,6 @@
       </c>
       <c r="C192" s="89">
         <f>H192</f>
-        <v/>
       </c>
       <c r="E192" s="84" t="inlineStr">
         <is>
@@ -14497,11 +13670,9 @@
       </c>
       <c r="G192" s="82">
         <f>I192+$C$173/$C$172/J192</f>
-        <v/>
       </c>
       <c r="H192" s="83">
         <f>G192*$C$172</f>
-        <v/>
       </c>
       <c r="I192" s="82" t="n">
         <v>12.4</v>
@@ -14523,7 +13694,6 @@
       </c>
       <c r="C193" s="89">
         <f>H193</f>
-        <v/>
       </c>
       <c r="E193" s="84" t="inlineStr">
         <is>
@@ -14537,11 +13707,9 @@
       </c>
       <c r="G193" s="82">
         <f>I193+$C$173/$C$172/J193</f>
-        <v/>
       </c>
       <c r="H193" s="83">
         <f>G193*$C$172</f>
-        <v/>
       </c>
       <c r="I193" s="82" t="n">
         <v>15.5</v>
@@ -14563,7 +13731,6 @@
       </c>
       <c r="C194" s="89">
         <f>H194</f>
-        <v/>
       </c>
       <c r="E194" s="84" t="inlineStr">
         <is>
@@ -14577,11 +13744,9 @@
       </c>
       <c r="G194" s="82">
         <f>I194+$C$173/$C$172/J194</f>
-        <v/>
       </c>
       <c r="H194" s="83">
         <f>G194*$C$172</f>
-        <v/>
       </c>
       <c r="I194" s="82" t="n">
         <v>18.8</v>
@@ -14603,7 +13768,6 @@
       </c>
       <c r="C195" s="89">
         <f>H195</f>
-        <v/>
       </c>
       <c r="E195" s="84" t="inlineStr">
         <is>
@@ -14617,11 +13781,9 @@
       </c>
       <c r="G195" s="82">
         <f>I195+$C$173/$C$172/J195</f>
-        <v/>
       </c>
       <c r="H195" s="83">
         <f>G195*$C$172</f>
-        <v/>
       </c>
       <c r="I195" s="82" t="n">
         <v>21.5</v>
@@ -14643,7 +13805,6 @@
       </c>
       <c r="C196" s="88">
         <f>H196</f>
-        <v/>
       </c>
       <c r="E196" s="79" t="inlineStr">
         <is>
@@ -14657,17 +13818,15 @@
       </c>
       <c r="G196" s="86">
         <f>I196+$C$173/$C$172/J196</f>
-        <v/>
       </c>
       <c r="H196" s="87">
         <f>G196*$C$172</f>
-        <v/>
       </c>
       <c r="I196" s="86" t="n">
-        <v>2.5</v>
+        <v>2.715</v>
       </c>
       <c r="J196" s="87" t="n">
-        <v>4060</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="197">
@@ -14683,7 +13842,6 @@
       </c>
       <c r="C197" s="88">
         <f>H197</f>
-        <v/>
       </c>
       <c r="E197" s="79" t="inlineStr">
         <is>
@@ -14697,17 +13855,15 @@
       </c>
       <c r="G197" s="86">
         <f>I197+$C$173/$C$172/J197</f>
-        <v/>
       </c>
       <c r="H197" s="87">
         <f>G197*$C$172</f>
-        <v/>
       </c>
       <c r="I197" s="86" t="n">
-        <v>4.4</v>
+        <v>4.873</v>
       </c>
       <c r="J197" s="87" t="n">
-        <v>2175</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="198">
@@ -14723,7 +13879,6 @@
       </c>
       <c r="C198" s="88">
         <f>H198</f>
-        <v/>
       </c>
       <c r="E198" s="79" t="inlineStr">
         <is>
@@ -14737,17 +13892,15 @@
       </c>
       <c r="G198" s="86">
         <f>I198+$C$173/$C$172/J198</f>
-        <v/>
       </c>
       <c r="H198" s="87">
         <f>G198*$C$172</f>
-        <v/>
       </c>
       <c r="I198" s="86" t="n">
-        <v>6.8</v>
+        <v>7.553</v>
       </c>
       <c r="J198" s="87" t="n">
-        <v>1425</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="199">
@@ -14763,7 +13916,6 @@
       </c>
       <c r="C199" s="88">
         <f>H199</f>
-        <v/>
       </c>
       <c r="E199" s="79" t="inlineStr">
         <is>
@@ -14777,17 +13929,15 @@
       </c>
       <c r="G199" s="86">
         <f>I199+$C$173/$C$172/J199</f>
-        <v/>
       </c>
       <c r="H199" s="87">
         <f>G199*$C$172</f>
-        <v/>
       </c>
       <c r="I199" s="86" t="n">
-        <v>7.8</v>
+        <v>9.882999999999999</v>
       </c>
       <c r="J199" s="87" t="n">
-        <v>1200</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="200">
@@ -14803,7 +13953,6 @@
       </c>
       <c r="C200" s="88">
         <f>H200</f>
-        <v/>
       </c>
       <c r="E200" s="79" t="inlineStr">
         <is>
@@ -14817,17 +13966,15 @@
       </c>
       <c r="G200" s="86">
         <f>I200+$C$173/$C$172/J200</f>
-        <v/>
       </c>
       <c r="H200" s="87">
         <f>G200*$C$172</f>
-        <v/>
       </c>
       <c r="I200" s="86" t="n">
-        <v>10</v>
+        <v>12.435</v>
       </c>
       <c r="J200" s="87" t="n">
-        <v>960</v>
+        <v>896</v>
       </c>
     </row>
     <row r="201">
@@ -14843,7 +13990,6 @@
       </c>
       <c r="C201" s="88">
         <f>H201</f>
-        <v/>
       </c>
       <c r="E201" s="79" t="inlineStr">
         <is>
@@ -14857,17 +14003,15 @@
       </c>
       <c r="G201" s="86">
         <f>I201+$C$173/$C$172/J201</f>
-        <v/>
       </c>
       <c r="H201" s="87">
         <f>G201*$C$172</f>
-        <v/>
       </c>
       <c r="I201" s="86" t="n">
-        <v>12.3</v>
+        <v>15.039</v>
       </c>
       <c r="J201" s="87" t="n">
-        <v>800</v>
+        <v>746</v>
       </c>
     </row>
     <row r="202">
@@ -14883,7 +14027,6 @@
       </c>
       <c r="C202" s="89">
         <f>H202</f>
-        <v/>
       </c>
       <c r="E202" s="84" t="inlineStr">
         <is>
@@ -14897,11 +14040,9 @@
       </c>
       <c r="G202" s="82">
         <f>I202+$C$173/$C$172/J202</f>
-        <v/>
       </c>
       <c r="H202" s="83">
         <f>G202*$C$172</f>
-        <v/>
       </c>
       <c r="I202" s="82" t="n">
         <v>2.8</v>
@@ -14923,7 +14064,6 @@
       </c>
       <c r="C203" s="89">
         <f>H203</f>
-        <v/>
       </c>
       <c r="E203" s="84" t="inlineStr">
         <is>
@@ -14937,11 +14077,9 @@
       </c>
       <c r="G203" s="82">
         <f>I203+$C$173/$C$172/J203</f>
-        <v/>
       </c>
       <c r="H203" s="83">
         <f>G203*$C$172</f>
-        <v/>
       </c>
       <c r="I203" s="82" t="n">
         <v>5.2</v>
@@ -14963,7 +14101,6 @@
       </c>
       <c r="C204" s="89">
         <f>H204</f>
-        <v/>
       </c>
       <c r="E204" s="84" t="inlineStr">
         <is>
@@ -14977,11 +14114,9 @@
       </c>
       <c r="G204" s="82">
         <f>I204+$C$173/$C$172/J204</f>
-        <v/>
       </c>
       <c r="H204" s="83">
         <f>G204*$C$172</f>
-        <v/>
       </c>
       <c r="I204" s="82" t="n">
         <v>8.15</v>
@@ -15003,7 +14138,6 @@
       </c>
       <c r="C205" s="89">
         <f>H205</f>
-        <v/>
       </c>
       <c r="E205" s="84" t="inlineStr">
         <is>
@@ -15017,11 +14151,9 @@
       </c>
       <c r="G205" s="82">
         <f>I205+$C$173/$C$172/J205</f>
-        <v/>
       </c>
       <c r="H205" s="83">
         <f>G205*$C$172</f>
-        <v/>
       </c>
       <c r="I205" s="82" t="n">
         <v>10.7</v>
@@ -15043,7 +14175,6 @@
       </c>
       <c r="C206" s="89">
         <f>H206</f>
-        <v/>
       </c>
       <c r="E206" s="84" t="inlineStr">
         <is>
@@ -15057,11 +14188,9 @@
       </c>
       <c r="G206" s="82">
         <f>I206+$C$173/$C$172/J206</f>
-        <v/>
       </c>
       <c r="H206" s="83">
         <f>G206*$C$172</f>
-        <v/>
       </c>
       <c r="I206" s="82" t="n">
         <v>13.4</v>
@@ -15083,7 +14212,6 @@
       </c>
       <c r="C207" s="89">
         <f>H207</f>
-        <v/>
       </c>
       <c r="E207" s="84" t="inlineStr">
         <is>
@@ -15097,11 +14225,9 @@
       </c>
       <c r="G207" s="82">
         <f>I207+$C$173/$C$172/J207</f>
-        <v/>
       </c>
       <c r="H207" s="83">
         <f>G207*$C$172</f>
-        <v/>
       </c>
       <c r="I207" s="82" t="n">
         <v>16</v>
@@ -15123,7 +14249,6 @@
       </c>
       <c r="C208" s="89">
         <f>H208</f>
-        <v/>
       </c>
       <c r="E208" s="84" t="inlineStr">
         <is>
@@ -15137,11 +14262,9 @@
       </c>
       <c r="G208" s="82">
         <f>I208+$C$173/$C$172/J208</f>
-        <v/>
       </c>
       <c r="H208" s="83">
         <f>G208*$C$172</f>
-        <v/>
       </c>
       <c r="I208" s="82" t="n">
         <v>2.8</v>
@@ -15163,7 +14286,6 @@
       </c>
       <c r="C209" s="89">
         <f>H209</f>
-        <v/>
       </c>
       <c r="E209" s="84" t="inlineStr">
         <is>
@@ -15177,11 +14299,9 @@
       </c>
       <c r="G209" s="82">
         <f>I209+$C$173/$C$172/J209</f>
-        <v/>
       </c>
       <c r="H209" s="83">
         <f>G209*$C$172</f>
-        <v/>
       </c>
       <c r="I209" s="82" t="n">
         <v>5.35</v>
@@ -15203,7 +14323,6 @@
       </c>
       <c r="C210" s="89">
         <f>H210</f>
-        <v/>
       </c>
       <c r="E210" s="84" t="inlineStr">
         <is>
@@ -15217,11 +14336,9 @@
       </c>
       <c r="G210" s="82">
         <f>I210+$C$173/$C$172/J210</f>
-        <v/>
       </c>
       <c r="H210" s="83">
         <f>G210*$C$172</f>
-        <v/>
       </c>
       <c r="I210" s="82" t="n">
         <v>7.5</v>
@@ -15243,7 +14360,6 @@
       </c>
       <c r="C211" s="89">
         <f>H211</f>
-        <v/>
       </c>
       <c r="E211" s="84" t="inlineStr">
         <is>
@@ -15257,11 +14373,9 @@
       </c>
       <c r="G211" s="82">
         <f>I211+$C$173/$C$172/J211</f>
-        <v/>
       </c>
       <c r="H211" s="83">
         <f>G211*$C$172</f>
-        <v/>
       </c>
       <c r="I211" s="82" t="n">
         <v>8.699999999999999</v>
@@ -15283,7 +14397,6 @@
       </c>
       <c r="C212" s="89">
         <f>H212</f>
-        <v/>
       </c>
       <c r="E212" s="84" t="inlineStr">
         <is>
@@ -15297,11 +14410,9 @@
       </c>
       <c r="G212" s="82">
         <f>I212+$C$173/$C$172/J212</f>
-        <v/>
       </c>
       <c r="H212" s="83">
         <f>G212*$C$172</f>
-        <v/>
       </c>
       <c r="I212" s="82" t="n">
         <v>11.05</v>
@@ -15323,7 +14434,6 @@
       </c>
       <c r="C213" s="89">
         <f>H213</f>
-        <v/>
       </c>
       <c r="E213" s="84" t="inlineStr">
         <is>
@@ -15337,11 +14447,9 @@
       </c>
       <c r="G213" s="82">
         <f>I213+$C$173/$C$172/J213</f>
-        <v/>
       </c>
       <c r="H213" s="83">
         <f>G213*$C$172</f>
-        <v/>
       </c>
       <c r="I213" s="82" t="n">
         <v>13.2</v>
@@ -15363,7 +14471,6 @@
       </c>
       <c r="C214" s="89">
         <f>H214</f>
-        <v/>
       </c>
       <c r="E214" s="84" t="inlineStr">
         <is>
@@ -15377,17 +14484,15 @@
       </c>
       <c r="G214" s="82">
         <f>I214+$C$173/$C$172/J214</f>
-        <v/>
       </c>
       <c r="H214" s="83">
         <f>G214*$C$172</f>
-        <v/>
       </c>
       <c r="I214" s="82" t="n">
-        <v>30.6</v>
+        <v>20.324</v>
       </c>
       <c r="J214" s="83" t="n">
-        <v>1040</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="215">
@@ -15403,7 +14508,6 @@
       </c>
       <c r="C215" s="89">
         <f>H215</f>
-        <v/>
       </c>
       <c r="E215" s="84" t="inlineStr">
         <is>
@@ -15417,20 +14521,17 @@
       </c>
       <c r="G215" s="82">
         <f>I215+$C$173/$C$172/J215</f>
-        <v/>
       </c>
       <c r="H215" s="83">
         <f>G215*$C$172</f>
-        <v/>
       </c>
       <c r="I215" s="82" t="n">
-        <v>35.5</v>
+        <v>24.043</v>
       </c>
       <c r="J215" s="83" t="n">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="216"/>
+        <v>933</v>
+      </c>
+    </row>
     <row r="217">
       <c r="A217" s="84" t="inlineStr">
         <is>
@@ -15451,7 +14552,6 @@
       </c>
       <c r="C218" s="89">
         <f t="array" ref="C218">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="E218" s="84" t="inlineStr">
         <is>
@@ -15465,11 +14565,9 @@
       </c>
       <c r="G218" s="82">
         <f t="array" ref="G218">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H218" s="83">
         <f>G218*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="219">
@@ -15485,7 +14583,6 @@
       </c>
       <c r="C219" s="89">
         <f t="array" ref="C219">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="E219" s="84" t="inlineStr">
         <is>
@@ -15499,11 +14596,9 @@
       </c>
       <c r="G219" s="82">
         <f t="array" ref="G219">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H219" s="83">
         <f>G219*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="220">
@@ -15519,7 +14614,6 @@
       </c>
       <c r="C220" s="89">
         <f t="array" ref="C220">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="E220" s="84" t="inlineStr">
         <is>
@@ -15533,11 +14627,9 @@
       </c>
       <c r="G220" s="82">
         <f t="array" ref="G220">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H220" s="83">
         <f>G220*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="221">
@@ -15553,7 +14645,6 @@
       </c>
       <c r="C221" s="89">
         <f t="array" ref="C221">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="E221" s="84" t="inlineStr">
         <is>
@@ -15567,11 +14658,9 @@
       </c>
       <c r="G221" s="82">
         <f t="array" ref="G221">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H221" s="83">
         <f>G221*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="222">
@@ -15587,7 +14676,6 @@
       </c>
       <c r="C222" s="89">
         <f t="array" ref="C222">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="E222" s="84" t="inlineStr">
         <is>
@@ -15601,11 +14689,9 @@
       </c>
       <c r="G222" s="82">
         <f t="array" ref="G222">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H222" s="83">
         <f>G222*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="223">
@@ -15621,7 +14707,6 @@
       </c>
       <c r="C223" s="89">
         <f t="array" ref="C223">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="E223" s="84" t="inlineStr">
         <is>
@@ -15635,11 +14720,9 @@
       </c>
       <c r="G223" s="82">
         <f t="array" ref="G223">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H223" s="83">
         <f>G223*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="224">
@@ -15655,7 +14738,6 @@
       </c>
       <c r="C224" s="89">
         <f t="array" ref="C224">INDEX($C$178:$C$215,MATCH("LND-MAR-15",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="E224" s="84" t="inlineStr">
         <is>
@@ -15669,11 +14751,9 @@
       </c>
       <c r="G224" s="82">
         <f t="array" ref="G224">INDEX($G$178:$G$215,MATCH("LND-MAR-15",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H224" s="83">
         <f>G224*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="225">
@@ -15689,7 +14769,6 @@
       </c>
       <c r="C225" s="89">
         <f t="array" ref="C225">INDEX($C$178:$C$215,MATCH("LND-MAR-18",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="E225" s="84" t="inlineStr">
         <is>
@@ -15703,14 +14782,11 @@
       </c>
       <c r="G225" s="82">
         <f t="array" ref="G225">INDEX($G$178:$G$215,MATCH("LND-MAR-18",$A$178:$A$215,0))</f>
-        <v/>
       </c>
       <c r="H225" s="83">
         <f>G225*$C$172</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226"/>
+      </c>
+    </row>
     <row r="227">
       <c r="A227" s="84" t="inlineStr">
         <is>
@@ -15741,7 +14817,6 @@
       </c>
       <c r="C228" s="89">
         <f>H228</f>
-        <v/>
       </c>
       <c r="E228" s="84" t="inlineStr">
         <is>
@@ -15758,7 +14833,6 @@
       </c>
       <c r="H228" s="83">
         <f>G228*$C$172</f>
-        <v/>
       </c>
     </row>
     <row r="229">
@@ -15774,7 +14848,6 @@
       </c>
       <c r="C229" s="89">
         <f>H229</f>
-        <v/>
       </c>
       <c r="E229" s="84" t="inlineStr">
         <is>
@@ -15791,780 +14864,8 @@
       </c>
       <c r="H229" s="83">
         <f>G229*$C$172</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18010,7 +16311,6 @@
       </c>
       <c r="G1" s="9">
         <f t="array" ref="G1">IFERROR(IF(INDEX(ITEMS!$E$5:$E$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$E$5:$E$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H1" s="67" t="n"/>
       <c r="I1" s="67" t="n"/>
@@ -18018,7 +16318,6 @@
       <c r="K1" s="68" t="n"/>
       <c r="L1" s="69">
         <f>IF(G6="","photo",_xludf.IMAGE(G6))</f>
-        <v/>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="59">
@@ -18029,7 +16328,6 @@
       </c>
       <c r="C2" s="9">
         <f t="array" ref="C2">IFERROR(IF(INDEX(ITEMS!$D$5:$D$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$D$5:$D$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="D2" s="66" t="inlineStr">
         <is>
@@ -18038,7 +16336,6 @@
       </c>
       <c r="G2" s="9">
         <f t="array" ref="G2">IFERROR(IF(INDEX(ITEMS!$F$5:$F$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$F$5:$F$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H2" s="67" t="n"/>
       <c r="I2" s="67" t="n"/>
@@ -18053,7 +16350,6 @@
       </c>
       <c r="C3" s="9">
         <f t="array" ref="C3">IFERROR(INDEX(ITEMS!$B$5:$B$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))&amp;" / "&amp;INDEX(ITEMS!$W$5:$W$120,MATCH($C$1,ITEMS!$C$5:$C$120,0)),"")</f>
-        <v/>
       </c>
       <c r="D3" s="66" t="inlineStr">
         <is>
@@ -18062,7 +16358,6 @@
       </c>
       <c r="G3" s="9">
         <f t="array" ref="G3">IFERROR(IF(INDEX(ITEMS!$G$5:$G$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$G$5:$G$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H3" s="67" t="n"/>
       <c r="I3" s="67" t="n"/>
@@ -18077,7 +16372,6 @@
       </c>
       <c r="C4" s="9">
         <f t="array" ref="C4">IFERROR(IF(INDEX(ITEMS!$H$5:$H$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$H$5:$H$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="D4" s="66" t="inlineStr">
         <is>
@@ -18086,7 +16380,6 @@
       </c>
       <c r="G4" s="9">
         <f t="array" ref="G4">IFERROR(IF(INDEX(ITEMS!$I$5:$I$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$I$5:$I$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H4" s="67" t="n"/>
       <c r="I4" s="67" t="n"/>
@@ -18111,7 +16404,6 @@
       </c>
       <c r="G5" s="9">
         <f t="array" ref="G5">IFERROR(IF(INDEX(ITEMS!$V$5:$V$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$V$5:$V$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="H5" s="67" t="n"/>
       <c r="I5" s="67" t="n"/>
@@ -18148,7 +16440,6 @@
       </c>
       <c r="C7" s="9">
         <f t="array" ref="C7">IFERROR(IF(INDEX(ITEMS!$X$5:$X$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$X$5:$X$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
-        <v/>
       </c>
       <c r="D7" s="66" t="inlineStr">
         <is>
@@ -18240,24 +16531,19 @@
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="14">
         <f>IF(D11="","",D11+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="I11" s="14">
         <f>IF(E11="","",E11+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="J11" s="14">
         <f>IF(F11="","",F11+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="17">
         <f>IF(H11="","",2*(H11*I11+H11*J11+I11*J11)/1000000*IF(G11="",1,G11))</f>
-        <v/>
       </c>
       <c r="M11" s="19">
         <f>IF(H11="","",H11*I11*J11/1000000000*IF(G11="",1,G11))</f>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -18272,24 +16558,19 @@
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="14">
         <f>IF(D12="","",D12+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="I12" s="14">
         <f>IF(E12="","",E12+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="J12" s="14">
         <f>IF(F12="","",F12+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="17">
         <f>IF(H12="","",2*(H12*I12+H12*J12+I12*J12)/1000000*IF(G12="",1,G12))</f>
-        <v/>
       </c>
       <c r="M12" s="19">
         <f>IF(H12="","",H12*I12*J12/1000000000*IF(G12="",1,G12))</f>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -18304,24 +16585,19 @@
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="14">
         <f>IF(D13="","",D13+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="I13" s="14">
         <f>IF(E13="","",E13+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="J13" s="14">
         <f>IF(F13="","",F13+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="17">
         <f>IF(H13="","",2*(H13*I13+H13*J13+I13*J13)/1000000*IF(G13="",1,G13))</f>
-        <v/>
       </c>
       <c r="M13" s="19">
         <f>IF(H13="","",H13*I13*J13/1000000000*IF(G13="",1,G13))</f>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -18336,24 +16612,19 @@
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="14">
         <f>IF(D14="","",D14+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="I14" s="14">
         <f>IF(E14="","",E14+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="J14" s="14">
         <f>IF(F14="","",F14+LISTS!$F$9)</f>
-        <v/>
       </c>
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="17">
         <f>IF(H14="","",2*(H14*I14+H14*J14+I14*J14)/1000000*IF(G14="",1,G14))</f>
-        <v/>
       </c>
       <c r="M14" s="19">
         <f>IF(H14="","",H14*I14*J14/1000000000*IF(G14="",1,G14))</f>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -18369,7 +16640,6 @@
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="22">
         <f>IF(D11="",1,SUM(G11:G14)+COUNTIFS(D11:D14,"&lt;&gt;",G11:G14,""))</f>
-        <v/>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -18381,11 +16651,9 @@
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="23">
         <f>IF(D11="",IF(OR(G1="",G2="",G3=""),0,2*((G1+LISTS!$F$9)*(G2+LISTS!$F$9)+(G1+LISTS!$F$9)*(G3+LISTS!$F$9)+(G2+LISTS!$F$9)*(G3+LISTS!$F$9))/1000000),SUM(L11:L14))</f>
-        <v/>
       </c>
       <c r="M15" s="24">
         <f>IF(D11="",IF(OR(G1="",G2="",G3=""),0,(G1+LISTS!$F$9)*(G2+LISTS!$F$9)*(G3+LISTS!$F$9)/1000000000),SUM(M11:M14))</f>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -18538,29 +16806,23 @@
       </c>
       <c r="M18" s="25">
         <f>IF(OR(E18="",F18="",G18=""),"",E18*F18*G18/1000000000*IF(H18="",1,H18))</f>
-        <v/>
       </c>
       <c r="N18" s="19">
         <f>IF(OR(E18="",F18=""),"",E18*F18/1000000*IF(H18="",1,H18))</f>
-        <v/>
       </c>
       <c r="O18" s="14">
         <f>IF(E18="","",IF(K18&lt;&gt;"",K18,IF(AND(E18*F18*G18/1000000000&lt;LISTS!$F$4,MAX(E18,F18,G18)&lt;LISTS!$F$5),"D",IF(I18="N","C",IF(J18="Y","A-CURVED",IF(AND(MEDIAN(E18,F18,G18)&lt;=LISTS!$F$10,MAX(E18,F18,G18)&lt;=LISTS!$F$11),"B",IF(MAX(E18,F18,G18)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P18" s="14" t="n"/>
       <c r="Q18" s="14" t="n"/>
       <c r="R18" s="14">
         <f>IF(E18="","",IF(B18="","material?",IF(OR(F18="",G18=""),"size?",IF(I18="","exposed Y/N?",IF(H18="","qty?",IF(B18="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S18" s="12">
         <f t="array" ref="S18">IF(OR(O18="",M18=""),"",IF(B18="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B18&amp;"_"&amp;SUBSTITUTE(O18,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T18" s="12">
         <f>IF(ISNUMBER(S18),M18*S18,"")</f>
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -18612,29 +16874,23 @@
       </c>
       <c r="M19" s="25">
         <f>IF(OR(E19="",F19="",G19=""),"",E19*F19*G19/1000000000*IF(H19="",1,H19))</f>
-        <v/>
       </c>
       <c r="N19" s="19">
         <f>IF(OR(E19="",F19=""),"",E19*F19/1000000*IF(H19="",1,H19))</f>
-        <v/>
       </c>
       <c r="O19" s="14">
         <f>IF(E19="","",IF(K19&lt;&gt;"",K19,IF(AND(E19*F19*G19/1000000000&lt;LISTS!$F$4,MAX(E19,F19,G19)&lt;LISTS!$F$5),"D",IF(I19="N","C",IF(J19="Y","A-CURVED",IF(AND(MEDIAN(E19,F19,G19)&lt;=LISTS!$F$10,MAX(E19,F19,G19)&lt;=LISTS!$F$11),"B",IF(MAX(E19,F19,G19)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P19" s="14" t="n"/>
       <c r="Q19" s="14" t="n"/>
       <c r="R19" s="14">
         <f>IF(E19="","",IF(B19="","material?",IF(OR(F19="",G19=""),"size?",IF(I19="","exposed Y/N?",IF(H19="","qty?",IF(B19="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S19" s="12">
         <f t="array" ref="S19">IF(OR(O19="",M19=""),"",IF(B19="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B19&amp;"_"&amp;SUBSTITUTE(O19,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T19" s="12">
         <f>IF(ISNUMBER(S19),M19*S19,"")</f>
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -18686,29 +16942,23 @@
       </c>
       <c r="M20" s="25">
         <f>IF(OR(E20="",F20="",G20=""),"",E20*F20*G20/1000000000*IF(H20="",1,H20))</f>
-        <v/>
       </c>
       <c r="N20" s="19">
         <f>IF(OR(E20="",F20=""),"",E20*F20/1000000*IF(H20="",1,H20))</f>
-        <v/>
       </c>
       <c r="O20" s="14">
         <f>IF(E20="","",IF(K20&lt;&gt;"",K20,IF(AND(E20*F20*G20/1000000000&lt;LISTS!$F$4,MAX(E20,F20,G20)&lt;LISTS!$F$5),"D",IF(I20="N","C",IF(J20="Y","A-CURVED",IF(AND(MEDIAN(E20,F20,G20)&lt;=LISTS!$F$10,MAX(E20,F20,G20)&lt;=LISTS!$F$11),"B",IF(MAX(E20,F20,G20)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P20" s="14" t="n"/>
       <c r="Q20" s="14" t="n"/>
       <c r="R20" s="14">
         <f>IF(E20="","",IF(B20="","material?",IF(OR(F20="",G20=""),"size?",IF(I20="","exposed Y/N?",IF(H20="","qty?",IF(B20="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S20" s="12">
         <f t="array" ref="S20">IF(OR(O20="",M20=""),"",IF(B20="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B20&amp;"_"&amp;SUBSTITUTE(O20,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T20" s="12">
         <f>IF(ISNUMBER(S20),M20*S20,"")</f>
-        <v/>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="59">
@@ -18760,29 +17010,23 @@
       </c>
       <c r="M21" s="25">
         <f>IF(OR(E21="",F21="",G21=""),"",E21*F21*G21/1000000000*IF(H21="",1,H21))</f>
-        <v/>
       </c>
       <c r="N21" s="19">
         <f>IF(OR(E21="",F21=""),"",E21*F21/1000000*IF(H21="",1,H21))</f>
-        <v/>
       </c>
       <c r="O21" s="14">
         <f>IF(E21="","",IF(K21&lt;&gt;"",K21,IF(AND(E21*F21*G21/1000000000&lt;LISTS!$F$4,MAX(E21,F21,G21)&lt;LISTS!$F$5),"D",IF(I21="N","C",IF(J21="Y","A-CURVED",IF(AND(MEDIAN(E21,F21,G21)&lt;=LISTS!$F$10,MAX(E21,F21,G21)&lt;=LISTS!$F$11),"B",IF(MAX(E21,F21,G21)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P21" s="14" t="n"/>
       <c r="Q21" s="14" t="n"/>
       <c r="R21" s="14">
         <f>IF(E21="","",IF(B21="","material?",IF(OR(F21="",G21=""),"size?",IF(I21="","exposed Y/N?",IF(H21="","qty?",IF(B21="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S21" s="12">
         <f t="array" ref="S21">IF(OR(O21="",M21=""),"",IF(B21="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B21&amp;"_"&amp;SUBSTITUTE(O21,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T21" s="12">
         <f>IF(ISNUMBER(S21),M21*S21,"")</f>
-        <v/>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="59">
@@ -18834,29 +17078,23 @@
       </c>
       <c r="M22" s="25">
         <f>IF(OR(E22="",F22="",G22=""),"",E22*F22*G22/1000000000*IF(H22="",1,H22))</f>
-        <v/>
       </c>
       <c r="N22" s="19">
         <f>IF(OR(E22="",F22=""),"",E22*F22/1000000*IF(H22="",1,H22))</f>
-        <v/>
       </c>
       <c r="O22" s="14">
         <f>IF(E22="","",IF(K22&lt;&gt;"",K22,IF(AND(E22*F22*G22/1000000000&lt;LISTS!$F$4,MAX(E22,F22,G22)&lt;LISTS!$F$5),"D",IF(I22="N","C",IF(J22="Y","A-CURVED",IF(AND(MEDIAN(E22,F22,G22)&lt;=LISTS!$F$10,MAX(E22,F22,G22)&lt;=LISTS!$F$11),"B",IF(MAX(E22,F22,G22)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P22" s="14" t="n"/>
       <c r="Q22" s="14" t="n"/>
       <c r="R22" s="14">
         <f>IF(E22="","",IF(B22="","material?",IF(OR(F22="",G22=""),"size?",IF(I22="","exposed Y/N?",IF(H22="","qty?",IF(B22="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S22" s="12">
         <f t="array" ref="S22">IF(OR(O22="",M22=""),"",IF(B22="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B22&amp;"_"&amp;SUBSTITUTE(O22,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T22" s="12">
         <f>IF(ISNUMBER(S22),M22*S22,"")</f>
-        <v/>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="59">
@@ -18908,29 +17146,23 @@
       </c>
       <c r="M23" s="25">
         <f>IF(OR(E23="",F23="",G23=""),"",E23*F23*G23/1000000000*IF(H23="",1,H23))</f>
-        <v/>
       </c>
       <c r="N23" s="19">
         <f>IF(OR(E23="",F23=""),"",E23*F23/1000000*IF(H23="",1,H23))</f>
-        <v/>
       </c>
       <c r="O23" s="14">
         <f>IF(E23="","",IF(K23&lt;&gt;"",K23,IF(AND(E23*F23*G23/1000000000&lt;LISTS!$F$4,MAX(E23,F23,G23)&lt;LISTS!$F$5),"D",IF(I23="N","C",IF(J23="Y","A-CURVED",IF(AND(MEDIAN(E23,F23,G23)&lt;=LISTS!$F$10,MAX(E23,F23,G23)&lt;=LISTS!$F$11),"B",IF(MAX(E23,F23,G23)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P23" s="14" t="n"/>
       <c r="Q23" s="14" t="n"/>
       <c r="R23" s="14">
         <f>IF(E23="","",IF(B23="","material?",IF(OR(F23="",G23=""),"size?",IF(I23="","exposed Y/N?",IF(H23="","qty?",IF(B23="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S23" s="12">
         <f t="array" ref="S23">IF(OR(O23="",M23=""),"",IF(B23="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B23&amp;"_"&amp;SUBSTITUTE(O23,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T23" s="12">
         <f>IF(ISNUMBER(S23),M23*S23,"")</f>
-        <v/>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="59">
@@ -18982,29 +17214,23 @@
       </c>
       <c r="M24" s="25">
         <f>IF(OR(E24="",F24="",G24=""),"",E24*F24*G24/1000000000*IF(H24="",1,H24))</f>
-        <v/>
       </c>
       <c r="N24" s="19">
         <f>IF(OR(E24="",F24=""),"",E24*F24/1000000*IF(H24="",1,H24))</f>
-        <v/>
       </c>
       <c r="O24" s="14">
         <f>IF(E24="","",IF(K24&lt;&gt;"",K24,IF(AND(E24*F24*G24/1000000000&lt;LISTS!$F$4,MAX(E24,F24,G24)&lt;LISTS!$F$5),"D",IF(I24="N","C",IF(J24="Y","A-CURVED",IF(AND(MEDIAN(E24,F24,G24)&lt;=LISTS!$F$10,MAX(E24,F24,G24)&lt;=LISTS!$F$11),"B",IF(MAX(E24,F24,G24)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P24" s="14" t="n"/>
       <c r="Q24" s="14" t="n"/>
       <c r="R24" s="14">
         <f>IF(E24="","",IF(B24="","material?",IF(OR(F24="",G24=""),"size?",IF(I24="","exposed Y/N?",IF(H24="","qty?",IF(B24="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S24" s="12">
         <f t="array" ref="S24">IF(OR(O24="",M24=""),"",IF(B24="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B24&amp;"_"&amp;SUBSTITUTE(O24,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T24" s="12">
         <f>IF(ISNUMBER(S24),M24*S24,"")</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="59">
@@ -19056,29 +17282,23 @@
       </c>
       <c r="M25" s="25">
         <f>IF(OR(E25="",F25="",G25=""),"",E25*F25*G25/1000000000*IF(H25="",1,H25))</f>
-        <v/>
       </c>
       <c r="N25" s="19">
         <f>IF(OR(E25="",F25=""),"",E25*F25/1000000*IF(H25="",1,H25))</f>
-        <v/>
       </c>
       <c r="O25" s="14">
         <f>IF(E25="","",IF(K25&lt;&gt;"",K25,IF(AND(E25*F25*G25/1000000000&lt;LISTS!$F$4,MAX(E25,F25,G25)&lt;LISTS!$F$5),"D",IF(I25="N","C",IF(J25="Y","A-CURVED",IF(AND(MEDIAN(E25,F25,G25)&lt;=LISTS!$F$10,MAX(E25,F25,G25)&lt;=LISTS!$F$11),"B",IF(MAX(E25,F25,G25)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P25" s="14" t="n"/>
       <c r="Q25" s="14" t="n"/>
       <c r="R25" s="14">
         <f>IF(E25="","",IF(B25="","material?",IF(OR(F25="",G25=""),"size?",IF(I25="","exposed Y/N?",IF(H25="","qty?",IF(B25="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S25" s="12">
         <f t="array" ref="S25">IF(OR(O25="",M25=""),"",IF(B25="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B25&amp;"_"&amp;SUBSTITUTE(O25,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T25" s="12">
         <f>IF(ISNUMBER(S25),M25*S25,"")</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="59">
@@ -19130,29 +17350,23 @@
       </c>
       <c r="M26" s="25">
         <f>IF(OR(E26="",F26="",G26=""),"",E26*F26*G26/1000000000*IF(H26="",1,H26))</f>
-        <v/>
       </c>
       <c r="N26" s="19">
         <f>IF(OR(E26="",F26=""),"",E26*F26/1000000*IF(H26="",1,H26))</f>
-        <v/>
       </c>
       <c r="O26" s="14">
         <f>IF(E26="","",IF(K26&lt;&gt;"",K26,IF(AND(E26*F26*G26/1000000000&lt;LISTS!$F$4,MAX(E26,F26,G26)&lt;LISTS!$F$5),"D",IF(I26="N","C",IF(J26="Y","A-CURVED",IF(AND(MEDIAN(E26,F26,G26)&lt;=LISTS!$F$10,MAX(E26,F26,G26)&lt;=LISTS!$F$11),"B",IF(MAX(E26,F26,G26)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P26" s="14" t="n"/>
       <c r="Q26" s="14" t="n"/>
       <c r="R26" s="14">
         <f>IF(E26="","",IF(B26="","material?",IF(OR(F26="",G26=""),"size?",IF(I26="","exposed Y/N?",IF(H26="","qty?",IF(B26="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S26" s="12">
         <f t="array" ref="S26">IF(OR(O26="",M26=""),"",IF(B26="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B26&amp;"_"&amp;SUBSTITUTE(O26,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T26" s="12">
         <f>IF(ISNUMBER(S26),M26*S26,"")</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="59">
@@ -19204,29 +17418,23 @@
       </c>
       <c r="M27" s="25">
         <f>IF(OR(E27="",F27="",G27=""),"",E27*F27*G27/1000000000*IF(H27="",1,H27))</f>
-        <v/>
       </c>
       <c r="N27" s="19">
         <f>IF(OR(E27="",F27=""),"",E27*F27/1000000*IF(H27="",1,H27))</f>
-        <v/>
       </c>
       <c r="O27" s="14">
         <f>IF(E27="","",IF(K27&lt;&gt;"",K27,IF(AND(E27*F27*G27/1000000000&lt;LISTS!$F$4,MAX(E27,F27,G27)&lt;LISTS!$F$5),"D",IF(I27="N","C",IF(J27="Y","A-CURVED",IF(AND(MEDIAN(E27,F27,G27)&lt;=LISTS!$F$10,MAX(E27,F27,G27)&lt;=LISTS!$F$11),"B",IF(MAX(E27,F27,G27)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P27" s="14" t="n"/>
       <c r="Q27" s="14" t="n"/>
       <c r="R27" s="14">
         <f>IF(E27="","",IF(B27="","material?",IF(OR(F27="",G27=""),"size?",IF(I27="","exposed Y/N?",IF(H27="","qty?",IF(B27="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S27" s="12">
         <f t="array" ref="S27">IF(OR(O27="",M27=""),"",IF(B27="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B27&amp;"_"&amp;SUBSTITUTE(O27,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T27" s="12">
         <f>IF(ISNUMBER(S27),M27*S27,"")</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="59">
@@ -19278,29 +17486,23 @@
       </c>
       <c r="M28" s="25">
         <f>IF(OR(E28="",F28="",G28=""),"",E28*F28*G28/1000000000*IF(H28="",1,H28))</f>
-        <v/>
       </c>
       <c r="N28" s="19">
         <f>IF(OR(E28="",F28=""),"",E28*F28/1000000*IF(H28="",1,H28))</f>
-        <v/>
       </c>
       <c r="O28" s="14">
         <f>IF(E28="","",IF(K28&lt;&gt;"",K28,IF(AND(E28*F28*G28/1000000000&lt;LISTS!$F$4,MAX(E28,F28,G28)&lt;LISTS!$F$5),"D",IF(I28="N","C",IF(J28="Y","A-CURVED",IF(AND(MEDIAN(E28,F28,G28)&lt;=LISTS!$F$10,MAX(E28,F28,G28)&lt;=LISTS!$F$11),"B",IF(MAX(E28,F28,G28)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P28" s="14" t="n"/>
       <c r="Q28" s="14" t="n"/>
       <c r="R28" s="14">
         <f>IF(E28="","",IF(B28="","material?",IF(OR(F28="",G28=""),"size?",IF(I28="","exposed Y/N?",IF(H28="","qty?",IF(B28="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S28" s="12">
         <f t="array" ref="S28">IF(OR(O28="",M28=""),"",IF(B28="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B28&amp;"_"&amp;SUBSTITUTE(O28,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T28" s="12">
         <f>IF(ISNUMBER(S28),M28*S28,"")</f>
-        <v/>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="59">
@@ -19320,29 +17522,23 @@
       <c r="L29" s="10" t="n"/>
       <c r="M29" s="25">
         <f>IF(OR(E29="",F29="",G29=""),"",E29*F29*G29/1000000000*IF(H29="",1,H29))</f>
-        <v/>
       </c>
       <c r="N29" s="19">
         <f>IF(OR(E29="",F29=""),"",E29*F29/1000000*IF(H29="",1,H29))</f>
-        <v/>
       </c>
       <c r="O29" s="14">
         <f>IF(E29="","",IF(K29&lt;&gt;"",K29,IF(AND(E29*F29*G29/1000000000&lt;LISTS!$F$4,MAX(E29,F29,G29)&lt;LISTS!$F$5),"D",IF(I29="N","C",IF(J29="Y","A-CURVED",IF(AND(MEDIAN(E29,F29,G29)&lt;=LISTS!$F$10,MAX(E29,F29,G29)&lt;=LISTS!$F$11),"B",IF(MAX(E29,F29,G29)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P29" s="14" t="n"/>
       <c r="Q29" s="14" t="n"/>
       <c r="R29" s="14">
         <f>IF(E29="","",IF(B29="","material?",IF(OR(F29="",G29=""),"size?",IF(I29="","exposed Y/N?",IF(H29="","qty?",IF(B29="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S29" s="12">
         <f t="array" ref="S29">IF(OR(O29="",M29=""),"",IF(B29="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B29&amp;"_"&amp;SUBSTITUTE(O29,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T29" s="12">
         <f>IF(ISNUMBER(S29),M29*S29,"")</f>
-        <v/>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="59">
@@ -19362,29 +17558,23 @@
       <c r="L30" s="10" t="n"/>
       <c r="M30" s="25">
         <f>IF(OR(E30="",F30="",G30=""),"",E30*F30*G30/1000000000*IF(H30="",1,H30))</f>
-        <v/>
       </c>
       <c r="N30" s="19">
         <f>IF(OR(E30="",F30=""),"",E30*F30/1000000*IF(H30="",1,H30))</f>
-        <v/>
       </c>
       <c r="O30" s="14">
         <f>IF(E30="","",IF(K30&lt;&gt;"",K30,IF(AND(E30*F30*G30/1000000000&lt;LISTS!$F$4,MAX(E30,F30,G30)&lt;LISTS!$F$5),"D",IF(I30="N","C",IF(J30="Y","A-CURVED",IF(AND(MEDIAN(E30,F30,G30)&lt;=LISTS!$F$10,MAX(E30,F30,G30)&lt;=LISTS!$F$11),"B",IF(MAX(E30,F30,G30)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P30" s="14" t="n"/>
       <c r="Q30" s="14" t="n"/>
       <c r="R30" s="14">
         <f>IF(E30="","",IF(B30="","material?",IF(OR(F30="",G30=""),"size?",IF(I30="","exposed Y/N?",IF(H30="","qty?",IF(B30="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S30" s="12">
         <f t="array" ref="S30">IF(OR(O30="",M30=""),"",IF(B30="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B30&amp;"_"&amp;SUBSTITUTE(O30,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T30" s="12">
         <f>IF(ISNUMBER(S30),M30*S30,"")</f>
-        <v/>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="59">
@@ -19404,29 +17594,23 @@
       <c r="L31" s="10" t="n"/>
       <c r="M31" s="25">
         <f>IF(OR(E31="",F31="",G31=""),"",E31*F31*G31/1000000000*IF(H31="",1,H31))</f>
-        <v/>
       </c>
       <c r="N31" s="19">
         <f>IF(OR(E31="",F31=""),"",E31*F31/1000000*IF(H31="",1,H31))</f>
-        <v/>
       </c>
       <c r="O31" s="14">
         <f>IF(E31="","",IF(K31&lt;&gt;"",K31,IF(AND(E31*F31*G31/1000000000&lt;LISTS!$F$4,MAX(E31,F31,G31)&lt;LISTS!$F$5),"D",IF(I31="N","C",IF(J31="Y","A-CURVED",IF(AND(MEDIAN(E31,F31,G31)&lt;=LISTS!$F$10,MAX(E31,F31,G31)&lt;=LISTS!$F$11),"B",IF(MAX(E31,F31,G31)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P31" s="14" t="n"/>
       <c r="Q31" s="14" t="n"/>
       <c r="R31" s="14">
         <f>IF(E31="","",IF(B31="","material?",IF(OR(F31="",G31=""),"size?",IF(I31="","exposed Y/N?",IF(H31="","qty?",IF(B31="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S31" s="12">
         <f t="array" ref="S31">IF(OR(O31="",M31=""),"",IF(B31="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B31&amp;"_"&amp;SUBSTITUTE(O31,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T31" s="12">
         <f>IF(ISNUMBER(S31),M31*S31,"")</f>
-        <v/>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="59">
@@ -19446,29 +17630,23 @@
       <c r="L32" s="10" t="n"/>
       <c r="M32" s="25">
         <f>IF(OR(E32="",F32="",G32=""),"",E32*F32*G32/1000000000*IF(H32="",1,H32))</f>
-        <v/>
       </c>
       <c r="N32" s="19">
         <f>IF(OR(E32="",F32=""),"",E32*F32/1000000*IF(H32="",1,H32))</f>
-        <v/>
       </c>
       <c r="O32" s="14">
         <f>IF(E32="","",IF(K32&lt;&gt;"",K32,IF(AND(E32*F32*G32/1000000000&lt;LISTS!$F$4,MAX(E32,F32,G32)&lt;LISTS!$F$5),"D",IF(I32="N","C",IF(J32="Y","A-CURVED",IF(AND(MEDIAN(E32,F32,G32)&lt;=LISTS!$F$10,MAX(E32,F32,G32)&lt;=LISTS!$F$11),"B",IF(MAX(E32,F32,G32)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P32" s="14" t="n"/>
       <c r="Q32" s="14" t="n"/>
       <c r="R32" s="14">
         <f>IF(E32="","",IF(B32="","material?",IF(OR(F32="",G32=""),"size?",IF(I32="","exposed Y/N?",IF(H32="","qty?",IF(B32="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S32" s="12">
         <f t="array" ref="S32">IF(OR(O32="",M32=""),"",IF(B32="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B32&amp;"_"&amp;SUBSTITUTE(O32,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T32" s="12">
         <f>IF(ISNUMBER(S32),M32*S32,"")</f>
-        <v/>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="59">
@@ -19488,29 +17666,23 @@
       <c r="L33" s="10" t="n"/>
       <c r="M33" s="25">
         <f>IF(OR(E33="",F33="",G33=""),"",E33*F33*G33/1000000000*IF(H33="",1,H33))</f>
-        <v/>
       </c>
       <c r="N33" s="19">
         <f>IF(OR(E33="",F33=""),"",E33*F33/1000000*IF(H33="",1,H33))</f>
-        <v/>
       </c>
       <c r="O33" s="14">
         <f>IF(E33="","",IF(K33&lt;&gt;"",K33,IF(AND(E33*F33*G33/1000000000&lt;LISTS!$F$4,MAX(E33,F33,G33)&lt;LISTS!$F$5),"D",IF(I33="N","C",IF(J33="Y","A-CURVED",IF(AND(MEDIAN(E33,F33,G33)&lt;=LISTS!$F$10,MAX(E33,F33,G33)&lt;=LISTS!$F$11),"B",IF(MAX(E33,F33,G33)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P33" s="14" t="n"/>
       <c r="Q33" s="14" t="n"/>
       <c r="R33" s="14">
         <f>IF(E33="","",IF(B33="","material?",IF(OR(F33="",G33=""),"size?",IF(I33="","exposed Y/N?",IF(H33="","qty?",IF(B33="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S33" s="12">
         <f t="array" ref="S33">IF(OR(O33="",M33=""),"",IF(B33="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B33&amp;"_"&amp;SUBSTITUTE(O33,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T33" s="12">
         <f>IF(ISNUMBER(S33),M33*S33,"")</f>
-        <v/>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="59">
@@ -19530,29 +17702,23 @@
       <c r="L34" s="10" t="n"/>
       <c r="M34" s="25">
         <f>IF(OR(E34="",F34="",G34=""),"",E34*F34*G34/1000000000*IF(H34="",1,H34))</f>
-        <v/>
       </c>
       <c r="N34" s="19">
         <f>IF(OR(E34="",F34=""),"",E34*F34/1000000*IF(H34="",1,H34))</f>
-        <v/>
       </c>
       <c r="O34" s="14">
         <f>IF(E34="","",IF(K34&lt;&gt;"",K34,IF(AND(E34*F34*G34/1000000000&lt;LISTS!$F$4,MAX(E34,F34,G34)&lt;LISTS!$F$5),"D",IF(I34="N","C",IF(J34="Y","A-CURVED",IF(AND(MEDIAN(E34,F34,G34)&lt;=LISTS!$F$10,MAX(E34,F34,G34)&lt;=LISTS!$F$11),"B",IF(MAX(E34,F34,G34)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P34" s="14" t="n"/>
       <c r="Q34" s="14" t="n"/>
       <c r="R34" s="14">
         <f>IF(E34="","",IF(B34="","material?",IF(OR(F34="",G34=""),"size?",IF(I34="","exposed Y/N?",IF(H34="","qty?",IF(B34="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S34" s="12">
         <f t="array" ref="S34">IF(OR(O34="",M34=""),"",IF(B34="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B34&amp;"_"&amp;SUBSTITUTE(O34,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T34" s="12">
         <f>IF(ISNUMBER(S34),M34*S34,"")</f>
-        <v/>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="59">
@@ -19572,29 +17738,23 @@
       <c r="L35" s="10" t="n"/>
       <c r="M35" s="25">
         <f>IF(OR(E35="",F35="",G35=""),"",E35*F35*G35/1000000000*IF(H35="",1,H35))</f>
-        <v/>
       </c>
       <c r="N35" s="19">
         <f>IF(OR(E35="",F35=""),"",E35*F35/1000000*IF(H35="",1,H35))</f>
-        <v/>
       </c>
       <c r="O35" s="14">
         <f>IF(E35="","",IF(K35&lt;&gt;"",K35,IF(AND(E35*F35*G35/1000000000&lt;LISTS!$F$4,MAX(E35,F35,G35)&lt;LISTS!$F$5),"D",IF(I35="N","C",IF(J35="Y","A-CURVED",IF(AND(MEDIAN(E35,F35,G35)&lt;=LISTS!$F$10,MAX(E35,F35,G35)&lt;=LISTS!$F$11),"B",IF(MAX(E35,F35,G35)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P35" s="14" t="n"/>
       <c r="Q35" s="14" t="n"/>
       <c r="R35" s="14">
         <f>IF(E35="","",IF(B35="","material?",IF(OR(F35="",G35=""),"size?",IF(I35="","exposed Y/N?",IF(H35="","qty?",IF(B35="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S35" s="12">
         <f t="array" ref="S35">IF(OR(O35="",M35=""),"",IF(B35="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B35&amp;"_"&amp;SUBSTITUTE(O35,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T35" s="12">
         <f>IF(ISNUMBER(S35),M35*S35,"")</f>
-        <v/>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="59">
@@ -19614,29 +17774,23 @@
       <c r="L36" s="10" t="n"/>
       <c r="M36" s="25">
         <f>IF(OR(E36="",F36="",G36=""),"",E36*F36*G36/1000000000*IF(H36="",1,H36))</f>
-        <v/>
       </c>
       <c r="N36" s="19">
         <f>IF(OR(E36="",F36=""),"",E36*F36/1000000*IF(H36="",1,H36))</f>
-        <v/>
       </c>
       <c r="O36" s="14">
         <f>IF(E36="","",IF(K36&lt;&gt;"",K36,IF(AND(E36*F36*G36/1000000000&lt;LISTS!$F$4,MAX(E36,F36,G36)&lt;LISTS!$F$5),"D",IF(I36="N","C",IF(J36="Y","A-CURVED",IF(AND(MEDIAN(E36,F36,G36)&lt;=LISTS!$F$10,MAX(E36,F36,G36)&lt;=LISTS!$F$11),"B",IF(MAX(E36,F36,G36)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P36" s="14" t="n"/>
       <c r="Q36" s="14" t="n"/>
       <c r="R36" s="14">
         <f>IF(E36="","",IF(B36="","material?",IF(OR(F36="",G36=""),"size?",IF(I36="","exposed Y/N?",IF(H36="","qty?",IF(B36="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S36" s="12">
         <f t="array" ref="S36">IF(OR(O36="",M36=""),"",IF(B36="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B36&amp;"_"&amp;SUBSTITUTE(O36,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T36" s="12">
         <f>IF(ISNUMBER(S36),M36*S36,"")</f>
-        <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="59">
@@ -19656,29 +17810,23 @@
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="25">
         <f>IF(OR(E37="",F37="",G37=""),"",E37*F37*G37/1000000000*IF(H37="",1,H37))</f>
-        <v/>
       </c>
       <c r="N37" s="19">
         <f>IF(OR(E37="",F37=""),"",E37*F37/1000000*IF(H37="",1,H37))</f>
-        <v/>
       </c>
       <c r="O37" s="14">
         <f>IF(E37="","",IF(K37&lt;&gt;"",K37,IF(AND(E37*F37*G37/1000000000&lt;LISTS!$F$4,MAX(E37,F37,G37)&lt;LISTS!$F$5),"D",IF(I37="N","C",IF(J37="Y","A-CURVED",IF(AND(MEDIAN(E37,F37,G37)&lt;=LISTS!$F$10,MAX(E37,F37,G37)&lt;=LISTS!$F$11),"B",IF(MAX(E37,F37,G37)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
       <c r="R37" s="14">
         <f>IF(E37="","",IF(B37="","material?",IF(OR(F37="",G37=""),"size?",IF(I37="","exposed Y/N?",IF(H37="","qty?",IF(B37="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S37" s="12">
         <f t="array" ref="S37">IF(OR(O37="",M37=""),"",IF(B37="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B37&amp;"_"&amp;SUBSTITUTE(O37,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T37" s="12">
         <f>IF(ISNUMBER(S37),M37*S37,"")</f>
-        <v/>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="59">
@@ -19698,29 +17846,23 @@
       <c r="L38" s="10" t="n"/>
       <c r="M38" s="25">
         <f>IF(OR(E38="",F38="",G38=""),"",E38*F38*G38/1000000000*IF(H38="",1,H38))</f>
-        <v/>
       </c>
       <c r="N38" s="19">
         <f>IF(OR(E38="",F38=""),"",E38*F38/1000000*IF(H38="",1,H38))</f>
-        <v/>
       </c>
       <c r="O38" s="14">
         <f>IF(E38="","",IF(K38&lt;&gt;"",K38,IF(AND(E38*F38*G38/1000000000&lt;LISTS!$F$4,MAX(E38,F38,G38)&lt;LISTS!$F$5),"D",IF(I38="N","C",IF(J38="Y","A-CURVED",IF(AND(MEDIAN(E38,F38,G38)&lt;=LISTS!$F$10,MAX(E38,F38,G38)&lt;=LISTS!$F$11),"B",IF(MAX(E38,F38,G38)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P38" s="14" t="n"/>
       <c r="Q38" s="14" t="n"/>
       <c r="R38" s="14">
         <f>IF(E38="","",IF(B38="","material?",IF(OR(F38="",G38=""),"size?",IF(I38="","exposed Y/N?",IF(H38="","qty?",IF(B38="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S38" s="12">
         <f t="array" ref="S38">IF(OR(O38="",M38=""),"",IF(B38="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B38&amp;"_"&amp;SUBSTITUTE(O38,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T38" s="12">
         <f>IF(ISNUMBER(S38),M38*S38,"")</f>
-        <v/>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="59">
@@ -19740,29 +17882,23 @@
       <c r="L39" s="10" t="n"/>
       <c r="M39" s="25">
         <f>IF(OR(E39="",F39="",G39=""),"",E39*F39*G39/1000000000*IF(H39="",1,H39))</f>
-        <v/>
       </c>
       <c r="N39" s="19">
         <f>IF(OR(E39="",F39=""),"",E39*F39/1000000*IF(H39="",1,H39))</f>
-        <v/>
       </c>
       <c r="O39" s="14">
         <f>IF(E39="","",IF(K39&lt;&gt;"",K39,IF(AND(E39*F39*G39/1000000000&lt;LISTS!$F$4,MAX(E39,F39,G39)&lt;LISTS!$F$5),"D",IF(I39="N","C",IF(J39="Y","A-CURVED",IF(AND(MEDIAN(E39,F39,G39)&lt;=LISTS!$F$10,MAX(E39,F39,G39)&lt;=LISTS!$F$11),"B",IF(MAX(E39,F39,G39)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P39" s="14" t="n"/>
       <c r="Q39" s="14" t="n"/>
       <c r="R39" s="14">
         <f>IF(E39="","",IF(B39="","material?",IF(OR(F39="",G39=""),"size?",IF(I39="","exposed Y/N?",IF(H39="","qty?",IF(B39="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S39" s="12">
         <f t="array" ref="S39">IF(OR(O39="",M39=""),"",IF(B39="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B39&amp;"_"&amp;SUBSTITUTE(O39,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T39" s="12">
         <f>IF(ISNUMBER(S39),M39*S39,"")</f>
-        <v/>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="59">
@@ -19782,29 +17918,23 @@
       <c r="L40" s="10" t="n"/>
       <c r="M40" s="25">
         <f>IF(OR(E40="",F40="",G40=""),"",E40*F40*G40/1000000000*IF(H40="",1,H40))</f>
-        <v/>
       </c>
       <c r="N40" s="19">
         <f>IF(OR(E40="",F40=""),"",E40*F40/1000000*IF(H40="",1,H40))</f>
-        <v/>
       </c>
       <c r="O40" s="14">
         <f>IF(E40="","",IF(K40&lt;&gt;"",K40,IF(AND(E40*F40*G40/1000000000&lt;LISTS!$F$4,MAX(E40,F40,G40)&lt;LISTS!$F$5),"D",IF(I40="N","C",IF(J40="Y","A-CURVED",IF(AND(MEDIAN(E40,F40,G40)&lt;=LISTS!$F$10,MAX(E40,F40,G40)&lt;=LISTS!$F$11),"B",IF(MAX(E40,F40,G40)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P40" s="14" t="n"/>
       <c r="Q40" s="14" t="n"/>
       <c r="R40" s="14">
         <f>IF(E40="","",IF(B40="","material?",IF(OR(F40="",G40=""),"size?",IF(I40="","exposed Y/N?",IF(H40="","qty?",IF(B40="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S40" s="12">
         <f t="array" ref="S40">IF(OR(O40="",M40=""),"",IF(B40="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B40&amp;"_"&amp;SUBSTITUTE(O40,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T40" s="12">
         <f>IF(ISNUMBER(S40),M40*S40,"")</f>
-        <v/>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="59">
@@ -19824,29 +17954,23 @@
       <c r="L41" s="10" t="n"/>
       <c r="M41" s="25">
         <f>IF(OR(E41="",F41="",G41=""),"",E41*F41*G41/1000000000*IF(H41="",1,H41))</f>
-        <v/>
       </c>
       <c r="N41" s="19">
         <f>IF(OR(E41="",F41=""),"",E41*F41/1000000*IF(H41="",1,H41))</f>
-        <v/>
       </c>
       <c r="O41" s="14">
         <f>IF(E41="","",IF(K41&lt;&gt;"",K41,IF(AND(E41*F41*G41/1000000000&lt;LISTS!$F$4,MAX(E41,F41,G41)&lt;LISTS!$F$5),"D",IF(I41="N","C",IF(J41="Y","A-CURVED",IF(AND(MEDIAN(E41,F41,G41)&lt;=LISTS!$F$10,MAX(E41,F41,G41)&lt;=LISTS!$F$11),"B",IF(MAX(E41,F41,G41)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P41" s="14" t="n"/>
       <c r="Q41" s="14" t="n"/>
       <c r="R41" s="14">
         <f>IF(E41="","",IF(B41="","material?",IF(OR(F41="",G41=""),"size?",IF(I41="","exposed Y/N?",IF(H41="","qty?",IF(B41="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S41" s="12">
         <f t="array" ref="S41">IF(OR(O41="",M41=""),"",IF(B41="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B41&amp;"_"&amp;SUBSTITUTE(O41,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T41" s="12">
         <f>IF(ISNUMBER(S41),M41*S41,"")</f>
-        <v/>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="59">
@@ -19866,29 +17990,23 @@
       <c r="L42" s="10" t="n"/>
       <c r="M42" s="25">
         <f>IF(OR(E42="",F42="",G42=""),"",E42*F42*G42/1000000000*IF(H42="",1,H42))</f>
-        <v/>
       </c>
       <c r="N42" s="19">
         <f>IF(OR(E42="",F42=""),"",E42*F42/1000000*IF(H42="",1,H42))</f>
-        <v/>
       </c>
       <c r="O42" s="14">
         <f>IF(E42="","",IF(K42&lt;&gt;"",K42,IF(AND(E42*F42*G42/1000000000&lt;LISTS!$F$4,MAX(E42,F42,G42)&lt;LISTS!$F$5),"D",IF(I42="N","C",IF(J42="Y","A-CURVED",IF(AND(MEDIAN(E42,F42,G42)&lt;=LISTS!$F$10,MAX(E42,F42,G42)&lt;=LISTS!$F$11),"B",IF(MAX(E42,F42,G42)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
       </c>
       <c r="P42" s="14" t="n"/>
       <c r="Q42" s="14" t="n"/>
       <c r="R42" s="14">
         <f>IF(E42="","",IF(B42="","material?",IF(OR(F42="",G42=""),"size?",IF(I42="","exposed Y/N?",IF(H42="","qty?",IF(B42="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
       </c>
       <c r="S42" s="12">
         <f t="array" ref="S42">IF(OR(O42="",M42=""),"",IF(B42="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B42&amp;"_"&amp;SUBSTITUTE(O42,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
       </c>
       <c r="T42" s="12">
         <f>IF(ISNUMBER(S42),M42*S42,"")</f>
-        <v/>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="59"/>
@@ -20040,35 +18158,27 @@
       </c>
       <c r="M46" s="25">
         <f>IF(OR(E46="",F46="",G46=""),"",E46*F46*G46/1000000000*IF(H46="",1,H46))</f>
-        <v/>
       </c>
       <c r="N46" s="19">
         <f>IF(OR(E46="",F46=""),"",E46*F46/1000000*IF(H46="",1,H46))</f>
-        <v/>
       </c>
       <c r="O46" s="14">
         <f>IF(OR(E46="",F46=""),"",MAX(INT(LISTS!$F$6/(E46+LISTS!$F$8))*INT(LISTS!$F$7/(F46+LISTS!$F$8)),INT(LISTS!$F$6/(F46+LISTS!$F$8))*INT(LISTS!$F$7/(E46+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P46" s="19">
         <f>IF(K46&lt;&gt;"",K46,IF(OR(O46="",O46=0),"",IF(H46="",1,H46)/O46))</f>
-        <v/>
       </c>
       <c r="Q46" s="36">
         <f>IF(OR(K46&lt;&gt;"",P46=""),"",1-(IF(H46="",1,H46)*E46*F46)/(ROUNDUP(P46,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R46" s="14">
         <f>IF(AND(E46="",K46=""),"",IF(B46="","panel type?",IF(AND(K46="",O46=0),"panel bigger than sheet",IF(AND(G46&lt;&gt;"",IFERROR(VALUE(MID(B46,5,FIND("-",B46,5)-5)),0)&lt;&gt;G46),"T must match panel type",IF(I46="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S46" s="12">
         <f t="array" ref="S46">IF(OR(B46="",P46=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B46,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T46" s="12">
         <f>IF(ISNUMBER(S46),IF(K46&lt;&gt;"",K46,IF(Q46&gt;RATES!$C$97,P46*(1+RATES!$C$98),ROUNDUP(P46,0)))*S46,"")</f>
-        <v/>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="59">
@@ -20114,35 +18224,27 @@
       </c>
       <c r="M47" s="25">
         <f>IF(OR(E47="",F47="",G47=""),"",E47*F47*G47/1000000000*IF(H47="",1,H47))</f>
-        <v/>
       </c>
       <c r="N47" s="19">
         <f>IF(OR(E47="",F47=""),"",E47*F47/1000000*IF(H47="",1,H47))</f>
-        <v/>
       </c>
       <c r="O47" s="14">
         <f>IF(OR(E47="",F47=""),"",MAX(INT(LISTS!$F$6/(E47+LISTS!$F$8))*INT(LISTS!$F$7/(F47+LISTS!$F$8)),INT(LISTS!$F$6/(F47+LISTS!$F$8))*INT(LISTS!$F$7/(E47+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P47" s="19">
         <f>IF(K47&lt;&gt;"",K47,IF(OR(O47="",O47=0),"",IF(H47="",1,H47)/O47))</f>
-        <v/>
       </c>
       <c r="Q47" s="36">
         <f>IF(OR(K47&lt;&gt;"",P47=""),"",1-(IF(H47="",1,H47)*E47*F47)/(ROUNDUP(P47,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R47" s="14">
         <f>IF(AND(E47="",K47=""),"",IF(B47="","panel type?",IF(AND(K47="",O47=0),"panel bigger than sheet",IF(AND(G47&lt;&gt;"",IFERROR(VALUE(MID(B47,5,FIND("-",B47,5)-5)),0)&lt;&gt;G47),"T must match panel type",IF(I47="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S47" s="12">
         <f t="array" ref="S47">IF(OR(B47="",P47=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B47,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T47" s="12">
         <f>IF(ISNUMBER(S47),IF(K47&lt;&gt;"",K47,IF(Q47&gt;RATES!$C$97,P47*(1+RATES!$C$98),ROUNDUP(P47,0)))*S47,"")</f>
-        <v/>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="59">
@@ -20188,35 +18290,27 @@
       </c>
       <c r="M48" s="25">
         <f>IF(OR(E48="",F48="",G48=""),"",E48*F48*G48/1000000000*IF(H48="",1,H48))</f>
-        <v/>
       </c>
       <c r="N48" s="19">
         <f>IF(OR(E48="",F48=""),"",E48*F48/1000000*IF(H48="",1,H48))</f>
-        <v/>
       </c>
       <c r="O48" s="14">
         <f>IF(OR(E48="",F48=""),"",MAX(INT(LISTS!$F$6/(E48+LISTS!$F$8))*INT(LISTS!$F$7/(F48+LISTS!$F$8)),INT(LISTS!$F$6/(F48+LISTS!$F$8))*INT(LISTS!$F$7/(E48+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P48" s="19">
         <f>IF(K48&lt;&gt;"",K48,IF(OR(O48="",O48=0),"",IF(H48="",1,H48)/O48))</f>
-        <v/>
       </c>
       <c r="Q48" s="36">
         <f>IF(OR(K48&lt;&gt;"",P48=""),"",1-(IF(H48="",1,H48)*E48*F48)/(ROUNDUP(P48,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R48" s="14">
         <f>IF(AND(E48="",K48=""),"",IF(B48="","panel type?",IF(AND(K48="",O48=0),"panel bigger than sheet",IF(AND(G48&lt;&gt;"",IFERROR(VALUE(MID(B48,5,FIND("-",B48,5)-5)),0)&lt;&gt;G48),"T must match panel type",IF(I48="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S48" s="12">
         <f t="array" ref="S48">IF(OR(B48="",P48=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B48,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T48" s="12">
         <f>IF(ISNUMBER(S48),IF(K48&lt;&gt;"",K48,IF(Q48&gt;RATES!$C$97,P48*(1+RATES!$C$98),ROUNDUP(P48,0)))*S48,"")</f>
-        <v/>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="59">
@@ -20262,35 +18356,27 @@
       </c>
       <c r="M49" s="25">
         <f>IF(OR(E49="",F49="",G49=""),"",E49*F49*G49/1000000000*IF(H49="",1,H49))</f>
-        <v/>
       </c>
       <c r="N49" s="19">
         <f>IF(OR(E49="",F49=""),"",E49*F49/1000000*IF(H49="",1,H49))</f>
-        <v/>
       </c>
       <c r="O49" s="14">
         <f>IF(OR(E49="",F49=""),"",MAX(INT(LISTS!$F$6/(E49+LISTS!$F$8))*INT(LISTS!$F$7/(F49+LISTS!$F$8)),INT(LISTS!$F$6/(F49+LISTS!$F$8))*INT(LISTS!$F$7/(E49+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P49" s="19">
         <f>IF(K49&lt;&gt;"",K49,IF(OR(O49="",O49=0),"",IF(H49="",1,H49)/O49))</f>
-        <v/>
       </c>
       <c r="Q49" s="36">
         <f>IF(OR(K49&lt;&gt;"",P49=""),"",1-(IF(H49="",1,H49)*E49*F49)/(ROUNDUP(P49,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R49" s="14">
         <f>IF(AND(E49="",K49=""),"",IF(B49="","panel type?",IF(AND(K49="",O49=0),"panel bigger than sheet",IF(AND(G49&lt;&gt;"",IFERROR(VALUE(MID(B49,5,FIND("-",B49,5)-5)),0)&lt;&gt;G49),"T must match panel type",IF(I49="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S49" s="12">
         <f t="array" ref="S49">IF(OR(B49="",P49=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B49,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T49" s="12">
         <f>IF(ISNUMBER(S49),IF(K49&lt;&gt;"",K49,IF(Q49&gt;RATES!$C$97,P49*(1+RATES!$C$98),ROUNDUP(P49,0)))*S49,"")</f>
-        <v/>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="59">
@@ -20336,35 +18422,27 @@
       </c>
       <c r="M50" s="25">
         <f>IF(OR(E50="",F50="",G50=""),"",E50*F50*G50/1000000000*IF(H50="",1,H50))</f>
-        <v/>
       </c>
       <c r="N50" s="19">
         <f>IF(OR(E50="",F50=""),"",E50*F50/1000000*IF(H50="",1,H50))</f>
-        <v/>
       </c>
       <c r="O50" s="14">
         <f>IF(OR(E50="",F50=""),"",MAX(INT(LISTS!$F$6/(E50+LISTS!$F$8))*INT(LISTS!$F$7/(F50+LISTS!$F$8)),INT(LISTS!$F$6/(F50+LISTS!$F$8))*INT(LISTS!$F$7/(E50+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P50" s="19">
         <f>IF(K50&lt;&gt;"",K50,IF(OR(O50="",O50=0),"",IF(H50="",1,H50)/O50))</f>
-        <v/>
       </c>
       <c r="Q50" s="36">
         <f>IF(OR(K50&lt;&gt;"",P50=""),"",1-(IF(H50="",1,H50)*E50*F50)/(ROUNDUP(P50,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R50" s="14">
         <f>IF(AND(E50="",K50=""),"",IF(B50="","panel type?",IF(AND(K50="",O50=0),"panel bigger than sheet",IF(AND(G50&lt;&gt;"",IFERROR(VALUE(MID(B50,5,FIND("-",B50,5)-5)),0)&lt;&gt;G50),"T must match panel type",IF(I50="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S50" s="12">
         <f t="array" ref="S50">IF(OR(B50="",P50=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B50,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T50" s="12">
         <f>IF(ISNUMBER(S50),IF(K50&lt;&gt;"",K50,IF(Q50&gt;RATES!$C$97,P50*(1+RATES!$C$98),ROUNDUP(P50,0)))*S50,"")</f>
-        <v/>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="59">
@@ -20410,35 +18488,27 @@
       </c>
       <c r="M51" s="25">
         <f>IF(OR(E51="",F51="",G51=""),"",E51*F51*G51/1000000000*IF(H51="",1,H51))</f>
-        <v/>
       </c>
       <c r="N51" s="19">
         <f>IF(OR(E51="",F51=""),"",E51*F51/1000000*IF(H51="",1,H51))</f>
-        <v/>
       </c>
       <c r="O51" s="14">
         <f>IF(OR(E51="",F51=""),"",MAX(INT(LISTS!$F$6/(E51+LISTS!$F$8))*INT(LISTS!$F$7/(F51+LISTS!$F$8)),INT(LISTS!$F$6/(F51+LISTS!$F$8))*INT(LISTS!$F$7/(E51+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P51" s="19">
         <f>IF(K51&lt;&gt;"",K51,IF(OR(O51="",O51=0),"",IF(H51="",1,H51)/O51))</f>
-        <v/>
       </c>
       <c r="Q51" s="36">
         <f>IF(OR(K51&lt;&gt;"",P51=""),"",1-(IF(H51="",1,H51)*E51*F51)/(ROUNDUP(P51,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R51" s="14">
         <f>IF(AND(E51="",K51=""),"",IF(B51="","panel type?",IF(AND(K51="",O51=0),"panel bigger than sheet",IF(AND(G51&lt;&gt;"",IFERROR(VALUE(MID(B51,5,FIND("-",B51,5)-5)),0)&lt;&gt;G51),"T must match panel type",IF(I51="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S51" s="12">
         <f t="array" ref="S51">IF(OR(B51="",P51=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B51,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T51" s="12">
         <f>IF(ISNUMBER(S51),IF(K51&lt;&gt;"",K51,IF(Q51&gt;RATES!$C$97,P51*(1+RATES!$C$98),ROUNDUP(P51,0)))*S51,"")</f>
-        <v/>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="59">
@@ -20484,35 +18554,27 @@
       </c>
       <c r="M52" s="25">
         <f>IF(OR(E52="",F52="",G52=""),"",E52*F52*G52/1000000000*IF(H52="",1,H52))</f>
-        <v/>
       </c>
       <c r="N52" s="19">
         <f>IF(OR(E52="",F52=""),"",E52*F52/1000000*IF(H52="",1,H52))</f>
-        <v/>
       </c>
       <c r="O52" s="14">
         <f>IF(OR(E52="",F52=""),"",MAX(INT(LISTS!$F$6/(E52+LISTS!$F$8))*INT(LISTS!$F$7/(F52+LISTS!$F$8)),INT(LISTS!$F$6/(F52+LISTS!$F$8))*INT(LISTS!$F$7/(E52+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P52" s="19">
         <f>IF(K52&lt;&gt;"",K52,IF(OR(O52="",O52=0),"",IF(H52="",1,H52)/O52))</f>
-        <v/>
       </c>
       <c r="Q52" s="36">
         <f>IF(OR(K52&lt;&gt;"",P52=""),"",1-(IF(H52="",1,H52)*E52*F52)/(ROUNDUP(P52,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R52" s="14">
         <f>IF(AND(E52="",K52=""),"",IF(B52="","panel type?",IF(AND(K52="",O52=0),"panel bigger than sheet",IF(AND(G52&lt;&gt;"",IFERROR(VALUE(MID(B52,5,FIND("-",B52,5)-5)),0)&lt;&gt;G52),"T must match panel type",IF(I52="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S52" s="12">
         <f t="array" ref="S52">IF(OR(B52="",P52=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B52,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T52" s="12">
         <f>IF(ISNUMBER(S52),IF(K52&lt;&gt;"",K52,IF(Q52&gt;RATES!$C$97,P52*(1+RATES!$C$98),ROUNDUP(P52,0)))*S52,"")</f>
-        <v/>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="59">
@@ -20532,35 +18594,27 @@
       <c r="L53" s="10" t="n"/>
       <c r="M53" s="25">
         <f>IF(OR(E53="",F53="",G53=""),"",E53*F53*G53/1000000000*IF(H53="",1,H53))</f>
-        <v/>
       </c>
       <c r="N53" s="19">
         <f>IF(OR(E53="",F53=""),"",E53*F53/1000000*IF(H53="",1,H53))</f>
-        <v/>
       </c>
       <c r="O53" s="14">
         <f>IF(OR(E53="",F53=""),"",MAX(INT(LISTS!$F$6/(E53+LISTS!$F$8))*INT(LISTS!$F$7/(F53+LISTS!$F$8)),INT(LISTS!$F$6/(F53+LISTS!$F$8))*INT(LISTS!$F$7/(E53+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P53" s="19">
         <f>IF(K53&lt;&gt;"",K53,IF(OR(O53="",O53=0),"",IF(H53="",1,H53)/O53))</f>
-        <v/>
       </c>
       <c r="Q53" s="36">
         <f>IF(OR(K53&lt;&gt;"",P53=""),"",1-(IF(H53="",1,H53)*E53*F53)/(ROUNDUP(P53,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R53" s="14">
         <f>IF(AND(E53="",K53=""),"",IF(B53="","panel type?",IF(AND(K53="",O53=0),"panel bigger than sheet",IF(AND(G53&lt;&gt;"",IFERROR(VALUE(MID(B53,5,FIND("-",B53,5)-5)),0)&lt;&gt;G53),"T must match panel type",IF(I53="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S53" s="12">
         <f t="array" ref="S53">IF(OR(B53="",P53=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B53,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T53" s="12">
         <f>IF(ISNUMBER(S53),IF(K53&lt;&gt;"",K53,IF(Q53&gt;RATES!$C$97,P53*(1+RATES!$C$98),ROUNDUP(P53,0)))*S53,"")</f>
-        <v/>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="59">
@@ -20580,35 +18634,27 @@
       <c r="L54" s="10" t="n"/>
       <c r="M54" s="25">
         <f>IF(OR(E54="",F54="",G54=""),"",E54*F54*G54/1000000000*IF(H54="",1,H54))</f>
-        <v/>
       </c>
       <c r="N54" s="19">
         <f>IF(OR(E54="",F54=""),"",E54*F54/1000000*IF(H54="",1,H54))</f>
-        <v/>
       </c>
       <c r="O54" s="14">
         <f>IF(OR(E54="",F54=""),"",MAX(INT(LISTS!$F$6/(E54+LISTS!$F$8))*INT(LISTS!$F$7/(F54+LISTS!$F$8)),INT(LISTS!$F$6/(F54+LISTS!$F$8))*INT(LISTS!$F$7/(E54+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P54" s="19">
         <f>IF(K54&lt;&gt;"",K54,IF(OR(O54="",O54=0),"",IF(H54="",1,H54)/O54))</f>
-        <v/>
       </c>
       <c r="Q54" s="36">
         <f>IF(OR(K54&lt;&gt;"",P54=""),"",1-(IF(H54="",1,H54)*E54*F54)/(ROUNDUP(P54,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R54" s="14">
         <f>IF(AND(E54="",K54=""),"",IF(B54="","panel type?",IF(AND(K54="",O54=0),"panel bigger than sheet",IF(AND(G54&lt;&gt;"",IFERROR(VALUE(MID(B54,5,FIND("-",B54,5)-5)),0)&lt;&gt;G54),"T must match panel type",IF(I54="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S54" s="12">
         <f t="array" ref="S54">IF(OR(B54="",P54=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B54,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T54" s="12">
         <f>IF(ISNUMBER(S54),IF(K54&lt;&gt;"",K54,IF(Q54&gt;RATES!$C$97,P54*(1+RATES!$C$98),ROUNDUP(P54,0)))*S54,"")</f>
-        <v/>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="59">
@@ -20628,35 +18674,27 @@
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="25">
         <f>IF(OR(E55="",F55="",G55=""),"",E55*F55*G55/1000000000*IF(H55="",1,H55))</f>
-        <v/>
       </c>
       <c r="N55" s="19">
         <f>IF(OR(E55="",F55=""),"",E55*F55/1000000*IF(H55="",1,H55))</f>
-        <v/>
       </c>
       <c r="O55" s="14">
         <f>IF(OR(E55="",F55=""),"",MAX(INT(LISTS!$F$6/(E55+LISTS!$F$8))*INT(LISTS!$F$7/(F55+LISTS!$F$8)),INT(LISTS!$F$6/(F55+LISTS!$F$8))*INT(LISTS!$F$7/(E55+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P55" s="19">
         <f>IF(K55&lt;&gt;"",K55,IF(OR(O55="",O55=0),"",IF(H55="",1,H55)/O55))</f>
-        <v/>
       </c>
       <c r="Q55" s="36">
         <f>IF(OR(K55&lt;&gt;"",P55=""),"",1-(IF(H55="",1,H55)*E55*F55)/(ROUNDUP(P55,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R55" s="14">
         <f>IF(AND(E55="",K55=""),"",IF(B55="","panel type?",IF(AND(K55="",O55=0),"panel bigger than sheet",IF(AND(G55&lt;&gt;"",IFERROR(VALUE(MID(B55,5,FIND("-",B55,5)-5)),0)&lt;&gt;G55),"T must match panel type",IF(I55="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S55" s="12">
         <f t="array" ref="S55">IF(OR(B55="",P55=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B55,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T55" s="12">
         <f>IF(ISNUMBER(S55),IF(K55&lt;&gt;"",K55,IF(Q55&gt;RATES!$C$97,P55*(1+RATES!$C$98),ROUNDUP(P55,0)))*S55,"")</f>
-        <v/>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="59">
@@ -20676,35 +18714,27 @@
       <c r="L56" s="10" t="n"/>
       <c r="M56" s="25">
         <f>IF(OR(E56="",F56="",G56=""),"",E56*F56*G56/1000000000*IF(H56="",1,H56))</f>
-        <v/>
       </c>
       <c r="N56" s="19">
         <f>IF(OR(E56="",F56=""),"",E56*F56/1000000*IF(H56="",1,H56))</f>
-        <v/>
       </c>
       <c r="O56" s="14">
         <f>IF(OR(E56="",F56=""),"",MAX(INT(LISTS!$F$6/(E56+LISTS!$F$8))*INT(LISTS!$F$7/(F56+LISTS!$F$8)),INT(LISTS!$F$6/(F56+LISTS!$F$8))*INT(LISTS!$F$7/(E56+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P56" s="19">
         <f>IF(K56&lt;&gt;"",K56,IF(OR(O56="",O56=0),"",IF(H56="",1,H56)/O56))</f>
-        <v/>
       </c>
       <c r="Q56" s="36">
         <f>IF(OR(K56&lt;&gt;"",P56=""),"",1-(IF(H56="",1,H56)*E56*F56)/(ROUNDUP(P56,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R56" s="14">
         <f>IF(AND(E56="",K56=""),"",IF(B56="","panel type?",IF(AND(K56="",O56=0),"panel bigger than sheet",IF(AND(G56&lt;&gt;"",IFERROR(VALUE(MID(B56,5,FIND("-",B56,5)-5)),0)&lt;&gt;G56),"T must match panel type",IF(I56="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S56" s="12">
         <f t="array" ref="S56">IF(OR(B56="",P56=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B56,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T56" s="12">
         <f>IF(ISNUMBER(S56),IF(K56&lt;&gt;"",K56,IF(Q56&gt;RATES!$C$97,P56*(1+RATES!$C$98),ROUNDUP(P56,0)))*S56,"")</f>
-        <v/>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="59">
@@ -20724,35 +18754,27 @@
       <c r="L57" s="10" t="n"/>
       <c r="M57" s="25">
         <f>IF(OR(E57="",F57="",G57=""),"",E57*F57*G57/1000000000*IF(H57="",1,H57))</f>
-        <v/>
       </c>
       <c r="N57" s="19">
         <f>IF(OR(E57="",F57=""),"",E57*F57/1000000*IF(H57="",1,H57))</f>
-        <v/>
       </c>
       <c r="O57" s="14">
         <f>IF(OR(E57="",F57=""),"",MAX(INT(LISTS!$F$6/(E57+LISTS!$F$8))*INT(LISTS!$F$7/(F57+LISTS!$F$8)),INT(LISTS!$F$6/(F57+LISTS!$F$8))*INT(LISTS!$F$7/(E57+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P57" s="19">
         <f>IF(K57&lt;&gt;"",K57,IF(OR(O57="",O57=0),"",IF(H57="",1,H57)/O57))</f>
-        <v/>
       </c>
       <c r="Q57" s="36">
         <f>IF(OR(K57&lt;&gt;"",P57=""),"",1-(IF(H57="",1,H57)*E57*F57)/(ROUNDUP(P57,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R57" s="14">
         <f>IF(AND(E57="",K57=""),"",IF(B57="","panel type?",IF(AND(K57="",O57=0),"panel bigger than sheet",IF(AND(G57&lt;&gt;"",IFERROR(VALUE(MID(B57,5,FIND("-",B57,5)-5)),0)&lt;&gt;G57),"T must match panel type",IF(I57="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S57" s="12">
         <f t="array" ref="S57">IF(OR(B57="",P57=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B57,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T57" s="12">
         <f>IF(ISNUMBER(S57),IF(K57&lt;&gt;"",K57,IF(Q57&gt;RATES!$C$97,P57*(1+RATES!$C$98),ROUNDUP(P57,0)))*S57,"")</f>
-        <v/>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="59">
@@ -20772,35 +18794,27 @@
       <c r="L58" s="10" t="n"/>
       <c r="M58" s="25">
         <f>IF(OR(E58="",F58="",G58=""),"",E58*F58*G58/1000000000*IF(H58="",1,H58))</f>
-        <v/>
       </c>
       <c r="N58" s="19">
         <f>IF(OR(E58="",F58=""),"",E58*F58/1000000*IF(H58="",1,H58))</f>
-        <v/>
       </c>
       <c r="O58" s="14">
         <f>IF(OR(E58="",F58=""),"",MAX(INT(LISTS!$F$6/(E58+LISTS!$F$8))*INT(LISTS!$F$7/(F58+LISTS!$F$8)),INT(LISTS!$F$6/(F58+LISTS!$F$8))*INT(LISTS!$F$7/(E58+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P58" s="19">
         <f>IF(K58&lt;&gt;"",K58,IF(OR(O58="",O58=0),"",IF(H58="",1,H58)/O58))</f>
-        <v/>
       </c>
       <c r="Q58" s="36">
         <f>IF(OR(K58&lt;&gt;"",P58=""),"",1-(IF(H58="",1,H58)*E58*F58)/(ROUNDUP(P58,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R58" s="14">
         <f>IF(AND(E58="",K58=""),"",IF(B58="","panel type?",IF(AND(K58="",O58=0),"panel bigger than sheet",IF(AND(G58&lt;&gt;"",IFERROR(VALUE(MID(B58,5,FIND("-",B58,5)-5)),0)&lt;&gt;G58),"T must match panel type",IF(I58="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S58" s="12">
         <f t="array" ref="S58">IF(OR(B58="",P58=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B58,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T58" s="12">
         <f>IF(ISNUMBER(S58),IF(K58&lt;&gt;"",K58,IF(Q58&gt;RATES!$C$97,P58*(1+RATES!$C$98),ROUNDUP(P58,0)))*S58,"")</f>
-        <v/>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="59">
@@ -20820,35 +18834,27 @@
       <c r="L59" s="10" t="n"/>
       <c r="M59" s="25">
         <f>IF(OR(E59="",F59="",G59=""),"",E59*F59*G59/1000000000*IF(H59="",1,H59))</f>
-        <v/>
       </c>
       <c r="N59" s="19">
         <f>IF(OR(E59="",F59=""),"",E59*F59/1000000*IF(H59="",1,H59))</f>
-        <v/>
       </c>
       <c r="O59" s="14">
         <f>IF(OR(E59="",F59=""),"",MAX(INT(LISTS!$F$6/(E59+LISTS!$F$8))*INT(LISTS!$F$7/(F59+LISTS!$F$8)),INT(LISTS!$F$6/(F59+LISTS!$F$8))*INT(LISTS!$F$7/(E59+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P59" s="19">
         <f>IF(K59&lt;&gt;"",K59,IF(OR(O59="",O59=0),"",IF(H59="",1,H59)/O59))</f>
-        <v/>
       </c>
       <c r="Q59" s="36">
         <f>IF(OR(K59&lt;&gt;"",P59=""),"",1-(IF(H59="",1,H59)*E59*F59)/(ROUNDUP(P59,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R59" s="14">
         <f>IF(AND(E59="",K59=""),"",IF(B59="","panel type?",IF(AND(K59="",O59=0),"panel bigger than sheet",IF(AND(G59&lt;&gt;"",IFERROR(VALUE(MID(B59,5,FIND("-",B59,5)-5)),0)&lt;&gt;G59),"T must match panel type",IF(I59="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S59" s="12">
         <f t="array" ref="S59">IF(OR(B59="",P59=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B59,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T59" s="12">
         <f>IF(ISNUMBER(S59),IF(K59&lt;&gt;"",K59,IF(Q59&gt;RATES!$C$97,P59*(1+RATES!$C$98),ROUNDUP(P59,0)))*S59,"")</f>
-        <v/>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="59">
@@ -20868,35 +18874,27 @@
       <c r="L60" s="10" t="n"/>
       <c r="M60" s="25">
         <f>IF(OR(E60="",F60="",G60=""),"",E60*F60*G60/1000000000*IF(H60="",1,H60))</f>
-        <v/>
       </c>
       <c r="N60" s="19">
         <f>IF(OR(E60="",F60=""),"",E60*F60/1000000*IF(H60="",1,H60))</f>
-        <v/>
       </c>
       <c r="O60" s="14">
         <f>IF(OR(E60="",F60=""),"",MAX(INT(LISTS!$F$6/(E60+LISTS!$F$8))*INT(LISTS!$F$7/(F60+LISTS!$F$8)),INT(LISTS!$F$6/(F60+LISTS!$F$8))*INT(LISTS!$F$7/(E60+LISTS!$F$8))))</f>
-        <v/>
       </c>
       <c r="P60" s="19">
         <f>IF(K60&lt;&gt;"",K60,IF(OR(O60="",O60=0),"",IF(H60="",1,H60)/O60))</f>
-        <v/>
       </c>
       <c r="Q60" s="36">
         <f>IF(OR(K60&lt;&gt;"",P60=""),"",1-(IF(H60="",1,H60)*E60*F60)/(ROUNDUP(P60,0)*LISTS!$F$6*LISTS!$F$7))</f>
-        <v/>
       </c>
       <c r="R60" s="14">
         <f>IF(AND(E60="",K60=""),"",IF(B60="","panel type?",IF(AND(K60="",O60=0),"panel bigger than sheet",IF(AND(G60&lt;&gt;"",IFERROR(VALUE(MID(B60,5,FIND("-",B60,5)-5)),0)&lt;&gt;G60),"T must match panel type",IF(I60="","exposed faces?","OK")))))</f>
-        <v/>
       </c>
       <c r="S60" s="12">
         <f t="array" ref="S60">IF(OR(B60="",P60=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B60,RATES!$A:$A,0)),"rate?"))</f>
-        <v/>
       </c>
       <c r="T60" s="12">
         <f>IF(ISNUMBER(S60),IF(K60&lt;&gt;"",K60,IF(Q60&gt;RATES!$C$97,P60*(1+RATES!$C$98),ROUNDUP(P60,0)))*S60,"")</f>
-        <v/>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="59"/>
@@ -21021,7 +19019,6 @@
       </c>
       <c r="T64" s="38">
         <f>IF(OR(H64="",S64=""),"",H64*S64)</f>
-        <v/>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="59">
@@ -21076,7 +19073,6 @@
       </c>
       <c r="T65" s="38">
         <f>IF(OR(H65="",S65=""),"",H65*S65)</f>
-        <v/>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="59">
@@ -21131,7 +19127,6 @@
       </c>
       <c r="T66" s="38">
         <f>IF(OR(H66="",S66=""),"",H66*S66)</f>
-        <v/>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="59">
@@ -21186,7 +19181,6 @@
       </c>
       <c r="T67" s="38">
         <f>IF(OR(H67="",S67=""),"",H67*S67)</f>
-        <v/>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="59">
@@ -21213,7 +19207,6 @@
       <c r="S68" s="37" t="n"/>
       <c r="T68" s="38">
         <f>IF(OR(H68="",S68=""),"",H68*S68)</f>
-        <v/>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="59">
@@ -21240,7 +19233,6 @@
       <c r="S69" s="37" t="n"/>
       <c r="T69" s="38">
         <f>IF(OR(H69="",S69=""),"",H69*S69)</f>
-        <v/>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="59">
@@ -21267,7 +19259,6 @@
       <c r="S70" s="37" t="n"/>
       <c r="T70" s="38">
         <f>IF(OR(H70="",S70=""),"",H70*S70)</f>
-        <v/>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="59">
@@ -21294,7 +19285,6 @@
       <c r="S71" s="37" t="n"/>
       <c r="T71" s="38">
         <f>IF(OR(H71="",S71=""),"",H71*S71)</f>
-        <v/>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="59">
@@ -21321,7 +19311,6 @@
       <c r="S72" s="37" t="n"/>
       <c r="T72" s="38">
         <f>IF(OR(H72="",S72=""),"",H72*S72)</f>
-        <v/>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="59">
@@ -21348,7 +19337,6 @@
       <c r="S73" s="37" t="n"/>
       <c r="T73" s="38">
         <f>IF(OR(H73="",S73=""),"",H73*S73)</f>
-        <v/>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="59">
@@ -21375,7 +19363,6 @@
       <c r="S74" s="37" t="n"/>
       <c r="T74" s="38">
         <f>IF(OR(H74="",S74=""),"",H74*S74)</f>
-        <v/>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="59">
@@ -21402,7 +19389,6 @@
       <c r="S75" s="37" t="n"/>
       <c r="T75" s="38">
         <f>IF(OR(H75="",S75=""),"",H75*S75)</f>
-        <v/>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="59">
@@ -21429,7 +19415,6 @@
       <c r="S76" s="37" t="n"/>
       <c r="T76" s="38">
         <f>IF(OR(H76="",S76=""),"",H76*S76)</f>
-        <v/>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="59">
@@ -21456,7 +19441,6 @@
       <c r="S77" s="37" t="n"/>
       <c r="T77" s="38">
         <f>IF(OR(H77="",S77=""),"",H77*S77)</f>
-        <v/>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="59">
@@ -21483,7 +19467,6 @@
       <c r="S78" s="37" t="n"/>
       <c r="T78" s="38">
         <f>IF(OR(H78="",S78=""),"",H78*S78)</f>
-        <v/>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="59"/>
@@ -21503,7 +19486,6 @@
       </c>
       <c r="D82" s="25">
         <f>SUM(M18:M42)</f>
-        <v/>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="59">
@@ -21514,7 +19496,6 @@
       </c>
       <c r="D83" s="17">
         <f>SUM(P46:P60)</f>
-        <v/>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="59">
@@ -21525,7 +19506,6 @@
       </c>
       <c r="D84" s="19">
         <f>SUMIF(I18:I42,"Y",N18:N42)+SUMIF(I46:I60,1,N46:N60)+2*SUMIF(I46:I60,2,N46:N60)</f>
-        <v/>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -21541,7 +19521,6 @@
       </c>
       <c r="D85" s="39">
         <f>G15</f>
-        <v/>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="59">
@@ -21552,7 +19531,6 @@
       </c>
       <c r="D86" s="19">
         <f>M15</f>
-        <v/>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="59">
@@ -21563,7 +19541,6 @@
       </c>
       <c r="D87" s="12">
         <f>SUM(T18:T42)</f>
-        <v/>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -21579,7 +19556,6 @@
       </c>
       <c r="D88" s="12">
         <f>D82*RATES!$C$46</f>
-        <v/>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -21595,7 +19571,6 @@
       </c>
       <c r="D89" s="12">
         <f>SUM(T46:T60)</f>
-        <v/>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -21611,7 +19586,6 @@
       </c>
       <c r="D90" s="12">
         <f>D84*RATES!$C$47*IF($C$5="NONE (RAW)",0,1)</f>
-        <v/>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -21627,7 +19601,6 @@
       </c>
       <c r="D91" s="12">
         <f>D84*RATES!$C$48*IF($C$5="NONE (RAW)",0,1)</f>
-        <v/>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -21643,7 +19616,6 @@
       </c>
       <c r="D92" s="12">
         <f>D84*RATES!$C$49*IF($C$5="NONE (RAW)",0,1)</f>
-        <v/>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -21659,7 +19631,6 @@
       </c>
       <c r="D93" s="12">
         <f>D84*RATES!$C$50*IF($C$5="NONE (RAW)",0,1)</f>
-        <v/>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -21675,7 +19646,6 @@
       </c>
       <c r="D94" s="12">
         <f>SUM(T64:T78)</f>
-        <v/>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -21691,7 +19661,6 @@
       </c>
       <c r="D95" s="12">
         <f>IF(L15=0,0,IF(L15&lt;RATES!$C$95,RATES!$C$53*G15,L15*RATES!$C$51*(1+IF(G15&gt;1,RATES!$C$96,0)))+M15*RATES!$C$52)</f>
-        <v/>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -21707,7 +19676,6 @@
       </c>
       <c r="D96" s="16">
         <f>SUM(D87:D95)</f>
-        <v/>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="59">
@@ -21718,7 +19686,6 @@
       </c>
       <c r="D97" s="12">
         <f>D96*RATES!$C$54</f>
-        <v/>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -21734,7 +19701,6 @@
       </c>
       <c r="D98" s="12">
         <f>(D96+D97)*RATES!$C$55</f>
-        <v/>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -21750,7 +19716,6 @@
       </c>
       <c r="D99" s="16">
         <f>D96+D97+D98</f>
-        <v/>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="59">
@@ -21761,7 +19726,6 @@
       </c>
       <c r="D100" s="19">
         <f>L15</f>
-        <v/>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="59">
@@ -21772,7 +19736,6 @@
       </c>
       <c r="D101" s="16">
         <f>IF(ISNUMBER(C4),C4,0)*D99</f>
-        <v/>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="59">
@@ -21783,7 +19746,6 @@
       </c>
       <c r="D102" s="40">
         <f>COUNTIF(R18:R42,"?*")-COUNTIF(R18:R42,"OK")+COUNTIF(R46:R60,"?*")-COUNTIF(R46:R60,"OK")+COUNTIF(S18:S60,"rate?")</f>
-        <v/>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -502,6 +502,9 @@
     </xf>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5536,7 +5539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T102"/>
+  <dimension ref="A1:U102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5" customWidth="1" style="59" min="1" max="1"/>
@@ -6006,6 +6009,12 @@
           <t>COST IDR (system)</t>
         </is>
       </c>
+      <c r="U17" s="90" t="inlineStr">
+        <is>
+          <t>COST USD
+(system)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -7012,6 +7021,12 @@
           <t>COST IDR (system)</t>
         </is>
       </c>
+      <c r="U45" s="90" t="inlineStr">
+        <is>
+          <t>COST USD
+(system)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="59">
       <c r="A46" s="9" t="n">
@@ -7044,7 +7059,7 @@
         <f>IF(OR(K46&lt;&gt;"",P46=""),"",1-(IF(H46="",1,H46)*E46*F46)/(ROUNDUP(P46,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R46" s="14">
-        <f>IF(AND(E46="",K46=""),"",IF(B46="","panel type?",IF(AND(K46="",O46=0),"panel bigger than sheet",IF(AND(G46&lt;&gt;"",IFERROR(VALUE(MID(B46,5,FIND("-",B46,5)-5)),0)&lt;&gt;G46),"T must match panel type",IF(I46="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E46="",K46=""),"",IF(B46="","panel type?",IF(AND(K46="",O46=0),"panel bigger than sheet",IF(AND(G46&lt;&gt;"",ISERROR(FIND("-"&amp;G46,B46))),"T must match panel type",IF(I46="","exposed faces?","OK")))))</f>
       </c>
       <c r="S46" s="12">
         <f t="array" ref="S46">IF(OR(B46="",P46=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B46,RATES!$A:$A,0)),"rate?"))</f>
@@ -7084,7 +7099,7 @@
         <f>IF(OR(K47&lt;&gt;"",P47=""),"",1-(IF(H47="",1,H47)*E47*F47)/(ROUNDUP(P47,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R47" s="14">
-        <f>IF(AND(E47="",K47=""),"",IF(B47="","panel type?",IF(AND(K47="",O47=0),"panel bigger than sheet",IF(AND(G47&lt;&gt;"",IFERROR(VALUE(MID(B47,5,FIND("-",B47,5)-5)),0)&lt;&gt;G47),"T must match panel type",IF(I47="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E47="",K47=""),"",IF(B47="","panel type?",IF(AND(K47="",O47=0),"panel bigger than sheet",IF(AND(G47&lt;&gt;"",ISERROR(FIND("-"&amp;G47,B47))),"T must match panel type",IF(I47="","exposed faces?","OK")))))</f>
       </c>
       <c r="S47" s="12">
         <f t="array" ref="S47">IF(OR(B47="",P47=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B47,RATES!$A:$A,0)),"rate?"))</f>
@@ -7124,7 +7139,7 @@
         <f>IF(OR(K48&lt;&gt;"",P48=""),"",1-(IF(H48="",1,H48)*E48*F48)/(ROUNDUP(P48,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R48" s="14">
-        <f>IF(AND(E48="",K48=""),"",IF(B48="","panel type?",IF(AND(K48="",O48=0),"panel bigger than sheet",IF(AND(G48&lt;&gt;"",IFERROR(VALUE(MID(B48,5,FIND("-",B48,5)-5)),0)&lt;&gt;G48),"T must match panel type",IF(I48="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E48="",K48=""),"",IF(B48="","panel type?",IF(AND(K48="",O48=0),"panel bigger than sheet",IF(AND(G48&lt;&gt;"",ISERROR(FIND("-"&amp;G48,B48))),"T must match panel type",IF(I48="","exposed faces?","OK")))))</f>
       </c>
       <c r="S48" s="12">
         <f t="array" ref="S48">IF(OR(B48="",P48=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B48,RATES!$A:$A,0)),"rate?"))</f>
@@ -7164,7 +7179,7 @@
         <f>IF(OR(K49&lt;&gt;"",P49=""),"",1-(IF(H49="",1,H49)*E49*F49)/(ROUNDUP(P49,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R49" s="14">
-        <f>IF(AND(E49="",K49=""),"",IF(B49="","panel type?",IF(AND(K49="",O49=0),"panel bigger than sheet",IF(AND(G49&lt;&gt;"",IFERROR(VALUE(MID(B49,5,FIND("-",B49,5)-5)),0)&lt;&gt;G49),"T must match panel type",IF(I49="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E49="",K49=""),"",IF(B49="","panel type?",IF(AND(K49="",O49=0),"panel bigger than sheet",IF(AND(G49&lt;&gt;"",ISERROR(FIND("-"&amp;G49,B49))),"T must match panel type",IF(I49="","exposed faces?","OK")))))</f>
       </c>
       <c r="S49" s="12">
         <f t="array" ref="S49">IF(OR(B49="",P49=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B49,RATES!$A:$A,0)),"rate?"))</f>
@@ -7204,7 +7219,7 @@
         <f>IF(OR(K50&lt;&gt;"",P50=""),"",1-(IF(H50="",1,H50)*E50*F50)/(ROUNDUP(P50,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R50" s="14">
-        <f>IF(AND(E50="",K50=""),"",IF(B50="","panel type?",IF(AND(K50="",O50=0),"panel bigger than sheet",IF(AND(G50&lt;&gt;"",IFERROR(VALUE(MID(B50,5,FIND("-",B50,5)-5)),0)&lt;&gt;G50),"T must match panel type",IF(I50="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E50="",K50=""),"",IF(B50="","panel type?",IF(AND(K50="",O50=0),"panel bigger than sheet",IF(AND(G50&lt;&gt;"",ISERROR(FIND("-"&amp;G50,B50))),"T must match panel type",IF(I50="","exposed faces?","OK")))))</f>
       </c>
       <c r="S50" s="12">
         <f t="array" ref="S50">IF(OR(B50="",P50=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B50,RATES!$A:$A,0)),"rate?"))</f>
@@ -7244,7 +7259,7 @@
         <f>IF(OR(K51&lt;&gt;"",P51=""),"",1-(IF(H51="",1,H51)*E51*F51)/(ROUNDUP(P51,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R51" s="14">
-        <f>IF(AND(E51="",K51=""),"",IF(B51="","panel type?",IF(AND(K51="",O51=0),"panel bigger than sheet",IF(AND(G51&lt;&gt;"",IFERROR(VALUE(MID(B51,5,FIND("-",B51,5)-5)),0)&lt;&gt;G51),"T must match panel type",IF(I51="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E51="",K51=""),"",IF(B51="","panel type?",IF(AND(K51="",O51=0),"panel bigger than sheet",IF(AND(G51&lt;&gt;"",ISERROR(FIND("-"&amp;G51,B51))),"T must match panel type",IF(I51="","exposed faces?","OK")))))</f>
       </c>
       <c r="S51" s="12">
         <f t="array" ref="S51">IF(OR(B51="",P51=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B51,RATES!$A:$A,0)),"rate?"))</f>
@@ -7284,7 +7299,7 @@
         <f>IF(OR(K52&lt;&gt;"",P52=""),"",1-(IF(H52="",1,H52)*E52*F52)/(ROUNDUP(P52,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R52" s="14">
-        <f>IF(AND(E52="",K52=""),"",IF(B52="","panel type?",IF(AND(K52="",O52=0),"panel bigger than sheet",IF(AND(G52&lt;&gt;"",IFERROR(VALUE(MID(B52,5,FIND("-",B52,5)-5)),0)&lt;&gt;G52),"T must match panel type",IF(I52="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E52="",K52=""),"",IF(B52="","panel type?",IF(AND(K52="",O52=0),"panel bigger than sheet",IF(AND(G52&lt;&gt;"",ISERROR(FIND("-"&amp;G52,B52))),"T must match panel type",IF(I52="","exposed faces?","OK")))))</f>
       </c>
       <c r="S52" s="12">
         <f t="array" ref="S52">IF(OR(B52="",P52=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B52,RATES!$A:$A,0)),"rate?"))</f>
@@ -7324,7 +7339,7 @@
         <f>IF(OR(K53&lt;&gt;"",P53=""),"",1-(IF(H53="",1,H53)*E53*F53)/(ROUNDUP(P53,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R53" s="14">
-        <f>IF(AND(E53="",K53=""),"",IF(B53="","panel type?",IF(AND(K53="",O53=0),"panel bigger than sheet",IF(AND(G53&lt;&gt;"",IFERROR(VALUE(MID(B53,5,FIND("-",B53,5)-5)),0)&lt;&gt;G53),"T must match panel type",IF(I53="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E53="",K53=""),"",IF(B53="","panel type?",IF(AND(K53="",O53=0),"panel bigger than sheet",IF(AND(G53&lt;&gt;"",ISERROR(FIND("-"&amp;G53,B53))),"T must match panel type",IF(I53="","exposed faces?","OK")))))</f>
       </c>
       <c r="S53" s="12">
         <f t="array" ref="S53">IF(OR(B53="",P53=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B53,RATES!$A:$A,0)),"rate?"))</f>
@@ -7364,7 +7379,7 @@
         <f>IF(OR(K54&lt;&gt;"",P54=""),"",1-(IF(H54="",1,H54)*E54*F54)/(ROUNDUP(P54,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R54" s="14">
-        <f>IF(AND(E54="",K54=""),"",IF(B54="","panel type?",IF(AND(K54="",O54=0),"panel bigger than sheet",IF(AND(G54&lt;&gt;"",IFERROR(VALUE(MID(B54,5,FIND("-",B54,5)-5)),0)&lt;&gt;G54),"T must match panel type",IF(I54="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E54="",K54=""),"",IF(B54="","panel type?",IF(AND(K54="",O54=0),"panel bigger than sheet",IF(AND(G54&lt;&gt;"",ISERROR(FIND("-"&amp;G54,B54))),"T must match panel type",IF(I54="","exposed faces?","OK")))))</f>
       </c>
       <c r="S54" s="12">
         <f t="array" ref="S54">IF(OR(B54="",P54=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B54,RATES!$A:$A,0)),"rate?"))</f>
@@ -7404,7 +7419,7 @@
         <f>IF(OR(K55&lt;&gt;"",P55=""),"",1-(IF(H55="",1,H55)*E55*F55)/(ROUNDUP(P55,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R55" s="14">
-        <f>IF(AND(E55="",K55=""),"",IF(B55="","panel type?",IF(AND(K55="",O55=0),"panel bigger than sheet",IF(AND(G55&lt;&gt;"",IFERROR(VALUE(MID(B55,5,FIND("-",B55,5)-5)),0)&lt;&gt;G55),"T must match panel type",IF(I55="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E55="",K55=""),"",IF(B55="","panel type?",IF(AND(K55="",O55=0),"panel bigger than sheet",IF(AND(G55&lt;&gt;"",ISERROR(FIND("-"&amp;G55,B55))),"T must match panel type",IF(I55="","exposed faces?","OK")))))</f>
       </c>
       <c r="S55" s="12">
         <f t="array" ref="S55">IF(OR(B55="",P55=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B55,RATES!$A:$A,0)),"rate?"))</f>
@@ -7444,7 +7459,7 @@
         <f>IF(OR(K56&lt;&gt;"",P56=""),"",1-(IF(H56="",1,H56)*E56*F56)/(ROUNDUP(P56,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R56" s="14">
-        <f>IF(AND(E56="",K56=""),"",IF(B56="","panel type?",IF(AND(K56="",O56=0),"panel bigger than sheet",IF(AND(G56&lt;&gt;"",IFERROR(VALUE(MID(B56,5,FIND("-",B56,5)-5)),0)&lt;&gt;G56),"T must match panel type",IF(I56="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E56="",K56=""),"",IF(B56="","panel type?",IF(AND(K56="",O56=0),"panel bigger than sheet",IF(AND(G56&lt;&gt;"",ISERROR(FIND("-"&amp;G56,B56))),"T must match panel type",IF(I56="","exposed faces?","OK")))))</f>
       </c>
       <c r="S56" s="12">
         <f t="array" ref="S56">IF(OR(B56="",P56=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B56,RATES!$A:$A,0)),"rate?"))</f>
@@ -7484,7 +7499,7 @@
         <f>IF(OR(K57&lt;&gt;"",P57=""),"",1-(IF(H57="",1,H57)*E57*F57)/(ROUNDUP(P57,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R57" s="14">
-        <f>IF(AND(E57="",K57=""),"",IF(B57="","panel type?",IF(AND(K57="",O57=0),"panel bigger than sheet",IF(AND(G57&lt;&gt;"",IFERROR(VALUE(MID(B57,5,FIND("-",B57,5)-5)),0)&lt;&gt;G57),"T must match panel type",IF(I57="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E57="",K57=""),"",IF(B57="","panel type?",IF(AND(K57="",O57=0),"panel bigger than sheet",IF(AND(G57&lt;&gt;"",ISERROR(FIND("-"&amp;G57,B57))),"T must match panel type",IF(I57="","exposed faces?","OK")))))</f>
       </c>
       <c r="S57" s="12">
         <f t="array" ref="S57">IF(OR(B57="",P57=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B57,RATES!$A:$A,0)),"rate?"))</f>
@@ -7524,7 +7539,7 @@
         <f>IF(OR(K58&lt;&gt;"",P58=""),"",1-(IF(H58="",1,H58)*E58*F58)/(ROUNDUP(P58,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R58" s="14">
-        <f>IF(AND(E58="",K58=""),"",IF(B58="","panel type?",IF(AND(K58="",O58=0),"panel bigger than sheet",IF(AND(G58&lt;&gt;"",IFERROR(VALUE(MID(B58,5,FIND("-",B58,5)-5)),0)&lt;&gt;G58),"T must match panel type",IF(I58="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E58="",K58=""),"",IF(B58="","panel type?",IF(AND(K58="",O58=0),"panel bigger than sheet",IF(AND(G58&lt;&gt;"",ISERROR(FIND("-"&amp;G58,B58))),"T must match panel type",IF(I58="","exposed faces?","OK")))))</f>
       </c>
       <c r="S58" s="12">
         <f t="array" ref="S58">IF(OR(B58="",P58=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B58,RATES!$A:$A,0)),"rate?"))</f>
@@ -7564,7 +7579,7 @@
         <f>IF(OR(K59&lt;&gt;"",P59=""),"",1-(IF(H59="",1,H59)*E59*F59)/(ROUNDUP(P59,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R59" s="14">
-        <f>IF(AND(E59="",K59=""),"",IF(B59="","panel type?",IF(AND(K59="",O59=0),"panel bigger than sheet",IF(AND(G59&lt;&gt;"",IFERROR(VALUE(MID(B59,5,FIND("-",B59,5)-5)),0)&lt;&gt;G59),"T must match panel type",IF(I59="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E59="",K59=""),"",IF(B59="","panel type?",IF(AND(K59="",O59=0),"panel bigger than sheet",IF(AND(G59&lt;&gt;"",ISERROR(FIND("-"&amp;G59,B59))),"T must match panel type",IF(I59="","exposed faces?","OK")))))</f>
       </c>
       <c r="S59" s="12">
         <f t="array" ref="S59">IF(OR(B59="",P59=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B59,RATES!$A:$A,0)),"rate?"))</f>
@@ -7604,7 +7619,7 @@
         <f>IF(OR(K60&lt;&gt;"",P60=""),"",1-(IF(H60="",1,H60)*E60*F60)/(ROUNDUP(P60,0)*LISTS!$F$6*LISTS!$F$7))</f>
       </c>
       <c r="R60" s="14">
-        <f>IF(AND(E60="",K60=""),"",IF(B60="","panel type?",IF(AND(K60="",O60=0),"panel bigger than sheet",IF(AND(G60&lt;&gt;"",IFERROR(VALUE(MID(B60,5,FIND("-",B60,5)-5)),0)&lt;&gt;G60),"T must match panel type",IF(I60="","exposed faces?","OK")))))</f>
+        <f>IF(AND(E60="",K60=""),"",IF(B60="","panel type?",IF(AND(K60="",O60=0),"panel bigger than sheet",IF(AND(G60&lt;&gt;"",ISERROR(FIND("-"&amp;G60,B60))),"T must match panel type",IF(I60="","exposed faces?","OK")))))</f>
       </c>
       <c r="S60" s="12">
         <f t="array" ref="S60">IF(OR(B60="",P60=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B60,RATES!$A:$A,0)),"rate?"))</f>
@@ -7680,6 +7695,11 @@
       <c r="T63" s="8" t="inlineStr">
         <is>
           <t>LINE TOTAL (calc)</t>
+        </is>
+      </c>
+      <c r="U63" s="90" t="inlineStr">
+        <is>
+          <t>LINE TOTAL USD</t>
         </is>
       </c>
     </row>
@@ -8079,6 +8099,11 @@
       <c r="A81" s="5" t="inlineStr">
         <is>
           <t>SUMMARY (system): cost per ONE item, from the RATES tab. Do not type here.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>COST USD (system)</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J229"/>
+  <dimension ref="A1:J249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10101,12 +10126,10 @@
           <t>Carpentry labour per m³ of component (inside every tier rate)</t>
         </is>
       </c>
-      <c r="C34" s="81">
-        <f>$C$10*(1-$C$11)/$C$12</f>
-      </c>
-      <c r="D34" s="81" t="n">
+      <c r="C34" s="81" t="n">
         <v>4000000</v>
       </c>
+      <c r="D34" s="81" t="n"/>
       <c r="E34" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10129,12 +10152,10 @@
           <t>Teak tier A</t>
         </is>
       </c>
-      <c r="C35" s="81">
-        <f>($C$6+$C$9)*$C$13+$C$34</f>
-      </c>
-      <c r="D35" s="81">
-        <f>C35*0.9</f>
-      </c>
+      <c r="C35" s="81" t="n">
+        <v>27507965.09</v>
+      </c>
+      <c r="D35" s="81" t="n"/>
       <c r="E35" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10157,12 +10178,10 @@
           <t>Teak tier A-CURVED</t>
         </is>
       </c>
-      <c r="C36" s="81">
-        <f>($C$6+$C$9)*$C$14+$C$34</f>
-      </c>
-      <c r="D36" s="81">
-        <f>C36*0.9</f>
-      </c>
+      <c r="C36" s="81" t="n">
+        <v>34040953.31</v>
+      </c>
+      <c r="D36" s="81" t="n"/>
       <c r="E36" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10180,12 +10199,10 @@
           <t>Teak tier B</t>
         </is>
       </c>
-      <c r="C37" s="81">
-        <f>($C$6+$C$9)*$C$15+$C$34</f>
-      </c>
-      <c r="D37" s="81">
-        <f>C37*0.9</f>
-      </c>
+      <c r="C37" s="81" t="n">
+        <v>21568884.89</v>
+      </c>
+      <c r="D37" s="81" t="n"/>
       <c r="E37" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10203,12 +10220,10 @@
           <t>Teak tier C</t>
         </is>
       </c>
-      <c r="C38" s="81">
-        <f>($C$6+$C$9)*$C$16+$C$34</f>
-      </c>
-      <c r="D38" s="81">
-        <f>C38*0.9</f>
-      </c>
+      <c r="C38" s="81" t="n">
+        <v>18599344.79</v>
+      </c>
+      <c r="D38" s="81" t="n"/>
       <c r="E38" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10226,12 +10241,10 @@
           <t>Teak tier D</t>
         </is>
       </c>
-      <c r="C39" s="81">
-        <f>($C$6+$C$9)*$C$17+$C$34</f>
-      </c>
-      <c r="D39" s="81">
-        <f>C39*0.9</f>
-      </c>
+      <c r="C39" s="81" t="n">
+        <v>15629804.69</v>
+      </c>
+      <c r="D39" s="81" t="n"/>
       <c r="E39" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10249,12 +10262,10 @@
           <t>Mindi tier A</t>
         </is>
       </c>
-      <c r="C40" s="81">
-        <f>($C$7+$C$9)*$C$13+$C$34</f>
-      </c>
-      <c r="D40" s="81">
-        <f>C40*0.9</f>
-      </c>
+      <c r="C40" s="81" t="n">
+        <v>18057965.09</v>
+      </c>
+      <c r="D40" s="81" t="n"/>
       <c r="E40" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10272,12 +10283,10 @@
           <t>Mindi tier A-CURVED</t>
         </is>
       </c>
-      <c r="C41" s="81">
-        <f>($C$7+$C$9)*$C$14+$C$34</f>
-      </c>
-      <c r="D41" s="81">
-        <f>C41*0.9</f>
-      </c>
+      <c r="C41" s="81" t="n">
+        <v>21620953.31</v>
+      </c>
+      <c r="D41" s="81" t="n"/>
       <c r="E41" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10295,12 +10304,10 @@
           <t>Mindi tier B</t>
         </is>
       </c>
-      <c r="C42" s="81">
-        <f>($C$7+$C$9)*$C$15+$C$34</f>
-      </c>
-      <c r="D42" s="81">
-        <f>C42*0.9</f>
-      </c>
+      <c r="C42" s="81" t="n">
+        <v>14818884.89</v>
+      </c>
+      <c r="D42" s="81" t="n"/>
       <c r="E42" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10318,12 +10325,10 @@
           <t>Mindi tier C</t>
         </is>
       </c>
-      <c r="C43" s="81">
-        <f>($C$7+$C$9)*$C$16+$C$34</f>
-      </c>
-      <c r="D43" s="81">
-        <f>C43*0.9</f>
-      </c>
+      <c r="C43" s="81" t="n">
+        <v>13199344.79</v>
+      </c>
+      <c r="D43" s="81" t="n"/>
       <c r="E43" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10341,12 +10346,10 @@
           <t>Mindi tier D</t>
         </is>
       </c>
-      <c r="C44" s="81">
-        <f>($C$7+$C$9)*$C$17+$C$34</f>
-      </c>
-      <c r="D44" s="81">
-        <f>C44*0.9</f>
-      </c>
+      <c r="C44" s="81" t="n">
+        <v>11579804.69</v>
+      </c>
+      <c r="D44" s="81" t="n"/>
       <c r="E44" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10364,12 +10367,10 @@
           <t>Meranti, any tier</t>
         </is>
       </c>
-      <c r="C45" s="81">
-        <f>$C$8*$C$18+$C$34</f>
-      </c>
-      <c r="D45" s="81">
-        <f>C45*0.9</f>
-      </c>
+      <c r="C45" s="81" t="n">
+        <v>18196184.39</v>
+      </c>
+      <c r="D45" s="81" t="n"/>
       <c r="E45" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10392,12 +10393,10 @@
           <t>Screws, nails, dowels, glue per m³ of component</t>
         </is>
       </c>
-      <c r="C46" s="81">
-        <f>$C$19/$C$12</f>
-      </c>
-      <c r="D46" s="81" t="n">
+      <c r="C46" s="81" t="n">
         <v>1000000</v>
       </c>
+      <c r="D46" s="81" t="n"/>
       <c r="E46" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10415,12 +10414,10 @@
           <t>Finishing materials (Zhanchen + thinner) per m² exposed</t>
         </is>
       </c>
-      <c r="C47" s="81">
-        <f>$C$20/$C$25</f>
-      </c>
-      <c r="D47" s="81" t="n">
+      <c r="C47" s="81" t="n">
         <v>37000</v>
       </c>
+      <c r="D47" s="81" t="n"/>
       <c r="E47" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
@@ -10438,12 +10435,10 @@
           <t>Sanding materials (abrasives) per m² exposed</t>
         </is>
       </c>
-      <c r="C48" s="81">
-        <f>$C$21/$C$25</f>
-      </c>
-      <c r="D48" s="81">
-        <f>C48*0.8</f>
-      </c>
+      <c r="C48" s="81" t="n">
+        <v>10235.64174</v>
+      </c>
+      <c r="D48" s="81" t="n"/>
       <c r="E48" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
@@ -10461,12 +10456,10 @@
           <t>Sanding labour (65% of sanding pool) per m² exposed</t>
         </is>
       </c>
-      <c r="C49" s="81">
-        <f>$C$23*$C$24/$C$25</f>
-      </c>
-      <c r="D49" s="81" t="n">
+      <c r="C49" s="81" t="n">
         <v>20000</v>
       </c>
+      <c r="D49" s="81" t="n"/>
       <c r="E49" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
@@ -10484,12 +10477,10 @@
           <t>Finishing labour (finishing pool) per m² exposed</t>
         </is>
       </c>
-      <c r="C50" s="81">
-        <f>$C$22/$C$25</f>
-      </c>
-      <c r="D50" s="81" t="n">
+      <c r="C50" s="81" t="n">
         <v>45000</v>
       </c>
+      <c r="D50" s="81" t="n"/>
       <c r="E50" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
@@ -10508,11 +10499,9 @@
         </is>
       </c>
       <c r="C51" s="80" t="n">
-        <v>42000</v>
-      </c>
-      <c r="D51" s="80" t="n">
         <v>40000</v>
       </c>
+      <c r="D51" s="80" t="n"/>
       <c r="E51" s="74" t="inlineStr">
         <is>
           <t>IDR/m²</t>
@@ -10536,11 +10525,9 @@
         </is>
       </c>
       <c r="C52" s="80" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D52" s="80" t="n">
         <v>50000</v>
       </c>
+      <c r="D52" s="80" t="n"/>
       <c r="E52" s="74" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -10665,12 +10652,10 @@
           <t>Mindi veneer added cost per face</t>
         </is>
       </c>
-      <c r="C58" s="81">
-        <f>$C$30*$C$31+$C$28*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
-      </c>
-      <c r="D58" s="81" t="n">
+      <c r="C58" s="81" t="n">
         <v>18000</v>
       </c>
+      <c r="D58" s="81" t="n"/>
       <c r="E58" s="74" t="inlineStr">
         <is>
           <t>m2</t>
@@ -12945,6 +12930,7 @@
         </is>
       </c>
     </row>
+    <row r="169"/>
     <row r="170">
       <c r="A170" s="84" t="inlineStr">
         <is>
@@ -13126,6 +13112,7 @@
         </is>
       </c>
     </row>
+    <row r="177"/>
     <row r="178">
       <c r="A178" s="79" t="inlineStr">
         <is>
@@ -14532,6 +14519,7 @@
         <v>933</v>
       </c>
     </row>
+    <row r="216"/>
     <row r="217">
       <c r="A217" s="84" t="inlineStr">
         <is>
@@ -14787,6 +14775,7 @@
         <f>G225*$C$172</f>
       </c>
     </row>
+    <row r="226"/>
     <row r="227">
       <c r="A227" s="84" t="inlineStr">
         <is>
@@ -14864,6 +14853,374 @@
       </c>
       <c r="H229" s="83">
         <f>G229*$C$172</f>
+      </c>
+    </row>
+    <row r="230"/>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>VENEERED LANDED BOARDS (E2 + Mindi Veneer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MSF</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Plywood E2 18 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C232">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-18",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MDF</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Plywood E2 18 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C233">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-18",$A$178:$A$215,0))+2*$C$175</f>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MSF</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Plywood E2 15 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C234">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-15",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MDF</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Plywood E2 15 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C235">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-15",$A$178:$A$215,0))+2*$C$175</f>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MSF</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Plywood E2 12 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C236">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-12",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MDF</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Plywood E2 12 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C237">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-12",$A$178:$A$215,0))+2*$C$175</f>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MSF</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Plywood E2 9 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C238">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-9",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MDF</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Plywood E2 9 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C239">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-9",$A$178:$A$215,0))+2*$C$175</f>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MSF</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Plywood E2 6 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C240">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-6",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MDF</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Plywood E2 6 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C241">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-6",$A$178:$A$215,0))+2*$C$175</f>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MSF</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Plywood E2 3 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C242">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-3",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MDF</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Plywood E2 3 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C243">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-3",$A$178:$A$215,0))+2*$C$175</f>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MSF</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>MDF E2 18 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C244">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-18",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MDF</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>MDF E2 18 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C245">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-18",$A$178:$A$215,0))+2*$C$175</f>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-15-MSF</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>MDF E2 15 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C246">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-15",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-12-MSF</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>MDF E2 12 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C247">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-12",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-9-MSF</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>MDF E2 9 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C248">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-9",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-6-MSF</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>MDF E2 6 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C249">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-6",$A$178:$A$215,0))+$C$175</f>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -506,6 +506,7 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2298,36 +2299,47 @@
       </c>
       <c r="J6" s="11">
         <f>IF($C6="","",IF(ISERROR(INDIRECT("'"&amp;$C6&amp;"'!C1")),"no tab yet",IF(N(Y6)+N(AA6)=0,"tab empty",IF(N(T6)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D87")+INDIRECT("'"&amp;$C6&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C6&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P6" s="12">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D97")+INDIRECT("'"&amp;$C6&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q6" s="16">
         <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R6" s="12">
         <f>IF(AND(ISNUMBER(H6),ISNUMBER(Q6)),H6*Q6,"")</f>
+        <v/>
       </c>
       <c r="S6" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T6" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U6" s="10" t="n"/>
       <c r="V6" s="10" t="n"/>
@@ -2335,12 +2347,15 @@
       <c r="X6" s="10" t="n"/>
       <c r="Y6" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z6" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA6" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D89")+INDIRECT("'"&amp;$C6&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -3022,36 +3037,47 @@
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="11">
         <f>IF($C30="","",IF(ISERROR(INDIRECT("'"&amp;$C30&amp;"'!C1")),"no tab yet",IF(N(Y30)+N(AA30)=0,"tab empty",IF(N(T30)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D87")+INDIRECT("'"&amp;$C30&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C30&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P30" s="12">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D97")+INDIRECT("'"&amp;$C30&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q30" s="16">
         <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R30" s="12">
         <f>IF(AND(ISNUMBER(H30),ISNUMBER(Q30)),H30*Q30,"")</f>
+        <v/>
       </c>
       <c r="S30" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T30" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U30" s="10" t="n"/>
       <c r="V30" s="10" t="n"/>
@@ -3059,12 +3085,15 @@
       <c r="X30" s="10" t="n"/>
       <c r="Y30" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z30" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA30" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D89")+INDIRECT("'"&amp;$C30&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="59">
@@ -3079,36 +3108,47 @@
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="11">
         <f>IF($C31="","",IF(ISERROR(INDIRECT("'"&amp;$C31&amp;"'!C1")),"no tab yet",IF(N(Y31)+N(AA31)=0,"tab empty",IF(N(T31)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D87")+INDIRECT("'"&amp;$C31&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C31&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P31" s="12">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D97")+INDIRECT("'"&amp;$C31&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q31" s="16">
         <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R31" s="12">
         <f>IF(AND(ISNUMBER(H31),ISNUMBER(Q31)),H31*Q31,"")</f>
+        <v/>
       </c>
       <c r="S31" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T31" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U31" s="10" t="n"/>
       <c r="V31" s="10" t="n"/>
@@ -3116,12 +3156,15 @@
       <c r="X31" s="10" t="n"/>
       <c r="Y31" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z31" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA31" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D89")+INDIRECT("'"&amp;$C31&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="59">
@@ -3136,36 +3179,47 @@
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="11">
         <f>IF($C32="","",IF(ISERROR(INDIRECT("'"&amp;$C32&amp;"'!C1")),"no tab yet",IF(N(Y32)+N(AA32)=0,"tab empty",IF(N(T32)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D87")+INDIRECT("'"&amp;$C32&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C32&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P32" s="12">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D97")+INDIRECT("'"&amp;$C32&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q32" s="16">
         <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R32" s="12">
         <f>IF(AND(ISNUMBER(H32),ISNUMBER(Q32)),H32*Q32,"")</f>
+        <v/>
       </c>
       <c r="S32" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T32" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
@@ -3173,12 +3227,15 @@
       <c r="X32" s="10" t="n"/>
       <c r="Y32" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z32" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA32" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D89")+INDIRECT("'"&amp;$C32&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="59">
@@ -3193,36 +3250,47 @@
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="11">
         <f>IF($C33="","",IF(ISERROR(INDIRECT("'"&amp;$C33&amp;"'!C1")),"no tab yet",IF(N(Y33)+N(AA33)=0,"tab empty",IF(N(T33)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D87")+INDIRECT("'"&amp;$C33&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C33&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P33" s="12">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D97")+INDIRECT("'"&amp;$C33&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q33" s="16">
         <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R33" s="12">
         <f>IF(AND(ISNUMBER(H33),ISNUMBER(Q33)),H33*Q33,"")</f>
+        <v/>
       </c>
       <c r="S33" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T33" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U33" s="10" t="n"/>
       <c r="V33" s="10" t="n"/>
@@ -3230,12 +3298,15 @@
       <c r="X33" s="10" t="n"/>
       <c r="Y33" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z33" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA33" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D89")+INDIRECT("'"&amp;$C33&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="59">
@@ -3250,36 +3321,47 @@
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="11">
         <f>IF($C34="","",IF(ISERROR(INDIRECT("'"&amp;$C34&amp;"'!C1")),"no tab yet",IF(N(Y34)+N(AA34)=0,"tab empty",IF(N(T34)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D87")+INDIRECT("'"&amp;$C34&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C34&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P34" s="12">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D97")+INDIRECT("'"&amp;$C34&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q34" s="16">
         <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R34" s="12">
         <f>IF(AND(ISNUMBER(H34),ISNUMBER(Q34)),H34*Q34,"")</f>
+        <v/>
       </c>
       <c r="S34" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T34" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
@@ -3287,12 +3369,15 @@
       <c r="X34" s="10" t="n"/>
       <c r="Y34" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z34" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA34" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D89")+INDIRECT("'"&amp;$C34&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="59">
@@ -3307,36 +3392,47 @@
       <c r="I35" s="10" t="n"/>
       <c r="J35" s="11">
         <f>IF($C35="","",IF(ISERROR(INDIRECT("'"&amp;$C35&amp;"'!C1")),"no tab yet",IF(N(Y35)+N(AA35)=0,"tab empty",IF(N(T35)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D87")+INDIRECT("'"&amp;$C35&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C35&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P35" s="12">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D97")+INDIRECT("'"&amp;$C35&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q35" s="16">
         <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R35" s="12">
         <f>IF(AND(ISNUMBER(H35),ISNUMBER(Q35)),H35*Q35,"")</f>
+        <v/>
       </c>
       <c r="S35" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T35" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U35" s="10" t="n"/>
       <c r="V35" s="10" t="n"/>
@@ -3344,12 +3440,15 @@
       <c r="X35" s="10" t="n"/>
       <c r="Y35" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z35" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA35" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D89")+INDIRECT("'"&amp;$C35&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="59">
@@ -3364,36 +3463,47 @@
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="11">
         <f>IF($C36="","",IF(ISERROR(INDIRECT("'"&amp;$C36&amp;"'!C1")),"no tab yet",IF(N(Y36)+N(AA36)=0,"tab empty",IF(N(T36)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D87")+INDIRECT("'"&amp;$C36&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C36&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P36" s="12">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D97")+INDIRECT("'"&amp;$C36&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q36" s="16">
         <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R36" s="12">
         <f>IF(AND(ISNUMBER(H36),ISNUMBER(Q36)),H36*Q36,"")</f>
+        <v/>
       </c>
       <c r="S36" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T36" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
@@ -3401,12 +3511,15 @@
       <c r="X36" s="10" t="n"/>
       <c r="Y36" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z36" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA36" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D89")+INDIRECT("'"&amp;$C36&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="59">
@@ -3421,36 +3534,47 @@
       <c r="I37" s="10" t="n"/>
       <c r="J37" s="11">
         <f>IF($C37="","",IF(ISERROR(INDIRECT("'"&amp;$C37&amp;"'!C1")),"no tab yet",IF(N(Y37)+N(AA37)=0,"tab empty",IF(N(T37)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D87")+INDIRECT("'"&amp;$C37&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C37&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P37" s="12">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D97")+INDIRECT("'"&amp;$C37&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q37" s="16">
         <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R37" s="12">
         <f>IF(AND(ISNUMBER(H37),ISNUMBER(Q37)),H37*Q37,"")</f>
+        <v/>
       </c>
       <c r="S37" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T37" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U37" s="10" t="n"/>
       <c r="V37" s="10" t="n"/>
@@ -3458,12 +3582,15 @@
       <c r="X37" s="10" t="n"/>
       <c r="Y37" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z37" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA37" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D89")+INDIRECT("'"&amp;$C37&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="59">
@@ -3478,36 +3605,47 @@
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="11">
         <f>IF($C38="","",IF(ISERROR(INDIRECT("'"&amp;$C38&amp;"'!C1")),"no tab yet",IF(N(Y38)+N(AA38)=0,"tab empty",IF(N(T38)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D87")+INDIRECT("'"&amp;$C38&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C38&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P38" s="12">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D97")+INDIRECT("'"&amp;$C38&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q38" s="16">
         <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R38" s="12">
         <f>IF(AND(ISNUMBER(H38),ISNUMBER(Q38)),H38*Q38,"")</f>
+        <v/>
       </c>
       <c r="S38" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T38" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
@@ -3515,12 +3653,15 @@
       <c r="X38" s="10" t="n"/>
       <c r="Y38" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z38" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA38" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D89")+INDIRECT("'"&amp;$C38&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="59">
@@ -3535,36 +3676,47 @@
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="11">
         <f>IF($C39="","",IF(ISERROR(INDIRECT("'"&amp;$C39&amp;"'!C1")),"no tab yet",IF(N(Y39)+N(AA39)=0,"tab empty",IF(N(T39)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D87")+INDIRECT("'"&amp;$C39&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C39&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P39" s="12">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D97")+INDIRECT("'"&amp;$C39&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q39" s="16">
         <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R39" s="12">
         <f>IF(AND(ISNUMBER(H39),ISNUMBER(Q39)),H39*Q39,"")</f>
+        <v/>
       </c>
       <c r="S39" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T39" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
@@ -3572,12 +3724,15 @@
       <c r="X39" s="10" t="n"/>
       <c r="Y39" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z39" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA39" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D89")+INDIRECT("'"&amp;$C39&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="59">
@@ -3592,36 +3747,47 @@
       <c r="I40" s="10" t="n"/>
       <c r="J40" s="11">
         <f>IF($C40="","",IF(ISERROR(INDIRECT("'"&amp;$C40&amp;"'!C1")),"no tab yet",IF(N(Y40)+N(AA40)=0,"tab empty",IF(N(T40)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D87")+INDIRECT("'"&amp;$C40&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C40&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P40" s="12">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D97")+INDIRECT("'"&amp;$C40&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q40" s="16">
         <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R40" s="12">
         <f>IF(AND(ISNUMBER(H40),ISNUMBER(Q40)),H40*Q40,"")</f>
+        <v/>
       </c>
       <c r="S40" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T40" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U40" s="10" t="n"/>
       <c r="V40" s="10" t="n"/>
@@ -3629,12 +3795,15 @@
       <c r="X40" s="10" t="n"/>
       <c r="Y40" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z40" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA40" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D89")+INDIRECT("'"&amp;$C40&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="59">
@@ -3649,36 +3818,47 @@
       <c r="I41" s="10" t="n"/>
       <c r="J41" s="11">
         <f>IF($C41="","",IF(ISERROR(INDIRECT("'"&amp;$C41&amp;"'!C1")),"no tab yet",IF(N(Y41)+N(AA41)=0,"tab empty",IF(N(T41)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D87")+INDIRECT("'"&amp;$C41&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C41&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P41" s="12">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D97")+INDIRECT("'"&amp;$C41&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q41" s="16">
         <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R41" s="12">
         <f>IF(AND(ISNUMBER(H41),ISNUMBER(Q41)),H41*Q41,"")</f>
+        <v/>
       </c>
       <c r="S41" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T41" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U41" s="10" t="n"/>
       <c r="V41" s="10" t="n"/>
@@ -3686,12 +3866,15 @@
       <c r="X41" s="10" t="n"/>
       <c r="Y41" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z41" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA41" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D89")+INDIRECT("'"&amp;$C41&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="59">
@@ -3706,36 +3889,47 @@
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="11">
         <f>IF($C42="","",IF(ISERROR(INDIRECT("'"&amp;$C42&amp;"'!C1")),"no tab yet",IF(N(Y42)+N(AA42)=0,"tab empty",IF(N(T42)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D87")+INDIRECT("'"&amp;$C42&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C42&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P42" s="12">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D97")+INDIRECT("'"&amp;$C42&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q42" s="16">
         <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R42" s="12">
         <f>IF(AND(ISNUMBER(H42),ISNUMBER(Q42)),H42*Q42,"")</f>
+        <v/>
       </c>
       <c r="S42" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T42" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
@@ -3743,12 +3937,15 @@
       <c r="X42" s="10" t="n"/>
       <c r="Y42" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z42" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA42" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D89")+INDIRECT("'"&amp;$C42&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="59">
@@ -3763,36 +3960,47 @@
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="11">
         <f>IF($C43="","",IF(ISERROR(INDIRECT("'"&amp;$C43&amp;"'!C1")),"no tab yet",IF(N(Y43)+N(AA43)=0,"tab empty",IF(N(T43)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D87")+INDIRECT("'"&amp;$C43&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C43&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P43" s="12">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D97")+INDIRECT("'"&amp;$C43&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q43" s="16">
         <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R43" s="12">
         <f>IF(AND(ISNUMBER(H43),ISNUMBER(Q43)),H43*Q43,"")</f>
+        <v/>
       </c>
       <c r="S43" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T43" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
@@ -3800,12 +4008,15 @@
       <c r="X43" s="10" t="n"/>
       <c r="Y43" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z43" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA43" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D89")+INDIRECT("'"&amp;$C43&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="59">
@@ -3820,36 +4031,47 @@
       <c r="I44" s="10" t="n"/>
       <c r="J44" s="11">
         <f>IF($C44="","",IF(ISERROR(INDIRECT("'"&amp;$C44&amp;"'!C1")),"no tab yet",IF(N(Y44)+N(AA44)=0,"tab empty",IF(N(T44)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D87")+INDIRECT("'"&amp;$C44&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C44&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P44" s="12">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D97")+INDIRECT("'"&amp;$C44&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q44" s="16">
         <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R44" s="12">
         <f>IF(AND(ISNUMBER(H44),ISNUMBER(Q44)),H44*Q44,"")</f>
+        <v/>
       </c>
       <c r="S44" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T44" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U44" s="10" t="n"/>
       <c r="V44" s="10" t="n"/>
@@ -3857,12 +4079,15 @@
       <c r="X44" s="10" t="n"/>
       <c r="Y44" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z44" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA44" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D89")+INDIRECT("'"&amp;$C44&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="59">
@@ -3877,36 +4102,47 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="11">
         <f>IF($C45="","",IF(ISERROR(INDIRECT("'"&amp;$C45&amp;"'!C1")),"no tab yet",IF(N(Y45)+N(AA45)=0,"tab empty",IF(N(T45)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D87")+INDIRECT("'"&amp;$C45&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C45&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P45" s="12">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D97")+INDIRECT("'"&amp;$C45&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q45" s="16">
         <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R45" s="12">
         <f>IF(AND(ISNUMBER(H45),ISNUMBER(Q45)),H45*Q45,"")</f>
+        <v/>
       </c>
       <c r="S45" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T45" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
@@ -3914,12 +4150,15 @@
       <c r="X45" s="10" t="n"/>
       <c r="Y45" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z45" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA45" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D89")+INDIRECT("'"&amp;$C45&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="59">
@@ -3934,36 +4173,47 @@
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="11">
         <f>IF($C46="","",IF(ISERROR(INDIRECT("'"&amp;$C46&amp;"'!C1")),"no tab yet",IF(N(Y46)+N(AA46)=0,"tab empty",IF(N(T46)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D87")+INDIRECT("'"&amp;$C46&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C46&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P46" s="12">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D97")+INDIRECT("'"&amp;$C46&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q46" s="16">
         <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R46" s="12">
         <f>IF(AND(ISNUMBER(H46),ISNUMBER(Q46)),H46*Q46,"")</f>
+        <v/>
       </c>
       <c r="S46" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T46" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
@@ -3971,12 +4221,15 @@
       <c r="X46" s="10" t="n"/>
       <c r="Y46" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z46" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA46" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D89")+INDIRECT("'"&amp;$C46&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="59">
@@ -3991,36 +4244,47 @@
       <c r="I47" s="10" t="n"/>
       <c r="J47" s="11">
         <f>IF($C47="","",IF(ISERROR(INDIRECT("'"&amp;$C47&amp;"'!C1")),"no tab yet",IF(N(Y47)+N(AA47)=0,"tab empty",IF(N(T47)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D87")+INDIRECT("'"&amp;$C47&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C47&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P47" s="12">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D97")+INDIRECT("'"&amp;$C47&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q47" s="16">
         <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R47" s="12">
         <f>IF(AND(ISNUMBER(H47),ISNUMBER(Q47)),H47*Q47,"")</f>
+        <v/>
       </c>
       <c r="S47" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T47" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U47" s="10" t="n"/>
       <c r="V47" s="10" t="n"/>
@@ -4028,12 +4292,15 @@
       <c r="X47" s="10" t="n"/>
       <c r="Y47" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z47" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA47" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D89")+INDIRECT("'"&amp;$C47&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="59">
@@ -4048,36 +4315,47 @@
       <c r="I48" s="10" t="n"/>
       <c r="J48" s="11">
         <f>IF($C48="","",IF(ISERROR(INDIRECT("'"&amp;$C48&amp;"'!C1")),"no tab yet",IF(N(Y48)+N(AA48)=0,"tab empty",IF(N(T48)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D87")+INDIRECT("'"&amp;$C48&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C48&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P48" s="12">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D97")+INDIRECT("'"&amp;$C48&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q48" s="16">
         <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R48" s="12">
         <f>IF(AND(ISNUMBER(H48),ISNUMBER(Q48)),H48*Q48,"")</f>
+        <v/>
       </c>
       <c r="S48" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T48" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U48" s="10" t="n"/>
       <c r="V48" s="10" t="n"/>
@@ -4085,12 +4363,15 @@
       <c r="X48" s="10" t="n"/>
       <c r="Y48" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z48" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA48" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D89")+INDIRECT("'"&amp;$C48&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="59">
@@ -4105,36 +4386,47 @@
       <c r="I49" s="10" t="n"/>
       <c r="J49" s="11">
         <f>IF($C49="","",IF(ISERROR(INDIRECT("'"&amp;$C49&amp;"'!C1")),"no tab yet",IF(N(Y49)+N(AA49)=0,"tab empty",IF(N(T49)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D87")+INDIRECT("'"&amp;$C49&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C49&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P49" s="12">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D97")+INDIRECT("'"&amp;$C49&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q49" s="16">
         <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R49" s="12">
         <f>IF(AND(ISNUMBER(H49),ISNUMBER(Q49)),H49*Q49,"")</f>
+        <v/>
       </c>
       <c r="S49" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T49" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U49" s="10" t="n"/>
       <c r="V49" s="10" t="n"/>
@@ -4142,12 +4434,15 @@
       <c r="X49" s="10" t="n"/>
       <c r="Y49" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z49" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA49" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D89")+INDIRECT("'"&amp;$C49&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="59">
@@ -4162,36 +4457,47 @@
       <c r="I50" s="10" t="n"/>
       <c r="J50" s="11">
         <f>IF($C50="","",IF(ISERROR(INDIRECT("'"&amp;$C50&amp;"'!C1")),"no tab yet",IF(N(Y50)+N(AA50)=0,"tab empty",IF(N(T50)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D87")+INDIRECT("'"&amp;$C50&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C50&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P50" s="12">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D97")+INDIRECT("'"&amp;$C50&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q50" s="16">
         <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R50" s="12">
         <f>IF(AND(ISNUMBER(H50),ISNUMBER(Q50)),H50*Q50,"")</f>
+        <v/>
       </c>
       <c r="S50" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T50" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
@@ -4199,12 +4505,15 @@
       <c r="X50" s="10" t="n"/>
       <c r="Y50" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z50" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA50" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D89")+INDIRECT("'"&amp;$C50&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="59">
@@ -4219,36 +4528,47 @@
       <c r="I51" s="10" t="n"/>
       <c r="J51" s="11">
         <f>IF($C51="","",IF(ISERROR(INDIRECT("'"&amp;$C51&amp;"'!C1")),"no tab yet",IF(N(Y51)+N(AA51)=0,"tab empty",IF(N(T51)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D87")+INDIRECT("'"&amp;$C51&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C51&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P51" s="12">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D97")+INDIRECT("'"&amp;$C51&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q51" s="16">
         <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R51" s="12">
         <f>IF(AND(ISNUMBER(H51),ISNUMBER(Q51)),H51*Q51,"")</f>
+        <v/>
       </c>
       <c r="S51" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T51" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U51" s="10" t="n"/>
       <c r="V51" s="10" t="n"/>
@@ -4256,12 +4576,15 @@
       <c r="X51" s="10" t="n"/>
       <c r="Y51" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z51" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA51" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D89")+INDIRECT("'"&amp;$C51&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="59">
@@ -4276,36 +4599,47 @@
       <c r="I52" s="10" t="n"/>
       <c r="J52" s="11">
         <f>IF($C52="","",IF(ISERROR(INDIRECT("'"&amp;$C52&amp;"'!C1")),"no tab yet",IF(N(Y52)+N(AA52)=0,"tab empty",IF(N(T52)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D87")+INDIRECT("'"&amp;$C52&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C52&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P52" s="12">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D97")+INDIRECT("'"&amp;$C52&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q52" s="16">
         <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R52" s="12">
         <f>IF(AND(ISNUMBER(H52),ISNUMBER(Q52)),H52*Q52,"")</f>
+        <v/>
       </c>
       <c r="S52" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T52" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
@@ -4313,12 +4647,15 @@
       <c r="X52" s="10" t="n"/>
       <c r="Y52" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z52" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA52" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D89")+INDIRECT("'"&amp;$C52&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="59">
@@ -4333,36 +4670,47 @@
       <c r="I53" s="10" t="n"/>
       <c r="J53" s="11">
         <f>IF($C53="","",IF(ISERROR(INDIRECT("'"&amp;$C53&amp;"'!C1")),"no tab yet",IF(N(Y53)+N(AA53)=0,"tab empty",IF(N(T53)&gt;0,"check inputs","costed"))))</f>
+        <v/>
       </c>
       <c r="K53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D87")+INDIRECT("'"&amp;$C53&amp;"'!D88"),""))</f>
+        <v/>
       </c>
       <c r="L53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D89")+0,""))</f>
+        <v/>
       </c>
       <c r="M53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(SUM(INDIRECT("'"&amp;$C53&amp;"'!D90:D93")),""))</f>
+        <v/>
       </c>
       <c r="N53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D94")+0,""))</f>
+        <v/>
       </c>
       <c r="O53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D95")+0,""))</f>
+        <v/>
       </c>
       <c r="P53" s="12">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D97")+INDIRECT("'"&amp;$C53&amp;"'!D98"),""))</f>
+        <v/>
       </c>
       <c r="Q53" s="16">
         <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D99")+0,""))</f>
+        <v/>
       </c>
       <c r="R53" s="12">
         <f>IF(AND(ISNUMBER(H53),ISNUMBER(Q53)),H53*Q53,"")</f>
+        <v/>
       </c>
       <c r="S53" s="18">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D86")+0,"")</f>
+        <v/>
       </c>
       <c r="T53" s="11">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D102")+0,"")</f>
+        <v/>
       </c>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
@@ -4370,12 +4718,15 @@
       <c r="X53" s="10" t="n"/>
       <c r="Y53" s="20">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D82")+0,"")</f>
+        <v/>
       </c>
       <c r="Z53" s="21">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D84")+0,"")</f>
+        <v/>
       </c>
       <c r="AA53" s="12">
         <f>IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D89")+INDIRECT("'"&amp;$C53&amp;"'!D94"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="59">
@@ -4390,6 +4741,7 @@
       <c r="I54" s="26" t="n"/>
       <c r="J54" s="27">
         <f>COUNTIF(J5:J53,"costed")&amp;" costed / "&amp;COUNTA(C5:C53)&amp;" items"</f>
+        <v/>
       </c>
       <c r="K54" s="26" t="n"/>
       <c r="L54" s="26" t="n"/>
@@ -4399,12 +4751,15 @@
       <c r="P54" s="26" t="n"/>
       <c r="Q54" s="28">
         <f>SUM(Q5:Q53)</f>
+        <v/>
       </c>
       <c r="R54" s="28">
         <f>SUM(R5:R53)</f>
+        <v/>
       </c>
       <c r="S54" s="29">
         <f>SUM(S5:S53)</f>
+        <v/>
       </c>
       <c r="T54" s="26" t="n"/>
       <c r="U54" s="26" t="n"/>
@@ -4413,9 +4768,11 @@
       <c r="X54" s="26" t="n"/>
       <c r="Y54" s="30">
         <f>SUM(Y5:Y53)</f>
+        <v/>
       </c>
       <c r="Z54" s="31">
         <f>SUM(Z5:Z53)</f>
+        <v/>
       </c>
       <c r="AA54" s="26" t="n"/>
     </row>
@@ -4482,6 +4839,7 @@
       <c r="I58" s="9" t="n"/>
       <c r="J58" s="9">
         <f>COUNTIFS($B$5:$B$53,$D58,$J$5:$J$53,"costed")</f>
+        <v/>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>
@@ -4491,12 +4849,15 @@
       <c r="P58" s="9" t="n"/>
       <c r="Q58" s="32">
         <f>SUMIF($B$5:$B$53,$D58,Q$5:Q$53)</f>
+        <v/>
       </c>
       <c r="R58" s="32">
         <f>SUMIF($B$5:$B$53,$D58,R$5:R$53)</f>
+        <v/>
       </c>
       <c r="S58" s="33">
         <f>SUMIF($B$5:$B$53,$D58,S$5:S$53)</f>
+        <v/>
       </c>
       <c r="T58" s="9" t="n"/>
       <c r="U58" s="9" t="n"/>
@@ -4505,9 +4866,11 @@
       <c r="X58" s="9" t="n"/>
       <c r="Y58" s="34">
         <f>SUMIF($B$5:$B$53,$D58,Y$5:Y$53)</f>
+        <v/>
       </c>
       <c r="Z58" s="35">
         <f>SUMIF($B$5:$B$53,$D58,Z$5:Z$53)</f>
+        <v/>
       </c>
       <c r="AA58" s="9" t="n"/>
     </row>
@@ -4520,6 +4883,7 @@
       <c r="I59" s="9" t="n"/>
       <c r="J59" s="9">
         <f>COUNTIFS($B$5:$B$53,$D59,$J$5:$J$53,"costed")</f>
+        <v/>
       </c>
       <c r="K59" s="9" t="n"/>
       <c r="L59" s="9" t="n"/>
@@ -4529,12 +4893,15 @@
       <c r="P59" s="9" t="n"/>
       <c r="Q59" s="32">
         <f>SUMIF($B$5:$B$53,$D59,Q$5:Q$53)</f>
+        <v/>
       </c>
       <c r="R59" s="32">
         <f>SUMIF($B$5:$B$53,$D59,R$5:R$53)</f>
+        <v/>
       </c>
       <c r="S59" s="33">
         <f>SUMIF($B$5:$B$53,$D59,S$5:S$53)</f>
+        <v/>
       </c>
       <c r="T59" s="9" t="n"/>
       <c r="U59" s="9" t="n"/>
@@ -4543,9 +4910,11 @@
       <c r="X59" s="9" t="n"/>
       <c r="Y59" s="34">
         <f>SUMIF($B$5:$B$53,$D59,Y$5:Y$53)</f>
+        <v/>
       </c>
       <c r="Z59" s="35">
         <f>SUMIF($B$5:$B$53,$D59,Z$5:Z$53)</f>
+        <v/>
       </c>
       <c r="AA59" s="9" t="n"/>
     </row>
@@ -4558,6 +4927,7 @@
       <c r="I60" s="9" t="n"/>
       <c r="J60" s="9">
         <f>COUNTIFS($B$5:$B$53,$D60,$J$5:$J$53,"costed")</f>
+        <v/>
       </c>
       <c r="K60" s="9" t="n"/>
       <c r="L60" s="9" t="n"/>
@@ -4567,12 +4937,15 @@
       <c r="P60" s="9" t="n"/>
       <c r="Q60" s="32">
         <f>SUMIF($B$5:$B$53,$D60,Q$5:Q$53)</f>
+        <v/>
       </c>
       <c r="R60" s="32">
         <f>SUMIF($B$5:$B$53,$D60,R$5:R$53)</f>
+        <v/>
       </c>
       <c r="S60" s="33">
         <f>SUMIF($B$5:$B$53,$D60,S$5:S$53)</f>
+        <v/>
       </c>
       <c r="T60" s="9" t="n"/>
       <c r="U60" s="9" t="n"/>
@@ -4581,9 +4954,11 @@
       <c r="X60" s="9" t="n"/>
       <c r="Y60" s="34">
         <f>SUMIF($B$5:$B$53,$D60,Y$5:Y$53)</f>
+        <v/>
       </c>
       <c r="Z60" s="35">
         <f>SUMIF($B$5:$B$53,$D60,Z$5:Z$53)</f>
+        <v/>
       </c>
       <c r="AA60" s="9" t="n"/>
     </row>
@@ -5572,6 +5947,7 @@
       </c>
       <c r="G1" s="9">
         <f t="array" ref="G1">IFERROR(IF(INDEX(ITEMS!$E$5:$E$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$E$5:$E$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H1" s="67" t="n"/>
       <c r="I1" s="67" t="n"/>
@@ -5579,6 +5955,7 @@
       <c r="K1" s="68" t="n"/>
       <c r="L1" s="69">
         <f>IF(G6="","photo",_xludf.IMAGE(G6))</f>
+        <v/>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="59">
@@ -5589,6 +5966,7 @@
       </c>
       <c r="C2" s="9">
         <f t="array" ref="C2">IFERROR(IF(INDEX(ITEMS!$D$5:$D$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$D$5:$D$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="D2" s="66" t="inlineStr">
         <is>
@@ -5597,6 +5975,7 @@
       </c>
       <c r="G2" s="9">
         <f t="array" ref="G2">IFERROR(IF(INDEX(ITEMS!$F$5:$F$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$F$5:$F$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H2" s="67" t="n"/>
       <c r="I2" s="67" t="n"/>
@@ -5611,6 +5990,7 @@
       </c>
       <c r="C3" s="9">
         <f t="array" ref="C3">IFERROR(INDEX(ITEMS!$B$5:$B$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))&amp;" / "&amp;INDEX(ITEMS!$W$5:$W$120,MATCH($C$1,ITEMS!$C$5:$C$120,0)),"")</f>
+        <v/>
       </c>
       <c r="D3" s="66" t="inlineStr">
         <is>
@@ -5619,6 +5999,7 @@
       </c>
       <c r="G3" s="9">
         <f t="array" ref="G3">IFERROR(IF(INDEX(ITEMS!$G$5:$G$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$G$5:$G$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H3" s="67" t="n"/>
       <c r="I3" s="67" t="n"/>
@@ -5633,6 +6014,7 @@
       </c>
       <c r="C4" s="9">
         <f t="array" ref="C4">IFERROR(IF(INDEX(ITEMS!$H$5:$H$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$H$5:$H$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="D4" s="66" t="inlineStr">
         <is>
@@ -5641,6 +6023,7 @@
       </c>
       <c r="G4" s="9">
         <f t="array" ref="G4">IFERROR(IF(INDEX(ITEMS!$I$5:$I$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$I$5:$I$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H4" s="67" t="n"/>
       <c r="I4" s="67" t="n"/>
@@ -5661,6 +6044,7 @@
       </c>
       <c r="G5" s="9">
         <f t="array" ref="G5">IFERROR(IF(INDEX(ITEMS!$V$5:$V$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$V$5:$V$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H5" s="67" t="n"/>
       <c r="I5" s="67" t="n"/>
@@ -5693,6 +6077,7 @@
       </c>
       <c r="C7" s="9">
         <f t="array" ref="C7">IFERROR(IF(INDEX(ITEMS!$X$5:$X$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$X$5:$X$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="D7" s="66" t="inlineStr">
         <is>
@@ -5784,19 +6169,24 @@
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="14">
         <f>IF(D11="","",D11+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="I11" s="14">
         <f>IF(E11="","",E11+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="J11" s="14">
         <f>IF(F11="","",F11+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="17">
         <f>IF(H11="","",2*(H11*I11+H11*J11+I11*J11)/1000000*IF(G11="",1,G11))</f>
+        <v/>
       </c>
       <c r="M11" s="19">
         <f>IF(H11="","",H11*I11*J11/1000000000*IF(G11="",1,G11))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -5811,19 +6201,24 @@
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="14">
         <f>IF(D12="","",D12+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="I12" s="14">
         <f>IF(E12="","",E12+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="J12" s="14">
         <f>IF(F12="","",F12+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="17">
         <f>IF(H12="","",2*(H12*I12+H12*J12+I12*J12)/1000000*IF(G12="",1,G12))</f>
+        <v/>
       </c>
       <c r="M12" s="19">
         <f>IF(H12="","",H12*I12*J12/1000000000*IF(G12="",1,G12))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -5838,19 +6233,24 @@
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="14">
         <f>IF(D13="","",D13+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="I13" s="14">
         <f>IF(E13="","",E13+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="J13" s="14">
         <f>IF(F13="","",F13+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="17">
         <f>IF(H13="","",2*(H13*I13+H13*J13+I13*J13)/1000000*IF(G13="",1,G13))</f>
+        <v/>
       </c>
       <c r="M13" s="19">
         <f>IF(H13="","",H13*I13*J13/1000000000*IF(G13="",1,G13))</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -5865,19 +6265,24 @@
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="14">
         <f>IF(D14="","",D14+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="I14" s="14">
         <f>IF(E14="","",E14+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="J14" s="14">
         <f>IF(F14="","",F14+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="17">
         <f>IF(H14="","",2*(H14*I14+H14*J14+I14*J14)/1000000*IF(G14="",1,G14))</f>
+        <v/>
       </c>
       <c r="M14" s="19">
         <f>IF(H14="","",H14*I14*J14/1000000000*IF(G14="",1,G14))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -5893,6 +6298,7 @@
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="22">
         <f>IF(D11="",1,SUM(G11:G14)+COUNTIFS(D11:D14,"&lt;&gt;",G11:G14,""))</f>
+        <v/>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -5904,9 +6310,11 @@
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="23">
         <f>IF(D11="",IF(OR(G1="",G2="",G3=""),0,2*((G1+LISTS!$F$9)*(G2+LISTS!$F$9)+(G1+LISTS!$F$9)*(G3+LISTS!$F$9)+(G2+LISTS!$F$9)*(G3+LISTS!$F$9))/1000000),SUM(L11:L14))</f>
+        <v/>
       </c>
       <c r="M15" s="24">
         <f>IF(D11="",IF(OR(G1="",G2="",G3=""),0,(G1+LISTS!$F$9)*(G2+LISTS!$F$9)*(G3+LISTS!$F$9)/1000000000),SUM(M11:M14))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -6033,23 +6441,29 @@
       <c r="L18" s="10" t="n"/>
       <c r="M18" s="25">
         <f>IF(OR(E18="",F18="",G18=""),"",E18*F18*G18/1000000000*IF(H18="",1,H18))</f>
+        <v/>
       </c>
       <c r="N18" s="19">
         <f>IF(OR(E18="",F18=""),"",E18*F18/1000000*IF(H18="",1,H18))</f>
+        <v/>
       </c>
       <c r="O18" s="14">
         <f>IF(E18="","",IF(K18&lt;&gt;"",K18,IF(AND(E18*F18*G18/1000000000&lt;LISTS!$F$4,MAX(E18,F18,G18)&lt;LISTS!$F$5),"D",IF(I18="N","C",IF(J18="Y","A-CURVED",IF(AND(MEDIAN(E18,F18,G18)&lt;=LISTS!$F$10,MAX(E18,F18,G18)&lt;=LISTS!$F$11),"B",IF(MAX(E18,F18,G18)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P18" s="14" t="n"/>
       <c r="Q18" s="14" t="n"/>
       <c r="R18" s="14">
         <f>IF(E18="","",IF(B18="","material?",IF(OR(F18="",G18=""),"size?",IF(I18="","exposed Y/N?",IF(H18="","qty?",IF(B18="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S18" s="12">
         <f t="array" ref="S18">IF(OR(O18="",M18=""),"",IF(B18="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B18&amp;"_"&amp;SUBSTITUTE(O18,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T18" s="12">
         <f>IF(ISNUMBER(S18),M18*S18,"")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -6069,23 +6483,29 @@
       <c r="L19" s="10" t="n"/>
       <c r="M19" s="25">
         <f>IF(OR(E19="",F19="",G19=""),"",E19*F19*G19/1000000000*IF(H19="",1,H19))</f>
+        <v/>
       </c>
       <c r="N19" s="19">
         <f>IF(OR(E19="",F19=""),"",E19*F19/1000000*IF(H19="",1,H19))</f>
+        <v/>
       </c>
       <c r="O19" s="14">
         <f>IF(E19="","",IF(K19&lt;&gt;"",K19,IF(AND(E19*F19*G19/1000000000&lt;LISTS!$F$4,MAX(E19,F19,G19)&lt;LISTS!$F$5),"D",IF(I19="N","C",IF(J19="Y","A-CURVED",IF(AND(MEDIAN(E19,F19,G19)&lt;=LISTS!$F$10,MAX(E19,F19,G19)&lt;=LISTS!$F$11),"B",IF(MAX(E19,F19,G19)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P19" s="14" t="n"/>
       <c r="Q19" s="14" t="n"/>
       <c r="R19" s="14">
         <f>IF(E19="","",IF(B19="","material?",IF(OR(F19="",G19=""),"size?",IF(I19="","exposed Y/N?",IF(H19="","qty?",IF(B19="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S19" s="12">
         <f t="array" ref="S19">IF(OR(O19="",M19=""),"",IF(B19="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B19&amp;"_"&amp;SUBSTITUTE(O19,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T19" s="12">
         <f>IF(ISNUMBER(S19),M19*S19,"")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -6105,23 +6525,29 @@
       <c r="L20" s="10" t="n"/>
       <c r="M20" s="25">
         <f>IF(OR(E20="",F20="",G20=""),"",E20*F20*G20/1000000000*IF(H20="",1,H20))</f>
+        <v/>
       </c>
       <c r="N20" s="19">
         <f>IF(OR(E20="",F20=""),"",E20*F20/1000000*IF(H20="",1,H20))</f>
+        <v/>
       </c>
       <c r="O20" s="14">
         <f>IF(E20="","",IF(K20&lt;&gt;"",K20,IF(AND(E20*F20*G20/1000000000&lt;LISTS!$F$4,MAX(E20,F20,G20)&lt;LISTS!$F$5),"D",IF(I20="N","C",IF(J20="Y","A-CURVED",IF(AND(MEDIAN(E20,F20,G20)&lt;=LISTS!$F$10,MAX(E20,F20,G20)&lt;=LISTS!$F$11),"B",IF(MAX(E20,F20,G20)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P20" s="14" t="n"/>
       <c r="Q20" s="14" t="n"/>
       <c r="R20" s="14">
         <f>IF(E20="","",IF(B20="","material?",IF(OR(F20="",G20=""),"size?",IF(I20="","exposed Y/N?",IF(H20="","qty?",IF(B20="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S20" s="12">
         <f t="array" ref="S20">IF(OR(O20="",M20=""),"",IF(B20="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B20&amp;"_"&amp;SUBSTITUTE(O20,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T20" s="12">
         <f>IF(ISNUMBER(S20),M20*S20,"")</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="59">
@@ -6141,23 +6567,29 @@
       <c r="L21" s="10" t="n"/>
       <c r="M21" s="25">
         <f>IF(OR(E21="",F21="",G21=""),"",E21*F21*G21/1000000000*IF(H21="",1,H21))</f>
+        <v/>
       </c>
       <c r="N21" s="19">
         <f>IF(OR(E21="",F21=""),"",E21*F21/1000000*IF(H21="",1,H21))</f>
+        <v/>
       </c>
       <c r="O21" s="14">
         <f>IF(E21="","",IF(K21&lt;&gt;"",K21,IF(AND(E21*F21*G21/1000000000&lt;LISTS!$F$4,MAX(E21,F21,G21)&lt;LISTS!$F$5),"D",IF(I21="N","C",IF(J21="Y","A-CURVED",IF(AND(MEDIAN(E21,F21,G21)&lt;=LISTS!$F$10,MAX(E21,F21,G21)&lt;=LISTS!$F$11),"B",IF(MAX(E21,F21,G21)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P21" s="14" t="n"/>
       <c r="Q21" s="14" t="n"/>
       <c r="R21" s="14">
         <f>IF(E21="","",IF(B21="","material?",IF(OR(F21="",G21=""),"size?",IF(I21="","exposed Y/N?",IF(H21="","qty?",IF(B21="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S21" s="12">
         <f t="array" ref="S21">IF(OR(O21="",M21=""),"",IF(B21="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B21&amp;"_"&amp;SUBSTITUTE(O21,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T21" s="12">
         <f>IF(ISNUMBER(S21),M21*S21,"")</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="59">
@@ -6177,23 +6609,29 @@
       <c r="L22" s="10" t="n"/>
       <c r="M22" s="25">
         <f>IF(OR(E22="",F22="",G22=""),"",E22*F22*G22/1000000000*IF(H22="",1,H22))</f>
+        <v/>
       </c>
       <c r="N22" s="19">
         <f>IF(OR(E22="",F22=""),"",E22*F22/1000000*IF(H22="",1,H22))</f>
+        <v/>
       </c>
       <c r="O22" s="14">
         <f>IF(E22="","",IF(K22&lt;&gt;"",K22,IF(AND(E22*F22*G22/1000000000&lt;LISTS!$F$4,MAX(E22,F22,G22)&lt;LISTS!$F$5),"D",IF(I22="N","C",IF(J22="Y","A-CURVED",IF(AND(MEDIAN(E22,F22,G22)&lt;=LISTS!$F$10,MAX(E22,F22,G22)&lt;=LISTS!$F$11),"B",IF(MAX(E22,F22,G22)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P22" s="14" t="n"/>
       <c r="Q22" s="14" t="n"/>
       <c r="R22" s="14">
         <f>IF(E22="","",IF(B22="","material?",IF(OR(F22="",G22=""),"size?",IF(I22="","exposed Y/N?",IF(H22="","qty?",IF(B22="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S22" s="12">
         <f t="array" ref="S22">IF(OR(O22="",M22=""),"",IF(B22="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B22&amp;"_"&amp;SUBSTITUTE(O22,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T22" s="12">
         <f>IF(ISNUMBER(S22),M22*S22,"")</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="59">
@@ -6213,23 +6651,29 @@
       <c r="L23" s="10" t="n"/>
       <c r="M23" s="25">
         <f>IF(OR(E23="",F23="",G23=""),"",E23*F23*G23/1000000000*IF(H23="",1,H23))</f>
+        <v/>
       </c>
       <c r="N23" s="19">
         <f>IF(OR(E23="",F23=""),"",E23*F23/1000000*IF(H23="",1,H23))</f>
+        <v/>
       </c>
       <c r="O23" s="14">
         <f>IF(E23="","",IF(K23&lt;&gt;"",K23,IF(AND(E23*F23*G23/1000000000&lt;LISTS!$F$4,MAX(E23,F23,G23)&lt;LISTS!$F$5),"D",IF(I23="N","C",IF(J23="Y","A-CURVED",IF(AND(MEDIAN(E23,F23,G23)&lt;=LISTS!$F$10,MAX(E23,F23,G23)&lt;=LISTS!$F$11),"B",IF(MAX(E23,F23,G23)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P23" s="14" t="n"/>
       <c r="Q23" s="14" t="n"/>
       <c r="R23" s="14">
         <f>IF(E23="","",IF(B23="","material?",IF(OR(F23="",G23=""),"size?",IF(I23="","exposed Y/N?",IF(H23="","qty?",IF(B23="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S23" s="12">
         <f t="array" ref="S23">IF(OR(O23="",M23=""),"",IF(B23="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B23&amp;"_"&amp;SUBSTITUTE(O23,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T23" s="12">
         <f>IF(ISNUMBER(S23),M23*S23,"")</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="59">
@@ -6249,23 +6693,29 @@
       <c r="L24" s="10" t="n"/>
       <c r="M24" s="25">
         <f>IF(OR(E24="",F24="",G24=""),"",E24*F24*G24/1000000000*IF(H24="",1,H24))</f>
+        <v/>
       </c>
       <c r="N24" s="19">
         <f>IF(OR(E24="",F24=""),"",E24*F24/1000000*IF(H24="",1,H24))</f>
+        <v/>
       </c>
       <c r="O24" s="14">
         <f>IF(E24="","",IF(K24&lt;&gt;"",K24,IF(AND(E24*F24*G24/1000000000&lt;LISTS!$F$4,MAX(E24,F24,G24)&lt;LISTS!$F$5),"D",IF(I24="N","C",IF(J24="Y","A-CURVED",IF(AND(MEDIAN(E24,F24,G24)&lt;=LISTS!$F$10,MAX(E24,F24,G24)&lt;=LISTS!$F$11),"B",IF(MAX(E24,F24,G24)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P24" s="14" t="n"/>
       <c r="Q24" s="14" t="n"/>
       <c r="R24" s="14">
         <f>IF(E24="","",IF(B24="","material?",IF(OR(F24="",G24=""),"size?",IF(I24="","exposed Y/N?",IF(H24="","qty?",IF(B24="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S24" s="12">
         <f t="array" ref="S24">IF(OR(O24="",M24=""),"",IF(B24="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B24&amp;"_"&amp;SUBSTITUTE(O24,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T24" s="12">
         <f>IF(ISNUMBER(S24),M24*S24,"")</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="59">
@@ -6285,23 +6735,29 @@
       <c r="L25" s="10" t="n"/>
       <c r="M25" s="25">
         <f>IF(OR(E25="",F25="",G25=""),"",E25*F25*G25/1000000000*IF(H25="",1,H25))</f>
+        <v/>
       </c>
       <c r="N25" s="19">
         <f>IF(OR(E25="",F25=""),"",E25*F25/1000000*IF(H25="",1,H25))</f>
+        <v/>
       </c>
       <c r="O25" s="14">
         <f>IF(E25="","",IF(K25&lt;&gt;"",K25,IF(AND(E25*F25*G25/1000000000&lt;LISTS!$F$4,MAX(E25,F25,G25)&lt;LISTS!$F$5),"D",IF(I25="N","C",IF(J25="Y","A-CURVED",IF(AND(MEDIAN(E25,F25,G25)&lt;=LISTS!$F$10,MAX(E25,F25,G25)&lt;=LISTS!$F$11),"B",IF(MAX(E25,F25,G25)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P25" s="14" t="n"/>
       <c r="Q25" s="14" t="n"/>
       <c r="R25" s="14">
         <f>IF(E25="","",IF(B25="","material?",IF(OR(F25="",G25=""),"size?",IF(I25="","exposed Y/N?",IF(H25="","qty?",IF(B25="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S25" s="12">
         <f t="array" ref="S25">IF(OR(O25="",M25=""),"",IF(B25="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B25&amp;"_"&amp;SUBSTITUTE(O25,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T25" s="12">
         <f>IF(ISNUMBER(S25),M25*S25,"")</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="59">
@@ -6321,23 +6777,29 @@
       <c r="L26" s="10" t="n"/>
       <c r="M26" s="25">
         <f>IF(OR(E26="",F26="",G26=""),"",E26*F26*G26/1000000000*IF(H26="",1,H26))</f>
+        <v/>
       </c>
       <c r="N26" s="19">
         <f>IF(OR(E26="",F26=""),"",E26*F26/1000000*IF(H26="",1,H26))</f>
+        <v/>
       </c>
       <c r="O26" s="14">
         <f>IF(E26="","",IF(K26&lt;&gt;"",K26,IF(AND(E26*F26*G26/1000000000&lt;LISTS!$F$4,MAX(E26,F26,G26)&lt;LISTS!$F$5),"D",IF(I26="N","C",IF(J26="Y","A-CURVED",IF(AND(MEDIAN(E26,F26,G26)&lt;=LISTS!$F$10,MAX(E26,F26,G26)&lt;=LISTS!$F$11),"B",IF(MAX(E26,F26,G26)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P26" s="14" t="n"/>
       <c r="Q26" s="14" t="n"/>
       <c r="R26" s="14">
         <f>IF(E26="","",IF(B26="","material?",IF(OR(F26="",G26=""),"size?",IF(I26="","exposed Y/N?",IF(H26="","qty?",IF(B26="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S26" s="12">
         <f t="array" ref="S26">IF(OR(O26="",M26=""),"",IF(B26="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B26&amp;"_"&amp;SUBSTITUTE(O26,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T26" s="12">
         <f>IF(ISNUMBER(S26),M26*S26,"")</f>
+        <v/>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="59">
@@ -6357,23 +6819,29 @@
       <c r="L27" s="10" t="n"/>
       <c r="M27" s="25">
         <f>IF(OR(E27="",F27="",G27=""),"",E27*F27*G27/1000000000*IF(H27="",1,H27))</f>
+        <v/>
       </c>
       <c r="N27" s="19">
         <f>IF(OR(E27="",F27=""),"",E27*F27/1000000*IF(H27="",1,H27))</f>
+        <v/>
       </c>
       <c r="O27" s="14">
         <f>IF(E27="","",IF(K27&lt;&gt;"",K27,IF(AND(E27*F27*G27/1000000000&lt;LISTS!$F$4,MAX(E27,F27,G27)&lt;LISTS!$F$5),"D",IF(I27="N","C",IF(J27="Y","A-CURVED",IF(AND(MEDIAN(E27,F27,G27)&lt;=LISTS!$F$10,MAX(E27,F27,G27)&lt;=LISTS!$F$11),"B",IF(MAX(E27,F27,G27)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P27" s="14" t="n"/>
       <c r="Q27" s="14" t="n"/>
       <c r="R27" s="14">
         <f>IF(E27="","",IF(B27="","material?",IF(OR(F27="",G27=""),"size?",IF(I27="","exposed Y/N?",IF(H27="","qty?",IF(B27="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S27" s="12">
         <f t="array" ref="S27">IF(OR(O27="",M27=""),"",IF(B27="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B27&amp;"_"&amp;SUBSTITUTE(O27,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T27" s="12">
         <f>IF(ISNUMBER(S27),M27*S27,"")</f>
+        <v/>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="59">
@@ -6393,23 +6861,29 @@
       <c r="L28" s="10" t="n"/>
       <c r="M28" s="25">
         <f>IF(OR(E28="",F28="",G28=""),"",E28*F28*G28/1000000000*IF(H28="",1,H28))</f>
+        <v/>
       </c>
       <c r="N28" s="19">
         <f>IF(OR(E28="",F28=""),"",E28*F28/1000000*IF(H28="",1,H28))</f>
+        <v/>
       </c>
       <c r="O28" s="14">
         <f>IF(E28="","",IF(K28&lt;&gt;"",K28,IF(AND(E28*F28*G28/1000000000&lt;LISTS!$F$4,MAX(E28,F28,G28)&lt;LISTS!$F$5),"D",IF(I28="N","C",IF(J28="Y","A-CURVED",IF(AND(MEDIAN(E28,F28,G28)&lt;=LISTS!$F$10,MAX(E28,F28,G28)&lt;=LISTS!$F$11),"B",IF(MAX(E28,F28,G28)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P28" s="14" t="n"/>
       <c r="Q28" s="14" t="n"/>
       <c r="R28" s="14">
         <f>IF(E28="","",IF(B28="","material?",IF(OR(F28="",G28=""),"size?",IF(I28="","exposed Y/N?",IF(H28="","qty?",IF(B28="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S28" s="12">
         <f t="array" ref="S28">IF(OR(O28="",M28=""),"",IF(B28="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B28&amp;"_"&amp;SUBSTITUTE(O28,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T28" s="12">
         <f>IF(ISNUMBER(S28),M28*S28,"")</f>
+        <v/>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="59">
@@ -6429,23 +6903,29 @@
       <c r="L29" s="10" t="n"/>
       <c r="M29" s="25">
         <f>IF(OR(E29="",F29="",G29=""),"",E29*F29*G29/1000000000*IF(H29="",1,H29))</f>
+        <v/>
       </c>
       <c r="N29" s="19">
         <f>IF(OR(E29="",F29=""),"",E29*F29/1000000*IF(H29="",1,H29))</f>
+        <v/>
       </c>
       <c r="O29" s="14">
         <f>IF(E29="","",IF(K29&lt;&gt;"",K29,IF(AND(E29*F29*G29/1000000000&lt;LISTS!$F$4,MAX(E29,F29,G29)&lt;LISTS!$F$5),"D",IF(I29="N","C",IF(J29="Y","A-CURVED",IF(AND(MEDIAN(E29,F29,G29)&lt;=LISTS!$F$10,MAX(E29,F29,G29)&lt;=LISTS!$F$11),"B",IF(MAX(E29,F29,G29)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P29" s="14" t="n"/>
       <c r="Q29" s="14" t="n"/>
       <c r="R29" s="14">
         <f>IF(E29="","",IF(B29="","material?",IF(OR(F29="",G29=""),"size?",IF(I29="","exposed Y/N?",IF(H29="","qty?",IF(B29="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S29" s="12">
         <f t="array" ref="S29">IF(OR(O29="",M29=""),"",IF(B29="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B29&amp;"_"&amp;SUBSTITUTE(O29,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T29" s="12">
         <f>IF(ISNUMBER(S29),M29*S29,"")</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="59">
@@ -6465,23 +6945,29 @@
       <c r="L30" s="10" t="n"/>
       <c r="M30" s="25">
         <f>IF(OR(E30="",F30="",G30=""),"",E30*F30*G30/1000000000*IF(H30="",1,H30))</f>
+        <v/>
       </c>
       <c r="N30" s="19">
         <f>IF(OR(E30="",F30=""),"",E30*F30/1000000*IF(H30="",1,H30))</f>
+        <v/>
       </c>
       <c r="O30" s="14">
         <f>IF(E30="","",IF(K30&lt;&gt;"",K30,IF(AND(E30*F30*G30/1000000000&lt;LISTS!$F$4,MAX(E30,F30,G30)&lt;LISTS!$F$5),"D",IF(I30="N","C",IF(J30="Y","A-CURVED",IF(AND(MEDIAN(E30,F30,G30)&lt;=LISTS!$F$10,MAX(E30,F30,G30)&lt;=LISTS!$F$11),"B",IF(MAX(E30,F30,G30)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P30" s="14" t="n"/>
       <c r="Q30" s="14" t="n"/>
       <c r="R30" s="14">
         <f>IF(E30="","",IF(B30="","material?",IF(OR(F30="",G30=""),"size?",IF(I30="","exposed Y/N?",IF(H30="","qty?",IF(B30="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S30" s="12">
         <f t="array" ref="S30">IF(OR(O30="",M30=""),"",IF(B30="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B30&amp;"_"&amp;SUBSTITUTE(O30,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T30" s="12">
         <f>IF(ISNUMBER(S30),M30*S30,"")</f>
+        <v/>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="59">
@@ -6501,23 +6987,29 @@
       <c r="L31" s="10" t="n"/>
       <c r="M31" s="25">
         <f>IF(OR(E31="",F31="",G31=""),"",E31*F31*G31/1000000000*IF(H31="",1,H31))</f>
+        <v/>
       </c>
       <c r="N31" s="19">
         <f>IF(OR(E31="",F31=""),"",E31*F31/1000000*IF(H31="",1,H31))</f>
+        <v/>
       </c>
       <c r="O31" s="14">
         <f>IF(E31="","",IF(K31&lt;&gt;"",K31,IF(AND(E31*F31*G31/1000000000&lt;LISTS!$F$4,MAX(E31,F31,G31)&lt;LISTS!$F$5),"D",IF(I31="N","C",IF(J31="Y","A-CURVED",IF(AND(MEDIAN(E31,F31,G31)&lt;=LISTS!$F$10,MAX(E31,F31,G31)&lt;=LISTS!$F$11),"B",IF(MAX(E31,F31,G31)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P31" s="14" t="n"/>
       <c r="Q31" s="14" t="n"/>
       <c r="R31" s="14">
         <f>IF(E31="","",IF(B31="","material?",IF(OR(F31="",G31=""),"size?",IF(I31="","exposed Y/N?",IF(H31="","qty?",IF(B31="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S31" s="12">
         <f t="array" ref="S31">IF(OR(O31="",M31=""),"",IF(B31="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B31&amp;"_"&amp;SUBSTITUTE(O31,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T31" s="12">
         <f>IF(ISNUMBER(S31),M31*S31,"")</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="59">
@@ -6537,23 +7029,29 @@
       <c r="L32" s="10" t="n"/>
       <c r="M32" s="25">
         <f>IF(OR(E32="",F32="",G32=""),"",E32*F32*G32/1000000000*IF(H32="",1,H32))</f>
+        <v/>
       </c>
       <c r="N32" s="19">
         <f>IF(OR(E32="",F32=""),"",E32*F32/1000000*IF(H32="",1,H32))</f>
+        <v/>
       </c>
       <c r="O32" s="14">
         <f>IF(E32="","",IF(K32&lt;&gt;"",K32,IF(AND(E32*F32*G32/1000000000&lt;LISTS!$F$4,MAX(E32,F32,G32)&lt;LISTS!$F$5),"D",IF(I32="N","C",IF(J32="Y","A-CURVED",IF(AND(MEDIAN(E32,F32,G32)&lt;=LISTS!$F$10,MAX(E32,F32,G32)&lt;=LISTS!$F$11),"B",IF(MAX(E32,F32,G32)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P32" s="14" t="n"/>
       <c r="Q32" s="14" t="n"/>
       <c r="R32" s="14">
         <f>IF(E32="","",IF(B32="","material?",IF(OR(F32="",G32=""),"size?",IF(I32="","exposed Y/N?",IF(H32="","qty?",IF(B32="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S32" s="12">
         <f t="array" ref="S32">IF(OR(O32="",M32=""),"",IF(B32="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B32&amp;"_"&amp;SUBSTITUTE(O32,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T32" s="12">
         <f>IF(ISNUMBER(S32),M32*S32,"")</f>
+        <v/>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="59">
@@ -6573,23 +7071,29 @@
       <c r="L33" s="10" t="n"/>
       <c r="M33" s="25">
         <f>IF(OR(E33="",F33="",G33=""),"",E33*F33*G33/1000000000*IF(H33="",1,H33))</f>
+        <v/>
       </c>
       <c r="N33" s="19">
         <f>IF(OR(E33="",F33=""),"",E33*F33/1000000*IF(H33="",1,H33))</f>
+        <v/>
       </c>
       <c r="O33" s="14">
         <f>IF(E33="","",IF(K33&lt;&gt;"",K33,IF(AND(E33*F33*G33/1000000000&lt;LISTS!$F$4,MAX(E33,F33,G33)&lt;LISTS!$F$5),"D",IF(I33="N","C",IF(J33="Y","A-CURVED",IF(AND(MEDIAN(E33,F33,G33)&lt;=LISTS!$F$10,MAX(E33,F33,G33)&lt;=LISTS!$F$11),"B",IF(MAX(E33,F33,G33)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P33" s="14" t="n"/>
       <c r="Q33" s="14" t="n"/>
       <c r="R33" s="14">
         <f>IF(E33="","",IF(B33="","material?",IF(OR(F33="",G33=""),"size?",IF(I33="","exposed Y/N?",IF(H33="","qty?",IF(B33="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S33" s="12">
         <f t="array" ref="S33">IF(OR(O33="",M33=""),"",IF(B33="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B33&amp;"_"&amp;SUBSTITUTE(O33,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T33" s="12">
         <f>IF(ISNUMBER(S33),M33*S33,"")</f>
+        <v/>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="59">
@@ -6609,23 +7113,29 @@
       <c r="L34" s="10" t="n"/>
       <c r="M34" s="25">
         <f>IF(OR(E34="",F34="",G34=""),"",E34*F34*G34/1000000000*IF(H34="",1,H34))</f>
+        <v/>
       </c>
       <c r="N34" s="19">
         <f>IF(OR(E34="",F34=""),"",E34*F34/1000000*IF(H34="",1,H34))</f>
+        <v/>
       </c>
       <c r="O34" s="14">
         <f>IF(E34="","",IF(K34&lt;&gt;"",K34,IF(AND(E34*F34*G34/1000000000&lt;LISTS!$F$4,MAX(E34,F34,G34)&lt;LISTS!$F$5),"D",IF(I34="N","C",IF(J34="Y","A-CURVED",IF(AND(MEDIAN(E34,F34,G34)&lt;=LISTS!$F$10,MAX(E34,F34,G34)&lt;=LISTS!$F$11),"B",IF(MAX(E34,F34,G34)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P34" s="14" t="n"/>
       <c r="Q34" s="14" t="n"/>
       <c r="R34" s="14">
         <f>IF(E34="","",IF(B34="","material?",IF(OR(F34="",G34=""),"size?",IF(I34="","exposed Y/N?",IF(H34="","qty?",IF(B34="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S34" s="12">
         <f t="array" ref="S34">IF(OR(O34="",M34=""),"",IF(B34="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B34&amp;"_"&amp;SUBSTITUTE(O34,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T34" s="12">
         <f>IF(ISNUMBER(S34),M34*S34,"")</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="59">
@@ -6645,23 +7155,29 @@
       <c r="L35" s="10" t="n"/>
       <c r="M35" s="25">
         <f>IF(OR(E35="",F35="",G35=""),"",E35*F35*G35/1000000000*IF(H35="",1,H35))</f>
+        <v/>
       </c>
       <c r="N35" s="19">
         <f>IF(OR(E35="",F35=""),"",E35*F35/1000000*IF(H35="",1,H35))</f>
+        <v/>
       </c>
       <c r="O35" s="14">
         <f>IF(E35="","",IF(K35&lt;&gt;"",K35,IF(AND(E35*F35*G35/1000000000&lt;LISTS!$F$4,MAX(E35,F35,G35)&lt;LISTS!$F$5),"D",IF(I35="N","C",IF(J35="Y","A-CURVED",IF(AND(MEDIAN(E35,F35,G35)&lt;=LISTS!$F$10,MAX(E35,F35,G35)&lt;=LISTS!$F$11),"B",IF(MAX(E35,F35,G35)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P35" s="14" t="n"/>
       <c r="Q35" s="14" t="n"/>
       <c r="R35" s="14">
         <f>IF(E35="","",IF(B35="","material?",IF(OR(F35="",G35=""),"size?",IF(I35="","exposed Y/N?",IF(H35="","qty?",IF(B35="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S35" s="12">
         <f t="array" ref="S35">IF(OR(O35="",M35=""),"",IF(B35="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B35&amp;"_"&amp;SUBSTITUTE(O35,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T35" s="12">
         <f>IF(ISNUMBER(S35),M35*S35,"")</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="59">
@@ -6681,23 +7197,29 @@
       <c r="L36" s="10" t="n"/>
       <c r="M36" s="25">
         <f>IF(OR(E36="",F36="",G36=""),"",E36*F36*G36/1000000000*IF(H36="",1,H36))</f>
+        <v/>
       </c>
       <c r="N36" s="19">
         <f>IF(OR(E36="",F36=""),"",E36*F36/1000000*IF(H36="",1,H36))</f>
+        <v/>
       </c>
       <c r="O36" s="14">
         <f>IF(E36="","",IF(K36&lt;&gt;"",K36,IF(AND(E36*F36*G36/1000000000&lt;LISTS!$F$4,MAX(E36,F36,G36)&lt;LISTS!$F$5),"D",IF(I36="N","C",IF(J36="Y","A-CURVED",IF(AND(MEDIAN(E36,F36,G36)&lt;=LISTS!$F$10,MAX(E36,F36,G36)&lt;=LISTS!$F$11),"B",IF(MAX(E36,F36,G36)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P36" s="14" t="n"/>
       <c r="Q36" s="14" t="n"/>
       <c r="R36" s="14">
         <f>IF(E36="","",IF(B36="","material?",IF(OR(F36="",G36=""),"size?",IF(I36="","exposed Y/N?",IF(H36="","qty?",IF(B36="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S36" s="12">
         <f t="array" ref="S36">IF(OR(O36="",M36=""),"",IF(B36="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B36&amp;"_"&amp;SUBSTITUTE(O36,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T36" s="12">
         <f>IF(ISNUMBER(S36),M36*S36,"")</f>
+        <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="59">
@@ -6717,23 +7239,29 @@
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="25">
         <f>IF(OR(E37="",F37="",G37=""),"",E37*F37*G37/1000000000*IF(H37="",1,H37))</f>
+        <v/>
       </c>
       <c r="N37" s="19">
         <f>IF(OR(E37="",F37=""),"",E37*F37/1000000*IF(H37="",1,H37))</f>
+        <v/>
       </c>
       <c r="O37" s="14">
         <f>IF(E37="","",IF(K37&lt;&gt;"",K37,IF(AND(E37*F37*G37/1000000000&lt;LISTS!$F$4,MAX(E37,F37,G37)&lt;LISTS!$F$5),"D",IF(I37="N","C",IF(J37="Y","A-CURVED",IF(AND(MEDIAN(E37,F37,G37)&lt;=LISTS!$F$10,MAX(E37,F37,G37)&lt;=LISTS!$F$11),"B",IF(MAX(E37,F37,G37)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
       <c r="R37" s="14">
         <f>IF(E37="","",IF(B37="","material?",IF(OR(F37="",G37=""),"size?",IF(I37="","exposed Y/N?",IF(H37="","qty?",IF(B37="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S37" s="12">
         <f t="array" ref="S37">IF(OR(O37="",M37=""),"",IF(B37="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B37&amp;"_"&amp;SUBSTITUTE(O37,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T37" s="12">
         <f>IF(ISNUMBER(S37),M37*S37,"")</f>
+        <v/>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="59">
@@ -6753,23 +7281,29 @@
       <c r="L38" s="10" t="n"/>
       <c r="M38" s="25">
         <f>IF(OR(E38="",F38="",G38=""),"",E38*F38*G38/1000000000*IF(H38="",1,H38))</f>
+        <v/>
       </c>
       <c r="N38" s="19">
         <f>IF(OR(E38="",F38=""),"",E38*F38/1000000*IF(H38="",1,H38))</f>
+        <v/>
       </c>
       <c r="O38" s="14">
         <f>IF(E38="","",IF(K38&lt;&gt;"",K38,IF(AND(E38*F38*G38/1000000000&lt;LISTS!$F$4,MAX(E38,F38,G38)&lt;LISTS!$F$5),"D",IF(I38="N","C",IF(J38="Y","A-CURVED",IF(AND(MEDIAN(E38,F38,G38)&lt;=LISTS!$F$10,MAX(E38,F38,G38)&lt;=LISTS!$F$11),"B",IF(MAX(E38,F38,G38)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P38" s="14" t="n"/>
       <c r="Q38" s="14" t="n"/>
       <c r="R38" s="14">
         <f>IF(E38="","",IF(B38="","material?",IF(OR(F38="",G38=""),"size?",IF(I38="","exposed Y/N?",IF(H38="","qty?",IF(B38="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S38" s="12">
         <f t="array" ref="S38">IF(OR(O38="",M38=""),"",IF(B38="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B38&amp;"_"&amp;SUBSTITUTE(O38,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T38" s="12">
         <f>IF(ISNUMBER(S38),M38*S38,"")</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="59">
@@ -6789,23 +7323,29 @@
       <c r="L39" s="10" t="n"/>
       <c r="M39" s="25">
         <f>IF(OR(E39="",F39="",G39=""),"",E39*F39*G39/1000000000*IF(H39="",1,H39))</f>
+        <v/>
       </c>
       <c r="N39" s="19">
         <f>IF(OR(E39="",F39=""),"",E39*F39/1000000*IF(H39="",1,H39))</f>
+        <v/>
       </c>
       <c r="O39" s="14">
         <f>IF(E39="","",IF(K39&lt;&gt;"",K39,IF(AND(E39*F39*G39/1000000000&lt;LISTS!$F$4,MAX(E39,F39,G39)&lt;LISTS!$F$5),"D",IF(I39="N","C",IF(J39="Y","A-CURVED",IF(AND(MEDIAN(E39,F39,G39)&lt;=LISTS!$F$10,MAX(E39,F39,G39)&lt;=LISTS!$F$11),"B",IF(MAX(E39,F39,G39)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P39" s="14" t="n"/>
       <c r="Q39" s="14" t="n"/>
       <c r="R39" s="14">
         <f>IF(E39="","",IF(B39="","material?",IF(OR(F39="",G39=""),"size?",IF(I39="","exposed Y/N?",IF(H39="","qty?",IF(B39="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S39" s="12">
         <f t="array" ref="S39">IF(OR(O39="",M39=""),"",IF(B39="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B39&amp;"_"&amp;SUBSTITUTE(O39,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T39" s="12">
         <f>IF(ISNUMBER(S39),M39*S39,"")</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="59">
@@ -6825,23 +7365,29 @@
       <c r="L40" s="10" t="n"/>
       <c r="M40" s="25">
         <f>IF(OR(E40="",F40="",G40=""),"",E40*F40*G40/1000000000*IF(H40="",1,H40))</f>
+        <v/>
       </c>
       <c r="N40" s="19">
         <f>IF(OR(E40="",F40=""),"",E40*F40/1000000*IF(H40="",1,H40))</f>
+        <v/>
       </c>
       <c r="O40" s="14">
         <f>IF(E40="","",IF(K40&lt;&gt;"",K40,IF(AND(E40*F40*G40/1000000000&lt;LISTS!$F$4,MAX(E40,F40,G40)&lt;LISTS!$F$5),"D",IF(I40="N","C",IF(J40="Y","A-CURVED",IF(AND(MEDIAN(E40,F40,G40)&lt;=LISTS!$F$10,MAX(E40,F40,G40)&lt;=LISTS!$F$11),"B",IF(MAX(E40,F40,G40)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P40" s="14" t="n"/>
       <c r="Q40" s="14" t="n"/>
       <c r="R40" s="14">
         <f>IF(E40="","",IF(B40="","material?",IF(OR(F40="",G40=""),"size?",IF(I40="","exposed Y/N?",IF(H40="","qty?",IF(B40="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S40" s="12">
         <f t="array" ref="S40">IF(OR(O40="",M40=""),"",IF(B40="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B40&amp;"_"&amp;SUBSTITUTE(O40,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T40" s="12">
         <f>IF(ISNUMBER(S40),M40*S40,"")</f>
+        <v/>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="59">
@@ -6861,23 +7407,29 @@
       <c r="L41" s="10" t="n"/>
       <c r="M41" s="25">
         <f>IF(OR(E41="",F41="",G41=""),"",E41*F41*G41/1000000000*IF(H41="",1,H41))</f>
+        <v/>
       </c>
       <c r="N41" s="19">
         <f>IF(OR(E41="",F41=""),"",E41*F41/1000000*IF(H41="",1,H41))</f>
+        <v/>
       </c>
       <c r="O41" s="14">
         <f>IF(E41="","",IF(K41&lt;&gt;"",K41,IF(AND(E41*F41*G41/1000000000&lt;LISTS!$F$4,MAX(E41,F41,G41)&lt;LISTS!$F$5),"D",IF(I41="N","C",IF(J41="Y","A-CURVED",IF(AND(MEDIAN(E41,F41,G41)&lt;=LISTS!$F$10,MAX(E41,F41,G41)&lt;=LISTS!$F$11),"B",IF(MAX(E41,F41,G41)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P41" s="14" t="n"/>
       <c r="Q41" s="14" t="n"/>
       <c r="R41" s="14">
         <f>IF(E41="","",IF(B41="","material?",IF(OR(F41="",G41=""),"size?",IF(I41="","exposed Y/N?",IF(H41="","qty?",IF(B41="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S41" s="12">
         <f t="array" ref="S41">IF(OR(O41="",M41=""),"",IF(B41="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B41&amp;"_"&amp;SUBSTITUTE(O41,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T41" s="12">
         <f>IF(ISNUMBER(S41),M41*S41,"")</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="59">
@@ -6897,23 +7449,29 @@
       <c r="L42" s="10" t="n"/>
       <c r="M42" s="25">
         <f>IF(OR(E42="",F42="",G42=""),"",E42*F42*G42/1000000000*IF(H42="",1,H42))</f>
+        <v/>
       </c>
       <c r="N42" s="19">
         <f>IF(OR(E42="",F42=""),"",E42*F42/1000000*IF(H42="",1,H42))</f>
+        <v/>
       </c>
       <c r="O42" s="14">
         <f>IF(E42="","",IF(K42&lt;&gt;"",K42,IF(AND(E42*F42*G42/1000000000&lt;LISTS!$F$4,MAX(E42,F42,G42)&lt;LISTS!$F$5),"D",IF(I42="N","C",IF(J42="Y","A-CURVED",IF(AND(MEDIAN(E42,F42,G42)&lt;=LISTS!$F$10,MAX(E42,F42,G42)&lt;=LISTS!$F$11),"B",IF(MAX(E42,F42,G42)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P42" s="14" t="n"/>
       <c r="Q42" s="14" t="n"/>
       <c r="R42" s="14">
         <f>IF(E42="","",IF(B42="","material?",IF(OR(F42="",G42=""),"size?",IF(I42="","exposed Y/N?",IF(H42="","qty?",IF(B42="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S42" s="12">
         <f t="array" ref="S42">IF(OR(O42="",M42=""),"",IF(B42="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B42&amp;"_"&amp;SUBSTITUTE(O42,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T42" s="12">
         <f>IF(ISNUMBER(S42),M42*S42,"")</f>
+        <v/>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="59"/>
@@ -7045,27 +7603,35 @@
       <c r="L46" s="10" t="n"/>
       <c r="M46" s="25">
         <f>IF(OR(E46="",F46="",G46=""),"",E46*F46*G46/1000000000*IF(H46="",1,H46))</f>
+        <v/>
       </c>
       <c r="N46" s="19">
         <f>IF(OR(E46="",F46=""),"",E46*F46/1000000*IF(H46="",1,H46))</f>
+        <v/>
       </c>
       <c r="O46" s="14">
         <f>IF(OR(E46="",F46=""),"",MAX(INT(LISTS!$F$6/(E46+LISTS!$F$8))*INT(LISTS!$F$7/(F46+LISTS!$F$8)),INT(LISTS!$F$6/(F46+LISTS!$F$8))*INT(LISTS!$F$7/(E46+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P46" s="19">
         <f>IF(K46&lt;&gt;"",K46,IF(OR(O46="",O46=0),"",IF(H46="",1,H46)/O46))</f>
+        <v/>
       </c>
       <c r="Q46" s="36">
         <f>IF(OR(K46&lt;&gt;"",P46=""),"",1-(IF(H46="",1,H46)*E46*F46)/(ROUNDUP(P46,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R46" s="14">
         <f>IF(AND(E46="",K46=""),"",IF(B46="","panel type?",IF(AND(K46="",O46=0),"panel bigger than sheet",IF(AND(G46&lt;&gt;"",ISERROR(FIND("-"&amp;G46,B46))),"T must match panel type",IF(I46="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S46" s="12">
         <f t="array" ref="S46">IF(OR(B46="",P46=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B46,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T46" s="12">
         <f>IF(ISNUMBER(S46),IF(K46&lt;&gt;"",K46,IF(Q46&gt;RATES!$C$97,P46*(1+RATES!$C$98),ROUNDUP(P46,0)))*S46,"")</f>
+        <v/>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="59">
@@ -7085,27 +7651,35 @@
       <c r="L47" s="10" t="n"/>
       <c r="M47" s="25">
         <f>IF(OR(E47="",F47="",G47=""),"",E47*F47*G47/1000000000*IF(H47="",1,H47))</f>
+        <v/>
       </c>
       <c r="N47" s="19">
         <f>IF(OR(E47="",F47=""),"",E47*F47/1000000*IF(H47="",1,H47))</f>
+        <v/>
       </c>
       <c r="O47" s="14">
         <f>IF(OR(E47="",F47=""),"",MAX(INT(LISTS!$F$6/(E47+LISTS!$F$8))*INT(LISTS!$F$7/(F47+LISTS!$F$8)),INT(LISTS!$F$6/(F47+LISTS!$F$8))*INT(LISTS!$F$7/(E47+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P47" s="19">
         <f>IF(K47&lt;&gt;"",K47,IF(OR(O47="",O47=0),"",IF(H47="",1,H47)/O47))</f>
+        <v/>
       </c>
       <c r="Q47" s="36">
         <f>IF(OR(K47&lt;&gt;"",P47=""),"",1-(IF(H47="",1,H47)*E47*F47)/(ROUNDUP(P47,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R47" s="14">
         <f>IF(AND(E47="",K47=""),"",IF(B47="","panel type?",IF(AND(K47="",O47=0),"panel bigger than sheet",IF(AND(G47&lt;&gt;"",ISERROR(FIND("-"&amp;G47,B47))),"T must match panel type",IF(I47="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S47" s="12">
         <f t="array" ref="S47">IF(OR(B47="",P47=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B47,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T47" s="12">
         <f>IF(ISNUMBER(S47),IF(K47&lt;&gt;"",K47,IF(Q47&gt;RATES!$C$97,P47*(1+RATES!$C$98),ROUNDUP(P47,0)))*S47,"")</f>
+        <v/>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="59">
@@ -7125,27 +7699,35 @@
       <c r="L48" s="10" t="n"/>
       <c r="M48" s="25">
         <f>IF(OR(E48="",F48="",G48=""),"",E48*F48*G48/1000000000*IF(H48="",1,H48))</f>
+        <v/>
       </c>
       <c r="N48" s="19">
         <f>IF(OR(E48="",F48=""),"",E48*F48/1000000*IF(H48="",1,H48))</f>
+        <v/>
       </c>
       <c r="O48" s="14">
         <f>IF(OR(E48="",F48=""),"",MAX(INT(LISTS!$F$6/(E48+LISTS!$F$8))*INT(LISTS!$F$7/(F48+LISTS!$F$8)),INT(LISTS!$F$6/(F48+LISTS!$F$8))*INT(LISTS!$F$7/(E48+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P48" s="19">
         <f>IF(K48&lt;&gt;"",K48,IF(OR(O48="",O48=0),"",IF(H48="",1,H48)/O48))</f>
+        <v/>
       </c>
       <c r="Q48" s="36">
         <f>IF(OR(K48&lt;&gt;"",P48=""),"",1-(IF(H48="",1,H48)*E48*F48)/(ROUNDUP(P48,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R48" s="14">
         <f>IF(AND(E48="",K48=""),"",IF(B48="","panel type?",IF(AND(K48="",O48=0),"panel bigger than sheet",IF(AND(G48&lt;&gt;"",ISERROR(FIND("-"&amp;G48,B48))),"T must match panel type",IF(I48="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S48" s="12">
         <f t="array" ref="S48">IF(OR(B48="",P48=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B48,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T48" s="12">
         <f>IF(ISNUMBER(S48),IF(K48&lt;&gt;"",K48,IF(Q48&gt;RATES!$C$97,P48*(1+RATES!$C$98),ROUNDUP(P48,0)))*S48,"")</f>
+        <v/>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="59">
@@ -7165,27 +7747,35 @@
       <c r="L49" s="10" t="n"/>
       <c r="M49" s="25">
         <f>IF(OR(E49="",F49="",G49=""),"",E49*F49*G49/1000000000*IF(H49="",1,H49))</f>
+        <v/>
       </c>
       <c r="N49" s="19">
         <f>IF(OR(E49="",F49=""),"",E49*F49/1000000*IF(H49="",1,H49))</f>
+        <v/>
       </c>
       <c r="O49" s="14">
         <f>IF(OR(E49="",F49=""),"",MAX(INT(LISTS!$F$6/(E49+LISTS!$F$8))*INT(LISTS!$F$7/(F49+LISTS!$F$8)),INT(LISTS!$F$6/(F49+LISTS!$F$8))*INT(LISTS!$F$7/(E49+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P49" s="19">
         <f>IF(K49&lt;&gt;"",K49,IF(OR(O49="",O49=0),"",IF(H49="",1,H49)/O49))</f>
+        <v/>
       </c>
       <c r="Q49" s="36">
         <f>IF(OR(K49&lt;&gt;"",P49=""),"",1-(IF(H49="",1,H49)*E49*F49)/(ROUNDUP(P49,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R49" s="14">
         <f>IF(AND(E49="",K49=""),"",IF(B49="","panel type?",IF(AND(K49="",O49=0),"panel bigger than sheet",IF(AND(G49&lt;&gt;"",ISERROR(FIND("-"&amp;G49,B49))),"T must match panel type",IF(I49="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S49" s="12">
         <f t="array" ref="S49">IF(OR(B49="",P49=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B49,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T49" s="12">
         <f>IF(ISNUMBER(S49),IF(K49&lt;&gt;"",K49,IF(Q49&gt;RATES!$C$97,P49*(1+RATES!$C$98),ROUNDUP(P49,0)))*S49,"")</f>
+        <v/>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="59">
@@ -7205,27 +7795,35 @@
       <c r="L50" s="10" t="n"/>
       <c r="M50" s="25">
         <f>IF(OR(E50="",F50="",G50=""),"",E50*F50*G50/1000000000*IF(H50="",1,H50))</f>
+        <v/>
       </c>
       <c r="N50" s="19">
         <f>IF(OR(E50="",F50=""),"",E50*F50/1000000*IF(H50="",1,H50))</f>
+        <v/>
       </c>
       <c r="O50" s="14">
         <f>IF(OR(E50="",F50=""),"",MAX(INT(LISTS!$F$6/(E50+LISTS!$F$8))*INT(LISTS!$F$7/(F50+LISTS!$F$8)),INT(LISTS!$F$6/(F50+LISTS!$F$8))*INT(LISTS!$F$7/(E50+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P50" s="19">
         <f>IF(K50&lt;&gt;"",K50,IF(OR(O50="",O50=0),"",IF(H50="",1,H50)/O50))</f>
+        <v/>
       </c>
       <c r="Q50" s="36">
         <f>IF(OR(K50&lt;&gt;"",P50=""),"",1-(IF(H50="",1,H50)*E50*F50)/(ROUNDUP(P50,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R50" s="14">
         <f>IF(AND(E50="",K50=""),"",IF(B50="","panel type?",IF(AND(K50="",O50=0),"panel bigger than sheet",IF(AND(G50&lt;&gt;"",ISERROR(FIND("-"&amp;G50,B50))),"T must match panel type",IF(I50="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S50" s="12">
         <f t="array" ref="S50">IF(OR(B50="",P50=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B50,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T50" s="12">
         <f>IF(ISNUMBER(S50),IF(K50&lt;&gt;"",K50,IF(Q50&gt;RATES!$C$97,P50*(1+RATES!$C$98),ROUNDUP(P50,0)))*S50,"")</f>
+        <v/>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="59">
@@ -7245,27 +7843,35 @@
       <c r="L51" s="10" t="n"/>
       <c r="M51" s="25">
         <f>IF(OR(E51="",F51="",G51=""),"",E51*F51*G51/1000000000*IF(H51="",1,H51))</f>
+        <v/>
       </c>
       <c r="N51" s="19">
         <f>IF(OR(E51="",F51=""),"",E51*F51/1000000*IF(H51="",1,H51))</f>
+        <v/>
       </c>
       <c r="O51" s="14">
         <f>IF(OR(E51="",F51=""),"",MAX(INT(LISTS!$F$6/(E51+LISTS!$F$8))*INT(LISTS!$F$7/(F51+LISTS!$F$8)),INT(LISTS!$F$6/(F51+LISTS!$F$8))*INT(LISTS!$F$7/(E51+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P51" s="19">
         <f>IF(K51&lt;&gt;"",K51,IF(OR(O51="",O51=0),"",IF(H51="",1,H51)/O51))</f>
+        <v/>
       </c>
       <c r="Q51" s="36">
         <f>IF(OR(K51&lt;&gt;"",P51=""),"",1-(IF(H51="",1,H51)*E51*F51)/(ROUNDUP(P51,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R51" s="14">
         <f>IF(AND(E51="",K51=""),"",IF(B51="","panel type?",IF(AND(K51="",O51=0),"panel bigger than sheet",IF(AND(G51&lt;&gt;"",ISERROR(FIND("-"&amp;G51,B51))),"T must match panel type",IF(I51="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S51" s="12">
         <f t="array" ref="S51">IF(OR(B51="",P51=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B51,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T51" s="12">
         <f>IF(ISNUMBER(S51),IF(K51&lt;&gt;"",K51,IF(Q51&gt;RATES!$C$97,P51*(1+RATES!$C$98),ROUNDUP(P51,0)))*S51,"")</f>
+        <v/>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="59">
@@ -7285,27 +7891,35 @@
       <c r="L52" s="10" t="n"/>
       <c r="M52" s="25">
         <f>IF(OR(E52="",F52="",G52=""),"",E52*F52*G52/1000000000*IF(H52="",1,H52))</f>
+        <v/>
       </c>
       <c r="N52" s="19">
         <f>IF(OR(E52="",F52=""),"",E52*F52/1000000*IF(H52="",1,H52))</f>
+        <v/>
       </c>
       <c r="O52" s="14">
         <f>IF(OR(E52="",F52=""),"",MAX(INT(LISTS!$F$6/(E52+LISTS!$F$8))*INT(LISTS!$F$7/(F52+LISTS!$F$8)),INT(LISTS!$F$6/(F52+LISTS!$F$8))*INT(LISTS!$F$7/(E52+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P52" s="19">
         <f>IF(K52&lt;&gt;"",K52,IF(OR(O52="",O52=0),"",IF(H52="",1,H52)/O52))</f>
+        <v/>
       </c>
       <c r="Q52" s="36">
         <f>IF(OR(K52&lt;&gt;"",P52=""),"",1-(IF(H52="",1,H52)*E52*F52)/(ROUNDUP(P52,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R52" s="14">
         <f>IF(AND(E52="",K52=""),"",IF(B52="","panel type?",IF(AND(K52="",O52=0),"panel bigger than sheet",IF(AND(G52&lt;&gt;"",ISERROR(FIND("-"&amp;G52,B52))),"T must match panel type",IF(I52="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S52" s="12">
         <f t="array" ref="S52">IF(OR(B52="",P52=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B52,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T52" s="12">
         <f>IF(ISNUMBER(S52),IF(K52&lt;&gt;"",K52,IF(Q52&gt;RATES!$C$97,P52*(1+RATES!$C$98),ROUNDUP(P52,0)))*S52,"")</f>
+        <v/>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="59">
@@ -7325,27 +7939,35 @@
       <c r="L53" s="10" t="n"/>
       <c r="M53" s="25">
         <f>IF(OR(E53="",F53="",G53=""),"",E53*F53*G53/1000000000*IF(H53="",1,H53))</f>
+        <v/>
       </c>
       <c r="N53" s="19">
         <f>IF(OR(E53="",F53=""),"",E53*F53/1000000*IF(H53="",1,H53))</f>
+        <v/>
       </c>
       <c r="O53" s="14">
         <f>IF(OR(E53="",F53=""),"",MAX(INT(LISTS!$F$6/(E53+LISTS!$F$8))*INT(LISTS!$F$7/(F53+LISTS!$F$8)),INT(LISTS!$F$6/(F53+LISTS!$F$8))*INT(LISTS!$F$7/(E53+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P53" s="19">
         <f>IF(K53&lt;&gt;"",K53,IF(OR(O53="",O53=0),"",IF(H53="",1,H53)/O53))</f>
+        <v/>
       </c>
       <c r="Q53" s="36">
         <f>IF(OR(K53&lt;&gt;"",P53=""),"",1-(IF(H53="",1,H53)*E53*F53)/(ROUNDUP(P53,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R53" s="14">
         <f>IF(AND(E53="",K53=""),"",IF(B53="","panel type?",IF(AND(K53="",O53=0),"panel bigger than sheet",IF(AND(G53&lt;&gt;"",ISERROR(FIND("-"&amp;G53,B53))),"T must match panel type",IF(I53="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S53" s="12">
         <f t="array" ref="S53">IF(OR(B53="",P53=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B53,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T53" s="12">
         <f>IF(ISNUMBER(S53),IF(K53&lt;&gt;"",K53,IF(Q53&gt;RATES!$C$97,P53*(1+RATES!$C$98),ROUNDUP(P53,0)))*S53,"")</f>
+        <v/>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="59">
@@ -7365,27 +7987,35 @@
       <c r="L54" s="10" t="n"/>
       <c r="M54" s="25">
         <f>IF(OR(E54="",F54="",G54=""),"",E54*F54*G54/1000000000*IF(H54="",1,H54))</f>
+        <v/>
       </c>
       <c r="N54" s="19">
         <f>IF(OR(E54="",F54=""),"",E54*F54/1000000*IF(H54="",1,H54))</f>
+        <v/>
       </c>
       <c r="O54" s="14">
         <f>IF(OR(E54="",F54=""),"",MAX(INT(LISTS!$F$6/(E54+LISTS!$F$8))*INT(LISTS!$F$7/(F54+LISTS!$F$8)),INT(LISTS!$F$6/(F54+LISTS!$F$8))*INT(LISTS!$F$7/(E54+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P54" s="19">
         <f>IF(K54&lt;&gt;"",K54,IF(OR(O54="",O54=0),"",IF(H54="",1,H54)/O54))</f>
+        <v/>
       </c>
       <c r="Q54" s="36">
         <f>IF(OR(K54&lt;&gt;"",P54=""),"",1-(IF(H54="",1,H54)*E54*F54)/(ROUNDUP(P54,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R54" s="14">
         <f>IF(AND(E54="",K54=""),"",IF(B54="","panel type?",IF(AND(K54="",O54=0),"panel bigger than sheet",IF(AND(G54&lt;&gt;"",ISERROR(FIND("-"&amp;G54,B54))),"T must match panel type",IF(I54="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S54" s="12">
         <f t="array" ref="S54">IF(OR(B54="",P54=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B54,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T54" s="12">
         <f>IF(ISNUMBER(S54),IF(K54&lt;&gt;"",K54,IF(Q54&gt;RATES!$C$97,P54*(1+RATES!$C$98),ROUNDUP(P54,0)))*S54,"")</f>
+        <v/>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="59">
@@ -7405,27 +8035,35 @@
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="25">
         <f>IF(OR(E55="",F55="",G55=""),"",E55*F55*G55/1000000000*IF(H55="",1,H55))</f>
+        <v/>
       </c>
       <c r="N55" s="19">
         <f>IF(OR(E55="",F55=""),"",E55*F55/1000000*IF(H55="",1,H55))</f>
+        <v/>
       </c>
       <c r="O55" s="14">
         <f>IF(OR(E55="",F55=""),"",MAX(INT(LISTS!$F$6/(E55+LISTS!$F$8))*INT(LISTS!$F$7/(F55+LISTS!$F$8)),INT(LISTS!$F$6/(F55+LISTS!$F$8))*INT(LISTS!$F$7/(E55+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P55" s="19">
         <f>IF(K55&lt;&gt;"",K55,IF(OR(O55="",O55=0),"",IF(H55="",1,H55)/O55))</f>
+        <v/>
       </c>
       <c r="Q55" s="36">
         <f>IF(OR(K55&lt;&gt;"",P55=""),"",1-(IF(H55="",1,H55)*E55*F55)/(ROUNDUP(P55,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R55" s="14">
         <f>IF(AND(E55="",K55=""),"",IF(B55="","panel type?",IF(AND(K55="",O55=0),"panel bigger than sheet",IF(AND(G55&lt;&gt;"",ISERROR(FIND("-"&amp;G55,B55))),"T must match panel type",IF(I55="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S55" s="12">
         <f t="array" ref="S55">IF(OR(B55="",P55=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B55,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T55" s="12">
         <f>IF(ISNUMBER(S55),IF(K55&lt;&gt;"",K55,IF(Q55&gt;RATES!$C$97,P55*(1+RATES!$C$98),ROUNDUP(P55,0)))*S55,"")</f>
+        <v/>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="59">
@@ -7445,27 +8083,35 @@
       <c r="L56" s="10" t="n"/>
       <c r="M56" s="25">
         <f>IF(OR(E56="",F56="",G56=""),"",E56*F56*G56/1000000000*IF(H56="",1,H56))</f>
+        <v/>
       </c>
       <c r="N56" s="19">
         <f>IF(OR(E56="",F56=""),"",E56*F56/1000000*IF(H56="",1,H56))</f>
+        <v/>
       </c>
       <c r="O56" s="14">
         <f>IF(OR(E56="",F56=""),"",MAX(INT(LISTS!$F$6/(E56+LISTS!$F$8))*INT(LISTS!$F$7/(F56+LISTS!$F$8)),INT(LISTS!$F$6/(F56+LISTS!$F$8))*INT(LISTS!$F$7/(E56+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P56" s="19">
         <f>IF(K56&lt;&gt;"",K56,IF(OR(O56="",O56=0),"",IF(H56="",1,H56)/O56))</f>
+        <v/>
       </c>
       <c r="Q56" s="36">
         <f>IF(OR(K56&lt;&gt;"",P56=""),"",1-(IF(H56="",1,H56)*E56*F56)/(ROUNDUP(P56,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R56" s="14">
         <f>IF(AND(E56="",K56=""),"",IF(B56="","panel type?",IF(AND(K56="",O56=0),"panel bigger than sheet",IF(AND(G56&lt;&gt;"",ISERROR(FIND("-"&amp;G56,B56))),"T must match panel type",IF(I56="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S56" s="12">
         <f t="array" ref="S56">IF(OR(B56="",P56=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B56,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T56" s="12">
         <f>IF(ISNUMBER(S56),IF(K56&lt;&gt;"",K56,IF(Q56&gt;RATES!$C$97,P56*(1+RATES!$C$98),ROUNDUP(P56,0)))*S56,"")</f>
+        <v/>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="59">
@@ -7485,27 +8131,35 @@
       <c r="L57" s="10" t="n"/>
       <c r="M57" s="25">
         <f>IF(OR(E57="",F57="",G57=""),"",E57*F57*G57/1000000000*IF(H57="",1,H57))</f>
+        <v/>
       </c>
       <c r="N57" s="19">
         <f>IF(OR(E57="",F57=""),"",E57*F57/1000000*IF(H57="",1,H57))</f>
+        <v/>
       </c>
       <c r="O57" s="14">
         <f>IF(OR(E57="",F57=""),"",MAX(INT(LISTS!$F$6/(E57+LISTS!$F$8))*INT(LISTS!$F$7/(F57+LISTS!$F$8)),INT(LISTS!$F$6/(F57+LISTS!$F$8))*INT(LISTS!$F$7/(E57+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P57" s="19">
         <f>IF(K57&lt;&gt;"",K57,IF(OR(O57="",O57=0),"",IF(H57="",1,H57)/O57))</f>
+        <v/>
       </c>
       <c r="Q57" s="36">
         <f>IF(OR(K57&lt;&gt;"",P57=""),"",1-(IF(H57="",1,H57)*E57*F57)/(ROUNDUP(P57,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R57" s="14">
         <f>IF(AND(E57="",K57=""),"",IF(B57="","panel type?",IF(AND(K57="",O57=0),"panel bigger than sheet",IF(AND(G57&lt;&gt;"",ISERROR(FIND("-"&amp;G57,B57))),"T must match panel type",IF(I57="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S57" s="12">
         <f t="array" ref="S57">IF(OR(B57="",P57=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B57,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T57" s="12">
         <f>IF(ISNUMBER(S57),IF(K57&lt;&gt;"",K57,IF(Q57&gt;RATES!$C$97,P57*(1+RATES!$C$98),ROUNDUP(P57,0)))*S57,"")</f>
+        <v/>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="59">
@@ -7525,27 +8179,35 @@
       <c r="L58" s="10" t="n"/>
       <c r="M58" s="25">
         <f>IF(OR(E58="",F58="",G58=""),"",E58*F58*G58/1000000000*IF(H58="",1,H58))</f>
+        <v/>
       </c>
       <c r="N58" s="19">
         <f>IF(OR(E58="",F58=""),"",E58*F58/1000000*IF(H58="",1,H58))</f>
+        <v/>
       </c>
       <c r="O58" s="14">
         <f>IF(OR(E58="",F58=""),"",MAX(INT(LISTS!$F$6/(E58+LISTS!$F$8))*INT(LISTS!$F$7/(F58+LISTS!$F$8)),INT(LISTS!$F$6/(F58+LISTS!$F$8))*INT(LISTS!$F$7/(E58+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P58" s="19">
         <f>IF(K58&lt;&gt;"",K58,IF(OR(O58="",O58=0),"",IF(H58="",1,H58)/O58))</f>
+        <v/>
       </c>
       <c r="Q58" s="36">
         <f>IF(OR(K58&lt;&gt;"",P58=""),"",1-(IF(H58="",1,H58)*E58*F58)/(ROUNDUP(P58,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R58" s="14">
         <f>IF(AND(E58="",K58=""),"",IF(B58="","panel type?",IF(AND(K58="",O58=0),"panel bigger than sheet",IF(AND(G58&lt;&gt;"",ISERROR(FIND("-"&amp;G58,B58))),"T must match panel type",IF(I58="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S58" s="12">
         <f t="array" ref="S58">IF(OR(B58="",P58=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B58,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T58" s="12">
         <f>IF(ISNUMBER(S58),IF(K58&lt;&gt;"",K58,IF(Q58&gt;RATES!$C$97,P58*(1+RATES!$C$98),ROUNDUP(P58,0)))*S58,"")</f>
+        <v/>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="59">
@@ -7565,27 +8227,35 @@
       <c r="L59" s="10" t="n"/>
       <c r="M59" s="25">
         <f>IF(OR(E59="",F59="",G59=""),"",E59*F59*G59/1000000000*IF(H59="",1,H59))</f>
+        <v/>
       </c>
       <c r="N59" s="19">
         <f>IF(OR(E59="",F59=""),"",E59*F59/1000000*IF(H59="",1,H59))</f>
+        <v/>
       </c>
       <c r="O59" s="14">
         <f>IF(OR(E59="",F59=""),"",MAX(INT(LISTS!$F$6/(E59+LISTS!$F$8))*INT(LISTS!$F$7/(F59+LISTS!$F$8)),INT(LISTS!$F$6/(F59+LISTS!$F$8))*INT(LISTS!$F$7/(E59+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P59" s="19">
         <f>IF(K59&lt;&gt;"",K59,IF(OR(O59="",O59=0),"",IF(H59="",1,H59)/O59))</f>
+        <v/>
       </c>
       <c r="Q59" s="36">
         <f>IF(OR(K59&lt;&gt;"",P59=""),"",1-(IF(H59="",1,H59)*E59*F59)/(ROUNDUP(P59,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R59" s="14">
         <f>IF(AND(E59="",K59=""),"",IF(B59="","panel type?",IF(AND(K59="",O59=0),"panel bigger than sheet",IF(AND(G59&lt;&gt;"",ISERROR(FIND("-"&amp;G59,B59))),"T must match panel type",IF(I59="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S59" s="12">
         <f t="array" ref="S59">IF(OR(B59="",P59=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B59,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T59" s="12">
         <f>IF(ISNUMBER(S59),IF(K59&lt;&gt;"",K59,IF(Q59&gt;RATES!$C$97,P59*(1+RATES!$C$98),ROUNDUP(P59,0)))*S59,"")</f>
+        <v/>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="59">
@@ -7605,27 +8275,35 @@
       <c r="L60" s="10" t="n"/>
       <c r="M60" s="25">
         <f>IF(OR(E60="",F60="",G60=""),"",E60*F60*G60/1000000000*IF(H60="",1,H60))</f>
+        <v/>
       </c>
       <c r="N60" s="19">
         <f>IF(OR(E60="",F60=""),"",E60*F60/1000000*IF(H60="",1,H60))</f>
+        <v/>
       </c>
       <c r="O60" s="14">
         <f>IF(OR(E60="",F60=""),"",MAX(INT(LISTS!$F$6/(E60+LISTS!$F$8))*INT(LISTS!$F$7/(F60+LISTS!$F$8)),INT(LISTS!$F$6/(F60+LISTS!$F$8))*INT(LISTS!$F$7/(E60+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P60" s="19">
         <f>IF(K60&lt;&gt;"",K60,IF(OR(O60="",O60=0),"",IF(H60="",1,H60)/O60))</f>
+        <v/>
       </c>
       <c r="Q60" s="36">
         <f>IF(OR(K60&lt;&gt;"",P60=""),"",1-(IF(H60="",1,H60)*E60*F60)/(ROUNDUP(P60,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R60" s="14">
         <f>IF(AND(E60="",K60=""),"",IF(B60="","panel type?",IF(AND(K60="",O60=0),"panel bigger than sheet",IF(AND(G60&lt;&gt;"",ISERROR(FIND("-"&amp;G60,B60))),"T must match panel type",IF(I60="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S60" s="12">
         <f t="array" ref="S60">IF(OR(B60="",P60=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B60,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T60" s="12">
         <f>IF(ISNUMBER(S60),IF(K60&lt;&gt;"",K60,IF(Q60&gt;RATES!$C$97,P60*(1+RATES!$C$98),ROUNDUP(P60,0)))*S60,"")</f>
+        <v/>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="59"/>
@@ -7727,6 +8405,7 @@
       <c r="S64" s="37" t="n"/>
       <c r="T64" s="38">
         <f>IF(OR(H64="",S64=""),"",H64*S64)</f>
+        <v/>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="59">
@@ -7753,6 +8432,7 @@
       <c r="S65" s="37" t="n"/>
       <c r="T65" s="38">
         <f>IF(OR(H65="",S65=""),"",H65*S65)</f>
+        <v/>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="59">
@@ -7779,6 +8459,7 @@
       <c r="S66" s="37" t="n"/>
       <c r="T66" s="38">
         <f>IF(OR(H66="",S66=""),"",H66*S66)</f>
+        <v/>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="59">
@@ -7805,6 +8486,7 @@
       <c r="S67" s="37" t="n"/>
       <c r="T67" s="38">
         <f>IF(OR(H67="",S67=""),"",H67*S67)</f>
+        <v/>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="59">
@@ -7831,6 +8513,7 @@
       <c r="S68" s="37" t="n"/>
       <c r="T68" s="38">
         <f>IF(OR(H68="",S68=""),"",H68*S68)</f>
+        <v/>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="59">
@@ -7857,6 +8540,7 @@
       <c r="S69" s="37" t="n"/>
       <c r="T69" s="38">
         <f>IF(OR(H69="",S69=""),"",H69*S69)</f>
+        <v/>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="59">
@@ -7883,6 +8567,7 @@
       <c r="S70" s="37" t="n"/>
       <c r="T70" s="38">
         <f>IF(OR(H70="",S70=""),"",H70*S70)</f>
+        <v/>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="59">
@@ -7909,6 +8594,7 @@
       <c r="S71" s="37" t="n"/>
       <c r="T71" s="38">
         <f>IF(OR(H71="",S71=""),"",H71*S71)</f>
+        <v/>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="59">
@@ -7935,6 +8621,7 @@
       <c r="S72" s="37" t="n"/>
       <c r="T72" s="38">
         <f>IF(OR(H72="",S72=""),"",H72*S72)</f>
+        <v/>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="59">
@@ -7961,6 +8648,7 @@
       <c r="S73" s="37" t="n"/>
       <c r="T73" s="38">
         <f>IF(OR(H73="",S73=""),"",H73*S73)</f>
+        <v/>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="59">
@@ -7987,6 +8675,7 @@
       <c r="S74" s="37" t="n"/>
       <c r="T74" s="38">
         <f>IF(OR(H74="",S74=""),"",H74*S74)</f>
+        <v/>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="59">
@@ -8013,6 +8702,7 @@
       <c r="S75" s="37" t="n"/>
       <c r="T75" s="38">
         <f>IF(OR(H75="",S75=""),"",H75*S75)</f>
+        <v/>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="59">
@@ -8039,6 +8729,7 @@
       <c r="S76" s="37" t="n"/>
       <c r="T76" s="38">
         <f>IF(OR(H76="",S76=""),"",H76*S76)</f>
+        <v/>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="59">
@@ -8065,6 +8756,7 @@
       <c r="S77" s="37" t="n"/>
       <c r="T77" s="38">
         <f>IF(OR(H77="",S77=""),"",H77*S77)</f>
+        <v/>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="59">
@@ -8091,6 +8783,7 @@
       <c r="S78" s="37" t="n"/>
       <c r="T78" s="38">
         <f>IF(OR(H78="",S78=""),"",H78*S78)</f>
+        <v/>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="59"/>
@@ -8115,6 +8808,7 @@
       </c>
       <c r="D82" s="25">
         <f>SUM(M18:M42)</f>
+        <v/>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="59">
@@ -8125,6 +8819,7 @@
       </c>
       <c r="D83" s="17">
         <f>SUM(P46:P60)</f>
+        <v/>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="59">
@@ -8135,6 +8830,7 @@
       </c>
       <c r="D84" s="19">
         <f>SUMIF(I18:I42,"Y",N18:N42)+SUMIF(I46:I60,1,N46:N60)+2*SUMIF(I46:I60,2,N46:N60)</f>
+        <v/>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -8150,6 +8846,7 @@
       </c>
       <c r="D85" s="39">
         <f>G15</f>
+        <v/>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="59">
@@ -8160,6 +8857,7 @@
       </c>
       <c r="D86" s="19">
         <f>M15</f>
+        <v/>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="59">
@@ -8170,6 +8868,7 @@
       </c>
       <c r="D87" s="12">
         <f>SUM(T18:T42)</f>
+        <v/>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -8185,6 +8884,7 @@
       </c>
       <c r="D88" s="12">
         <f>D82*RATES!$C$46</f>
+        <v/>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -8200,6 +8900,7 @@
       </c>
       <c r="D89" s="12">
         <f>SUM(T46:T60)</f>
+        <v/>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -8215,6 +8916,7 @@
       </c>
       <c r="D90" s="12">
         <f>D84*RATES!$C$47*IF($C$5="NONE (RAW)",0,1)</f>
+        <v/>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -8230,6 +8932,7 @@
       </c>
       <c r="D91" s="12">
         <f>D84*RATES!$C$48*IF($C$5="NONE (RAW)",0,1)</f>
+        <v/>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -8245,6 +8948,7 @@
       </c>
       <c r="D92" s="12">
         <f>D84*RATES!$C$49*IF($C$5="NONE (RAW)",0,1)</f>
+        <v/>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -8260,6 +8964,7 @@
       </c>
       <c r="D93" s="12">
         <f>D84*RATES!$C$50*IF($C$5="NONE (RAW)",0,1)</f>
+        <v/>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -8275,6 +8980,7 @@
       </c>
       <c r="D94" s="12">
         <f>SUM(T64:T78)</f>
+        <v/>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -8290,6 +8996,7 @@
       </c>
       <c r="D95" s="12">
         <f>IF(L15=0,0,IF(L15&lt;RATES!$C$95,RATES!$C$53*G15,L15*RATES!$C$51*(1+IF(G15&gt;1,RATES!$C$96,0)))+M15*RATES!$C$52)</f>
+        <v/>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -8305,6 +9012,7 @@
       </c>
       <c r="D96" s="16">
         <f>SUM(D87:D95)</f>
+        <v/>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="59">
@@ -8315,6 +9023,7 @@
       </c>
       <c r="D97" s="12">
         <f>D96*RATES!$C$54</f>
+        <v/>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -8330,6 +9039,7 @@
       </c>
       <c r="D98" s="12">
         <f>(D96+D97)*RATES!$C$55</f>
+        <v/>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -8345,6 +9055,7 @@
       </c>
       <c r="D99" s="16">
         <f>D96+D97+D98</f>
+        <v/>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="59">
@@ -8355,6 +9066,7 @@
       </c>
       <c r="D100" s="19">
         <f>L15</f>
+        <v/>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="59">
@@ -8365,6 +9077,7 @@
       </c>
       <c r="D101" s="16">
         <f>IF(ISNUMBER(C4),C4,0)*D99</f>
+        <v/>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="59">
@@ -8375,6 +9088,7 @@
       </c>
       <c r="D102" s="40">
         <f>COUNTIF(R18:R42,"?*")-COUNTIF(R18:R42,"OK")+COUNTIF(R46:R60,"?*")-COUNTIF(R46:R60,"OK")+COUNTIF(S18:S60,"rate?")</f>
+        <v/>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -9365,7 +10079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J249"/>
+  <dimension ref="A1:J257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10602,6 +11316,7 @@
       </c>
       <c r="C55" s="81">
         <f>$C$26/$C$27</f>
+        <v/>
       </c>
       <c r="E55" s="74" t="inlineStr">
         <is>
@@ -10634,6 +11349,7 @@
       </c>
       <c r="C57" s="81">
         <f>$C$29*$C$31+$C$28*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
+        <v/>
       </c>
       <c r="E57" s="74" t="inlineStr">
         <is>
@@ -10675,6 +11391,7 @@
       </c>
       <c r="C59" s="80">
         <f>H59</f>
+        <v/>
       </c>
       <c r="E59" s="74" t="inlineStr">
         <is>
@@ -10688,9 +11405,11 @@
       </c>
       <c r="G59" s="82">
         <f t="array" ref="G59">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H59" s="83">
         <f>G59*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -10706,6 +11425,7 @@
       </c>
       <c r="C60" s="81">
         <f>C59+$C$175</f>
+        <v/>
       </c>
       <c r="E60" s="74" t="inlineStr">
         <is>
@@ -10726,6 +11446,7 @@
       </c>
       <c r="C61" s="81">
         <f>C59+2*$C$175</f>
+        <v/>
       </c>
       <c r="E61" s="74" t="inlineStr">
         <is>
@@ -10746,6 +11467,7 @@
       </c>
       <c r="C62" s="81">
         <f>C59+$C$176</f>
+        <v/>
       </c>
       <c r="E62" s="74" t="inlineStr">
         <is>
@@ -10766,6 +11488,7 @@
       </c>
       <c r="C63" s="81">
         <f>C59+2*$C$176</f>
+        <v/>
       </c>
       <c r="E63" s="74" t="inlineStr">
         <is>
@@ -10786,6 +11509,7 @@
       </c>
       <c r="C64" s="80">
         <f>H64</f>
+        <v/>
       </c>
       <c r="E64" s="74" t="inlineStr">
         <is>
@@ -10799,9 +11523,11 @@
       </c>
       <c r="G64" s="82">
         <f t="array" ref="G64">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H64" s="83">
         <f>G64*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -10817,6 +11543,7 @@
       </c>
       <c r="C65" s="81">
         <f>C64+$C$175</f>
+        <v/>
       </c>
       <c r="E65" s="74" t="inlineStr">
         <is>
@@ -10837,6 +11564,7 @@
       </c>
       <c r="C66" s="81">
         <f>C64+2*$C$175</f>
+        <v/>
       </c>
       <c r="E66" s="74" t="inlineStr">
         <is>
@@ -10857,6 +11585,7 @@
       </c>
       <c r="C67" s="81">
         <f>C64+$C$176</f>
+        <v/>
       </c>
       <c r="E67" s="74" t="inlineStr">
         <is>
@@ -10877,6 +11606,7 @@
       </c>
       <c r="C68" s="81">
         <f>C64+2*$C$176</f>
+        <v/>
       </c>
       <c r="E68" s="74" t="inlineStr">
         <is>
@@ -10897,6 +11627,7 @@
       </c>
       <c r="C69" s="80">
         <f>H69</f>
+        <v/>
       </c>
       <c r="E69" s="74" t="inlineStr">
         <is>
@@ -10910,9 +11641,11 @@
       </c>
       <c r="G69" s="82">
         <f t="array" ref="G69">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H69" s="83">
         <f>G69*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -10928,6 +11661,7 @@
       </c>
       <c r="C70" s="81">
         <f>C69+$C$175</f>
+        <v/>
       </c>
       <c r="E70" s="74" t="inlineStr">
         <is>
@@ -10948,6 +11682,7 @@
       </c>
       <c r="C71" s="81">
         <f>C69+2*$C$175</f>
+        <v/>
       </c>
       <c r="E71" s="74" t="inlineStr">
         <is>
@@ -10968,6 +11703,7 @@
       </c>
       <c r="C72" s="81">
         <f>C69+$C$176</f>
+        <v/>
       </c>
       <c r="E72" s="74" t="inlineStr">
         <is>
@@ -10988,6 +11724,7 @@
       </c>
       <c r="C73" s="81">
         <f>C69+2*$C$176</f>
+        <v/>
       </c>
       <c r="E73" s="74" t="inlineStr">
         <is>
@@ -11008,6 +11745,7 @@
       </c>
       <c r="C74" s="80">
         <f>H74</f>
+        <v/>
       </c>
       <c r="E74" s="74" t="inlineStr">
         <is>
@@ -11021,9 +11759,11 @@
       </c>
       <c r="G74" s="82">
         <f t="array" ref="G74">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H74" s="83">
         <f>G74*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -11039,6 +11779,7 @@
       </c>
       <c r="C75" s="81">
         <f>C74+$C$175</f>
+        <v/>
       </c>
       <c r="E75" s="74" t="inlineStr">
         <is>
@@ -11059,6 +11800,7 @@
       </c>
       <c r="C76" s="81">
         <f>C74+2*$C$175</f>
+        <v/>
       </c>
       <c r="E76" s="74" t="inlineStr">
         <is>
@@ -11079,6 +11821,7 @@
       </c>
       <c r="C77" s="81">
         <f>C74+$C$176</f>
+        <v/>
       </c>
       <c r="E77" s="74" t="inlineStr">
         <is>
@@ -11099,6 +11842,7 @@
       </c>
       <c r="C78" s="81">
         <f>C74+2*$C$176</f>
+        <v/>
       </c>
       <c r="E78" s="74" t="inlineStr">
         <is>
@@ -11132,9 +11876,11 @@
       </c>
       <c r="G79" s="82">
         <f t="array" ref="G79">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H79" s="83">
         <f>G79*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -11230,6 +11976,7 @@
       </c>
       <c r="C84" s="80">
         <f>H84</f>
+        <v/>
       </c>
       <c r="E84" s="74" t="inlineStr">
         <is>
@@ -11243,9 +11990,11 @@
       </c>
       <c r="G84" s="82">
         <f t="array" ref="G84">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H84" s="83">
         <f>G84*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -11261,6 +12010,7 @@
       </c>
       <c r="C85" s="81">
         <f>C84+$C$175</f>
+        <v/>
       </c>
       <c r="E85" s="74" t="inlineStr">
         <is>
@@ -11281,6 +12031,7 @@
       </c>
       <c r="C86" s="81">
         <f>C84+2*$C$175</f>
+        <v/>
       </c>
       <c r="E86" s="74" t="inlineStr">
         <is>
@@ -11301,6 +12052,7 @@
       </c>
       <c r="C87" s="81">
         <f>C84+$C$176</f>
+        <v/>
       </c>
       <c r="E87" s="74" t="inlineStr">
         <is>
@@ -11321,6 +12073,7 @@
       </c>
       <c r="C88" s="81">
         <f>C84+2*$C$176</f>
+        <v/>
       </c>
       <c r="E88" s="74" t="inlineStr">
         <is>
@@ -12930,7 +13683,6 @@
         </is>
       </c>
     </row>
-    <row r="169"/>
     <row r="170">
       <c r="A170" s="84" t="inlineStr">
         <is>
@@ -13112,7 +13864,6 @@
         </is>
       </c>
     </row>
-    <row r="177"/>
     <row r="178">
       <c r="A178" s="79" t="inlineStr">
         <is>
@@ -13126,6 +13877,7 @@
       </c>
       <c r="C178" s="88">
         <f>H178</f>
+        <v/>
       </c>
       <c r="E178" s="79" t="inlineStr">
         <is>
@@ -13139,9 +13891,11 @@
       </c>
       <c r="G178" s="86">
         <f>I178+$C$173/$C$172/J178</f>
+        <v/>
       </c>
       <c r="H178" s="87">
         <f>G178*$C$172</f>
+        <v/>
       </c>
       <c r="I178" s="86" t="n">
         <v>5.248</v>
@@ -13163,6 +13917,7 @@
       </c>
       <c r="C179" s="88">
         <f>H179</f>
+        <v/>
       </c>
       <c r="E179" s="79" t="inlineStr">
         <is>
@@ -13176,9 +13931,11 @@
       </c>
       <c r="G179" s="86">
         <f>I179+$C$173/$C$172/J179</f>
+        <v/>
       </c>
       <c r="H179" s="87">
         <f>G179*$C$172</f>
+        <v/>
       </c>
       <c r="I179" s="86" t="n">
         <v>7.779</v>
@@ -13200,6 +13957,7 @@
       </c>
       <c r="C180" s="88">
         <f>H180</f>
+        <v/>
       </c>
       <c r="E180" s="79" t="inlineStr">
         <is>
@@ -13213,9 +13971,11 @@
       </c>
       <c r="G180" s="86">
         <f>I180+$C$173/$C$172/J180</f>
+        <v/>
       </c>
       <c r="H180" s="87">
         <f>G180*$C$172</f>
+        <v/>
       </c>
       <c r="I180" s="86" t="n">
         <v>11.017</v>
@@ -13237,6 +13997,7 @@
       </c>
       <c r="C181" s="88">
         <f>H181</f>
+        <v/>
       </c>
       <c r="E181" s="79" t="inlineStr">
         <is>
@@ -13250,9 +14011,11 @@
       </c>
       <c r="G181" s="86">
         <f>I181+$C$173/$C$172/J181</f>
+        <v/>
       </c>
       <c r="H181" s="87">
         <f>G181*$C$172</f>
+        <v/>
       </c>
       <c r="I181" s="86" t="n">
         <v>14.144</v>
@@ -13274,6 +14037,7 @@
       </c>
       <c r="C182" s="88">
         <f>H182</f>
+        <v/>
       </c>
       <c r="E182" s="79" t="inlineStr">
         <is>
@@ -13287,9 +14051,11 @@
       </c>
       <c r="G182" s="86">
         <f>I182+$C$173/$C$172/J182</f>
+        <v/>
       </c>
       <c r="H182" s="87">
         <f>G182*$C$172</f>
+        <v/>
       </c>
       <c r="I182" s="86" t="n">
         <v>17.655</v>
@@ -13311,6 +14077,7 @@
       </c>
       <c r="C183" s="88">
         <f>H183</f>
+        <v/>
       </c>
       <c r="E183" s="79" t="inlineStr">
         <is>
@@ -13324,9 +14091,11 @@
       </c>
       <c r="G183" s="86">
         <f>I183+$C$173/$C$172/J183</f>
+        <v/>
       </c>
       <c r="H183" s="87">
         <f>G183*$C$172</f>
+        <v/>
       </c>
       <c r="I183" s="86" t="n">
         <v>20.469</v>
@@ -13348,6 +14117,7 @@
       </c>
       <c r="C184" s="89">
         <f>H184</f>
+        <v/>
       </c>
       <c r="E184" s="84" t="inlineStr">
         <is>
@@ -13361,9 +14131,11 @@
       </c>
       <c r="G184" s="82">
         <f>I184+$C$173/$C$172/J184</f>
+        <v/>
       </c>
       <c r="H184" s="83">
         <f>G184*$C$172</f>
+        <v/>
       </c>
       <c r="I184" s="82" t="n">
         <v>5.45</v>
@@ -13385,6 +14157,7 @@
       </c>
       <c r="C185" s="89">
         <f>H185</f>
+        <v/>
       </c>
       <c r="E185" s="84" t="inlineStr">
         <is>
@@ -13398,9 +14171,11 @@
       </c>
       <c r="G185" s="82">
         <f>I185+$C$173/$C$172/J185</f>
+        <v/>
       </c>
       <c r="H185" s="83">
         <f>G185*$C$172</f>
+        <v/>
       </c>
       <c r="I185" s="82" t="n">
         <v>8.449999999999999</v>
@@ -13422,6 +14197,7 @@
       </c>
       <c r="C186" s="89">
         <f>H186</f>
+        <v/>
       </c>
       <c r="E186" s="84" t="inlineStr">
         <is>
@@ -13435,9 +14211,11 @@
       </c>
       <c r="G186" s="82">
         <f>I186+$C$173/$C$172/J186</f>
+        <v/>
       </c>
       <c r="H186" s="83">
         <f>G186*$C$172</f>
+        <v/>
       </c>
       <c r="I186" s="82" t="n">
         <v>12.4</v>
@@ -13459,6 +14237,7 @@
       </c>
       <c r="C187" s="89">
         <f>H187</f>
+        <v/>
       </c>
       <c r="E187" s="84" t="inlineStr">
         <is>
@@ -13472,9 +14251,11 @@
       </c>
       <c r="G187" s="82">
         <f>I187+$C$173/$C$172/J187</f>
+        <v/>
       </c>
       <c r="H187" s="83">
         <f>G187*$C$172</f>
+        <v/>
       </c>
       <c r="I187" s="82" t="n">
         <v>15.4</v>
@@ -13496,6 +14277,7 @@
       </c>
       <c r="C188" s="89">
         <f>H188</f>
+        <v/>
       </c>
       <c r="E188" s="84" t="inlineStr">
         <is>
@@ -13509,9 +14291,11 @@
       </c>
       <c r="G188" s="82">
         <f>I188+$C$173/$C$172/J188</f>
+        <v/>
       </c>
       <c r="H188" s="83">
         <f>G188*$C$172</f>
+        <v/>
       </c>
       <c r="I188" s="82" t="n">
         <v>18.7</v>
@@ -13533,6 +14317,7 @@
       </c>
       <c r="C189" s="89">
         <f>H189</f>
+        <v/>
       </c>
       <c r="E189" s="84" t="inlineStr">
         <is>
@@ -13546,9 +14331,11 @@
       </c>
       <c r="G189" s="82">
         <f>I189+$C$173/$C$172/J189</f>
+        <v/>
       </c>
       <c r="H189" s="83">
         <f>G189*$C$172</f>
+        <v/>
       </c>
       <c r="I189" s="82" t="n">
         <v>21.4</v>
@@ -13570,6 +14357,7 @@
       </c>
       <c r="C190" s="89">
         <f>H190</f>
+        <v/>
       </c>
       <c r="E190" s="84" t="inlineStr">
         <is>
@@ -13583,9 +14371,11 @@
       </c>
       <c r="G190" s="82">
         <f>I190+$C$173/$C$172/J190</f>
+        <v/>
       </c>
       <c r="H190" s="83">
         <f>G190*$C$172</f>
+        <v/>
       </c>
       <c r="I190" s="82" t="n">
         <v>5.5</v>
@@ -13607,6 +14397,7 @@
       </c>
       <c r="C191" s="89">
         <f>H191</f>
+        <v/>
       </c>
       <c r="E191" s="84" t="inlineStr">
         <is>
@@ -13620,9 +14411,11 @@
       </c>
       <c r="G191" s="82">
         <f>I191+$C$173/$C$172/J191</f>
+        <v/>
       </c>
       <c r="H191" s="83">
         <f>G191*$C$172</f>
+        <v/>
       </c>
       <c r="I191" s="82" t="n">
         <v>8.5</v>
@@ -13644,6 +14437,7 @@
       </c>
       <c r="C192" s="89">
         <f>H192</f>
+        <v/>
       </c>
       <c r="E192" s="84" t="inlineStr">
         <is>
@@ -13657,9 +14451,11 @@
       </c>
       <c r="G192" s="82">
         <f>I192+$C$173/$C$172/J192</f>
+        <v/>
       </c>
       <c r="H192" s="83">
         <f>G192*$C$172</f>
+        <v/>
       </c>
       <c r="I192" s="82" t="n">
         <v>12.4</v>
@@ -13681,6 +14477,7 @@
       </c>
       <c r="C193" s="89">
         <f>H193</f>
+        <v/>
       </c>
       <c r="E193" s="84" t="inlineStr">
         <is>
@@ -13694,9 +14491,11 @@
       </c>
       <c r="G193" s="82">
         <f>I193+$C$173/$C$172/J193</f>
+        <v/>
       </c>
       <c r="H193" s="83">
         <f>G193*$C$172</f>
+        <v/>
       </c>
       <c r="I193" s="82" t="n">
         <v>15.5</v>
@@ -13718,6 +14517,7 @@
       </c>
       <c r="C194" s="89">
         <f>H194</f>
+        <v/>
       </c>
       <c r="E194" s="84" t="inlineStr">
         <is>
@@ -13731,9 +14531,11 @@
       </c>
       <c r="G194" s="82">
         <f>I194+$C$173/$C$172/J194</f>
+        <v/>
       </c>
       <c r="H194" s="83">
         <f>G194*$C$172</f>
+        <v/>
       </c>
       <c r="I194" s="82" t="n">
         <v>18.8</v>
@@ -13755,6 +14557,7 @@
       </c>
       <c r="C195" s="89">
         <f>H195</f>
+        <v/>
       </c>
       <c r="E195" s="84" t="inlineStr">
         <is>
@@ -13768,9 +14571,11 @@
       </c>
       <c r="G195" s="82">
         <f>I195+$C$173/$C$172/J195</f>
+        <v/>
       </c>
       <c r="H195" s="83">
         <f>G195*$C$172</f>
+        <v/>
       </c>
       <c r="I195" s="82" t="n">
         <v>21.5</v>
@@ -13792,6 +14597,7 @@
       </c>
       <c r="C196" s="88">
         <f>H196</f>
+        <v/>
       </c>
       <c r="E196" s="79" t="inlineStr">
         <is>
@@ -13805,9 +14611,11 @@
       </c>
       <c r="G196" s="86">
         <f>I196+$C$173/$C$172/J196</f>
+        <v/>
       </c>
       <c r="H196" s="87">
         <f>G196*$C$172</f>
+        <v/>
       </c>
       <c r="I196" s="86" t="n">
         <v>2.715</v>
@@ -13829,6 +14637,7 @@
       </c>
       <c r="C197" s="88">
         <f>H197</f>
+        <v/>
       </c>
       <c r="E197" s="79" t="inlineStr">
         <is>
@@ -13842,9 +14651,11 @@
       </c>
       <c r="G197" s="86">
         <f>I197+$C$173/$C$172/J197</f>
+        <v/>
       </c>
       <c r="H197" s="87">
         <f>G197*$C$172</f>
+        <v/>
       </c>
       <c r="I197" s="86" t="n">
         <v>4.873</v>
@@ -13866,6 +14677,7 @@
       </c>
       <c r="C198" s="88">
         <f>H198</f>
+        <v/>
       </c>
       <c r="E198" s="79" t="inlineStr">
         <is>
@@ -13879,9 +14691,11 @@
       </c>
       <c r="G198" s="86">
         <f>I198+$C$173/$C$172/J198</f>
+        <v/>
       </c>
       <c r="H198" s="87">
         <f>G198*$C$172</f>
+        <v/>
       </c>
       <c r="I198" s="86" t="n">
         <v>7.553</v>
@@ -13903,6 +14717,7 @@
       </c>
       <c r="C199" s="88">
         <f>H199</f>
+        <v/>
       </c>
       <c r="E199" s="79" t="inlineStr">
         <is>
@@ -13916,9 +14731,11 @@
       </c>
       <c r="G199" s="86">
         <f>I199+$C$173/$C$172/J199</f>
+        <v/>
       </c>
       <c r="H199" s="87">
         <f>G199*$C$172</f>
+        <v/>
       </c>
       <c r="I199" s="86" t="n">
         <v>9.882999999999999</v>
@@ -13940,6 +14757,7 @@
       </c>
       <c r="C200" s="88">
         <f>H200</f>
+        <v/>
       </c>
       <c r="E200" s="79" t="inlineStr">
         <is>
@@ -13953,9 +14771,11 @@
       </c>
       <c r="G200" s="86">
         <f>I200+$C$173/$C$172/J200</f>
+        <v/>
       </c>
       <c r="H200" s="87">
         <f>G200*$C$172</f>
+        <v/>
       </c>
       <c r="I200" s="86" t="n">
         <v>12.435</v>
@@ -13977,6 +14797,7 @@
       </c>
       <c r="C201" s="88">
         <f>H201</f>
+        <v/>
       </c>
       <c r="E201" s="79" t="inlineStr">
         <is>
@@ -13990,9 +14811,11 @@
       </c>
       <c r="G201" s="86">
         <f>I201+$C$173/$C$172/J201</f>
+        <v/>
       </c>
       <c r="H201" s="87">
         <f>G201*$C$172</f>
+        <v/>
       </c>
       <c r="I201" s="86" t="n">
         <v>15.039</v>
@@ -14014,6 +14837,7 @@
       </c>
       <c r="C202" s="89">
         <f>H202</f>
+        <v/>
       </c>
       <c r="E202" s="84" t="inlineStr">
         <is>
@@ -14027,9 +14851,11 @@
       </c>
       <c r="G202" s="82">
         <f>I202+$C$173/$C$172/J202</f>
+        <v/>
       </c>
       <c r="H202" s="83">
         <f>G202*$C$172</f>
+        <v/>
       </c>
       <c r="I202" s="82" t="n">
         <v>2.8</v>
@@ -14051,6 +14877,7 @@
       </c>
       <c r="C203" s="89">
         <f>H203</f>
+        <v/>
       </c>
       <c r="E203" s="84" t="inlineStr">
         <is>
@@ -14064,9 +14891,11 @@
       </c>
       <c r="G203" s="82">
         <f>I203+$C$173/$C$172/J203</f>
+        <v/>
       </c>
       <c r="H203" s="83">
         <f>G203*$C$172</f>
+        <v/>
       </c>
       <c r="I203" s="82" t="n">
         <v>5.2</v>
@@ -14088,6 +14917,7 @@
       </c>
       <c r="C204" s="89">
         <f>H204</f>
+        <v/>
       </c>
       <c r="E204" s="84" t="inlineStr">
         <is>
@@ -14101,9 +14931,11 @@
       </c>
       <c r="G204" s="82">
         <f>I204+$C$173/$C$172/J204</f>
+        <v/>
       </c>
       <c r="H204" s="83">
         <f>G204*$C$172</f>
+        <v/>
       </c>
       <c r="I204" s="82" t="n">
         <v>8.15</v>
@@ -14125,6 +14957,7 @@
       </c>
       <c r="C205" s="89">
         <f>H205</f>
+        <v/>
       </c>
       <c r="E205" s="84" t="inlineStr">
         <is>
@@ -14138,9 +14971,11 @@
       </c>
       <c r="G205" s="82">
         <f>I205+$C$173/$C$172/J205</f>
+        <v/>
       </c>
       <c r="H205" s="83">
         <f>G205*$C$172</f>
+        <v/>
       </c>
       <c r="I205" s="82" t="n">
         <v>10.7</v>
@@ -14162,6 +14997,7 @@
       </c>
       <c r="C206" s="89">
         <f>H206</f>
+        <v/>
       </c>
       <c r="E206" s="84" t="inlineStr">
         <is>
@@ -14175,9 +15011,11 @@
       </c>
       <c r="G206" s="82">
         <f>I206+$C$173/$C$172/J206</f>
+        <v/>
       </c>
       <c r="H206" s="83">
         <f>G206*$C$172</f>
+        <v/>
       </c>
       <c r="I206" s="82" t="n">
         <v>13.4</v>
@@ -14199,6 +15037,7 @@
       </c>
       <c r="C207" s="89">
         <f>H207</f>
+        <v/>
       </c>
       <c r="E207" s="84" t="inlineStr">
         <is>
@@ -14212,9 +15051,11 @@
       </c>
       <c r="G207" s="82">
         <f>I207+$C$173/$C$172/J207</f>
+        <v/>
       </c>
       <c r="H207" s="83">
         <f>G207*$C$172</f>
+        <v/>
       </c>
       <c r="I207" s="82" t="n">
         <v>16</v>
@@ -14236,6 +15077,7 @@
       </c>
       <c r="C208" s="89">
         <f>H208</f>
+        <v/>
       </c>
       <c r="E208" s="84" t="inlineStr">
         <is>
@@ -14249,9 +15091,11 @@
       </c>
       <c r="G208" s="82">
         <f>I208+$C$173/$C$172/J208</f>
+        <v/>
       </c>
       <c r="H208" s="83">
         <f>G208*$C$172</f>
+        <v/>
       </c>
       <c r="I208" s="82" t="n">
         <v>2.8</v>
@@ -14273,6 +15117,7 @@
       </c>
       <c r="C209" s="89">
         <f>H209</f>
+        <v/>
       </c>
       <c r="E209" s="84" t="inlineStr">
         <is>
@@ -14286,9 +15131,11 @@
       </c>
       <c r="G209" s="82">
         <f>I209+$C$173/$C$172/J209</f>
+        <v/>
       </c>
       <c r="H209" s="83">
         <f>G209*$C$172</f>
+        <v/>
       </c>
       <c r="I209" s="82" t="n">
         <v>5.35</v>
@@ -14310,6 +15157,7 @@
       </c>
       <c r="C210" s="89">
         <f>H210</f>
+        <v/>
       </c>
       <c r="E210" s="84" t="inlineStr">
         <is>
@@ -14323,9 +15171,11 @@
       </c>
       <c r="G210" s="82">
         <f>I210+$C$173/$C$172/J210</f>
+        <v/>
       </c>
       <c r="H210" s="83">
         <f>G210*$C$172</f>
+        <v/>
       </c>
       <c r="I210" s="82" t="n">
         <v>7.5</v>
@@ -14347,6 +15197,7 @@
       </c>
       <c r="C211" s="89">
         <f>H211</f>
+        <v/>
       </c>
       <c r="E211" s="84" t="inlineStr">
         <is>
@@ -14360,9 +15211,11 @@
       </c>
       <c r="G211" s="82">
         <f>I211+$C$173/$C$172/J211</f>
+        <v/>
       </c>
       <c r="H211" s="83">
         <f>G211*$C$172</f>
+        <v/>
       </c>
       <c r="I211" s="82" t="n">
         <v>8.699999999999999</v>
@@ -14384,6 +15237,7 @@
       </c>
       <c r="C212" s="89">
         <f>H212</f>
+        <v/>
       </c>
       <c r="E212" s="84" t="inlineStr">
         <is>
@@ -14397,9 +15251,11 @@
       </c>
       <c r="G212" s="82">
         <f>I212+$C$173/$C$172/J212</f>
+        <v/>
       </c>
       <c r="H212" s="83">
         <f>G212*$C$172</f>
+        <v/>
       </c>
       <c r="I212" s="82" t="n">
         <v>11.05</v>
@@ -14421,6 +15277,7 @@
       </c>
       <c r="C213" s="89">
         <f>H213</f>
+        <v/>
       </c>
       <c r="E213" s="84" t="inlineStr">
         <is>
@@ -14434,9 +15291,11 @@
       </c>
       <c r="G213" s="82">
         <f>I213+$C$173/$C$172/J213</f>
+        <v/>
       </c>
       <c r="H213" s="83">
         <f>G213*$C$172</f>
+        <v/>
       </c>
       <c r="I213" s="82" t="n">
         <v>13.2</v>
@@ -14458,6 +15317,7 @@
       </c>
       <c r="C214" s="89">
         <f>H214</f>
+        <v/>
       </c>
       <c r="E214" s="84" t="inlineStr">
         <is>
@@ -14471,9 +15331,11 @@
       </c>
       <c r="G214" s="82">
         <f>I214+$C$173/$C$172/J214</f>
+        <v/>
       </c>
       <c r="H214" s="83">
         <f>G214*$C$172</f>
+        <v/>
       </c>
       <c r="I214" s="82" t="n">
         <v>20.324</v>
@@ -14495,6 +15357,7 @@
       </c>
       <c r="C215" s="89">
         <f>H215</f>
+        <v/>
       </c>
       <c r="E215" s="84" t="inlineStr">
         <is>
@@ -14508,9 +15371,11 @@
       </c>
       <c r="G215" s="82">
         <f>I215+$C$173/$C$172/J215</f>
+        <v/>
       </c>
       <c r="H215" s="83">
         <f>G215*$C$172</f>
+        <v/>
       </c>
       <c r="I215" s="82" t="n">
         <v>24.043</v>
@@ -14519,7 +15384,6 @@
         <v>933</v>
       </c>
     </row>
-    <row r="216"/>
     <row r="217">
       <c r="A217" s="84" t="inlineStr">
         <is>
@@ -14540,6 +15404,7 @@
       </c>
       <c r="C218" s="89">
         <f t="array" ref="C218">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="E218" s="84" t="inlineStr">
         <is>
@@ -14553,9 +15418,11 @@
       </c>
       <c r="G218" s="82">
         <f t="array" ref="G218">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H218" s="83">
         <f>G218*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="219">
@@ -14571,6 +15438,7 @@
       </c>
       <c r="C219" s="89">
         <f t="array" ref="C219">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="E219" s="84" t="inlineStr">
         <is>
@@ -14584,9 +15452,11 @@
       </c>
       <c r="G219" s="82">
         <f t="array" ref="G219">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H219" s="83">
         <f>G219*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="220">
@@ -14602,6 +15472,7 @@
       </c>
       <c r="C220" s="89">
         <f t="array" ref="C220">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="E220" s="84" t="inlineStr">
         <is>
@@ -14615,9 +15486,11 @@
       </c>
       <c r="G220" s="82">
         <f t="array" ref="G220">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H220" s="83">
         <f>G220*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="221">
@@ -14633,6 +15506,7 @@
       </c>
       <c r="C221" s="89">
         <f t="array" ref="C221">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="E221" s="84" t="inlineStr">
         <is>
@@ -14646,9 +15520,11 @@
       </c>
       <c r="G221" s="82">
         <f t="array" ref="G221">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H221" s="83">
         <f>G221*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="222">
@@ -14664,6 +15540,7 @@
       </c>
       <c r="C222" s="89">
         <f t="array" ref="C222">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="E222" s="84" t="inlineStr">
         <is>
@@ -14677,9 +15554,11 @@
       </c>
       <c r="G222" s="82">
         <f t="array" ref="G222">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H222" s="83">
         <f>G222*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="223">
@@ -14695,6 +15574,7 @@
       </c>
       <c r="C223" s="89">
         <f t="array" ref="C223">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="E223" s="84" t="inlineStr">
         <is>
@@ -14708,9 +15588,11 @@
       </c>
       <c r="G223" s="82">
         <f t="array" ref="G223">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H223" s="83">
         <f>G223*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="224">
@@ -14726,6 +15608,7 @@
       </c>
       <c r="C224" s="89">
         <f t="array" ref="C224">INDEX($C$178:$C$215,MATCH("LND-MAR-15",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="E224" s="84" t="inlineStr">
         <is>
@@ -14739,9 +15622,11 @@
       </c>
       <c r="G224" s="82">
         <f t="array" ref="G224">INDEX($G$178:$G$215,MATCH("LND-MAR-15",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H224" s="83">
         <f>G224*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="225">
@@ -14757,6 +15642,7 @@
       </c>
       <c r="C225" s="89">
         <f t="array" ref="C225">INDEX($C$178:$C$215,MATCH("LND-MAR-18",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="E225" s="84" t="inlineStr">
         <is>
@@ -14770,12 +15656,13 @@
       </c>
       <c r="G225" s="82">
         <f t="array" ref="G225">INDEX($G$178:$G$215,MATCH("LND-MAR-18",$A$178:$A$215,0))</f>
+        <v/>
       </c>
       <c r="H225" s="83">
         <f>G225*$C$172</f>
-      </c>
-    </row>
-    <row r="226"/>
+        <v/>
+      </c>
+    </row>
     <row r="227">
       <c r="A227" s="84" t="inlineStr">
         <is>
@@ -14806,6 +15693,7 @@
       </c>
       <c r="C228" s="89">
         <f>H228</f>
+        <v/>
       </c>
       <c r="E228" s="84" t="inlineStr">
         <is>
@@ -14822,6 +15710,7 @@
       </c>
       <c r="H228" s="83">
         <f>G228*$C$172</f>
+        <v/>
       </c>
     </row>
     <row r="229">
@@ -14837,6 +15726,7 @@
       </c>
       <c r="C229" s="89">
         <f>H229</f>
+        <v/>
       </c>
       <c r="E229" s="84" t="inlineStr">
         <is>
@@ -14853,9 +15743,9 @@
       </c>
       <c r="H229" s="83">
         <f>G229*$C$172</f>
-      </c>
-    </row>
-    <row r="230"/>
+        <v/>
+      </c>
+    </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
@@ -14876,6 +15766,7 @@
       </c>
       <c r="C232">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-18",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -14896,6 +15787,7 @@
       </c>
       <c r="C233">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-18",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -14916,6 +15808,7 @@
       </c>
       <c r="C234">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-15",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -14936,6 +15829,7 @@
       </c>
       <c r="C235">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-15",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -14956,6 +15850,7 @@
       </c>
       <c r="C236">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-12",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -14976,6 +15871,7 @@
       </c>
       <c r="C237">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-12",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -14996,6 +15892,7 @@
       </c>
       <c r="C238">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-9",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -15016,6 +15913,7 @@
       </c>
       <c r="C239">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-9",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -15036,6 +15934,7 @@
       </c>
       <c r="C240">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-6",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -15056,6 +15955,7 @@
       </c>
       <c r="C241">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-6",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -15076,6 +15976,7 @@
       </c>
       <c r="C242">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-3",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -15096,6 +15997,7 @@
       </c>
       <c r="C243">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-3",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -15116,6 +16018,7 @@
       </c>
       <c r="C244">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-18",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -15136,6 +16039,7 @@
       </c>
       <c r="C245">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-18",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -15156,6 +16060,7 @@
       </c>
       <c r="C246">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-15",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -15176,6 +16081,7 @@
       </c>
       <c r="C247">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-12",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -15196,6 +16102,7 @@
       </c>
       <c r="C248">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-9",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -15216,10 +16123,156 @@
       </c>
       <c r="C249">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-6",$A$178:$A$215,0))+$C$175</f>
+        <v/>
       </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="91" t="inlineStr">
+        <is>
+          <t>METAL (added 19 Oct 2026). Value EMPTY: price not yet received. Fill column C; METAL parts cost 0 until filled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="84" t="inlineStr">
+        <is>
+          <t>METAL_A</t>
+        </is>
+      </c>
+      <c r="B252" s="84" t="inlineStr">
+        <is>
+          <t>Metal tier A (exposed, long), per m³ of component</t>
+        </is>
+      </c>
+      <c r="C252" s="89" t="n"/>
+      <c r="E252" s="84" t="inlineStr">
+        <is>
+          <t>IDR/m³</t>
+        </is>
+      </c>
+      <c r="F252" s="84" t="inlineStr">
+        <is>
+          <t>EMPTY: waiting for price</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="84" t="inlineStr">
+        <is>
+          <t>METAL_B</t>
+        </is>
+      </c>
+      <c r="B253" s="84" t="inlineStr">
+        <is>
+          <t>Metal tier B</t>
+        </is>
+      </c>
+      <c r="C253" s="89" t="n"/>
+      <c r="E253" s="84" t="inlineStr">
+        <is>
+          <t>IDR/m³</t>
+        </is>
+      </c>
+      <c r="F253" s="84" t="inlineStr">
+        <is>
+          <t>EMPTY: waiting for price</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="84" t="inlineStr">
+        <is>
+          <t>METAL_C</t>
+        </is>
+      </c>
+      <c r="B254" s="84" t="inlineStr">
+        <is>
+          <t>Metal tier C</t>
+        </is>
+      </c>
+      <c r="C254" s="89" t="n"/>
+      <c r="E254" s="84" t="inlineStr">
+        <is>
+          <t>IDR/m³</t>
+        </is>
+      </c>
+      <c r="F254" s="84" t="inlineStr">
+        <is>
+          <t>EMPTY: waiting for price</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="84" t="inlineStr">
+        <is>
+          <t>METAL_D</t>
+        </is>
+      </c>
+      <c r="B255" s="84" t="inlineStr">
+        <is>
+          <t>Metal tier D</t>
+        </is>
+      </c>
+      <c r="C255" s="89" t="n"/>
+      <c r="E255" s="84" t="inlineStr">
+        <is>
+          <t>IDR/m³</t>
+        </is>
+      </c>
+      <c r="F255" s="84" t="inlineStr">
+        <is>
+          <t>EMPTY: waiting for price</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="84" t="inlineStr">
+        <is>
+          <t>metal_brass</t>
+        </is>
+      </c>
+      <c r="B256" s="84" t="inlineStr">
+        <is>
+          <t>Brass, per kg (reference)</t>
+        </is>
+      </c>
+      <c r="C256" s="89" t="n"/>
+      <c r="E256" s="84" t="inlineStr">
+        <is>
+          <t>IDR/kg</t>
+        </is>
+      </c>
+      <c r="F256" s="84" t="inlineStr">
+        <is>
+          <t>EMPTY: waiting for price</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="84" t="inlineStr">
+        <is>
+          <t>metal_steel</t>
+        </is>
+      </c>
+      <c r="B257" s="84" t="inlineStr">
+        <is>
+          <t>Steel / hollow section, per kg (reference)</t>
+        </is>
+      </c>
+      <c r="C257" s="89" t="n"/>
+      <c r="E257" s="84" t="inlineStr">
+        <is>
+          <t>IDR/kg</t>
+        </is>
+      </c>
+      <c r="F257" s="84" t="inlineStr">
+        <is>
+          <t>EMPTY: waiting for price</t>
         </is>
       </c>
     </row>
@@ -16668,6 +17721,7 @@
       </c>
       <c r="G1" s="9">
         <f t="array" ref="G1">IFERROR(IF(INDEX(ITEMS!$E$5:$E$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$E$5:$E$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H1" s="67" t="n"/>
       <c r="I1" s="67" t="n"/>
@@ -16675,6 +17729,7 @@
       <c r="K1" s="68" t="n"/>
       <c r="L1" s="69">
         <f>IF(G6="","photo",_xludf.IMAGE(G6))</f>
+        <v/>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="59">
@@ -16685,6 +17740,7 @@
       </c>
       <c r="C2" s="9">
         <f t="array" ref="C2">IFERROR(IF(INDEX(ITEMS!$D$5:$D$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$D$5:$D$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="D2" s="66" t="inlineStr">
         <is>
@@ -16693,6 +17749,7 @@
       </c>
       <c r="G2" s="9">
         <f t="array" ref="G2">IFERROR(IF(INDEX(ITEMS!$F$5:$F$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$F$5:$F$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H2" s="67" t="n"/>
       <c r="I2" s="67" t="n"/>
@@ -16707,6 +17764,7 @@
       </c>
       <c r="C3" s="9">
         <f t="array" ref="C3">IFERROR(INDEX(ITEMS!$B$5:$B$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))&amp;" / "&amp;INDEX(ITEMS!$W$5:$W$120,MATCH($C$1,ITEMS!$C$5:$C$120,0)),"")</f>
+        <v/>
       </c>
       <c r="D3" s="66" t="inlineStr">
         <is>
@@ -16715,6 +17773,7 @@
       </c>
       <c r="G3" s="9">
         <f t="array" ref="G3">IFERROR(IF(INDEX(ITEMS!$G$5:$G$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$G$5:$G$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H3" s="67" t="n"/>
       <c r="I3" s="67" t="n"/>
@@ -16729,6 +17788,7 @@
       </c>
       <c r="C4" s="9">
         <f t="array" ref="C4">IFERROR(IF(INDEX(ITEMS!$H$5:$H$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$H$5:$H$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="D4" s="66" t="inlineStr">
         <is>
@@ -16737,6 +17797,7 @@
       </c>
       <c r="G4" s="9">
         <f t="array" ref="G4">IFERROR(IF(INDEX(ITEMS!$I$5:$I$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$I$5:$I$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H4" s="67" t="n"/>
       <c r="I4" s="67" t="n"/>
@@ -16761,6 +17822,7 @@
       </c>
       <c r="G5" s="9">
         <f t="array" ref="G5">IFERROR(IF(INDEX(ITEMS!$V$5:$V$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$V$5:$V$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="H5" s="67" t="n"/>
       <c r="I5" s="67" t="n"/>
@@ -16797,6 +17859,7 @@
       </c>
       <c r="C7" s="9">
         <f t="array" ref="C7">IFERROR(IF(INDEX(ITEMS!$X$5:$X$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))="","",INDEX(ITEMS!$X$5:$X$120,MATCH($C$1,ITEMS!$C$5:$C$120,0))),"")</f>
+        <v/>
       </c>
       <c r="D7" s="66" t="inlineStr">
         <is>
@@ -16888,19 +17951,24 @@
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="14">
         <f>IF(D11="","",D11+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="I11" s="14">
         <f>IF(E11="","",E11+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="J11" s="14">
         <f>IF(F11="","",F11+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="17">
         <f>IF(H11="","",2*(H11*I11+H11*J11+I11*J11)/1000000*IF(G11="",1,G11))</f>
+        <v/>
       </c>
       <c r="M11" s="19">
         <f>IF(H11="","",H11*I11*J11/1000000000*IF(G11="",1,G11))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -16915,19 +17983,24 @@
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="14">
         <f>IF(D12="","",D12+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="I12" s="14">
         <f>IF(E12="","",E12+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="J12" s="14">
         <f>IF(F12="","",F12+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="17">
         <f>IF(H12="","",2*(H12*I12+H12*J12+I12*J12)/1000000*IF(G12="",1,G12))</f>
+        <v/>
       </c>
       <c r="M12" s="19">
         <f>IF(H12="","",H12*I12*J12/1000000000*IF(G12="",1,G12))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -16942,19 +18015,24 @@
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="14">
         <f>IF(D13="","",D13+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="I13" s="14">
         <f>IF(E13="","",E13+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="J13" s="14">
         <f>IF(F13="","",F13+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="17">
         <f>IF(H13="","",2*(H13*I13+H13*J13+I13*J13)/1000000*IF(G13="",1,G13))</f>
+        <v/>
       </c>
       <c r="M13" s="19">
         <f>IF(H13="","",H13*I13*J13/1000000000*IF(G13="",1,G13))</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -16969,19 +18047,24 @@
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="14">
         <f>IF(D14="","",D14+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="I14" s="14">
         <f>IF(E14="","",E14+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="J14" s="14">
         <f>IF(F14="","",F14+LISTS!$F$9)</f>
+        <v/>
       </c>
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="17">
         <f>IF(H14="","",2*(H14*I14+H14*J14+I14*J14)/1000000*IF(G14="",1,G14))</f>
+        <v/>
       </c>
       <c r="M14" s="19">
         <f>IF(H14="","",H14*I14*J14/1000000000*IF(G14="",1,G14))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -16997,6 +18080,7 @@
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="22">
         <f>IF(D11="",1,SUM(G11:G14)+COUNTIFS(D11:D14,"&lt;&gt;",G11:G14,""))</f>
+        <v/>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -17008,9 +18092,11 @@
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="23">
         <f>IF(D11="",IF(OR(G1="",G2="",G3=""),0,2*((G1+LISTS!$F$9)*(G2+LISTS!$F$9)+(G1+LISTS!$F$9)*(G3+LISTS!$F$9)+(G2+LISTS!$F$9)*(G3+LISTS!$F$9))/1000000),SUM(L11:L14))</f>
+        <v/>
       </c>
       <c r="M15" s="24">
         <f>IF(D11="",IF(OR(G1="",G2="",G3=""),0,(G1+LISTS!$F$9)*(G2+LISTS!$F$9)*(G3+LISTS!$F$9)/1000000000),SUM(M11:M14))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -17163,23 +18249,29 @@
       </c>
       <c r="M18" s="25">
         <f>IF(OR(E18="",F18="",G18=""),"",E18*F18*G18/1000000000*IF(H18="",1,H18))</f>
+        <v/>
       </c>
       <c r="N18" s="19">
         <f>IF(OR(E18="",F18=""),"",E18*F18/1000000*IF(H18="",1,H18))</f>
+        <v/>
       </c>
       <c r="O18" s="14">
         <f>IF(E18="","",IF(K18&lt;&gt;"",K18,IF(AND(E18*F18*G18/1000000000&lt;LISTS!$F$4,MAX(E18,F18,G18)&lt;LISTS!$F$5),"D",IF(I18="N","C",IF(J18="Y","A-CURVED",IF(AND(MEDIAN(E18,F18,G18)&lt;=LISTS!$F$10,MAX(E18,F18,G18)&lt;=LISTS!$F$11),"B",IF(MAX(E18,F18,G18)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P18" s="14" t="n"/>
       <c r="Q18" s="14" t="n"/>
       <c r="R18" s="14">
         <f>IF(E18="","",IF(B18="","material?",IF(OR(F18="",G18=""),"size?",IF(I18="","exposed Y/N?",IF(H18="","qty?",IF(B18="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S18" s="12">
         <f t="array" ref="S18">IF(OR(O18="",M18=""),"",IF(B18="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B18&amp;"_"&amp;SUBSTITUTE(O18,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T18" s="12">
         <f>IF(ISNUMBER(S18),M18*S18,"")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -17231,23 +18323,29 @@
       </c>
       <c r="M19" s="25">
         <f>IF(OR(E19="",F19="",G19=""),"",E19*F19*G19/1000000000*IF(H19="",1,H19))</f>
+        <v/>
       </c>
       <c r="N19" s="19">
         <f>IF(OR(E19="",F19=""),"",E19*F19/1000000*IF(H19="",1,H19))</f>
+        <v/>
       </c>
       <c r="O19" s="14">
         <f>IF(E19="","",IF(K19&lt;&gt;"",K19,IF(AND(E19*F19*G19/1000000000&lt;LISTS!$F$4,MAX(E19,F19,G19)&lt;LISTS!$F$5),"D",IF(I19="N","C",IF(J19="Y","A-CURVED",IF(AND(MEDIAN(E19,F19,G19)&lt;=LISTS!$F$10,MAX(E19,F19,G19)&lt;=LISTS!$F$11),"B",IF(MAX(E19,F19,G19)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P19" s="14" t="n"/>
       <c r="Q19" s="14" t="n"/>
       <c r="R19" s="14">
         <f>IF(E19="","",IF(B19="","material?",IF(OR(F19="",G19=""),"size?",IF(I19="","exposed Y/N?",IF(H19="","qty?",IF(B19="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S19" s="12">
         <f t="array" ref="S19">IF(OR(O19="",M19=""),"",IF(B19="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B19&amp;"_"&amp;SUBSTITUTE(O19,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T19" s="12">
         <f>IF(ISNUMBER(S19),M19*S19,"")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -17299,23 +18397,29 @@
       </c>
       <c r="M20" s="25">
         <f>IF(OR(E20="",F20="",G20=""),"",E20*F20*G20/1000000000*IF(H20="",1,H20))</f>
+        <v/>
       </c>
       <c r="N20" s="19">
         <f>IF(OR(E20="",F20=""),"",E20*F20/1000000*IF(H20="",1,H20))</f>
+        <v/>
       </c>
       <c r="O20" s="14">
         <f>IF(E20="","",IF(K20&lt;&gt;"",K20,IF(AND(E20*F20*G20/1000000000&lt;LISTS!$F$4,MAX(E20,F20,G20)&lt;LISTS!$F$5),"D",IF(I20="N","C",IF(J20="Y","A-CURVED",IF(AND(MEDIAN(E20,F20,G20)&lt;=LISTS!$F$10,MAX(E20,F20,G20)&lt;=LISTS!$F$11),"B",IF(MAX(E20,F20,G20)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P20" s="14" t="n"/>
       <c r="Q20" s="14" t="n"/>
       <c r="R20" s="14">
         <f>IF(E20="","",IF(B20="","material?",IF(OR(F20="",G20=""),"size?",IF(I20="","exposed Y/N?",IF(H20="","qty?",IF(B20="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S20" s="12">
         <f t="array" ref="S20">IF(OR(O20="",M20=""),"",IF(B20="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B20&amp;"_"&amp;SUBSTITUTE(O20,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T20" s="12">
         <f>IF(ISNUMBER(S20),M20*S20,"")</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="59">
@@ -17367,23 +18471,29 @@
       </c>
       <c r="M21" s="25">
         <f>IF(OR(E21="",F21="",G21=""),"",E21*F21*G21/1000000000*IF(H21="",1,H21))</f>
+        <v/>
       </c>
       <c r="N21" s="19">
         <f>IF(OR(E21="",F21=""),"",E21*F21/1000000*IF(H21="",1,H21))</f>
+        <v/>
       </c>
       <c r="O21" s="14">
         <f>IF(E21="","",IF(K21&lt;&gt;"",K21,IF(AND(E21*F21*G21/1000000000&lt;LISTS!$F$4,MAX(E21,F21,G21)&lt;LISTS!$F$5),"D",IF(I21="N","C",IF(J21="Y","A-CURVED",IF(AND(MEDIAN(E21,F21,G21)&lt;=LISTS!$F$10,MAX(E21,F21,G21)&lt;=LISTS!$F$11),"B",IF(MAX(E21,F21,G21)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P21" s="14" t="n"/>
       <c r="Q21" s="14" t="n"/>
       <c r="R21" s="14">
         <f>IF(E21="","",IF(B21="","material?",IF(OR(F21="",G21=""),"size?",IF(I21="","exposed Y/N?",IF(H21="","qty?",IF(B21="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S21" s="12">
         <f t="array" ref="S21">IF(OR(O21="",M21=""),"",IF(B21="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B21&amp;"_"&amp;SUBSTITUTE(O21,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T21" s="12">
         <f>IF(ISNUMBER(S21),M21*S21,"")</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="59">
@@ -17435,23 +18545,29 @@
       </c>
       <c r="M22" s="25">
         <f>IF(OR(E22="",F22="",G22=""),"",E22*F22*G22/1000000000*IF(H22="",1,H22))</f>
+        <v/>
       </c>
       <c r="N22" s="19">
         <f>IF(OR(E22="",F22=""),"",E22*F22/1000000*IF(H22="",1,H22))</f>
+        <v/>
       </c>
       <c r="O22" s="14">
         <f>IF(E22="","",IF(K22&lt;&gt;"",K22,IF(AND(E22*F22*G22/1000000000&lt;LISTS!$F$4,MAX(E22,F22,G22)&lt;LISTS!$F$5),"D",IF(I22="N","C",IF(J22="Y","A-CURVED",IF(AND(MEDIAN(E22,F22,G22)&lt;=LISTS!$F$10,MAX(E22,F22,G22)&lt;=LISTS!$F$11),"B",IF(MAX(E22,F22,G22)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P22" s="14" t="n"/>
       <c r="Q22" s="14" t="n"/>
       <c r="R22" s="14">
         <f>IF(E22="","",IF(B22="","material?",IF(OR(F22="",G22=""),"size?",IF(I22="","exposed Y/N?",IF(H22="","qty?",IF(B22="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S22" s="12">
         <f t="array" ref="S22">IF(OR(O22="",M22=""),"",IF(B22="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B22&amp;"_"&amp;SUBSTITUTE(O22,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T22" s="12">
         <f>IF(ISNUMBER(S22),M22*S22,"")</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="59">
@@ -17503,23 +18619,29 @@
       </c>
       <c r="M23" s="25">
         <f>IF(OR(E23="",F23="",G23=""),"",E23*F23*G23/1000000000*IF(H23="",1,H23))</f>
+        <v/>
       </c>
       <c r="N23" s="19">
         <f>IF(OR(E23="",F23=""),"",E23*F23/1000000*IF(H23="",1,H23))</f>
+        <v/>
       </c>
       <c r="O23" s="14">
         <f>IF(E23="","",IF(K23&lt;&gt;"",K23,IF(AND(E23*F23*G23/1000000000&lt;LISTS!$F$4,MAX(E23,F23,G23)&lt;LISTS!$F$5),"D",IF(I23="N","C",IF(J23="Y","A-CURVED",IF(AND(MEDIAN(E23,F23,G23)&lt;=LISTS!$F$10,MAX(E23,F23,G23)&lt;=LISTS!$F$11),"B",IF(MAX(E23,F23,G23)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P23" s="14" t="n"/>
       <c r="Q23" s="14" t="n"/>
       <c r="R23" s="14">
         <f>IF(E23="","",IF(B23="","material?",IF(OR(F23="",G23=""),"size?",IF(I23="","exposed Y/N?",IF(H23="","qty?",IF(B23="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S23" s="12">
         <f t="array" ref="S23">IF(OR(O23="",M23=""),"",IF(B23="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B23&amp;"_"&amp;SUBSTITUTE(O23,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T23" s="12">
         <f>IF(ISNUMBER(S23),M23*S23,"")</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="59">
@@ -17571,23 +18693,29 @@
       </c>
       <c r="M24" s="25">
         <f>IF(OR(E24="",F24="",G24=""),"",E24*F24*G24/1000000000*IF(H24="",1,H24))</f>
+        <v/>
       </c>
       <c r="N24" s="19">
         <f>IF(OR(E24="",F24=""),"",E24*F24/1000000*IF(H24="",1,H24))</f>
+        <v/>
       </c>
       <c r="O24" s="14">
         <f>IF(E24="","",IF(K24&lt;&gt;"",K24,IF(AND(E24*F24*G24/1000000000&lt;LISTS!$F$4,MAX(E24,F24,G24)&lt;LISTS!$F$5),"D",IF(I24="N","C",IF(J24="Y","A-CURVED",IF(AND(MEDIAN(E24,F24,G24)&lt;=LISTS!$F$10,MAX(E24,F24,G24)&lt;=LISTS!$F$11),"B",IF(MAX(E24,F24,G24)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P24" s="14" t="n"/>
       <c r="Q24" s="14" t="n"/>
       <c r="R24" s="14">
         <f>IF(E24="","",IF(B24="","material?",IF(OR(F24="",G24=""),"size?",IF(I24="","exposed Y/N?",IF(H24="","qty?",IF(B24="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S24" s="12">
         <f t="array" ref="S24">IF(OR(O24="",M24=""),"",IF(B24="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B24&amp;"_"&amp;SUBSTITUTE(O24,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T24" s="12">
         <f>IF(ISNUMBER(S24),M24*S24,"")</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="59">
@@ -17639,23 +18767,29 @@
       </c>
       <c r="M25" s="25">
         <f>IF(OR(E25="",F25="",G25=""),"",E25*F25*G25/1000000000*IF(H25="",1,H25))</f>
+        <v/>
       </c>
       <c r="N25" s="19">
         <f>IF(OR(E25="",F25=""),"",E25*F25/1000000*IF(H25="",1,H25))</f>
+        <v/>
       </c>
       <c r="O25" s="14">
         <f>IF(E25="","",IF(K25&lt;&gt;"",K25,IF(AND(E25*F25*G25/1000000000&lt;LISTS!$F$4,MAX(E25,F25,G25)&lt;LISTS!$F$5),"D",IF(I25="N","C",IF(J25="Y","A-CURVED",IF(AND(MEDIAN(E25,F25,G25)&lt;=LISTS!$F$10,MAX(E25,F25,G25)&lt;=LISTS!$F$11),"B",IF(MAX(E25,F25,G25)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P25" s="14" t="n"/>
       <c r="Q25" s="14" t="n"/>
       <c r="R25" s="14">
         <f>IF(E25="","",IF(B25="","material?",IF(OR(F25="",G25=""),"size?",IF(I25="","exposed Y/N?",IF(H25="","qty?",IF(B25="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S25" s="12">
         <f t="array" ref="S25">IF(OR(O25="",M25=""),"",IF(B25="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B25&amp;"_"&amp;SUBSTITUTE(O25,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T25" s="12">
         <f>IF(ISNUMBER(S25),M25*S25,"")</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="59">
@@ -17707,23 +18841,29 @@
       </c>
       <c r="M26" s="25">
         <f>IF(OR(E26="",F26="",G26=""),"",E26*F26*G26/1000000000*IF(H26="",1,H26))</f>
+        <v/>
       </c>
       <c r="N26" s="19">
         <f>IF(OR(E26="",F26=""),"",E26*F26/1000000*IF(H26="",1,H26))</f>
+        <v/>
       </c>
       <c r="O26" s="14">
         <f>IF(E26="","",IF(K26&lt;&gt;"",K26,IF(AND(E26*F26*G26/1000000000&lt;LISTS!$F$4,MAX(E26,F26,G26)&lt;LISTS!$F$5),"D",IF(I26="N","C",IF(J26="Y","A-CURVED",IF(AND(MEDIAN(E26,F26,G26)&lt;=LISTS!$F$10,MAX(E26,F26,G26)&lt;=LISTS!$F$11),"B",IF(MAX(E26,F26,G26)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P26" s="14" t="n"/>
       <c r="Q26" s="14" t="n"/>
       <c r="R26" s="14">
         <f>IF(E26="","",IF(B26="","material?",IF(OR(F26="",G26=""),"size?",IF(I26="","exposed Y/N?",IF(H26="","qty?",IF(B26="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S26" s="12">
         <f t="array" ref="S26">IF(OR(O26="",M26=""),"",IF(B26="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B26&amp;"_"&amp;SUBSTITUTE(O26,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T26" s="12">
         <f>IF(ISNUMBER(S26),M26*S26,"")</f>
+        <v/>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="59">
@@ -17775,23 +18915,29 @@
       </c>
       <c r="M27" s="25">
         <f>IF(OR(E27="",F27="",G27=""),"",E27*F27*G27/1000000000*IF(H27="",1,H27))</f>
+        <v/>
       </c>
       <c r="N27" s="19">
         <f>IF(OR(E27="",F27=""),"",E27*F27/1000000*IF(H27="",1,H27))</f>
+        <v/>
       </c>
       <c r="O27" s="14">
         <f>IF(E27="","",IF(K27&lt;&gt;"",K27,IF(AND(E27*F27*G27/1000000000&lt;LISTS!$F$4,MAX(E27,F27,G27)&lt;LISTS!$F$5),"D",IF(I27="N","C",IF(J27="Y","A-CURVED",IF(AND(MEDIAN(E27,F27,G27)&lt;=LISTS!$F$10,MAX(E27,F27,G27)&lt;=LISTS!$F$11),"B",IF(MAX(E27,F27,G27)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P27" s="14" t="n"/>
       <c r="Q27" s="14" t="n"/>
       <c r="R27" s="14">
         <f>IF(E27="","",IF(B27="","material?",IF(OR(F27="",G27=""),"size?",IF(I27="","exposed Y/N?",IF(H27="","qty?",IF(B27="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S27" s="12">
         <f t="array" ref="S27">IF(OR(O27="",M27=""),"",IF(B27="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B27&amp;"_"&amp;SUBSTITUTE(O27,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T27" s="12">
         <f>IF(ISNUMBER(S27),M27*S27,"")</f>
+        <v/>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="59">
@@ -17843,23 +18989,29 @@
       </c>
       <c r="M28" s="25">
         <f>IF(OR(E28="",F28="",G28=""),"",E28*F28*G28/1000000000*IF(H28="",1,H28))</f>
+        <v/>
       </c>
       <c r="N28" s="19">
         <f>IF(OR(E28="",F28=""),"",E28*F28/1000000*IF(H28="",1,H28))</f>
+        <v/>
       </c>
       <c r="O28" s="14">
         <f>IF(E28="","",IF(K28&lt;&gt;"",K28,IF(AND(E28*F28*G28/1000000000&lt;LISTS!$F$4,MAX(E28,F28,G28)&lt;LISTS!$F$5),"D",IF(I28="N","C",IF(J28="Y","A-CURVED",IF(AND(MEDIAN(E28,F28,G28)&lt;=LISTS!$F$10,MAX(E28,F28,G28)&lt;=LISTS!$F$11),"B",IF(MAX(E28,F28,G28)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P28" s="14" t="n"/>
       <c r="Q28" s="14" t="n"/>
       <c r="R28" s="14">
         <f>IF(E28="","",IF(B28="","material?",IF(OR(F28="",G28=""),"size?",IF(I28="","exposed Y/N?",IF(H28="","qty?",IF(B28="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S28" s="12">
         <f t="array" ref="S28">IF(OR(O28="",M28=""),"",IF(B28="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B28&amp;"_"&amp;SUBSTITUTE(O28,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T28" s="12">
         <f>IF(ISNUMBER(S28),M28*S28,"")</f>
+        <v/>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="59">
@@ -17879,23 +19031,29 @@
       <c r="L29" s="10" t="n"/>
       <c r="M29" s="25">
         <f>IF(OR(E29="",F29="",G29=""),"",E29*F29*G29/1000000000*IF(H29="",1,H29))</f>
+        <v/>
       </c>
       <c r="N29" s="19">
         <f>IF(OR(E29="",F29=""),"",E29*F29/1000000*IF(H29="",1,H29))</f>
+        <v/>
       </c>
       <c r="O29" s="14">
         <f>IF(E29="","",IF(K29&lt;&gt;"",K29,IF(AND(E29*F29*G29/1000000000&lt;LISTS!$F$4,MAX(E29,F29,G29)&lt;LISTS!$F$5),"D",IF(I29="N","C",IF(J29="Y","A-CURVED",IF(AND(MEDIAN(E29,F29,G29)&lt;=LISTS!$F$10,MAX(E29,F29,G29)&lt;=LISTS!$F$11),"B",IF(MAX(E29,F29,G29)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P29" s="14" t="n"/>
       <c r="Q29" s="14" t="n"/>
       <c r="R29" s="14">
         <f>IF(E29="","",IF(B29="","material?",IF(OR(F29="",G29=""),"size?",IF(I29="","exposed Y/N?",IF(H29="","qty?",IF(B29="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S29" s="12">
         <f t="array" ref="S29">IF(OR(O29="",M29=""),"",IF(B29="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B29&amp;"_"&amp;SUBSTITUTE(O29,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T29" s="12">
         <f>IF(ISNUMBER(S29),M29*S29,"")</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="59">
@@ -17915,23 +19073,29 @@
       <c r="L30" s="10" t="n"/>
       <c r="M30" s="25">
         <f>IF(OR(E30="",F30="",G30=""),"",E30*F30*G30/1000000000*IF(H30="",1,H30))</f>
+        <v/>
       </c>
       <c r="N30" s="19">
         <f>IF(OR(E30="",F30=""),"",E30*F30/1000000*IF(H30="",1,H30))</f>
+        <v/>
       </c>
       <c r="O30" s="14">
         <f>IF(E30="","",IF(K30&lt;&gt;"",K30,IF(AND(E30*F30*G30/1000000000&lt;LISTS!$F$4,MAX(E30,F30,G30)&lt;LISTS!$F$5),"D",IF(I30="N","C",IF(J30="Y","A-CURVED",IF(AND(MEDIAN(E30,F30,G30)&lt;=LISTS!$F$10,MAX(E30,F30,G30)&lt;=LISTS!$F$11),"B",IF(MAX(E30,F30,G30)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P30" s="14" t="n"/>
       <c r="Q30" s="14" t="n"/>
       <c r="R30" s="14">
         <f>IF(E30="","",IF(B30="","material?",IF(OR(F30="",G30=""),"size?",IF(I30="","exposed Y/N?",IF(H30="","qty?",IF(B30="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S30" s="12">
         <f t="array" ref="S30">IF(OR(O30="",M30=""),"",IF(B30="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B30&amp;"_"&amp;SUBSTITUTE(O30,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T30" s="12">
         <f>IF(ISNUMBER(S30),M30*S30,"")</f>
+        <v/>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="59">
@@ -17951,23 +19115,29 @@
       <c r="L31" s="10" t="n"/>
       <c r="M31" s="25">
         <f>IF(OR(E31="",F31="",G31=""),"",E31*F31*G31/1000000000*IF(H31="",1,H31))</f>
+        <v/>
       </c>
       <c r="N31" s="19">
         <f>IF(OR(E31="",F31=""),"",E31*F31/1000000*IF(H31="",1,H31))</f>
+        <v/>
       </c>
       <c r="O31" s="14">
         <f>IF(E31="","",IF(K31&lt;&gt;"",K31,IF(AND(E31*F31*G31/1000000000&lt;LISTS!$F$4,MAX(E31,F31,G31)&lt;LISTS!$F$5),"D",IF(I31="N","C",IF(J31="Y","A-CURVED",IF(AND(MEDIAN(E31,F31,G31)&lt;=LISTS!$F$10,MAX(E31,F31,G31)&lt;=LISTS!$F$11),"B",IF(MAX(E31,F31,G31)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P31" s="14" t="n"/>
       <c r="Q31" s="14" t="n"/>
       <c r="R31" s="14">
         <f>IF(E31="","",IF(B31="","material?",IF(OR(F31="",G31=""),"size?",IF(I31="","exposed Y/N?",IF(H31="","qty?",IF(B31="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S31" s="12">
         <f t="array" ref="S31">IF(OR(O31="",M31=""),"",IF(B31="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B31&amp;"_"&amp;SUBSTITUTE(O31,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T31" s="12">
         <f>IF(ISNUMBER(S31),M31*S31,"")</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="59">
@@ -17987,23 +19157,29 @@
       <c r="L32" s="10" t="n"/>
       <c r="M32" s="25">
         <f>IF(OR(E32="",F32="",G32=""),"",E32*F32*G32/1000000000*IF(H32="",1,H32))</f>
+        <v/>
       </c>
       <c r="N32" s="19">
         <f>IF(OR(E32="",F32=""),"",E32*F32/1000000*IF(H32="",1,H32))</f>
+        <v/>
       </c>
       <c r="O32" s="14">
         <f>IF(E32="","",IF(K32&lt;&gt;"",K32,IF(AND(E32*F32*G32/1000000000&lt;LISTS!$F$4,MAX(E32,F32,G32)&lt;LISTS!$F$5),"D",IF(I32="N","C",IF(J32="Y","A-CURVED",IF(AND(MEDIAN(E32,F32,G32)&lt;=LISTS!$F$10,MAX(E32,F32,G32)&lt;=LISTS!$F$11),"B",IF(MAX(E32,F32,G32)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P32" s="14" t="n"/>
       <c r="Q32" s="14" t="n"/>
       <c r="R32" s="14">
         <f>IF(E32="","",IF(B32="","material?",IF(OR(F32="",G32=""),"size?",IF(I32="","exposed Y/N?",IF(H32="","qty?",IF(B32="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S32" s="12">
         <f t="array" ref="S32">IF(OR(O32="",M32=""),"",IF(B32="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B32&amp;"_"&amp;SUBSTITUTE(O32,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T32" s="12">
         <f>IF(ISNUMBER(S32),M32*S32,"")</f>
+        <v/>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="59">
@@ -18023,23 +19199,29 @@
       <c r="L33" s="10" t="n"/>
       <c r="M33" s="25">
         <f>IF(OR(E33="",F33="",G33=""),"",E33*F33*G33/1000000000*IF(H33="",1,H33))</f>
+        <v/>
       </c>
       <c r="N33" s="19">
         <f>IF(OR(E33="",F33=""),"",E33*F33/1000000*IF(H33="",1,H33))</f>
+        <v/>
       </c>
       <c r="O33" s="14">
         <f>IF(E33="","",IF(K33&lt;&gt;"",K33,IF(AND(E33*F33*G33/1000000000&lt;LISTS!$F$4,MAX(E33,F33,G33)&lt;LISTS!$F$5),"D",IF(I33="N","C",IF(J33="Y","A-CURVED",IF(AND(MEDIAN(E33,F33,G33)&lt;=LISTS!$F$10,MAX(E33,F33,G33)&lt;=LISTS!$F$11),"B",IF(MAX(E33,F33,G33)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P33" s="14" t="n"/>
       <c r="Q33" s="14" t="n"/>
       <c r="R33" s="14">
         <f>IF(E33="","",IF(B33="","material?",IF(OR(F33="",G33=""),"size?",IF(I33="","exposed Y/N?",IF(H33="","qty?",IF(B33="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S33" s="12">
         <f t="array" ref="S33">IF(OR(O33="",M33=""),"",IF(B33="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B33&amp;"_"&amp;SUBSTITUTE(O33,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T33" s="12">
         <f>IF(ISNUMBER(S33),M33*S33,"")</f>
+        <v/>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="59">
@@ -18059,23 +19241,29 @@
       <c r="L34" s="10" t="n"/>
       <c r="M34" s="25">
         <f>IF(OR(E34="",F34="",G34=""),"",E34*F34*G34/1000000000*IF(H34="",1,H34))</f>
+        <v/>
       </c>
       <c r="N34" s="19">
         <f>IF(OR(E34="",F34=""),"",E34*F34/1000000*IF(H34="",1,H34))</f>
+        <v/>
       </c>
       <c r="O34" s="14">
         <f>IF(E34="","",IF(K34&lt;&gt;"",K34,IF(AND(E34*F34*G34/1000000000&lt;LISTS!$F$4,MAX(E34,F34,G34)&lt;LISTS!$F$5),"D",IF(I34="N","C",IF(J34="Y","A-CURVED",IF(AND(MEDIAN(E34,F34,G34)&lt;=LISTS!$F$10,MAX(E34,F34,G34)&lt;=LISTS!$F$11),"B",IF(MAX(E34,F34,G34)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P34" s="14" t="n"/>
       <c r="Q34" s="14" t="n"/>
       <c r="R34" s="14">
         <f>IF(E34="","",IF(B34="","material?",IF(OR(F34="",G34=""),"size?",IF(I34="","exposed Y/N?",IF(H34="","qty?",IF(B34="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S34" s="12">
         <f t="array" ref="S34">IF(OR(O34="",M34=""),"",IF(B34="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B34&amp;"_"&amp;SUBSTITUTE(O34,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T34" s="12">
         <f>IF(ISNUMBER(S34),M34*S34,"")</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="59">
@@ -18095,23 +19283,29 @@
       <c r="L35" s="10" t="n"/>
       <c r="M35" s="25">
         <f>IF(OR(E35="",F35="",G35=""),"",E35*F35*G35/1000000000*IF(H35="",1,H35))</f>
+        <v/>
       </c>
       <c r="N35" s="19">
         <f>IF(OR(E35="",F35=""),"",E35*F35/1000000*IF(H35="",1,H35))</f>
+        <v/>
       </c>
       <c r="O35" s="14">
         <f>IF(E35="","",IF(K35&lt;&gt;"",K35,IF(AND(E35*F35*G35/1000000000&lt;LISTS!$F$4,MAX(E35,F35,G35)&lt;LISTS!$F$5),"D",IF(I35="N","C",IF(J35="Y","A-CURVED",IF(AND(MEDIAN(E35,F35,G35)&lt;=LISTS!$F$10,MAX(E35,F35,G35)&lt;=LISTS!$F$11),"B",IF(MAX(E35,F35,G35)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P35" s="14" t="n"/>
       <c r="Q35" s="14" t="n"/>
       <c r="R35" s="14">
         <f>IF(E35="","",IF(B35="","material?",IF(OR(F35="",G35=""),"size?",IF(I35="","exposed Y/N?",IF(H35="","qty?",IF(B35="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S35" s="12">
         <f t="array" ref="S35">IF(OR(O35="",M35=""),"",IF(B35="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B35&amp;"_"&amp;SUBSTITUTE(O35,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T35" s="12">
         <f>IF(ISNUMBER(S35),M35*S35,"")</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="59">
@@ -18131,23 +19325,29 @@
       <c r="L36" s="10" t="n"/>
       <c r="M36" s="25">
         <f>IF(OR(E36="",F36="",G36=""),"",E36*F36*G36/1000000000*IF(H36="",1,H36))</f>
+        <v/>
       </c>
       <c r="N36" s="19">
         <f>IF(OR(E36="",F36=""),"",E36*F36/1000000*IF(H36="",1,H36))</f>
+        <v/>
       </c>
       <c r="O36" s="14">
         <f>IF(E36="","",IF(K36&lt;&gt;"",K36,IF(AND(E36*F36*G36/1000000000&lt;LISTS!$F$4,MAX(E36,F36,G36)&lt;LISTS!$F$5),"D",IF(I36="N","C",IF(J36="Y","A-CURVED",IF(AND(MEDIAN(E36,F36,G36)&lt;=LISTS!$F$10,MAX(E36,F36,G36)&lt;=LISTS!$F$11),"B",IF(MAX(E36,F36,G36)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P36" s="14" t="n"/>
       <c r="Q36" s="14" t="n"/>
       <c r="R36" s="14">
         <f>IF(E36="","",IF(B36="","material?",IF(OR(F36="",G36=""),"size?",IF(I36="","exposed Y/N?",IF(H36="","qty?",IF(B36="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S36" s="12">
         <f t="array" ref="S36">IF(OR(O36="",M36=""),"",IF(B36="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B36&amp;"_"&amp;SUBSTITUTE(O36,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T36" s="12">
         <f>IF(ISNUMBER(S36),M36*S36,"")</f>
+        <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="59">
@@ -18167,23 +19367,29 @@
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="25">
         <f>IF(OR(E37="",F37="",G37=""),"",E37*F37*G37/1000000000*IF(H37="",1,H37))</f>
+        <v/>
       </c>
       <c r="N37" s="19">
         <f>IF(OR(E37="",F37=""),"",E37*F37/1000000*IF(H37="",1,H37))</f>
+        <v/>
       </c>
       <c r="O37" s="14">
         <f>IF(E37="","",IF(K37&lt;&gt;"",K37,IF(AND(E37*F37*G37/1000000000&lt;LISTS!$F$4,MAX(E37,F37,G37)&lt;LISTS!$F$5),"D",IF(I37="N","C",IF(J37="Y","A-CURVED",IF(AND(MEDIAN(E37,F37,G37)&lt;=LISTS!$F$10,MAX(E37,F37,G37)&lt;=LISTS!$F$11),"B",IF(MAX(E37,F37,G37)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
       <c r="R37" s="14">
         <f>IF(E37="","",IF(B37="","material?",IF(OR(F37="",G37=""),"size?",IF(I37="","exposed Y/N?",IF(H37="","qty?",IF(B37="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S37" s="12">
         <f t="array" ref="S37">IF(OR(O37="",M37=""),"",IF(B37="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B37&amp;"_"&amp;SUBSTITUTE(O37,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T37" s="12">
         <f>IF(ISNUMBER(S37),M37*S37,"")</f>
+        <v/>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="59">
@@ -18203,23 +19409,29 @@
       <c r="L38" s="10" t="n"/>
       <c r="M38" s="25">
         <f>IF(OR(E38="",F38="",G38=""),"",E38*F38*G38/1000000000*IF(H38="",1,H38))</f>
+        <v/>
       </c>
       <c r="N38" s="19">
         <f>IF(OR(E38="",F38=""),"",E38*F38/1000000*IF(H38="",1,H38))</f>
+        <v/>
       </c>
       <c r="O38" s="14">
         <f>IF(E38="","",IF(K38&lt;&gt;"",K38,IF(AND(E38*F38*G38/1000000000&lt;LISTS!$F$4,MAX(E38,F38,G38)&lt;LISTS!$F$5),"D",IF(I38="N","C",IF(J38="Y","A-CURVED",IF(AND(MEDIAN(E38,F38,G38)&lt;=LISTS!$F$10,MAX(E38,F38,G38)&lt;=LISTS!$F$11),"B",IF(MAX(E38,F38,G38)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P38" s="14" t="n"/>
       <c r="Q38" s="14" t="n"/>
       <c r="R38" s="14">
         <f>IF(E38="","",IF(B38="","material?",IF(OR(F38="",G38=""),"size?",IF(I38="","exposed Y/N?",IF(H38="","qty?",IF(B38="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S38" s="12">
         <f t="array" ref="S38">IF(OR(O38="",M38=""),"",IF(B38="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B38&amp;"_"&amp;SUBSTITUTE(O38,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T38" s="12">
         <f>IF(ISNUMBER(S38),M38*S38,"")</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="59">
@@ -18239,23 +19451,29 @@
       <c r="L39" s="10" t="n"/>
       <c r="M39" s="25">
         <f>IF(OR(E39="",F39="",G39=""),"",E39*F39*G39/1000000000*IF(H39="",1,H39))</f>
+        <v/>
       </c>
       <c r="N39" s="19">
         <f>IF(OR(E39="",F39=""),"",E39*F39/1000000*IF(H39="",1,H39))</f>
+        <v/>
       </c>
       <c r="O39" s="14">
         <f>IF(E39="","",IF(K39&lt;&gt;"",K39,IF(AND(E39*F39*G39/1000000000&lt;LISTS!$F$4,MAX(E39,F39,G39)&lt;LISTS!$F$5),"D",IF(I39="N","C",IF(J39="Y","A-CURVED",IF(AND(MEDIAN(E39,F39,G39)&lt;=LISTS!$F$10,MAX(E39,F39,G39)&lt;=LISTS!$F$11),"B",IF(MAX(E39,F39,G39)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P39" s="14" t="n"/>
       <c r="Q39" s="14" t="n"/>
       <c r="R39" s="14">
         <f>IF(E39="","",IF(B39="","material?",IF(OR(F39="",G39=""),"size?",IF(I39="","exposed Y/N?",IF(H39="","qty?",IF(B39="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S39" s="12">
         <f t="array" ref="S39">IF(OR(O39="",M39=""),"",IF(B39="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B39&amp;"_"&amp;SUBSTITUTE(O39,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T39" s="12">
         <f>IF(ISNUMBER(S39),M39*S39,"")</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="59">
@@ -18275,23 +19493,29 @@
       <c r="L40" s="10" t="n"/>
       <c r="M40" s="25">
         <f>IF(OR(E40="",F40="",G40=""),"",E40*F40*G40/1000000000*IF(H40="",1,H40))</f>
+        <v/>
       </c>
       <c r="N40" s="19">
         <f>IF(OR(E40="",F40=""),"",E40*F40/1000000*IF(H40="",1,H40))</f>
+        <v/>
       </c>
       <c r="O40" s="14">
         <f>IF(E40="","",IF(K40&lt;&gt;"",K40,IF(AND(E40*F40*G40/1000000000&lt;LISTS!$F$4,MAX(E40,F40,G40)&lt;LISTS!$F$5),"D",IF(I40="N","C",IF(J40="Y","A-CURVED",IF(AND(MEDIAN(E40,F40,G40)&lt;=LISTS!$F$10,MAX(E40,F40,G40)&lt;=LISTS!$F$11),"B",IF(MAX(E40,F40,G40)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P40" s="14" t="n"/>
       <c r="Q40" s="14" t="n"/>
       <c r="R40" s="14">
         <f>IF(E40="","",IF(B40="","material?",IF(OR(F40="",G40=""),"size?",IF(I40="","exposed Y/N?",IF(H40="","qty?",IF(B40="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S40" s="12">
         <f t="array" ref="S40">IF(OR(O40="",M40=""),"",IF(B40="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B40&amp;"_"&amp;SUBSTITUTE(O40,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T40" s="12">
         <f>IF(ISNUMBER(S40),M40*S40,"")</f>
+        <v/>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="59">
@@ -18311,23 +19535,29 @@
       <c r="L41" s="10" t="n"/>
       <c r="M41" s="25">
         <f>IF(OR(E41="",F41="",G41=""),"",E41*F41*G41/1000000000*IF(H41="",1,H41))</f>
+        <v/>
       </c>
       <c r="N41" s="19">
         <f>IF(OR(E41="",F41=""),"",E41*F41/1000000*IF(H41="",1,H41))</f>
+        <v/>
       </c>
       <c r="O41" s="14">
         <f>IF(E41="","",IF(K41&lt;&gt;"",K41,IF(AND(E41*F41*G41/1000000000&lt;LISTS!$F$4,MAX(E41,F41,G41)&lt;LISTS!$F$5),"D",IF(I41="N","C",IF(J41="Y","A-CURVED",IF(AND(MEDIAN(E41,F41,G41)&lt;=LISTS!$F$10,MAX(E41,F41,G41)&lt;=LISTS!$F$11),"B",IF(MAX(E41,F41,G41)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P41" s="14" t="n"/>
       <c r="Q41" s="14" t="n"/>
       <c r="R41" s="14">
         <f>IF(E41="","",IF(B41="","material?",IF(OR(F41="",G41=""),"size?",IF(I41="","exposed Y/N?",IF(H41="","qty?",IF(B41="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S41" s="12">
         <f t="array" ref="S41">IF(OR(O41="",M41=""),"",IF(B41="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B41&amp;"_"&amp;SUBSTITUTE(O41,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T41" s="12">
         <f>IF(ISNUMBER(S41),M41*S41,"")</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="59">
@@ -18347,23 +19577,29 @@
       <c r="L42" s="10" t="n"/>
       <c r="M42" s="25">
         <f>IF(OR(E42="",F42="",G42=""),"",E42*F42*G42/1000000000*IF(H42="",1,H42))</f>
+        <v/>
       </c>
       <c r="N42" s="19">
         <f>IF(OR(E42="",F42=""),"",E42*F42/1000000*IF(H42="",1,H42))</f>
+        <v/>
       </c>
       <c r="O42" s="14">
         <f>IF(E42="","",IF(K42&lt;&gt;"",K42,IF(AND(E42*F42*G42/1000000000&lt;LISTS!$F$4,MAX(E42,F42,G42)&lt;LISTS!$F$5),"D",IF(I42="N","C",IF(J42="Y","A-CURVED",IF(AND(MEDIAN(E42,F42,G42)&lt;=LISTS!$F$10,MAX(E42,F42,G42)&lt;=LISTS!$F$11),"B",IF(MAX(E42,F42,G42)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <v/>
       </c>
       <c r="P42" s="14" t="n"/>
       <c r="Q42" s="14" t="n"/>
       <c r="R42" s="14">
         <f>IF(E42="","",IF(B42="","material?",IF(OR(F42="",G42=""),"size?",IF(I42="","exposed Y/N?",IF(H42="","qty?",IF(B42="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
+        <v/>
       </c>
       <c r="S42" s="12">
         <f t="array" ref="S42">IF(OR(O42="",M42=""),"",IF(B42="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B42&amp;"_"&amp;SUBSTITUTE(O42,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
+        <v/>
       </c>
       <c r="T42" s="12">
         <f>IF(ISNUMBER(S42),M42*S42,"")</f>
+        <v/>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="59"/>
@@ -18515,27 +19751,35 @@
       </c>
       <c r="M46" s="25">
         <f>IF(OR(E46="",F46="",G46=""),"",E46*F46*G46/1000000000*IF(H46="",1,H46))</f>
+        <v/>
       </c>
       <c r="N46" s="19">
         <f>IF(OR(E46="",F46=""),"",E46*F46/1000000*IF(H46="",1,H46))</f>
+        <v/>
       </c>
       <c r="O46" s="14">
         <f>IF(OR(E46="",F46=""),"",MAX(INT(LISTS!$F$6/(E46+LISTS!$F$8))*INT(LISTS!$F$7/(F46+LISTS!$F$8)),INT(LISTS!$F$6/(F46+LISTS!$F$8))*INT(LISTS!$F$7/(E46+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P46" s="19">
         <f>IF(K46&lt;&gt;"",K46,IF(OR(O46="",O46=0),"",IF(H46="",1,H46)/O46))</f>
+        <v/>
       </c>
       <c r="Q46" s="36">
         <f>IF(OR(K46&lt;&gt;"",P46=""),"",1-(IF(H46="",1,H46)*E46*F46)/(ROUNDUP(P46,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R46" s="14">
         <f>IF(AND(E46="",K46=""),"",IF(B46="","panel type?",IF(AND(K46="",O46=0),"panel bigger than sheet",IF(AND(G46&lt;&gt;"",IFERROR(VALUE(MID(B46,5,FIND("-",B46,5)-5)),0)&lt;&gt;G46),"T must match panel type",IF(I46="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S46" s="12">
         <f t="array" ref="S46">IF(OR(B46="",P46=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B46,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T46" s="12">
         <f>IF(ISNUMBER(S46),IF(K46&lt;&gt;"",K46,IF(Q46&gt;RATES!$C$97,P46*(1+RATES!$C$98),ROUNDUP(P46,0)))*S46,"")</f>
+        <v/>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="59">
@@ -18581,27 +19825,35 @@
       </c>
       <c r="M47" s="25">
         <f>IF(OR(E47="",F47="",G47=""),"",E47*F47*G47/1000000000*IF(H47="",1,H47))</f>
+        <v/>
       </c>
       <c r="N47" s="19">
         <f>IF(OR(E47="",F47=""),"",E47*F47/1000000*IF(H47="",1,H47))</f>
+        <v/>
       </c>
       <c r="O47" s="14">
         <f>IF(OR(E47="",F47=""),"",MAX(INT(LISTS!$F$6/(E47+LISTS!$F$8))*INT(LISTS!$F$7/(F47+LISTS!$F$8)),INT(LISTS!$F$6/(F47+LISTS!$F$8))*INT(LISTS!$F$7/(E47+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P47" s="19">
         <f>IF(K47&lt;&gt;"",K47,IF(OR(O47="",O47=0),"",IF(H47="",1,H47)/O47))</f>
+        <v/>
       </c>
       <c r="Q47" s="36">
         <f>IF(OR(K47&lt;&gt;"",P47=""),"",1-(IF(H47="",1,H47)*E47*F47)/(ROUNDUP(P47,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R47" s="14">
         <f>IF(AND(E47="",K47=""),"",IF(B47="","panel type?",IF(AND(K47="",O47=0),"panel bigger than sheet",IF(AND(G47&lt;&gt;"",IFERROR(VALUE(MID(B47,5,FIND("-",B47,5)-5)),0)&lt;&gt;G47),"T must match panel type",IF(I47="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S47" s="12">
         <f t="array" ref="S47">IF(OR(B47="",P47=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B47,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T47" s="12">
         <f>IF(ISNUMBER(S47),IF(K47&lt;&gt;"",K47,IF(Q47&gt;RATES!$C$97,P47*(1+RATES!$C$98),ROUNDUP(P47,0)))*S47,"")</f>
+        <v/>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="59">
@@ -18647,27 +19899,35 @@
       </c>
       <c r="M48" s="25">
         <f>IF(OR(E48="",F48="",G48=""),"",E48*F48*G48/1000000000*IF(H48="",1,H48))</f>
+        <v/>
       </c>
       <c r="N48" s="19">
         <f>IF(OR(E48="",F48=""),"",E48*F48/1000000*IF(H48="",1,H48))</f>
+        <v/>
       </c>
       <c r="O48" s="14">
         <f>IF(OR(E48="",F48=""),"",MAX(INT(LISTS!$F$6/(E48+LISTS!$F$8))*INT(LISTS!$F$7/(F48+LISTS!$F$8)),INT(LISTS!$F$6/(F48+LISTS!$F$8))*INT(LISTS!$F$7/(E48+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P48" s="19">
         <f>IF(K48&lt;&gt;"",K48,IF(OR(O48="",O48=0),"",IF(H48="",1,H48)/O48))</f>
+        <v/>
       </c>
       <c r="Q48" s="36">
         <f>IF(OR(K48&lt;&gt;"",P48=""),"",1-(IF(H48="",1,H48)*E48*F48)/(ROUNDUP(P48,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R48" s="14">
         <f>IF(AND(E48="",K48=""),"",IF(B48="","panel type?",IF(AND(K48="",O48=0),"panel bigger than sheet",IF(AND(G48&lt;&gt;"",IFERROR(VALUE(MID(B48,5,FIND("-",B48,5)-5)),0)&lt;&gt;G48),"T must match panel type",IF(I48="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S48" s="12">
         <f t="array" ref="S48">IF(OR(B48="",P48=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B48,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T48" s="12">
         <f>IF(ISNUMBER(S48),IF(K48&lt;&gt;"",K48,IF(Q48&gt;RATES!$C$97,P48*(1+RATES!$C$98),ROUNDUP(P48,0)))*S48,"")</f>
+        <v/>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="59">
@@ -18713,27 +19973,35 @@
       </c>
       <c r="M49" s="25">
         <f>IF(OR(E49="",F49="",G49=""),"",E49*F49*G49/1000000000*IF(H49="",1,H49))</f>
+        <v/>
       </c>
       <c r="N49" s="19">
         <f>IF(OR(E49="",F49=""),"",E49*F49/1000000*IF(H49="",1,H49))</f>
+        <v/>
       </c>
       <c r="O49" s="14">
         <f>IF(OR(E49="",F49=""),"",MAX(INT(LISTS!$F$6/(E49+LISTS!$F$8))*INT(LISTS!$F$7/(F49+LISTS!$F$8)),INT(LISTS!$F$6/(F49+LISTS!$F$8))*INT(LISTS!$F$7/(E49+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P49" s="19">
         <f>IF(K49&lt;&gt;"",K49,IF(OR(O49="",O49=0),"",IF(H49="",1,H49)/O49))</f>
+        <v/>
       </c>
       <c r="Q49" s="36">
         <f>IF(OR(K49&lt;&gt;"",P49=""),"",1-(IF(H49="",1,H49)*E49*F49)/(ROUNDUP(P49,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R49" s="14">
         <f>IF(AND(E49="",K49=""),"",IF(B49="","panel type?",IF(AND(K49="",O49=0),"panel bigger than sheet",IF(AND(G49&lt;&gt;"",IFERROR(VALUE(MID(B49,5,FIND("-",B49,5)-5)),0)&lt;&gt;G49),"T must match panel type",IF(I49="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S49" s="12">
         <f t="array" ref="S49">IF(OR(B49="",P49=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B49,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T49" s="12">
         <f>IF(ISNUMBER(S49),IF(K49&lt;&gt;"",K49,IF(Q49&gt;RATES!$C$97,P49*(1+RATES!$C$98),ROUNDUP(P49,0)))*S49,"")</f>
+        <v/>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="59">
@@ -18779,27 +20047,35 @@
       </c>
       <c r="M50" s="25">
         <f>IF(OR(E50="",F50="",G50=""),"",E50*F50*G50/1000000000*IF(H50="",1,H50))</f>
+        <v/>
       </c>
       <c r="N50" s="19">
         <f>IF(OR(E50="",F50=""),"",E50*F50/1000000*IF(H50="",1,H50))</f>
+        <v/>
       </c>
       <c r="O50" s="14">
         <f>IF(OR(E50="",F50=""),"",MAX(INT(LISTS!$F$6/(E50+LISTS!$F$8))*INT(LISTS!$F$7/(F50+LISTS!$F$8)),INT(LISTS!$F$6/(F50+LISTS!$F$8))*INT(LISTS!$F$7/(E50+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P50" s="19">
         <f>IF(K50&lt;&gt;"",K50,IF(OR(O50="",O50=0),"",IF(H50="",1,H50)/O50))</f>
+        <v/>
       </c>
       <c r="Q50" s="36">
         <f>IF(OR(K50&lt;&gt;"",P50=""),"",1-(IF(H50="",1,H50)*E50*F50)/(ROUNDUP(P50,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R50" s="14">
         <f>IF(AND(E50="",K50=""),"",IF(B50="","panel type?",IF(AND(K50="",O50=0),"panel bigger than sheet",IF(AND(G50&lt;&gt;"",IFERROR(VALUE(MID(B50,5,FIND("-",B50,5)-5)),0)&lt;&gt;G50),"T must match panel type",IF(I50="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S50" s="12">
         <f t="array" ref="S50">IF(OR(B50="",P50=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B50,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T50" s="12">
         <f>IF(ISNUMBER(S50),IF(K50&lt;&gt;"",K50,IF(Q50&gt;RATES!$C$97,P50*(1+RATES!$C$98),ROUNDUP(P50,0)))*S50,"")</f>
+        <v/>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="59">
@@ -18845,27 +20121,35 @@
       </c>
       <c r="M51" s="25">
         <f>IF(OR(E51="",F51="",G51=""),"",E51*F51*G51/1000000000*IF(H51="",1,H51))</f>
+        <v/>
       </c>
       <c r="N51" s="19">
         <f>IF(OR(E51="",F51=""),"",E51*F51/1000000*IF(H51="",1,H51))</f>
+        <v/>
       </c>
       <c r="O51" s="14">
         <f>IF(OR(E51="",F51=""),"",MAX(INT(LISTS!$F$6/(E51+LISTS!$F$8))*INT(LISTS!$F$7/(F51+LISTS!$F$8)),INT(LISTS!$F$6/(F51+LISTS!$F$8))*INT(LISTS!$F$7/(E51+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P51" s="19">
         <f>IF(K51&lt;&gt;"",K51,IF(OR(O51="",O51=0),"",IF(H51="",1,H51)/O51))</f>
+        <v/>
       </c>
       <c r="Q51" s="36">
         <f>IF(OR(K51&lt;&gt;"",P51=""),"",1-(IF(H51="",1,H51)*E51*F51)/(ROUNDUP(P51,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R51" s="14">
         <f>IF(AND(E51="",K51=""),"",IF(B51="","panel type?",IF(AND(K51="",O51=0),"panel bigger than sheet",IF(AND(G51&lt;&gt;"",IFERROR(VALUE(MID(B51,5,FIND("-",B51,5)-5)),0)&lt;&gt;G51),"T must match panel type",IF(I51="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S51" s="12">
         <f t="array" ref="S51">IF(OR(B51="",P51=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B51,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T51" s="12">
         <f>IF(ISNUMBER(S51),IF(K51&lt;&gt;"",K51,IF(Q51&gt;RATES!$C$97,P51*(1+RATES!$C$98),ROUNDUP(P51,0)))*S51,"")</f>
+        <v/>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="59">
@@ -18911,27 +20195,35 @@
       </c>
       <c r="M52" s="25">
         <f>IF(OR(E52="",F52="",G52=""),"",E52*F52*G52/1000000000*IF(H52="",1,H52))</f>
+        <v/>
       </c>
       <c r="N52" s="19">
         <f>IF(OR(E52="",F52=""),"",E52*F52/1000000*IF(H52="",1,H52))</f>
+        <v/>
       </c>
       <c r="O52" s="14">
         <f>IF(OR(E52="",F52=""),"",MAX(INT(LISTS!$F$6/(E52+LISTS!$F$8))*INT(LISTS!$F$7/(F52+LISTS!$F$8)),INT(LISTS!$F$6/(F52+LISTS!$F$8))*INT(LISTS!$F$7/(E52+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P52" s="19">
         <f>IF(K52&lt;&gt;"",K52,IF(OR(O52="",O52=0),"",IF(H52="",1,H52)/O52))</f>
+        <v/>
       </c>
       <c r="Q52" s="36">
         <f>IF(OR(K52&lt;&gt;"",P52=""),"",1-(IF(H52="",1,H52)*E52*F52)/(ROUNDUP(P52,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R52" s="14">
         <f>IF(AND(E52="",K52=""),"",IF(B52="","panel type?",IF(AND(K52="",O52=0),"panel bigger than sheet",IF(AND(G52&lt;&gt;"",IFERROR(VALUE(MID(B52,5,FIND("-",B52,5)-5)),0)&lt;&gt;G52),"T must match panel type",IF(I52="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S52" s="12">
         <f t="array" ref="S52">IF(OR(B52="",P52=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B52,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T52" s="12">
         <f>IF(ISNUMBER(S52),IF(K52&lt;&gt;"",K52,IF(Q52&gt;RATES!$C$97,P52*(1+RATES!$C$98),ROUNDUP(P52,0)))*S52,"")</f>
+        <v/>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="59">
@@ -18951,27 +20243,35 @@
       <c r="L53" s="10" t="n"/>
       <c r="M53" s="25">
         <f>IF(OR(E53="",F53="",G53=""),"",E53*F53*G53/1000000000*IF(H53="",1,H53))</f>
+        <v/>
       </c>
       <c r="N53" s="19">
         <f>IF(OR(E53="",F53=""),"",E53*F53/1000000*IF(H53="",1,H53))</f>
+        <v/>
       </c>
       <c r="O53" s="14">
         <f>IF(OR(E53="",F53=""),"",MAX(INT(LISTS!$F$6/(E53+LISTS!$F$8))*INT(LISTS!$F$7/(F53+LISTS!$F$8)),INT(LISTS!$F$6/(F53+LISTS!$F$8))*INT(LISTS!$F$7/(E53+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P53" s="19">
         <f>IF(K53&lt;&gt;"",K53,IF(OR(O53="",O53=0),"",IF(H53="",1,H53)/O53))</f>
+        <v/>
       </c>
       <c r="Q53" s="36">
         <f>IF(OR(K53&lt;&gt;"",P53=""),"",1-(IF(H53="",1,H53)*E53*F53)/(ROUNDUP(P53,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R53" s="14">
         <f>IF(AND(E53="",K53=""),"",IF(B53="","panel type?",IF(AND(K53="",O53=0),"panel bigger than sheet",IF(AND(G53&lt;&gt;"",IFERROR(VALUE(MID(B53,5,FIND("-",B53,5)-5)),0)&lt;&gt;G53),"T must match panel type",IF(I53="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S53" s="12">
         <f t="array" ref="S53">IF(OR(B53="",P53=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B53,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T53" s="12">
         <f>IF(ISNUMBER(S53),IF(K53&lt;&gt;"",K53,IF(Q53&gt;RATES!$C$97,P53*(1+RATES!$C$98),ROUNDUP(P53,0)))*S53,"")</f>
+        <v/>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="59">
@@ -18991,27 +20291,35 @@
       <c r="L54" s="10" t="n"/>
       <c r="M54" s="25">
         <f>IF(OR(E54="",F54="",G54=""),"",E54*F54*G54/1000000000*IF(H54="",1,H54))</f>
+        <v/>
       </c>
       <c r="N54" s="19">
         <f>IF(OR(E54="",F54=""),"",E54*F54/1000000*IF(H54="",1,H54))</f>
+        <v/>
       </c>
       <c r="O54" s="14">
         <f>IF(OR(E54="",F54=""),"",MAX(INT(LISTS!$F$6/(E54+LISTS!$F$8))*INT(LISTS!$F$7/(F54+LISTS!$F$8)),INT(LISTS!$F$6/(F54+LISTS!$F$8))*INT(LISTS!$F$7/(E54+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P54" s="19">
         <f>IF(K54&lt;&gt;"",K54,IF(OR(O54="",O54=0),"",IF(H54="",1,H54)/O54))</f>
+        <v/>
       </c>
       <c r="Q54" s="36">
         <f>IF(OR(K54&lt;&gt;"",P54=""),"",1-(IF(H54="",1,H54)*E54*F54)/(ROUNDUP(P54,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R54" s="14">
         <f>IF(AND(E54="",K54=""),"",IF(B54="","panel type?",IF(AND(K54="",O54=0),"panel bigger than sheet",IF(AND(G54&lt;&gt;"",IFERROR(VALUE(MID(B54,5,FIND("-",B54,5)-5)),0)&lt;&gt;G54),"T must match panel type",IF(I54="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S54" s="12">
         <f t="array" ref="S54">IF(OR(B54="",P54=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B54,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T54" s="12">
         <f>IF(ISNUMBER(S54),IF(K54&lt;&gt;"",K54,IF(Q54&gt;RATES!$C$97,P54*(1+RATES!$C$98),ROUNDUP(P54,0)))*S54,"")</f>
+        <v/>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="59">
@@ -19031,27 +20339,35 @@
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="25">
         <f>IF(OR(E55="",F55="",G55=""),"",E55*F55*G55/1000000000*IF(H55="",1,H55))</f>
+        <v/>
       </c>
       <c r="N55" s="19">
         <f>IF(OR(E55="",F55=""),"",E55*F55/1000000*IF(H55="",1,H55))</f>
+        <v/>
       </c>
       <c r="O55" s="14">
         <f>IF(OR(E55="",F55=""),"",MAX(INT(LISTS!$F$6/(E55+LISTS!$F$8))*INT(LISTS!$F$7/(F55+LISTS!$F$8)),INT(LISTS!$F$6/(F55+LISTS!$F$8))*INT(LISTS!$F$7/(E55+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P55" s="19">
         <f>IF(K55&lt;&gt;"",K55,IF(OR(O55="",O55=0),"",IF(H55="",1,H55)/O55))</f>
+        <v/>
       </c>
       <c r="Q55" s="36">
         <f>IF(OR(K55&lt;&gt;"",P55=""),"",1-(IF(H55="",1,H55)*E55*F55)/(ROUNDUP(P55,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R55" s="14">
         <f>IF(AND(E55="",K55=""),"",IF(B55="","panel type?",IF(AND(K55="",O55=0),"panel bigger than sheet",IF(AND(G55&lt;&gt;"",IFERROR(VALUE(MID(B55,5,FIND("-",B55,5)-5)),0)&lt;&gt;G55),"T must match panel type",IF(I55="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S55" s="12">
         <f t="array" ref="S55">IF(OR(B55="",P55=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B55,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T55" s="12">
         <f>IF(ISNUMBER(S55),IF(K55&lt;&gt;"",K55,IF(Q55&gt;RATES!$C$97,P55*(1+RATES!$C$98),ROUNDUP(P55,0)))*S55,"")</f>
+        <v/>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="59">
@@ -19071,27 +20387,35 @@
       <c r="L56" s="10" t="n"/>
       <c r="M56" s="25">
         <f>IF(OR(E56="",F56="",G56=""),"",E56*F56*G56/1000000000*IF(H56="",1,H56))</f>
+        <v/>
       </c>
       <c r="N56" s="19">
         <f>IF(OR(E56="",F56=""),"",E56*F56/1000000*IF(H56="",1,H56))</f>
+        <v/>
       </c>
       <c r="O56" s="14">
         <f>IF(OR(E56="",F56=""),"",MAX(INT(LISTS!$F$6/(E56+LISTS!$F$8))*INT(LISTS!$F$7/(F56+LISTS!$F$8)),INT(LISTS!$F$6/(F56+LISTS!$F$8))*INT(LISTS!$F$7/(E56+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P56" s="19">
         <f>IF(K56&lt;&gt;"",K56,IF(OR(O56="",O56=0),"",IF(H56="",1,H56)/O56))</f>
+        <v/>
       </c>
       <c r="Q56" s="36">
         <f>IF(OR(K56&lt;&gt;"",P56=""),"",1-(IF(H56="",1,H56)*E56*F56)/(ROUNDUP(P56,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R56" s="14">
         <f>IF(AND(E56="",K56=""),"",IF(B56="","panel type?",IF(AND(K56="",O56=0),"panel bigger than sheet",IF(AND(G56&lt;&gt;"",IFERROR(VALUE(MID(B56,5,FIND("-",B56,5)-5)),0)&lt;&gt;G56),"T must match panel type",IF(I56="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S56" s="12">
         <f t="array" ref="S56">IF(OR(B56="",P56=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B56,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T56" s="12">
         <f>IF(ISNUMBER(S56),IF(K56&lt;&gt;"",K56,IF(Q56&gt;RATES!$C$97,P56*(1+RATES!$C$98),ROUNDUP(P56,0)))*S56,"")</f>
+        <v/>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="59">
@@ -19111,27 +20435,35 @@
       <c r="L57" s="10" t="n"/>
       <c r="M57" s="25">
         <f>IF(OR(E57="",F57="",G57=""),"",E57*F57*G57/1000000000*IF(H57="",1,H57))</f>
+        <v/>
       </c>
       <c r="N57" s="19">
         <f>IF(OR(E57="",F57=""),"",E57*F57/1000000*IF(H57="",1,H57))</f>
+        <v/>
       </c>
       <c r="O57" s="14">
         <f>IF(OR(E57="",F57=""),"",MAX(INT(LISTS!$F$6/(E57+LISTS!$F$8))*INT(LISTS!$F$7/(F57+LISTS!$F$8)),INT(LISTS!$F$6/(F57+LISTS!$F$8))*INT(LISTS!$F$7/(E57+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P57" s="19">
         <f>IF(K57&lt;&gt;"",K57,IF(OR(O57="",O57=0),"",IF(H57="",1,H57)/O57))</f>
+        <v/>
       </c>
       <c r="Q57" s="36">
         <f>IF(OR(K57&lt;&gt;"",P57=""),"",1-(IF(H57="",1,H57)*E57*F57)/(ROUNDUP(P57,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R57" s="14">
         <f>IF(AND(E57="",K57=""),"",IF(B57="","panel type?",IF(AND(K57="",O57=0),"panel bigger than sheet",IF(AND(G57&lt;&gt;"",IFERROR(VALUE(MID(B57,5,FIND("-",B57,5)-5)),0)&lt;&gt;G57),"T must match panel type",IF(I57="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S57" s="12">
         <f t="array" ref="S57">IF(OR(B57="",P57=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B57,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T57" s="12">
         <f>IF(ISNUMBER(S57),IF(K57&lt;&gt;"",K57,IF(Q57&gt;RATES!$C$97,P57*(1+RATES!$C$98),ROUNDUP(P57,0)))*S57,"")</f>
+        <v/>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="59">
@@ -19151,27 +20483,35 @@
       <c r="L58" s="10" t="n"/>
       <c r="M58" s="25">
         <f>IF(OR(E58="",F58="",G58=""),"",E58*F58*G58/1000000000*IF(H58="",1,H58))</f>
+        <v/>
       </c>
       <c r="N58" s="19">
         <f>IF(OR(E58="",F58=""),"",E58*F58/1000000*IF(H58="",1,H58))</f>
+        <v/>
       </c>
       <c r="O58" s="14">
         <f>IF(OR(E58="",F58=""),"",MAX(INT(LISTS!$F$6/(E58+LISTS!$F$8))*INT(LISTS!$F$7/(F58+LISTS!$F$8)),INT(LISTS!$F$6/(F58+LISTS!$F$8))*INT(LISTS!$F$7/(E58+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P58" s="19">
         <f>IF(K58&lt;&gt;"",K58,IF(OR(O58="",O58=0),"",IF(H58="",1,H58)/O58))</f>
+        <v/>
       </c>
       <c r="Q58" s="36">
         <f>IF(OR(K58&lt;&gt;"",P58=""),"",1-(IF(H58="",1,H58)*E58*F58)/(ROUNDUP(P58,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R58" s="14">
         <f>IF(AND(E58="",K58=""),"",IF(B58="","panel type?",IF(AND(K58="",O58=0),"panel bigger than sheet",IF(AND(G58&lt;&gt;"",IFERROR(VALUE(MID(B58,5,FIND("-",B58,5)-5)),0)&lt;&gt;G58),"T must match panel type",IF(I58="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S58" s="12">
         <f t="array" ref="S58">IF(OR(B58="",P58=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B58,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T58" s="12">
         <f>IF(ISNUMBER(S58),IF(K58&lt;&gt;"",K58,IF(Q58&gt;RATES!$C$97,P58*(1+RATES!$C$98),ROUNDUP(P58,0)))*S58,"")</f>
+        <v/>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="59">
@@ -19191,27 +20531,35 @@
       <c r="L59" s="10" t="n"/>
       <c r="M59" s="25">
         <f>IF(OR(E59="",F59="",G59=""),"",E59*F59*G59/1000000000*IF(H59="",1,H59))</f>
+        <v/>
       </c>
       <c r="N59" s="19">
         <f>IF(OR(E59="",F59=""),"",E59*F59/1000000*IF(H59="",1,H59))</f>
+        <v/>
       </c>
       <c r="O59" s="14">
         <f>IF(OR(E59="",F59=""),"",MAX(INT(LISTS!$F$6/(E59+LISTS!$F$8))*INT(LISTS!$F$7/(F59+LISTS!$F$8)),INT(LISTS!$F$6/(F59+LISTS!$F$8))*INT(LISTS!$F$7/(E59+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P59" s="19">
         <f>IF(K59&lt;&gt;"",K59,IF(OR(O59="",O59=0),"",IF(H59="",1,H59)/O59))</f>
+        <v/>
       </c>
       <c r="Q59" s="36">
         <f>IF(OR(K59&lt;&gt;"",P59=""),"",1-(IF(H59="",1,H59)*E59*F59)/(ROUNDUP(P59,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R59" s="14">
         <f>IF(AND(E59="",K59=""),"",IF(B59="","panel type?",IF(AND(K59="",O59=0),"panel bigger than sheet",IF(AND(G59&lt;&gt;"",IFERROR(VALUE(MID(B59,5,FIND("-",B59,5)-5)),0)&lt;&gt;G59),"T must match panel type",IF(I59="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S59" s="12">
         <f t="array" ref="S59">IF(OR(B59="",P59=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B59,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T59" s="12">
         <f>IF(ISNUMBER(S59),IF(K59&lt;&gt;"",K59,IF(Q59&gt;RATES!$C$97,P59*(1+RATES!$C$98),ROUNDUP(P59,0)))*S59,"")</f>
+        <v/>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="59">
@@ -19231,27 +20579,35 @@
       <c r="L60" s="10" t="n"/>
       <c r="M60" s="25">
         <f>IF(OR(E60="",F60="",G60=""),"",E60*F60*G60/1000000000*IF(H60="",1,H60))</f>
+        <v/>
       </c>
       <c r="N60" s="19">
         <f>IF(OR(E60="",F60=""),"",E60*F60/1000000*IF(H60="",1,H60))</f>
+        <v/>
       </c>
       <c r="O60" s="14">
         <f>IF(OR(E60="",F60=""),"",MAX(INT(LISTS!$F$6/(E60+LISTS!$F$8))*INT(LISTS!$F$7/(F60+LISTS!$F$8)),INT(LISTS!$F$6/(F60+LISTS!$F$8))*INT(LISTS!$F$7/(E60+LISTS!$F$8))))</f>
+        <v/>
       </c>
       <c r="P60" s="19">
         <f>IF(K60&lt;&gt;"",K60,IF(OR(O60="",O60=0),"",IF(H60="",1,H60)/O60))</f>
+        <v/>
       </c>
       <c r="Q60" s="36">
         <f>IF(OR(K60&lt;&gt;"",P60=""),"",1-(IF(H60="",1,H60)*E60*F60)/(ROUNDUP(P60,0)*LISTS!$F$6*LISTS!$F$7))</f>
+        <v/>
       </c>
       <c r="R60" s="14">
         <f>IF(AND(E60="",K60=""),"",IF(B60="","panel type?",IF(AND(K60="",O60=0),"panel bigger than sheet",IF(AND(G60&lt;&gt;"",IFERROR(VALUE(MID(B60,5,FIND("-",B60,5)-5)),0)&lt;&gt;G60),"T must match panel type",IF(I60="","exposed faces?","OK")))))</f>
+        <v/>
       </c>
       <c r="S60" s="12">
         <f t="array" ref="S60">IF(OR(B60="",P60=""),"",IFERROR(INDEX(RATES!$C:$C,MATCH(B60,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
       </c>
       <c r="T60" s="12">
         <f>IF(ISNUMBER(S60),IF(K60&lt;&gt;"",K60,IF(Q60&gt;RATES!$C$97,P60*(1+RATES!$C$98),ROUNDUP(P60,0)))*S60,"")</f>
+        <v/>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="59"/>
@@ -19376,6 +20732,7 @@
       </c>
       <c r="T64" s="38">
         <f>IF(OR(H64="",S64=""),"",H64*S64)</f>
+        <v/>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="59">
@@ -19430,6 +20787,7 @@
       </c>
       <c r="T65" s="38">
         <f>IF(OR(H65="",S65=""),"",H65*S65)</f>
+        <v/>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="59">
@@ -19484,6 +20842,7 @@
       </c>
       <c r="T66" s="38">
         <f>IF(OR(H66="",S66=""),"",H66*S66)</f>
+        <v/>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="59">
@@ -19538,6 +20897,7 @@
       </c>
       <c r="T67" s="38">
         <f>IF(OR(H67="",S67=""),"",H67*S67)</f>
+        <v/>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="59">
@@ -19564,6 +20924,7 @@
       <c r="S68" s="37" t="n"/>
       <c r="T68" s="38">
         <f>IF(OR(H68="",S68=""),"",H68*S68)</f>
+        <v/>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="59">
@@ -19590,6 +20951,7 @@
       <c r="S69" s="37" t="n"/>
       <c r="T69" s="38">
         <f>IF(OR(H69="",S69=""),"",H69*S69)</f>
+        <v/>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="59">
@@ -19616,6 +20978,7 @@
       <c r="S70" s="37" t="n"/>
       <c r="T70" s="38">
         <f>IF(OR(H70="",S70=""),"",H70*S70)</f>
+        <v/>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="59">
@@ -19642,6 +21005,7 @@
       <c r="S71" s="37" t="n"/>
       <c r="T71" s="38">
         <f>IF(OR(H71="",S71=""),"",H71*S71)</f>
+        <v/>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="59">
@@ -19668,6 +21032,7 @@
       <c r="S72" s="37" t="n"/>
       <c r="T72" s="38">
         <f>IF(OR(H72="",S72=""),"",H72*S72)</f>
+        <v/>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="59">
@@ -19694,6 +21059,7 @@
       <c r="S73" s="37" t="n"/>
       <c r="T73" s="38">
         <f>IF(OR(H73="",S73=""),"",H73*S73)</f>
+        <v/>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="59">
@@ -19720,6 +21086,7 @@
       <c r="S74" s="37" t="n"/>
       <c r="T74" s="38">
         <f>IF(OR(H74="",S74=""),"",H74*S74)</f>
+        <v/>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="59">
@@ -19746,6 +21113,7 @@
       <c r="S75" s="37" t="n"/>
       <c r="T75" s="38">
         <f>IF(OR(H75="",S75=""),"",H75*S75)</f>
+        <v/>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="59">
@@ -19772,6 +21140,7 @@
       <c r="S76" s="37" t="n"/>
       <c r="T76" s="38">
         <f>IF(OR(H76="",S76=""),"",H76*S76)</f>
+        <v/>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="59">
@@ -19798,6 +21167,7 @@
       <c r="S77" s="37" t="n"/>
       <c r="T77" s="38">
         <f>IF(OR(H77="",S77=""),"",H77*S77)</f>
+        <v/>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="59">
@@ -19824,6 +21194,7 @@
       <c r="S78" s="37" t="n"/>
       <c r="T78" s="38">
         <f>IF(OR(H78="",S78=""),"",H78*S78)</f>
+        <v/>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="59"/>
@@ -19843,6 +21214,7 @@
       </c>
       <c r="D82" s="25">
         <f>SUM(M18:M42)</f>
+        <v/>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="59">
@@ -19853,6 +21225,7 @@
       </c>
       <c r="D83" s="17">
         <f>SUM(P46:P60)</f>
+        <v/>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="59">
@@ -19863,6 +21236,7 @@
       </c>
       <c r="D84" s="19">
         <f>SUMIF(I18:I42,"Y",N18:N42)+SUMIF(I46:I60,1,N46:N60)+2*SUMIF(I46:I60,2,N46:N60)</f>
+        <v/>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -19878,6 +21252,7 @@
       </c>
       <c r="D85" s="39">
         <f>G15</f>
+        <v/>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="59">
@@ -19888,6 +21263,7 @@
       </c>
       <c r="D86" s="19">
         <f>M15</f>
+        <v/>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="59">
@@ -19898,6 +21274,7 @@
       </c>
       <c r="D87" s="12">
         <f>SUM(T18:T42)</f>
+        <v/>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -19913,6 +21290,7 @@
       </c>
       <c r="D88" s="12">
         <f>D82*RATES!$C$46</f>
+        <v/>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -19928,6 +21306,7 @@
       </c>
       <c r="D89" s="12">
         <f>SUM(T46:T60)</f>
+        <v/>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -19943,6 +21322,7 @@
       </c>
       <c r="D90" s="12">
         <f>D84*RATES!$C$47*IF($C$5="NONE (RAW)",0,1)</f>
+        <v/>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -19958,6 +21338,7 @@
       </c>
       <c r="D91" s="12">
         <f>D84*RATES!$C$48*IF($C$5="NONE (RAW)",0,1)</f>
+        <v/>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -19973,6 +21354,7 @@
       </c>
       <c r="D92" s="12">
         <f>D84*RATES!$C$49*IF($C$5="NONE (RAW)",0,1)</f>
+        <v/>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -19988,6 +21370,7 @@
       </c>
       <c r="D93" s="12">
         <f>D84*RATES!$C$50*IF($C$5="NONE (RAW)",0,1)</f>
+        <v/>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -20003,6 +21386,7 @@
       </c>
       <c r="D94" s="12">
         <f>SUM(T64:T78)</f>
+        <v/>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -20018,6 +21402,7 @@
       </c>
       <c r="D95" s="12">
         <f>IF(L15=0,0,IF(L15&lt;RATES!$C$95,RATES!$C$53*G15,L15*RATES!$C$51*(1+IF(G15&gt;1,RATES!$C$96,0)))+M15*RATES!$C$52)</f>
+        <v/>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -20033,6 +21418,7 @@
       </c>
       <c r="D96" s="16">
         <f>SUM(D87:D95)</f>
+        <v/>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="59">
@@ -20043,6 +21429,7 @@
       </c>
       <c r="D97" s="12">
         <f>D96*RATES!$C$54</f>
+        <v/>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -20058,6 +21445,7 @@
       </c>
       <c r="D98" s="12">
         <f>(D96+D97)*RATES!$C$55</f>
+        <v/>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -20073,6 +21461,7 @@
       </c>
       <c r="D99" s="16">
         <f>D96+D97+D98</f>
+        <v/>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="59">
@@ -20083,6 +21472,7 @@
       </c>
       <c r="D100" s="19">
         <f>L15</f>
+        <v/>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="59">
@@ -20093,6 +21483,7 @@
       </c>
       <c r="D101" s="16">
         <f>IF(ISNUMBER(C4),C4,0)*D99</f>
+        <v/>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="59">
@@ -20103,6 +21494,7 @@
       </c>
       <c r="D102" s="40">
         <f>COUNTIF(R18:R42,"?*")-COUNTIF(R18:R42,"OK")+COUNTIF(R46:R60,"?*")-COUNTIF(R46:R60,"OK")+COUNTIF(S18:S60,"rate?")</f>
+        <v/>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="[$Rp]#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -145,8 +145,16 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -195,8 +203,18 @@
         <bgColor rgb="002B180D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDE5EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -360,11 +378,16 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -507,6 +530,114 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10079,6202 +10210,7191 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J257"/>
+  <dimension ref="A1:I257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="59" min="1" max="1"/>
+    <col width="52" customWidth="1" style="59" min="2" max="2"/>
+    <col width="17" customWidth="1" style="59" min="3" max="3"/>
+    <col width="11" customWidth="1" style="59" min="4" max="4"/>
+    <col width="48" customWidth="1" style="59" min="5" max="5"/>
+    <col width="22" customWidth="1" style="59" min="6" max="6"/>
+    <col width="24" customWidth="1" style="59" min="7" max="7"/>
+    <col width="16" customWidth="1" style="59" min="8" max="8"/>
+    <col width="16" customWidth="1" style="59" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="92" t="inlineStr">
         <is>
           <t>RATES: PLV BOM Rate Card 29 Sep 26 (rates_version 2026-09-29), with the 30 Sep changes: finishing split into four rates, 40 × 40 section rule</t>
         </is>
       </c>
+      <c r="B1" s="93" t="n"/>
+      <c r="C1" s="94" t="n"/>
+      <c r="D1" s="95" t="n"/>
+      <c r="E1" s="95" t="n"/>
+      <c r="F1" s="95" t="n"/>
+      <c r="G1" s="95" t="n"/>
+      <c r="H1" s="95" t="n"/>
+      <c r="I1" s="95" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="74" t="inlineStr">
+      <c r="A2" s="96" t="inlineStr">
         <is>
           <t>Blue = base figure (change it and every cost in this workbook follows). Black = formula. Item tabs look rates up by the code in column A. Only the rate owner edits this tab.</t>
         </is>
       </c>
+      <c r="B2" s="93" t="n"/>
+      <c r="C2" s="94" t="n"/>
+      <c r="D2" s="95" t="n"/>
+      <c r="E2" s="95" t="n"/>
+      <c r="F2" s="95" t="n"/>
+      <c r="G2" s="95" t="n"/>
+      <c r="H2" s="95" t="n"/>
+      <c r="I2" s="95" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="97" t="inlineStr">
         <is>
           <t>Same rate card as the PLV BOM Costing Workbook v3 (teak, mindi, meranti, plywood). Plywood keeps the Mojo Indah Sep 2026 rates; columns F and G show the Linyi Ocean landed quote of 16 Oct 2026 in USD and IDR for comparison. MDF, marine plywood (rows 170 onward) and DTC rails and hinges (rows 227–229) are priced from USD. Orange rows = rate with both a USD and an IDR price. No rates yet for oak / ash, oak veneer, rattan or metal frames.</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="76" t="inlineStr">
+      <c r="B3" s="98" t="n"/>
+      <c r="C3" s="98" t="n"/>
+      <c r="D3" s="98" t="n"/>
+      <c r="E3" s="98" t="n"/>
+      <c r="F3" s="98" t="n"/>
+      <c r="G3" s="98" t="n"/>
+      <c r="H3" s="98" t="n"/>
+      <c r="I3" s="98" t="n"/>
+    </row>
+    <row r="4" ht="32" customHeight="1" s="59">
+      <c r="A4" s="99" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B4" s="76" t="inlineStr">
+      <c r="B4" s="99" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C4" s="77" t="inlineStr">
+      <c r="C4" s="100" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E4" s="76" t="inlineStr">
+      <c r="D4" s="101" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F4" s="78" t="inlineStr">
+      <c r="E4" s="99" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="G4" s="79" t="inlineStr">
+      <c r="F4" s="99" t="inlineStr">
         <is>
           <t>Quote USD (Linyi Ocean landed, 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="H4" s="79" t="inlineStr">
+      <c r="G4" s="99" t="inlineStr">
         <is>
           <t>Quote IDR (USD × FX_USD)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="75" t="inlineStr">
+      <c r="A5" s="97" t="inlineStr">
         <is>
           <t>BASE FIGURES: STMV (Standard Maldives) ledger, payroll and vendor lists</t>
         </is>
       </c>
+      <c r="B5" s="98" t="n"/>
+      <c r="C5" s="98" t="n"/>
+      <c r="D5" s="98" t="n"/>
+      <c r="E5" s="98" t="n"/>
+      <c r="F5" s="98" t="n"/>
+      <c r="G5" s="98" t="n"/>
+      <c r="H5" s="98" t="n"/>
+      <c r="I5" s="98" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="102" t="inlineStr">
         <is>
           <t>log_teak</t>
         </is>
       </c>
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="103" t="inlineStr">
         <is>
           <t>Teak log price, implied</t>
         </is>
       </c>
-      <c r="C6" s="80" t="n">
+      <c r="C6" s="104" t="n">
         <v>6000000</v>
       </c>
-      <c r="E6" s="74" t="inlineStr">
+      <c r="D6" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F6" s="74" t="inlineStr">
+      <c r="E6" s="96" t="inlineStr">
         <is>
           <t>Ledger 152.3m ÷ 14 m³. Status CONFIRM: replace with nota price</t>
         </is>
       </c>
+      <c r="F6" s="95" t="n"/>
+      <c r="G6" s="95" t="n"/>
+      <c r="H6" s="95" t="n"/>
+      <c r="I6" s="95" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="75" t="inlineStr">
+      <c r="A7" s="102" t="inlineStr">
         <is>
           <t>log_mindi</t>
         </is>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="103" t="inlineStr">
         <is>
           <t>Mindi log price, implied</t>
         </is>
       </c>
-      <c r="C7" s="80" t="n">
+      <c r="C7" s="104" t="n">
         <v>3000000</v>
       </c>
-      <c r="E7" s="74" t="inlineStr">
+      <c r="D7" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F7" s="74" t="inlineStr">
+      <c r="E7" s="96" t="inlineStr">
         <is>
           <t>Ledger 126.1m ÷ 41 m³. Status CONFIRM</t>
         </is>
       </c>
+      <c r="F7" s="95" t="n"/>
+      <c r="G7" s="95" t="n"/>
+      <c r="H7" s="95" t="n"/>
+      <c r="I7" s="95" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="102" t="inlineStr">
         <is>
           <t>meranti_sawn</t>
         </is>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="103" t="inlineStr">
         <is>
           <t>Meranti dry sawn timber</t>
         </is>
       </c>
-      <c r="C8" s="80" t="n">
+      <c r="C8" s="104" t="n">
         <v>8500000</v>
       </c>
-      <c r="E8" s="74" t="inlineStr">
+      <c r="D8" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F8" s="74" t="inlineStr">
+      <c r="E8" s="96" t="inlineStr">
         <is>
           <t>STMV BOM price. Status CONFIRM</t>
         </is>
       </c>
+      <c r="F8" s="95" t="n"/>
+      <c r="G8" s="95" t="n"/>
+      <c r="H8" s="95" t="n"/>
+      <c r="I8" s="95" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="102" t="inlineStr">
         <is>
           <t>processing</t>
         </is>
       </c>
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="103" t="inlineStr">
         <is>
           <t>Wood processing (kiln + sawmill + hauling + sawmill staff), per m³ of log</t>
         </is>
       </c>
-      <c r="C9" s="80" t="n">
+      <c r="C9" s="104" t="n">
         <v>598978</v>
       </c>
-      <c r="E9" s="74" t="inlineStr">
+      <c r="D9" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F9" s="74" t="inlineStr">
+      <c r="E9" s="96" t="inlineStr">
         <is>
           <t>Ledger ÷ 75.82 m³ teak + mindi</t>
         </is>
       </c>
+      <c r="F9" s="95" t="n"/>
+      <c r="G9" s="95" t="n"/>
+      <c r="H9" s="95" t="n"/>
+      <c r="I9" s="95" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="75" t="inlineStr">
+      <c r="A10" s="102" t="inlineStr">
         <is>
           <t>carp_pool</t>
         </is>
       </c>
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="103" t="inlineStr">
         <is>
           <t>Carpentry payroll pool Mar–Sep 2026</t>
         </is>
       </c>
-      <c r="C10" s="80" t="n">
+      <c r="C10" s="105" t="n">
         <v>270175017</v>
       </c>
-      <c r="E10" s="74" t="inlineStr">
+      <c r="D10" s="96" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="F10" s="74" t="inlineStr">
+      <c r="E10" s="96" t="inlineStr">
         <is>
           <t>Payroll categorised by name, 29 Sep</t>
         </is>
       </c>
+      <c r="F10" s="95" t="n"/>
+      <c r="G10" s="95" t="n"/>
+      <c r="H10" s="95" t="n"/>
+      <c r="I10" s="95" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="75" t="inlineStr">
+      <c r="A11" s="102" t="inlineStr">
         <is>
           <t>carp_deduct</t>
         </is>
       </c>
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="103" t="inlineStr">
         <is>
           <t>Less panel cutting / pressing (already in panel rate)</t>
         </is>
       </c>
-      <c r="C11" s="80" t="n">
+      <c r="C11" s="106" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="74" t="inlineStr">
+      <c r="D11" s="96" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F11" s="74" t="inlineStr">
+      <c r="E11" s="96" t="inlineStr">
         <is>
           <t>Decision 29 Sep</t>
         </is>
       </c>
+      <c r="F11" s="95" t="n"/>
+      <c r="G11" s="95" t="n"/>
+      <c r="H11" s="95" t="n"/>
+      <c r="I11" s="95" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="102" t="inlineStr">
         <is>
           <t>comp_m3</t>
         </is>
       </c>
-      <c r="B12" s="74" t="inlineStr">
+      <c r="B12" s="103" t="inlineStr">
         <is>
           <t>STMV solid wood in components (teak 12.21 + mindi 13.15 + meranti 7.20)</t>
         </is>
       </c>
-      <c r="C12" s="80" t="n">
+      <c r="C12" s="107" t="n">
         <v>32.56</v>
       </c>
-      <c r="E12" s="74" t="inlineStr">
+      <c r="D12" s="96" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F12" s="74" t="inlineStr">
+      <c r="E12" s="96" t="inlineStr">
         <is>
           <t>REVISI BOM 21 MEI 26</t>
         </is>
       </c>
+      <c r="F12" s="95" t="n"/>
+      <c r="G12" s="95" t="n"/>
+      <c r="H12" s="95" t="n"/>
+      <c r="I12" s="95" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="75" t="inlineStr">
+      <c r="A13" s="102" t="inlineStr">
         <is>
           <t>yield_A</t>
         </is>
       </c>
-      <c r="B13" s="74" t="inlineStr">
+      <c r="B13" s="103" t="inlineStr">
         <is>
           <t>Yield factor tier A (exposed, straight, ≥ 1000 mm)</t>
         </is>
       </c>
-      <c r="C13" s="80" t="n">
+      <c r="C13" s="107" t="n">
         <v>3.5</v>
       </c>
-      <c r="E13" s="74" t="inlineStr">
+      <c r="D13" s="96" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F13" s="74" t="inlineStr">
+      <c r="E13" s="96" t="inlineStr">
         <is>
           <t>Judgement, open item</t>
         </is>
       </c>
+      <c r="F13" s="95" t="n"/>
+      <c r="G13" s="95" t="n"/>
+      <c r="H13" s="95" t="n"/>
+      <c r="I13" s="95" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="75" t="inlineStr">
+      <c r="A14" s="102" t="inlineStr">
         <is>
           <t>yield_AC</t>
         </is>
       </c>
-      <c r="B14" s="74" t="inlineStr">
+      <c r="B14" s="103" t="inlineStr">
         <is>
           <t>Yield factor tier A-CURVED / wide board</t>
         </is>
       </c>
-      <c r="C14" s="80" t="n">
+      <c r="C14" s="107" t="n">
         <v>4.6</v>
       </c>
-      <c r="E14" s="74" t="inlineStr">
+      <c r="D14" s="96" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F14" s="74" t="inlineStr">
+      <c r="E14" s="96" t="inlineStr">
         <is>
           <t>STMV mindi</t>
         </is>
       </c>
+      <c r="F14" s="95" t="n"/>
+      <c r="G14" s="95" t="n"/>
+      <c r="H14" s="95" t="n"/>
+      <c r="I14" s="95" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="102" t="inlineStr">
         <is>
           <t>yield_B</t>
         </is>
       </c>
-      <c r="B15" s="74" t="inlineStr">
+      <c r="B15" s="103" t="inlineStr">
         <is>
           <t>Yield factor tier B (exposed &lt; 1000 mm, or section ≤ 40 × 40 up to 1500 mm)</t>
         </is>
       </c>
-      <c r="C15" s="80" t="n">
+      <c r="C15" s="107" t="n">
         <v>2.5</v>
       </c>
-      <c r="E15" s="74" t="inlineStr">
+      <c r="D15" s="96" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F15" s="74" t="inlineStr">
+      <c r="E15" s="96" t="inlineStr">
         <is>
           <t>Judgement, open item</t>
         </is>
       </c>
+      <c r="F15" s="95" t="n"/>
+      <c r="G15" s="95" t="n"/>
+      <c r="H15" s="95" t="n"/>
+      <c r="I15" s="95" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="75" t="inlineStr">
+      <c r="A16" s="102" t="inlineStr">
         <is>
           <t>yield_C</t>
         </is>
       </c>
-      <c r="B16" s="74" t="inlineStr">
+      <c r="B16" s="103" t="inlineStr">
         <is>
           <t>Yield factor tier C (not exposed)</t>
         </is>
       </c>
-      <c r="C16" s="80" t="n">
+      <c r="C16" s="107" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="74" t="inlineStr">
+      <c r="D16" s="96" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F16" s="74" t="inlineStr">
+      <c r="E16" s="96" t="inlineStr">
         <is>
           <t>STMV teak</t>
         </is>
       </c>
+      <c r="F16" s="95" t="n"/>
+      <c r="G16" s="95" t="n"/>
+      <c r="H16" s="95" t="n"/>
+      <c r="I16" s="95" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="75" t="inlineStr">
+      <c r="A17" s="102" t="inlineStr">
         <is>
           <t>yield_D</t>
         </is>
       </c>
-      <c r="B17" s="74" t="inlineStr">
+      <c r="B17" s="103" t="inlineStr">
         <is>
           <t>Yield factor tier D (very small parts)</t>
         </is>
       </c>
-      <c r="C17" s="80" t="n">
+      <c r="C17" s="107" t="n">
         <v>1.5</v>
       </c>
-      <c r="E17" s="74" t="inlineStr">
+      <c r="D17" s="96" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F17" s="74" t="inlineStr">
+      <c r="E17" s="96" t="inlineStr">
         <is>
           <t>Judgement, open item</t>
         </is>
       </c>
+      <c r="F17" s="95" t="n"/>
+      <c r="G17" s="95" t="n"/>
+      <c r="H17" s="95" t="n"/>
+      <c r="I17" s="95" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="75" t="inlineStr">
+      <c r="A18" s="102" t="inlineStr">
         <is>
           <t>yield_MER</t>
         </is>
       </c>
-      <c r="B18" s="74" t="inlineStr">
+      <c r="B18" s="103" t="inlineStr">
         <is>
           <t>Meranti sawn-to-component yield</t>
         </is>
       </c>
-      <c r="C18" s="80" t="n">
+      <c r="C18" s="107" t="n">
         <v>1.5</v>
       </c>
-      <c r="E18" s="74" t="inlineStr">
+      <c r="D18" s="96" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F18" s="74" t="inlineStr">
+      <c r="E18" s="96" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
+      <c r="F18" s="95" t="n"/>
+      <c r="G18" s="95" t="n"/>
+      <c r="H18" s="95" t="n"/>
+      <c r="I18" s="95" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="75" t="inlineStr">
+      <c r="A19" s="102" t="inlineStr">
         <is>
           <t>fast_total</t>
         </is>
       </c>
-      <c r="B19" s="74" t="inlineStr">
+      <c r="B19" s="103" t="inlineStr">
         <is>
           <t>Screws, nails, dowels, wood glue: STMV ledger estimate</t>
         </is>
       </c>
-      <c r="C19" s="80" t="n">
+      <c r="C19" s="105" t="n">
         <v>57000000</v>
       </c>
-      <c r="E19" s="74" t="inlineStr">
+      <c r="D19" s="96" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="F19" s="74" t="inlineStr">
+      <c r="E19" s="96" t="inlineStr">
         <is>
           <t>Status CONFIRM</t>
         </is>
       </c>
+      <c r="F19" s="95" t="n"/>
+      <c r="G19" s="95" t="n"/>
+      <c r="H19" s="95" t="n"/>
+      <c r="I19" s="95" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="75" t="inlineStr">
+      <c r="A20" s="102" t="inlineStr">
         <is>
           <t>paint_total</t>
         </is>
       </c>
-      <c r="B20" s="74" t="inlineStr">
+      <c r="B20" s="103" t="inlineStr">
         <is>
           <t>Finishing materials: Zhanchen all-in 52,888,326 + thinner 31,249,000</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n">
+      <c r="C20" s="105" t="n">
         <v>84137326</v>
       </c>
-      <c r="E20" s="74" t="inlineStr">
+      <c r="D20" s="96" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="F20" s="74" t="inlineStr">
+      <c r="E20" s="96" t="inlineStr">
         <is>
           <t>Ledger, agreed 28 Sep</t>
         </is>
       </c>
+      <c r="F20" s="95" t="n"/>
+      <c r="G20" s="95" t="n"/>
+      <c r="H20" s="95" t="n"/>
+      <c r="I20" s="95" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="75" t="inlineStr">
+      <c r="A21" s="102" t="inlineStr">
         <is>
           <t>abrasive_total</t>
         </is>
       </c>
-      <c r="B21" s="74" t="inlineStr">
+      <c r="B21" s="103" t="inlineStr">
         <is>
           <t>Sanding materials: abrasives / sandpaper</t>
         </is>
       </c>
-      <c r="C21" s="80" t="n">
+      <c r="C21" s="105" t="n">
         <v>27713000</v>
       </c>
-      <c r="E21" s="74" t="inlineStr">
+      <c r="D21" s="96" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="F21" s="74" t="inlineStr">
+      <c r="E21" s="96" t="inlineStr">
         <is>
           <t>Ledger, agreed 28 Sep</t>
         </is>
       </c>
+      <c r="F21" s="95" t="n"/>
+      <c r="G21" s="95" t="n"/>
+      <c r="H21" s="95" t="n"/>
+      <c r="I21" s="95" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="75" t="inlineStr">
+      <c r="A22" s="102" t="inlineStr">
         <is>
           <t>fin_pool</t>
         </is>
       </c>
-      <c r="B22" s="74" t="inlineStr">
+      <c r="B22" s="103" t="inlineStr">
         <is>
           <t>Finishing payroll pool excl. sanding (finishing, PU, gerinda, helper)</t>
         </is>
       </c>
-      <c r="C22" s="80" t="n">
+      <c r="C22" s="105" t="n">
         <v>192243271</v>
       </c>
-      <c r="E22" s="74" t="inlineStr">
+      <c r="D22" s="96" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="F22" s="74" t="inlineStr">
+      <c r="E22" s="96" t="inlineStr">
         <is>
           <t>Payroll, 29 Sep</t>
         </is>
       </c>
+      <c r="F22" s="95" t="n"/>
+      <c r="G22" s="95" t="n"/>
+      <c r="H22" s="95" t="n"/>
+      <c r="I22" s="95" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="75" t="inlineStr">
+      <c r="A23" s="102" t="inlineStr">
         <is>
           <t>sand_pool</t>
         </is>
       </c>
-      <c r="B23" s="74" t="inlineStr">
+      <c r="B23" s="103" t="inlineStr">
         <is>
           <t>Sanding payroll pool, as paid</t>
         </is>
       </c>
-      <c r="C23" s="80" t="n">
+      <c r="C23" s="105" t="n">
         <v>131550191</v>
       </c>
-      <c r="E23" s="74" t="inlineStr">
+      <c r="D23" s="96" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="F23" s="74" t="inlineStr">
+      <c r="E23" s="96" t="inlineStr">
         <is>
           <t>Payroll, 29 Sep</t>
         </is>
       </c>
+      <c r="F23" s="95" t="n"/>
+      <c r="G23" s="95" t="n"/>
+      <c r="H23" s="95" t="n"/>
+      <c r="I23" s="95" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="75" t="inlineStr">
+      <c r="A24" s="102" t="inlineStr">
         <is>
           <t>sand_keep</t>
         </is>
       </c>
-      <c r="B24" s="74" t="inlineStr">
+      <c r="B24" s="103" t="inlineStr">
         <is>
           <t>Sanding share kept (35% removed: bleach re-sanding, packing work)</t>
         </is>
       </c>
-      <c r="C24" s="80" t="n">
+      <c r="C24" s="106" t="n">
         <v>0.65</v>
       </c>
-      <c r="E24" s="74" t="inlineStr">
+      <c r="D24" s="96" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F24" s="74" t="inlineStr">
+      <c r="E24" s="96" t="inlineStr">
         <is>
           <t>Decision 29 Sep</t>
         </is>
       </c>
+      <c r="F24" s="95" t="n"/>
+      <c r="G24" s="95" t="n"/>
+      <c r="H24" s="95" t="n"/>
+      <c r="I24" s="95" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="75" t="inlineStr">
+      <c r="A25" s="102" t="inlineStr">
         <is>
           <t>fin_m2</t>
         </is>
       </c>
-      <c r="B25" s="74" t="inlineStr">
+      <c r="B25" s="103" t="inlineStr">
         <is>
           <t>STMV finishing surface</t>
         </is>
       </c>
-      <c r="C25" s="80" t="n">
+      <c r="C25" s="107" t="n">
         <v>2166</v>
       </c>
-      <c r="E25" s="74" t="inlineStr">
+      <c r="D25" s="96" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F25" s="74" t="inlineStr">
+      <c r="E25" s="96" t="inlineStr">
         <is>
           <t>Items tab estimate</t>
         </is>
       </c>
+      <c r="F25" s="95" t="n"/>
+      <c r="G25" s="95" t="n"/>
+      <c r="H25" s="95" t="n"/>
+      <c r="I25" s="95" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="75" t="inlineStr">
+      <c r="A26" s="102" t="inlineStr">
         <is>
           <t>oh_pool</t>
         </is>
       </c>
-      <c r="B26" s="74" t="inlineStr">
+      <c r="B26" s="103" t="inlineStr">
         <is>
           <t>Overhead payroll 213,627,079 + utilities 144,633,030 − PLN upgrade 49,700,000</t>
         </is>
       </c>
-      <c r="C26" s="80" t="n">
+      <c r="C26" s="105" t="n">
         <v>308560109</v>
       </c>
-      <c r="E26" s="74" t="inlineStr">
+      <c r="D26" s="96" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="F26" s="74" t="inlineStr">
+      <c r="E26" s="96" t="inlineStr">
         <is>
           <t>Payroll + reconciliation 23 Sep</t>
         </is>
       </c>
+      <c r="F26" s="95" t="n"/>
+      <c r="G26" s="95" t="n"/>
+      <c r="H26" s="95" t="n"/>
+      <c r="I26" s="95" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="75" t="inlineStr">
+      <c r="A27" s="102" t="inlineStr">
         <is>
           <t>stmv_direct</t>
         </is>
       </c>
-      <c r="B27" s="74" t="inlineStr">
+      <c r="B27" s="103" t="inlineStr">
         <is>
           <t>STMV direct cost</t>
         </is>
       </c>
-      <c r="C27" s="80" t="n">
+      <c r="C27" s="105" t="n">
         <v>2374841837</v>
       </c>
-      <c r="E27" s="74" t="inlineStr">
+      <c r="D27" s="96" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="F27" s="74" t="inlineStr">
+      <c r="E27" s="96" t="inlineStr">
         <is>
           <t>Reconciliation 23 Sep, section A</t>
         </is>
       </c>
+      <c r="F27" s="95" t="n"/>
+      <c r="G27" s="95" t="n"/>
+      <c r="H27" s="95" t="n"/>
+      <c r="I27" s="95" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="75" t="inlineStr">
+      <c r="A28" s="102" t="inlineStr">
         <is>
           <t>glue_tape</t>
         </is>
       </c>
-      <c r="B28" s="74" t="inlineStr">
+      <c r="B28" s="103" t="inlineStr">
         <is>
           <t>Adino glue + gum tape per m² veneered</t>
         </is>
       </c>
-      <c r="C28" s="80" t="n">
+      <c r="C28" s="105" t="n">
         <v>10424</v>
       </c>
-      <c r="E28" s="74" t="inlineStr">
+      <c r="D28" s="96" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
-      <c r="F28" s="74" t="inlineStr">
+      <c r="E28" s="96" t="inlineStr">
         <is>
           <t>3,912,750 + 600,000 ÷ 432.9 m² (122 doors × 2 faces)</t>
         </is>
       </c>
+      <c r="F28" s="95" t="n"/>
+      <c r="G28" s="95" t="n"/>
+      <c r="H28" s="95" t="n"/>
+      <c r="I28" s="95" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="75" t="inlineStr">
+      <c r="A29" s="102" t="inlineStr">
         <is>
           <t>ven_teak</t>
         </is>
       </c>
-      <c r="B29" s="74" t="inlineStr">
+      <c r="B29" s="103" t="inlineStr">
         <is>
           <t>Teak veneer per running metre (1.35 m wide)</t>
         </is>
       </c>
-      <c r="C29" s="80" t="n">
+      <c r="C29" s="105" t="n">
         <v>110000</v>
       </c>
-      <c r="E29" s="74" t="inlineStr">
+      <c r="D29" s="96" t="inlineStr">
         <is>
           <t>IDR/m</t>
         </is>
       </c>
-      <c r="F29" s="74" t="inlineStr">
+      <c r="E29" s="96" t="inlineStr">
         <is>
           <t>User figure 28 Sep. Status CONFIRM</t>
         </is>
       </c>
+      <c r="F29" s="95" t="n"/>
+      <c r="G29" s="95" t="n"/>
+      <c r="H29" s="95" t="n"/>
+      <c r="I29" s="95" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="75" t="inlineStr">
+      <c r="A30" s="102" t="inlineStr">
         <is>
           <t>ven_mindi</t>
         </is>
       </c>
-      <c r="B30" s="74" t="inlineStr">
+      <c r="B30" s="103" t="inlineStr">
         <is>
           <t>Mindi veneer per running metre</t>
         </is>
       </c>
-      <c r="C30" s="80" t="n">
+      <c r="C30" s="105" t="n">
         <v>20000</v>
       </c>
-      <c r="E30" s="74" t="inlineStr">
+      <c r="D30" s="96" t="inlineStr">
         <is>
           <t>IDR/m</t>
         </is>
       </c>
-      <c r="F30" s="74" t="inlineStr">
+      <c r="E30" s="96" t="inlineStr">
         <is>
           <t>User figure 28 Sep. Status CONFIRM (width ≥ 1.22 m)</t>
         </is>
       </c>
+      <c r="F30" s="95" t="n"/>
+      <c r="G30" s="95" t="n"/>
+      <c r="H30" s="95" t="n"/>
+      <c r="I30" s="95" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="75" t="inlineStr">
+      <c r="A31" s="102" t="inlineStr">
         <is>
           <t>ven_len</t>
         </is>
       </c>
-      <c r="B31" s="74" t="inlineStr">
+      <c r="B31" s="103" t="inlineStr">
         <is>
           <t>Veneer length used per face</t>
         </is>
       </c>
-      <c r="C31" s="80" t="n">
+      <c r="C31" s="107" t="n">
         <v>2.5</v>
       </c>
-      <c r="E31" s="74" t="inlineStr">
+      <c r="D31" s="96" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F31" s="74" t="inlineStr">
+      <c r="E31" s="96" t="inlineStr">
         <is>
           <t>One 2.5 m length per face, offcuts not reused</t>
         </is>
       </c>
+      <c r="F31" s="95" t="n"/>
+      <c r="G31" s="95" t="n"/>
+      <c r="H31" s="95" t="n"/>
+      <c r="I31" s="95" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="75" t="inlineStr">
+      <c r="A32" s="102" t="inlineStr">
         <is>
           <t>ven_labour</t>
         </is>
       </c>
-      <c r="B32" s="74" t="inlineStr">
+      <c r="B32" s="103" t="inlineStr">
         <is>
           <t>Pressing labour per face (tape, press, sand, cut)</t>
         </is>
       </c>
-      <c r="C32" s="80" t="n">
+      <c r="C32" s="105" t="n">
         <v>57142.86</v>
       </c>
-      <c r="E32" s="74" t="inlineStr">
+      <c r="D32" s="96" t="inlineStr">
         <is>
           <t>IDR/face</t>
         </is>
       </c>
-      <c r="F32" s="74" t="inlineStr">
+      <c r="E32" s="96" t="inlineStr">
         <is>
           <t>800,000 ÷ 14 sheets. Status CONFIRM</t>
         </is>
       </c>
+      <c r="F32" s="95" t="n"/>
+      <c r="G32" s="95" t="n"/>
+      <c r="H32" s="95" t="n"/>
+      <c r="I32" s="95" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="75" t="inlineStr">
+      <c r="A33" s="97" t="inlineStr">
         <is>
           <t>RATE CARD: applied by the item tabs</t>
         </is>
       </c>
+      <c r="B33" s="98" t="n"/>
+      <c r="C33" s="98" t="n"/>
+      <c r="D33" s="98" t="n"/>
+      <c r="E33" s="98" t="n"/>
+      <c r="F33" s="98" t="n"/>
+      <c r="G33" s="98" t="n"/>
+      <c r="H33" s="98" t="n"/>
+      <c r="I33" s="98" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="75" t="inlineStr">
+      <c r="A34" s="102" t="inlineStr">
         <is>
           <t>LAB_CARP</t>
         </is>
       </c>
-      <c r="B34" s="74" t="inlineStr">
+      <c r="B34" s="103" t="inlineStr">
         <is>
           <t>Carpentry labour per m³ of component (inside every tier rate)</t>
         </is>
       </c>
-      <c r="C34" s="81" t="n">
+      <c r="C34" s="108" t="n">
         <v>4000000</v>
       </c>
-      <c r="D34" s="81" t="n"/>
-      <c r="E34" s="74" t="inlineStr">
+      <c r="D34" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F34" s="74" t="inlineStr">
+      <c r="E34" s="96" t="inlineStr">
         <is>
           <t>Pool less 10% ÷ component m³</t>
         </is>
       </c>
+      <c r="F34" s="95" t="n"/>
+      <c r="G34" s="95" t="n"/>
+      <c r="H34" s="95" t="n"/>
+      <c r="I34" s="95" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="75" t="inlineStr">
+      <c r="A35" s="102" t="inlineStr">
         <is>
           <t>TEAK_A</t>
         </is>
       </c>
-      <c r="B35" s="74" t="inlineStr">
+      <c r="B35" s="103" t="inlineStr">
         <is>
           <t>Teak tier A</t>
         </is>
       </c>
-      <c r="C35" s="81" t="n">
+      <c r="C35" s="108" t="n">
         <v>27507965.09</v>
       </c>
-      <c r="D35" s="81" t="n"/>
-      <c r="E35" s="74" t="inlineStr">
+      <c r="D35" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F35" s="74" t="inlineStr">
+      <c r="E35" s="96" t="inlineStr">
         <is>
           <t>(log + processing) × yield + labour</t>
         </is>
       </c>
+      <c r="F35" s="95" t="n"/>
+      <c r="G35" s="95" t="n"/>
+      <c r="H35" s="95" t="n"/>
+      <c r="I35" s="95" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="75" t="inlineStr">
+      <c r="A36" s="102" t="inlineStr">
         <is>
           <t>TEAK_AC</t>
         </is>
       </c>
-      <c r="B36" s="74" t="inlineStr">
+      <c r="B36" s="103" t="inlineStr">
         <is>
           <t>Teak tier A-CURVED</t>
         </is>
       </c>
-      <c r="C36" s="81" t="n">
+      <c r="C36" s="108" t="n">
         <v>34040953.31</v>
       </c>
-      <c r="D36" s="81" t="n"/>
-      <c r="E36" s="74" t="inlineStr">
+      <c r="D36" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E36" s="95" t="n"/>
+      <c r="F36" s="95" t="n"/>
+      <c r="G36" s="95" t="n"/>
+      <c r="H36" s="95" t="n"/>
+      <c r="I36" s="95" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="75" t="inlineStr">
+      <c r="A37" s="102" t="inlineStr">
         <is>
           <t>TEAK_B</t>
         </is>
       </c>
-      <c r="B37" s="74" t="inlineStr">
+      <c r="B37" s="103" t="inlineStr">
         <is>
           <t>Teak tier B</t>
         </is>
       </c>
-      <c r="C37" s="81" t="n">
+      <c r="C37" s="108" t="n">
         <v>21568884.89</v>
       </c>
-      <c r="D37" s="81" t="n"/>
-      <c r="E37" s="74" t="inlineStr">
+      <c r="D37" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E37" s="95" t="n"/>
+      <c r="F37" s="95" t="n"/>
+      <c r="G37" s="95" t="n"/>
+      <c r="H37" s="95" t="n"/>
+      <c r="I37" s="95" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="75" t="inlineStr">
+      <c r="A38" s="102" t="inlineStr">
         <is>
           <t>TEAK_C</t>
         </is>
       </c>
-      <c r="B38" s="74" t="inlineStr">
+      <c r="B38" s="103" t="inlineStr">
         <is>
           <t>Teak tier C</t>
         </is>
       </c>
-      <c r="C38" s="81" t="n">
+      <c r="C38" s="108" t="n">
         <v>18599344.79</v>
       </c>
-      <c r="D38" s="81" t="n"/>
-      <c r="E38" s="74" t="inlineStr">
+      <c r="D38" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E38" s="95" t="n"/>
+      <c r="F38" s="95" t="n"/>
+      <c r="G38" s="95" t="n"/>
+      <c r="H38" s="95" t="n"/>
+      <c r="I38" s="95" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="75" t="inlineStr">
+      <c r="A39" s="102" t="inlineStr">
         <is>
           <t>TEAK_D</t>
         </is>
       </c>
-      <c r="B39" s="74" t="inlineStr">
+      <c r="B39" s="103" t="inlineStr">
         <is>
           <t>Teak tier D</t>
         </is>
       </c>
-      <c r="C39" s="81" t="n">
+      <c r="C39" s="108" t="n">
         <v>15629804.69</v>
       </c>
-      <c r="D39" s="81" t="n"/>
-      <c r="E39" s="74" t="inlineStr">
+      <c r="D39" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E39" s="95" t="n"/>
+      <c r="F39" s="95" t="n"/>
+      <c r="G39" s="95" t="n"/>
+      <c r="H39" s="95" t="n"/>
+      <c r="I39" s="95" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="75" t="inlineStr">
+      <c r="A40" s="102" t="inlineStr">
         <is>
           <t>MINDI_A</t>
         </is>
       </c>
-      <c r="B40" s="74" t="inlineStr">
+      <c r="B40" s="103" t="inlineStr">
         <is>
           <t>Mindi tier A</t>
         </is>
       </c>
-      <c r="C40" s="81" t="n">
+      <c r="C40" s="108" t="n">
         <v>18057965.09</v>
       </c>
-      <c r="D40" s="81" t="n"/>
-      <c r="E40" s="74" t="inlineStr">
+      <c r="D40" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E40" s="95" t="n"/>
+      <c r="F40" s="95" t="n"/>
+      <c r="G40" s="95" t="n"/>
+      <c r="H40" s="95" t="n"/>
+      <c r="I40" s="95" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="75" t="inlineStr">
+      <c r="A41" s="102" t="inlineStr">
         <is>
           <t>MINDI_AC</t>
         </is>
       </c>
-      <c r="B41" s="74" t="inlineStr">
+      <c r="B41" s="103" t="inlineStr">
         <is>
           <t>Mindi tier A-CURVED</t>
         </is>
       </c>
-      <c r="C41" s="81" t="n">
+      <c r="C41" s="108" t="n">
         <v>21620953.31</v>
       </c>
-      <c r="D41" s="81" t="n"/>
-      <c r="E41" s="74" t="inlineStr">
+      <c r="D41" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E41" s="95" t="n"/>
+      <c r="F41" s="95" t="n"/>
+      <c r="G41" s="95" t="n"/>
+      <c r="H41" s="95" t="n"/>
+      <c r="I41" s="95" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="75" t="inlineStr">
+      <c r="A42" s="102" t="inlineStr">
         <is>
           <t>MINDI_B</t>
         </is>
       </c>
-      <c r="B42" s="74" t="inlineStr">
+      <c r="B42" s="103" t="inlineStr">
         <is>
           <t>Mindi tier B</t>
         </is>
       </c>
-      <c r="C42" s="81" t="n">
+      <c r="C42" s="108" t="n">
         <v>14818884.89</v>
       </c>
-      <c r="D42" s="81" t="n"/>
-      <c r="E42" s="74" t="inlineStr">
+      <c r="D42" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E42" s="95" t="n"/>
+      <c r="F42" s="95" t="n"/>
+      <c r="G42" s="95" t="n"/>
+      <c r="H42" s="95" t="n"/>
+      <c r="I42" s="95" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="75" t="inlineStr">
+      <c r="A43" s="102" t="inlineStr">
         <is>
           <t>MINDI_C</t>
         </is>
       </c>
-      <c r="B43" s="74" t="inlineStr">
+      <c r="B43" s="103" t="inlineStr">
         <is>
           <t>Mindi tier C</t>
         </is>
       </c>
-      <c r="C43" s="81" t="n">
+      <c r="C43" s="108" t="n">
         <v>13199344.79</v>
       </c>
-      <c r="D43" s="81" t="n"/>
-      <c r="E43" s="74" t="inlineStr">
+      <c r="D43" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E43" s="95" t="n"/>
+      <c r="F43" s="95" t="n"/>
+      <c r="G43" s="95" t="n"/>
+      <c r="H43" s="95" t="n"/>
+      <c r="I43" s="95" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="75" t="inlineStr">
+      <c r="A44" s="102" t="inlineStr">
         <is>
           <t>MINDI_D</t>
         </is>
       </c>
-      <c r="B44" s="74" t="inlineStr">
+      <c r="B44" s="103" t="inlineStr">
         <is>
           <t>Mindi tier D</t>
         </is>
       </c>
-      <c r="C44" s="81" t="n">
+      <c r="C44" s="108" t="n">
         <v>11579804.69</v>
       </c>
-      <c r="D44" s="81" t="n"/>
-      <c r="E44" s="74" t="inlineStr">
+      <c r="D44" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E44" s="95" t="n"/>
+      <c r="F44" s="95" t="n"/>
+      <c r="G44" s="95" t="n"/>
+      <c r="H44" s="95" t="n"/>
+      <c r="I44" s="95" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="75" t="inlineStr">
+      <c r="A45" s="102" t="inlineStr">
         <is>
           <t>MERANTI</t>
         </is>
       </c>
-      <c r="B45" s="74" t="inlineStr">
+      <c r="B45" s="103" t="inlineStr">
         <is>
           <t>Meranti, any tier</t>
         </is>
       </c>
-      <c r="C45" s="81" t="n">
+      <c r="C45" s="108" t="n">
         <v>18196184.39</v>
       </c>
-      <c r="D45" s="81" t="n"/>
-      <c r="E45" s="74" t="inlineStr">
+      <c r="D45" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F45" s="74" t="inlineStr">
+      <c r="E45" s="96" t="inlineStr">
         <is>
           <t>Sawn price × yield + labour, no processing</t>
         </is>
       </c>
+      <c r="F45" s="95" t="n"/>
+      <c r="G45" s="95" t="n"/>
+      <c r="H45" s="95" t="n"/>
+      <c r="I45" s="95" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="75" t="inlineStr">
+      <c r="A46" s="102" t="inlineStr">
         <is>
           <t>FASTENERS</t>
         </is>
       </c>
-      <c r="B46" s="74" t="inlineStr">
+      <c r="B46" s="103" t="inlineStr">
         <is>
           <t>Screws, nails, dowels, glue per m³ of component</t>
         </is>
       </c>
-      <c r="C46" s="81" t="n">
+      <c r="C46" s="108" t="n">
         <v>1000000</v>
       </c>
-      <c r="D46" s="81" t="n"/>
-      <c r="E46" s="74" t="inlineStr">
+      <c r="D46" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
+      <c r="E46" s="95" t="n"/>
+      <c r="F46" s="95" t="n"/>
+      <c r="G46" s="95" t="n"/>
+      <c r="H46" s="95" t="n"/>
+      <c r="I46" s="95" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="75" t="inlineStr">
+      <c r="A47" s="102" t="inlineStr">
         <is>
           <t>FIN_MAT</t>
         </is>
       </c>
-      <c r="B47" s="74" t="inlineStr">
+      <c r="B47" s="103" t="inlineStr">
         <is>
           <t>Finishing materials (Zhanchen + thinner) per m² exposed</t>
         </is>
       </c>
-      <c r="C47" s="81" t="n">
+      <c r="C47" s="109" t="n">
         <v>37000</v>
       </c>
-      <c r="D47" s="81" t="n"/>
-      <c r="E47" s="74" t="inlineStr">
+      <c r="D47" s="96" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
+      <c r="E47" s="95" t="n"/>
+      <c r="F47" s="95" t="n"/>
+      <c r="G47" s="95" t="n"/>
+      <c r="H47" s="95" t="n"/>
+      <c r="I47" s="95" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="75" t="inlineStr">
+      <c r="A48" s="102" t="inlineStr">
         <is>
           <t>SAND_MAT</t>
         </is>
       </c>
-      <c r="B48" s="74" t="inlineStr">
+      <c r="B48" s="103" t="inlineStr">
         <is>
           <t>Sanding materials (abrasives) per m² exposed</t>
         </is>
       </c>
-      <c r="C48" s="81" t="n">
+      <c r="C48" s="109" t="n">
         <v>10235.64174</v>
       </c>
-      <c r="D48" s="81" t="n"/>
-      <c r="E48" s="74" t="inlineStr">
+      <c r="D48" s="96" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
+      <c r="E48" s="95" t="n"/>
+      <c r="F48" s="95" t="n"/>
+      <c r="G48" s="95" t="n"/>
+      <c r="H48" s="95" t="n"/>
+      <c r="I48" s="95" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="75" t="inlineStr">
+      <c r="A49" s="102" t="inlineStr">
         <is>
           <t>SAND_LAB</t>
         </is>
       </c>
-      <c r="B49" s="74" t="inlineStr">
+      <c r="B49" s="103" t="inlineStr">
         <is>
           <t>Sanding labour (65% of sanding pool) per m² exposed</t>
         </is>
       </c>
-      <c r="C49" s="81" t="n">
+      <c r="C49" s="109" t="n">
         <v>20000</v>
       </c>
-      <c r="D49" s="81" t="n"/>
-      <c r="E49" s="74" t="inlineStr">
+      <c r="D49" s="96" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
+      <c r="E49" s="95" t="n"/>
+      <c r="F49" s="95" t="n"/>
+      <c r="G49" s="95" t="n"/>
+      <c r="H49" s="95" t="n"/>
+      <c r="I49" s="95" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="75" t="inlineStr">
+      <c r="A50" s="102" t="inlineStr">
         <is>
           <t>FIN_LAB</t>
         </is>
       </c>
-      <c r="B50" s="74" t="inlineStr">
+      <c r="B50" s="103" t="inlineStr">
         <is>
           <t>Finishing labour (finishing pool) per m² exposed</t>
         </is>
       </c>
-      <c r="C50" s="81" t="n">
+      <c r="C50" s="109" t="n">
         <v>45000</v>
       </c>
-      <c r="D50" s="81" t="n"/>
-      <c r="E50" s="74" t="inlineStr">
+      <c r="D50" s="96" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
+      <c r="E50" s="95" t="n"/>
+      <c r="F50" s="95" t="n"/>
+      <c r="G50" s="95" t="n"/>
+      <c r="H50" s="95" t="n"/>
+      <c r="I50" s="95" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="75" t="inlineStr">
+      <c r="A51" s="102" t="inlineStr">
         <is>
           <t>CARTON_M2</t>
         </is>
       </c>
-      <c r="B51" s="74" t="inlineStr">
+      <c r="B51" s="103" t="inlineStr">
         <is>
           <t>Carton + consumables per m² of carton board (6 sides)</t>
         </is>
       </c>
-      <c r="C51" s="80" t="n">
+      <c r="C51" s="105" t="n">
         <v>40000</v>
       </c>
-      <c r="D51" s="80" t="n"/>
-      <c r="E51" s="74" t="inlineStr">
+      <c r="D51" s="96" t="inlineStr">
         <is>
           <t>IDR/m²</t>
         </is>
       </c>
-      <c r="F51" s="74" t="inlineStr">
+      <c r="E51" s="96" t="inlineStr">
         <is>
           <t>Cartons 59.4m + 40% of other packing materials</t>
         </is>
       </c>
+      <c r="F51" s="95" t="n"/>
+      <c r="G51" s="95" t="n"/>
+      <c r="H51" s="95" t="n"/>
+      <c r="I51" s="95" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="75" t="inlineStr">
+      <c r="A52" s="102" t="inlineStr">
         <is>
           <t>PACK_LAB</t>
         </is>
       </c>
-      <c r="B52" s="74" t="inlineStr">
+      <c r="B52" s="103" t="inlineStr">
         <is>
           <t>Packing labour per m³ of carton</t>
         </is>
       </c>
-      <c r="C52" s="80" t="n">
+      <c r="C52" s="104" t="n">
         <v>50000</v>
       </c>
-      <c r="D52" s="80" t="n"/>
-      <c r="E52" s="74" t="inlineStr">
+      <c r="D52" s="96" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F52" s="74" t="inlineStr">
+      <c r="E52" s="96" t="inlineStr">
         <is>
           <t>6 people × 8 days per container. Status CONFIRM</t>
         </is>
       </c>
+      <c r="F52" s="95" t="n"/>
+      <c r="G52" s="95" t="n"/>
+      <c r="H52" s="95" t="n"/>
+      <c r="I52" s="95" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="75" t="inlineStr">
+      <c r="A53" s="102" t="inlineStr">
         <is>
           <t>GRP_A</t>
         </is>
       </c>
-      <c r="B53" s="74" t="inlineStr">
+      <c r="B53" s="103" t="inlineStr">
         <is>
           <t>Carton group A price (boxes under CARTON_MIN_M2)</t>
         </is>
       </c>
-      <c r="C53" s="80" t="n">
+      <c r="C53" s="105" t="n">
         <v>24000</v>
       </c>
-      <c r="E53" s="74" t="inlineStr">
+      <c r="D53" s="96" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="F53" s="74" t="inlineStr">
+      <c r="E53" s="96" t="inlineStr">
         <is>
           <t>STMV carton groups, 28 Sep</t>
         </is>
       </c>
+      <c r="F53" s="95" t="n"/>
+      <c r="G53" s="95" t="n"/>
+      <c r="H53" s="95" t="n"/>
+      <c r="I53" s="95" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="75" t="inlineStr">
+      <c r="A54" s="102" t="inlineStr">
         <is>
           <t>MISC_PCT</t>
         </is>
       </c>
-      <c r="B54" s="74" t="inlineStr">
+      <c r="B54" s="103" t="inlineStr">
         <is>
           <t>Miscellaneous, × direct cost</t>
         </is>
       </c>
-      <c r="C54" s="80" t="n">
+      <c r="C54" s="106" t="n">
         <v>0.05</v>
       </c>
-      <c r="E54" s="74" t="inlineStr">
+      <c r="D54" s="96" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F54" s="74" t="inlineStr">
+      <c r="E54" s="96" t="inlineStr">
         <is>
           <t>Decision 29 Sep</t>
         </is>
       </c>
+      <c r="F54" s="95" t="n"/>
+      <c r="G54" s="95" t="n"/>
+      <c r="H54" s="95" t="n"/>
+      <c r="I54" s="95" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="75" t="inlineStr">
+      <c r="A55" s="102" t="inlineStr">
         <is>
           <t>OH_PCT</t>
         </is>
       </c>
-      <c r="B55" s="74" t="inlineStr">
+      <c r="B55" s="103" t="inlineStr">
         <is>
           <t>Overhead, × (direct + misc)</t>
         </is>
       </c>
-      <c r="C55" s="81">
+      <c r="C55" s="110">
         <f>$C$26/$C$27</f>
         <v/>
       </c>
-      <c r="E55" s="74" t="inlineStr">
+      <c r="D55" s="96" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F55" s="74" t="inlineStr">
+      <c r="E55" s="96" t="inlineStr">
         <is>
           <t>Overhead pool ÷ STMV direct cost</t>
         </is>
       </c>
+      <c r="F55" s="95" t="n"/>
+      <c r="G55" s="95" t="n"/>
+      <c r="H55" s="95" t="n"/>
+      <c r="I55" s="95" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="75" t="inlineStr">
+      <c r="A56" s="97" t="inlineStr">
         <is>
           <t>PLYWOOD per 2440 × 1220 sheet. RAW = board only; MSF / MDF = mindi veneer 1 / 2 faces; TSF / TDF = teak veneer 1 / 2 faces</t>
         </is>
       </c>
+      <c r="B56" s="98" t="n"/>
+      <c r="C56" s="98" t="n"/>
+      <c r="D56" s="98" t="n"/>
+      <c r="E56" s="98" t="n"/>
+      <c r="F56" s="98" t="n"/>
+      <c r="G56" s="98" t="n"/>
+      <c r="H56" s="98" t="n"/>
+      <c r="I56" s="98" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="75" t="inlineStr">
+      <c r="A57" s="102" t="inlineStr">
         <is>
           <t>VEN_TEAK_FACE</t>
         </is>
       </c>
-      <c r="B57" s="74" t="inlineStr">
+      <c r="B57" s="103" t="inlineStr">
         <is>
           <t>Teak veneer added cost per face (veneer + glue/tape + pressing labour)</t>
         </is>
       </c>
-      <c r="C57" s="81">
+      <c r="C57" s="109">
         <f>$C$29*$C$31+$C$28*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
         <v/>
       </c>
-      <c r="E57" s="74" t="inlineStr">
+      <c r="D57" s="96" t="inlineStr">
         <is>
           <t>IDR/face</t>
         </is>
       </c>
+      <c r="E57" s="95" t="n"/>
+      <c r="F57" s="95" t="n"/>
+      <c r="G57" s="95" t="n"/>
+      <c r="H57" s="95" t="n"/>
+      <c r="I57" s="95" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="75" t="inlineStr">
+      <c r="A58" s="102" t="inlineStr">
         <is>
           <t>VEN_MINDI_FACE</t>
         </is>
       </c>
-      <c r="B58" s="74" t="inlineStr">
+      <c r="B58" s="103" t="inlineStr">
         <is>
           <t>Mindi veneer added cost per face</t>
         </is>
       </c>
-      <c r="C58" s="81" t="n">
+      <c r="C58" s="111" t="n">
         <v>18000</v>
       </c>
-      <c r="D58" s="81" t="n"/>
-      <c r="E58" s="74" t="inlineStr">
+      <c r="D58" s="96" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
+      <c r="E58" s="95" t="n"/>
+      <c r="F58" s="95" t="n"/>
+      <c r="G58" s="95" t="n"/>
+      <c r="H58" s="95" t="n"/>
+      <c r="I58" s="95" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="75" t="inlineStr">
+      <c r="A59" s="102" t="inlineStr">
         <is>
           <t>PLY-3-RAW</t>
         </is>
       </c>
-      <c r="B59" s="74" t="inlineStr">
+      <c r="B59" s="103" t="inlineStr">
         <is>
           <t>Plywood 3 mm, raw</t>
         </is>
       </c>
-      <c r="C59" s="80">
-        <f>H59</f>
-        <v/>
-      </c>
-      <c r="E59" s="74" t="inlineStr">
+      <c r="C59" s="105">
+        <f>G59</f>
+        <v/>
+      </c>
+      <c r="D59" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F59" s="74" t="inlineStr">
+      <c r="E59" s="96" t="inlineStr">
         <is>
           <t>Mojo Indah list, Sep 2026</t>
         </is>
       </c>
-      <c r="G59" s="82">
-        <f t="array" ref="G59">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H59" s="83">
-        <f>G59*$C$172</f>
-        <v/>
-      </c>
+      <c r="F59" s="112">
+        <f t="array" ref="F59">INDEX($F$178:$F$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G59" s="112">
+        <f>F59*$C$172</f>
+        <v/>
+      </c>
+      <c r="H59" s="95" t="n"/>
+      <c r="I59" s="95" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="75" t="inlineStr">
+      <c r="A60" s="102" t="inlineStr">
         <is>
           <t>PLY-3-MSF</t>
         </is>
       </c>
-      <c r="B60" s="74" t="inlineStr">
+      <c r="B60" s="103" t="inlineStr">
         <is>
           <t>Plywood 3 mm, mindi single face</t>
         </is>
       </c>
-      <c r="C60" s="81">
+      <c r="C60" s="109">
         <f>C59+$C$175</f>
         <v/>
       </c>
-      <c r="E60" s="74" t="inlineStr">
+      <c r="D60" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E60" s="95" t="n"/>
+      <c r="F60" s="95" t="n"/>
+      <c r="G60" s="95" t="n"/>
+      <c r="H60" s="95" t="n"/>
+      <c r="I60" s="95" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="75" t="inlineStr">
+      <c r="A61" s="102" t="inlineStr">
         <is>
           <t>PLY-3-MDF</t>
         </is>
       </c>
-      <c r="B61" s="74" t="inlineStr">
+      <c r="B61" s="103" t="inlineStr">
         <is>
           <t>Plywood 3 mm, mindi double face</t>
         </is>
       </c>
-      <c r="C61" s="81">
+      <c r="C61" s="109">
         <f>C59+2*$C$175</f>
         <v/>
       </c>
-      <c r="E61" s="74" t="inlineStr">
+      <c r="D61" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E61" s="95" t="n"/>
+      <c r="F61" s="95" t="n"/>
+      <c r="G61" s="95" t="n"/>
+      <c r="H61" s="95" t="n"/>
+      <c r="I61" s="95" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="75" t="inlineStr">
+      <c r="A62" s="102" t="inlineStr">
         <is>
           <t>PLY-3-TSF</t>
         </is>
       </c>
-      <c r="B62" s="74" t="inlineStr">
+      <c r="B62" s="103" t="inlineStr">
         <is>
           <t>Plywood 3 mm, teak single face</t>
         </is>
       </c>
-      <c r="C62" s="81">
+      <c r="C62" s="109">
         <f>C59+$C$176</f>
         <v/>
       </c>
-      <c r="E62" s="74" t="inlineStr">
+      <c r="D62" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E62" s="95" t="n"/>
+      <c r="F62" s="95" t="n"/>
+      <c r="G62" s="95" t="n"/>
+      <c r="H62" s="95" t="n"/>
+      <c r="I62" s="95" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="75" t="inlineStr">
+      <c r="A63" s="102" t="inlineStr">
         <is>
           <t>PLY-3-TDF</t>
         </is>
       </c>
-      <c r="B63" s="74" t="inlineStr">
+      <c r="B63" s="103" t="inlineStr">
         <is>
           <t>Plywood 3 mm, teak double face</t>
         </is>
       </c>
-      <c r="C63" s="81">
+      <c r="C63" s="109">
         <f>C59+2*$C$176</f>
         <v/>
       </c>
-      <c r="E63" s="74" t="inlineStr">
+      <c r="D63" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E63" s="95" t="n"/>
+      <c r="F63" s="95" t="n"/>
+      <c r="G63" s="95" t="n"/>
+      <c r="H63" s="95" t="n"/>
+      <c r="I63" s="95" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="75" t="inlineStr">
+      <c r="A64" s="102" t="inlineStr">
         <is>
           <t>PLY-6-RAW</t>
         </is>
       </c>
-      <c r="B64" s="74" t="inlineStr">
+      <c r="B64" s="103" t="inlineStr">
         <is>
           <t>Plywood 6 mm, raw</t>
         </is>
       </c>
-      <c r="C64" s="80">
-        <f>H64</f>
-        <v/>
-      </c>
-      <c r="E64" s="74" t="inlineStr">
+      <c r="C64" s="105">
+        <f>G64</f>
+        <v/>
+      </c>
+      <c r="D64" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F64" s="74" t="inlineStr">
+      <c r="E64" s="96" t="inlineStr">
         <is>
           <t>Mojo Indah list, Sep 2026</t>
         </is>
       </c>
-      <c r="G64" s="82">
-        <f t="array" ref="G64">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H64" s="83">
-        <f>G64*$C$172</f>
-        <v/>
-      </c>
+      <c r="F64" s="112">
+        <f t="array" ref="F64">INDEX($F$178:$F$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G64" s="112">
+        <f>F64*$C$172</f>
+        <v/>
+      </c>
+      <c r="H64" s="95" t="n"/>
+      <c r="I64" s="95" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="75" t="inlineStr">
+      <c r="A65" s="102" t="inlineStr">
         <is>
           <t>PLY-6-MSF</t>
         </is>
       </c>
-      <c r="B65" s="74" t="inlineStr">
+      <c r="B65" s="103" t="inlineStr">
         <is>
           <t>Plywood 6 mm, mindi single face</t>
         </is>
       </c>
-      <c r="C65" s="81">
+      <c r="C65" s="109">
         <f>C64+$C$175</f>
         <v/>
       </c>
-      <c r="E65" s="74" t="inlineStr">
+      <c r="D65" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E65" s="95" t="n"/>
+      <c r="F65" s="95" t="n"/>
+      <c r="G65" s="95" t="n"/>
+      <c r="H65" s="95" t="n"/>
+      <c r="I65" s="95" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="75" t="inlineStr">
+      <c r="A66" s="102" t="inlineStr">
         <is>
           <t>PLY-6-MDF</t>
         </is>
       </c>
-      <c r="B66" s="74" t="inlineStr">
+      <c r="B66" s="103" t="inlineStr">
         <is>
           <t>Plywood 6 mm, mindi double face</t>
         </is>
       </c>
-      <c r="C66" s="81">
+      <c r="C66" s="109">
         <f>C64+2*$C$175</f>
         <v/>
       </c>
-      <c r="E66" s="74" t="inlineStr">
+      <c r="D66" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E66" s="95" t="n"/>
+      <c r="F66" s="95" t="n"/>
+      <c r="G66" s="95" t="n"/>
+      <c r="H66" s="95" t="n"/>
+      <c r="I66" s="95" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="75" t="inlineStr">
+      <c r="A67" s="102" t="inlineStr">
         <is>
           <t>PLY-6-TSF</t>
         </is>
       </c>
-      <c r="B67" s="74" t="inlineStr">
+      <c r="B67" s="103" t="inlineStr">
         <is>
           <t>Plywood 6 mm, teak single face</t>
         </is>
       </c>
-      <c r="C67" s="81">
+      <c r="C67" s="109">
         <f>C64+$C$176</f>
         <v/>
       </c>
-      <c r="E67" s="74" t="inlineStr">
+      <c r="D67" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E67" s="95" t="n"/>
+      <c r="F67" s="95" t="n"/>
+      <c r="G67" s="95" t="n"/>
+      <c r="H67" s="95" t="n"/>
+      <c r="I67" s="95" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="75" t="inlineStr">
+      <c r="A68" s="102" t="inlineStr">
         <is>
           <t>PLY-6-TDF</t>
         </is>
       </c>
-      <c r="B68" s="74" t="inlineStr">
+      <c r="B68" s="103" t="inlineStr">
         <is>
           <t>Plywood 6 mm, teak double face</t>
         </is>
       </c>
-      <c r="C68" s="81">
+      <c r="C68" s="109">
         <f>C64+2*$C$176</f>
         <v/>
       </c>
-      <c r="E68" s="74" t="inlineStr">
+      <c r="D68" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E68" s="95" t="n"/>
+      <c r="F68" s="95" t="n"/>
+      <c r="G68" s="95" t="n"/>
+      <c r="H68" s="95" t="n"/>
+      <c r="I68" s="95" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="75" t="inlineStr">
+      <c r="A69" s="102" t="inlineStr">
         <is>
           <t>PLY-9-RAW</t>
         </is>
       </c>
-      <c r="B69" s="74" t="inlineStr">
+      <c r="B69" s="103" t="inlineStr">
         <is>
           <t>Plywood 9 mm, raw</t>
         </is>
       </c>
-      <c r="C69" s="80">
-        <f>H69</f>
-        <v/>
-      </c>
-      <c r="E69" s="74" t="inlineStr">
+      <c r="C69" s="105">
+        <f>G69</f>
+        <v/>
+      </c>
+      <c r="D69" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F69" s="74" t="inlineStr">
+      <c r="E69" s="96" t="inlineStr">
         <is>
           <t>Mojo Indah list, Sep 2026</t>
         </is>
       </c>
-      <c r="G69" s="82">
-        <f t="array" ref="G69">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H69" s="83">
-        <f>G69*$C$172</f>
-        <v/>
-      </c>
+      <c r="F69" s="112">
+        <f t="array" ref="F69">INDEX($F$178:$F$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G69" s="112">
+        <f>F69*$C$172</f>
+        <v/>
+      </c>
+      <c r="H69" s="95" t="n"/>
+      <c r="I69" s="95" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="75" t="inlineStr">
+      <c r="A70" s="102" t="inlineStr">
         <is>
           <t>PLY-9-MSF</t>
         </is>
       </c>
-      <c r="B70" s="74" t="inlineStr">
+      <c r="B70" s="103" t="inlineStr">
         <is>
           <t>Plywood 9 mm, mindi single face</t>
         </is>
       </c>
-      <c r="C70" s="81">
+      <c r="C70" s="109">
         <f>C69+$C$175</f>
         <v/>
       </c>
-      <c r="E70" s="74" t="inlineStr">
+      <c r="D70" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E70" s="95" t="n"/>
+      <c r="F70" s="95" t="n"/>
+      <c r="G70" s="95" t="n"/>
+      <c r="H70" s="95" t="n"/>
+      <c r="I70" s="95" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="75" t="inlineStr">
+      <c r="A71" s="102" t="inlineStr">
         <is>
           <t>PLY-9-MDF</t>
         </is>
       </c>
-      <c r="B71" s="74" t="inlineStr">
+      <c r="B71" s="103" t="inlineStr">
         <is>
           <t>Plywood 9 mm, mindi double face</t>
         </is>
       </c>
-      <c r="C71" s="81">
+      <c r="C71" s="109">
         <f>C69+2*$C$175</f>
         <v/>
       </c>
-      <c r="E71" s="74" t="inlineStr">
+      <c r="D71" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E71" s="95" t="n"/>
+      <c r="F71" s="95" t="n"/>
+      <c r="G71" s="95" t="n"/>
+      <c r="H71" s="95" t="n"/>
+      <c r="I71" s="95" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="75" t="inlineStr">
+      <c r="A72" s="102" t="inlineStr">
         <is>
           <t>PLY-9-TSF</t>
         </is>
       </c>
-      <c r="B72" s="74" t="inlineStr">
+      <c r="B72" s="103" t="inlineStr">
         <is>
           <t>Plywood 9 mm, teak single face</t>
         </is>
       </c>
-      <c r="C72" s="81">
+      <c r="C72" s="109">
         <f>C69+$C$176</f>
         <v/>
       </c>
-      <c r="E72" s="74" t="inlineStr">
+      <c r="D72" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E72" s="95" t="n"/>
+      <c r="F72" s="95" t="n"/>
+      <c r="G72" s="95" t="n"/>
+      <c r="H72" s="95" t="n"/>
+      <c r="I72" s="95" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="75" t="inlineStr">
+      <c r="A73" s="102" t="inlineStr">
         <is>
           <t>PLY-9-TDF</t>
         </is>
       </c>
-      <c r="B73" s="74" t="inlineStr">
+      <c r="B73" s="103" t="inlineStr">
         <is>
           <t>Plywood 9 mm, teak double face</t>
         </is>
       </c>
-      <c r="C73" s="81">
+      <c r="C73" s="109">
         <f>C69+2*$C$176</f>
         <v/>
       </c>
-      <c r="E73" s="74" t="inlineStr">
+      <c r="D73" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E73" s="95" t="n"/>
+      <c r="F73" s="95" t="n"/>
+      <c r="G73" s="95" t="n"/>
+      <c r="H73" s="95" t="n"/>
+      <c r="I73" s="95" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="75" t="inlineStr">
+      <c r="A74" s="102" t="inlineStr">
         <is>
           <t>PLY-12-RAW</t>
         </is>
       </c>
-      <c r="B74" s="74" t="inlineStr">
+      <c r="B74" s="103" t="inlineStr">
         <is>
           <t>Plywood 12 mm, raw</t>
         </is>
       </c>
-      <c r="C74" s="80">
-        <f>H74</f>
-        <v/>
-      </c>
-      <c r="E74" s="74" t="inlineStr">
+      <c r="C74" s="105">
+        <f>G74</f>
+        <v/>
+      </c>
+      <c r="D74" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F74" s="74" t="inlineStr">
+      <c r="E74" s="96" t="inlineStr">
         <is>
           <t>Mojo Indah list, Sep 2026</t>
         </is>
       </c>
-      <c r="G74" s="82">
-        <f t="array" ref="G74">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H74" s="83">
-        <f>G74*$C$172</f>
-        <v/>
-      </c>
+      <c r="F74" s="112">
+        <f t="array" ref="F74">INDEX($F$178:$F$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G74" s="112">
+        <f>F74*$C$172</f>
+        <v/>
+      </c>
+      <c r="H74" s="95" t="n"/>
+      <c r="I74" s="95" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="75" t="inlineStr">
+      <c r="A75" s="102" t="inlineStr">
         <is>
           <t>PLY-12-MSF</t>
         </is>
       </c>
-      <c r="B75" s="74" t="inlineStr">
+      <c r="B75" s="103" t="inlineStr">
         <is>
           <t>Plywood 12 mm, mindi single face</t>
         </is>
       </c>
-      <c r="C75" s="81">
+      <c r="C75" s="109">
         <f>C74+$C$175</f>
         <v/>
       </c>
-      <c r="E75" s="74" t="inlineStr">
+      <c r="D75" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E75" s="95" t="n"/>
+      <c r="F75" s="95" t="n"/>
+      <c r="G75" s="95" t="n"/>
+      <c r="H75" s="95" t="n"/>
+      <c r="I75" s="95" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="75" t="inlineStr">
+      <c r="A76" s="102" t="inlineStr">
         <is>
           <t>PLY-12-MDF</t>
         </is>
       </c>
-      <c r="B76" s="74" t="inlineStr">
+      <c r="B76" s="103" t="inlineStr">
         <is>
           <t>Plywood 12 mm, mindi double face</t>
         </is>
       </c>
-      <c r="C76" s="81">
+      <c r="C76" s="109">
         <f>C74+2*$C$175</f>
         <v/>
       </c>
-      <c r="E76" s="74" t="inlineStr">
+      <c r="D76" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E76" s="95" t="n"/>
+      <c r="F76" s="95" t="n"/>
+      <c r="G76" s="95" t="n"/>
+      <c r="H76" s="95" t="n"/>
+      <c r="I76" s="95" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="75" t="inlineStr">
+      <c r="A77" s="102" t="inlineStr">
         <is>
           <t>PLY-12-TSF</t>
         </is>
       </c>
-      <c r="B77" s="74" t="inlineStr">
+      <c r="B77" s="103" t="inlineStr">
         <is>
           <t>Plywood 12 mm, teak single face</t>
         </is>
       </c>
-      <c r="C77" s="81">
+      <c r="C77" s="109">
         <f>C74+$C$176</f>
         <v/>
       </c>
-      <c r="E77" s="74" t="inlineStr">
+      <c r="D77" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E77" s="95" t="n"/>
+      <c r="F77" s="95" t="n"/>
+      <c r="G77" s="95" t="n"/>
+      <c r="H77" s="95" t="n"/>
+      <c r="I77" s="95" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="75" t="inlineStr">
+      <c r="A78" s="102" t="inlineStr">
         <is>
           <t>PLY-12-TDF</t>
         </is>
       </c>
-      <c r="B78" s="74" t="inlineStr">
+      <c r="B78" s="103" t="inlineStr">
         <is>
           <t>Plywood 12 mm, teak double face</t>
         </is>
       </c>
-      <c r="C78" s="81">
+      <c r="C78" s="109">
         <f>C74+2*$C$176</f>
         <v/>
       </c>
-      <c r="E78" s="74" t="inlineStr">
+      <c r="D78" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E78" s="95" t="n"/>
+      <c r="F78" s="95" t="n"/>
+      <c r="G78" s="95" t="n"/>
+      <c r="H78" s="95" t="n"/>
+      <c r="I78" s="95" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="75" t="inlineStr">
+      <c r="A79" s="102" t="inlineStr">
         <is>
           <t>PLY-15-RAW</t>
         </is>
       </c>
-      <c r="B79" s="74" t="inlineStr">
+      <c r="B79" s="103" t="inlineStr">
         <is>
           <t>Plywood 15 mm, raw</t>
         </is>
       </c>
-      <c r="C79" s="80" t="n">
+      <c r="C79" s="105" t="n">
         <v>260000</v>
       </c>
-      <c r="E79" s="74" t="inlineStr">
+      <c r="D79" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F79" s="74" t="inlineStr">
+      <c r="E79" s="96" t="inlineStr">
         <is>
           <t>Mojo Indah list, Sep 2026</t>
         </is>
       </c>
-      <c r="G79" s="82">
-        <f t="array" ref="G79">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H79" s="83">
-        <f>G79*$C$172</f>
-        <v/>
-      </c>
+      <c r="F79" s="112">
+        <f t="array" ref="F79">INDEX($F$178:$F$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G79" s="112">
+        <f>F79*$C$172</f>
+        <v/>
+      </c>
+      <c r="H79" s="95" t="n"/>
+      <c r="I79" s="95" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="75" t="inlineStr">
+      <c r="A80" s="102" t="inlineStr">
         <is>
           <t>PLY-15-MSF</t>
         </is>
       </c>
-      <c r="B80" s="74" t="inlineStr">
+      <c r="B80" s="103" t="inlineStr">
         <is>
           <t>Plywood 15 mm, mindi single face</t>
         </is>
       </c>
-      <c r="C80" s="81" t="n">
+      <c r="C80" s="109" t="n">
         <v>407709.02</v>
       </c>
-      <c r="E80" s="74" t="inlineStr">
+      <c r="D80" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E80" s="95" t="n"/>
+      <c r="F80" s="95" t="n"/>
+      <c r="G80" s="95" t="n"/>
+      <c r="H80" s="95" t="n"/>
+      <c r="I80" s="95" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="75" t="inlineStr">
+      <c r="A81" s="102" t="inlineStr">
         <is>
           <t>PLY-15-MDF</t>
         </is>
       </c>
-      <c r="B81" s="74" t="inlineStr">
+      <c r="B81" s="103" t="inlineStr">
         <is>
           <t>Plywood 15 mm, mindi double face</t>
         </is>
       </c>
-      <c r="C81" s="81" t="n">
+      <c r="C81" s="109" t="n">
         <v>555418.04</v>
       </c>
-      <c r="E81" s="74" t="inlineStr">
+      <c r="D81" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E81" s="95" t="n"/>
+      <c r="F81" s="95" t="n"/>
+      <c r="G81" s="95" t="n"/>
+      <c r="H81" s="95" t="n"/>
+      <c r="I81" s="95" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="75" t="inlineStr">
+      <c r="A82" s="102" t="inlineStr">
         <is>
           <t>PLY-15-TSF</t>
         </is>
       </c>
-      <c r="B82" s="74" t="inlineStr">
+      <c r="B82" s="103" t="inlineStr">
         <is>
           <t>Plywood 15 mm, teak single face</t>
         </is>
       </c>
-      <c r="C82" s="81" t="n">
+      <c r="C82" s="109" t="n">
         <v>601201.02</v>
       </c>
-      <c r="E82" s="74" t="inlineStr">
+      <c r="D82" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E82" s="95" t="n"/>
+      <c r="F82" s="95" t="n"/>
+      <c r="G82" s="95" t="n"/>
+      <c r="H82" s="95" t="n"/>
+      <c r="I82" s="95" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="75" t="inlineStr">
+      <c r="A83" s="102" t="inlineStr">
         <is>
           <t>PLY-15-TDF</t>
         </is>
       </c>
-      <c r="B83" s="74" t="inlineStr">
+      <c r="B83" s="103" t="inlineStr">
         <is>
           <t>Plywood 15 mm, teak double face</t>
         </is>
       </c>
-      <c r="C83" s="81" t="n">
+      <c r="C83" s="109" t="n">
         <v>942402.04</v>
       </c>
-      <c r="E83" s="74" t="inlineStr">
+      <c r="D83" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E83" s="95" t="n"/>
+      <c r="F83" s="95" t="n"/>
+      <c r="G83" s="95" t="n"/>
+      <c r="H83" s="95" t="n"/>
+      <c r="I83" s="95" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="75" t="inlineStr">
+      <c r="A84" s="102" t="inlineStr">
         <is>
           <t>PLY-18-RAW</t>
         </is>
       </c>
-      <c r="B84" s="74" t="inlineStr">
+      <c r="B84" s="103" t="inlineStr">
         <is>
           <t>Plywood 18 mm, raw</t>
         </is>
       </c>
-      <c r="C84" s="80">
-        <f>H84</f>
-        <v/>
-      </c>
-      <c r="E84" s="74" t="inlineStr">
+      <c r="C84" s="105">
+        <f>G84</f>
+        <v/>
+      </c>
+      <c r="D84" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F84" s="74" t="inlineStr">
+      <c r="E84" s="96" t="inlineStr">
         <is>
           <t>Mojo Indah list, Sep 2026</t>
         </is>
       </c>
-      <c r="G84" s="82">
-        <f t="array" ref="G84">INDEX($G$178:$G$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H84" s="83">
-        <f>G84*$C$172</f>
-        <v/>
-      </c>
+      <c r="F84" s="112">
+        <f t="array" ref="F84">INDEX($F$178:$F$215,MATCH("LND-PLY-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G84" s="112">
+        <f>F84*$C$172</f>
+        <v/>
+      </c>
+      <c r="H84" s="95" t="n"/>
+      <c r="I84" s="95" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="75" t="inlineStr">
+      <c r="A85" s="102" t="inlineStr">
         <is>
           <t>PLY-18-MSF</t>
         </is>
       </c>
-      <c r="B85" s="74" t="inlineStr">
+      <c r="B85" s="103" t="inlineStr">
         <is>
           <t>Plywood 18 mm, mindi single face</t>
         </is>
       </c>
-      <c r="C85" s="81">
+      <c r="C85" s="109">
         <f>C84+$C$175</f>
         <v/>
       </c>
-      <c r="E85" s="74" t="inlineStr">
+      <c r="D85" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E85" s="95" t="n"/>
+      <c r="F85" s="95" t="n"/>
+      <c r="G85" s="95" t="n"/>
+      <c r="H85" s="95" t="n"/>
+      <c r="I85" s="95" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="75" t="inlineStr">
+      <c r="A86" s="102" t="inlineStr">
         <is>
           <t>PLY-18-MDF</t>
         </is>
       </c>
-      <c r="B86" s="74" t="inlineStr">
+      <c r="B86" s="103" t="inlineStr">
         <is>
           <t>Plywood 18 mm, mindi double face</t>
         </is>
       </c>
-      <c r="C86" s="81">
+      <c r="C86" s="109">
         <f>C84+2*$C$175</f>
         <v/>
       </c>
-      <c r="E86" s="74" t="inlineStr">
+      <c r="D86" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E86" s="95" t="n"/>
+      <c r="F86" s="95" t="n"/>
+      <c r="G86" s="95" t="n"/>
+      <c r="H86" s="95" t="n"/>
+      <c r="I86" s="95" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="75" t="inlineStr">
+      <c r="A87" s="102" t="inlineStr">
         <is>
           <t>PLY-18-TSF</t>
         </is>
       </c>
-      <c r="B87" s="74" t="inlineStr">
+      <c r="B87" s="103" t="inlineStr">
         <is>
           <t>Plywood 18 mm, teak single face</t>
         </is>
       </c>
-      <c r="C87" s="81">
+      <c r="C87" s="109">
         <f>C84+$C$176</f>
         <v/>
       </c>
-      <c r="E87" s="74" t="inlineStr">
+      <c r="D87" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E87" s="95" t="n"/>
+      <c r="F87" s="95" t="n"/>
+      <c r="G87" s="95" t="n"/>
+      <c r="H87" s="95" t="n"/>
+      <c r="I87" s="95" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="75" t="inlineStr">
+      <c r="A88" s="102" t="inlineStr">
         <is>
           <t>PLY-18-TDF</t>
         </is>
       </c>
-      <c r="B88" s="74" t="inlineStr">
+      <c r="B88" s="103" t="inlineStr">
         <is>
           <t>Plywood 18 mm, teak double face</t>
         </is>
       </c>
-      <c r="C88" s="81">
+      <c r="C88" s="109">
         <f>C84+2*$C$176</f>
         <v/>
       </c>
-      <c r="E88" s="74" t="inlineStr">
+      <c r="D88" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E88" s="95" t="n"/>
+      <c r="F88" s="95" t="n"/>
+      <c r="G88" s="95" t="n"/>
+      <c r="H88" s="95" t="n"/>
+      <c r="I88" s="95" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="75" t="inlineStr">
+      <c r="A89" s="102" t="inlineStr">
         <is>
           <t>PLY-24-RAW</t>
         </is>
       </c>
-      <c r="B89" s="74" t="inlineStr">
+      <c r="B89" s="103" t="inlineStr">
         <is>
           <t>Plywood 24 mm, raw</t>
         </is>
       </c>
-      <c r="C89" s="80" t="n">
+      <c r="C89" s="105" t="n">
         <v>375000</v>
       </c>
-      <c r="E89" s="74" t="inlineStr">
+      <c r="D89" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F89" s="74" t="inlineStr">
+      <c r="E89" s="96" t="inlineStr">
         <is>
           <t>Extrapolated. Status CONFIRM</t>
         </is>
       </c>
+      <c r="F89" s="95" t="n"/>
+      <c r="G89" s="95" t="n"/>
+      <c r="H89" s="95" t="n"/>
+      <c r="I89" s="95" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="75" t="inlineStr">
+      <c r="A90" s="102" t="inlineStr">
         <is>
           <t>PLY-24-MSF</t>
         </is>
       </c>
-      <c r="B90" s="74" t="inlineStr">
+      <c r="B90" s="103" t="inlineStr">
         <is>
           <t>Plywood 24 mm, mindi single face</t>
         </is>
       </c>
-      <c r="C90" s="81" t="n">
+      <c r="C90" s="109" t="n">
         <v>522709.02</v>
       </c>
-      <c r="E90" s="74" t="inlineStr">
+      <c r="D90" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E90" s="95" t="n"/>
+      <c r="F90" s="95" t="n"/>
+      <c r="G90" s="95" t="n"/>
+      <c r="H90" s="95" t="n"/>
+      <c r="I90" s="95" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="75" t="inlineStr">
+      <c r="A91" s="102" t="inlineStr">
         <is>
           <t>PLY-24-MDF</t>
         </is>
       </c>
-      <c r="B91" s="74" t="inlineStr">
+      <c r="B91" s="103" t="inlineStr">
         <is>
           <t>Plywood 24 mm, mindi double face</t>
         </is>
       </c>
-      <c r="C91" s="81" t="n">
+      <c r="C91" s="109" t="n">
         <v>670418.04</v>
       </c>
-      <c r="E91" s="74" t="inlineStr">
+      <c r="D91" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E91" s="95" t="n"/>
+      <c r="F91" s="95" t="n"/>
+      <c r="G91" s="95" t="n"/>
+      <c r="H91" s="95" t="n"/>
+      <c r="I91" s="95" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="75" t="inlineStr">
+      <c r="A92" s="102" t="inlineStr">
         <is>
           <t>PLY-24-TSF</t>
         </is>
       </c>
-      <c r="B92" s="74" t="inlineStr">
+      <c r="B92" s="103" t="inlineStr">
         <is>
           <t>Plywood 24 mm, teak single face</t>
         </is>
       </c>
-      <c r="C92" s="81" t="n">
+      <c r="C92" s="109" t="n">
         <v>716201.02</v>
       </c>
-      <c r="E92" s="74" t="inlineStr">
+      <c r="D92" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E92" s="95" t="n"/>
+      <c r="F92" s="95" t="n"/>
+      <c r="G92" s="95" t="n"/>
+      <c r="H92" s="95" t="n"/>
+      <c r="I92" s="95" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="75" t="inlineStr">
+      <c r="A93" s="102" t="inlineStr">
         <is>
           <t>PLY-24-TDF</t>
         </is>
       </c>
-      <c r="B93" s="74" t="inlineStr">
+      <c r="B93" s="103" t="inlineStr">
         <is>
           <t>Plywood 24 mm, teak double face</t>
         </is>
       </c>
-      <c r="C93" s="81" t="n">
+      <c r="C93" s="109" t="n">
         <v>1057402.04</v>
       </c>
-      <c r="E93" s="74" t="inlineStr">
+      <c r="D93" s="96" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E93" s="95" t="n"/>
+      <c r="F93" s="95" t="n"/>
+      <c r="G93" s="95" t="n"/>
+      <c r="H93" s="95" t="n"/>
+      <c r="I93" s="95" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="75" t="inlineStr">
+      <c r="A94" s="102" t="inlineStr">
         <is>
           <t>NORMS</t>
         </is>
       </c>
+      <c r="B94" s="93" t="n"/>
+      <c r="C94" s="94" t="n"/>
+      <c r="D94" s="95" t="n"/>
+      <c r="E94" s="95" t="n"/>
+      <c r="F94" s="95" t="n"/>
+      <c r="G94" s="95" t="n"/>
+      <c r="H94" s="95" t="n"/>
+      <c r="I94" s="95" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="75" t="inlineStr">
+      <c r="A95" s="102" t="inlineStr">
         <is>
           <t>CARTON_MIN_M2</t>
         </is>
       </c>
-      <c r="B95" s="74" t="inlineStr">
+      <c r="B95" s="103" t="inlineStr">
         <is>
           <t>Below this carton area use group A price</t>
         </is>
       </c>
-      <c r="C95" s="80" t="n">
+      <c r="C95" s="107" t="n">
         <v>0.15</v>
       </c>
-      <c r="E95" s="74" t="inlineStr">
+      <c r="D95" s="96" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
+      <c r="E95" s="95" t="n"/>
+      <c r="F95" s="95" t="n"/>
+      <c r="G95" s="95" t="n"/>
+      <c r="H95" s="95" t="n"/>
+      <c r="I95" s="95" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="75" t="inlineStr">
+      <c r="A96" s="102" t="inlineStr">
         <is>
           <t>KD_PACK_FACTOR</t>
         </is>
       </c>
-      <c r="B96" s="74" t="inlineStr">
+      <c r="B96" s="103" t="inlineStr">
         <is>
           <t>Extra consumables factor for flatpack (2+ boxes)</t>
         </is>
       </c>
-      <c r="C96" s="80" t="n">
+      <c r="C96" s="106" t="n">
         <v>0</v>
       </c>
-      <c r="E96" s="74" t="inlineStr">
+      <c r="D96" s="96" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F96" s="74" t="inlineStr">
+      <c r="E96" s="96" t="inlineStr">
         <is>
           <t>0 = off</t>
         </is>
       </c>
+      <c r="F96" s="95" t="n"/>
+      <c r="G96" s="95" t="n"/>
+      <c r="H96" s="95" t="n"/>
+      <c r="I96" s="95" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="75" t="inlineStr">
+      <c r="A97" s="102" t="inlineStr">
         <is>
           <t>WASTE_REUSE_MIN</t>
         </is>
       </c>
-      <c r="B97" s="74" t="inlineStr">
+      <c r="B97" s="103" t="inlineStr">
         <is>
           <t>Offcut on the last sheet counts as reusable when waste exceeds this</t>
         </is>
       </c>
-      <c r="C97" s="80" t="n">
+      <c r="C97" s="106" t="n">
         <v>0.25</v>
       </c>
-      <c r="E97" s="74" t="inlineStr">
+      <c r="D97" s="96" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F97" s="74" t="inlineStr">
+      <c r="E97" s="96" t="inlineStr">
         <is>
           <t>Decision 29 Sep</t>
         </is>
       </c>
+      <c r="F97" s="95" t="n"/>
+      <c r="G97" s="95" t="n"/>
+      <c r="H97" s="95" t="n"/>
+      <c r="I97" s="95" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="75" t="inlineStr">
+      <c r="A98" s="102" t="inlineStr">
         <is>
           <t>OFFCUT_HANDLING</t>
         </is>
       </c>
-      <c r="B98" s="74" t="inlineStr">
+      <c r="B98" s="103" t="inlineStr">
         <is>
           <t>Handling factor on fractional sheets when the offcut is reused</t>
         </is>
       </c>
-      <c r="C98" s="80" t="n">
+      <c r="C98" s="106" t="n">
         <v>0.05</v>
       </c>
-      <c r="E98" s="74" t="inlineStr">
+      <c r="D98" s="96" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
+      <c r="E98" s="95" t="n"/>
+      <c r="F98" s="95" t="n"/>
+      <c r="G98" s="95" t="n"/>
+      <c r="H98" s="95" t="n"/>
+      <c r="I98" s="95" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="84" t="inlineStr">
+      <c r="A99" s="113" t="inlineStr">
         <is>
           <t>PLY-12-CDF</t>
         </is>
       </c>
-      <c r="C99" s="85" t="n">
+      <c r="B99" s="93" t="n"/>
+      <c r="C99" s="114" t="n">
         <v>718794.04</v>
       </c>
-      <c r="E99" s="84" t="inlineStr">
+      <c r="D99" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F99" s="84" t="inlineStr">
+      <c r="E99" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F99" s="95" t="n"/>
+      <c r="G99" s="95" t="n"/>
+      <c r="H99" s="95" t="n"/>
+      <c r="I99" s="95" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="84" t="inlineStr">
+      <c r="A100" s="113" t="inlineStr">
         <is>
           <t>PLY-12-CSF</t>
         </is>
       </c>
-      <c r="C100" s="85" t="n">
+      <c r="B100" s="93" t="n"/>
+      <c r="C100" s="114" t="n">
         <v>466897.02</v>
       </c>
-      <c r="E100" s="84" t="inlineStr">
+      <c r="D100" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F100" s="84" t="inlineStr">
+      <c r="E100" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F100" s="95" t="n"/>
+      <c r="G100" s="95" t="n"/>
+      <c r="H100" s="95" t="n"/>
+      <c r="I100" s="95" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="84" t="inlineStr">
+      <c r="A101" s="113" t="inlineStr">
         <is>
           <t>PLY-12-HDF</t>
         </is>
       </c>
-      <c r="C101" s="85" t="n">
+      <c r="B101" s="93" t="n"/>
+      <c r="C101" s="114" t="n">
         <v>510418.04</v>
       </c>
-      <c r="E101" s="84" t="inlineStr">
+      <c r="D101" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F101" s="84" t="inlineStr">
+      <c r="E101" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F101" s="95" t="n"/>
+      <c r="G101" s="95" t="n"/>
+      <c r="H101" s="95" t="n"/>
+      <c r="I101" s="95" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="84" t="inlineStr">
+      <c r="A102" s="113" t="inlineStr">
         <is>
           <t>PLY-12-HSF</t>
         </is>
       </c>
-      <c r="C102" s="85" t="n">
+      <c r="B102" s="93" t="n"/>
+      <c r="C102" s="114" t="n">
         <v>362709.02</v>
       </c>
-      <c r="E102" s="84" t="inlineStr">
+      <c r="D102" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F102" s="84" t="inlineStr">
+      <c r="E102" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F102" s="95" t="n"/>
+      <c r="G102" s="95" t="n"/>
+      <c r="H102" s="95" t="n"/>
+      <c r="I102" s="95" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="84" t="inlineStr">
+      <c r="A103" s="113" t="inlineStr">
         <is>
           <t>PLY-12-ODF</t>
         </is>
       </c>
-      <c r="C103" s="85" t="n">
+      <c r="B103" s="93" t="n"/>
+      <c r="C103" s="114" t="n">
         <v>1016474.04</v>
       </c>
-      <c r="E103" s="84" t="inlineStr">
+      <c r="D103" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F103" s="84" t="inlineStr">
+      <c r="E103" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F103" s="95" t="n"/>
+      <c r="G103" s="95" t="n"/>
+      <c r="H103" s="95" t="n"/>
+      <c r="I103" s="95" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="84" t="inlineStr">
+      <c r="A104" s="113" t="inlineStr">
         <is>
           <t>PLY-12-OSF</t>
         </is>
       </c>
-      <c r="C104" s="85" t="n">
+      <c r="B104" s="93" t="n"/>
+      <c r="C104" s="114" t="n">
         <v>615737.02</v>
       </c>
-      <c r="E104" s="84" t="inlineStr">
+      <c r="D104" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F104" s="84" t="inlineStr">
+      <c r="E104" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F104" s="95" t="n"/>
+      <c r="G104" s="95" t="n"/>
+      <c r="H104" s="95" t="n"/>
+      <c r="I104" s="95" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="84" t="inlineStr">
+      <c r="A105" s="113" t="inlineStr">
         <is>
           <t>PLY-12-SDF</t>
         </is>
       </c>
-      <c r="C105" s="85" t="n">
+      <c r="B105" s="93" t="n"/>
+      <c r="C105" s="114" t="n">
         <v>689026.04</v>
       </c>
-      <c r="E105" s="84" t="inlineStr">
+      <c r="D105" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F105" s="84" t="inlineStr">
+      <c r="E105" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F105" s="95" t="n"/>
+      <c r="G105" s="95" t="n"/>
+      <c r="H105" s="95" t="n"/>
+      <c r="I105" s="95" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="84" t="inlineStr">
+      <c r="A106" s="113" t="inlineStr">
         <is>
           <t>PLY-12-SSF</t>
         </is>
       </c>
-      <c r="C106" s="85" t="n">
+      <c r="B106" s="93" t="n"/>
+      <c r="C106" s="114" t="n">
         <v>452013.02</v>
       </c>
-      <c r="E106" s="84" t="inlineStr">
+      <c r="D106" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F106" s="84" t="inlineStr">
+      <c r="E106" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F106" s="95" t="n"/>
+      <c r="G106" s="95" t="n"/>
+      <c r="H106" s="95" t="n"/>
+      <c r="I106" s="95" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="84" t="inlineStr">
+      <c r="A107" s="113" t="inlineStr">
         <is>
           <t>PLY-12-WDF</t>
         </is>
       </c>
-      <c r="C107" s="85" t="n">
+      <c r="B107" s="93" t="n"/>
+      <c r="C107" s="114" t="n">
         <v>1105778.04</v>
       </c>
-      <c r="E107" s="84" t="inlineStr">
+      <c r="D107" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F107" s="84" t="inlineStr">
+      <c r="E107" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F107" s="95" t="n"/>
+      <c r="G107" s="95" t="n"/>
+      <c r="H107" s="95" t="n"/>
+      <c r="I107" s="95" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="84" t="inlineStr">
+      <c r="A108" s="113" t="inlineStr">
         <is>
           <t>PLY-12-WSF</t>
         </is>
       </c>
-      <c r="C108" s="85" t="n">
+      <c r="B108" s="93" t="n"/>
+      <c r="C108" s="114" t="n">
         <v>660389.02</v>
       </c>
-      <c r="E108" s="84" t="inlineStr">
+      <c r="D108" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F108" s="84" t="inlineStr">
+      <c r="E108" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F108" s="95" t="n"/>
+      <c r="G108" s="95" t="n"/>
+      <c r="H108" s="95" t="n"/>
+      <c r="I108" s="95" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="84" t="inlineStr">
+      <c r="A109" s="113" t="inlineStr">
         <is>
           <t>PLY-15-CDF</t>
         </is>
       </c>
-      <c r="C109" s="85" t="n">
+      <c r="B109" s="93" t="n"/>
+      <c r="C109" s="114" t="n">
         <v>763794.04</v>
       </c>
-      <c r="E109" s="84" t="inlineStr">
+      <c r="D109" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F109" s="84" t="inlineStr">
+      <c r="E109" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F109" s="95" t="n"/>
+      <c r="G109" s="95" t="n"/>
+      <c r="H109" s="95" t="n"/>
+      <c r="I109" s="95" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="84" t="inlineStr">
+      <c r="A110" s="113" t="inlineStr">
         <is>
           <t>PLY-15-CSF</t>
         </is>
       </c>
-      <c r="C110" s="85" t="n">
+      <c r="B110" s="93" t="n"/>
+      <c r="C110" s="114" t="n">
         <v>511897.02</v>
       </c>
-      <c r="E110" s="84" t="inlineStr">
+      <c r="D110" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F110" s="84" t="inlineStr">
+      <c r="E110" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F110" s="95" t="n"/>
+      <c r="G110" s="95" t="n"/>
+      <c r="H110" s="95" t="n"/>
+      <c r="I110" s="95" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="84" t="inlineStr">
+      <c r="A111" s="113" t="inlineStr">
         <is>
           <t>PLY-15-HDF</t>
         </is>
       </c>
-      <c r="C111" s="85" t="n">
+      <c r="B111" s="93" t="n"/>
+      <c r="C111" s="114" t="n">
         <v>555418.04</v>
       </c>
-      <c r="E111" s="84" t="inlineStr">
+      <c r="D111" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F111" s="84" t="inlineStr">
+      <c r="E111" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F111" s="95" t="n"/>
+      <c r="G111" s="95" t="n"/>
+      <c r="H111" s="95" t="n"/>
+      <c r="I111" s="95" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="84" t="inlineStr">
+      <c r="A112" s="113" t="inlineStr">
         <is>
           <t>PLY-15-HSF</t>
         </is>
       </c>
-      <c r="C112" s="85" t="n">
+      <c r="B112" s="93" t="n"/>
+      <c r="C112" s="114" t="n">
         <v>407709.02</v>
       </c>
-      <c r="E112" s="84" t="inlineStr">
+      <c r="D112" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F112" s="84" t="inlineStr">
+      <c r="E112" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F112" s="95" t="n"/>
+      <c r="G112" s="95" t="n"/>
+      <c r="H112" s="95" t="n"/>
+      <c r="I112" s="95" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="84" t="inlineStr">
+      <c r="A113" s="113" t="inlineStr">
         <is>
           <t>PLY-15-ODF</t>
         </is>
       </c>
-      <c r="C113" s="85" t="n">
+      <c r="B113" s="93" t="n"/>
+      <c r="C113" s="114" t="n">
         <v>1061474.04</v>
       </c>
-      <c r="E113" s="84" t="inlineStr">
+      <c r="D113" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F113" s="84" t="inlineStr">
+      <c r="E113" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F113" s="95" t="n"/>
+      <c r="G113" s="95" t="n"/>
+      <c r="H113" s="95" t="n"/>
+      <c r="I113" s="95" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="84" t="inlineStr">
+      <c r="A114" s="113" t="inlineStr">
         <is>
           <t>PLY-15-OSF</t>
         </is>
       </c>
-      <c r="C114" s="85" t="n">
+      <c r="B114" s="93" t="n"/>
+      <c r="C114" s="114" t="n">
         <v>660737.02</v>
       </c>
-      <c r="E114" s="84" t="inlineStr">
+      <c r="D114" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F114" s="84" t="inlineStr">
+      <c r="E114" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F114" s="95" t="n"/>
+      <c r="G114" s="95" t="n"/>
+      <c r="H114" s="95" t="n"/>
+      <c r="I114" s="95" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="84" t="inlineStr">
+      <c r="A115" s="113" t="inlineStr">
         <is>
           <t>PLY-15-SDF</t>
         </is>
       </c>
-      <c r="C115" s="85" t="n">
+      <c r="B115" s="93" t="n"/>
+      <c r="C115" s="114" t="n">
         <v>734026.04</v>
       </c>
-      <c r="E115" s="84" t="inlineStr">
+      <c r="D115" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F115" s="84" t="inlineStr">
+      <c r="E115" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F115" s="95" t="n"/>
+      <c r="G115" s="95" t="n"/>
+      <c r="H115" s="95" t="n"/>
+      <c r="I115" s="95" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="84" t="inlineStr">
+      <c r="A116" s="113" t="inlineStr">
         <is>
           <t>PLY-15-SSF</t>
         </is>
       </c>
-      <c r="C116" s="85" t="n">
+      <c r="B116" s="93" t="n"/>
+      <c r="C116" s="114" t="n">
         <v>497013.02</v>
       </c>
-      <c r="E116" s="84" t="inlineStr">
+      <c r="D116" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F116" s="84" t="inlineStr">
+      <c r="E116" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F116" s="95" t="n"/>
+      <c r="G116" s="95" t="n"/>
+      <c r="H116" s="95" t="n"/>
+      <c r="I116" s="95" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="84" t="inlineStr">
+      <c r="A117" s="113" t="inlineStr">
         <is>
           <t>PLY-15-WDF</t>
         </is>
       </c>
-      <c r="C117" s="85" t="n">
+      <c r="B117" s="93" t="n"/>
+      <c r="C117" s="114" t="n">
         <v>1150778.04</v>
       </c>
-      <c r="E117" s="84" t="inlineStr">
+      <c r="D117" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F117" s="84" t="inlineStr">
+      <c r="E117" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F117" s="95" t="n"/>
+      <c r="G117" s="95" t="n"/>
+      <c r="H117" s="95" t="n"/>
+      <c r="I117" s="95" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="84" t="inlineStr">
+      <c r="A118" s="113" t="inlineStr">
         <is>
           <t>PLY-15-WSF</t>
         </is>
       </c>
-      <c r="C118" s="85" t="n">
+      <c r="B118" s="93" t="n"/>
+      <c r="C118" s="114" t="n">
         <v>705389.02</v>
       </c>
-      <c r="E118" s="84" t="inlineStr">
+      <c r="D118" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F118" s="84" t="inlineStr">
+      <c r="E118" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F118" s="95" t="n"/>
+      <c r="G118" s="95" t="n"/>
+      <c r="H118" s="95" t="n"/>
+      <c r="I118" s="95" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="84" t="inlineStr">
+      <c r="A119" s="113" t="inlineStr">
         <is>
           <t>PLY-18-CDF</t>
         </is>
       </c>
-      <c r="C119" s="85" t="n">
+      <c r="B119" s="93" t="n"/>
+      <c r="C119" s="114" t="n">
         <v>798794.04</v>
       </c>
-      <c r="E119" s="84" t="inlineStr">
+      <c r="D119" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F119" s="84" t="inlineStr">
+      <c r="E119" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F119" s="95" t="n"/>
+      <c r="G119" s="95" t="n"/>
+      <c r="H119" s="95" t="n"/>
+      <c r="I119" s="95" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="84" t="inlineStr">
+      <c r="A120" s="113" t="inlineStr">
         <is>
           <t>PLY-18-CSF</t>
         </is>
       </c>
-      <c r="C120" s="85" t="n">
+      <c r="B120" s="93" t="n"/>
+      <c r="C120" s="114" t="n">
         <v>546897.02</v>
       </c>
-      <c r="E120" s="84" t="inlineStr">
+      <c r="D120" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F120" s="84" t="inlineStr">
+      <c r="E120" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F120" s="95" t="n"/>
+      <c r="G120" s="95" t="n"/>
+      <c r="H120" s="95" t="n"/>
+      <c r="I120" s="95" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="84" t="inlineStr">
+      <c r="A121" s="113" t="inlineStr">
         <is>
           <t>PLY-18-HDF</t>
         </is>
       </c>
-      <c r="C121" s="85" t="n">
+      <c r="B121" s="93" t="n"/>
+      <c r="C121" s="114" t="n">
         <v>590418.04</v>
       </c>
-      <c r="E121" s="84" t="inlineStr">
+      <c r="D121" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F121" s="84" t="inlineStr">
+      <c r="E121" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F121" s="95" t="n"/>
+      <c r="G121" s="95" t="n"/>
+      <c r="H121" s="95" t="n"/>
+      <c r="I121" s="95" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="84" t="inlineStr">
+      <c r="A122" s="113" t="inlineStr">
         <is>
           <t>PLY-18-HSF</t>
         </is>
       </c>
-      <c r="C122" s="85" t="n">
+      <c r="B122" s="93" t="n"/>
+      <c r="C122" s="114" t="n">
         <v>442709.02</v>
       </c>
-      <c r="E122" s="84" t="inlineStr">
+      <c r="D122" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F122" s="84" t="inlineStr">
+      <c r="E122" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F122" s="95" t="n"/>
+      <c r="G122" s="95" t="n"/>
+      <c r="H122" s="95" t="n"/>
+      <c r="I122" s="95" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="84" t="inlineStr">
+      <c r="A123" s="113" t="inlineStr">
         <is>
           <t>PLY-18-ODF</t>
         </is>
       </c>
-      <c r="C123" s="85" t="n">
+      <c r="B123" s="93" t="n"/>
+      <c r="C123" s="114" t="n">
         <v>1096474.04</v>
       </c>
-      <c r="E123" s="84" t="inlineStr">
+      <c r="D123" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F123" s="84" t="inlineStr">
+      <c r="E123" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F123" s="95" t="n"/>
+      <c r="G123" s="95" t="n"/>
+      <c r="H123" s="95" t="n"/>
+      <c r="I123" s="95" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="84" t="inlineStr">
+      <c r="A124" s="113" t="inlineStr">
         <is>
           <t>PLY-18-OSF</t>
         </is>
       </c>
-      <c r="C124" s="85" t="n">
+      <c r="B124" s="93" t="n"/>
+      <c r="C124" s="114" t="n">
         <v>695737.02</v>
       </c>
-      <c r="E124" s="84" t="inlineStr">
+      <c r="D124" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F124" s="84" t="inlineStr">
+      <c r="E124" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F124" s="95" t="n"/>
+      <c r="G124" s="95" t="n"/>
+      <c r="H124" s="95" t="n"/>
+      <c r="I124" s="95" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="84" t="inlineStr">
+      <c r="A125" s="113" t="inlineStr">
         <is>
           <t>PLY-18-SDF</t>
         </is>
       </c>
-      <c r="C125" s="85" t="n">
+      <c r="B125" s="93" t="n"/>
+      <c r="C125" s="114" t="n">
         <v>769026.04</v>
       </c>
-      <c r="E125" s="84" t="inlineStr">
+      <c r="D125" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F125" s="84" t="inlineStr">
+      <c r="E125" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F125" s="95" t="n"/>
+      <c r="G125" s="95" t="n"/>
+      <c r="H125" s="95" t="n"/>
+      <c r="I125" s="95" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="84" t="inlineStr">
+      <c r="A126" s="113" t="inlineStr">
         <is>
           <t>PLY-18-SSF</t>
         </is>
       </c>
-      <c r="C126" s="85" t="n">
+      <c r="B126" s="93" t="n"/>
+      <c r="C126" s="114" t="n">
         <v>532013.02</v>
       </c>
-      <c r="E126" s="84" t="inlineStr">
+      <c r="D126" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F126" s="84" t="inlineStr">
+      <c r="E126" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F126" s="95" t="n"/>
+      <c r="G126" s="95" t="n"/>
+      <c r="H126" s="95" t="n"/>
+      <c r="I126" s="95" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="84" t="inlineStr">
+      <c r="A127" s="113" t="inlineStr">
         <is>
           <t>PLY-18-WDF</t>
         </is>
       </c>
-      <c r="C127" s="85" t="n">
+      <c r="B127" s="93" t="n"/>
+      <c r="C127" s="114" t="n">
         <v>1185778.04</v>
       </c>
-      <c r="E127" s="84" t="inlineStr">
+      <c r="D127" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F127" s="84" t="inlineStr">
+      <c r="E127" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F127" s="95" t="n"/>
+      <c r="G127" s="95" t="n"/>
+      <c r="H127" s="95" t="n"/>
+      <c r="I127" s="95" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="84" t="inlineStr">
+      <c r="A128" s="113" t="inlineStr">
         <is>
           <t>PLY-18-WSF</t>
         </is>
       </c>
-      <c r="C128" s="85" t="n">
+      <c r="B128" s="93" t="n"/>
+      <c r="C128" s="114" t="n">
         <v>740389.02</v>
       </c>
-      <c r="E128" s="84" t="inlineStr">
+      <c r="D128" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F128" s="84" t="inlineStr">
+      <c r="E128" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F128" s="95" t="n"/>
+      <c r="G128" s="95" t="n"/>
+      <c r="H128" s="95" t="n"/>
+      <c r="I128" s="95" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="84" t="inlineStr">
+      <c r="A129" s="113" t="inlineStr">
         <is>
           <t>PLY-24-CDF</t>
         </is>
       </c>
-      <c r="C129" s="85" t="n">
+      <c r="B129" s="93" t="n"/>
+      <c r="C129" s="114" t="n">
         <v>878794.04</v>
       </c>
-      <c r="E129" s="84" t="inlineStr">
+      <c r="D129" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F129" s="84" t="inlineStr">
+      <c r="E129" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F129" s="95" t="n"/>
+      <c r="G129" s="95" t="n"/>
+      <c r="H129" s="95" t="n"/>
+      <c r="I129" s="95" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="84" t="inlineStr">
+      <c r="A130" s="113" t="inlineStr">
         <is>
           <t>PLY-24-CSF</t>
         </is>
       </c>
-      <c r="C130" s="85" t="n">
+      <c r="B130" s="93" t="n"/>
+      <c r="C130" s="114" t="n">
         <v>626897.02</v>
       </c>
-      <c r="E130" s="84" t="inlineStr">
+      <c r="D130" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F130" s="84" t="inlineStr">
+      <c r="E130" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F130" s="95" t="n"/>
+      <c r="G130" s="95" t="n"/>
+      <c r="H130" s="95" t="n"/>
+      <c r="I130" s="95" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="84" t="inlineStr">
+      <c r="A131" s="113" t="inlineStr">
         <is>
           <t>PLY-24-HDF</t>
         </is>
       </c>
-      <c r="C131" s="85" t="n">
+      <c r="B131" s="93" t="n"/>
+      <c r="C131" s="114" t="n">
         <v>670418.04</v>
       </c>
-      <c r="E131" s="84" t="inlineStr">
+      <c r="D131" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F131" s="84" t="inlineStr">
+      <c r="E131" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F131" s="95" t="n"/>
+      <c r="G131" s="95" t="n"/>
+      <c r="H131" s="95" t="n"/>
+      <c r="I131" s="95" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="84" t="inlineStr">
+      <c r="A132" s="113" t="inlineStr">
         <is>
           <t>PLY-24-HSF</t>
         </is>
       </c>
-      <c r="C132" s="85" t="n">
+      <c r="B132" s="93" t="n"/>
+      <c r="C132" s="114" t="n">
         <v>522709.02</v>
       </c>
-      <c r="E132" s="84" t="inlineStr">
+      <c r="D132" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F132" s="84" t="inlineStr">
+      <c r="E132" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F132" s="95" t="n"/>
+      <c r="G132" s="95" t="n"/>
+      <c r="H132" s="95" t="n"/>
+      <c r="I132" s="95" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="84" t="inlineStr">
+      <c r="A133" s="113" t="inlineStr">
         <is>
           <t>PLY-24-ODF</t>
         </is>
       </c>
-      <c r="C133" s="85" t="n">
+      <c r="B133" s="93" t="n"/>
+      <c r="C133" s="114" t="n">
         <v>1176474.04</v>
       </c>
-      <c r="E133" s="84" t="inlineStr">
+      <c r="D133" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F133" s="84" t="inlineStr">
+      <c r="E133" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F133" s="95" t="n"/>
+      <c r="G133" s="95" t="n"/>
+      <c r="H133" s="95" t="n"/>
+      <c r="I133" s="95" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="84" t="inlineStr">
+      <c r="A134" s="113" t="inlineStr">
         <is>
           <t>PLY-24-OSF</t>
         </is>
       </c>
-      <c r="C134" s="85" t="n">
+      <c r="B134" s="93" t="n"/>
+      <c r="C134" s="114" t="n">
         <v>775737.02</v>
       </c>
-      <c r="E134" s="84" t="inlineStr">
+      <c r="D134" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F134" s="84" t="inlineStr">
+      <c r="E134" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F134" s="95" t="n"/>
+      <c r="G134" s="95" t="n"/>
+      <c r="H134" s="95" t="n"/>
+      <c r="I134" s="95" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="84" t="inlineStr">
+      <c r="A135" s="113" t="inlineStr">
         <is>
           <t>PLY-24-SDF</t>
         </is>
       </c>
-      <c r="C135" s="85" t="n">
+      <c r="B135" s="93" t="n"/>
+      <c r="C135" s="114" t="n">
         <v>849026.04</v>
       </c>
-      <c r="E135" s="84" t="inlineStr">
+      <c r="D135" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F135" s="84" t="inlineStr">
+      <c r="E135" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F135" s="95" t="n"/>
+      <c r="G135" s="95" t="n"/>
+      <c r="H135" s="95" t="n"/>
+      <c r="I135" s="95" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="84" t="inlineStr">
+      <c r="A136" s="113" t="inlineStr">
         <is>
           <t>PLY-24-SSF</t>
         </is>
       </c>
-      <c r="C136" s="85" t="n">
+      <c r="B136" s="93" t="n"/>
+      <c r="C136" s="114" t="n">
         <v>612013.02</v>
       </c>
-      <c r="E136" s="84" t="inlineStr">
+      <c r="D136" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F136" s="84" t="inlineStr">
+      <c r="E136" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F136" s="95" t="n"/>
+      <c r="G136" s="95" t="n"/>
+      <c r="H136" s="95" t="n"/>
+      <c r="I136" s="95" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="84" t="inlineStr">
+      <c r="A137" s="113" t="inlineStr">
         <is>
           <t>PLY-24-WDF</t>
         </is>
       </c>
-      <c r="C137" s="85" t="n">
+      <c r="B137" s="93" t="n"/>
+      <c r="C137" s="114" t="n">
         <v>1265778.04</v>
       </c>
-      <c r="E137" s="84" t="inlineStr">
+      <c r="D137" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F137" s="84" t="inlineStr">
+      <c r="E137" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F137" s="95" t="n"/>
+      <c r="G137" s="95" t="n"/>
+      <c r="H137" s="95" t="n"/>
+      <c r="I137" s="95" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="84" t="inlineStr">
+      <c r="A138" s="113" t="inlineStr">
         <is>
           <t>PLY-24-WSF</t>
         </is>
       </c>
-      <c r="C138" s="85" t="n">
+      <c r="B138" s="93" t="n"/>
+      <c r="C138" s="114" t="n">
         <v>820389.02</v>
       </c>
-      <c r="E138" s="84" t="inlineStr">
+      <c r="D138" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F138" s="84" t="inlineStr">
+      <c r="E138" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F138" s="95" t="n"/>
+      <c r="G138" s="95" t="n"/>
+      <c r="H138" s="95" t="n"/>
+      <c r="I138" s="95" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="84" t="inlineStr">
+      <c r="A139" s="113" t="inlineStr">
         <is>
           <t>PLY-3-CDF</t>
         </is>
       </c>
-      <c r="C139" s="85" t="n">
+      <c r="B139" s="93" t="n"/>
+      <c r="C139" s="114" t="n">
         <v>581294.04</v>
       </c>
-      <c r="E139" s="84" t="inlineStr">
+      <c r="D139" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F139" s="84" t="inlineStr">
+      <c r="E139" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F139" s="95" t="n"/>
+      <c r="G139" s="95" t="n"/>
+      <c r="H139" s="95" t="n"/>
+      <c r="I139" s="95" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="84" t="inlineStr">
+      <c r="A140" s="113" t="inlineStr">
         <is>
           <t>PLY-3-CSF</t>
         </is>
       </c>
-      <c r="C140" s="85" t="n">
+      <c r="B140" s="93" t="n"/>
+      <c r="C140" s="114" t="n">
         <v>329397.02</v>
       </c>
-      <c r="E140" s="84" t="inlineStr">
+      <c r="D140" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F140" s="84" t="inlineStr">
+      <c r="E140" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F140" s="95" t="n"/>
+      <c r="G140" s="95" t="n"/>
+      <c r="H140" s="95" t="n"/>
+      <c r="I140" s="95" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="84" t="inlineStr">
+      <c r="A141" s="113" t="inlineStr">
         <is>
           <t>PLY-3-HDF</t>
         </is>
       </c>
-      <c r="C141" s="85" t="n">
+      <c r="B141" s="93" t="n"/>
+      <c r="C141" s="114" t="n">
         <v>372918.04</v>
       </c>
-      <c r="E141" s="84" t="inlineStr">
+      <c r="D141" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F141" s="84" t="inlineStr">
+      <c r="E141" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F141" s="95" t="n"/>
+      <c r="G141" s="95" t="n"/>
+      <c r="H141" s="95" t="n"/>
+      <c r="I141" s="95" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="84" t="inlineStr">
+      <c r="A142" s="113" t="inlineStr">
         <is>
           <t>PLY-3-HSF</t>
         </is>
       </c>
-      <c r="C142" s="85" t="n">
+      <c r="B142" s="93" t="n"/>
+      <c r="C142" s="114" t="n">
         <v>225209.02</v>
       </c>
-      <c r="E142" s="84" t="inlineStr">
+      <c r="D142" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F142" s="84" t="inlineStr">
+      <c r="E142" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F142" s="95" t="n"/>
+      <c r="G142" s="95" t="n"/>
+      <c r="H142" s="95" t="n"/>
+      <c r="I142" s="95" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="84" t="inlineStr">
+      <c r="A143" s="113" t="inlineStr">
         <is>
           <t>PLY-3-ODF</t>
         </is>
       </c>
-      <c r="C143" s="85" t="n">
+      <c r="B143" s="93" t="n"/>
+      <c r="C143" s="114" t="n">
         <v>878974.04</v>
       </c>
-      <c r="E143" s="84" t="inlineStr">
+      <c r="D143" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F143" s="84" t="inlineStr">
+      <c r="E143" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F143" s="95" t="n"/>
+      <c r="G143" s="95" t="n"/>
+      <c r="H143" s="95" t="n"/>
+      <c r="I143" s="95" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="84" t="inlineStr">
+      <c r="A144" s="113" t="inlineStr">
         <is>
           <t>PLY-3-OSF</t>
         </is>
       </c>
-      <c r="C144" s="85" t="n">
+      <c r="B144" s="93" t="n"/>
+      <c r="C144" s="114" t="n">
         <v>478237.02</v>
       </c>
-      <c r="E144" s="84" t="inlineStr">
+      <c r="D144" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F144" s="84" t="inlineStr">
+      <c r="E144" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F144" s="95" t="n"/>
+      <c r="G144" s="95" t="n"/>
+      <c r="H144" s="95" t="n"/>
+      <c r="I144" s="95" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="84" t="inlineStr">
+      <c r="A145" s="113" t="inlineStr">
         <is>
           <t>PLY-3-SDF</t>
         </is>
       </c>
-      <c r="C145" s="85" t="n">
+      <c r="B145" s="93" t="n"/>
+      <c r="C145" s="114" t="n">
         <v>551526.04</v>
       </c>
-      <c r="E145" s="84" t="inlineStr">
+      <c r="D145" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F145" s="84" t="inlineStr">
+      <c r="E145" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F145" s="95" t="n"/>
+      <c r="G145" s="95" t="n"/>
+      <c r="H145" s="95" t="n"/>
+      <c r="I145" s="95" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="84" t="inlineStr">
+      <c r="A146" s="113" t="inlineStr">
         <is>
           <t>PLY-3-SSF</t>
         </is>
       </c>
-      <c r="C146" s="85" t="n">
+      <c r="B146" s="93" t="n"/>
+      <c r="C146" s="114" t="n">
         <v>314513.02</v>
       </c>
-      <c r="E146" s="84" t="inlineStr">
+      <c r="D146" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F146" s="84" t="inlineStr">
+      <c r="E146" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F146" s="95" t="n"/>
+      <c r="G146" s="95" t="n"/>
+      <c r="H146" s="95" t="n"/>
+      <c r="I146" s="95" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="84" t="inlineStr">
+      <c r="A147" s="113" t="inlineStr">
         <is>
           <t>PLY-3-WDF</t>
         </is>
       </c>
-      <c r="C147" s="85" t="n">
+      <c r="B147" s="93" t="n"/>
+      <c r="C147" s="114" t="n">
         <v>968278.04</v>
       </c>
-      <c r="E147" s="84" t="inlineStr">
+      <c r="D147" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F147" s="84" t="inlineStr">
+      <c r="E147" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F147" s="95" t="n"/>
+      <c r="G147" s="95" t="n"/>
+      <c r="H147" s="95" t="n"/>
+      <c r="I147" s="95" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="84" t="inlineStr">
+      <c r="A148" s="113" t="inlineStr">
         <is>
           <t>PLY-3-WSF</t>
         </is>
       </c>
-      <c r="C148" s="85" t="n">
+      <c r="B148" s="93" t="n"/>
+      <c r="C148" s="114" t="n">
         <v>522889.02</v>
       </c>
-      <c r="E148" s="84" t="inlineStr">
+      <c r="D148" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F148" s="84" t="inlineStr">
+      <c r="E148" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F148" s="95" t="n"/>
+      <c r="G148" s="95" t="n"/>
+      <c r="H148" s="95" t="n"/>
+      <c r="I148" s="95" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="84" t="inlineStr">
+      <c r="A149" s="113" t="inlineStr">
         <is>
           <t>PLY-6-CDF</t>
         </is>
       </c>
-      <c r="C149" s="85" t="n">
+      <c r="B149" s="93" t="n"/>
+      <c r="C149" s="114" t="n">
         <v>618794.04</v>
       </c>
-      <c r="E149" s="84" t="inlineStr">
+      <c r="D149" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F149" s="84" t="inlineStr">
+      <c r="E149" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F149" s="95" t="n"/>
+      <c r="G149" s="95" t="n"/>
+      <c r="H149" s="95" t="n"/>
+      <c r="I149" s="95" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="84" t="inlineStr">
+      <c r="A150" s="113" t="inlineStr">
         <is>
           <t>PLY-6-CSF</t>
         </is>
       </c>
-      <c r="C150" s="85" t="n">
+      <c r="B150" s="93" t="n"/>
+      <c r="C150" s="114" t="n">
         <v>366897.02</v>
       </c>
-      <c r="E150" s="84" t="inlineStr">
+      <c r="D150" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F150" s="84" t="inlineStr">
+      <c r="E150" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F150" s="95" t="n"/>
+      <c r="G150" s="95" t="n"/>
+      <c r="H150" s="95" t="n"/>
+      <c r="I150" s="95" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="84" t="inlineStr">
+      <c r="A151" s="113" t="inlineStr">
         <is>
           <t>PLY-6-HDF</t>
         </is>
       </c>
-      <c r="C151" s="85" t="n">
+      <c r="B151" s="93" t="n"/>
+      <c r="C151" s="114" t="n">
         <v>410418.04</v>
       </c>
-      <c r="E151" s="84" t="inlineStr">
+      <c r="D151" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F151" s="84" t="inlineStr">
+      <c r="E151" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F151" s="95" t="n"/>
+      <c r="G151" s="95" t="n"/>
+      <c r="H151" s="95" t="n"/>
+      <c r="I151" s="95" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="84" t="inlineStr">
+      <c r="A152" s="113" t="inlineStr">
         <is>
           <t>PLY-6-HSF</t>
         </is>
       </c>
-      <c r="C152" s="85" t="n">
+      <c r="B152" s="93" t="n"/>
+      <c r="C152" s="114" t="n">
         <v>262709.02</v>
       </c>
-      <c r="E152" s="84" t="inlineStr">
+      <c r="D152" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F152" s="84" t="inlineStr">
+      <c r="E152" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F152" s="95" t="n"/>
+      <c r="G152" s="95" t="n"/>
+      <c r="H152" s="95" t="n"/>
+      <c r="I152" s="95" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="84" t="inlineStr">
+      <c r="A153" s="113" t="inlineStr">
         <is>
           <t>PLY-6-ODF</t>
         </is>
       </c>
-      <c r="C153" s="85" t="n">
+      <c r="B153" s="93" t="n"/>
+      <c r="C153" s="114" t="n">
         <v>916474.04</v>
       </c>
-      <c r="E153" s="84" t="inlineStr">
+      <c r="D153" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F153" s="84" t="inlineStr">
+      <c r="E153" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F153" s="95" t="n"/>
+      <c r="G153" s="95" t="n"/>
+      <c r="H153" s="95" t="n"/>
+      <c r="I153" s="95" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="84" t="inlineStr">
+      <c r="A154" s="113" t="inlineStr">
         <is>
           <t>PLY-6-OSF</t>
         </is>
       </c>
-      <c r="C154" s="85" t="n">
+      <c r="B154" s="93" t="n"/>
+      <c r="C154" s="114" t="n">
         <v>515737.02</v>
       </c>
-      <c r="E154" s="84" t="inlineStr">
+      <c r="D154" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F154" s="84" t="inlineStr">
+      <c r="E154" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F154" s="95" t="n"/>
+      <c r="G154" s="95" t="n"/>
+      <c r="H154" s="95" t="n"/>
+      <c r="I154" s="95" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="84" t="inlineStr">
+      <c r="A155" s="113" t="inlineStr">
         <is>
           <t>PLY-6-SDF</t>
         </is>
       </c>
-      <c r="C155" s="85" t="n">
+      <c r="B155" s="93" t="n"/>
+      <c r="C155" s="114" t="n">
         <v>589026.04</v>
       </c>
-      <c r="E155" s="84" t="inlineStr">
+      <c r="D155" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F155" s="84" t="inlineStr">
+      <c r="E155" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F155" s="95" t="n"/>
+      <c r="G155" s="95" t="n"/>
+      <c r="H155" s="95" t="n"/>
+      <c r="I155" s="95" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="84" t="inlineStr">
+      <c r="A156" s="113" t="inlineStr">
         <is>
           <t>PLY-6-SSF</t>
         </is>
       </c>
-      <c r="C156" s="85" t="n">
+      <c r="B156" s="93" t="n"/>
+      <c r="C156" s="114" t="n">
         <v>352013.02</v>
       </c>
-      <c r="E156" s="84" t="inlineStr">
+      <c r="D156" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F156" s="84" t="inlineStr">
+      <c r="E156" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F156" s="95" t="n"/>
+      <c r="G156" s="95" t="n"/>
+      <c r="H156" s="95" t="n"/>
+      <c r="I156" s="95" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="84" t="inlineStr">
+      <c r="A157" s="113" t="inlineStr">
         <is>
           <t>PLY-6-WDF</t>
         </is>
       </c>
-      <c r="C157" s="85" t="n">
+      <c r="B157" s="93" t="n"/>
+      <c r="C157" s="114" t="n">
         <v>1005778.04</v>
       </c>
-      <c r="E157" s="84" t="inlineStr">
+      <c r="D157" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F157" s="84" t="inlineStr">
+      <c r="E157" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F157" s="95" t="n"/>
+      <c r="G157" s="95" t="n"/>
+      <c r="H157" s="95" t="n"/>
+      <c r="I157" s="95" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="84" t="inlineStr">
+      <c r="A158" s="113" t="inlineStr">
         <is>
           <t>PLY-6-WSF</t>
         </is>
       </c>
-      <c r="C158" s="85" t="n">
+      <c r="B158" s="93" t="n"/>
+      <c r="C158" s="114" t="n">
         <v>560389.02</v>
       </c>
-      <c r="E158" s="84" t="inlineStr">
+      <c r="D158" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F158" s="84" t="inlineStr">
+      <c r="E158" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F158" s="95" t="n"/>
+      <c r="G158" s="95" t="n"/>
+      <c r="H158" s="95" t="n"/>
+      <c r="I158" s="95" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="84" t="inlineStr">
+      <c r="A159" s="113" t="inlineStr">
         <is>
           <t>PLY-9-CDF</t>
         </is>
       </c>
-      <c r="C159" s="85" t="n">
+      <c r="B159" s="93" t="n"/>
+      <c r="C159" s="114" t="n">
         <v>676294.04</v>
       </c>
-      <c r="E159" s="84" t="inlineStr">
+      <c r="D159" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F159" s="84" t="inlineStr">
+      <c r="E159" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F159" s="95" t="n"/>
+      <c r="G159" s="95" t="n"/>
+      <c r="H159" s="95" t="n"/>
+      <c r="I159" s="95" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="84" t="inlineStr">
+      <c r="A160" s="113" t="inlineStr">
         <is>
           <t>PLY-9-CSF</t>
         </is>
       </c>
-      <c r="C160" s="85" t="n">
+      <c r="B160" s="93" t="n"/>
+      <c r="C160" s="114" t="n">
         <v>424397.02</v>
       </c>
-      <c r="E160" s="84" t="inlineStr">
+      <c r="D160" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F160" s="84" t="inlineStr">
+      <c r="E160" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F160" s="95" t="n"/>
+      <c r="G160" s="95" t="n"/>
+      <c r="H160" s="95" t="n"/>
+      <c r="I160" s="95" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="84" t="inlineStr">
+      <c r="A161" s="113" t="inlineStr">
         <is>
           <t>PLY-9-HDF</t>
         </is>
       </c>
-      <c r="C161" s="85" t="n">
+      <c r="B161" s="93" t="n"/>
+      <c r="C161" s="114" t="n">
         <v>467918.04</v>
       </c>
-      <c r="E161" s="84" t="inlineStr">
+      <c r="D161" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F161" s="84" t="inlineStr">
+      <c r="E161" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F161" s="95" t="n"/>
+      <c r="G161" s="95" t="n"/>
+      <c r="H161" s="95" t="n"/>
+      <c r="I161" s="95" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="84" t="inlineStr">
+      <c r="A162" s="113" t="inlineStr">
         <is>
           <t>PLY-9-HSF</t>
         </is>
       </c>
-      <c r="C162" s="85" t="n">
+      <c r="B162" s="93" t="n"/>
+      <c r="C162" s="114" t="n">
         <v>320209.02</v>
       </c>
-      <c r="E162" s="84" t="inlineStr">
+      <c r="D162" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F162" s="84" t="inlineStr">
+      <c r="E162" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F162" s="95" t="n"/>
+      <c r="G162" s="95" t="n"/>
+      <c r="H162" s="95" t="n"/>
+      <c r="I162" s="95" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="84" t="inlineStr">
+      <c r="A163" s="113" t="inlineStr">
         <is>
           <t>PLY-9-ODF</t>
         </is>
       </c>
-      <c r="C163" s="85" t="n">
+      <c r="B163" s="93" t="n"/>
+      <c r="C163" s="114" t="n">
         <v>973974.04</v>
       </c>
-      <c r="E163" s="84" t="inlineStr">
+      <c r="D163" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F163" s="84" t="inlineStr">
+      <c r="E163" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F163" s="95" t="n"/>
+      <c r="G163" s="95" t="n"/>
+      <c r="H163" s="95" t="n"/>
+      <c r="I163" s="95" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="84" t="inlineStr">
+      <c r="A164" s="113" t="inlineStr">
         <is>
           <t>PLY-9-OSF</t>
         </is>
       </c>
-      <c r="C164" s="85" t="n">
+      <c r="B164" s="93" t="n"/>
+      <c r="C164" s="114" t="n">
         <v>573237.02</v>
       </c>
-      <c r="E164" s="84" t="inlineStr">
+      <c r="D164" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F164" s="84" t="inlineStr">
+      <c r="E164" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F164" s="95" t="n"/>
+      <c r="G164" s="95" t="n"/>
+      <c r="H164" s="95" t="n"/>
+      <c r="I164" s="95" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="84" t="inlineStr">
+      <c r="A165" s="113" t="inlineStr">
         <is>
           <t>PLY-9-SDF</t>
         </is>
       </c>
-      <c r="C165" s="85" t="n">
+      <c r="B165" s="93" t="n"/>
+      <c r="C165" s="114" t="n">
         <v>646526.04</v>
       </c>
-      <c r="E165" s="84" t="inlineStr">
+      <c r="D165" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F165" s="84" t="inlineStr">
+      <c r="E165" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F165" s="95" t="n"/>
+      <c r="G165" s="95" t="n"/>
+      <c r="H165" s="95" t="n"/>
+      <c r="I165" s="95" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="84" t="inlineStr">
+      <c r="A166" s="113" t="inlineStr">
         <is>
           <t>PLY-9-SSF</t>
         </is>
       </c>
-      <c r="C166" s="85" t="n">
+      <c r="B166" s="93" t="n"/>
+      <c r="C166" s="114" t="n">
         <v>409513.02</v>
       </c>
-      <c r="E166" s="84" t="inlineStr">
+      <c r="D166" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F166" s="84" t="inlineStr">
+      <c r="E166" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F166" s="95" t="n"/>
+      <c r="G166" s="95" t="n"/>
+      <c r="H166" s="95" t="n"/>
+      <c r="I166" s="95" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="84" t="inlineStr">
+      <c r="A167" s="113" t="inlineStr">
         <is>
           <t>PLY-9-WDF</t>
         </is>
       </c>
-      <c r="C167" s="85" t="n">
+      <c r="B167" s="93" t="n"/>
+      <c r="C167" s="114" t="n">
         <v>1063278.04</v>
       </c>
-      <c r="E167" s="84" t="inlineStr">
+      <c r="D167" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F167" s="84" t="inlineStr">
+      <c r="E167" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
+      <c r="F167" s="95" t="n"/>
+      <c r="G167" s="95" t="n"/>
+      <c r="H167" s="95" t="n"/>
+      <c r="I167" s="95" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="84" t="inlineStr">
+      <c r="A168" s="113" t="inlineStr">
         <is>
           <t>PLY-9-WSF</t>
         </is>
       </c>
-      <c r="C168" s="85" t="n">
+      <c r="B168" s="93" t="n"/>
+      <c r="C168" s="114" t="n">
         <v>617889.02</v>
       </c>
-      <c r="E168" s="84" t="inlineStr">
+      <c r="D168" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F168" s="84" t="inlineStr">
+      <c r="E168" s="113" t="inlineStr">
         <is>
           <t>rate card DB (price list 2026)</t>
         </is>
       </c>
-    </row>
+      <c r="F168" s="95" t="n"/>
+      <c r="G168" s="95" t="n"/>
+      <c r="H168" s="95" t="n"/>
+      <c r="I168" s="95" t="n"/>
+    </row>
+    <row r="169"/>
     <row r="170">
-      <c r="A170" s="84" t="inlineStr">
+      <c r="A170" s="97" t="inlineStr">
         <is>
           <t>LANDED BOARD PRICES: Linyi Consmos Imp.&amp;Exp. Co., Ltd., quotation 14 Oct 2026. CIF Semarang plus port, clearance and trucking to Kudus. Value = CIF USD × FX_USD + LAND_40HC ÷ sheets/box.</t>
         </is>
       </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="84" t="inlineStr">
+      <c r="B170" s="98" t="n"/>
+      <c r="C170" s="98" t="n"/>
+      <c r="D170" s="98" t="n"/>
+      <c r="E170" s="98" t="n"/>
+      <c r="F170" s="98" t="n"/>
+      <c r="G170" s="98" t="n"/>
+      <c r="H170" s="98" t="n"/>
+      <c r="I170" s="98" t="n"/>
+    </row>
+    <row r="171" ht="32" customHeight="1" s="59">
+      <c r="A171" s="99" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B171" s="84" t="inlineStr">
+      <c r="B171" s="99" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C171" s="85" t="inlineStr">
+      <c r="C171" s="100" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E171" s="84" t="inlineStr">
+      <c r="D171" s="101" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F171" s="84" t="inlineStr">
+      <c r="E171" s="99" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="G171" s="86" t="inlineStr">
+      <c r="F171" s="115" t="inlineStr">
         <is>
           <t>Quote USD / sheet (landed Kudus)</t>
         </is>
       </c>
-      <c r="H171" s="87" t="inlineStr">
+      <c r="G171" s="116" t="inlineStr">
         <is>
           <t>Quote IDR / sheet (USD × FX_USD)</t>
         </is>
       </c>
-      <c r="I171" s="79" t="inlineStr">
+      <c r="H171" s="99" t="inlineStr">
         <is>
           <t>CIF USD / sheet</t>
         </is>
       </c>
-      <c r="J171" s="79" t="inlineStr">
+      <c r="I171" s="99" t="inlineStr">
         <is>
           <t>Sheets / 40' HC</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="84" t="inlineStr">
+      <c r="A172" s="113" t="inlineStr">
         <is>
           <t>FX_USD</t>
         </is>
       </c>
-      <c r="B172" s="84" t="inlineStr">
+      <c r="B172" s="117" t="inlineStr">
         <is>
           <t>Exchange rate</t>
         </is>
       </c>
-      <c r="C172" s="85" t="n">
+      <c r="C172" s="114" t="n">
         <v>18040</v>
       </c>
-      <c r="E172" s="84" t="inlineStr">
+      <c r="D172" s="113" t="inlineStr">
         <is>
           <t>IDR/USD</t>
         </is>
       </c>
-      <c r="F172" s="84" t="inlineStr">
+      <c r="E172" s="113" t="inlineStr">
         <is>
           <t>RFQ file, Landing Assumptions. Change to the booked rate.</t>
         </is>
       </c>
+      <c r="F172" s="95" t="n"/>
+      <c r="G172" s="95" t="n"/>
+      <c r="H172" s="95" t="n"/>
+      <c r="I172" s="95" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="84" t="inlineStr">
+      <c r="A173" s="113" t="inlineStr">
         <is>
           <t>LAND_40HC</t>
         </is>
       </c>
-      <c r="B173" s="84" t="inlineStr">
+      <c r="B173" s="117" t="inlineStr">
         <is>
           <t>Landing cost per 40' HC: line local charges, THC, lift-off, PPJK (BC 2.3), documents, trucking Tg. Emas to Kudus, 20% red-lane allowance</t>
         </is>
       </c>
-      <c r="C173" s="85" t="n">
+      <c r="C173" s="114" t="n">
         <v>13350000</v>
       </c>
-      <c r="E173" s="84" t="inlineStr">
+      <c r="D173" s="113" t="inlineStr">
         <is>
           <t>IDR/box</t>
         </is>
       </c>
-      <c r="F173" s="84" t="inlineStr">
+      <c r="E173" s="113" t="inlineStr">
         <is>
           <t>RFQ file, Landing Assumptions</t>
         </is>
       </c>
+      <c r="F173" s="95" t="n"/>
+      <c r="G173" s="95" t="n"/>
+      <c r="H173" s="95" t="n"/>
+      <c r="I173" s="95" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="84" t="inlineStr">
+      <c r="A174" s="113" t="inlineStr">
         <is>
           <t>PANEL_GRADE</t>
         </is>
       </c>
-      <c r="B174" s="84" t="inlineStr">
+      <c r="B174" s="117" t="inlineStr">
         <is>
           <t>Board grade feeding the PLY-x and MDF-x rates (type E2, E0 or CARB)</t>
         </is>
       </c>
-      <c r="C174" s="85" t="inlineStr">
+      <c r="C174" s="118" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="E174" s="84" t="inlineStr">
+      <c r="D174" s="113" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F174" s="84" t="inlineStr">
+      <c r="E174" s="113" t="inlineStr">
         <is>
           <t>CARB Phase 2 / TSCA Title VI: required for US hotel projects, accepted for EU</t>
         </is>
       </c>
+      <c r="F174" s="95" t="n"/>
+      <c r="G174" s="95" t="n"/>
+      <c r="H174" s="95" t="n"/>
+      <c r="I174" s="95" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="84" t="inlineStr">
+      <c r="A175" s="113" t="inlineStr">
         <is>
           <t>VEN_M_ADD</t>
         </is>
       </c>
-      <c r="B175" s="84" t="inlineStr">
+      <c r="B175" s="117" t="inlineStr">
         <is>
           <t>Mindi veneer added per face inside the PLY-x-MSF / MDF rates</t>
         </is>
       </c>
-      <c r="C175" s="85" t="n">
+      <c r="C175" s="114" t="n">
         <v>147709.02</v>
       </c>
-      <c r="E175" s="84" t="inlineStr">
+      <c r="D175" s="113" t="inlineStr">
         <is>
           <t>IDR/face</t>
         </is>
       </c>
-      <c r="F175" s="84" t="inlineStr">
+      <c r="E175" s="113" t="inlineStr">
         <is>
           <t>Back-calculated from the 29 Sep rate card (PLY-x-MSF minus PLY-x-RAW). Not the same as VEN_MINDI_FACE.</t>
         </is>
       </c>
+      <c r="F175" s="95" t="n"/>
+      <c r="G175" s="95" t="n"/>
+      <c r="H175" s="95" t="n"/>
+      <c r="I175" s="95" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="84" t="inlineStr">
+      <c r="A176" s="113" t="inlineStr">
         <is>
           <t>VEN_T_ADD</t>
         </is>
       </c>
-      <c r="B176" s="84" t="inlineStr">
+      <c r="B176" s="117" t="inlineStr">
         <is>
           <t>Teak veneer added per face inside the PLY-x-TSF / TDF rates</t>
         </is>
       </c>
-      <c r="C176" s="85" t="n">
+      <c r="C176" s="114" t="n">
         <v>341201.02</v>
       </c>
-      <c r="E176" s="84" t="inlineStr">
+      <c r="D176" s="113" t="inlineStr">
         <is>
           <t>IDR/face</t>
         </is>
       </c>
-      <c r="F176" s="84" t="inlineStr">
+      <c r="E176" s="113" t="inlineStr">
         <is>
           <t>Back-calculated from the 29 Sep rate card (PLY-x-TSF minus PLY-x-RAW). Not the same as VEN_TEAK_FACE.</t>
         </is>
       </c>
-    </row>
+      <c r="F176" s="95" t="n"/>
+      <c r="G176" s="95" t="n"/>
+      <c r="H176" s="95" t="n"/>
+      <c r="I176" s="95" t="n"/>
+    </row>
+    <row r="177"/>
     <row r="178">
-      <c r="A178" s="79" t="inlineStr">
+      <c r="A178" s="119" t="inlineStr">
         <is>
           <t>LND-PLY-E2-3</t>
         </is>
       </c>
-      <c r="B178" s="79" t="inlineStr">
+      <c r="B178" s="120" t="inlineStr">
         <is>
           <t>Furniture plywood 3 mm, E2, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C178" s="88">
-        <f>H178</f>
-        <v/>
-      </c>
-      <c r="E178" s="79" t="inlineStr">
+      <c r="C178" s="121">
+        <f>G178</f>
+        <v/>
+      </c>
+      <c r="D178" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F178" s="79" t="inlineStr">
+      <c r="E178" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G178" s="86">
-        <f>I178+$C$173/$C$172/J178</f>
-        <v/>
-      </c>
-      <c r="H178" s="87">
-        <f>G178*$C$172</f>
-        <v/>
-      </c>
-      <c r="I178" s="86" t="n">
+      <c r="F178" s="122">
+        <f>H178+$C$173/$C$172/I178</f>
+        <v/>
+      </c>
+      <c r="G178" s="122">
+        <f>F178*$C$172</f>
+        <v/>
+      </c>
+      <c r="H178" s="122" t="n">
         <v>5.248</v>
       </c>
-      <c r="J178" s="87" t="n">
+      <c r="I178" s="123" t="n">
         <v>5823</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="79" t="inlineStr">
+      <c r="A179" s="119" t="inlineStr">
         <is>
           <t>LND-PLY-E2-6</t>
         </is>
       </c>
-      <c r="B179" s="79" t="inlineStr">
+      <c r="B179" s="120" t="inlineStr">
         <is>
           <t>Furniture plywood 6 mm, E2, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C179" s="88">
-        <f>H179</f>
-        <v/>
-      </c>
-      <c r="E179" s="79" t="inlineStr">
+      <c r="C179" s="121">
+        <f>G179</f>
+        <v/>
+      </c>
+      <c r="D179" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F179" s="79" t="inlineStr">
+      <c r="E179" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G179" s="86">
-        <f>I179+$C$173/$C$172/J179</f>
-        <v/>
-      </c>
-      <c r="H179" s="87">
-        <f>G179*$C$172</f>
-        <v/>
-      </c>
-      <c r="I179" s="86" t="n">
+      <c r="F179" s="122">
+        <f>H179+$C$173/$C$172/I179</f>
+        <v/>
+      </c>
+      <c r="G179" s="122">
+        <f>F179*$C$172</f>
+        <v/>
+      </c>
+      <c r="H179" s="122" t="n">
         <v>7.779</v>
       </c>
-      <c r="J179" s="87" t="n">
+      <c r="I179" s="123" t="n">
         <v>2911</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="79" t="inlineStr">
+      <c r="A180" s="119" t="inlineStr">
         <is>
           <t>LND-PLY-E2-9</t>
         </is>
       </c>
-      <c r="B180" s="79" t="inlineStr">
+      <c r="B180" s="120" t="inlineStr">
         <is>
           <t>Furniture plywood 9 mm, E2, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C180" s="88">
-        <f>H180</f>
-        <v/>
-      </c>
-      <c r="E180" s="79" t="inlineStr">
+      <c r="C180" s="121">
+        <f>G180</f>
+        <v/>
+      </c>
+      <c r="D180" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F180" s="79" t="inlineStr">
+      <c r="E180" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G180" s="86">
-        <f>I180+$C$173/$C$172/J180</f>
-        <v/>
-      </c>
-      <c r="H180" s="87">
-        <f>G180*$C$172</f>
-        <v/>
-      </c>
-      <c r="I180" s="86" t="n">
+      <c r="F180" s="122">
+        <f>H180+$C$173/$C$172/I180</f>
+        <v/>
+      </c>
+      <c r="G180" s="122">
+        <f>F180*$C$172</f>
+        <v/>
+      </c>
+      <c r="H180" s="122" t="n">
         <v>11.017</v>
       </c>
-      <c r="J180" s="87" t="n">
+      <c r="I180" s="123" t="n">
         <v>1941</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="79" t="inlineStr">
+      <c r="A181" s="119" t="inlineStr">
         <is>
           <t>LND-PLY-E2-12</t>
         </is>
       </c>
-      <c r="B181" s="79" t="inlineStr">
+      <c r="B181" s="120" t="inlineStr">
         <is>
           <t>Furniture plywood 12 mm, E2, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C181" s="88">
-        <f>H181</f>
-        <v/>
-      </c>
-      <c r="E181" s="79" t="inlineStr">
+      <c r="C181" s="121">
+        <f>G181</f>
+        <v/>
+      </c>
+      <c r="D181" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F181" s="79" t="inlineStr">
+      <c r="E181" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G181" s="86">
-        <f>I181+$C$173/$C$172/J181</f>
-        <v/>
-      </c>
-      <c r="H181" s="87">
-        <f>G181*$C$172</f>
-        <v/>
-      </c>
-      <c r="I181" s="86" t="n">
+      <c r="F181" s="122">
+        <f>H181+$C$173/$C$172/I181</f>
+        <v/>
+      </c>
+      <c r="G181" s="122">
+        <f>F181*$C$172</f>
+        <v/>
+      </c>
+      <c r="H181" s="122" t="n">
         <v>14.144</v>
       </c>
-      <c r="J181" s="87" t="n">
+      <c r="I181" s="123" t="n">
         <v>1456</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="79" t="inlineStr">
+      <c r="A182" s="119" t="inlineStr">
         <is>
           <t>LND-PLY-E2-15</t>
         </is>
       </c>
-      <c r="B182" s="79" t="inlineStr">
+      <c r="B182" s="120" t="inlineStr">
         <is>
           <t>Furniture plywood 15 mm, E2, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C182" s="88">
-        <f>H182</f>
-        <v/>
-      </c>
-      <c r="E182" s="79" t="inlineStr">
+      <c r="C182" s="121">
+        <f>G182</f>
+        <v/>
+      </c>
+      <c r="D182" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F182" s="79" t="inlineStr">
+      <c r="E182" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G182" s="86">
-        <f>I182+$C$173/$C$172/J182</f>
-        <v/>
-      </c>
-      <c r="H182" s="87">
-        <f>G182*$C$172</f>
-        <v/>
-      </c>
-      <c r="I182" s="86" t="n">
+      <c r="F182" s="122">
+        <f>H182+$C$173/$C$172/I182</f>
+        <v/>
+      </c>
+      <c r="G182" s="122">
+        <f>F182*$C$172</f>
+        <v/>
+      </c>
+      <c r="H182" s="122" t="n">
         <v>17.655</v>
       </c>
-      <c r="J182" s="87" t="n">
+      <c r="I182" s="123" t="n">
         <v>1165</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="79" t="inlineStr">
+      <c r="A183" s="119" t="inlineStr">
         <is>
           <t>LND-PLY-E2-18</t>
         </is>
       </c>
-      <c r="B183" s="79" t="inlineStr">
+      <c r="B183" s="120" t="inlineStr">
         <is>
           <t>Furniture plywood 18 mm, E2, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C183" s="88">
-        <f>H183</f>
-        <v/>
-      </c>
-      <c r="E183" s="79" t="inlineStr">
+      <c r="C183" s="121">
+        <f>G183</f>
+        <v/>
+      </c>
+      <c r="D183" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F183" s="79" t="inlineStr">
+      <c r="E183" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G183" s="86">
-        <f>I183+$C$173/$C$172/J183</f>
-        <v/>
-      </c>
-      <c r="H183" s="87">
-        <f>G183*$C$172</f>
-        <v/>
-      </c>
-      <c r="I183" s="86" t="n">
+      <c r="F183" s="122">
+        <f>H183+$C$173/$C$172/I183</f>
+        <v/>
+      </c>
+      <c r="G183" s="122">
+        <f>F183*$C$172</f>
+        <v/>
+      </c>
+      <c r="H183" s="122" t="n">
         <v>20.469</v>
       </c>
-      <c r="J183" s="87" t="n">
+      <c r="I183" s="123" t="n">
         <v>970</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="84" t="inlineStr">
+      <c r="A184" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-E0-3</t>
         </is>
       </c>
-      <c r="B184" s="84" t="inlineStr">
+      <c r="B184" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 3 mm, E0, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C184" s="89">
-        <f>H184</f>
-        <v/>
-      </c>
-      <c r="E184" s="84" t="inlineStr">
+      <c r="C184" s="114">
+        <f>G184</f>
+        <v/>
+      </c>
+      <c r="D184" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F184" s="84" t="inlineStr">
+      <c r="E184" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G184" s="82">
-        <f>I184+$C$173/$C$172/J184</f>
-        <v/>
-      </c>
-      <c r="H184" s="83">
-        <f>G184*$C$172</f>
-        <v/>
-      </c>
-      <c r="I184" s="82" t="n">
+      <c r="F184" s="112">
+        <f>H184+$C$173/$C$172/I184</f>
+        <v/>
+      </c>
+      <c r="G184" s="112">
+        <f>F184*$C$172</f>
+        <v/>
+      </c>
+      <c r="H184" s="112" t="n">
         <v>5.45</v>
       </c>
-      <c r="J184" s="83" t="n">
+      <c r="I184" s="124" t="n">
         <v>5760</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="84" t="inlineStr">
+      <c r="A185" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-E0-6</t>
         </is>
       </c>
-      <c r="B185" s="84" t="inlineStr">
+      <c r="B185" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 6 mm, E0, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C185" s="89">
-        <f>H185</f>
-        <v/>
-      </c>
-      <c r="E185" s="84" t="inlineStr">
+      <c r="C185" s="114">
+        <f>G185</f>
+        <v/>
+      </c>
+      <c r="D185" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F185" s="84" t="inlineStr">
+      <c r="E185" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G185" s="82">
-        <f>I185+$C$173/$C$172/J185</f>
-        <v/>
-      </c>
-      <c r="H185" s="83">
-        <f>G185*$C$172</f>
-        <v/>
-      </c>
-      <c r="I185" s="82" t="n">
+      <c r="F185" s="112">
+        <f>H185+$C$173/$C$172/I185</f>
+        <v/>
+      </c>
+      <c r="G185" s="112">
+        <f>F185*$C$172</f>
+        <v/>
+      </c>
+      <c r="H185" s="112" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="J185" s="83" t="n">
+      <c r="I185" s="124" t="n">
         <v>2880</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="84" t="inlineStr">
+      <c r="A186" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-E0-9</t>
         </is>
       </c>
-      <c r="B186" s="84" t="inlineStr">
+      <c r="B186" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 9 mm, E0, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C186" s="89">
-        <f>H186</f>
-        <v/>
-      </c>
-      <c r="E186" s="84" t="inlineStr">
+      <c r="C186" s="114">
+        <f>G186</f>
+        <v/>
+      </c>
+      <c r="D186" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F186" s="84" t="inlineStr">
+      <c r="E186" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G186" s="82">
-        <f>I186+$C$173/$C$172/J186</f>
-        <v/>
-      </c>
-      <c r="H186" s="83">
-        <f>G186*$C$172</f>
-        <v/>
-      </c>
-      <c r="I186" s="82" t="n">
+      <c r="F186" s="112">
+        <f>H186+$C$173/$C$172/I186</f>
+        <v/>
+      </c>
+      <c r="G186" s="112">
+        <f>F186*$C$172</f>
+        <v/>
+      </c>
+      <c r="H186" s="112" t="n">
         <v>12.4</v>
       </c>
-      <c r="J186" s="83" t="n">
+      <c r="I186" s="124" t="n">
         <v>1890</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="84" t="inlineStr">
+      <c r="A187" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-E0-12</t>
         </is>
       </c>
-      <c r="B187" s="84" t="inlineStr">
+      <c r="B187" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 12 mm, E0, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C187" s="89">
-        <f>H187</f>
-        <v/>
-      </c>
-      <c r="E187" s="84" t="inlineStr">
+      <c r="C187" s="114">
+        <f>G187</f>
+        <v/>
+      </c>
+      <c r="D187" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F187" s="84" t="inlineStr">
+      <c r="E187" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G187" s="82">
-        <f>I187+$C$173/$C$172/J187</f>
-        <v/>
-      </c>
-      <c r="H187" s="83">
-        <f>G187*$C$172</f>
-        <v/>
-      </c>
-      <c r="I187" s="82" t="n">
+      <c r="F187" s="112">
+        <f>H187+$C$173/$C$172/I187</f>
+        <v/>
+      </c>
+      <c r="G187" s="112">
+        <f>F187*$C$172</f>
+        <v/>
+      </c>
+      <c r="H187" s="112" t="n">
         <v>15.4</v>
       </c>
-      <c r="J187" s="83" t="n">
+      <c r="I187" s="124" t="n">
         <v>1440</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="84" t="inlineStr">
+      <c r="A188" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-E0-15</t>
         </is>
       </c>
-      <c r="B188" s="84" t="inlineStr">
+      <c r="B188" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 15 mm, E0, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C188" s="89">
-        <f>H188</f>
-        <v/>
-      </c>
-      <c r="E188" s="84" t="inlineStr">
+      <c r="C188" s="114">
+        <f>G188</f>
+        <v/>
+      </c>
+      <c r="D188" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F188" s="84" t="inlineStr">
+      <c r="E188" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G188" s="82">
-        <f>I188+$C$173/$C$172/J188</f>
-        <v/>
-      </c>
-      <c r="H188" s="83">
-        <f>G188*$C$172</f>
-        <v/>
-      </c>
-      <c r="I188" s="82" t="n">
+      <c r="F188" s="112">
+        <f>H188+$C$173/$C$172/I188</f>
+        <v/>
+      </c>
+      <c r="G188" s="112">
+        <f>F188*$C$172</f>
+        <v/>
+      </c>
+      <c r="H188" s="112" t="n">
         <v>18.7</v>
       </c>
-      <c r="J188" s="83" t="n">
+      <c r="I188" s="124" t="n">
         <v>1170</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="84" t="inlineStr">
+      <c r="A189" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-E0-18</t>
         </is>
       </c>
-      <c r="B189" s="84" t="inlineStr">
+      <c r="B189" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 18 mm, E0, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C189" s="89">
-        <f>H189</f>
-        <v/>
-      </c>
-      <c r="E189" s="84" t="inlineStr">
+      <c r="C189" s="114">
+        <f>G189</f>
+        <v/>
+      </c>
+      <c r="D189" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F189" s="84" t="inlineStr">
+      <c r="E189" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G189" s="82">
-        <f>I189+$C$173/$C$172/J189</f>
-        <v/>
-      </c>
-      <c r="H189" s="83">
-        <f>G189*$C$172</f>
-        <v/>
-      </c>
-      <c r="I189" s="82" t="n">
+      <c r="F189" s="112">
+        <f>H189+$C$173/$C$172/I189</f>
+        <v/>
+      </c>
+      <c r="G189" s="112">
+        <f>F189*$C$172</f>
+        <v/>
+      </c>
+      <c r="H189" s="112" t="n">
         <v>21.4</v>
       </c>
-      <c r="J189" s="83" t="n">
+      <c r="I189" s="124" t="n">
         <v>990</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="84" t="inlineStr">
+      <c r="A190" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-CARB-3</t>
         </is>
       </c>
-      <c r="B190" s="84" t="inlineStr">
+      <c r="B190" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 3 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C190" s="89">
-        <f>H190</f>
-        <v/>
-      </c>
-      <c r="E190" s="84" t="inlineStr">
+      <c r="C190" s="114">
+        <f>G190</f>
+        <v/>
+      </c>
+      <c r="D190" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F190" s="84" t="inlineStr">
+      <c r="E190" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G190" s="82">
-        <f>I190+$C$173/$C$172/J190</f>
-        <v/>
-      </c>
-      <c r="H190" s="83">
-        <f>G190*$C$172</f>
-        <v/>
-      </c>
-      <c r="I190" s="82" t="n">
+      <c r="F190" s="112">
+        <f>H190+$C$173/$C$172/I190</f>
+        <v/>
+      </c>
+      <c r="G190" s="112">
+        <f>F190*$C$172</f>
+        <v/>
+      </c>
+      <c r="H190" s="112" t="n">
         <v>5.5</v>
       </c>
-      <c r="J190" s="83" t="n">
+      <c r="I190" s="124" t="n">
         <v>5760</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="84" t="inlineStr">
+      <c r="A191" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-CARB-6</t>
         </is>
       </c>
-      <c r="B191" s="84" t="inlineStr">
+      <c r="B191" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 6 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C191" s="89">
-        <f>H191</f>
-        <v/>
-      </c>
-      <c r="E191" s="84" t="inlineStr">
+      <c r="C191" s="114">
+        <f>G191</f>
+        <v/>
+      </c>
+      <c r="D191" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F191" s="84" t="inlineStr">
+      <c r="E191" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G191" s="82">
-        <f>I191+$C$173/$C$172/J191</f>
-        <v/>
-      </c>
-      <c r="H191" s="83">
-        <f>G191*$C$172</f>
-        <v/>
-      </c>
-      <c r="I191" s="82" t="n">
+      <c r="F191" s="112">
+        <f>H191+$C$173/$C$172/I191</f>
+        <v/>
+      </c>
+      <c r="G191" s="112">
+        <f>F191*$C$172</f>
+        <v/>
+      </c>
+      <c r="H191" s="112" t="n">
         <v>8.5</v>
       </c>
-      <c r="J191" s="83" t="n">
+      <c r="I191" s="124" t="n">
         <v>2880</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="84" t="inlineStr">
+      <c r="A192" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-CARB-9</t>
         </is>
       </c>
-      <c r="B192" s="84" t="inlineStr">
+      <c r="B192" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 9 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C192" s="89">
-        <f>H192</f>
-        <v/>
-      </c>
-      <c r="E192" s="84" t="inlineStr">
+      <c r="C192" s="114">
+        <f>G192</f>
+        <v/>
+      </c>
+      <c r="D192" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F192" s="84" t="inlineStr">
+      <c r="E192" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G192" s="82">
-        <f>I192+$C$173/$C$172/J192</f>
-        <v/>
-      </c>
-      <c r="H192" s="83">
-        <f>G192*$C$172</f>
-        <v/>
-      </c>
-      <c r="I192" s="82" t="n">
+      <c r="F192" s="112">
+        <f>H192+$C$173/$C$172/I192</f>
+        <v/>
+      </c>
+      <c r="G192" s="112">
+        <f>F192*$C$172</f>
+        <v/>
+      </c>
+      <c r="H192" s="112" t="n">
         <v>12.4</v>
       </c>
-      <c r="J192" s="83" t="n">
+      <c r="I192" s="124" t="n">
         <v>1890</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="84" t="inlineStr">
+      <c r="A193" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-CARB-12</t>
         </is>
       </c>
-      <c r="B193" s="84" t="inlineStr">
+      <c r="B193" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 12 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C193" s="89">
-        <f>H193</f>
-        <v/>
-      </c>
-      <c r="E193" s="84" t="inlineStr">
+      <c r="C193" s="114">
+        <f>G193</f>
+        <v/>
+      </c>
+      <c r="D193" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F193" s="84" t="inlineStr">
+      <c r="E193" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G193" s="82">
-        <f>I193+$C$173/$C$172/J193</f>
-        <v/>
-      </c>
-      <c r="H193" s="83">
-        <f>G193*$C$172</f>
-        <v/>
-      </c>
-      <c r="I193" s="82" t="n">
+      <c r="F193" s="112">
+        <f>H193+$C$173/$C$172/I193</f>
+        <v/>
+      </c>
+      <c r="G193" s="112">
+        <f>F193*$C$172</f>
+        <v/>
+      </c>
+      <c r="H193" s="112" t="n">
         <v>15.5</v>
       </c>
-      <c r="J193" s="83" t="n">
+      <c r="I193" s="124" t="n">
         <v>1440</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="84" t="inlineStr">
+      <c r="A194" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-CARB-15</t>
         </is>
       </c>
-      <c r="B194" s="84" t="inlineStr">
+      <c r="B194" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 15 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C194" s="89">
-        <f>H194</f>
-        <v/>
-      </c>
-      <c r="E194" s="84" t="inlineStr">
+      <c r="C194" s="114">
+        <f>G194</f>
+        <v/>
+      </c>
+      <c r="D194" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F194" s="84" t="inlineStr">
+      <c r="E194" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G194" s="82">
-        <f>I194+$C$173/$C$172/J194</f>
-        <v/>
-      </c>
-      <c r="H194" s="83">
-        <f>G194*$C$172</f>
-        <v/>
-      </c>
-      <c r="I194" s="82" t="n">
+      <c r="F194" s="112">
+        <f>H194+$C$173/$C$172/I194</f>
+        <v/>
+      </c>
+      <c r="G194" s="112">
+        <f>F194*$C$172</f>
+        <v/>
+      </c>
+      <c r="H194" s="112" t="n">
         <v>18.8</v>
       </c>
-      <c r="J194" s="83" t="n">
+      <c r="I194" s="124" t="n">
         <v>1170</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="84" t="inlineStr">
+      <c r="A195" s="113" t="inlineStr">
         <is>
           <t>LND-PLY-CARB-18</t>
         </is>
       </c>
-      <c r="B195" s="84" t="inlineStr">
+      <c r="B195" s="117" t="inlineStr">
         <is>
           <t>Furniture plywood 18 mm, CARB Phase 2 / TSCA Title VI, poplar core, okoume face, landed Kudus</t>
         </is>
       </c>
-      <c r="C195" s="89">
-        <f>H195</f>
-        <v/>
-      </c>
-      <c r="E195" s="84" t="inlineStr">
+      <c r="C195" s="114">
+        <f>G195</f>
+        <v/>
+      </c>
+      <c r="D195" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F195" s="84" t="inlineStr">
+      <c r="E195" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G195" s="82">
-        <f>I195+$C$173/$C$172/J195</f>
-        <v/>
-      </c>
-      <c r="H195" s="83">
-        <f>G195*$C$172</f>
-        <v/>
-      </c>
-      <c r="I195" s="82" t="n">
+      <c r="F195" s="112">
+        <f>H195+$C$173/$C$172/I195</f>
+        <v/>
+      </c>
+      <c r="G195" s="112">
+        <f>F195*$C$172</f>
+        <v/>
+      </c>
+      <c r="H195" s="112" t="n">
         <v>21.5</v>
       </c>
-      <c r="J195" s="83" t="n">
+      <c r="I195" s="124" t="n">
         <v>990</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="79" t="inlineStr">
+      <c r="A196" s="119" t="inlineStr">
         <is>
           <t>LND-MDF-E2-3</t>
         </is>
       </c>
-      <c r="B196" s="79" t="inlineStr">
+      <c r="B196" s="120" t="inlineStr">
         <is>
           <t>MDF 3 mm, E2, landed Kudus</t>
         </is>
       </c>
-      <c r="C196" s="88">
-        <f>H196</f>
-        <v/>
-      </c>
-      <c r="E196" s="79" t="inlineStr">
+      <c r="C196" s="121">
+        <f>G196</f>
+        <v/>
+      </c>
+      <c r="D196" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F196" s="79" t="inlineStr">
+      <c r="E196" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G196" s="86">
-        <f>I196+$C$173/$C$172/J196</f>
-        <v/>
-      </c>
-      <c r="H196" s="87">
-        <f>G196*$C$172</f>
-        <v/>
-      </c>
-      <c r="I196" s="86" t="n">
+      <c r="F196" s="122">
+        <f>H196+$C$173/$C$172/I196</f>
+        <v/>
+      </c>
+      <c r="G196" s="122">
+        <f>F196*$C$172</f>
+        <v/>
+      </c>
+      <c r="H196" s="122" t="n">
         <v>2.715</v>
       </c>
-      <c r="J196" s="87" t="n">
+      <c r="I196" s="123" t="n">
         <v>4143</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="79" t="inlineStr">
+      <c r="A197" s="119" t="inlineStr">
         <is>
           <t>LND-MDF-E2-6</t>
         </is>
       </c>
-      <c r="B197" s="79" t="inlineStr">
+      <c r="B197" s="120" t="inlineStr">
         <is>
           <t>MDF 6 mm, E2, landed Kudus</t>
         </is>
       </c>
-      <c r="C197" s="88">
-        <f>H197</f>
-        <v/>
-      </c>
-      <c r="E197" s="79" t="inlineStr">
+      <c r="C197" s="121">
+        <f>G197</f>
+        <v/>
+      </c>
+      <c r="D197" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F197" s="79" t="inlineStr">
+      <c r="E197" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G197" s="86">
-        <f>I197+$C$173/$C$172/J197</f>
-        <v/>
-      </c>
-      <c r="H197" s="87">
-        <f>G197*$C$172</f>
-        <v/>
-      </c>
-      <c r="I197" s="86" t="n">
+      <c r="F197" s="122">
+        <f>H197+$C$173/$C$172/I197</f>
+        <v/>
+      </c>
+      <c r="G197" s="122">
+        <f>F197*$C$172</f>
+        <v/>
+      </c>
+      <c r="H197" s="122" t="n">
         <v>4.873</v>
       </c>
-      <c r="J197" s="87" t="n">
+      <c r="I197" s="123" t="n">
         <v>2072</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="79" t="inlineStr">
+      <c r="A198" s="119" t="inlineStr">
         <is>
           <t>LND-MDF-E2-9</t>
         </is>
       </c>
-      <c r="B198" s="79" t="inlineStr">
+      <c r="B198" s="120" t="inlineStr">
         <is>
           <t>MDF 9 mm, E2, landed Kudus</t>
         </is>
       </c>
-      <c r="C198" s="88">
-        <f>H198</f>
-        <v/>
-      </c>
-      <c r="E198" s="79" t="inlineStr">
+      <c r="C198" s="121">
+        <f>G198</f>
+        <v/>
+      </c>
+      <c r="D198" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F198" s="79" t="inlineStr">
+      <c r="E198" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G198" s="86">
-        <f>I198+$C$173/$C$172/J198</f>
-        <v/>
-      </c>
-      <c r="H198" s="87">
-        <f>G198*$C$172</f>
-        <v/>
-      </c>
-      <c r="I198" s="86" t="n">
+      <c r="F198" s="122">
+        <f>H198+$C$173/$C$172/I198</f>
+        <v/>
+      </c>
+      <c r="G198" s="122">
+        <f>F198*$C$172</f>
+        <v/>
+      </c>
+      <c r="H198" s="122" t="n">
         <v>7.553</v>
       </c>
-      <c r="J198" s="87" t="n">
+      <c r="I198" s="123" t="n">
         <v>1493</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="79" t="inlineStr">
+      <c r="A199" s="119" t="inlineStr">
         <is>
           <t>LND-MDF-E2-12</t>
         </is>
       </c>
-      <c r="B199" s="79" t="inlineStr">
+      <c r="B199" s="120" t="inlineStr">
         <is>
           <t>MDF 12 mm, E2, landed Kudus</t>
         </is>
       </c>
-      <c r="C199" s="88">
-        <f>H199</f>
-        <v/>
-      </c>
-      <c r="E199" s="79" t="inlineStr">
+      <c r="C199" s="121">
+        <f>G199</f>
+        <v/>
+      </c>
+      <c r="D199" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F199" s="79" t="inlineStr">
+      <c r="E199" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G199" s="86">
-        <f>I199+$C$173/$C$172/J199</f>
-        <v/>
-      </c>
-      <c r="H199" s="87">
-        <f>G199*$C$172</f>
-        <v/>
-      </c>
-      <c r="I199" s="86" t="n">
+      <c r="F199" s="122">
+        <f>H199+$C$173/$C$172/I199</f>
+        <v/>
+      </c>
+      <c r="G199" s="122">
+        <f>F199*$C$172</f>
+        <v/>
+      </c>
+      <c r="H199" s="122" t="n">
         <v>9.882999999999999</v>
       </c>
-      <c r="J199" s="87" t="n">
+      <c r="I199" s="123" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="79" t="inlineStr">
+      <c r="A200" s="119" t="inlineStr">
         <is>
           <t>LND-MDF-E2-15</t>
         </is>
       </c>
-      <c r="B200" s="79" t="inlineStr">
+      <c r="B200" s="120" t="inlineStr">
         <is>
           <t>MDF 15 mm, E2, landed Kudus</t>
         </is>
       </c>
-      <c r="C200" s="88">
-        <f>H200</f>
-        <v/>
-      </c>
-      <c r="E200" s="79" t="inlineStr">
+      <c r="C200" s="121">
+        <f>G200</f>
+        <v/>
+      </c>
+      <c r="D200" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F200" s="79" t="inlineStr">
+      <c r="E200" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G200" s="86">
-        <f>I200+$C$173/$C$172/J200</f>
-        <v/>
-      </c>
-      <c r="H200" s="87">
-        <f>G200*$C$172</f>
-        <v/>
-      </c>
-      <c r="I200" s="86" t="n">
+      <c r="F200" s="122">
+        <f>H200+$C$173/$C$172/I200</f>
+        <v/>
+      </c>
+      <c r="G200" s="122">
+        <f>F200*$C$172</f>
+        <v/>
+      </c>
+      <c r="H200" s="122" t="n">
         <v>12.435</v>
       </c>
-      <c r="J200" s="87" t="n">
+      <c r="I200" s="123" t="n">
         <v>896</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="79" t="inlineStr">
+      <c r="A201" s="119" t="inlineStr">
         <is>
           <t>LND-MDF-E2-18</t>
         </is>
       </c>
-      <c r="B201" s="79" t="inlineStr">
+      <c r="B201" s="120" t="inlineStr">
         <is>
           <t>MDF 18 mm, E2, landed Kudus</t>
         </is>
       </c>
-      <c r="C201" s="88">
-        <f>H201</f>
-        <v/>
-      </c>
-      <c r="E201" s="79" t="inlineStr">
+      <c r="C201" s="121">
+        <f>G201</f>
+        <v/>
+      </c>
+      <c r="D201" s="119" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F201" s="79" t="inlineStr">
+      <c r="E201" s="119" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G201" s="86">
-        <f>I201+$C$173/$C$172/J201</f>
-        <v/>
-      </c>
-      <c r="H201" s="87">
-        <f>G201*$C$172</f>
-        <v/>
-      </c>
-      <c r="I201" s="86" t="n">
+      <c r="F201" s="122">
+        <f>H201+$C$173/$C$172/I201</f>
+        <v/>
+      </c>
+      <c r="G201" s="122">
+        <f>F201*$C$172</f>
+        <v/>
+      </c>
+      <c r="H201" s="122" t="n">
         <v>15.039</v>
       </c>
-      <c r="J201" s="87" t="n">
+      <c r="I201" s="123" t="n">
         <v>746</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="84" t="inlineStr">
+      <c r="A202" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-E0-3</t>
         </is>
       </c>
-      <c r="B202" s="84" t="inlineStr">
+      <c r="B202" s="117" t="inlineStr">
         <is>
           <t>MDF 3 mm, E0, landed Kudus</t>
         </is>
       </c>
-      <c r="C202" s="89">
-        <f>H202</f>
-        <v/>
-      </c>
-      <c r="E202" s="84" t="inlineStr">
+      <c r="C202" s="114">
+        <f>G202</f>
+        <v/>
+      </c>
+      <c r="D202" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F202" s="84" t="inlineStr">
+      <c r="E202" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G202" s="82">
-        <f>I202+$C$173/$C$172/J202</f>
-        <v/>
-      </c>
-      <c r="H202" s="83">
-        <f>G202*$C$172</f>
-        <v/>
-      </c>
-      <c r="I202" s="82" t="n">
+      <c r="F202" s="112">
+        <f>H202+$C$173/$C$172/I202</f>
+        <v/>
+      </c>
+      <c r="G202" s="112">
+        <f>F202*$C$172</f>
+        <v/>
+      </c>
+      <c r="H202" s="112" t="n">
         <v>2.8</v>
       </c>
-      <c r="J202" s="83" t="n">
+      <c r="I202" s="124" t="n">
         <v>4060</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="84" t="inlineStr">
+      <c r="A203" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-E0-6</t>
         </is>
       </c>
-      <c r="B203" s="84" t="inlineStr">
+      <c r="B203" s="117" t="inlineStr">
         <is>
           <t>MDF 6 mm, E0, landed Kudus</t>
         </is>
       </c>
-      <c r="C203" s="89">
-        <f>H203</f>
-        <v/>
-      </c>
-      <c r="E203" s="84" t="inlineStr">
+      <c r="C203" s="114">
+        <f>G203</f>
+        <v/>
+      </c>
+      <c r="D203" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F203" s="84" t="inlineStr">
+      <c r="E203" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G203" s="82">
-        <f>I203+$C$173/$C$172/J203</f>
-        <v/>
-      </c>
-      <c r="H203" s="83">
-        <f>G203*$C$172</f>
-        <v/>
-      </c>
-      <c r="I203" s="82" t="n">
+      <c r="F203" s="112">
+        <f>H203+$C$173/$C$172/I203</f>
+        <v/>
+      </c>
+      <c r="G203" s="112">
+        <f>F203*$C$172</f>
+        <v/>
+      </c>
+      <c r="H203" s="112" t="n">
         <v>5.2</v>
       </c>
-      <c r="J203" s="83" t="n">
+      <c r="I203" s="124" t="n">
         <v>2250</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="84" t="inlineStr">
+      <c r="A204" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-E0-9</t>
         </is>
       </c>
-      <c r="B204" s="84" t="inlineStr">
+      <c r="B204" s="117" t="inlineStr">
         <is>
           <t>MDF 9 mm, E0, landed Kudus</t>
         </is>
       </c>
-      <c r="C204" s="89">
-        <f>H204</f>
-        <v/>
-      </c>
-      <c r="E204" s="84" t="inlineStr">
+      <c r="C204" s="114">
+        <f>G204</f>
+        <v/>
+      </c>
+      <c r="D204" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F204" s="84" t="inlineStr">
+      <c r="E204" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G204" s="82">
-        <f>I204+$C$173/$C$172/J204</f>
-        <v/>
-      </c>
-      <c r="H204" s="83">
-        <f>G204*$C$172</f>
-        <v/>
-      </c>
-      <c r="I204" s="82" t="n">
+      <c r="F204" s="112">
+        <f>H204+$C$173/$C$172/I204</f>
+        <v/>
+      </c>
+      <c r="G204" s="112">
+        <f>F204*$C$172</f>
+        <v/>
+      </c>
+      <c r="H204" s="112" t="n">
         <v>8.15</v>
       </c>
-      <c r="J204" s="83" t="n">
+      <c r="I204" s="124" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="84" t="inlineStr">
+      <c r="A205" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-E0-12</t>
         </is>
       </c>
-      <c r="B205" s="84" t="inlineStr">
+      <c r="B205" s="117" t="inlineStr">
         <is>
           <t>MDF 12 mm, E0, landed Kudus</t>
         </is>
       </c>
-      <c r="C205" s="89">
-        <f>H205</f>
-        <v/>
-      </c>
-      <c r="E205" s="84" t="inlineStr">
+      <c r="C205" s="114">
+        <f>G205</f>
+        <v/>
+      </c>
+      <c r="D205" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F205" s="84" t="inlineStr">
+      <c r="E205" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G205" s="82">
-        <f>I205+$C$173/$C$172/J205</f>
-        <v/>
-      </c>
-      <c r="H205" s="83">
-        <f>G205*$C$172</f>
-        <v/>
-      </c>
-      <c r="I205" s="82" t="n">
+      <c r="F205" s="112">
+        <f>H205+$C$173/$C$172/I205</f>
+        <v/>
+      </c>
+      <c r="G205" s="112">
+        <f>F205*$C$172</f>
+        <v/>
+      </c>
+      <c r="H205" s="112" t="n">
         <v>10.7</v>
       </c>
-      <c r="J205" s="83" t="n">
+      <c r="I205" s="124" t="n">
         <v>1125</v>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="84" t="inlineStr">
+      <c r="A206" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-E0-15</t>
         </is>
       </c>
-      <c r="B206" s="84" t="inlineStr">
+      <c r="B206" s="117" t="inlineStr">
         <is>
           <t>MDF 15 mm, E0, landed Kudus</t>
         </is>
       </c>
-      <c r="C206" s="89">
-        <f>H206</f>
-        <v/>
-      </c>
-      <c r="E206" s="84" t="inlineStr">
+      <c r="C206" s="114">
+        <f>G206</f>
+        <v/>
+      </c>
+      <c r="D206" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F206" s="84" t="inlineStr">
+      <c r="E206" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G206" s="82">
-        <f>I206+$C$173/$C$172/J206</f>
-        <v/>
-      </c>
-      <c r="H206" s="83">
-        <f>G206*$C$172</f>
-        <v/>
-      </c>
-      <c r="I206" s="82" t="n">
+      <c r="F206" s="112">
+        <f>H206+$C$173/$C$172/I206</f>
+        <v/>
+      </c>
+      <c r="G206" s="112">
+        <f>F206*$C$172</f>
+        <v/>
+      </c>
+      <c r="H206" s="112" t="n">
         <v>13.4</v>
       </c>
-      <c r="J206" s="83" t="n">
+      <c r="I206" s="124" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="84" t="inlineStr">
+      <c r="A207" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-E0-18</t>
         </is>
       </c>
-      <c r="B207" s="84" t="inlineStr">
+      <c r="B207" s="117" t="inlineStr">
         <is>
           <t>MDF 18 mm, E0, landed Kudus</t>
         </is>
       </c>
-      <c r="C207" s="89">
-        <f>H207</f>
-        <v/>
-      </c>
-      <c r="E207" s="84" t="inlineStr">
+      <c r="C207" s="114">
+        <f>G207</f>
+        <v/>
+      </c>
+      <c r="D207" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F207" s="84" t="inlineStr">
+      <c r="E207" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G207" s="82">
-        <f>I207+$C$173/$C$172/J207</f>
-        <v/>
-      </c>
-      <c r="H207" s="83">
-        <f>G207*$C$172</f>
-        <v/>
-      </c>
-      <c r="I207" s="82" t="n">
+      <c r="F207" s="112">
+        <f>H207+$C$173/$C$172/I207</f>
+        <v/>
+      </c>
+      <c r="G207" s="112">
+        <f>F207*$C$172</f>
+        <v/>
+      </c>
+      <c r="H207" s="112" t="n">
         <v>16</v>
       </c>
-      <c r="J207" s="83" t="n">
+      <c r="I207" s="124" t="n">
         <v>750</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="84" t="inlineStr">
+      <c r="A208" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-CARB-3</t>
         </is>
       </c>
-      <c r="B208" s="84" t="inlineStr">
+      <c r="B208" s="117" t="inlineStr">
         <is>
           <t>MDF 3 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
         </is>
       </c>
-      <c r="C208" s="89">
-        <f>H208</f>
-        <v/>
-      </c>
-      <c r="E208" s="84" t="inlineStr">
+      <c r="C208" s="114">
+        <f>G208</f>
+        <v/>
+      </c>
+      <c r="D208" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F208" s="84" t="inlineStr">
+      <c r="E208" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G208" s="82">
-        <f>I208+$C$173/$C$172/J208</f>
-        <v/>
-      </c>
-      <c r="H208" s="83">
-        <f>G208*$C$172</f>
-        <v/>
-      </c>
-      <c r="I208" s="82" t="n">
+      <c r="F208" s="112">
+        <f>H208+$C$173/$C$172/I208</f>
+        <v/>
+      </c>
+      <c r="G208" s="112">
+        <f>F208*$C$172</f>
+        <v/>
+      </c>
+      <c r="H208" s="112" t="n">
         <v>2.8</v>
       </c>
-      <c r="J208" s="83" t="n">
+      <c r="I208" s="124" t="n">
         <v>4060</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="84" t="inlineStr">
+      <c r="A209" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-CARB-6</t>
         </is>
       </c>
-      <c r="B209" s="84" t="inlineStr">
+      <c r="B209" s="117" t="inlineStr">
         <is>
           <t>MDF 6 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
         </is>
       </c>
-      <c r="C209" s="89">
-        <f>H209</f>
-        <v/>
-      </c>
-      <c r="E209" s="84" t="inlineStr">
+      <c r="C209" s="114">
+        <f>G209</f>
+        <v/>
+      </c>
+      <c r="D209" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F209" s="84" t="inlineStr">
+      <c r="E209" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G209" s="82">
-        <f>I209+$C$173/$C$172/J209</f>
-        <v/>
-      </c>
-      <c r="H209" s="83">
-        <f>G209*$C$172</f>
-        <v/>
-      </c>
-      <c r="I209" s="82" t="n">
+      <c r="F209" s="112">
+        <f>H209+$C$173/$C$172/I209</f>
+        <v/>
+      </c>
+      <c r="G209" s="112">
+        <f>F209*$C$172</f>
+        <v/>
+      </c>
+      <c r="H209" s="112" t="n">
         <v>5.35</v>
       </c>
-      <c r="J209" s="83" t="n">
+      <c r="I209" s="124" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="84" t="inlineStr">
+      <c r="A210" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-CARB-9</t>
         </is>
       </c>
-      <c r="B210" s="84" t="inlineStr">
+      <c r="B210" s="117" t="inlineStr">
         <is>
           <t>MDF 9 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
         </is>
       </c>
-      <c r="C210" s="89">
-        <f>H210</f>
-        <v/>
-      </c>
-      <c r="E210" s="84" t="inlineStr">
+      <c r="C210" s="114">
+        <f>G210</f>
+        <v/>
+      </c>
+      <c r="D210" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F210" s="84" t="inlineStr">
+      <c r="E210" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G210" s="82">
-        <f>I210+$C$173/$C$172/J210</f>
-        <v/>
-      </c>
-      <c r="H210" s="83">
-        <f>G210*$C$172</f>
-        <v/>
-      </c>
-      <c r="I210" s="82" t="n">
+      <c r="F210" s="112">
+        <f>H210+$C$173/$C$172/I210</f>
+        <v/>
+      </c>
+      <c r="G210" s="112">
+        <f>F210*$C$172</f>
+        <v/>
+      </c>
+      <c r="H210" s="112" t="n">
         <v>7.5</v>
       </c>
-      <c r="J210" s="83" t="n">
+      <c r="I210" s="124" t="n">
         <v>1425</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="84" t="inlineStr">
+      <c r="A211" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-CARB-12</t>
         </is>
       </c>
-      <c r="B211" s="84" t="inlineStr">
+      <c r="B211" s="117" t="inlineStr">
         <is>
           <t>MDF 12 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
         </is>
       </c>
-      <c r="C211" s="89">
-        <f>H211</f>
-        <v/>
-      </c>
-      <c r="E211" s="84" t="inlineStr">
+      <c r="C211" s="114">
+        <f>G211</f>
+        <v/>
+      </c>
+      <c r="D211" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F211" s="84" t="inlineStr">
+      <c r="E211" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G211" s="82">
-        <f>I211+$C$173/$C$172/J211</f>
-        <v/>
-      </c>
-      <c r="H211" s="83">
-        <f>G211*$C$172</f>
-        <v/>
-      </c>
-      <c r="I211" s="82" t="n">
+      <c r="F211" s="112">
+        <f>H211+$C$173/$C$172/I211</f>
+        <v/>
+      </c>
+      <c r="G211" s="112">
+        <f>F211*$C$172</f>
+        <v/>
+      </c>
+      <c r="H211" s="112" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J211" s="83" t="n">
+      <c r="I211" s="124" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="84" t="inlineStr">
+      <c r="A212" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-CARB-15</t>
         </is>
       </c>
-      <c r="B212" s="84" t="inlineStr">
+      <c r="B212" s="117" t="inlineStr">
         <is>
           <t>MDF 15 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
         </is>
       </c>
-      <c r="C212" s="89">
-        <f>H212</f>
-        <v/>
-      </c>
-      <c r="E212" s="84" t="inlineStr">
+      <c r="C212" s="114">
+        <f>G212</f>
+        <v/>
+      </c>
+      <c r="D212" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F212" s="84" t="inlineStr">
+      <c r="E212" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G212" s="82">
-        <f>I212+$C$173/$C$172/J212</f>
-        <v/>
-      </c>
-      <c r="H212" s="83">
-        <f>G212*$C$172</f>
-        <v/>
-      </c>
-      <c r="I212" s="82" t="n">
+      <c r="F212" s="112">
+        <f>H212+$C$173/$C$172/I212</f>
+        <v/>
+      </c>
+      <c r="G212" s="112">
+        <f>F212*$C$172</f>
+        <v/>
+      </c>
+      <c r="H212" s="112" t="n">
         <v>11.05</v>
       </c>
-      <c r="J212" s="83" t="n">
+      <c r="I212" s="124" t="n">
         <v>960</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="84" t="inlineStr">
+      <c r="A213" s="113" t="inlineStr">
         <is>
           <t>LND-MDF-CARB-18</t>
         </is>
       </c>
-      <c r="B213" s="84" t="inlineStr">
+      <c r="B213" s="117" t="inlineStr">
         <is>
           <t>MDF 18 mm, CARB Phase 2 / TSCA Title VI, landed Kudus</t>
         </is>
       </c>
-      <c r="C213" s="89">
-        <f>H213</f>
-        <v/>
-      </c>
-      <c r="E213" s="84" t="inlineStr">
+      <c r="C213" s="114">
+        <f>G213</f>
+        <v/>
+      </c>
+      <c r="D213" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F213" s="84" t="inlineStr">
+      <c r="E213" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G213" s="82">
-        <f>I213+$C$173/$C$172/J213</f>
-        <v/>
-      </c>
-      <c r="H213" s="83">
-        <f>G213*$C$172</f>
-        <v/>
-      </c>
-      <c r="I213" s="82" t="n">
+      <c r="F213" s="112">
+        <f>H213+$C$173/$C$172/I213</f>
+        <v/>
+      </c>
+      <c r="G213" s="112">
+        <f>F213*$C$172</f>
+        <v/>
+      </c>
+      <c r="H213" s="112" t="n">
         <v>13.2</v>
       </c>
-      <c r="J213" s="83" t="n">
+      <c r="I213" s="124" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="84" t="inlineStr">
+      <c r="A214" s="113" t="inlineStr">
         <is>
           <t>LND-MAR-15</t>
         </is>
       </c>
-      <c r="B214" s="84" t="inlineStr">
+      <c r="B214" s="117" t="inlineStr">
         <is>
           <t>Marine plywood 15 mm, BS 1088 type, WBP glue, landed Kudus</t>
         </is>
       </c>
-      <c r="C214" s="89">
-        <f>H214</f>
-        <v/>
-      </c>
-      <c r="E214" s="84" t="inlineStr">
+      <c r="C214" s="114">
+        <f>G214</f>
+        <v/>
+      </c>
+      <c r="D214" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F214" s="84" t="inlineStr">
+      <c r="E214" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G214" s="82">
-        <f>I214+$C$173/$C$172/J214</f>
-        <v/>
-      </c>
-      <c r="H214" s="83">
-        <f>G214*$C$172</f>
-        <v/>
-      </c>
-      <c r="I214" s="82" t="n">
+      <c r="F214" s="112">
+        <f>H214+$C$173/$C$172/I214</f>
+        <v/>
+      </c>
+      <c r="G214" s="112">
+        <f>F214*$C$172</f>
+        <v/>
+      </c>
+      <c r="H214" s="112" t="n">
         <v>20.324</v>
       </c>
-      <c r="J214" s="83" t="n">
+      <c r="I214" s="124" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="84" t="inlineStr">
+      <c r="A215" s="113" t="inlineStr">
         <is>
           <t>LND-MAR-18</t>
         </is>
       </c>
-      <c r="B215" s="84" t="inlineStr">
+      <c r="B215" s="117" t="inlineStr">
         <is>
           <t>Marine plywood 18 mm, BS 1088 type, WBP glue, landed Kudus</t>
         </is>
       </c>
-      <c r="C215" s="89">
-        <f>H215</f>
-        <v/>
-      </c>
-      <c r="E215" s="84" t="inlineStr">
+      <c r="C215" s="114">
+        <f>G215</f>
+        <v/>
+      </c>
+      <c r="D215" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F215" s="84" t="inlineStr">
+      <c r="E215" s="113" t="inlineStr">
         <is>
           <t>RFQ_MDF_Plywood_Landed_Kudus_Tala_Living.xlsx, Landed Rates sheet (Linyi Ocean quote 16 Oct 2026)</t>
         </is>
       </c>
-      <c r="G215" s="82">
-        <f>I215+$C$173/$C$172/J215</f>
-        <v/>
-      </c>
-      <c r="H215" s="83">
-        <f>G215*$C$172</f>
-        <v/>
-      </c>
-      <c r="I215" s="82" t="n">
+      <c r="F215" s="112">
+        <f>H215+$C$173/$C$172/I215</f>
+        <v/>
+      </c>
+      <c r="G215" s="112">
+        <f>F215*$C$172</f>
+        <v/>
+      </c>
+      <c r="H215" s="112" t="n">
         <v>24.043</v>
       </c>
-      <c r="J215" s="83" t="n">
+      <c r="I215" s="124" t="n">
         <v>933</v>
       </c>
     </row>
+    <row r="216"/>
     <row r="217">
-      <c r="A217" s="84" t="inlineStr">
+      <c r="A217" s="97" t="inlineStr">
         <is>
           <t>BOARD RATES ADDED 16 OCT 2026 (use as PANEL TYPE on item tabs)</t>
         </is>
       </c>
+      <c r="B217" s="98" t="n"/>
+      <c r="C217" s="98" t="n"/>
+      <c r="D217" s="98" t="n"/>
+      <c r="E217" s="98" t="n"/>
+      <c r="F217" s="98" t="n"/>
+      <c r="G217" s="98" t="n"/>
+      <c r="H217" s="98" t="n"/>
+      <c r="I217" s="98" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="84" t="inlineStr">
+      <c r="A218" s="113" t="inlineStr">
         <is>
           <t>MDF-3-RAW</t>
         </is>
       </c>
-      <c r="B218" s="84" t="inlineStr">
+      <c r="B218" s="117" t="inlineStr">
         <is>
           <t>MDF 3 mm, raw, grade per PANEL_GRADE</t>
         </is>
       </c>
-      <c r="C218" s="89">
+      <c r="C218" s="114">
         <f t="array" ref="C218">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
         <v/>
       </c>
-      <c r="E218" s="84" t="inlineStr">
+      <c r="D218" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F218" s="84" t="inlineStr">
+      <c r="E218" s="113" t="inlineStr">
         <is>
           <t>Landed rows above</t>
         </is>
       </c>
-      <c r="G218" s="82">
-        <f t="array" ref="G218">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H218" s="83">
-        <f>G218*$C$172</f>
-        <v/>
-      </c>
+      <c r="F218" s="112">
+        <f t="array" ref="F218">INDEX($F$178:$F$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-3",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G218" s="112">
+        <f>F218*$C$172</f>
+        <v/>
+      </c>
+      <c r="H218" s="95" t="n"/>
+      <c r="I218" s="95" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="84" t="inlineStr">
+      <c r="A219" s="113" t="inlineStr">
         <is>
           <t>MDF-6-RAW</t>
         </is>
       </c>
-      <c r="B219" s="84" t="inlineStr">
+      <c r="B219" s="117" t="inlineStr">
         <is>
           <t>MDF 6 mm, raw, grade per PANEL_GRADE</t>
         </is>
       </c>
-      <c r="C219" s="89">
+      <c r="C219" s="114">
         <f t="array" ref="C219">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
         <v/>
       </c>
-      <c r="E219" s="84" t="inlineStr">
+      <c r="D219" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F219" s="84" t="inlineStr">
+      <c r="E219" s="113" t="inlineStr">
         <is>
           <t>Landed rows above</t>
         </is>
       </c>
-      <c r="G219" s="82">
-        <f t="array" ref="G219">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H219" s="83">
-        <f>G219*$C$172</f>
-        <v/>
-      </c>
+      <c r="F219" s="112">
+        <f t="array" ref="F219">INDEX($F$178:$F$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-6",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G219" s="112">
+        <f>F219*$C$172</f>
+        <v/>
+      </c>
+      <c r="H219" s="95" t="n"/>
+      <c r="I219" s="95" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="84" t="inlineStr">
+      <c r="A220" s="113" t="inlineStr">
         <is>
           <t>MDF-9-RAW</t>
         </is>
       </c>
-      <c r="B220" s="84" t="inlineStr">
+      <c r="B220" s="117" t="inlineStr">
         <is>
           <t>MDF 9 mm, raw, grade per PANEL_GRADE</t>
         </is>
       </c>
-      <c r="C220" s="89">
+      <c r="C220" s="114">
         <f t="array" ref="C220">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
         <v/>
       </c>
-      <c r="E220" s="84" t="inlineStr">
+      <c r="D220" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F220" s="84" t="inlineStr">
+      <c r="E220" s="113" t="inlineStr">
         <is>
           <t>Landed rows above</t>
         </is>
       </c>
-      <c r="G220" s="82">
-        <f t="array" ref="G220">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H220" s="83">
-        <f>G220*$C$172</f>
-        <v/>
-      </c>
+      <c r="F220" s="112">
+        <f t="array" ref="F220">INDEX($F$178:$F$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-9",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G220" s="112">
+        <f>F220*$C$172</f>
+        <v/>
+      </c>
+      <c r="H220" s="95" t="n"/>
+      <c r="I220" s="95" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="84" t="inlineStr">
+      <c r="A221" s="113" t="inlineStr">
         <is>
           <t>MDF-12-RAW</t>
         </is>
       </c>
-      <c r="B221" s="84" t="inlineStr">
+      <c r="B221" s="117" t="inlineStr">
         <is>
           <t>MDF 12 mm, raw, grade per PANEL_GRADE</t>
         </is>
       </c>
-      <c r="C221" s="89">
+      <c r="C221" s="114">
         <f t="array" ref="C221">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
         <v/>
       </c>
-      <c r="E221" s="84" t="inlineStr">
+      <c r="D221" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F221" s="84" t="inlineStr">
+      <c r="E221" s="113" t="inlineStr">
         <is>
           <t>Landed rows above</t>
         </is>
       </c>
-      <c r="G221" s="82">
-        <f t="array" ref="G221">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H221" s="83">
-        <f>G221*$C$172</f>
-        <v/>
-      </c>
+      <c r="F221" s="112">
+        <f t="array" ref="F221">INDEX($F$178:$F$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-12",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G221" s="112">
+        <f>F221*$C$172</f>
+        <v/>
+      </c>
+      <c r="H221" s="95" t="n"/>
+      <c r="I221" s="95" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="84" t="inlineStr">
+      <c r="A222" s="113" t="inlineStr">
         <is>
           <t>MDF-15-RAW</t>
         </is>
       </c>
-      <c r="B222" s="84" t="inlineStr">
+      <c r="B222" s="117" t="inlineStr">
         <is>
           <t>MDF 15 mm, raw, grade per PANEL_GRADE</t>
         </is>
       </c>
-      <c r="C222" s="89">
+      <c r="C222" s="114">
         <f t="array" ref="C222">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
         <v/>
       </c>
-      <c r="E222" s="84" t="inlineStr">
+      <c r="D222" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F222" s="84" t="inlineStr">
+      <c r="E222" s="113" t="inlineStr">
         <is>
           <t>Landed rows above</t>
         </is>
       </c>
-      <c r="G222" s="82">
-        <f t="array" ref="G222">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H222" s="83">
-        <f>G222*$C$172</f>
-        <v/>
-      </c>
+      <c r="F222" s="112">
+        <f t="array" ref="F222">INDEX($F$178:$F$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-15",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G222" s="112">
+        <f>F222*$C$172</f>
+        <v/>
+      </c>
+      <c r="H222" s="95" t="n"/>
+      <c r="I222" s="95" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="84" t="inlineStr">
+      <c r="A223" s="113" t="inlineStr">
         <is>
           <t>MDF-18-RAW</t>
         </is>
       </c>
-      <c r="B223" s="84" t="inlineStr">
+      <c r="B223" s="117" t="inlineStr">
         <is>
           <t>MDF 18 mm, raw, grade per PANEL_GRADE</t>
         </is>
       </c>
-      <c r="C223" s="89">
+      <c r="C223" s="114">
         <f t="array" ref="C223">INDEX($C$178:$C$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
         <v/>
       </c>
-      <c r="E223" s="84" t="inlineStr">
+      <c r="D223" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F223" s="84" t="inlineStr">
+      <c r="E223" s="113" t="inlineStr">
         <is>
           <t>Landed rows above</t>
         </is>
       </c>
-      <c r="G223" s="82">
-        <f t="array" ref="G223">INDEX($G$178:$G$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H223" s="83">
-        <f>G223*$C$172</f>
-        <v/>
-      </c>
+      <c r="F223" s="112">
+        <f t="array" ref="F223">INDEX($F$178:$F$215,MATCH("LND-MDF-"&amp;$C$174&amp;"-18",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G223" s="112">
+        <f>F223*$C$172</f>
+        <v/>
+      </c>
+      <c r="H223" s="95" t="n"/>
+      <c r="I223" s="95" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="84" t="inlineStr">
+      <c r="A224" s="113" t="inlineStr">
         <is>
           <t>PLY-15-MAR</t>
         </is>
       </c>
-      <c r="B224" s="84" t="inlineStr">
+      <c r="B224" s="117" t="inlineStr">
         <is>
           <t>Marine plywood 15 mm, raw</t>
         </is>
       </c>
-      <c r="C224" s="89">
+      <c r="C224" s="114">
         <f t="array" ref="C224">INDEX($C$178:$C$215,MATCH("LND-MAR-15",$A$178:$A$215,0))</f>
         <v/>
       </c>
-      <c r="E224" s="84" t="inlineStr">
+      <c r="D224" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F224" s="84" t="inlineStr">
+      <c r="E224" s="113" t="inlineStr">
         <is>
           <t>Landed rows above</t>
         </is>
       </c>
-      <c r="G224" s="82">
-        <f t="array" ref="G224">INDEX($G$178:$G$215,MATCH("LND-MAR-15",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H224" s="83">
-        <f>G224*$C$172</f>
-        <v/>
-      </c>
+      <c r="F224" s="112">
+        <f t="array" ref="F224">INDEX($F$178:$F$215,MATCH("LND-MAR-15",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G224" s="112">
+        <f>F224*$C$172</f>
+        <v/>
+      </c>
+      <c r="H224" s="95" t="n"/>
+      <c r="I224" s="95" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="84" t="inlineStr">
+      <c r="A225" s="113" t="inlineStr">
         <is>
           <t>PLY-18-MAR</t>
         </is>
       </c>
-      <c r="B225" s="84" t="inlineStr">
+      <c r="B225" s="117" t="inlineStr">
         <is>
           <t>Marine plywood 18 mm, raw</t>
         </is>
       </c>
-      <c r="C225" s="89">
+      <c r="C225" s="114">
         <f t="array" ref="C225">INDEX($C$178:$C$215,MATCH("LND-MAR-18",$A$178:$A$215,0))</f>
         <v/>
       </c>
-      <c r="E225" s="84" t="inlineStr">
+      <c r="D225" s="113" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-      <c r="F225" s="84" t="inlineStr">
+      <c r="E225" s="113" t="inlineStr">
         <is>
           <t>Landed rows above</t>
         </is>
       </c>
-      <c r="G225" s="82">
-        <f t="array" ref="G225">INDEX($G$178:$G$215,MATCH("LND-MAR-18",$A$178:$A$215,0))</f>
-        <v/>
-      </c>
-      <c r="H225" s="83">
-        <f>G225*$C$172</f>
-        <v/>
-      </c>
-    </row>
+      <c r="F225" s="112">
+        <f t="array" ref="F225">INDEX($F$178:$F$215,MATCH("LND-MAR-18",$A$178:$A$215,0))</f>
+        <v/>
+      </c>
+      <c r="G225" s="112">
+        <f>F225*$C$172</f>
+        <v/>
+      </c>
+      <c r="H225" s="95" t="n"/>
+      <c r="I225" s="95" t="n"/>
+    </row>
+    <row r="226"/>
     <row r="227">
-      <c r="A227" s="84" t="inlineStr">
+      <c r="A227" s="97" t="inlineStr">
         <is>
           <t>HARDWARE (bought-in). Value = USD price × FX_USD.</t>
         </is>
       </c>
-      <c r="G227" s="86" t="inlineStr">
+      <c r="B227" s="98" t="n"/>
+      <c r="C227" s="98" t="n"/>
+      <c r="D227" s="98" t="n"/>
+      <c r="E227" s="98" t="n"/>
+      <c r="F227" s="125" t="inlineStr">
         <is>
           <t>Quote USD</t>
         </is>
       </c>
-      <c r="H227" s="87" t="inlineStr">
+      <c r="G227" s="126" t="inlineStr">
         <is>
           <t>Quote IDR (USD × FX_USD)</t>
         </is>
       </c>
+      <c r="H227" s="98" t="n"/>
+      <c r="I227" s="98" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="84" t="inlineStr">
+      <c r="A228" s="113" t="inlineStr">
         <is>
           <t>HW-RAIL-DTC</t>
         </is>
       </c>
-      <c r="B228" s="84" t="inlineStr">
+      <c r="B228" s="117" t="inlineStr">
         <is>
           <t>Drawer rail DTC, side-mount, soft-close, ball-bearing</t>
         </is>
       </c>
-      <c r="C228" s="89">
-        <f>H228</f>
-        <v/>
-      </c>
-      <c r="E228" s="84" t="inlineStr">
+      <c r="C228" s="114">
+        <f>G228</f>
+        <v/>
+      </c>
+      <c r="D228" s="113" t="inlineStr">
         <is>
           <t>IDR/pair</t>
         </is>
       </c>
-      <c r="F228" s="84" t="inlineStr">
+      <c r="E228" s="113" t="inlineStr">
         <is>
           <t>Approved by David 7 Oct 2026 (project doc HARDWARE PRICE 16 OCT). Same price for all lengths.</t>
         </is>
       </c>
-      <c r="G228" s="82" t="n">
+      <c r="F228" s="112" t="n">
         <v>2.75</v>
       </c>
-      <c r="H228" s="83">
-        <f>G228*$C$172</f>
-        <v/>
-      </c>
+      <c r="G228" s="112">
+        <f>F228*$C$172</f>
+        <v/>
+      </c>
+      <c r="H228" s="95" t="n"/>
+      <c r="I228" s="95" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="84" t="inlineStr">
+      <c r="A229" s="113" t="inlineStr">
         <is>
           <t>HW-HINGE-DTC</t>
         </is>
       </c>
-      <c r="B229" s="84" t="inlineStr">
+      <c r="B229" s="117" t="inlineStr">
         <is>
           <t>Soft-close hinge DTC</t>
         </is>
       </c>
-      <c r="C229" s="89">
-        <f>H229</f>
-        <v/>
-      </c>
-      <c r="E229" s="84" t="inlineStr">
+      <c r="C229" s="114">
+        <f>G229</f>
+        <v/>
+      </c>
+      <c r="D229" s="113" t="inlineStr">
         <is>
           <t>IDR/pc</t>
         </is>
       </c>
-      <c r="F229" s="84" t="inlineStr">
+      <c r="E229" s="113" t="inlineStr">
         <is>
           <t>Approved by David 7 Oct 2026 (project doc HARDWARE PRICE 16 OCT)</t>
         </is>
       </c>
-      <c r="G229" s="82" t="n">
+      <c r="F229" s="112" t="n">
         <v>0.6</v>
       </c>
-      <c r="H229" s="83">
-        <f>G229*$C$172</f>
-        <v/>
-      </c>
-    </row>
+      <c r="G229" s="112">
+        <f>F229*$C$172</f>
+        <v/>
+      </c>
+      <c r="H229" s="95" t="n"/>
+      <c r="I229" s="95" t="n"/>
+    </row>
+    <row r="230"/>
     <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="127" t="inlineStr">
         <is>
           <t>VENEERED LANDED BOARDS (E2 + Mindi Veneer)</t>
         </is>
       </c>
+      <c r="B231" s="98" t="n"/>
+      <c r="C231" s="98" t="n"/>
+      <c r="D231" s="98" t="n"/>
+      <c r="E231" s="98" t="n"/>
+      <c r="F231" s="98" t="n"/>
+      <c r="G231" s="98" t="n"/>
+      <c r="H231" s="98" t="n"/>
+      <c r="I231" s="98" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-18-MSF</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 18 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C232">
+      <c r="C232" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-18",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="D232" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E232" s="95" t="n"/>
+      <c r="F232" s="95" t="n"/>
+      <c r="G232" s="95" t="n"/>
+      <c r="H232" s="95" t="n"/>
+      <c r="I232" s="95" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-18-MDF</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 18 mm, Mindi double face</t>
         </is>
       </c>
-      <c r="C233">
+      <c r="C233" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-18",$A$178:$A$215,0))+2*$C$175</f>
         <v/>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="D233" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E233" s="95" t="n"/>
+      <c r="F233" s="95" t="n"/>
+      <c r="G233" s="95" t="n"/>
+      <c r="H233" s="95" t="n"/>
+      <c r="I233" s="95" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-15-MSF</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 15 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C234">
+      <c r="C234" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-15",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="D234" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E234" s="95" t="n"/>
+      <c r="F234" s="95" t="n"/>
+      <c r="G234" s="95" t="n"/>
+      <c r="H234" s="95" t="n"/>
+      <c r="I234" s="95" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-15-MDF</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 15 mm, Mindi double face</t>
         </is>
       </c>
-      <c r="C235">
+      <c r="C235" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-15",$A$178:$A$215,0))+2*$C$175</f>
         <v/>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="D235" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E235" s="95" t="n"/>
+      <c r="F235" s="95" t="n"/>
+      <c r="G235" s="95" t="n"/>
+      <c r="H235" s="95" t="n"/>
+      <c r="I235" s="95" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-12-MSF</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 12 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C236">
+      <c r="C236" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-12",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="D236" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E236" s="95" t="n"/>
+      <c r="F236" s="95" t="n"/>
+      <c r="G236" s="95" t="n"/>
+      <c r="H236" s="95" t="n"/>
+      <c r="I236" s="95" t="n"/>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-12-MDF</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 12 mm, Mindi double face</t>
         </is>
       </c>
-      <c r="C237">
+      <c r="C237" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-12",$A$178:$A$215,0))+2*$C$175</f>
         <v/>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="D237" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E237" s="95" t="n"/>
+      <c r="F237" s="95" t="n"/>
+      <c r="G237" s="95" t="n"/>
+      <c r="H237" s="95" t="n"/>
+      <c r="I237" s="95" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-9-MSF</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 9 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C238">
+      <c r="C238" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-9",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="D238" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E238" s="95" t="n"/>
+      <c r="F238" s="95" t="n"/>
+      <c r="G238" s="95" t="n"/>
+      <c r="H238" s="95" t="n"/>
+      <c r="I238" s="95" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-9-MDF</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 9 mm, Mindi double face</t>
         </is>
       </c>
-      <c r="C239">
+      <c r="C239" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-9",$A$178:$A$215,0))+2*$C$175</f>
         <v/>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="D239" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E239" s="95" t="n"/>
+      <c r="F239" s="95" t="n"/>
+      <c r="G239" s="95" t="n"/>
+      <c r="H239" s="95" t="n"/>
+      <c r="I239" s="95" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-6-MSF</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 6 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C240">
+      <c r="C240" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-6",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="D240" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E240" s="95" t="n"/>
+      <c r="F240" s="95" t="n"/>
+      <c r="G240" s="95" t="n"/>
+      <c r="H240" s="95" t="n"/>
+      <c r="I240" s="95" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-6-MDF</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 6 mm, Mindi double face</t>
         </is>
       </c>
-      <c r="C241">
+      <c r="C241" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-6",$A$178:$A$215,0))+2*$C$175</f>
         <v/>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="D241" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E241" s="95" t="n"/>
+      <c r="F241" s="95" t="n"/>
+      <c r="G241" s="95" t="n"/>
+      <c r="H241" s="95" t="n"/>
+      <c r="I241" s="95" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-3-MSF</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B242" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 3 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C242">
+      <c r="C242" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-3",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="D242" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E242" s="95" t="n"/>
+      <c r="F242" s="95" t="n"/>
+      <c r="G242" s="95" t="n"/>
+      <c r="H242" s="95" t="n"/>
+      <c r="I242" s="95" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="95" t="inlineStr">
         <is>
           <t>LND-PLY-E2-3-MDF</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B243" s="93" t="inlineStr">
         <is>
           <t>Plywood E2 3 mm, Mindi double face</t>
         </is>
       </c>
-      <c r="C243">
+      <c r="C243" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E2-3",$A$178:$A$215,0))+2*$C$175</f>
         <v/>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="D243" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E243" s="95" t="n"/>
+      <c r="F243" s="95" t="n"/>
+      <c r="G243" s="95" t="n"/>
+      <c r="H243" s="95" t="n"/>
+      <c r="I243" s="95" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="95" t="inlineStr">
         <is>
           <t>LND-MDF-E2-18-MSF</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B244" s="93" t="inlineStr">
         <is>
           <t>MDF E2 18 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C244">
+      <c r="C244" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-18",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="D244" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E244" s="95" t="n"/>
+      <c r="F244" s="95" t="n"/>
+      <c r="G244" s="95" t="n"/>
+      <c r="H244" s="95" t="n"/>
+      <c r="I244" s="95" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="95" t="inlineStr">
         <is>
           <t>LND-MDF-E2-18-MDF</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B245" s="93" t="inlineStr">
         <is>
           <t>MDF E2 18 mm, Mindi double face</t>
         </is>
       </c>
-      <c r="C245">
+      <c r="C245" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-18",$A$178:$A$215,0))+2*$C$175</f>
         <v/>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="D245" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E245" s="95" t="n"/>
+      <c r="F245" s="95" t="n"/>
+      <c r="G245" s="95" t="n"/>
+      <c r="H245" s="95" t="n"/>
+      <c r="I245" s="95" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="95" t="inlineStr">
         <is>
           <t>LND-MDF-E2-15-MSF</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B246" s="93" t="inlineStr">
         <is>
           <t>MDF E2 15 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C246">
+      <c r="C246" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-15",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="D246" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E246" s="95" t="n"/>
+      <c r="F246" s="95" t="n"/>
+      <c r="G246" s="95" t="n"/>
+      <c r="H246" s="95" t="n"/>
+      <c r="I246" s="95" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="95" t="inlineStr">
         <is>
           <t>LND-MDF-E2-12-MSF</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B247" s="93" t="inlineStr">
         <is>
           <t>MDF E2 12 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C247">
+      <c r="C247" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-12",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="D247" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E247" s="95" t="n"/>
+      <c r="F247" s="95" t="n"/>
+      <c r="G247" s="95" t="n"/>
+      <c r="H247" s="95" t="n"/>
+      <c r="I247" s="95" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="95" t="inlineStr">
         <is>
           <t>LND-MDF-E2-9-MSF</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B248" s="93" t="inlineStr">
         <is>
           <t>MDF E2 9 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C248">
+      <c r="C248" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-9",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="D248" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
+      <c r="E248" s="95" t="n"/>
+      <c r="F248" s="95" t="n"/>
+      <c r="G248" s="95" t="n"/>
+      <c r="H248" s="95" t="n"/>
+      <c r="I248" s="95" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="95" t="inlineStr">
         <is>
           <t>LND-MDF-E2-6-MSF</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B249" s="93" t="inlineStr">
         <is>
           <t>MDF E2 6 mm, Mindi single face</t>
         </is>
       </c>
-      <c r="C249">
+      <c r="C249" s="128">
         <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E2-6",$A$178:$A$215,0))+$C$175</f>
         <v/>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="D249" s="95" t="inlineStr">
         <is>
           <t>IDR/sheet</t>
         </is>
       </c>
-    </row>
+      <c r="E249" s="95" t="n"/>
+      <c r="F249" s="95" t="n"/>
+      <c r="G249" s="95" t="n"/>
+      <c r="H249" s="95" t="n"/>
+      <c r="I249" s="95" t="n"/>
+    </row>
+    <row r="250"/>
     <row r="251">
-      <c r="A251" s="91" t="inlineStr">
+      <c r="A251" s="127" t="inlineStr">
         <is>
           <t>METAL (added 19 Oct 2026). Value EMPTY: price not yet received. Fill column C; METAL parts cost 0 until filled.</t>
         </is>
       </c>
+      <c r="B251" s="98" t="n"/>
+      <c r="C251" s="98" t="n"/>
+      <c r="D251" s="98" t="n"/>
+      <c r="E251" s="98" t="n"/>
+      <c r="F251" s="98" t="n"/>
+      <c r="G251" s="98" t="n"/>
+      <c r="H251" s="98" t="n"/>
+      <c r="I251" s="98" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="84" t="inlineStr">
+      <c r="A252" s="113" t="inlineStr">
         <is>
           <t>METAL_A</t>
         </is>
       </c>
-      <c r="B252" s="84" t="inlineStr">
+      <c r="B252" s="117" t="inlineStr">
         <is>
           <t>Metal tier A (exposed, long), per m³ of component</t>
         </is>
       </c>
-      <c r="C252" s="89" t="n"/>
-      <c r="E252" s="84" t="inlineStr">
+      <c r="C252" s="129" t="n"/>
+      <c r="D252" s="113" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F252" s="84" t="inlineStr">
+      <c r="E252" s="113" t="inlineStr">
         <is>
           <t>EMPTY: waiting for price</t>
         </is>
       </c>
+      <c r="F252" s="95" t="n"/>
+      <c r="G252" s="95" t="n"/>
+      <c r="H252" s="95" t="n"/>
+      <c r="I252" s="95" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="84" t="inlineStr">
+      <c r="A253" s="113" t="inlineStr">
         <is>
           <t>METAL_B</t>
         </is>
       </c>
-      <c r="B253" s="84" t="inlineStr">
+      <c r="B253" s="117" t="inlineStr">
         <is>
           <t>Metal tier B</t>
         </is>
       </c>
-      <c r="C253" s="89" t="n"/>
-      <c r="E253" s="84" t="inlineStr">
+      <c r="C253" s="129" t="n"/>
+      <c r="D253" s="113" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F253" s="84" t="inlineStr">
+      <c r="E253" s="113" t="inlineStr">
         <is>
           <t>EMPTY: waiting for price</t>
         </is>
       </c>
+      <c r="F253" s="95" t="n"/>
+      <c r="G253" s="95" t="n"/>
+      <c r="H253" s="95" t="n"/>
+      <c r="I253" s="95" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="84" t="inlineStr">
+      <c r="A254" s="113" t="inlineStr">
         <is>
           <t>METAL_C</t>
         </is>
       </c>
-      <c r="B254" s="84" t="inlineStr">
+      <c r="B254" s="117" t="inlineStr">
         <is>
           <t>Metal tier C</t>
         </is>
       </c>
-      <c r="C254" s="89" t="n"/>
-      <c r="E254" s="84" t="inlineStr">
+      <c r="C254" s="129" t="n"/>
+      <c r="D254" s="113" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F254" s="84" t="inlineStr">
+      <c r="E254" s="113" t="inlineStr">
         <is>
           <t>EMPTY: waiting for price</t>
         </is>
       </c>
+      <c r="F254" s="95" t="n"/>
+      <c r="G254" s="95" t="n"/>
+      <c r="H254" s="95" t="n"/>
+      <c r="I254" s="95" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="84" t="inlineStr">
+      <c r="A255" s="113" t="inlineStr">
         <is>
           <t>METAL_D</t>
         </is>
       </c>
-      <c r="B255" s="84" t="inlineStr">
+      <c r="B255" s="117" t="inlineStr">
         <is>
           <t>Metal tier D</t>
         </is>
       </c>
-      <c r="C255" s="89" t="n"/>
-      <c r="E255" s="84" t="inlineStr">
+      <c r="C255" s="129" t="n"/>
+      <c r="D255" s="113" t="inlineStr">
         <is>
           <t>IDR/m³</t>
         </is>
       </c>
-      <c r="F255" s="84" t="inlineStr">
+      <c r="E255" s="113" t="inlineStr">
         <is>
           <t>EMPTY: waiting for price</t>
         </is>
       </c>
+      <c r="F255" s="95" t="n"/>
+      <c r="G255" s="95" t="n"/>
+      <c r="H255" s="95" t="n"/>
+      <c r="I255" s="95" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="84" t="inlineStr">
+      <c r="A256" s="113" t="inlineStr">
         <is>
           <t>metal_brass</t>
         </is>
       </c>
-      <c r="B256" s="84" t="inlineStr">
+      <c r="B256" s="117" t="inlineStr">
         <is>
           <t>Brass, per kg (reference)</t>
         </is>
       </c>
-      <c r="C256" s="89" t="n"/>
-      <c r="E256" s="84" t="inlineStr">
+      <c r="C256" s="129" t="n"/>
+      <c r="D256" s="113" t="inlineStr">
         <is>
           <t>IDR/kg</t>
         </is>
       </c>
-      <c r="F256" s="84" t="inlineStr">
+      <c r="E256" s="113" t="inlineStr">
         <is>
           <t>EMPTY: waiting for price</t>
         </is>
       </c>
+      <c r="F256" s="95" t="n"/>
+      <c r="G256" s="95" t="n"/>
+      <c r="H256" s="95" t="n"/>
+      <c r="I256" s="95" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="84" t="inlineStr">
+      <c r="A257" s="113" t="inlineStr">
         <is>
           <t>metal_steel</t>
         </is>
       </c>
-      <c r="B257" s="84" t="inlineStr">
+      <c r="B257" s="117" t="inlineStr">
         <is>
           <t>Steel / hollow section, per kg (reference)</t>
         </is>
       </c>
-      <c r="C257" s="89" t="n"/>
-      <c r="E257" s="84" t="inlineStr">
+      <c r="C257" s="129" t="n"/>
+      <c r="D257" s="113" t="inlineStr">
         <is>
           <t>IDR/kg</t>
         </is>
       </c>
-      <c r="F257" s="84" t="inlineStr">
+      <c r="E257" s="113" t="inlineStr">
         <is>
           <t>EMPTY: waiting for price</t>
         </is>
       </c>
+      <c r="F257" s="95" t="n"/>
+      <c r="G257" s="95" t="n"/>
+      <c r="H257" s="95" t="n"/>
+      <c r="I257" s="95" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -11790,7 +11790,7 @@
       </c>
       <c r="E59" s="96" t="inlineStr">
         <is>
-          <t>Mojo Indah list, Sep 2026</t>
+          <t>E2 landed Kudus (Linyi quote 16 Oct 2026). Grade LOCKED E2</t>
         </is>
       </c>
       <c r="F59" s="112">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="E64" s="96" t="inlineStr">
         <is>
-          <t>Mojo Indah list, Sep 2026</t>
+          <t>E2 landed Kudus (Linyi quote 16 Oct 2026). Grade LOCKED E2</t>
         </is>
       </c>
       <c r="F64" s="112">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="E69" s="96" t="inlineStr">
         <is>
-          <t>Mojo Indah list, Sep 2026</t>
+          <t>E2 landed Kudus (Linyi quote 16 Oct 2026). Grade LOCKED E2</t>
         </is>
       </c>
       <c r="F69" s="112">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="E74" s="96" t="inlineStr">
         <is>
-          <t>Mojo Indah list, Sep 2026</t>
+          <t>E2 landed Kudus (Linyi quote 16 Oct 2026). Grade LOCKED E2</t>
         </is>
       </c>
       <c r="F74" s="112">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E79" s="96" t="inlineStr">
         <is>
-          <t>Mojo Indah list, Sep 2026</t>
+          <t>E2 landed Kudus (Linyi quote 16 Oct 2026). Grade LOCKED E2</t>
         </is>
       </c>
       <c r="F79" s="112">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="E84" s="96" t="inlineStr">
         <is>
-          <t>Mojo Indah list, Sep 2026</t>
+          <t>E2 landed Kudus (Linyi quote 16 Oct 2026). Grade LOCKED E2</t>
         </is>
       </c>
       <c r="F84" s="112">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="B174" s="117" t="inlineStr">
         <is>
-          <t>Board grade feeding the PLY-x and MDF-x rates (type E2, E0 or CARB)</t>
+          <t>Board grade for ALL plywood and MDF (LOCKED E2, rule 19 Oct 2026). Do not change.</t>
         </is>
       </c>
       <c r="C174" s="118" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="E174" s="113" t="inlineStr">
         <is>
-          <t>CARB Phase 2 / TSCA Title VI: required for US hotel projects, accepted for EU</t>
+          <t>Rule: plywood (B group) and MDF (C group) always E2, landed Kudus. E0 / CARB rows are reference only.</t>
         </is>
       </c>
       <c r="F174" s="95" t="n"/>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -17407,7 +17407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="59" min="1" max="2"/>
@@ -17465,7 +17465,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PLY-3-RAW</t>
+          <t>LND-PLY-E2-3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PLY-3-MSF</t>
+          <t>LND-PLY-E2-6</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PLY-3-MDF</t>
+          <t>LND-PLY-E2-9</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PLY-3-TSF</t>
+          <t>LND-PLY-E2-12</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -17570,7 +17570,7 @@
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>PLY-3-TDF</t>
+          <t>LND-PLY-E2-15</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -17590,7 +17590,7 @@
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PLY-6-RAW</t>
+          <t>LND-PLY-E2-18</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -17605,7 +17605,7 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>PLY-6-MSF</t>
+          <t>LND-MDF-E2-3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -17620,7 +17620,7 @@
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PLY-6-MDF</t>
+          <t>LND-MDF-E2-6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -17635,7 +17635,7 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PLY-6-TSF</t>
+          <t>LND-MDF-E2-9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -17650,184 +17650,164 @@
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PLY-6-TDF</t>
+          <t>LND-MDF-E2-12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PLY-9-RAW</t>
+          <t>LND-MDF-E2-15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PLY-9-MSF</t>
+          <t>LND-MDF-E2-18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PLY-9-MDF</t>
+          <t>LND-PLY-E2-18-MSF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PLY-9-TSF</t>
+          <t>LND-PLY-E2-18-MDF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PLY-9-TDF</t>
+          <t>LND-PLY-E2-15-MSF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PLY-12-RAW</t>
+          <t>LND-PLY-E2-15-MDF</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PLY-12-MSF</t>
+          <t>LND-PLY-E2-12-MSF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PLY-12-MDF</t>
+          <t>LND-PLY-E2-12-MDF</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="59">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>PLY-12-TSF</t>
+          <t>LND-PLY-E2-9-MSF</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="59">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PLY-12-TDF</t>
+          <t>LND-PLY-E2-9-MDF</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="59">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PLY-15-RAW</t>
+          <t>LND-PLY-E2-6-MSF</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="59">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PLY-15-MSF</t>
+          <t>LND-PLY-E2-6-MDF</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="59">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PLY-15-MDF</t>
+          <t>LND-PLY-E2-3-MSF</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="59">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PLY-15-TSF</t>
+          <t>LND-PLY-E2-3-MDF</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="59">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>PLY-15-TDF</t>
+          <t>LND-MDF-E2-18-MSF</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="59">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>PLY-18-RAW</t>
+          <t>LND-MDF-E2-18-MDF</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="59">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>PLY-18-MSF</t>
+          <t>LND-MDF-E2-15-MSF</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="59">
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>PLY-18-MDF</t>
+          <t>LND-MDF-E2-12-MSF</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="59">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>PLY-18-TSF</t>
+          <t>LND-MDF-E2-9-MSF</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="59">
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>PLY-18-TDF</t>
+          <t>LND-MDF-E2-6-MSF</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="59">
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>PLY-24-RAW</t>
-        </is>
-      </c>
+      <c r="B33" s="2" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="59">
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>PLY-24-MSF</t>
-        </is>
-      </c>
+      <c r="B34" s="2" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="59">
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>PLY-24-MDF</t>
-        </is>
-      </c>
+      <c r="B35" s="2" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="59">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>PLY-24-TSF</t>
-        </is>
-      </c>
+      <c r="B36" s="2" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="59">
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>PLY-24-TDF</t>
-        </is>
-      </c>
+      <c r="B37" s="2" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="59"/>
     <row r="39" ht="15.75" customHeight="1" s="59"/>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -642,6 +642,20 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C2B00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7A0"/>
+          <bgColor rgb="00FFC7A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -10185,6 +10199,21 @@
     <mergeCell ref="L76:R76"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
+  <conditionalFormatting sqref="S18:T42">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>AND($E18&lt;&gt;"",OR(S18="",S18=0,S18="rate?"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S46:T60">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND($E46&lt;&gt;"",OR(S46="",S46=0,S46="rate?"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S64:T78">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
+      <formula>AND($D64&lt;&gt;"",OR(S64="",S64=0))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation sqref="K18:K42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,A-CURVED,B,C,D"</formula1>
@@ -14605,7 +14634,6 @@
       <c r="H168" s="95" t="n"/>
       <c r="I168" s="95" t="n"/>
     </row>
-    <row r="169"/>
     <row r="170">
       <c r="A170" s="97" t="inlineStr">
         <is>
@@ -14815,7 +14843,6 @@
       <c r="H176" s="95" t="n"/>
       <c r="I176" s="95" t="n"/>
     </row>
-    <row r="177"/>
     <row r="178">
       <c r="A178" s="119" t="inlineStr">
         <is>
@@ -16336,7 +16363,6 @@
         <v>933</v>
       </c>
     </row>
-    <row r="216"/>
     <row r="217">
       <c r="A217" s="97" t="inlineStr">
         <is>
@@ -16640,7 +16666,6 @@
       <c r="H225" s="95" t="n"/>
       <c r="I225" s="95" t="n"/>
     </row>
-    <row r="226"/>
     <row r="227">
       <c r="A227" s="97" t="inlineStr">
         <is>
@@ -16734,7 +16759,6 @@
       <c r="H229" s="95" t="n"/>
       <c r="I229" s="95" t="n"/>
     </row>
-    <row r="230"/>
     <row r="231">
       <c r="A231" s="127" t="inlineStr">
         <is>
@@ -17218,7 +17242,6 @@
       <c r="H249" s="95" t="n"/>
       <c r="I249" s="95" t="n"/>
     </row>
-    <row r="250"/>
     <row r="251">
       <c r="A251" s="127" t="inlineStr">
         <is>
@@ -17397,6 +17420,11 @@
       <c r="I257" s="95" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C5:C400">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>AND($A5&lt;&gt;"",$A5&lt;&gt;"code",$B5&lt;&gt;"",$C5="")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17407,7 +17435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="59" min="1" max="2"/>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -10239,7 +10239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I257"/>
+  <dimension ref="A1:I260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="59" min="1" max="1"/>
@@ -14634,6 +14634,7 @@
       <c r="H168" s="95" t="n"/>
       <c r="I168" s="95" t="n"/>
     </row>
+    <row r="169"/>
     <row r="170">
       <c r="A170" s="97" t="inlineStr">
         <is>
@@ -14843,6 +14844,7 @@
       <c r="H176" s="95" t="n"/>
       <c r="I176" s="95" t="n"/>
     </row>
+    <row r="177"/>
     <row r="178">
       <c r="A178" s="119" t="inlineStr">
         <is>
@@ -16363,6 +16365,7 @@
         <v>933</v>
       </c>
     </row>
+    <row r="216"/>
     <row r="217">
       <c r="A217" s="97" t="inlineStr">
         <is>
@@ -16666,6 +16669,7 @@
       <c r="H225" s="95" t="n"/>
       <c r="I225" s="95" t="n"/>
     </row>
+    <row r="226"/>
     <row r="227">
       <c r="A227" s="97" t="inlineStr">
         <is>
@@ -16759,6 +16763,7 @@
       <c r="H229" s="95" t="n"/>
       <c r="I229" s="95" t="n"/>
     </row>
+    <row r="230"/>
     <row r="231">
       <c r="A231" s="127" t="inlineStr">
         <is>
@@ -17242,6 +17247,7 @@
       <c r="H249" s="95" t="n"/>
       <c r="I249" s="95" t="n"/>
     </row>
+    <row r="250"/>
     <row r="251">
       <c r="A251" s="127" t="inlineStr">
         <is>
@@ -17418,6 +17424,41 @@
       <c r="G257" s="95" t="n"/>
       <c r="H257" s="95" t="n"/>
       <c r="I257" s="95" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="127" t="inlineStr">
+        <is>
+          <t>CURVES (added 19 Oct 2026). Rounded corners R30/R40: tier A-CURVED, blank = finished + arc + tolerance. Value EMPTY until factory gives the tolerance.</t>
+        </is>
+      </c>
+      <c r="B259" s="98" t="n"/>
+      <c r="C259" s="98" t="n"/>
+      <c r="D259" s="98" t="n"/>
+      <c r="E259" s="98" t="n"/>
+      <c r="F259" s="98" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="113" t="inlineStr">
+        <is>
+          <t>CURVE_ALLOW</t>
+        </is>
+      </c>
+      <c r="B260" s="117" t="inlineStr">
+        <is>
+          <t>Tolerance added to length and width of a curved part (arc is computed from the radius)</t>
+        </is>
+      </c>
+      <c r="C260" s="129" t="n"/>
+      <c r="D260" s="113" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E260" s="113" t="inlineStr">
+        <is>
+          <t>EMPTY: waiting for factory figure</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C400">

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -10239,7 +10239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I260"/>
+  <dimension ref="A1:I315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="59" min="1" max="1"/>
@@ -14797,8 +14797,9 @@
           <t>Mindi veneer added per face inside the PLY-x-MSF / MDF rates</t>
         </is>
       </c>
-      <c r="C175" s="114" t="n">
-        <v>147709.02</v>
+      <c r="C175" s="114">
+        <f>C275</f>
+        <v/>
       </c>
       <c r="D175" s="113" t="inlineStr">
         <is>
@@ -14807,7 +14808,7 @@
       </c>
       <c r="E175" s="113" t="inlineStr">
         <is>
-          <t>Back-calculated from the 29 Sep rate card (PLY-x-MSF minus PLY-x-RAW). Not the same as VEN_MINDI_FACE.</t>
+          <t>Now a formula: 0.6 mm face from the VENEER block below (was fixed 147,709).</t>
         </is>
       </c>
       <c r="F175" s="95" t="n"/>
@@ -17425,6 +17426,7 @@
       <c r="H257" s="95" t="n"/>
       <c r="I257" s="95" t="n"/>
     </row>
+    <row r="258"/>
     <row r="259">
       <c r="A259" s="127" t="inlineStr">
         <is>
@@ -17459,6 +17461,1386 @@
           <t>EMPTY: waiting for factory figure</t>
         </is>
       </c>
+    </row>
+    <row r="261"/>
+    <row r="262">
+      <c r="A262" s="127" t="inlineStr">
+        <is>
+          <t>VENEER (added 19 Oct 2026). Face veneer cost is built from log price, slicing yield and vendor fee, for 0.6 / 1.0 / 1.2 mm. Default board codes (-MSF, -MDF) use 0.6 mm. Add -V10 or -V12 to the code for 1.0 or 1.2 mm.</t>
+        </is>
+      </c>
+      <c r="B262" s="98" t="n"/>
+      <c r="C262" s="98" t="n"/>
+      <c r="D262" s="98" t="n"/>
+      <c r="E262" s="98" t="n"/>
+      <c r="F262" s="98" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="113" t="inlineStr">
+        <is>
+          <t>VEN_LOG_PRICE</t>
+        </is>
+      </c>
+      <c r="B263" s="117" t="inlineStr">
+        <is>
+          <t>Mindi log price for veneer</t>
+        </is>
+      </c>
+      <c r="C263" s="129" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="D263" s="113" t="inlineStr">
+        <is>
+          <t>IDR/m³</t>
+        </is>
+      </c>
+      <c r="E263" s="113" t="inlineStr">
+        <is>
+          <t>Update 19 Oct 2026. Status CONFIRM (log_mindi in this card is 3,000,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="113" t="inlineStr">
+        <is>
+          <t>VEN_SLICE_YIELD</t>
+        </is>
+      </c>
+      <c r="B264" s="117" t="inlineStr">
+        <is>
+          <t>Slicing yield quoted by the veneer vendor</t>
+        </is>
+      </c>
+      <c r="C264" s="129" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D264" s="113" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E264" s="113" t="inlineStr">
+        <is>
+          <t>Vendor, mindi / mahogany. Status CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="113" t="inlineStr">
+        <is>
+          <t>VEN_FLITCH_W</t>
+        </is>
+      </c>
+      <c r="B265" s="117" t="inlineStr">
+        <is>
+          <t>Flitch width before trimming</t>
+        </is>
+      </c>
+      <c r="C265" s="129" t="n">
+        <v>160</v>
+      </c>
+      <c r="D265" s="113" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E265" s="113" t="inlineStr">
+        <is>
+          <t>Vendor flitch 2.5 m long</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="113" t="inlineStr">
+        <is>
+          <t>VEN_TRIM_W</t>
+        </is>
+      </c>
+      <c r="B266" s="117" t="inlineStr">
+        <is>
+          <t>Flitch width after trimming</t>
+        </is>
+      </c>
+      <c r="C266" s="129" t="n">
+        <v>150</v>
+      </c>
+      <c r="D266" s="113" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E266" s="113" t="inlineStr">
+        <is>
+          <t>Vendor flitch 2.5 m long</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="113" t="inlineStr">
+        <is>
+          <t>VEN_YIELD_EFF</t>
+        </is>
+      </c>
+      <c r="B267" s="117" t="inlineStr">
+        <is>
+          <t>Effective yield = slicing yield x trim width / flitch width</t>
+        </is>
+      </c>
+      <c r="C267" s="129">
+        <f>C264*C266/C265</f>
+        <v/>
+      </c>
+      <c r="D267" s="113" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E267" s="113" t="inlineStr">
+        <is>
+          <t>Formula (28.125% with the figures above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="113" t="inlineStr">
+        <is>
+          <t>VEN_SLICE_FEE</t>
+        </is>
+      </c>
+      <c r="B268" s="117" t="inlineStr">
+        <is>
+          <t>Slicing fee, per m2 of usable veneer</t>
+        </is>
+      </c>
+      <c r="C268" s="129" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D268" s="113" t="inlineStr">
+        <is>
+          <t>IDR/m²</t>
+        </is>
+      </c>
+      <c r="E268" s="113" t="inlineStr">
+        <is>
+          <t>Vendor. Matches market 0.6 mm at 18-20 ribu. Status CONFIRM (assumed billed on usable m2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="113" t="inlineStr">
+        <is>
+          <t>VEN_T_06</t>
+        </is>
+      </c>
+      <c r="B269" s="117" t="inlineStr">
+        <is>
+          <t>Veneer thickness 0.6 mm</t>
+        </is>
+      </c>
+      <c r="C269" s="129" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D269" s="113" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E269" s="113" t="inlineStr">
+        <is>
+          <t>Industry sliced thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="113" t="inlineStr">
+        <is>
+          <t>VEN_T_10</t>
+        </is>
+      </c>
+      <c r="B270" s="117" t="inlineStr">
+        <is>
+          <t>Veneer thickness 1.0 mm</t>
+        </is>
+      </c>
+      <c r="C270" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" s="113" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E270" s="113" t="inlineStr">
+        <is>
+          <t>Industry sliced thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="113" t="inlineStr">
+        <is>
+          <t>VEN_T_12</t>
+        </is>
+      </c>
+      <c r="B271" s="117" t="inlineStr">
+        <is>
+          <t>Veneer thickness 1.2 mm</t>
+        </is>
+      </c>
+      <c r="C271" s="129" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D271" s="113" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E271" s="113" t="inlineStr">
+        <is>
+          <t>Industry sliced thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="113" t="inlineStr">
+        <is>
+          <t>VEN_M2_06</t>
+        </is>
+      </c>
+      <c r="B272" s="117" t="inlineStr">
+        <is>
+          <t>Veneer cost per m2 usable, 0.6 mm (wood + slicing fee)</t>
+        </is>
+      </c>
+      <c r="C272" s="129">
+        <f>C263*C269/1000/C267+C268</f>
+        <v/>
+      </c>
+      <c r="D272" s="113" t="inlineStr">
+        <is>
+          <t>IDR/m²</t>
+        </is>
+      </c>
+      <c r="E272" s="113" t="inlineStr">
+        <is>
+          <t>Formula: log price x thickness / effective yield + fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="113" t="inlineStr">
+        <is>
+          <t>VEN_M2_10</t>
+        </is>
+      </c>
+      <c r="B273" s="117" t="inlineStr">
+        <is>
+          <t>Veneer cost per m2 usable, 1.0 mm (wood + slicing fee)</t>
+        </is>
+      </c>
+      <c r="C273" s="129">
+        <f>C263*C270/1000/C267+C268</f>
+        <v/>
+      </c>
+      <c r="D273" s="113" t="inlineStr">
+        <is>
+          <t>IDR/m²</t>
+        </is>
+      </c>
+      <c r="E273" s="113" t="inlineStr">
+        <is>
+          <t>Formula: log price x thickness / effective yield + fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="113" t="inlineStr">
+        <is>
+          <t>VEN_M2_12</t>
+        </is>
+      </c>
+      <c r="B274" s="117" t="inlineStr">
+        <is>
+          <t>Veneer cost per m2 usable, 1.2 mm (wood + slicing fee)</t>
+        </is>
+      </c>
+      <c r="C274" s="129">
+        <f>C263*C271/1000/C267+C268</f>
+        <v/>
+      </c>
+      <c r="D274" s="113" t="inlineStr">
+        <is>
+          <t>IDR/m²</t>
+        </is>
+      </c>
+      <c r="E274" s="113" t="inlineStr">
+        <is>
+          <t>Formula: log price x thickness / effective yield + fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="113" t="inlineStr">
+        <is>
+          <t>VEN_FACE_06</t>
+        </is>
+      </c>
+      <c r="B275" s="117" t="inlineStr">
+        <is>
+          <t>Veneer added per board face, 0.6 mm (veneer + glue/tape on a full sheet + pressing labour)</t>
+        </is>
+      </c>
+      <c r="C275" s="129">
+        <f>(C272+$C$28)*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
+        <v/>
+      </c>
+      <c r="D275" s="113" t="inlineStr">
+        <is>
+          <t>IDR/face</t>
+        </is>
+      </c>
+      <c r="E275" s="113" t="inlineStr">
+        <is>
+          <t>Formula: (veneer m2 + glue_tape) x sheet area + ven_labour</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="113" t="inlineStr">
+        <is>
+          <t>VEN_FACE_10</t>
+        </is>
+      </c>
+      <c r="B276" s="117" t="inlineStr">
+        <is>
+          <t>Veneer added per board face, 1.0 mm (veneer + glue/tape on a full sheet + pressing labour)</t>
+        </is>
+      </c>
+      <c r="C276" s="129">
+        <f>(C273+$C$28)*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
+        <v/>
+      </c>
+      <c r="D276" s="113" t="inlineStr">
+        <is>
+          <t>IDR/face</t>
+        </is>
+      </c>
+      <c r="E276" s="113" t="inlineStr">
+        <is>
+          <t>Formula: (veneer m2 + glue_tape) x sheet area + ven_labour</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="113" t="inlineStr">
+        <is>
+          <t>VEN_FACE_12</t>
+        </is>
+      </c>
+      <c r="B277" s="117" t="inlineStr">
+        <is>
+          <t>Veneer added per board face, 1.2 mm (veneer + glue/tape on a full sheet + pressing labour)</t>
+        </is>
+      </c>
+      <c r="C277" s="129">
+        <f>(C274+$C$28)*(LISTS!$F$6*LISTS!$F$7/1000000)+$C$32</f>
+        <v/>
+      </c>
+      <c r="D277" s="113" t="inlineStr">
+        <is>
+          <t>IDR/face</t>
+        </is>
+      </c>
+      <c r="E277" s="113" t="inlineStr">
+        <is>
+          <t>Formula: (veneer m2 + glue_tape) x sheet area + ven_labour</t>
+        </is>
+      </c>
+    </row>
+    <row r="278"/>
+    <row r="279">
+      <c r="A279" s="127" t="inlineStr">
+        <is>
+          <t>VENEERED BOARDS 1.0 / 1.2 mm (code + -V10 or -V12). Equals the default board code + number of faces x (face cost of that thickness - 0.6 mm face).</t>
+        </is>
+      </c>
+      <c r="B279" s="98" t="n"/>
+      <c r="C279" s="98" t="n"/>
+      <c r="D279" s="98" t="n"/>
+      <c r="E279" s="98" t="n"/>
+      <c r="F279" s="98" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B280" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 18 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C280" s="128">
+        <f>C232+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D280" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E280" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F280" s="95" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B281" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 18 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C281" s="128">
+        <f>C232+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D281" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E281" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F281" s="95" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B282" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 18 mm, Mindi double face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C282" s="128">
+        <f>C233+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D282" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E282" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F282" s="95" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B283" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 18 mm, Mindi double face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C283" s="128">
+        <f>C233+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D283" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E283" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F283" s="95" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B284" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 15 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C284" s="128">
+        <f>C234+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D284" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E284" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F284" s="95" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B285" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 15 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C285" s="128">
+        <f>C234+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D285" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E285" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F285" s="95" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B286" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 15 mm, Mindi double face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C286" s="128">
+        <f>C235+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D286" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E286" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F286" s="95" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B287" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 15 mm, Mindi double face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C287" s="128">
+        <f>C235+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D287" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E287" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F287" s="95" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B288" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 12 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C288" s="128">
+        <f>C236+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D288" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E288" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F288" s="95" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B289" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 12 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C289" s="128">
+        <f>C236+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D289" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E289" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F289" s="95" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B290" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 12 mm, Mindi double face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C290" s="128">
+        <f>C237+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D290" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E290" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F290" s="95" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B291" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 12 mm, Mindi double face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C291" s="128">
+        <f>C237+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D291" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E291" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F291" s="95" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B292" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 9 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C292" s="128">
+        <f>C238+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D292" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E292" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F292" s="95" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B293" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 9 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C293" s="128">
+        <f>C238+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D293" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E293" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F293" s="95" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B294" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 9 mm, Mindi double face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C294" s="128">
+        <f>C239+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D294" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E294" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F294" s="95" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B295" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 9 mm, Mindi double face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C295" s="128">
+        <f>C239+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D295" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E295" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F295" s="95" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B296" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 6 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C296" s="128">
+        <f>C240+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D296" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E296" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F296" s="95" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B297" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 6 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C297" s="128">
+        <f>C240+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D297" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E297" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F297" s="95" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B298" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 6 mm, Mindi double face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C298" s="128">
+        <f>C241+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D298" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E298" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F298" s="95" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B299" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 6 mm, Mindi double face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C299" s="128">
+        <f>C241+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D299" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E299" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F299" s="95" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B300" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 3 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C300" s="128">
+        <f>C242+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D300" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E300" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F300" s="95" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B301" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 3 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C301" s="128">
+        <f>C242+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D301" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E301" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F301" s="95" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B302" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 3 mm, Mindi double face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C302" s="128">
+        <f>C243+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D302" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E302" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F302" s="95" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B303" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E2 3 mm, Mindi double face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C303" s="128">
+        <f>C243+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D303" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E303" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F303" s="95" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B304" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 18 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C304" s="128">
+        <f>C244+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D304" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E304" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F304" s="95" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B305" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 18 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C305" s="128">
+        <f>C244+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D305" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E305" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F305" s="95" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B306" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 18 mm, Mindi double face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C306" s="128">
+        <f>C245+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D306" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E306" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F306" s="95" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B307" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 18 mm, Mindi double face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C307" s="128">
+        <f>C245+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D307" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E307" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F307" s="95" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-15-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B308" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 15 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C308" s="128">
+        <f>C246+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D308" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E308" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F308" s="95" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-15-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B309" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 15 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C309" s="128">
+        <f>C246+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D309" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E309" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F309" s="95" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-12-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B310" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 12 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C310" s="128">
+        <f>C247+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D310" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E310" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F310" s="95" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-12-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B311" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 12 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C311" s="128">
+        <f>C247+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D311" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E311" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F311" s="95" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-9-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B312" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 9 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C312" s="128">
+        <f>C248+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D312" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E312" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F312" s="95" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-9-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B313" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 9 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C313" s="128">
+        <f>C248+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D313" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E313" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F313" s="95" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-6-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B314" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 6 mm, Mindi single face (1.0 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C314" s="128">
+        <f>C249+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D314" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E314" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F314" s="95" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-6-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B315" s="93" t="inlineStr">
+        <is>
+          <t>MDF E2 6 mm, Mindi single face (1.2 mm veneer)</t>
+        </is>
+      </c>
+      <c r="C315" s="128">
+        <f>C249+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D315" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E315" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F315" s="95" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C400">
@@ -17476,7 +18858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="59" min="1" max="2"/>
@@ -17864,51 +19246,257 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="59">
-      <c r="B33" s="2" t="n"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MSF-V10</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="59">
-      <c r="B34" s="2" t="n"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MSF-V12</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="59">
-      <c r="B35" s="2" t="n"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MDF-V10</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="59">
-      <c r="B36" s="2" t="n"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-18-MDF-V12</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="59">
-      <c r="B37" s="2" t="n"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1" s="59"/>
-    <row r="39" ht="15.75" customHeight="1" s="59"/>
-    <row r="40" ht="15.75" customHeight="1" s="59"/>
-    <row r="41" ht="15.75" customHeight="1" s="59"/>
-    <row r="42" ht="15.75" customHeight="1" s="59"/>
-    <row r="43" ht="15.75" customHeight="1" s="59"/>
-    <row r="44" ht="15.75" customHeight="1" s="59"/>
-    <row r="45" ht="15.75" customHeight="1" s="59"/>
-    <row r="46" ht="15.75" customHeight="1" s="59"/>
-    <row r="47" ht="15.75" customHeight="1" s="59"/>
-    <row r="48" ht="15.75" customHeight="1" s="59"/>
-    <row r="49" ht="15.75" customHeight="1" s="59"/>
-    <row r="50" ht="15.75" customHeight="1" s="59"/>
-    <row r="51" ht="15.75" customHeight="1" s="59"/>
-    <row r="52" ht="15.75" customHeight="1" s="59"/>
-    <row r="53" ht="15.75" customHeight="1" s="59"/>
-    <row r="54" ht="15.75" customHeight="1" s="59"/>
-    <row r="55" ht="15.75" customHeight="1" s="59"/>
-    <row r="56" ht="15.75" customHeight="1" s="59"/>
-    <row r="57" ht="15.75" customHeight="1" s="59"/>
-    <row r="58" ht="15.75" customHeight="1" s="59"/>
-    <row r="59" ht="15.75" customHeight="1" s="59"/>
-    <row r="60" ht="15.75" customHeight="1" s="59"/>
-    <row r="61" ht="15.75" customHeight="1" s="59"/>
-    <row r="62" ht="15.75" customHeight="1" s="59"/>
-    <row r="63" ht="15.75" customHeight="1" s="59"/>
-    <row r="64" ht="15.75" customHeight="1" s="59"/>
-    <row r="65" ht="15.75" customHeight="1" s="59"/>
-    <row r="66" ht="15.75" customHeight="1" s="59"/>
-    <row r="67" ht="15.75" customHeight="1" s="59"/>
-    <row r="68" ht="15.75" customHeight="1" s="59"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="59">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="59">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MDF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="59">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-15-MDF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="59">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="59">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="59">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MDF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="59">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-12-MDF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="59">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" s="59">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="59">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MDF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1" s="59">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-9-MDF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" s="59">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" s="59">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1" s="59">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MDF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1" s="59">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-6-MDF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" s="59">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" s="59">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" s="59">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MDF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="59">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LND-PLY-E2-3-MDF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="59">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" s="59">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1" s="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MDF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" s="59">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-18-MDF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" s="59">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-15-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" s="59">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-15-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" s="59">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-12-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1" s="59">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-12-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1" s="59">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-9-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" s="59">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-9-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" s="59">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-6-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" s="59">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LND-MDF-E2-6-MSF-V12</t>
+        </is>
+      </c>
+    </row>
     <row r="69" ht="15.75" customHeight="1" s="59"/>
     <row r="70" ht="15.75" customHeight="1" s="59"/>
     <row r="71" ht="15.75" customHeight="1" s="59"/>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -10239,7 +10239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I315"/>
+  <dimension ref="A1:I389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="59" min="1" max="1"/>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="B174" s="117" t="inlineStr">
         <is>
-          <t>Board grade for ALL plywood and MDF (LOCKED E2, rule 19 Oct 2026). Do not change.</t>
+          <t>Board grade for ALL plywood and MDF (LOCKED E0, meeting rule 19 Oct 2026). Replaces E2.</t>
         </is>
       </c>
       <c r="C174" s="118" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="D174" s="113" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="E174" s="113" t="inlineStr">
         <is>
-          <t>Rule: plywood (B group) and MDF (C group) always E2, landed Kudus. E0 / CARB rows are reference only.</t>
+          <t>Rule: plywood and MDF always E0, landed Kudus. E2 / CARB rows are reference only.</t>
         </is>
       </c>
       <c r="F174" s="95" t="n"/>
@@ -18841,6 +18841,1963 @@
         </is>
       </c>
       <c r="F315" s="95" t="n"/>
+    </row>
+    <row r="316"/>
+    <row r="317">
+      <c r="A317" s="127" t="inlineStr">
+        <is>
+          <t>E0 BOARDS (rule 19 Oct 2026, meeting): ALL plywood and MDF use grade E0. Veneered E0 boards = raw E0 landed board + faces x veneer face cost (0.6 mm default; -V10 / -V12 for 1.0 / 1.2 mm).</t>
+        </is>
+      </c>
+      <c r="B317" s="98" t="n"/>
+      <c r="C317" s="98" t="n"/>
+      <c r="D317" s="98" t="n"/>
+      <c r="E317" s="98" t="n"/>
+      <c r="F317" s="98" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-3-MSF</t>
+        </is>
+      </c>
+      <c r="B318" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 3 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C318" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-3",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D318" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E318" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F318" s="95" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-3-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B319" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 3 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C319" s="128">
+        <f>C318+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D319" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E319" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F319" s="95" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-3-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B320" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 3 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C320" s="128">
+        <f>C318+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D320" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E320" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F320" s="95" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-3-MDF</t>
+        </is>
+      </c>
+      <c r="B321" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 3 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C321" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-3",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D321" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E321" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F321" s="95" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-3-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B322" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 3 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C322" s="128">
+        <f>C321+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D322" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E322" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F322" s="95" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-3-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B323" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 3 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C323" s="128">
+        <f>C321+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D323" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E323" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F323" s="95" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-6-MSF</t>
+        </is>
+      </c>
+      <c r="B324" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 6 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C324" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-6",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D324" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E324" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F324" s="95" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-6-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B325" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 6 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C325" s="128">
+        <f>C324+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D325" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E325" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F325" s="95" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-6-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B326" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 6 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C326" s="128">
+        <f>C324+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D326" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E326" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F326" s="95" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-6-MDF</t>
+        </is>
+      </c>
+      <c r="B327" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 6 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C327" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-6",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D327" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E327" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F327" s="95" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-6-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B328" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 6 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C328" s="128">
+        <f>C327+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D328" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E328" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F328" s="95" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-6-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B329" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 6 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C329" s="128">
+        <f>C327+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D329" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E329" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F329" s="95" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-9-MSF</t>
+        </is>
+      </c>
+      <c r="B330" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 9 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C330" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-9",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D330" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E330" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F330" s="95" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-9-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B331" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 9 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C331" s="128">
+        <f>C330+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D331" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E331" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F331" s="95" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-9-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B332" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 9 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C332" s="128">
+        <f>C330+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D332" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E332" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F332" s="95" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-9-MDF</t>
+        </is>
+      </c>
+      <c r="B333" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 9 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C333" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-9",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D333" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E333" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F333" s="95" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-9-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B334" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 9 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C334" s="128">
+        <f>C333+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D334" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E334" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F334" s="95" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-9-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B335" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 9 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C335" s="128">
+        <f>C333+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D335" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E335" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F335" s="95" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-12-MSF</t>
+        </is>
+      </c>
+      <c r="B336" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 12 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C336" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-12",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D336" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E336" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F336" s="95" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-12-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B337" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 12 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C337" s="128">
+        <f>C336+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D337" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E337" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F337" s="95" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-12-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B338" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 12 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C338" s="128">
+        <f>C336+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D338" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E338" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F338" s="95" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-12-MDF</t>
+        </is>
+      </c>
+      <c r="B339" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 12 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C339" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-12",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D339" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E339" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F339" s="95" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-12-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B340" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 12 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C340" s="128">
+        <f>C339+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D340" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E340" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F340" s="95" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-12-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B341" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 12 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C341" s="128">
+        <f>C339+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D341" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E341" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F341" s="95" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-15-MSF</t>
+        </is>
+      </c>
+      <c r="B342" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 15 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C342" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-15",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D342" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E342" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F342" s="95" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-15-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B343" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 15 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C343" s="128">
+        <f>C342+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D343" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E343" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F343" s="95" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-15-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B344" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 15 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C344" s="128">
+        <f>C342+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D344" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E344" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F344" s="95" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-15-MDF</t>
+        </is>
+      </c>
+      <c r="B345" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 15 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C345" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-15",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D345" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E345" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F345" s="95" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-15-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B346" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 15 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C346" s="128">
+        <f>C345+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D346" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E346" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F346" s="95" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-15-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B347" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 15 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C347" s="128">
+        <f>C345+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D347" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E347" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F347" s="95" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-18-MSF</t>
+        </is>
+      </c>
+      <c r="B348" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 18 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C348" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-18",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D348" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E348" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F348" s="95" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-18-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B349" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 18 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C349" s="128">
+        <f>C348+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D349" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E349" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F349" s="95" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-18-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B350" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 18 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C350" s="128">
+        <f>C348+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D350" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E350" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F350" s="95" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-18-MDF</t>
+        </is>
+      </c>
+      <c r="B351" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 18 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C351" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-PLY-E0-18",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D351" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E351" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F351" s="95" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-18-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B352" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 18 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C352" s="128">
+        <f>C351+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D352" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E352" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F352" s="95" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="95" t="inlineStr">
+        <is>
+          <t>LND-PLY-E0-18-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B353" s="93" t="inlineStr">
+        <is>
+          <t>Plywood E0 18 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C353" s="128">
+        <f>C351+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D353" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E353" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F353" s="95" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-3-MSF</t>
+        </is>
+      </c>
+      <c r="B354" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 3 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C354" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-3",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D354" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E354" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F354" s="95" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-3-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B355" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 3 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C355" s="128">
+        <f>C354+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D355" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E355" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F355" s="95" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-3-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B356" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 3 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C356" s="128">
+        <f>C354+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D356" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E356" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F356" s="95" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-3-MDF</t>
+        </is>
+      </c>
+      <c r="B357" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 3 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C357" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-3",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D357" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E357" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F357" s="95" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-3-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B358" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 3 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C358" s="128">
+        <f>C357+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D358" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E358" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F358" s="95" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-3-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B359" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 3 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C359" s="128">
+        <f>C357+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D359" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E359" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F359" s="95" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-6-MSF</t>
+        </is>
+      </c>
+      <c r="B360" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 6 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C360" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-6",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D360" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E360" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F360" s="95" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-6-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B361" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 6 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C361" s="128">
+        <f>C360+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D361" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E361" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F361" s="95" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-6-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B362" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 6 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C362" s="128">
+        <f>C360+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D362" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E362" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F362" s="95" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-6-MDF</t>
+        </is>
+      </c>
+      <c r="B363" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 6 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C363" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-6",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D363" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E363" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F363" s="95" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-6-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B364" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 6 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C364" s="128">
+        <f>C363+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D364" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E364" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F364" s="95" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-6-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B365" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 6 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C365" s="128">
+        <f>C363+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D365" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E365" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F365" s="95" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-9-MSF</t>
+        </is>
+      </c>
+      <c r="B366" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 9 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C366" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-9",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D366" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E366" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F366" s="95" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-9-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B367" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 9 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C367" s="128">
+        <f>C366+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D367" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E367" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F367" s="95" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-9-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B368" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 9 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C368" s="128">
+        <f>C366+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D368" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E368" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F368" s="95" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-9-MDF</t>
+        </is>
+      </c>
+      <c r="B369" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 9 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C369" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-9",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D369" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E369" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F369" s="95" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-9-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B370" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 9 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C370" s="128">
+        <f>C369+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D370" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E370" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F370" s="95" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-9-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B371" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 9 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C371" s="128">
+        <f>C369+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D371" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E371" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F371" s="95" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MSF</t>
+        </is>
+      </c>
+      <c r="B372" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 12 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C372" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-12",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D372" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E372" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F372" s="95" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B373" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 12 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C373" s="128">
+        <f>C372+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D373" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E373" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F373" s="95" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B374" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 12 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C374" s="128">
+        <f>C372+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D374" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E374" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F374" s="95" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MDF</t>
+        </is>
+      </c>
+      <c r="B375" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 12 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C375" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-12",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D375" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E375" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F375" s="95" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B376" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 12 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C376" s="128">
+        <f>C375+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D376" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E376" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F376" s="95" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B377" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 12 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C377" s="128">
+        <f>C375+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D377" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E377" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F377" s="95" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MSF</t>
+        </is>
+      </c>
+      <c r="B378" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 15 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C378" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-15",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D378" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E378" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F378" s="95" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B379" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 15 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C379" s="128">
+        <f>C378+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D379" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E379" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F379" s="95" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B380" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 15 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C380" s="128">
+        <f>C378+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D380" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E380" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F380" s="95" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MDF</t>
+        </is>
+      </c>
+      <c r="B381" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 15 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C381" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-15",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D381" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E381" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F381" s="95" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B382" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 15 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C382" s="128">
+        <f>C381+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D382" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E382" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F382" s="95" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B383" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 15 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C383" s="128">
+        <f>C381+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D383" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E383" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F383" s="95" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MSF</t>
+        </is>
+      </c>
+      <c r="B384" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 18 mm, Mindi single face</t>
+        </is>
+      </c>
+      <c r="C384" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-18",$A$178:$A$215,0))+1*$C$175</f>
+        <v/>
+      </c>
+      <c r="D384" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E384" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F384" s="95" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MSF-V10</t>
+        </is>
+      </c>
+      <c r="B385" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 18 mm, Mindi single face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C385" s="128">
+        <f>C384+1*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D385" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E385" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F385" s="95" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MSF-V12</t>
+        </is>
+      </c>
+      <c r="B386" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 18 mm, Mindi single face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C386" s="128">
+        <f>C384+1*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D386" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E386" s="95" t="inlineStr">
+        <is>
+          <t>1 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F386" s="95" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MDF</t>
+        </is>
+      </c>
+      <c r="B387" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 18 mm, Mindi double face</t>
+        </is>
+      </c>
+      <c r="C387" s="128">
+        <f>INDEX($C$178:$C$215,MATCH("LND-MDF-E0-18",$A$178:$A$215,0))+2*$C$175</f>
+        <v/>
+      </c>
+      <c r="D387" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E387" s="95" t="inlineStr">
+        <is>
+          <t>E0 raw landed + veneer face (0.6 mm)</t>
+        </is>
+      </c>
+      <c r="F387" s="95" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MDF-V10</t>
+        </is>
+      </c>
+      <c r="B388" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 18 mm, Mindi double face, 1.0 mm veneer</t>
+        </is>
+      </c>
+      <c r="C388" s="128">
+        <f>C387+2*(C276-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D388" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E388" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.0 mm</t>
+        </is>
+      </c>
+      <c r="F388" s="95" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="95" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MDF-V12</t>
+        </is>
+      </c>
+      <c r="B389" s="93" t="inlineStr">
+        <is>
+          <t>MDF E0 18 mm, Mindi double face, 1.2 mm veneer</t>
+        </is>
+      </c>
+      <c r="C389" s="128">
+        <f>C387+2*(C277-$C$175)</f>
+        <v/>
+      </c>
+      <c r="D389" s="95" t="inlineStr">
+        <is>
+          <t>IDR/sheet</t>
+        </is>
+      </c>
+      <c r="E389" s="95" t="inlineStr">
+        <is>
+          <t>2 face(s) at 1.2 mm</t>
+        </is>
+      </c>
+      <c r="F389" s="95" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C400">
@@ -18858,7 +20815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="59" min="1" max="2"/>
@@ -18916,7 +20873,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-3</t>
+          <t>LND-PLY-E0-3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -18946,7 +20903,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-6</t>
+          <t>LND-PLY-E0-6</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -18976,7 +20933,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-9</t>
+          <t>LND-PLY-E0-9</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -19001,7 +20958,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-12</t>
+          <t>LND-PLY-E0-12</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -19021,7 +20978,7 @@
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-15</t>
+          <t>LND-PLY-E0-15</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -19041,7 +20998,7 @@
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-18</t>
+          <t>LND-PLY-E0-18</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -19056,7 +21013,7 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-3</t>
+          <t>LND-MDF-E0-3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -19071,7 +21028,7 @@
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-6</t>
+          <t>LND-MDF-E0-6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -19086,7 +21043,7 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-9</t>
+          <t>LND-MDF-E0-9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -19101,420 +21058,528 @@
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-12</t>
+          <t>LND-MDF-E0-12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-15</t>
+          <t>LND-MDF-E0-15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-18</t>
+          <t>LND-MDF-E0-18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-18-MSF</t>
+          <t>LND-PLY-E0-3-MSF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-18-MDF</t>
+          <t>LND-PLY-E0-3-MSF-V10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-15-MSF</t>
+          <t>LND-PLY-E0-3-MSF-V12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-15-MDF</t>
+          <t>LND-PLY-E0-3-MDF</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-12-MSF</t>
+          <t>LND-PLY-E0-3-MDF-V10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-12-MDF</t>
+          <t>LND-PLY-E0-3-MDF-V12</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="59">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-9-MSF</t>
+          <t>LND-PLY-E0-6-MSF</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="59">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-9-MDF</t>
+          <t>LND-PLY-E0-6-MSF-V10</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="59">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-6-MSF</t>
+          <t>LND-PLY-E0-6-MSF-V12</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="59">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-6-MDF</t>
+          <t>LND-PLY-E0-6-MDF</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="59">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-3-MSF</t>
+          <t>LND-PLY-E0-6-MDF-V10</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="59">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-3-MDF</t>
+          <t>LND-PLY-E0-6-MDF-V12</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="59">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-18-MSF</t>
+          <t>LND-PLY-E0-9-MSF</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="59">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-18-MDF</t>
+          <t>LND-PLY-E0-9-MSF-V10</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="59">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-15-MSF</t>
+          <t>LND-PLY-E0-9-MSF-V12</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="59">
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-12-MSF</t>
+          <t>LND-PLY-E0-9-MDF</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="59">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-9-MSF</t>
+          <t>LND-PLY-E0-9-MDF-V10</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="59">
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-6-MSF</t>
+          <t>LND-PLY-E0-9-MDF-V12</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="59">
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-18-MSF-V10</t>
+          <t>LND-PLY-E0-12-MSF</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="59">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-18-MSF-V12</t>
+          <t>LND-PLY-E0-12-MSF-V10</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="59">
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-18-MDF-V10</t>
+          <t>LND-PLY-E0-12-MSF-V12</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="59">
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-18-MDF-V12</t>
+          <t>LND-PLY-E0-12-MDF</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="59">
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-15-MSF-V10</t>
+          <t>LND-PLY-E0-12-MDF-V10</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="59">
       <c r="B38" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-15-MSF-V12</t>
+          <t>LND-PLY-E0-12-MDF-V12</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="59">
       <c r="B39" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-15-MDF-V10</t>
+          <t>LND-PLY-E0-15-MSF</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="59">
       <c r="B40" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-15-MDF-V12</t>
+          <t>LND-PLY-E0-15-MSF-V10</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="59">
       <c r="B41" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-12-MSF-V10</t>
+          <t>LND-PLY-E0-15-MSF-V12</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="59">
       <c r="B42" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-12-MSF-V12</t>
+          <t>LND-PLY-E0-15-MDF</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="59">
       <c r="B43" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-12-MDF-V10</t>
+          <t>LND-PLY-E0-15-MDF-V10</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="59">
       <c r="B44" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-12-MDF-V12</t>
+          <t>LND-PLY-E0-15-MDF-V12</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="59">
       <c r="B45" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-9-MSF-V10</t>
+          <t>LND-PLY-E0-18-MSF</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="59">
       <c r="B46" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-9-MSF-V12</t>
+          <t>LND-PLY-E0-18-MSF-V10</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="59">
       <c r="B47" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-9-MDF-V10</t>
+          <t>LND-PLY-E0-18-MSF-V12</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="59">
       <c r="B48" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-9-MDF-V12</t>
+          <t>LND-PLY-E0-18-MDF</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="59">
       <c r="B49" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-6-MSF-V10</t>
+          <t>LND-PLY-E0-18-MDF-V10</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="59">
       <c r="B50" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-6-MSF-V12</t>
+          <t>LND-PLY-E0-18-MDF-V12</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="59">
       <c r="B51" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-6-MDF-V10</t>
+          <t>LND-MDF-E0-3-MSF</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="59">
       <c r="B52" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-6-MDF-V12</t>
+          <t>LND-MDF-E0-3-MSF-V10</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="59">
       <c r="B53" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-3-MSF-V10</t>
+          <t>LND-MDF-E0-3-MSF-V12</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="59">
       <c r="B54" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-3-MSF-V12</t>
+          <t>LND-MDF-E0-3-MDF</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="59">
       <c r="B55" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-3-MDF-V10</t>
+          <t>LND-MDF-E0-3-MDF-V10</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="59">
       <c r="B56" t="inlineStr">
         <is>
-          <t>LND-PLY-E2-3-MDF-V12</t>
+          <t>LND-MDF-E0-3-MDF-V12</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="59">
       <c r="B57" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-18-MSF-V10</t>
+          <t>LND-MDF-E0-6-MSF</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="59">
       <c r="B58" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-18-MSF-V12</t>
+          <t>LND-MDF-E0-6-MSF-V10</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-18-MDF-V10</t>
+          <t>LND-MDF-E0-6-MSF-V12</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="59">
       <c r="B60" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-18-MDF-V12</t>
+          <t>LND-MDF-E0-6-MDF</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="59">
       <c r="B61" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-15-MSF-V10</t>
+          <t>LND-MDF-E0-6-MDF-V10</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="59">
       <c r="B62" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-15-MSF-V12</t>
+          <t>LND-MDF-E0-6-MDF-V12</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="59">
       <c r="B63" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-12-MSF-V10</t>
+          <t>LND-MDF-E0-9-MSF</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="59">
       <c r="B64" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-12-MSF-V12</t>
+          <t>LND-MDF-E0-9-MSF-V10</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="59">
       <c r="B65" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-9-MSF-V10</t>
+          <t>LND-MDF-E0-9-MSF-V12</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="59">
       <c r="B66" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-9-MSF-V12</t>
+          <t>LND-MDF-E0-9-MDF</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="59">
       <c r="B67" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-6-MSF-V10</t>
+          <t>LND-MDF-E0-9-MDF-V10</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="59">
       <c r="B68" t="inlineStr">
         <is>
-          <t>LND-MDF-E2-6-MSF-V12</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1" s="59"/>
-    <row r="70" ht="15.75" customHeight="1" s="59"/>
-    <row r="71" ht="15.75" customHeight="1" s="59"/>
-    <row r="72" ht="15.75" customHeight="1" s="59"/>
-    <row r="73" ht="15.75" customHeight="1" s="59"/>
-    <row r="74" ht="15.75" customHeight="1" s="59"/>
-    <row r="75" ht="15.75" customHeight="1" s="59"/>
-    <row r="76" ht="15.75" customHeight="1" s="59"/>
-    <row r="77" ht="15.75" customHeight="1" s="59"/>
-    <row r="78" ht="15.75" customHeight="1" s="59"/>
-    <row r="79" ht="15.75" customHeight="1" s="59"/>
-    <row r="80" ht="15.75" customHeight="1" s="59"/>
-    <row r="81" ht="15.75" customHeight="1" s="59"/>
-    <row r="82" ht="15.75" customHeight="1" s="59"/>
-    <row r="83" ht="15.75" customHeight="1" s="59"/>
-    <row r="84" ht="15.75" customHeight="1" s="59"/>
-    <row r="85" ht="15.75" customHeight="1" s="59"/>
-    <row r="86" ht="15.75" customHeight="1" s="59"/>
+          <t>LND-MDF-E0-9-MDF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" s="59">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1" s="59">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" s="59">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1" s="59">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" s="59">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MDF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" s="59">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-12-MDF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" s="59">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" s="59">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" s="59">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1" s="59">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" s="59">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MDF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" s="59">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-15-MDF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1" s="59">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1" s="59">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MSF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1" s="59">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MSF-V12</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" s="59">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="59">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MDF-V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" s="59">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>LND-MDF-E0-18-MDF-V12</t>
+        </is>
+      </c>
+    </row>
     <row r="87" ht="15.75" customHeight="1" s="59"/>
     <row r="88" ht="15.75" customHeight="1" s="59"/>
     <row r="89" ht="15.75" customHeight="1" s="59"/>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -14643,6 +14643,7 @@
       <c r="H168" s="95" t="n"/>
       <c r="I168" s="95" t="n"/>
     </row>
+    <row r="169"/>
     <row r="170">
       <c r="A170" s="97" t="inlineStr">
         <is>
@@ -14853,6 +14854,7 @@
       <c r="H176" s="95" t="n"/>
       <c r="I176" s="95" t="n"/>
     </row>
+    <row r="177"/>
     <row r="178">
       <c r="A178" s="119" t="inlineStr">
         <is>
@@ -16373,6 +16375,7 @@
         <v>933</v>
       </c>
     </row>
+    <row r="216"/>
     <row r="217">
       <c r="A217" s="97" t="inlineStr">
         <is>
@@ -16676,6 +16679,7 @@
       <c r="H225" s="95" t="n"/>
       <c r="I225" s="95" t="n"/>
     </row>
+    <row r="226"/>
     <row r="227">
       <c r="A227" s="97" t="inlineStr">
         <is>
@@ -16769,6 +16773,7 @@
       <c r="H229" s="95" t="n"/>
       <c r="I229" s="95" t="n"/>
     </row>
+    <row r="230"/>
     <row r="231">
       <c r="A231" s="127" t="inlineStr">
         <is>
@@ -17252,10 +17257,11 @@
       <c r="H249" s="95" t="n"/>
       <c r="I249" s="95" t="n"/>
     </row>
+    <row r="250"/>
     <row r="251">
       <c r="A251" s="127" t="inlineStr">
         <is>
-          <t>METAL (added 19 Oct 2026). Value EMPTY: price not yet received. Fill column C; METAL parts cost 0 until filled.</t>
+          <t>METAL = black hollow steel (rule 19 Oct 2026). METAL parts are priced from the STEEL HOLLOW SECTION list below: length x qty x IDR/m of HOLLOW-&lt;a&gt;x&lt;b&gt;x&lt;wall&gt;. Set the wall thickness here.</t>
         </is>
       </c>
       <c r="B251" s="98" t="n"/>
@@ -17270,23 +17276,25 @@
     <row r="252">
       <c r="A252" s="113" t="inlineStr">
         <is>
-          <t>METAL_A</t>
+          <t>HOLLOW_WALL</t>
         </is>
       </c>
       <c r="B252" s="117" t="inlineStr">
         <is>
-          <t>Metal tier A (exposed, long), per m³ of component</t>
-        </is>
-      </c>
-      <c r="C252" s="129" t="n"/>
+          <t>Wall thickness used for ALL METAL parts (not on drawings)</t>
+        </is>
+      </c>
+      <c r="C252" s="129" t="n">
+        <v>1.2</v>
+      </c>
       <c r="D252" s="113" t="inlineStr">
         <is>
-          <t>IDR/m³</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E252" s="113" t="inlineStr">
         <is>
-          <t>EMPTY: waiting for price</t>
+          <t>CONFIRM with factory: 1.2 assumed. Used: 0.8, 1.0, 1.2, 1.5, 1.8, 2.0 (as listed)</t>
         </is>
       </c>
       <c r="F252" s="95" t="n"/>
@@ -17305,7 +17313,11 @@
           <t>Metal tier B</t>
         </is>
       </c>
-      <c r="C253" s="129" t="n"/>
+      <c r="C253" s="129" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="D253" s="113" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -17313,7 +17325,7 @@
       </c>
       <c r="E253" s="113" t="inlineStr">
         <is>
-          <t>EMPTY: waiting for price</t>
+          <t>Not used: METAL parts are priced from the HOLLOW-... list</t>
         </is>
       </c>
       <c r="F253" s="95" t="n"/>
@@ -17332,7 +17344,11 @@
           <t>Metal tier C</t>
         </is>
       </c>
-      <c r="C254" s="129" t="n"/>
+      <c r="C254" s="129" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="D254" s="113" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -17340,7 +17356,7 @@
       </c>
       <c r="E254" s="113" t="inlineStr">
         <is>
-          <t>EMPTY: waiting for price</t>
+          <t>Not used: METAL parts are priced from the HOLLOW-... list</t>
         </is>
       </c>
       <c r="F254" s="95" t="n"/>
@@ -17359,7 +17375,11 @@
           <t>Metal tier D</t>
         </is>
       </c>
-      <c r="C255" s="129" t="n"/>
+      <c r="C255" s="129" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="D255" s="113" t="inlineStr">
         <is>
           <t>IDR/m³</t>
@@ -17367,7 +17387,7 @@
       </c>
       <c r="E255" s="113" t="inlineStr">
         <is>
-          <t>EMPTY: waiting for price</t>
+          <t>Not used: METAL parts are priced from the HOLLOW-... list</t>
         </is>
       </c>
       <c r="F255" s="95" t="n"/>
@@ -17386,7 +17406,11 @@
           <t>Brass, per kg (reference)</t>
         </is>
       </c>
-      <c r="C256" s="129" t="n"/>
+      <c r="C256" s="129" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="D256" s="113" t="inlineStr">
         <is>
           <t>IDR/kg</t>
@@ -17394,7 +17418,7 @@
       </c>
       <c r="E256" s="113" t="inlineStr">
         <is>
-          <t>EMPTY: waiting for price</t>
+          <t>Not used: METAL parts are priced from the HOLLOW-... list</t>
         </is>
       </c>
       <c r="F256" s="95" t="n"/>
@@ -17413,7 +17437,11 @@
           <t>Steel / hollow section, per kg (reference)</t>
         </is>
       </c>
-      <c r="C257" s="129" t="n"/>
+      <c r="C257" s="129" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="D257" s="113" t="inlineStr">
         <is>
           <t>IDR/kg</t>
@@ -17421,7 +17449,7 @@
       </c>
       <c r="E257" s="113" t="inlineStr">
         <is>
-          <t>EMPTY: waiting for price</t>
+          <t>Not used: METAL parts are priced from the HOLLOW-... list</t>
         </is>
       </c>
       <c r="F257" s="95" t="n"/>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -17285,7 +17285,7 @@
         </is>
       </c>
       <c r="C252" s="129" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D252" s="113" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="E252" s="113" t="inlineStr">
         <is>
-          <t>CONFIRM with factory: 1.2 assumed. Used: 0.8, 1.0, 1.2, 1.5, 1.8, 2.0 (as listed)</t>
+          <t>0.8 mm for now (decision 19 Oct 2026). Change by hand. If a section has no such wall in the list (50x50, 40x60 start at 1.0), the next listed wall is used.</t>
         </is>
       </c>
       <c r="F252" s="95" t="n"/>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -393,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -647,6 +647,13 @@
     <xf numFmtId="2" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6471,7 +6478,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" s="59">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>SOLID WOOD: one line per component, mm, qty per ONE item</t>
@@ -6578,7 +6585,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" s="59">
       <c r="A18" s="9" t="n">
         <v>1</v>
       </c>
@@ -7208,93 +7215,128 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="59">
-      <c r="A33" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="48" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="10" t="n"/>
-      <c r="M33" s="25">
-        <f>IF(OR(E33="",F33="",G33=""),"",E33*F33*G33/1000000000*IF(H33="",1,H33))</f>
-        <v/>
-      </c>
-      <c r="N33" s="19">
-        <f>IF(OR(E33="",F33=""),"",E33*F33/1000000*IF(H33="",1,H33))</f>
-        <v/>
-      </c>
-      <c r="O33" s="14">
-        <f>IF(E33="","",IF(K33&lt;&gt;"",K33,IF(AND(E33*F33*G33/1000000000&lt;LISTS!$F$4,MAX(E33,F33,G33)&lt;LISTS!$F$5),"D",IF(I33="N","C",IF(J33="Y","A-CURVED",IF(AND(MEDIAN(E33,F33,G33)&lt;=LISTS!$F$10,MAX(E33,F33,G33)&lt;=LISTS!$F$11),"B",IF(MAX(E33,F33,G33)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
-      </c>
-      <c r="P33" s="14" t="n"/>
-      <c r="Q33" s="14" t="n"/>
-      <c r="R33" s="14">
-        <f>IF(E33="","",IF(B33="","material?",IF(OR(F33="",G33=""),"size?",IF(I33="","exposed Y/N?",IF(H33="","qty?",IF(B33="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S33" s="12">
-        <f t="array" ref="S33">IF(OR(O33="",M33=""),"",IF(B33="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B33&amp;"_"&amp;SUBSTITUTE(O33,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T33" s="12">
-        <f>IF(ISNUMBER(S33),M33*S33,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" s="59">
-      <c r="A34" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="48" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="10" t="n"/>
-      <c r="M34" s="25">
-        <f>IF(OR(E34="",F34="",G34=""),"",E34*F34*G34/1000000000*IF(H34="",1,H34))</f>
-        <v/>
-      </c>
-      <c r="N34" s="19">
-        <f>IF(OR(E34="",F34=""),"",E34*F34/1000000*IF(H34="",1,H34))</f>
-        <v/>
-      </c>
-      <c r="O34" s="14">
-        <f>IF(E34="","",IF(K34&lt;&gt;"",K34,IF(AND(E34*F34*G34/1000000000&lt;LISTS!$F$4,MAX(E34,F34,G34)&lt;LISTS!$F$5),"D",IF(I34="N","C",IF(J34="Y","A-CURVED",IF(AND(MEDIAN(E34,F34,G34)&lt;=LISTS!$F$10,MAX(E34,F34,G34)&lt;=LISTS!$F$11),"B",IF(MAX(E34,F34,G34)&gt;=LISTS!$F$3,"A","B")))))))</f>
-        <v/>
-      </c>
-      <c r="P34" s="14" t="n"/>
-      <c r="Q34" s="14" t="n"/>
-      <c r="R34" s="14">
-        <f>IF(E34="","",IF(B34="","material?",IF(OR(F34="",G34=""),"size?",IF(I34="","exposed Y/N?",IF(H34="","qty?",IF(B34="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S34" s="12">
-        <f t="array" ref="S34">IF(OR(O34="",M34=""),"",IF(B34="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B34&amp;"_"&amp;SUBSTITUTE(O34,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T34" s="12">
-        <f>IF(ISNUMBER(S34),M34*S34,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" s="59">
+    <row r="33" s="59">
+      <c r="A33" s="133" t="inlineStr">
+        <is>
+          <t>METAL (hollow steel): one line per part, priced PER METRE from the RATES hollow list. MATERIAL = hollow code HOLLOW-&lt;a&gt;x&lt;b&gt;x&lt;wall&gt;, or METAL (= section W x T with RATES!HOLLOW_WALL)</t>
+        </is>
+      </c>
+      <c r="B33" s="134" t="n"/>
+      <c r="C33" s="134" t="n"/>
+      <c r="D33" s="134" t="n"/>
+      <c r="E33" s="134" t="n"/>
+      <c r="F33" s="134" t="n"/>
+      <c r="G33" s="134" t="n"/>
+      <c r="H33" s="134" t="n"/>
+      <c r="I33" s="134" t="n"/>
+      <c r="J33" s="134" t="n"/>
+      <c r="K33" s="134" t="n"/>
+      <c r="L33" s="134" t="n"/>
+      <c r="M33" s="134" t="n"/>
+      <c r="N33" s="134" t="n"/>
+      <c r="O33" s="134" t="n"/>
+      <c r="P33" s="134" t="n"/>
+      <c r="Q33" s="134" t="n"/>
+      <c r="R33" s="134" t="n"/>
+      <c r="S33" s="134" t="n"/>
+      <c r="T33" s="134" t="n"/>
+      <c r="U33" s="134" t="n"/>
+    </row>
+    <row r="34" ht="31.5" customHeight="1" s="59">
+      <c r="A34" s="47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B34" s="47" t="inlineStr">
+        <is>
+          <t>MATERIAL / HOLLOW CODE</t>
+        </is>
+      </c>
+      <c r="C34" s="47" t="inlineStr">
+        <is>
+          <t>LABEL</t>
+        </is>
+      </c>
+      <c r="D34" s="47" t="inlineStr">
+        <is>
+          <t>COMPONENT</t>
+        </is>
+      </c>
+      <c r="E34" s="47" t="inlineStr">
+        <is>
+          <t>L mm</t>
+        </is>
+      </c>
+      <c r="F34" s="47" t="inlineStr">
+        <is>
+          <t>W mm</t>
+        </is>
+      </c>
+      <c r="G34" s="47" t="inlineStr">
+        <is>
+          <t>T mm</t>
+        </is>
+      </c>
+      <c r="H34" s="47" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="I34" s="47" t="inlineStr">
+        <is>
+          <t>EXPOSED Y/N</t>
+        </is>
+      </c>
+      <c r="J34" s="47" t="n"/>
+      <c r="K34" s="47" t="n"/>
+      <c r="L34" s="47" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="M34" s="47" t="inlineStr">
+        <is>
+          <t>LENGTH m (calc)</t>
+        </is>
+      </c>
+      <c r="N34" s="47" t="inlineStr">
+        <is>
+          <t>FACE m² (calc)</t>
+        </is>
+      </c>
+      <c r="O34" s="47" t="inlineStr">
+        <is>
+          <t>CODE USED (calc)</t>
+        </is>
+      </c>
+      <c r="P34" s="47" t="n"/>
+      <c r="Q34" s="47" t="n"/>
+      <c r="R34" s="47" t="inlineStr">
+        <is>
+          <t>CHECK (calc)</t>
+        </is>
+      </c>
+      <c r="S34" s="47" t="inlineStr">
+        <is>
+          <t>RATE IDR/m (system)</t>
+        </is>
+      </c>
+      <c r="T34" s="47" t="inlineStr">
+        <is>
+          <t>COST IDR (system)</t>
+        </is>
+      </c>
+      <c r="U34" s="135" t="inlineStr">
+        <is>
+          <t>COST USD
+(system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" s="59">
       <c r="A35" s="9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="48" t="n"/>
@@ -7307,8 +7349,8 @@
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="10" t="n"/>
-      <c r="M35" s="25">
-        <f>IF(OR(E35="",F35="",G35=""),"",E35*F35*G35/1000000000*IF(H35="",1,H35))</f>
+      <c r="M35" s="19">
+        <f>IF(E35="","",E35/1000*IF(H35="",1,H35))</f>
         <v/>
       </c>
       <c r="N35" s="19">
@@ -7316,27 +7358,31 @@
         <v/>
       </c>
       <c r="O35" s="14">
-        <f>IF(E35="","",IF(K35&lt;&gt;"",K35,IF(AND(E35*F35*G35/1000000000&lt;LISTS!$F$4,MAX(E35,F35,G35)&lt;LISTS!$F$5),"D",IF(I35="N","C",IF(J35="Y","A-CURVED",IF(AND(MEDIAN(E35,F35,G35)&lt;=LISTS!$F$10,MAX(E35,F35,G35)&lt;=LISTS!$F$11),"B",IF(MAX(E35,F35,G35)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <f>IF(E35="","",IF(UPPER(B35)="METAL",IFERROR(IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F35,G35)&amp;"x"&amp;MAX(F35,G35)&amp;"x"&amp;SUBSTITUTE(RATES!$C$252&amp;"",",","."),RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F35,G35)&amp;"x"&amp;MAX(F35,G35)&amp;"x"&amp;"1",RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F35,G35)&amp;"x"&amp;MAX(F35,G35)&amp;"x"&amp;"1.2",RATES!$A:$A,0)),INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F35,G35)&amp;"x"&amp;MAX(F35,G35)&amp;"x"&amp;"1.5",RATES!$A:$A,0))))),"not in list"),IFERROR(INDEX(RATES!$A:$A,MATCH(IF(LEFT(UPPER(B35),7)="HOLLOW-",UPPER(B35),"HOLLOW-"&amp;B35),RATES!$A:$A,0)),"not in list")))</f>
         <v/>
       </c>
       <c r="P35" s="14" t="n"/>
       <c r="Q35" s="14" t="n"/>
       <c r="R35" s="14">
-        <f>IF(E35="","",IF(B35="","material?",IF(OR(F35="",G35=""),"size?",IF(I35="","exposed Y/N?",IF(H35="","qty?",IF(B35="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S35" s="12">
-        <f t="array" ref="S35">IF(OR(O35="",M35=""),"",IF(B35="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B35&amp;"_"&amp;SUBSTITUTE(O35,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T35" s="12">
-        <f>IF(ISNUMBER(S35),M35*S35,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" s="59">
+        <f>IF(E35="","",IF(B35="","material?",IF(OR(F35="",G35=""),"size?",IF(I35="","exposed Y/N?",IF(H35="","qty?",IF(O35="not in list","hollow code?","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="S35" s="136">
+        <f>IF(E35="","",IFERROR(INDEX(RATES!$C:$C,MATCH(O35,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
+      </c>
+      <c r="T35" s="136">
+        <f>IF(AND(ISNUMBER(S35),ISNUMBER(M35)),M35*S35,"")</f>
+        <v/>
+      </c>
+      <c r="U35" s="134">
+        <f>IF(T35="","",T35/RATES!$C$172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" s="59">
       <c r="A36" s="9" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="48" t="n"/>
@@ -7349,8 +7395,8 @@
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="10" t="n"/>
-      <c r="M36" s="25">
-        <f>IF(OR(E36="",F36="",G36=""),"",E36*F36*G36/1000000000*IF(H36="",1,H36))</f>
+      <c r="M36" s="19">
+        <f>IF(E36="","",E36/1000*IF(H36="",1,H36))</f>
         <v/>
       </c>
       <c r="N36" s="19">
@@ -7358,27 +7404,31 @@
         <v/>
       </c>
       <c r="O36" s="14">
-        <f>IF(E36="","",IF(K36&lt;&gt;"",K36,IF(AND(E36*F36*G36/1000000000&lt;LISTS!$F$4,MAX(E36,F36,G36)&lt;LISTS!$F$5),"D",IF(I36="N","C",IF(J36="Y","A-CURVED",IF(AND(MEDIAN(E36,F36,G36)&lt;=LISTS!$F$10,MAX(E36,F36,G36)&lt;=LISTS!$F$11),"B",IF(MAX(E36,F36,G36)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <f>IF(E36="","",IF(UPPER(B36)="METAL",IFERROR(IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F36,G36)&amp;"x"&amp;MAX(F36,G36)&amp;"x"&amp;SUBSTITUTE(RATES!$C$252&amp;"",",","."),RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F36,G36)&amp;"x"&amp;MAX(F36,G36)&amp;"x"&amp;"1",RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F36,G36)&amp;"x"&amp;MAX(F36,G36)&amp;"x"&amp;"1.2",RATES!$A:$A,0)),INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F36,G36)&amp;"x"&amp;MAX(F36,G36)&amp;"x"&amp;"1.5",RATES!$A:$A,0))))),"not in list"),IFERROR(INDEX(RATES!$A:$A,MATCH(IF(LEFT(UPPER(B36),7)="HOLLOW-",UPPER(B36),"HOLLOW-"&amp;B36),RATES!$A:$A,0)),"not in list")))</f>
         <v/>
       </c>
       <c r="P36" s="14" t="n"/>
       <c r="Q36" s="14" t="n"/>
       <c r="R36" s="14">
-        <f>IF(E36="","",IF(B36="","material?",IF(OR(F36="",G36=""),"size?",IF(I36="","exposed Y/N?",IF(H36="","qty?",IF(B36="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S36" s="12">
-        <f t="array" ref="S36">IF(OR(O36="",M36=""),"",IF(B36="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B36&amp;"_"&amp;SUBSTITUTE(O36,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T36" s="12">
-        <f>IF(ISNUMBER(S36),M36*S36,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" s="59">
+        <f>IF(E36="","",IF(B36="","material?",IF(OR(F36="",G36=""),"size?",IF(I36="","exposed Y/N?",IF(H36="","qty?",IF(O36="not in list","hollow code?","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="S36" s="136">
+        <f>IF(E36="","",IFERROR(INDEX(RATES!$C:$C,MATCH(O36,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
+      </c>
+      <c r="T36" s="136">
+        <f>IF(AND(ISNUMBER(S36),ISNUMBER(M36)),M36*S36,"")</f>
+        <v/>
+      </c>
+      <c r="U36" s="134">
+        <f>IF(T36="","",T36/RATES!$C$172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" s="59">
       <c r="A37" s="9" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="48" t="n"/>
@@ -7391,8 +7441,8 @@
       <c r="J37" s="10" t="n"/>
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="n"/>
-      <c r="M37" s="25">
-        <f>IF(OR(E37="",F37="",G37=""),"",E37*F37*G37/1000000000*IF(H37="",1,H37))</f>
+      <c r="M37" s="19">
+        <f>IF(E37="","",E37/1000*IF(H37="",1,H37))</f>
         <v/>
       </c>
       <c r="N37" s="19">
@@ -7400,27 +7450,31 @@
         <v/>
       </c>
       <c r="O37" s="14">
-        <f>IF(E37="","",IF(K37&lt;&gt;"",K37,IF(AND(E37*F37*G37/1000000000&lt;LISTS!$F$4,MAX(E37,F37,G37)&lt;LISTS!$F$5),"D",IF(I37="N","C",IF(J37="Y","A-CURVED",IF(AND(MEDIAN(E37,F37,G37)&lt;=LISTS!$F$10,MAX(E37,F37,G37)&lt;=LISTS!$F$11),"B",IF(MAX(E37,F37,G37)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <f>IF(E37="","",IF(UPPER(B37)="METAL",IFERROR(IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F37,G37)&amp;"x"&amp;MAX(F37,G37)&amp;"x"&amp;SUBSTITUTE(RATES!$C$252&amp;"",",","."),RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F37,G37)&amp;"x"&amp;MAX(F37,G37)&amp;"x"&amp;"1",RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F37,G37)&amp;"x"&amp;MAX(F37,G37)&amp;"x"&amp;"1.2",RATES!$A:$A,0)),INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F37,G37)&amp;"x"&amp;MAX(F37,G37)&amp;"x"&amp;"1.5",RATES!$A:$A,0))))),"not in list"),IFERROR(INDEX(RATES!$A:$A,MATCH(IF(LEFT(UPPER(B37),7)="HOLLOW-",UPPER(B37),"HOLLOW-"&amp;B37),RATES!$A:$A,0)),"not in list")))</f>
         <v/>
       </c>
       <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
       <c r="R37" s="14">
-        <f>IF(E37="","",IF(B37="","material?",IF(OR(F37="",G37=""),"size?",IF(I37="","exposed Y/N?",IF(H37="","qty?",IF(B37="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S37" s="12">
-        <f t="array" ref="S37">IF(OR(O37="",M37=""),"",IF(B37="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B37&amp;"_"&amp;SUBSTITUTE(O37,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T37" s="12">
-        <f>IF(ISNUMBER(S37),M37*S37,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1" s="59">
+        <f>IF(E37="","",IF(B37="","material?",IF(OR(F37="",G37=""),"size?",IF(I37="","exposed Y/N?",IF(H37="","qty?",IF(O37="not in list","hollow code?","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="S37" s="136">
+        <f>IF(E37="","",IFERROR(INDEX(RATES!$C:$C,MATCH(O37,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
+      </c>
+      <c r="T37" s="136">
+        <f>IF(AND(ISNUMBER(S37),ISNUMBER(M37)),M37*S37,"")</f>
+        <v/>
+      </c>
+      <c r="U37" s="134">
+        <f>IF(T37="","",T37/RATES!$C$172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" s="59">
       <c r="A38" s="9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="48" t="n"/>
@@ -7433,8 +7487,8 @@
       <c r="J38" s="10" t="n"/>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="10" t="n"/>
-      <c r="M38" s="25">
-        <f>IF(OR(E38="",F38="",G38=""),"",E38*F38*G38/1000000000*IF(H38="",1,H38))</f>
+      <c r="M38" s="19">
+        <f>IF(E38="","",E38/1000*IF(H38="",1,H38))</f>
         <v/>
       </c>
       <c r="N38" s="19">
@@ -7442,27 +7496,31 @@
         <v/>
       </c>
       <c r="O38" s="14">
-        <f>IF(E38="","",IF(K38&lt;&gt;"",K38,IF(AND(E38*F38*G38/1000000000&lt;LISTS!$F$4,MAX(E38,F38,G38)&lt;LISTS!$F$5),"D",IF(I38="N","C",IF(J38="Y","A-CURVED",IF(AND(MEDIAN(E38,F38,G38)&lt;=LISTS!$F$10,MAX(E38,F38,G38)&lt;=LISTS!$F$11),"B",IF(MAX(E38,F38,G38)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <f>IF(E38="","",IF(UPPER(B38)="METAL",IFERROR(IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F38,G38)&amp;"x"&amp;MAX(F38,G38)&amp;"x"&amp;SUBSTITUTE(RATES!$C$252&amp;"",",","."),RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F38,G38)&amp;"x"&amp;MAX(F38,G38)&amp;"x"&amp;"1",RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F38,G38)&amp;"x"&amp;MAX(F38,G38)&amp;"x"&amp;"1.2",RATES!$A:$A,0)),INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F38,G38)&amp;"x"&amp;MAX(F38,G38)&amp;"x"&amp;"1.5",RATES!$A:$A,0))))),"not in list"),IFERROR(INDEX(RATES!$A:$A,MATCH(IF(LEFT(UPPER(B38),7)="HOLLOW-",UPPER(B38),"HOLLOW-"&amp;B38),RATES!$A:$A,0)),"not in list")))</f>
         <v/>
       </c>
       <c r="P38" s="14" t="n"/>
       <c r="Q38" s="14" t="n"/>
       <c r="R38" s="14">
-        <f>IF(E38="","",IF(B38="","material?",IF(OR(F38="",G38=""),"size?",IF(I38="","exposed Y/N?",IF(H38="","qty?",IF(B38="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S38" s="12">
-        <f t="array" ref="S38">IF(OR(O38="",M38=""),"",IF(B38="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B38&amp;"_"&amp;SUBSTITUTE(O38,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T38" s="12">
-        <f>IF(ISNUMBER(S38),M38*S38,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" s="59">
+        <f>IF(E38="","",IF(B38="","material?",IF(OR(F38="",G38=""),"size?",IF(I38="","exposed Y/N?",IF(H38="","qty?",IF(O38="not in list","hollow code?","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="S38" s="136">
+        <f>IF(E38="","",IFERROR(INDEX(RATES!$C:$C,MATCH(O38,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
+      </c>
+      <c r="T38" s="136">
+        <f>IF(AND(ISNUMBER(S38),ISNUMBER(M38)),M38*S38,"")</f>
+        <v/>
+      </c>
+      <c r="U38" s="134">
+        <f>IF(T38="","",T38/RATES!$C$172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" s="59">
       <c r="A39" s="9" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="48" t="n"/>
@@ -7475,8 +7533,8 @@
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="n"/>
       <c r="L39" s="10" t="n"/>
-      <c r="M39" s="25">
-        <f>IF(OR(E39="",F39="",G39=""),"",E39*F39*G39/1000000000*IF(H39="",1,H39))</f>
+      <c r="M39" s="19">
+        <f>IF(E39="","",E39/1000*IF(H39="",1,H39))</f>
         <v/>
       </c>
       <c r="N39" s="19">
@@ -7484,27 +7542,31 @@
         <v/>
       </c>
       <c r="O39" s="14">
-        <f>IF(E39="","",IF(K39&lt;&gt;"",K39,IF(AND(E39*F39*G39/1000000000&lt;LISTS!$F$4,MAX(E39,F39,G39)&lt;LISTS!$F$5),"D",IF(I39="N","C",IF(J39="Y","A-CURVED",IF(AND(MEDIAN(E39,F39,G39)&lt;=LISTS!$F$10,MAX(E39,F39,G39)&lt;=LISTS!$F$11),"B",IF(MAX(E39,F39,G39)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <f>IF(E39="","",IF(UPPER(B39)="METAL",IFERROR(IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F39,G39)&amp;"x"&amp;MAX(F39,G39)&amp;"x"&amp;SUBSTITUTE(RATES!$C$252&amp;"",",","."),RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F39,G39)&amp;"x"&amp;MAX(F39,G39)&amp;"x"&amp;"1",RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F39,G39)&amp;"x"&amp;MAX(F39,G39)&amp;"x"&amp;"1.2",RATES!$A:$A,0)),INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F39,G39)&amp;"x"&amp;MAX(F39,G39)&amp;"x"&amp;"1.5",RATES!$A:$A,0))))),"not in list"),IFERROR(INDEX(RATES!$A:$A,MATCH(IF(LEFT(UPPER(B39),7)="HOLLOW-",UPPER(B39),"HOLLOW-"&amp;B39),RATES!$A:$A,0)),"not in list")))</f>
         <v/>
       </c>
       <c r="P39" s="14" t="n"/>
       <c r="Q39" s="14" t="n"/>
       <c r="R39" s="14">
-        <f>IF(E39="","",IF(B39="","material?",IF(OR(F39="",G39=""),"size?",IF(I39="","exposed Y/N?",IF(H39="","qty?",IF(B39="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S39" s="12">
-        <f t="array" ref="S39">IF(OR(O39="",M39=""),"",IF(B39="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B39&amp;"_"&amp;SUBSTITUTE(O39,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T39" s="12">
-        <f>IF(ISNUMBER(S39),M39*S39,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1" s="59">
+        <f>IF(E39="","",IF(B39="","material?",IF(OR(F39="",G39=""),"size?",IF(I39="","exposed Y/N?",IF(H39="","qty?",IF(O39="not in list","hollow code?","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="S39" s="136">
+        <f>IF(E39="","",IFERROR(INDEX(RATES!$C:$C,MATCH(O39,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
+      </c>
+      <c r="T39" s="136">
+        <f>IF(AND(ISNUMBER(S39),ISNUMBER(M39)),M39*S39,"")</f>
+        <v/>
+      </c>
+      <c r="U39" s="134">
+        <f>IF(T39="","",T39/RATES!$C$172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" s="59">
       <c r="A40" s="9" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="48" t="n"/>
@@ -7517,8 +7579,8 @@
       <c r="J40" s="10" t="n"/>
       <c r="K40" s="10" t="n"/>
       <c r="L40" s="10" t="n"/>
-      <c r="M40" s="25">
-        <f>IF(OR(E40="",F40="",G40=""),"",E40*F40*G40/1000000000*IF(H40="",1,H40))</f>
+      <c r="M40" s="19">
+        <f>IF(E40="","",E40/1000*IF(H40="",1,H40))</f>
         <v/>
       </c>
       <c r="N40" s="19">
@@ -7526,27 +7588,31 @@
         <v/>
       </c>
       <c r="O40" s="14">
-        <f>IF(E40="","",IF(K40&lt;&gt;"",K40,IF(AND(E40*F40*G40/1000000000&lt;LISTS!$F$4,MAX(E40,F40,G40)&lt;LISTS!$F$5),"D",IF(I40="N","C",IF(J40="Y","A-CURVED",IF(AND(MEDIAN(E40,F40,G40)&lt;=LISTS!$F$10,MAX(E40,F40,G40)&lt;=LISTS!$F$11),"B",IF(MAX(E40,F40,G40)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <f>IF(E40="","",IF(UPPER(B40)="METAL",IFERROR(IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F40,G40)&amp;"x"&amp;MAX(F40,G40)&amp;"x"&amp;SUBSTITUTE(RATES!$C$252&amp;"",",","."),RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F40,G40)&amp;"x"&amp;MAX(F40,G40)&amp;"x"&amp;"1",RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F40,G40)&amp;"x"&amp;MAX(F40,G40)&amp;"x"&amp;"1.2",RATES!$A:$A,0)),INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F40,G40)&amp;"x"&amp;MAX(F40,G40)&amp;"x"&amp;"1.5",RATES!$A:$A,0))))),"not in list"),IFERROR(INDEX(RATES!$A:$A,MATCH(IF(LEFT(UPPER(B40),7)="HOLLOW-",UPPER(B40),"HOLLOW-"&amp;B40),RATES!$A:$A,0)),"not in list")))</f>
         <v/>
       </c>
       <c r="P40" s="14" t="n"/>
       <c r="Q40" s="14" t="n"/>
       <c r="R40" s="14">
-        <f>IF(E40="","",IF(B40="","material?",IF(OR(F40="",G40=""),"size?",IF(I40="","exposed Y/N?",IF(H40="","qty?",IF(B40="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S40" s="12">
-        <f t="array" ref="S40">IF(OR(O40="",M40=""),"",IF(B40="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B40&amp;"_"&amp;SUBSTITUTE(O40,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T40" s="12">
-        <f>IF(ISNUMBER(S40),M40*S40,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" s="59">
+        <f>IF(E40="","",IF(B40="","material?",IF(OR(F40="",G40=""),"size?",IF(I40="","exposed Y/N?",IF(H40="","qty?",IF(O40="not in list","hollow code?","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="S40" s="136">
+        <f>IF(E40="","",IFERROR(INDEX(RATES!$C:$C,MATCH(O40,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
+      </c>
+      <c r="T40" s="136">
+        <f>IF(AND(ISNUMBER(S40),ISNUMBER(M40)),M40*S40,"")</f>
+        <v/>
+      </c>
+      <c r="U40" s="134">
+        <f>IF(T40="","",T40/RATES!$C$172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" s="59">
       <c r="A41" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="48" t="n"/>
@@ -7559,8 +7625,8 @@
       <c r="J41" s="10" t="n"/>
       <c r="K41" s="10" t="n"/>
       <c r="L41" s="10" t="n"/>
-      <c r="M41" s="25">
-        <f>IF(OR(E41="",F41="",G41=""),"",E41*F41*G41/1000000000*IF(H41="",1,H41))</f>
+      <c r="M41" s="19">
+        <f>IF(E41="","",E41/1000*IF(H41="",1,H41))</f>
         <v/>
       </c>
       <c r="N41" s="19">
@@ -7568,27 +7634,31 @@
         <v/>
       </c>
       <c r="O41" s="14">
-        <f>IF(E41="","",IF(K41&lt;&gt;"",K41,IF(AND(E41*F41*G41/1000000000&lt;LISTS!$F$4,MAX(E41,F41,G41)&lt;LISTS!$F$5),"D",IF(I41="N","C",IF(J41="Y","A-CURVED",IF(AND(MEDIAN(E41,F41,G41)&lt;=LISTS!$F$10,MAX(E41,F41,G41)&lt;=LISTS!$F$11),"B",IF(MAX(E41,F41,G41)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <f>IF(E41="","",IF(UPPER(B41)="METAL",IFERROR(IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F41,G41)&amp;"x"&amp;MAX(F41,G41)&amp;"x"&amp;SUBSTITUTE(RATES!$C$252&amp;"",",","."),RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F41,G41)&amp;"x"&amp;MAX(F41,G41)&amp;"x"&amp;"1",RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F41,G41)&amp;"x"&amp;MAX(F41,G41)&amp;"x"&amp;"1.2",RATES!$A:$A,0)),INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F41,G41)&amp;"x"&amp;MAX(F41,G41)&amp;"x"&amp;"1.5",RATES!$A:$A,0))))),"not in list"),IFERROR(INDEX(RATES!$A:$A,MATCH(IF(LEFT(UPPER(B41),7)="HOLLOW-",UPPER(B41),"HOLLOW-"&amp;B41),RATES!$A:$A,0)),"not in list")))</f>
         <v/>
       </c>
       <c r="P41" s="14" t="n"/>
       <c r="Q41" s="14" t="n"/>
       <c r="R41" s="14">
-        <f>IF(E41="","",IF(B41="","material?",IF(OR(F41="",G41=""),"size?",IF(I41="","exposed Y/N?",IF(H41="","qty?",IF(B41="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S41" s="12">
-        <f t="array" ref="S41">IF(OR(O41="",M41=""),"",IF(B41="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B41&amp;"_"&amp;SUBSTITUTE(O41,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T41" s="12">
-        <f>IF(ISNUMBER(S41),M41*S41,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" s="59">
+        <f>IF(E41="","",IF(B41="","material?",IF(OR(F41="",G41=""),"size?",IF(I41="","exposed Y/N?",IF(H41="","qty?",IF(O41="not in list","hollow code?","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="S41" s="136">
+        <f>IF(E41="","",IFERROR(INDEX(RATES!$C:$C,MATCH(O41,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
+      </c>
+      <c r="T41" s="136">
+        <f>IF(AND(ISNUMBER(S41),ISNUMBER(M41)),M41*S41,"")</f>
+        <v/>
+      </c>
+      <c r="U41" s="134">
+        <f>IF(T41="","",T41/RATES!$C$172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" s="59">
       <c r="A42" s="9" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="48" t="n"/>
@@ -7601,8 +7671,8 @@
       <c r="J42" s="10" t="n"/>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="10" t="n"/>
-      <c r="M42" s="25">
-        <f>IF(OR(E42="",F42="",G42=""),"",E42*F42*G42/1000000000*IF(H42="",1,H42))</f>
+      <c r="M42" s="19">
+        <f>IF(E42="","",E42/1000*IF(H42="",1,H42))</f>
         <v/>
       </c>
       <c r="N42" s="19">
@@ -7610,21 +7680,25 @@
         <v/>
       </c>
       <c r="O42" s="14">
-        <f>IF(E42="","",IF(K42&lt;&gt;"",K42,IF(AND(E42*F42*G42/1000000000&lt;LISTS!$F$4,MAX(E42,F42,G42)&lt;LISTS!$F$5),"D",IF(I42="N","C",IF(J42="Y","A-CURVED",IF(AND(MEDIAN(E42,F42,G42)&lt;=LISTS!$F$10,MAX(E42,F42,G42)&lt;=LISTS!$F$11),"B",IF(MAX(E42,F42,G42)&gt;=LISTS!$F$3,"A","B")))))))</f>
+        <f>IF(E42="","",IF(UPPER(B42)="METAL",IFERROR(IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F42,G42)&amp;"x"&amp;MAX(F42,G42)&amp;"x"&amp;SUBSTITUTE(RATES!$C$252&amp;"",",","."),RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F42,G42)&amp;"x"&amp;MAX(F42,G42)&amp;"x"&amp;"1",RATES!$A:$A,0)),IFERROR(INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F42,G42)&amp;"x"&amp;MAX(F42,G42)&amp;"x"&amp;"1.2",RATES!$A:$A,0)),INDEX(RATES!$A:$A,MATCH("HOLLOW-"&amp;MIN(F42,G42)&amp;"x"&amp;MAX(F42,G42)&amp;"x"&amp;"1.5",RATES!$A:$A,0))))),"not in list"),IFERROR(INDEX(RATES!$A:$A,MATCH(IF(LEFT(UPPER(B42),7)="HOLLOW-",UPPER(B42),"HOLLOW-"&amp;B42),RATES!$A:$A,0)),"not in list")))</f>
         <v/>
       </c>
       <c r="P42" s="14" t="n"/>
       <c r="Q42" s="14" t="n"/>
       <c r="R42" s="14">
-        <f>IF(E42="","",IF(B42="","material?",IF(OR(F42="",G42=""),"size?",IF(I42="","exposed Y/N?",IF(H42="","qty?",IF(B42="OTHER","OTHER: no rate, price it under hardware","OK"))))))</f>
-        <v/>
-      </c>
-      <c r="S42" s="12">
-        <f t="array" ref="S42">IF(OR(O42="",M42=""),"",IF(B42="MERANTI",RATES!$C$45,IFERROR(INDEX(RATES!$C:$C,MATCH(B42&amp;"_"&amp;SUBSTITUTE(O42,"-CURVED","C"),RATES!$A:$A,0)),"rate?")))</f>
-        <v/>
-      </c>
-      <c r="T42" s="12">
-        <f>IF(ISNUMBER(S42),M42*S42,"")</f>
+        <f>IF(E42="","",IF(B42="","material?",IF(OR(F42="",G42=""),"size?",IF(I42="","exposed Y/N?",IF(H42="","qty?",IF(O42="not in list","hollow code?","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="S42" s="136">
+        <f>IF(E42="","",IFERROR(INDEX(RATES!$C:$C,MATCH(O42,RATES!$A:$A,0)),"rate?"))</f>
+        <v/>
+      </c>
+      <c r="T42" s="136">
+        <f>IF(AND(ISNUMBER(S42),ISNUMBER(M42)),M42*S42,"")</f>
+        <v/>
+      </c>
+      <c r="U42" s="134">
+        <f>IF(T42="","",T42/RATES!$C$172)</f>
         <v/>
       </c>
     </row>
@@ -8941,7 +9015,22 @@
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="59"/>
-    <row r="80" ht="15.75" customHeight="1" s="59"/>
+    <row r="80" ht="15.75" customHeight="1" s="59">
+      <c r="C80" s="137" t="inlineStr">
+        <is>
+          <t>METAL (hollow, per m)</t>
+        </is>
+      </c>
+      <c r="D80" s="137">
+        <f>SUM(T35:T42)</f>
+        <v/>
+      </c>
+      <c r="F80" s="137" t="inlineStr">
+        <is>
+          <t>Σ length m × IDR/m of the hollow code (RATES list)</t>
+        </is>
+      </c>
+    </row>
     <row r="81" ht="15.75" customHeight="1" s="59">
       <c r="A81" s="5" t="inlineStr">
         <is>
@@ -8961,7 +9050,7 @@
         </is>
       </c>
       <c r="D82" s="25">
-        <f>SUM(M18:M42)</f>
+        <f>SUM(M18:M32)</f>
         <v/>
       </c>
     </row>
@@ -8983,7 +9072,7 @@
         </is>
       </c>
       <c r="D84" s="19">
-        <f>SUMIF(I18:I42,"Y",N18:N42)+SUMIF(I46:I60,1,N46:N60)+2*SUMIF(I46:I60,2,N46:N60)</f>
+        <f>SUMIF(I18:I32,"Y",N18:N32)+SUMIF(I35:I42,"Y",N35:N42)+SUMIF(I46:I60,1,N46:N60)+2*SUMIF(I46:I60,2,N46:N60)</f>
         <v/>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -9021,7 +9110,7 @@
         </is>
       </c>
       <c r="D87" s="12">
-        <f>SUM(T18:T42)</f>
+        <f>SUM(T18:T32)</f>
         <v/>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -9165,8 +9254,13 @@
         </is>
       </c>
       <c r="D96" s="16">
-        <f>SUM(D87:D95)</f>
-        <v/>
+        <f>SUM(D87:D95)+D80</f>
+        <v/>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>timber + metal + fasteners + panels + finishing + hardware + packing</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="59">
@@ -9241,7 +9335,7 @@
         </is>
       </c>
       <c r="D102" s="40">
-        <f>COUNTIF(R18:R42,"?*")-COUNTIF(R18:R42,"OK")+COUNTIF(R46:R60,"?*")-COUNTIF(R46:R60,"OK")+COUNTIF(S18:S60,"rate?")</f>
+        <f>COUNTIF(R18:R32,"?*")-COUNTIF(R18:R32,"OK")+COUNTIF(R35:R42,"?*")-COUNTIF(R35:R42,"OK")+COUNTIF(R46:R60,"?*")-COUNTIF(R46:R60,"OK")+COUNTIF(S18:S60,"rate?")</f>
         <v/>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -10224,13 +10318,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="K18:K42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K18:K32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,A-CURVED,B,C,D"</formula1>
     </dataValidation>
     <dataValidation sqref="I46:I60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation sqref="C6 I18:J42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pilih dari daftar" error="Nilai di luar daftar; pilih dari dropdown agar rumus mengenalinya." type="list" errorStyle="warning">
+    <dataValidation sqref="C6 I18:J32 I35:I42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pilih dari daftar" error="Nilai di luar daftar; pilih dari dropdown agar rumus mengenalinya." type="list" errorStyle="warning">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation sqref="B64:B78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pilih dari daftar" error="Nilai di luar daftar; pilih dari dropdown agar rumus mengenalinya." type="list" errorStyle="warning">

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -21,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -29,6 +29,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="[$Rp]#,##0"/>
+    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -393,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -654,6 +655,10 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="2" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2334,12 +2339,12 @@
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>MISC + OVERHEAD</t>
+          <t>MISC 4%</t>
         </is>
       </c>
       <c r="Q4" s="8" t="inlineStr">
         <is>
-          <t>UNIT COST IDR</t>
+          <t>DIRECT COST IDR (HPP)</t>
         </is>
       </c>
       <c r="R4" s="8" t="inlineStr">
@@ -2483,11 +2488,11 @@
         <v/>
       </c>
       <c r="P6" s="12">
-        <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D97")+INDIRECT("'"&amp;$C6&amp;"'!D98"),""))</f>
+        <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q6" s="16">
-        <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J6="",$J6="no tab yet",$J6="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C6&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R6" s="12">
@@ -3221,11 +3226,11 @@
         <v/>
       </c>
       <c r="P30" s="12">
-        <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D97")+INDIRECT("'"&amp;$C30&amp;"'!D98"),""))</f>
+        <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q30" s="16">
-        <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J30="",$J30="no tab yet",$J30="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C30&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R30" s="12">
@@ -3292,11 +3297,11 @@
         <v/>
       </c>
       <c r="P31" s="12">
-        <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D97")+INDIRECT("'"&amp;$C31&amp;"'!D98"),""))</f>
+        <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q31" s="16">
-        <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J31="",$J31="no tab yet",$J31="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C31&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R31" s="12">
@@ -3363,11 +3368,11 @@
         <v/>
       </c>
       <c r="P32" s="12">
-        <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D97")+INDIRECT("'"&amp;$C32&amp;"'!D98"),""))</f>
+        <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q32" s="16">
-        <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J32="",$J32="no tab yet",$J32="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C32&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R32" s="12">
@@ -3434,11 +3439,11 @@
         <v/>
       </c>
       <c r="P33" s="12">
-        <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D97")+INDIRECT("'"&amp;$C33&amp;"'!D98"),""))</f>
+        <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q33" s="16">
-        <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J33="",$J33="no tab yet",$J33="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C33&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R33" s="12">
@@ -3505,11 +3510,11 @@
         <v/>
       </c>
       <c r="P34" s="12">
-        <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D97")+INDIRECT("'"&amp;$C34&amp;"'!D98"),""))</f>
+        <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q34" s="16">
-        <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J34="",$J34="no tab yet",$J34="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C34&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R34" s="12">
@@ -3576,11 +3581,11 @@
         <v/>
       </c>
       <c r="P35" s="12">
-        <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D97")+INDIRECT("'"&amp;$C35&amp;"'!D98"),""))</f>
+        <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q35" s="16">
-        <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J35="",$J35="no tab yet",$J35="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C35&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R35" s="12">
@@ -3647,11 +3652,11 @@
         <v/>
       </c>
       <c r="P36" s="12">
-        <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D97")+INDIRECT("'"&amp;$C36&amp;"'!D98"),""))</f>
+        <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q36" s="16">
-        <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J36="",$J36="no tab yet",$J36="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C36&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R36" s="12">
@@ -3718,11 +3723,11 @@
         <v/>
       </c>
       <c r="P37" s="12">
-        <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D97")+INDIRECT("'"&amp;$C37&amp;"'!D98"),""))</f>
+        <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q37" s="16">
-        <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J37="",$J37="no tab yet",$J37="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C37&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R37" s="12">
@@ -3789,11 +3794,11 @@
         <v/>
       </c>
       <c r="P38" s="12">
-        <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D97")+INDIRECT("'"&amp;$C38&amp;"'!D98"),""))</f>
+        <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q38" s="16">
-        <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J38="",$J38="no tab yet",$J38="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C38&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R38" s="12">
@@ -3860,11 +3865,11 @@
         <v/>
       </c>
       <c r="P39" s="12">
-        <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D97")+INDIRECT("'"&amp;$C39&amp;"'!D98"),""))</f>
+        <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q39" s="16">
-        <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J39="",$J39="no tab yet",$J39="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C39&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R39" s="12">
@@ -3931,11 +3936,11 @@
         <v/>
       </c>
       <c r="P40" s="12">
-        <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D97")+INDIRECT("'"&amp;$C40&amp;"'!D98"),""))</f>
+        <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q40" s="16">
-        <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J40="",$J40="no tab yet",$J40="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C40&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R40" s="12">
@@ -4002,11 +4007,11 @@
         <v/>
       </c>
       <c r="P41" s="12">
-        <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D97")+INDIRECT("'"&amp;$C41&amp;"'!D98"),""))</f>
+        <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q41" s="16">
-        <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J41="",$J41="no tab yet",$J41="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C41&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R41" s="12">
@@ -4073,11 +4078,11 @@
         <v/>
       </c>
       <c r="P42" s="12">
-        <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D97")+INDIRECT("'"&amp;$C42&amp;"'!D98"),""))</f>
+        <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q42" s="16">
-        <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J42="",$J42="no tab yet",$J42="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C42&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R42" s="12">
@@ -4144,11 +4149,11 @@
         <v/>
       </c>
       <c r="P43" s="12">
-        <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D97")+INDIRECT("'"&amp;$C43&amp;"'!D98"),""))</f>
+        <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q43" s="16">
-        <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J43="",$J43="no tab yet",$J43="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C43&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R43" s="12">
@@ -4215,11 +4220,11 @@
         <v/>
       </c>
       <c r="P44" s="12">
-        <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D97")+INDIRECT("'"&amp;$C44&amp;"'!D98"),""))</f>
+        <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q44" s="16">
-        <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J44="",$J44="no tab yet",$J44="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C44&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R44" s="12">
@@ -4286,11 +4291,11 @@
         <v/>
       </c>
       <c r="P45" s="12">
-        <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D97")+INDIRECT("'"&amp;$C45&amp;"'!D98"),""))</f>
+        <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q45" s="16">
-        <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J45="",$J45="no tab yet",$J45="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C45&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R45" s="12">
@@ -4357,11 +4362,11 @@
         <v/>
       </c>
       <c r="P46" s="12">
-        <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D97")+INDIRECT("'"&amp;$C46&amp;"'!D98"),""))</f>
+        <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q46" s="16">
-        <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J46="",$J46="no tab yet",$J46="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C46&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R46" s="12">
@@ -4428,11 +4433,11 @@
         <v/>
       </c>
       <c r="P47" s="12">
-        <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D97")+INDIRECT("'"&amp;$C47&amp;"'!D98"),""))</f>
+        <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q47" s="16">
-        <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J47="",$J47="no tab yet",$J47="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C47&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R47" s="12">
@@ -4499,11 +4504,11 @@
         <v/>
       </c>
       <c r="P48" s="12">
-        <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D97")+INDIRECT("'"&amp;$C48&amp;"'!D98"),""))</f>
+        <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q48" s="16">
-        <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J48="",$J48="no tab yet",$J48="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C48&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R48" s="12">
@@ -4570,11 +4575,11 @@
         <v/>
       </c>
       <c r="P49" s="12">
-        <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D97")+INDIRECT("'"&amp;$C49&amp;"'!D98"),""))</f>
+        <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q49" s="16">
-        <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J49="",$J49="no tab yet",$J49="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C49&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R49" s="12">
@@ -4641,11 +4646,11 @@
         <v/>
       </c>
       <c r="P50" s="12">
-        <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D97")+INDIRECT("'"&amp;$C50&amp;"'!D98"),""))</f>
+        <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q50" s="16">
-        <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J50="",$J50="no tab yet",$J50="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C50&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R50" s="12">
@@ -4712,11 +4717,11 @@
         <v/>
       </c>
       <c r="P51" s="12">
-        <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D97")+INDIRECT("'"&amp;$C51&amp;"'!D98"),""))</f>
+        <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q51" s="16">
-        <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J51="",$J51="no tab yet",$J51="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C51&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R51" s="12">
@@ -4783,11 +4788,11 @@
         <v/>
       </c>
       <c r="P52" s="12">
-        <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D97")+INDIRECT("'"&amp;$C52&amp;"'!D98"),""))</f>
+        <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q52" s="16">
-        <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J52="",$J52="no tab yet",$J52="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C52&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R52" s="12">
@@ -4854,11 +4859,11 @@
         <v/>
       </c>
       <c r="P53" s="12">
-        <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D97")+INDIRECT("'"&amp;$C53&amp;"'!D98"),""))</f>
+        <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D97"),""))</f>
         <v/>
       </c>
       <c r="Q53" s="16">
-        <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D99")+0,""))</f>
+        <f>IF(OR($J53="",$J53="no tab yet",$J53="tab empty"),"",IFERROR(INDIRECT("'"&amp;$C53&amp;"'!D98")+0,""))</f>
         <v/>
       </c>
       <c r="R53" s="12">
@@ -9250,23 +9255,23 @@
     <row r="96" ht="15.75" customHeight="1" s="59">
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>DIRECT COST</t>
+          <t>TOTAL COST</t>
         </is>
       </c>
       <c r="D96" s="16">
-        <f>SUM(D87:D95)+D80</f>
+        <f>SUM(D87:D95)</f>
         <v/>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>timber + metal + fasteners + panels + finishing + hardware + packing</t>
+          <t>Σ of the nine lines above</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="59">
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>MISC 5%</t>
+          <t>MISC 4%</t>
         </is>
       </c>
       <c r="D97" s="12">
@@ -9275,56 +9280,70 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>direct × MISC_PCT</t>
+          <t>total cost × MISC_PCT</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="59">
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>OVERHEAD</t>
-        </is>
-      </c>
-      <c r="D98" s="12">
-        <f>(D96+D97)*RATES!$C$55</f>
-        <v/>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>(direct + misc) × OH_PCT</t>
+          <t>DIRECT COST IDR (HPP)</t>
+        </is>
+      </c>
+      <c r="D98" s="16">
+        <f>D96+D97</f>
+        <v/>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>total cost + misc</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="59">
+      <c r="B99" s="132">
+        <f>RATES!$C$169</f>
+        <v/>
+      </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>UNIT COST IDR</t>
-        </is>
-      </c>
-      <c r="D99" s="16">
-        <f>D96+D97+D98</f>
-        <v/>
+          <t>DIRECT COST USD</t>
+        </is>
+      </c>
+      <c r="D99" s="138">
+        <f>D98/RATES!$C$169</f>
+        <v/>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>HPP ÷ FX_TARGET (IDR/USD in column B)</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="59">
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Carton board m² (6 sides)</t>
-        </is>
-      </c>
-      <c r="D100" s="19">
-        <f>L15</f>
-        <v/>
+          <t>TARGET PRICE USD</t>
+        </is>
+      </c>
+      <c r="D100" s="138">
+        <f>D99*RATES!$C$55</f>
+        <v/>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>direct cost USD × TARGET_X</t>
+        </is>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="59">
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>ORDER QTY × UNIT COST</t>
+          <t>ORDER QTY × DIRECT COST IDR</t>
         </is>
       </c>
       <c r="D101" s="16">
-        <f>IF(ISNUMBER(C4),C4,0)*D99</f>
+        <f>IF(ISNUMBER(C4),C4,0)*D98</f>
         <v/>
       </c>
     </row>
@@ -11421,7 +11440,7 @@
         </is>
       </c>
       <c r="C40" s="108" t="n">
-        <v>18057965.09</v>
+        <v>11918256.96</v>
       </c>
       <c r="D40" s="96" t="inlineStr">
         <is>
@@ -11446,7 +11465,7 @@
         </is>
       </c>
       <c r="C41" s="108" t="n">
-        <v>21620953.31</v>
+        <v>14269829.18</v>
       </c>
       <c r="D41" s="96" t="inlineStr">
         <is>
@@ -11471,7 +11490,7 @@
         </is>
       </c>
       <c r="C42" s="108" t="n">
-        <v>14818884.89</v>
+        <v>9780464.027000001</v>
       </c>
       <c r="D42" s="96" t="inlineStr">
         <is>
@@ -11496,7 +11515,7 @@
         </is>
       </c>
       <c r="C43" s="108" t="n">
-        <v>13199344.79</v>
+        <v>8711567.561000001</v>
       </c>
       <c r="D43" s="96" t="inlineStr">
         <is>
@@ -11521,7 +11540,7 @@
         </is>
       </c>
       <c r="C44" s="108" t="n">
-        <v>11579804.69</v>
+        <v>7642671.095</v>
       </c>
       <c r="D44" s="96" t="inlineStr">
         <is>
@@ -11787,7 +11806,7 @@
         </is>
       </c>
       <c r="C54" s="106" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D54" s="96" t="inlineStr">
         <is>
@@ -11796,7 +11815,7 @@
       </c>
       <c r="E54" s="96" t="inlineStr">
         <is>
-          <t>Decision 29 Sep</t>
+          <t>Rizky 23 Okt 2026: 4% of TOTAL COST (was 5%)</t>
         </is>
       </c>
       <c r="F54" s="95" t="n"/>
@@ -11807,26 +11826,25 @@
     <row r="55">
       <c r="A55" s="102" t="inlineStr">
         <is>
-          <t>OH_PCT</t>
+          <t>TARGET_X</t>
         </is>
       </c>
       <c r="B55" s="103" t="inlineStr">
         <is>
-          <t>Overhead, × (direct + misc)</t>
-        </is>
-      </c>
-      <c r="C55" s="110">
-        <f>$C$26/$C$27</f>
-        <v/>
+          <t>Target price = DIRECT COST in USD x this factor</t>
+        </is>
+      </c>
+      <c r="C55" s="139" t="n">
+        <v>1.5</v>
       </c>
       <c r="D55" s="96" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E55" s="96" t="inlineStr">
         <is>
-          <t>Overhead pool ÷ STMV direct cost</t>
+          <t>Rizky 23 Okt 2026 (replaces OH_PCT, deleted). Blue = input</t>
         </is>
       </c>
       <c r="F55" s="95" t="n"/>
@@ -14737,7 +14755,33 @@
       <c r="H168" s="95" t="n"/>
       <c r="I168" s="95" t="n"/>
     </row>
-    <row r="169"/>
+    <row r="169">
+      <c r="A169" s="113" t="inlineStr">
+        <is>
+          <t>FX_TARGET</t>
+        </is>
+      </c>
+      <c r="B169" s="117" t="inlineStr">
+        <is>
+          <t>USD rate for the summary USD lines, ITEMS USD columns and target price</t>
+        </is>
+      </c>
+      <c r="C169" s="114" t="n">
+        <v>17800</v>
+      </c>
+      <c r="D169" s="113" t="inlineStr">
+        <is>
+          <t>IDR/USD</t>
+        </is>
+      </c>
+      <c r="E169" s="113" t="inlineStr">
+        <is>
+          <t>Rizky 23 Okt 2026. Hardware/board quotes still use FX_USD (row 172)</t>
+        </is>
+      </c>
+      <c r="F169" s="95" t="n"/>
+      <c r="G169" s="95" t="n"/>
+    </row>
     <row r="170">
       <c r="A170" s="97" t="inlineStr">
         <is>
@@ -14948,7 +14992,6 @@
       <c r="H176" s="95" t="n"/>
       <c r="I176" s="95" t="n"/>
     </row>
-    <row r="177"/>
     <row r="178">
       <c r="A178" s="119" t="inlineStr">
         <is>
@@ -16469,7 +16512,6 @@
         <v>933</v>
       </c>
     </row>
-    <row r="216"/>
     <row r="217">
       <c r="A217" s="97" t="inlineStr">
         <is>
@@ -16773,7 +16815,6 @@
       <c r="H225" s="95" t="n"/>
       <c r="I225" s="95" t="n"/>
     </row>
-    <row r="226"/>
     <row r="227">
       <c r="A227" s="97" t="inlineStr">
         <is>
@@ -16867,7 +16908,6 @@
       <c r="H229" s="95" t="n"/>
       <c r="I229" s="95" t="n"/>
     </row>
-    <row r="230"/>
     <row r="231">
       <c r="A231" s="127" t="inlineStr">
         <is>
@@ -17351,7 +17391,6 @@
       <c r="H249" s="95" t="n"/>
       <c r="I249" s="95" t="n"/>
     </row>
-    <row r="250"/>
     <row r="251">
       <c r="A251" s="127" t="inlineStr">
         <is>
@@ -36929,6 +36968,11 @@
           <t>SUMMARY (system): cost per ONE item, from the RATES tab. Do not type here.</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>COST USD (system)</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="59">
       <c r="C82" s="5" t="inlineStr">
@@ -37137,18 +37181,23 @@
     <row r="96" ht="15.75" customHeight="1" s="59">
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>DIRECT COST</t>
+          <t>TOTAL COST</t>
         </is>
       </c>
       <c r="D96" s="16">
         <f>SUM(D87:D95)</f>
         <v/>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Σ of the nine lines above</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="59">
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>MISC 5%</t>
+          <t>MISC 4%</t>
         </is>
       </c>
       <c r="D97" s="12">
@@ -37157,56 +37206,70 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>direct × MISC_PCT</t>
+          <t>total cost × MISC_PCT</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="59">
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>OVERHEAD</t>
-        </is>
-      </c>
-      <c r="D98" s="12">
-        <f>(D96+D97)*RATES!$C$55</f>
-        <v/>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>(direct + misc) × OH_PCT</t>
+          <t>DIRECT COST IDR (HPP)</t>
+        </is>
+      </c>
+      <c r="D98" s="16">
+        <f>D96+D97</f>
+        <v/>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>total cost + misc</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="59">
+      <c r="B99" s="132">
+        <f>RATES!$C$169</f>
+        <v/>
+      </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>UNIT COST IDR</t>
-        </is>
-      </c>
-      <c r="D99" s="16">
-        <f>D96+D97+D98</f>
-        <v/>
+          <t>DIRECT COST USD</t>
+        </is>
+      </c>
+      <c r="D99" s="138">
+        <f>D98/RATES!$C$169</f>
+        <v/>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>HPP ÷ FX_TARGET (IDR/USD in column B)</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="59">
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Carton board m² (6 sides)</t>
-        </is>
-      </c>
-      <c r="D100" s="19">
-        <f>L15</f>
-        <v/>
+          <t>TARGET PRICE USD</t>
+        </is>
+      </c>
+      <c r="D100" s="138">
+        <f>D99*RATES!$C$55</f>
+        <v/>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>direct cost USD × TARGET_X</t>
+        </is>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="59">
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>ORDER QTY × UNIT COST</t>
+          <t>ORDER QTY × DIRECT COST IDR</t>
         </is>
       </c>
       <c r="D101" s="16">
-        <f>IF(ISNUMBER(C4),C4,0)*D99</f>
+        <f>IF(ISNUMBER(C4),C4,0)*D98</f>
         <v/>
       </c>
     </row>

--- a/data/GOLDEN_MASTER.xlsx
+++ b/data/GOLDEN_MASTER.xlsx
@@ -9339,7 +9339,7 @@
     <row r="101" ht="15.75" customHeight="1" s="59">
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>ORDER QTY × DIRECT COST IDR</t>
+          <t>ORDER QTY × HPP IDR</t>
         </is>
       </c>
       <c r="D101" s="16">
@@ -37265,7 +37265,7 @@
     <row r="101" ht="15.75" customHeight="1" s="59">
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>ORDER QTY × DIRECT COST IDR</t>
+          <t>ORDER QTY × HPP IDR</t>
         </is>
       </c>
       <c r="D101" s="16">
